--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -188,108 +188,108 @@
     <t>bethnal green and stepney</t>
   </si>
   <si>
+    <t>E14001086</t>
+  </si>
+  <si>
+    <t>beverley and holderness</t>
+  </si>
+  <si>
+    <t>E14001087</t>
+  </si>
+  <si>
+    <t>bexhill and battle</t>
+  </si>
+  <si>
+    <t>E14001088</t>
+  </si>
+  <si>
+    <t>bexleyheath and crayford</t>
+  </si>
+  <si>
+    <t>E14001089</t>
+  </si>
+  <si>
+    <t>bicester and woodstock</t>
+  </si>
+  <si>
+    <t>E14001090</t>
+  </si>
+  <si>
+    <t>birkenhead</t>
+  </si>
+  <si>
+    <t>E14001091</t>
+  </si>
+  <si>
+    <t>birmingham edgbaston</t>
+  </si>
+  <si>
+    <t>E14001092</t>
+  </si>
+  <si>
+    <t>birmingham erdington</t>
+  </si>
+  <si>
+    <t>E14001093</t>
+  </si>
+  <si>
+    <t>birmingham hall green and moseley</t>
+  </si>
+  <si>
+    <t>E14001094</t>
+  </si>
+  <si>
+    <t>birmingham hodge hill and solihull north</t>
+  </si>
+  <si>
+    <t>E14001095</t>
+  </si>
+  <si>
+    <t>birmingham ladywood</t>
+  </si>
+  <si>
+    <t>E14001096</t>
+  </si>
+  <si>
+    <t>birmingham northfield</t>
+  </si>
+  <si>
     <t>Green Party</t>
   </si>
   <si>
-    <t>E14001086</t>
-  </si>
-  <si>
-    <t>beverley and holderness</t>
-  </si>
-  <si>
-    <t>E14001087</t>
-  </si>
-  <si>
-    <t>bexhill and battle</t>
-  </si>
-  <si>
-    <t>E14001088</t>
-  </si>
-  <si>
-    <t>bexleyheath and crayford</t>
-  </si>
-  <si>
-    <t>E14001089</t>
-  </si>
-  <si>
-    <t>bicester and woodstock</t>
-  </si>
-  <si>
-    <t>E14001090</t>
-  </si>
-  <si>
-    <t>birkenhead</t>
-  </si>
-  <si>
-    <t>E14001091</t>
-  </si>
-  <si>
-    <t>birmingham edgbaston</t>
-  </si>
-  <si>
-    <t>E14001092</t>
-  </si>
-  <si>
-    <t>birmingham erdington</t>
-  </si>
-  <si>
-    <t>E14001093</t>
-  </si>
-  <si>
-    <t>birmingham hall green and moseley</t>
+    <t>E14001097</t>
+  </si>
+  <si>
+    <t>birmingham perry barr</t>
+  </si>
+  <si>
+    <t>E14001098</t>
+  </si>
+  <si>
+    <t>birmingham selly oak</t>
+  </si>
+  <si>
+    <t>E14001099</t>
+  </si>
+  <si>
+    <t>birmingham yardley</t>
+  </si>
+  <si>
+    <t>E14001100</t>
+  </si>
+  <si>
+    <t>bishop auckland</t>
+  </si>
+  <si>
+    <t>E14001101</t>
+  </si>
+  <si>
+    <t>blackburn</t>
   </si>
   <si>
     <t>Other</t>
   </si>
   <si>
-    <t>E14001094</t>
-  </si>
-  <si>
-    <t>birmingham hodge hill and solihull north</t>
-  </si>
-  <si>
-    <t>E14001095</t>
-  </si>
-  <si>
-    <t>birmingham ladywood</t>
-  </si>
-  <si>
-    <t>E14001096</t>
-  </si>
-  <si>
-    <t>birmingham northfield</t>
-  </si>
-  <si>
-    <t>E14001097</t>
-  </si>
-  <si>
-    <t>birmingham perry barr</t>
-  </si>
-  <si>
-    <t>E14001098</t>
-  </si>
-  <si>
-    <t>birmingham selly oak</t>
-  </si>
-  <si>
-    <t>E14001099</t>
-  </si>
-  <si>
-    <t>birmingham yardley</t>
-  </si>
-  <si>
-    <t>E14001100</t>
-  </si>
-  <si>
-    <t>bishop auckland</t>
-  </si>
-  <si>
-    <t>E14001101</t>
-  </si>
-  <si>
-    <t>blackburn</t>
-  </si>
-  <si>
     <t>E14001102</t>
   </si>
   <si>
@@ -3794,28 +3794,28 @@
     <t>aberafan maesteg</t>
   </si>
   <si>
+    <t>Wales</t>
+  </si>
+  <si>
+    <t>W07000081</t>
+  </si>
+  <si>
+    <t>alyn and deeside</t>
+  </si>
+  <si>
+    <t>W07000082</t>
+  </si>
+  <si>
+    <t>bangor aberconwy</t>
+  </si>
+  <si>
+    <t>W07000083</t>
+  </si>
+  <si>
+    <t>blaenau gwent and rhymney</t>
+  </si>
+  <si>
     <t>Plaid Cymru</t>
-  </si>
-  <si>
-    <t>Wales</t>
-  </si>
-  <si>
-    <t>W07000081</t>
-  </si>
-  <si>
-    <t>alyn and deeside</t>
-  </si>
-  <si>
-    <t>W07000082</t>
-  </si>
-  <si>
-    <t>bangor aberconwy</t>
-  </si>
-  <si>
-    <t>W07000083</t>
-  </si>
-  <si>
-    <t>blaenau gwent and rhymney</t>
   </si>
   <si>
     <t>W07000084</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.316350785394942</v>
+        <v>0.2743444238476875</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3506053825489492</v>
+        <v>0.4306257315310673</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4391,10 +4391,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3274160608013169</v>
+        <v>0.373494124041068</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3885622903176738</v>
+        <v>0.3628350310946563</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.2713414115077503</v>
+        <v>0.3981919005891298</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>0.3475541363123775</v>
+        <v>0.288756374381785</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3836217923570994</v>
+        <v>0.3704416954380614</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4476,10 +4476,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3839149541080739</v>
+        <v>0.3489600248924803</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3824539558354068</v>
+        <v>0.3488926235782247</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4510,10 +4510,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>0.3130618110653728</v>
+        <v>0.2592917531370745</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4339284735556221</v>
+        <v>0.420396247153849</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.4148250955942566</v>
+        <v>0.331350451680347</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.4612699514905743</v>
+        <v>0.4376222424814795</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>0.2979077142874187</v>
+        <v>0.358822867810817</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.2862967097672173</v>
+        <v>0.2960141810973982</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2741559695875622</v>
+        <v>0.2799300224866167</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4629,10 +4629,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>0.316974293706087</v>
+        <v>0.2990320534284463</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.3808236011326893</v>
+        <v>0.4395706191880912</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3808215008039953</v>
+        <v>0.4289788063058347</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3885533505439849</v>
+        <v>0.4362543298434937</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3653783939308851</v>
+        <v>0.3315892761078534</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4714,10 +4714,10 @@
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3429692425028381</v>
+        <v>0.3992717543703808</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4731,10 +4731,10 @@
         <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>0.4187257054254516</v>
+        <v>0.3617409043902401</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4748,282 +4748,282 @@
         <v>56</v>
       </c>
       <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>0.6451364534577115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
         <v>57</v>
-      </c>
-      <c r="C25">
-        <v>0.3973450367732351</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>0.310625971837748</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
         <v>59</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26">
-        <v>0.285501084631829</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.3197850680449864</v>
+        <v>0.2872011873757053</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3502646416735276</v>
+        <v>0.3219530658013316</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4760574518828478</v>
+        <v>0.4792689177560632</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>0.3868608482301406</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30">
-        <v>0.3203097815203277</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>0.4261490112537247</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
         <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>0.4239180657150456</v>
-      </c>
-      <c r="D31" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4706271750938808</v>
+        <v>0.4285784189418017</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>0.3964205475865312</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
         <v>73</v>
-      </c>
-      <c r="B33" t="s">
-        <v>74</v>
-      </c>
-      <c r="C33">
-        <v>0.3727703557661501</v>
-      </c>
-      <c r="D33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3373028924481469</v>
+        <v>0.339615188084268</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4178780825973589</v>
+        <v>0.4882366263833827</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36">
+        <v>0.2289664496481518</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" t="s">
         <v>80</v>
-      </c>
-      <c r="B36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36">
-        <v>0.2630072944824936</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
+        <v>81</v>
+      </c>
+      <c r="B37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37">
+        <v>0.3069074787993796</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
         <v>82</v>
-      </c>
-      <c r="B37" t="s">
-        <v>57</v>
-      </c>
-      <c r="C37">
-        <v>0.284254071285075</v>
-      </c>
-      <c r="D37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>0.3469283668127385</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s">
         <v>84</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38">
-        <v>0.2827517651275357</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.4188618350136816</v>
+        <v>0.374704157142648</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0.4620618260676042</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
         <v>88</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>0.4584902117804512</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
         <v>90</v>
       </c>
-      <c r="B41" t="s">
-        <v>74</v>
-      </c>
       <c r="C41">
-        <v>0.4455701348714</v>
+        <v>0.2721288066982321</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.4542506980283002</v>
+        <v>0.5476223114334171</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3726282830858654</v>
+        <v>0.4110831855074111</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4805609665111659</v>
+        <v>0.4167067244624789</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3796740156182514</v>
+        <v>0.401540474342546</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5105,10 +5105,10 @@
         <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C46">
-        <v>0.3108844060809482</v>
+        <v>0.4369714045974112</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.3480125270298432</v>
+        <v>0.2951391246925901</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4594828401989216</v>
+        <v>0.428975461745873</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.4951788450265723</v>
+        <v>0.3484875365028581</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5173,10 +5173,10 @@
         <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3531131402011599</v>
+        <v>0.3896756533676329</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5190,10 +5190,10 @@
         <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C51">
-        <v>0.323354181733407</v>
+        <v>0.3684724416934421</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5427859245134361</v>
+        <v>0.5326253927344151</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5224,10 +5224,10 @@
         <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4130512130669287</v>
+        <v>0.4448334497955047</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.34118085134502</v>
+        <v>0.3960441600488505</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5258,10 +5258,10 @@
         <v>118</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2978743396430074</v>
+        <v>0.2906101140192583</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3213454958393421</v>
+        <v>0.359377709199482</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5375034221986559</v>
+        <v>0.5866865374405409</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>15</v>
       </c>
       <c r="C58">
-        <v>0.3617812978196643</v>
+        <v>0.3387049529650369</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.6726785830761239</v>
+        <v>0.418040944778058</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5343,10 +5343,10 @@
         <v>128</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3058101956231619</v>
+        <v>0.2802636851558155</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.4459794433732649</v>
+        <v>0.3465987220348992</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5377,10 +5377,10 @@
         <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>0.4195223282118365</v>
+        <v>0.3554827409459266</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5394,10 +5394,10 @@
         <v>134</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3110067785053684</v>
+        <v>0.377822842625364</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5411,10 +5411,10 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C64">
-        <v>0.317597837956376</v>
+        <v>0.2411085964039868</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3360535528337216</v>
+        <v>0.3380481255559311</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5448,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3779212442405824</v>
+        <v>0.3326191692625839</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.2625652437441524</v>
+        <v>0.3670901745753551</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.3534028677262354</v>
+        <v>0.2662243770271415</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5496,10 +5496,10 @@
         <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C69">
-        <v>0.5079820859072748</v>
+        <v>0.5752178585727976</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5513,10 +5513,10 @@
         <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C70">
-        <v>0.4814655945153792</v>
+        <v>0.5139168238589952</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5530,10 +5530,10 @@
         <v>150</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4687989404614262</v>
+        <v>0.5105534951542032</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3285000646029586</v>
+        <v>0.3741996669766918</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.6236999611151678</v>
+        <v>0.545060761004782</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4237262814988386</v>
+        <v>0.4999662791352072</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5598,10 +5598,10 @@
         <v>158</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2773390144046763</v>
+        <v>0.2566796673355865</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3013217449014938</v>
+        <v>0.3861670199087062</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5632,10 +5632,10 @@
         <v>162</v>
       </c>
       <c r="B77" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C77">
-        <v>0.249493288291045</v>
+        <v>0.3507708557075714</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4134842371363205</v>
+        <v>0.4321583143919466</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>0.2663666384010577</v>
+        <v>0.2536855763458504</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3002919062810917</v>
+        <v>0.3780323775834545</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.3848080339871208</v>
+        <v>0.3250940696668205</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4653557164267351</v>
+        <v>0.4345841003048698</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.4728617223063263</v>
+        <v>0.3996691271634397</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>15</v>
       </c>
       <c r="C84">
-        <v>0.2535189726290397</v>
+        <v>0.3039098653722838</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3489215081403085</v>
+        <v>0.3511342050494848</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3018328345921447</v>
+        <v>0.2942281260880815</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5802,10 +5802,10 @@
         <v>182</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C87">
-        <v>0.309730426785432</v>
+        <v>0.2654540862652238</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5819,10 +5819,10 @@
         <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C88">
-        <v>0.3679149896410964</v>
+        <v>0.3175290193067311</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3736053234820912</v>
+        <v>0.3091833187353051</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.318995887840612</v>
+        <v>0.2941001741876766</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>15</v>
       </c>
       <c r="C91">
-        <v>0.2913572018752582</v>
+        <v>0.2707349989006477</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.4400768052875699</v>
+        <v>0.3390803863832717</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.6383968519862481</v>
+        <v>0.4067607070222479</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.2323921319889963</v>
+        <v>0.2681426861307242</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5938,10 +5938,10 @@
         <v>198</v>
       </c>
       <c r="B95" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3267149325165826</v>
+        <v>0.3313015334207891</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5955,10 +5955,10 @@
         <v>200</v>
       </c>
       <c r="B96" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3794414310247461</v>
+        <v>0.3916184379003206</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3648724108897022</v>
+        <v>0.3636423743697733</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.4216126864457175</v>
+        <v>0.3674296938775312</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4389487963543141</v>
+        <v>0.4408367175454333</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6023,10 +6023,10 @@
         <v>208</v>
       </c>
       <c r="B100" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3885313855526709</v>
+        <v>0.4035193228528987</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.475416725394474</v>
+        <v>0.4567652865107409</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4093583116458546</v>
+        <v>0.4613246281683068</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.4403865028276475</v>
+        <v>0.350512790711995</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3773130853141128</v>
+        <v>0.3704359969894747</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.417624372957094</v>
+        <v>0.3496659789409031</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.333256472701059</v>
+        <v>0.4111007953503558</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.4271099846068673</v>
+        <v>0.3509383947208228</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6159,10 +6159,10 @@
         <v>224</v>
       </c>
       <c r="B108" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4530834704413474</v>
+        <v>0.4065108007481238</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6176,10 +6176,10 @@
         <v>226</v>
       </c>
       <c r="B109" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C109">
-        <v>0.371621804259199</v>
+        <v>0.2649498884738904</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.3794990433702201</v>
+        <v>0.2945735820979558</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4705814875574499</v>
+        <v>0.5353796735510493</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.347452739861815</v>
+        <v>0.3905223239457118</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.5493074348049346</v>
+        <v>0.5285800306227033</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.473206881174094</v>
+        <v>0.6859572483384525</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.4008143715667125</v>
+        <v>0.3139025483315097</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4384105985447858</v>
+        <v>0.4426836698890262</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="C117">
-        <v>0.362851625715421</v>
+        <v>0.2761325587972868</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6329,10 +6329,10 @@
         <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C118">
-        <v>0.365294298749748</v>
+        <v>0.4078913507053042</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3362395891590449</v>
+        <v>0.3763142611007187</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.508345609893369</v>
+        <v>0.3740157215264653</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.4947014524837794</v>
+        <v>0.3189678581175269</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.2840372114595891</v>
+        <v>0.3546441343707352</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.3294834537888663</v>
+        <v>0.3020082664986499</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.351817469254404</v>
+        <v>0.3915947795650886</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>0.2970587175967553</v>
+        <v>0.2880372858423364</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.538727015433314</v>
+        <v>0.3805236719469925</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4770749305360535</v>
+        <v>0.5089749539855166</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.451354788760142</v>
+        <v>0.4504933725224523</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C129">
-        <v>0.2934419529567258</v>
+        <v>0.3023225262410847</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.4170462287022464</v>
+        <v>0.4644546663652233</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.3577734384944085</v>
+        <v>0.2830431694334888</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3758987017116162</v>
+        <v>0.3645834761611966</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.4911206862521967</v>
+        <v>0.3527482372664351</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.4101060834873549</v>
+        <v>0.3180921283532087</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3406289825720688</v>
+        <v>0.3552984565744476</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.2661623688814963</v>
+        <v>0.3531851695055268</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3806067929421142</v>
+        <v>0.3992815295665175</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6669,10 +6669,10 @@
         <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C138">
-        <v>0.364245189406897</v>
+        <v>0.3227998878422417</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4011094767728716</v>
+        <v>0.4427156640453834</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.4987675823069326</v>
+        <v>0.4056683410752389</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3408089829551237</v>
+        <v>0.3464714192787845</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.2996703122348711</v>
+        <v>0.4059302073110285</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>15</v>
       </c>
       <c r="C143">
-        <v>0.4715264632191067</v>
+        <v>0.3121103410919873</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.4792904465499764</v>
+        <v>0.5876306152288507</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.254596386584923</v>
+        <v>0.2698367060463446</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.5504748286770732</v>
+        <v>0.4436468803715153</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4299493943555019</v>
+        <v>0.4430331727848163</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3221119615632319</v>
+        <v>0.3410568608326927</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6856,10 +6856,10 @@
         <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C149">
-        <v>0.4169957425310582</v>
+        <v>0.3934490642266766</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6873,10 +6873,10 @@
         <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3778232765083684</v>
+        <v>0.3507126082059528</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6890,10 +6890,10 @@
         <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2170797015712606</v>
+        <v>0.2554218915426055</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.5350750940464969</v>
+        <v>0.7114191000189132</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3255526150663647</v>
+        <v>0.3501963425533418</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="C154">
-        <v>0.3358123223848263</v>
+        <v>0.3407134977412515</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="C155">
-        <v>0.3013090226232087</v>
+        <v>0.2854371134548503</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6975,10 +6975,10 @@
         <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3441791975829186</v>
+        <v>0.3539525694085282</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6992,10 +6992,10 @@
         <v>322</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3856687248445346</v>
+        <v>0.3625942292439459</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.4065616047500487</v>
+        <v>0.3798322416946763</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3759797807192213</v>
+        <v>0.4019867013544833</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3696049173106342</v>
+        <v>0.4053565284969917</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.359893787641196</v>
+        <v>0.3719536093618472</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5243434114052826</v>
+        <v>0.5725432951507149</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4239467951983913</v>
+        <v>0.4744984356189673</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7111,10 +7111,10 @@
         <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C164">
-        <v>0.2918895286669715</v>
+        <v>0.3050193227252472</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.4157663413045199</v>
+        <v>0.3650739699344572</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C166">
-        <v>0.3690547466324342</v>
+        <v>0.3470995012544706</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.4762575097416735</v>
+        <v>0.3544724057355421</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5282007463661706</v>
+        <v>0.614115150250741</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7196,10 +7196,10 @@
         <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C169">
-        <v>0.4490455529146484</v>
+        <v>0.368090560040471</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7213,10 +7213,10 @@
         <v>348</v>
       </c>
       <c r="B170" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C170">
-        <v>0.285284634028278</v>
+        <v>0.3705491472245697</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>44</v>
       </c>
       <c r="C171">
-        <v>0.2611140005460192</v>
+        <v>0.2636412962725487</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.2868046060760976</v>
+        <v>0.4507377688796738</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7264,10 +7264,10 @@
         <v>354</v>
       </c>
       <c r="B173" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3245692410270193</v>
+        <v>0.3610347389161275</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3587860306990842</v>
+        <v>0.3081199017600114</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.323047393177077</v>
+        <v>0.3361432062887905</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.2691420423299638</v>
+        <v>0.4076225954532831</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5372389899629637</v>
+        <v>0.575313154034593</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.398567274544371</v>
+        <v>0.4206166336705622</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7366,10 +7366,10 @@
         <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C179">
-        <v>0.288335681498431</v>
+        <v>0.3219155427982095</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.4028564538018126</v>
+        <v>0.3860290995248083</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.2846899897931296</v>
+        <v>0.3343575362767849</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.4473671598857214</v>
+        <v>0.3149893672484506</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.305228489355711</v>
+        <v>0.3228210668523822</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.39664040412151</v>
+        <v>0.3375247279803752</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>15</v>
       </c>
       <c r="C185">
-        <v>0.4348248919404306</v>
+        <v>0.3493140845936578</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4176764062581963</v>
+        <v>0.4322765039583277</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C187">
-        <v>0.3575681968954388</v>
+        <v>0.2413737410871</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4603765171184246</v>
+        <v>0.4859491608544575</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7536,10 +7536,10 @@
         <v>386</v>
       </c>
       <c r="B189" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3983872435225704</v>
+        <v>0.3438749075360664</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C190">
-        <v>0.3410621695141173</v>
+        <v>0.2785476024702784</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3640614590456545</v>
+        <v>0.3624031903689905</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4469180241045319</v>
+        <v>0.4356359928017999</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.5066321300364638</v>
+        <v>0.4739236572872539</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7621,10 +7621,10 @@
         <v>396</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C194">
-        <v>0.4716941345491761</v>
+        <v>0.3557742961409078</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7638,10 +7638,10 @@
         <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="C195">
-        <v>0.5116592367358882</v>
+        <v>0.3635426152846116</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.4087771271720285</v>
+        <v>0.3414954242128251</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7672,10 +7672,10 @@
         <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C197">
-        <v>0.403430183054763</v>
+        <v>0.3266679327406622</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.6608599638059425</v>
+        <v>0.5623044250432531</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.5210799110215514</v>
+        <v>0.6125430051275563</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C200">
-        <v>0.376262891028586</v>
+        <v>0.3387073719857271</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.4352163310789412</v>
+        <v>0.3457962986129706</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3073474599598061</v>
+        <v>0.3743517246921917</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.3266844057198133</v>
+        <v>0.5429971199338652</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7791,10 +7791,10 @@
         <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C204">
-        <v>0.2569429680195952</v>
+        <v>0.5186862375199359</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.3862729295064393</v>
+        <v>0.4508976631949783</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.4028284562619518</v>
+        <v>0.3782220559035051</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.462147605499012</v>
+        <v>0.5539401568102398</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.4104916256072946</v>
+        <v>0.4102780853458416</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5119340498339588</v>
+        <v>0.5413927187876494</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4342830044767902</v>
+        <v>0.4534345217955247</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.5271695434872081</v>
+        <v>0.439416666741628</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C212">
-        <v>0.3096695339468054</v>
+        <v>0.2881211563689072</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3855040322998441</v>
+        <v>0.3691045762980391</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.4137435437819707</v>
+        <v>0.3751914000070358</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5980827015688588</v>
+        <v>0.6266573508386495</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7995,10 +7995,10 @@
         <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3814621143830731</v>
+        <v>0.3377949474695567</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3619003638783752</v>
+        <v>0.3286159680771591</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8029,10 +8029,10 @@
         <v>444</v>
       </c>
       <c r="B218" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C218">
-        <v>0.4973312586046847</v>
+        <v>0.3741361653400642</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4727983675990594</v>
+        <v>0.4855048758879948</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C220">
-        <v>0.3085317189843124</v>
+        <v>0.3039043475760219</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8080,10 +8080,10 @@
         <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3255280530388726</v>
+        <v>0.3668190301943769</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C222">
-        <v>0.3680627573347163</v>
+        <v>0.3039675129177595</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.3948233621779556</v>
+        <v>0.559145004915129</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8131,10 +8131,10 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3137694260111725</v>
+        <v>0.3828430335216658</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8148,10 +8148,10 @@
         <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3589203651329897</v>
+        <v>0.3733838150041052</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4176460419883185</v>
+        <v>0.4959513437609812</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3962942905560115</v>
+        <v>0.3574968832743508</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.5011602086826974</v>
+        <v>0.4816183600183679</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5651343029158862</v>
+        <v>0.5367738379176054</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.340031134655193</v>
+        <v>0.3785288301989626</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8250,10 +8250,10 @@
         <v>470</v>
       </c>
       <c r="B231" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C231">
-        <v>0.4084639420792352</v>
+        <v>0.3069538930674262</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5385967862122777</v>
+        <v>0.6497386231481003</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4446278880133379</v>
+        <v>0.468236039387981</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8301,10 +8301,10 @@
         <v>476</v>
       </c>
       <c r="B234" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C234">
-        <v>0.3981125068024319</v>
+        <v>0.4104949323252272</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4820766261819324</v>
+        <v>0.5393772623810018</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8335,10 +8335,10 @@
         <v>480</v>
       </c>
       <c r="B236" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2666651658670983</v>
+        <v>0.2612702022392781</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3107838602140152</v>
+        <v>0.3543692429051519</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8369,10 +8369,10 @@
         <v>484</v>
       </c>
       <c r="B238" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3129943459374555</v>
+        <v>0.3222078940091243</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8386,10 +8386,10 @@
         <v>486</v>
       </c>
       <c r="B239" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C239">
-        <v>0.2651745230026338</v>
+        <v>0.4077159947115215</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8403,10 +8403,10 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C240">
-        <v>0.3478401987950409</v>
+        <v>0.3721774718566679</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>6</v>
       </c>
       <c r="C241">
-        <v>0.3399937577388623</v>
+        <v>0.2433747260458472</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>15</v>
       </c>
       <c r="C242">
-        <v>0.3001268268092488</v>
+        <v>0.3066572761382347</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.427752672292946</v>
+        <v>0.467528112104981</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8471,10 +8471,10 @@
         <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C244">
-        <v>0.4614673290078119</v>
+        <v>0.3659217696377142</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.7226077255966272</v>
+        <v>0.6713804484255201</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8505,10 +8505,10 @@
         <v>500</v>
       </c>
       <c r="B246" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C246">
-        <v>0.3694185156472615</v>
+        <v>0.4619845478485745</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4691182717903514</v>
+        <v>0.4460376994763179</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3710557995031346</v>
+        <v>0.376431345408876</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4324355346819376</v>
+        <v>0.4769308951287688</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.4324873131254978</v>
+        <v>0.3797564451442427</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.534373923846325</v>
+        <v>0.4917488824495321</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.349479977612212</v>
+        <v>0.4621345194059519</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.4250587331934396</v>
+        <v>0.3672623700275011</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.5225074294070798</v>
+        <v>0.4745440679804606</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4590875031324584</v>
+        <v>0.4467230938139757</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.3718016601013951</v>
+        <v>0.5808962699141962</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4677602837855972</v>
+        <v>0.3972305702805617</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.5530754287884769</v>
+        <v>0.5401195914597928</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3657122858110103</v>
+        <v>0.3187354885186393</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4318289016194459</v>
+        <v>0.4082505245598554</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4093628933027214</v>
+        <v>0.4343187889360684</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8777,10 +8777,10 @@
         <v>532</v>
       </c>
       <c r="B262" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3922355536445638</v>
+        <v>0.4248047082751661</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4232604675589435</v>
+        <v>0.4914265973220349</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.5040298145290514</v>
+        <v>0.4195553335894438</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3124841753413151</v>
+        <v>0.3201101819094134</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="C266">
-        <v>0.3740090946827731</v>
+        <v>0.3360797308459521</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
         <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2371076788229894</v>
+        <v>0.2876181657059387</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8879,10 +8879,10 @@
         <v>544</v>
       </c>
       <c r="B268" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C268">
-        <v>0.3945798302897766</v>
+        <v>0.4586770186223819</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.5566148552506475</v>
+        <v>0.3777765555733613</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5504477662154521</v>
+        <v>0.5510074061370909</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5461261843991059</v>
+        <v>0.5752194339335136</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.336788895220286</v>
+        <v>0.3393085749834798</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.4288144348506044</v>
+        <v>0.5484497548144663</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3404406960057493</v>
+        <v>0.3566305204150331</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C275">
-        <v>0.3188658739748532</v>
+        <v>0.2602235164734286</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.4287941711585449</v>
+        <v>0.3356125217906785</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>6</v>
       </c>
       <c r="C277">
-        <v>0.4447750347597811</v>
+        <v>0.3833036982855891</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.6428597578013655</v>
+        <v>0.4511810914535584</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.4730392035836319</v>
+        <v>0.5819364180795003</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.5474175468873622</v>
+        <v>0.4698542271897259</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9100,10 +9100,10 @@
         <v>570</v>
       </c>
       <c r="B281" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3875420734795574</v>
+        <v>0.3703746920095099</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3271174890834872</v>
+        <v>0.3789099141469114</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9134,10 +9134,10 @@
         <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3526649998356546</v>
+        <v>0.39274494688999</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9151,10 +9151,10 @@
         <v>576</v>
       </c>
       <c r="B284" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3846480354376433</v>
+        <v>0.3263026243309614</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.3407052885776497</v>
+        <v>0.2933204873692673</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.4364846141169154</v>
+        <v>0.3133903807423313</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9202,10 +9202,10 @@
         <v>582</v>
       </c>
       <c r="B287" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4178219639498749</v>
+        <v>0.5020866422744739</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>15</v>
       </c>
       <c r="C288">
-        <v>0.3200893000371269</v>
+        <v>0.2518567574199793</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9236,10 +9236,10 @@
         <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C289">
-        <v>0.4497735523769872</v>
+        <v>0.3692506217142567</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3924383408462104</v>
+        <v>0.3857685525049637</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9270,10 +9270,10 @@
         <v>590</v>
       </c>
       <c r="B291" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C291">
-        <v>0.339223260719778</v>
+        <v>0.479888109000133</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C292">
-        <v>0.5832170910480158</v>
+        <v>0.4370979051100437</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.4586524322856672</v>
+        <v>0.6394420513558626</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.398645416958825</v>
+        <v>0.4152711526580308</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.411245137937143</v>
+        <v>0.3767584980418999</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.4998863460985885</v>
+        <v>0.2807865678957987</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.466169982202717</v>
+        <v>0.5165195832041586</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.426300133263804</v>
+        <v>0.3996531629557994</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.3031473446410002</v>
+        <v>0.3217930581193317</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3621923616863917</v>
+        <v>0.3588216202846792</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3300240610166729</v>
+        <v>0.3651607757176786</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.4970557266285839</v>
+        <v>0.5140415001731807</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3562574243435672</v>
+        <v>0.341016039496665</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C304">
-        <v>0.3641009400825236</v>
+        <v>0.2862679774029669</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4172419760516067</v>
+        <v>0.4642279452496298</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4206674112416655</v>
+        <v>0.4202644499284598</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.3358013231924812</v>
+        <v>0.4527634361577014</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3705148816052832</v>
+        <v>0.363707626036357</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9576,10 +9576,10 @@
         <v>626</v>
       </c>
       <c r="B309" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C309">
-        <v>0.2832247569092026</v>
+        <v>0.2699507709782042</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.5043305670679854</v>
+        <v>0.4188825687795267</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9610,10 +9610,10 @@
         <v>630</v>
       </c>
       <c r="B311" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3041523051189654</v>
+        <v>0.3531006745579697</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>10</v>
       </c>
       <c r="C312">
-        <v>0.2563953786791235</v>
+        <v>0.3073322112340575</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>10</v>
       </c>
       <c r="C313">
-        <v>0.3193744009036322</v>
+        <v>0.2847734851528541</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3417047269525447</v>
+        <v>0.3379436281896377</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4077992899894587</v>
+        <v>0.5112185816367065</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3324334289108644</v>
+        <v>0.4071636140258336</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.4135709676256938</v>
+        <v>0.5199076383421941</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.4098765833326815</v>
+        <v>0.5742442027706895</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3657990951057367</v>
+        <v>0.3142549239722319</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.3321811725405738</v>
+        <v>0.2712017216778262</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9780,10 +9780,10 @@
         <v>650</v>
       </c>
       <c r="B321" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3825352475423019</v>
+        <v>0.309562728182086</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9797,10 +9797,10 @@
         <v>652</v>
       </c>
       <c r="B322" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C322">
-        <v>0.4045284318677827</v>
+        <v>0.4335211909117278</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.383244124235289</v>
+        <v>0.4058365174089516</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.4500449284437803</v>
+        <v>0.4210085744395568</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>10</v>
       </c>
       <c r="C325">
-        <v>0.3020325110554349</v>
+        <v>0.2749540226592071</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>10</v>
       </c>
       <c r="C326">
-        <v>0.3287164082685232</v>
+        <v>0.3629440808977026</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3532039936956921</v>
+        <v>0.3473699753843887</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.3950484095007625</v>
+        <v>0.2955943871396476</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C329">
-        <v>0.3308257189755571</v>
+        <v>0.3210191544958206</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3169026162253227</v>
+        <v>0.3044819590833273</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3688470823111906</v>
+        <v>0.3621789566677379</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9967,10 +9967,10 @@
         <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C332">
-        <v>0.2685326332180226</v>
+        <v>0.3960756227371886</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4861157766925537</v>
+        <v>0.4711440114121606</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C334">
-        <v>0.3653246225819929</v>
+        <v>0.3027920816593779</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10018,10 +10018,10 @@
         <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3780977321667507</v>
+        <v>0.3384357220007716</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3257526495578424</v>
+        <v>0.2955520573676881</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4965766362905008</v>
+        <v>0.5083904485963793</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.5064224751116001</v>
+        <v>0.3076671657252991</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4295050323447828</v>
+        <v>0.4866788728278647</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10103,10 +10103,10 @@
         <v>688</v>
       </c>
       <c r="B340" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C340">
-        <v>0.2704866913851728</v>
+        <v>0.3319224649693254</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10120,10 +10120,10 @@
         <v>690</v>
       </c>
       <c r="B341" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2518563766550741</v>
+        <v>0.2562049710781969</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10137,10 +10137,10 @@
         <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C342">
-        <v>0.3100966893270585</v>
+        <v>0.2788386902775188</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4096250760800239</v>
+        <v>0.4068537796651799</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C344">
-        <v>0.395066126361049</v>
+        <v>0.3075110764991976</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.379140625775289</v>
+        <v>0.3635797524737669</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.4319004892269448</v>
+        <v>0.3807348232669976</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.4503006387247473</v>
+        <v>0.3513732134382796</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.285047020202825</v>
+        <v>0.3180399291509251</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4913822118518461</v>
+        <v>0.5355330991510647</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.4324360475450967</v>
+        <v>0.3884437293359401</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C351">
-        <v>0.2785285085097486</v>
+        <v>0.269424734642764</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3203949561726578</v>
+        <v>0.4332365231767719</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3014865249995081</v>
+        <v>0.3907395632429125</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10341,10 +10341,10 @@
         <v>716</v>
       </c>
       <c r="B354" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C354">
-        <v>0.406195186073376</v>
+        <v>0.2650705888120313</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10358,10 +10358,10 @@
         <v>718</v>
       </c>
       <c r="B355" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3208616007839735</v>
+        <v>0.3380656660017344</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="C356">
-        <v>0.3328800853669359</v>
+        <v>0.3253388590616574</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10392,10 +10392,10 @@
         <v>722</v>
       </c>
       <c r="B357" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C357">
-        <v>0.369352997694251</v>
+        <v>0.4344200158129855</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3546800340941299</v>
+        <v>0.3703488318211703</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.5848315323315839</v>
+        <v>0.4818351331819922</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.617180237248045</v>
+        <v>0.5018564300612518</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3978351674551446</v>
+        <v>0.3179286888901702</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.2986687083417393</v>
+        <v>0.3343850199301769</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10494,10 +10494,10 @@
         <v>734</v>
       </c>
       <c r="B363" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C363">
-        <v>0.3687793273543531</v>
+        <v>0.2988635787777628</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.2617936170428184</v>
+        <v>0.3078490298728246</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10528,10 +10528,10 @@
         <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C365">
-        <v>0.2848494311341045</v>
+        <v>0.3155836159118277</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.307569013351872</v>
+        <v>0.2730510265689933</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>15</v>
       </c>
       <c r="C367">
-        <v>0.4514282521334257</v>
+        <v>0.3001816188839767</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3858403447032491</v>
+        <v>0.34326543587904</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.6132319452168646</v>
+        <v>0.4752978901289066</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3680108786197201</v>
+        <v>0.3677059874788612</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.5536621434649546</v>
+        <v>0.5099768483985874</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3761392179720027</v>
+        <v>0.3304779804596841</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.5211043197771339</v>
+        <v>0.4283493391246398</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.2549101567733491</v>
+        <v>0.5050129438518015</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.491339662642258</v>
+        <v>0.4432111578560545</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.366328552336194</v>
+        <v>0.400880816374967</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.5204110997980357</v>
+        <v>0.5222064043234128</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10749,10 +10749,10 @@
         <v>764</v>
       </c>
       <c r="B378" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3316343697508276</v>
+        <v>0.282460825437609</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10766,10 +10766,10 @@
         <v>766</v>
       </c>
       <c r="B379" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C379">
-        <v>0.337777870617924</v>
+        <v>0.3150026215436118</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3277829416478255</v>
+        <v>0.3497363192872168</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10800,10 +10800,10 @@
         <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C381">
-        <v>0.2594997443250948</v>
+        <v>0.4740058115104633</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.457455088333118</v>
+        <v>0.346764465547226</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.4294386764050589</v>
+        <v>0.373563559915764</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.5460968498675166</v>
+        <v>0.4919147384049176</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.419319016925548</v>
+        <v>0.3896018325778609</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3729955305966289</v>
+        <v>0.3133180531837769</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4348802854365715</v>
+        <v>0.4679781380932894</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3465739207750783</v>
+        <v>0.3572038526890338</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10936,10 +10936,10 @@
         <v>786</v>
       </c>
       <c r="B389" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3675022118488377</v>
+        <v>0.3780470899693529</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.29875710745958</v>
+        <v>0.3579556075963025</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10970,10 +10970,10 @@
         <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C391">
-        <v>0.4292292149566048</v>
+        <v>0.3785658851539945</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3086794770774272</v>
+        <v>0.355741699612033</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.286171716934738</v>
+        <v>0.4561117874847074</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11021,10 +11021,10 @@
         <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3010447332795923</v>
+        <v>0.3828111969087217</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3959422524532651</v>
+        <v>0.4161448850851163</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.486386542275466</v>
+        <v>0.4136607867095036</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3555273132448496</v>
+        <v>0.3900709117182337</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.574829094850433</v>
+        <v>0.5166344469058195</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.4072055805506207</v>
+        <v>0.3469227574063841</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11123,10 +11123,10 @@
         <v>808</v>
       </c>
       <c r="B400" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C400">
-        <v>0.4082683891670438</v>
+        <v>0.317476785210755</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4294047234772305</v>
+        <v>0.4587751895135407</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3719449728297917</v>
+        <v>0.4019140610892505</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.3378504285724557</v>
+        <v>0.2931894169464963</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>44</v>
       </c>
       <c r="C404">
-        <v>0.2821154580281621</v>
+        <v>0.3173854687910198</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.3330011853806542</v>
+        <v>0.4205301903818507</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>6</v>
       </c>
       <c r="C406">
-        <v>0.5326022261720084</v>
+        <v>0.4916167964759152</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.4362362369548697</v>
+        <v>0.3817202312977135</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4505627543954459</v>
+        <v>0.4734426073990602</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4302809742877904</v>
+        <v>0.5130959572438536</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11293,10 +11293,10 @@
         <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C410">
-        <v>0.2865656488690019</v>
+        <v>0.3302831339563063</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11310,10 +11310,10 @@
         <v>830</v>
       </c>
       <c r="B411" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3609868920225222</v>
+        <v>0.3241466270282546</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.3779717371136816</v>
+        <v>0.4785869478502672</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.3200099685021095</v>
+        <v>0.2810957467636199</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11361,10 +11361,10 @@
         <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C414">
-        <v>0.3007872918109911</v>
+        <v>0.3566670128553855</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3483420523908261</v>
+        <v>0.3420937850526287</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11395,10 +11395,10 @@
         <v>840</v>
       </c>
       <c r="B416" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="C416">
-        <v>0.311595571758371</v>
+        <v>0.3742353273248115</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.3349136597488546</v>
+        <v>0.3198840271206917</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>44</v>
       </c>
       <c r="C418">
-        <v>0.2922475079748574</v>
+        <v>0.3181847601448357</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11446,10 +11446,10 @@
         <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3257827952419469</v>
+        <v>0.4143289756792773</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.3617412186670143</v>
+        <v>0.4528897926210088</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4215287343577652</v>
+        <v>0.4006252975805643</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3740271338460177</v>
+        <v>0.3735265231332319</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.3719385632513119</v>
+        <v>0.4640165755358109</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.415617613040745</v>
+        <v>0.3325229993088122</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3106632142681557</v>
+        <v>0.3247809281701205</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3206225904484328</v>
+        <v>0.3772309142513167</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11582,10 +11582,10 @@
         <v>862</v>
       </c>
       <c r="B427" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2887299120787639</v>
+        <v>0.2608351460719957</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2503800120534355</v>
+        <v>0.2793402396159717</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11616,10 +11616,10 @@
         <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C429">
-        <v>0.263091253518287</v>
+        <v>0.3836820575179162</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.2849428077775598</v>
+        <v>0.3160536192646429</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>15</v>
       </c>
       <c r="C431">
-        <v>0.3082036254960941</v>
+        <v>0.2998975711920567</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.2792297534347161</v>
+        <v>0.331597973018401</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11684,10 +11684,10 @@
         <v>874</v>
       </c>
       <c r="B433" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C433">
-        <v>0.2486301986976782</v>
+        <v>0.3185244884909684</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11701,10 +11701,10 @@
         <v>876</v>
       </c>
       <c r="B434" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3550472571395922</v>
+        <v>0.3616339994183591</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.326540587817982</v>
+        <v>0.426279773788339</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3324807374846773</v>
+        <v>0.3591371610925511</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3536983297676203</v>
+        <v>0.3331881383000567</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3867744410244405</v>
+        <v>0.3953120153372238</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.4434059035841788</v>
+        <v>0.3424144269501241</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3460540320284144</v>
+        <v>0.3412019405599855</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11820,10 +11820,10 @@
         <v>890</v>
       </c>
       <c r="B441" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C441">
-        <v>0.3238603910098123</v>
+        <v>0.3039308640375215</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.4049875414614426</v>
+        <v>0.3635243741334956</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3746389720831347</v>
+        <v>0.3113812451305115</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11871,10 +11871,10 @@
         <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C444">
-        <v>0.314866626281367</v>
+        <v>0.3377911189301578</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.4590231371082275</v>
+        <v>0.3497565401390224</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3997242933457682</v>
+        <v>0.3922462912833353</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2963942655334452</v>
+        <v>0.3041494228845325</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11939,10 +11939,10 @@
         <v>904</v>
       </c>
       <c r="B448" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3172253464647868</v>
+        <v>0.3988597409304627</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3363179013969554</v>
+        <v>0.3762184921137278</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.4197439569547413</v>
+        <v>0.3703665128163428</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4300822737098711</v>
+        <v>0.4568756961313837</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12007,10 +12007,10 @@
         <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C452">
-        <v>0.298495305026504</v>
+        <v>0.2827762978712109</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3293979581742361</v>
+        <v>0.3941841036599131</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12041,10 +12041,10 @@
         <v>916</v>
       </c>
       <c r="B454" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C454">
-        <v>0.4233146640960258</v>
+        <v>0.2947473069018948</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3364905375407837</v>
+        <v>0.3309425170789219</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12075,10 +12075,10 @@
         <v>920</v>
       </c>
       <c r="B456" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3614875405943177</v>
+        <v>0.3505895778151284</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.4474551504437838</v>
+        <v>0.3872018054345991</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3130604797965813</v>
+        <v>0.3357582341024452</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.4210388855260574</v>
+        <v>0.3507381635844327</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>15</v>
       </c>
       <c r="C460">
-        <v>0.4364977266537235</v>
+        <v>0.3898248151995047</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>10</v>
       </c>
       <c r="C461">
-        <v>0.4024927259879569</v>
+        <v>0.3292635202021108</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12177,10 +12177,10 @@
         <v>932</v>
       </c>
       <c r="B462" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C462">
-        <v>0.2704967635242541</v>
+        <v>0.3020884787026801</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3631715103387161</v>
+        <v>0.3290988686133663</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3469676977666851</v>
+        <v>0.4401225507382625</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3867651473311656</v>
+        <v>0.4056166773141336</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5415543146020466</v>
+        <v>0.5711362775788509</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.3190623399276331</v>
+        <v>0.4615192046468659</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3737113145444627</v>
+        <v>0.4069828858218998</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
         <v>946</v>
       </c>
       <c r="B469" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C469">
-        <v>0.3137767418139595</v>
+        <v>0.3018741319553296</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3389964531947993</v>
+        <v>0.337776417518129</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12330,10 +12330,10 @@
         <v>950</v>
       </c>
       <c r="B471" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3334606048370234</v>
+        <v>0.3351166778175548</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12347,10 +12347,10 @@
         <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3027744075786963</v>
+        <v>0.3616106943071908</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3190524562181222</v>
+        <v>0.3561869227662535</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.2985080811928911</v>
+        <v>0.3880470330068618</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12398,10 +12398,10 @@
         <v>958</v>
       </c>
       <c r="B475" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C475">
-        <v>0.350943019130758</v>
+        <v>0.3742631477366594</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3265153436593144</v>
+        <v>0.3166353472815191</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>15</v>
       </c>
       <c r="C477">
-        <v>0.3430871899792018</v>
+        <v>0.3534526540337829</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12449,10 +12449,10 @@
         <v>964</v>
       </c>
       <c r="B478" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C478">
-        <v>0.3588994249993746</v>
+        <v>0.4223264987054359</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4507409527640741</v>
+        <v>0.4200488163297086</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4311811654570705</v>
+        <v>0.4514351849346507</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3724013580000242</v>
+        <v>0.3811394420795335</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3072889041325275</v>
+        <v>0.3288384918364493</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.308115340223401</v>
+        <v>0.3446280567111195</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12551,10 +12551,10 @@
         <v>976</v>
       </c>
       <c r="B484" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C484">
-        <v>0.4210541624040544</v>
+        <v>0.3820042284062229</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.4055997064024809</v>
+        <v>0.4024708034122653</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.5232448543718984</v>
+        <v>0.4226357280140805</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.3859961293919434</v>
+        <v>0.4509265078934047</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12619,10 +12619,10 @@
         <v>984</v>
       </c>
       <c r="B488" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C488">
-        <v>0.2100656671962154</v>
+        <v>0.3837807891370171</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4210708414260347</v>
+        <v>0.4968743394763223</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3743364642032755</v>
+        <v>0.3428082574731809</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C491">
-        <v>0.2540693964967167</v>
+        <v>0.281045675292399</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4812213430657428</v>
+        <v>0.5304550786594751</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.4260234640820065</v>
+        <v>0.3295031102426207</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>44</v>
       </c>
       <c r="C494">
-        <v>0.3688024669236976</v>
+        <v>0.3193176679625419</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.561869835515996</v>
+        <v>0.5471474828345227</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4405074703374894</v>
+        <v>0.4905229698219487</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
         <v>1002</v>
       </c>
       <c r="B497" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3011032319158836</v>
+        <v>0.3751617727867874</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.7251231227472159</v>
+        <v>0.7208180903680157</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3648232957765887</v>
+        <v>0.4164872252154111</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3963329223667192</v>
+        <v>0.3943267507387416</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4102213194928263</v>
+        <v>0.3728521907159971</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.646248130626668</v>
+        <v>0.6301891065138235</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12874,10 +12874,10 @@
         <v>1014</v>
       </c>
       <c r="B503" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3648989578977161</v>
+        <v>0.3821492204497333</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C504">
-        <v>0.2974449683323425</v>
+        <v>0.3123464980621902</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.3781594142143653</v>
+        <v>0.4573156491572166</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4120881483150217</v>
+        <v>0.4966510128918018</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.494183327821807</v>
+        <v>0.3226515520479352</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12959,10 +12959,10 @@
         <v>1024</v>
       </c>
       <c r="B508" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3694715128059776</v>
+        <v>0.3581285198657512</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4142083042059146</v>
+        <v>0.4868700420546586</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12993,10 +12993,10 @@
         <v>1028</v>
       </c>
       <c r="B510" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3719108717943466</v>
+        <v>0.3832140657500053</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.291421570199756</v>
+        <v>0.4002956522463696</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.4965281829982736</v>
+        <v>0.2945093231863476</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.4130076724644182</v>
+        <v>0.389275447609536</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.3628632143291706</v>
+        <v>0.4245501843823383</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4981884802024392</v>
+        <v>0.5617419992367746</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3159828531216405</v>
+        <v>0.3103045015107687</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3510385044687283</v>
+        <v>0.3360781606157007</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.234552944546554</v>
+        <v>0.3342259312229136</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.430268176262293</v>
+        <v>0.481233076827528</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3305217621519389</v>
+        <v>0.3477510435961427</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13180,10 +13180,10 @@
         <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3715254617175261</v>
+        <v>0.3332957457588769</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3818251620415858</v>
+        <v>0.3739859518526156</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4609145312415809</v>
+        <v>0.4547305845510159</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13231,10 +13231,10 @@
         <v>1056</v>
       </c>
       <c r="B524" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3340199088001575</v>
+        <v>0.2949141063007796</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4417529995388452</v>
+        <v>0.4526918593537551</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.3995789482727499</v>
+        <v>0.452569278729548</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.2980733427680437</v>
+        <v>0.3761839404766265</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.3677505479697602</v>
+        <v>0.4737974547594956</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3655602677437411</v>
+        <v>0.3481609487251634</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4901550343618048</v>
+        <v>0.5070412521509874</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5633345760129628</v>
+        <v>0.6060838145642971</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C532">
-        <v>0.3331598648687272</v>
+        <v>0.3157390365205732</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4201272550224452</v>
+        <v>0.4727195100380562</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3986253680684593</v>
+        <v>0.3199035927362817</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.4293504726964789</v>
+        <v>0.3023043600393073</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3946732913370717</v>
+        <v>0.3221586764954804</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13452,10 +13452,10 @@
         <v>1082</v>
       </c>
       <c r="B537" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3306429327988877</v>
+        <v>0.4222813201451429</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C538">
-        <v>0.347668737876053</v>
+        <v>0.2949399381791736</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
         <v>1086</v>
       </c>
       <c r="B539" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3087298930813142</v>
+        <v>0.3095952973161565</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.351951694445898</v>
+        <v>0.2881023938442137</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13520,10 +13520,10 @@
         <v>1090</v>
       </c>
       <c r="B541" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C541">
-        <v>0.3701475185273889</v>
+        <v>0.4452570861377024</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3344494138022293</v>
+        <v>0.4030427253243088</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.4975306138644267</v>
+        <v>0.4522944302958911</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.4585718534757235</v>
+        <v>0.3765856908900599</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.3231131480085778</v>
+        <v>0.3032762648047834</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.4066512303493768</v>
+        <v>0.3531039416695648</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.3278231437226111</v>
+        <v>0.3076666390457057</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.4779006907596356</v>
+        <v>0.4907216867804695</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4222465517659341</v>
+        <v>0.4238249431858235</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3665308303122244</v>
+        <v>0.3684223588301463</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2885834119064375</v>
+        <v>0.3066190561849952</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13959,10 +13959,10 @@
         <v>1158</v>
       </c>
       <c r="B570" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.3342397311140648</v>
+        <v>0.3098005487786876</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.3288066247569617</v>
+        <v>0.3025596542441778</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.3149073591794695</v>
+        <v>0.3597870223807797</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14010,10 +14010,10 @@
         <v>1164</v>
       </c>
       <c r="B573" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.290388621250887</v>
+        <v>0.3050634886121578</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14027,10 +14027,10 @@
         <v>1166</v>
       </c>
       <c r="B574" t="s">
-        <v>1143</v>
+        <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3008023574800684</v>
+        <v>0.3227511442277982</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3411380114920909</v>
+        <v>0.3371033177670684</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14061,10 +14061,10 @@
         <v>1170</v>
       </c>
       <c r="B576" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3713225549798762</v>
+        <v>0.3897751160083814</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14078,10 +14078,10 @@
         <v>1172</v>
       </c>
       <c r="B577" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C577">
-        <v>0.3166378321262134</v>
+        <v>0.2841597472232418</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3456256271589355</v>
+        <v>0.3890065758143285</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3002937606572226</v>
+        <v>0.3281385619552016</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3267838195943273</v>
+        <v>0.3685731822947451</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4348111788272715</v>
+        <v>0.4449098081558612</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3115213879386876</v>
+        <v>0.3118414788894101</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14180,10 +14180,10 @@
         <v>1184</v>
       </c>
       <c r="B583" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C583">
-        <v>0.4040381478715941</v>
+        <v>0.3676439037715044</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3439586018951448</v>
+        <v>0.3041133165010727</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.3651366509461922</v>
+        <v>0.3921049488558505</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.3104260496879022</v>
+        <v>0.3110312942285105</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2692410619941479</v>
+        <v>0.3292717537634981</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3280218948955543</v>
+        <v>0.2915438760173306</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3395111383209079</v>
+        <v>0.3456207620168386</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.3701287036974238</v>
+        <v>0.4030196804948968</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.3989202263205405</v>
+        <v>0.4704354123402085</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.2885426380580247</v>
+        <v>0.3851910777979292</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.5323088333391208</v>
+        <v>0.5418925974074438</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.3286665563902816</v>
+        <v>0.4222690750438409</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>1143</v>
       </c>
       <c r="C595">
-        <v>0.3328472982924794</v>
+        <v>0.3346530825625604</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.3584064917439271</v>
+        <v>0.4327481944721272</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.4180076979341758</v>
+        <v>0.3741442853546899</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C598">
-        <v>0.30131255340819</v>
+        <v>0.2849978342499468</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.3428081368210406</v>
+        <v>0.3218449368484785</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.369584887067049</v>
+        <v>0.3039958818503642</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14486,10 +14486,10 @@
         <v>1220</v>
       </c>
       <c r="B601" t="s">
-        <v>44</v>
+        <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.315226109862878</v>
+        <v>0.3155177535017599</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3710218202835396</v>
+        <v>0.3967551010112958</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.3382137199041061</v>
+        <v>0.3240206318110657</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3515824177648869</v>
+        <v>0.2969274373347594</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.3233409026496176</v>
+        <v>0.2957363704839646</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3833787326151961</v>
+        <v>0.3656187619977456</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3820302917531948</v>
+        <v>0.317704705795591</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14605,10 +14605,10 @@
         <v>1234</v>
       </c>
       <c r="B608" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C608">
-        <v>0.3455349691473419</v>
+        <v>0.3221291059284625</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2946401527810165</v>
+        <v>0.3294718102079252</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.3480459600616244</v>
+        <v>0.268710503691466</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4534456639436498</v>
+        <v>0.4846106870503183</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.415413363479192</v>
+        <v>0.4297736490016794</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3898833655408745</v>
+        <v>0.3518523567980054</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.3874331910754172</v>
+        <v>0.3913391249140533</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.4476374654422076</v>
+        <v>0.3579411795091575</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4074035776198009</v>
+        <v>0.3924376116817266</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3436499375699926</v>
+        <v>0.3580591422994894</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14775,10 +14775,10 @@
         <v>1254</v>
       </c>
       <c r="B618" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C618">
-        <v>0.2990104807294856</v>
+        <v>0.3179779610056626</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4026609324845756</v>
+        <v>0.4310891558384365</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,64 +14809,64 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
+        <v>15</v>
+      </c>
+      <c r="C620">
+        <v>0.2890539426284621</v>
+      </c>
+      <c r="D620" t="s">
         <v>1259</v>
       </c>
-      <c r="C620">
-        <v>0.307282925476921</v>
-      </c>
-      <c r="D620" t="s">
+      <c r="E620" t="s">
         <v>1260</v>
-      </c>
-      <c r="E620" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="621" spans="1:5">
       <c r="A621" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B621" t="s">
+        <v>15</v>
+      </c>
+      <c r="C621">
+        <v>0.3264652590983719</v>
+      </c>
+      <c r="D621" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E621" t="s">
         <v>1262</v>
-      </c>
-      <c r="B621" t="s">
-        <v>6</v>
-      </c>
-      <c r="C621">
-        <v>0.2870033500116722</v>
-      </c>
-      <c r="D621" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E621" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="622" spans="1:5">
       <c r="A622" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B622" t="s">
+        <v>15</v>
+      </c>
+      <c r="C622">
+        <v>0.2274980912335571</v>
+      </c>
+      <c r="D622" t="s">
+        <v>1259</v>
+      </c>
+      <c r="E622" t="s">
         <v>1264</v>
-      </c>
-      <c r="B622" t="s">
-        <v>6</v>
-      </c>
-      <c r="C622">
-        <v>0.2296330773028979</v>
-      </c>
-      <c r="D622" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E622" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="623" spans="1:5">
       <c r="A623" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B623" t="s">
         <v>1266</v>
       </c>
-      <c r="B623" t="s">
-        <v>15</v>
-      </c>
       <c r="C623">
-        <v>0.2602398601744634</v>
+        <v>0.2429884473956745</v>
       </c>
       <c r="D623" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E623" t="s">
         <v>1267</v>
@@ -14880,10 +14880,10 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2503437369381914</v>
+        <v>0.2690408351901146</v>
       </c>
       <c r="D624" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E624" t="s">
         <v>1269</v>
@@ -14894,13 +14894,13 @@
         <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C625">
-        <v>0.2547655669534196</v>
+        <v>0.2504897389124233</v>
       </c>
       <c r="D625" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E625" t="s">
         <v>1271</v>
@@ -14911,13 +14911,13 @@
         <v>1272</v>
       </c>
       <c r="B626" t="s">
+        <v>15</v>
+      </c>
+      <c r="C626">
+        <v>0.3024316527710464</v>
+      </c>
+      <c r="D626" t="s">
         <v>1259</v>
-      </c>
-      <c r="C626">
-        <v>0.3908567377511304</v>
-      </c>
-      <c r="D626" t="s">
-        <v>1260</v>
       </c>
       <c r="E626" t="s">
         <v>1273</v>
@@ -14928,13 +14928,13 @@
         <v>1274</v>
       </c>
       <c r="B627" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C627">
+        <v>0.3259183667833081</v>
+      </c>
+      <c r="D627" t="s">
         <v>1259</v>
-      </c>
-      <c r="C627">
-        <v>0.2639227200845429</v>
-      </c>
-      <c r="D627" t="s">
-        <v>1260</v>
       </c>
       <c r="E627" t="s">
         <v>1275</v>
@@ -14945,13 +14945,13 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C628">
+        <v>0.2870318579605975</v>
+      </c>
+      <c r="D628" t="s">
         <v>1259</v>
-      </c>
-      <c r="C628">
-        <v>0.3945412694747829</v>
-      </c>
-      <c r="D628" t="s">
-        <v>1260</v>
       </c>
       <c r="E628" t="s">
         <v>1277</v>
@@ -14962,13 +14962,13 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C629">
+        <v>0.2223251664995292</v>
+      </c>
+      <c r="D629" t="s">
         <v>1259</v>
-      </c>
-      <c r="C629">
-        <v>0.2319758224647556</v>
-      </c>
-      <c r="D629" t="s">
-        <v>1260</v>
       </c>
       <c r="E629" t="s">
         <v>1279</v>
@@ -14979,13 +14979,13 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C630">
+        <v>0.3930299238157548</v>
+      </c>
+      <c r="D630" t="s">
         <v>1259</v>
-      </c>
-      <c r="C630">
-        <v>0.3618023684677659</v>
-      </c>
-      <c r="D630" t="s">
-        <v>1260</v>
       </c>
       <c r="E630" t="s">
         <v>1281</v>
@@ -14996,13 +14996,13 @@
         <v>1282</v>
       </c>
       <c r="B631" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C631">
+        <v>0.4040703574019626</v>
+      </c>
+      <c r="D631" t="s">
         <v>1259</v>
-      </c>
-      <c r="C631">
-        <v>0.3877522445453552</v>
-      </c>
-      <c r="D631" t="s">
-        <v>1260</v>
       </c>
       <c r="E631" t="s">
         <v>1283</v>
@@ -15013,13 +15013,13 @@
         <v>1284</v>
       </c>
       <c r="B632" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C632">
+        <v>0.4557776174784538</v>
+      </c>
+      <c r="D632" t="s">
         <v>1259</v>
-      </c>
-      <c r="C632">
-        <v>0.3956892188159999</v>
-      </c>
-      <c r="D632" t="s">
-        <v>1260</v>
       </c>
       <c r="E632" t="s">
         <v>1285</v>
@@ -15033,10 +15033,10 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2712368123519923</v>
+        <v>0.265804185567516</v>
       </c>
       <c r="D633" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E633" t="s">
         <v>1287</v>
@@ -15050,10 +15050,10 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.2927921379332419</v>
+        <v>0.3325964414456429</v>
       </c>
       <c r="D634" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E634" t="s">
         <v>1289</v>
@@ -15064,13 +15064,13 @@
         <v>1290</v>
       </c>
       <c r="B635" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C635">
+        <v>0.4695927819330701</v>
+      </c>
+      <c r="D635" t="s">
         <v>1259</v>
-      </c>
-      <c r="C635">
-        <v>0.6057493009487379</v>
-      </c>
-      <c r="D635" t="s">
-        <v>1260</v>
       </c>
       <c r="E635" t="s">
         <v>1291</v>
@@ -15081,13 +15081,13 @@
         <v>1292</v>
       </c>
       <c r="B636" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C636">
-        <v>0.2218612202300237</v>
+        <v>0.3618594904497027</v>
       </c>
       <c r="D636" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E636" t="s">
         <v>1293</v>
@@ -15098,13 +15098,13 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C637">
+        <v>0.3234625111819353</v>
+      </c>
+      <c r="D637" t="s">
         <v>1259</v>
-      </c>
-      <c r="C637">
-        <v>0.3061035777308354</v>
-      </c>
-      <c r="D637" t="s">
-        <v>1260</v>
       </c>
       <c r="E637" t="s">
         <v>1295</v>
@@ -15115,13 +15115,13 @@
         <v>1296</v>
       </c>
       <c r="B638" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C638">
+        <v>0.4903627901137151</v>
+      </c>
+      <c r="D638" t="s">
         <v>1259</v>
-      </c>
-      <c r="C638">
-        <v>0.4970545864277076</v>
-      </c>
-      <c r="D638" t="s">
-        <v>1260</v>
       </c>
       <c r="E638" t="s">
         <v>1297</v>
@@ -15135,10 +15135,10 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.2952902815595186</v>
+        <v>0.3080109935756575</v>
       </c>
       <c r="D639" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E639" t="s">
         <v>1299</v>
@@ -15152,10 +15152,10 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2654344721812085</v>
+        <v>0.2600392705901694</v>
       </c>
       <c r="D640" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E640" t="s">
         <v>1301</v>
@@ -15166,13 +15166,13 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C641">
-        <v>0.2792152072964989</v>
+        <v>0.2878169316923523</v>
       </c>
       <c r="D641" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E641" t="s">
         <v>1303</v>
@@ -15183,13 +15183,13 @@
         <v>1304</v>
       </c>
       <c r="B642" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C642">
+        <v>0.3355545985743619</v>
+      </c>
+      <c r="D642" t="s">
         <v>1259</v>
-      </c>
-      <c r="C642">
-        <v>0.3267848073113218</v>
-      </c>
-      <c r="D642" t="s">
-        <v>1260</v>
       </c>
       <c r="E642" t="s">
         <v>1305</v>
@@ -15203,10 +15203,10 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.2432435900911922</v>
+        <v>0.3026071747601911</v>
       </c>
       <c r="D643" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E643" t="s">
         <v>1307</v>
@@ -15220,10 +15220,10 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.3160162859289942</v>
+        <v>0.2912869579012972</v>
       </c>
       <c r="D644" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E644" t="s">
         <v>1309</v>
@@ -15234,13 +15234,13 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C645">
-        <v>0.263914901084524</v>
+        <v>0.2499418303546379</v>
       </c>
       <c r="D645" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E645" t="s">
         <v>1311</v>
@@ -15254,10 +15254,10 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.4190582423574253</v>
+        <v>0.3302226417810288</v>
       </c>
       <c r="D646" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E646" t="s">
         <v>1313</v>
@@ -15268,13 +15268,13 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C647">
-        <v>0.2597546322031286</v>
+        <v>0.3296166688505361</v>
       </c>
       <c r="D647" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E647" t="s">
         <v>1315</v>
@@ -15288,10 +15288,10 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.3033028912722967</v>
+        <v>0.2697526705414868</v>
       </c>
       <c r="D648" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E648" t="s">
         <v>1317</v>
@@ -15305,10 +15305,10 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.2767483544396126</v>
+        <v>0.2930271360542232</v>
       </c>
       <c r="D649" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E649" t="s">
         <v>1319</v>
@@ -15319,13 +15319,13 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C650">
+        <v>0.2818298737363125</v>
+      </c>
+      <c r="D650" t="s">
         <v>1259</v>
-      </c>
-      <c r="C650">
-        <v>0.2515705731357527</v>
-      </c>
-      <c r="D650" t="s">
-        <v>1260</v>
       </c>
       <c r="E650" t="s">
         <v>1321</v>
@@ -15336,13 +15336,13 @@
         <v>1322</v>
       </c>
       <c r="B651" t="s">
+        <v>15</v>
+      </c>
+      <c r="C651">
+        <v>0.301028925047235</v>
+      </c>
+      <c r="D651" t="s">
         <v>1259</v>
-      </c>
-      <c r="C651">
-        <v>0.3634470392135357</v>
-      </c>
-      <c r="D651" t="s">
-        <v>1260</v>
       </c>
       <c r="E651" t="s">
         <v>1323</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,15 +15379,15 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,23 +15403,23 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>1259</v>
+        <v>1266</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2743444238476875</v>
+        <v>0.2707688023253016</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4306257315310673</v>
+        <v>0.4273550040153515</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.373494124041068</v>
+        <v>0.3721229598856683</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3628350310946563</v>
+        <v>0.3557925576187628</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3981919005891298</v>
+        <v>0.3941300358670415</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>0.288756374381785</v>
+        <v>0.2830914975431358</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3704416954380614</v>
+        <v>0.3653476068513238</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3489600248924803</v>
+        <v>0.3412451391907707</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3488926235782247</v>
+        <v>0.3464507969288235</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2592917531370745</v>
+        <v>0.2539011792253815</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.420396247153849</v>
+        <v>0.4147227394802035</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.331350451680347</v>
+        <v>0.3247670644942205</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.4376222424814795</v>
+        <v>0.4307827381421535</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.358822867810817</v>
+        <v>0.3553771857214677</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.2960141810973982</v>
+        <v>0.2933009965118885</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2799300224866167</v>
+        <v>0.2753778203808029</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2990320534284463</v>
+        <v>0.2947385930946325</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4395706191880912</v>
+        <v>0.4360049105756226</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4289788063058347</v>
+        <v>0.4189960882201127</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4362543298434937</v>
+        <v>0.4361717024392023</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3315892761078534</v>
+        <v>0.327776106359753</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3992717543703808</v>
+        <v>0.3969006339241101</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3617409043902401</v>
+        <v>0.3439240076363249</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6451364534577115</v>
+        <v>0.6223155428152148</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.310625971837748</v>
+        <v>0.3073101306719332</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2872011873757053</v>
+        <v>0.2844572302731646</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3219530658013316</v>
+        <v>0.3176173211194649</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4792689177560632</v>
+        <v>0.4788310853692099</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3868608482301406</v>
+        <v>0.378042005269581</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4261490112537247</v>
+        <v>0.4242921960687304</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4285784189418017</v>
+        <v>0.4226553042105923</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3964205475865312</v>
+        <v>0.3901552397622838</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.339615188084268</v>
+        <v>0.3312561804615002</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4882366263833827</v>
+        <v>0.4669123446346876</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="C36">
-        <v>0.2289664496481518</v>
+        <v>0.2625399423195997</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.3069074787993796</v>
+        <v>0.2991815861609693</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3469283668127385</v>
+        <v>0.3375690440010488</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.374704157142648</v>
+        <v>0.3678491486038083</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4620618260676042</v>
+        <v>0.4606636025130146</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>90</v>
       </c>
       <c r="C41">
-        <v>0.2721288066982321</v>
+        <v>0.2721692936521675</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5476223114334171</v>
+        <v>0.5414220825177557</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.4110831855074111</v>
+        <v>0.4060875385124043</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4167067244624789</v>
+        <v>0.411634669568714</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.401540474342546</v>
+        <v>0.39770654985971</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4369714045974112</v>
+        <v>0.4339180874155192</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2951391246925901</v>
+        <v>0.2915652766643496</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.428975461745873</v>
+        <v>0.4233680717804375</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3484875365028581</v>
+        <v>0.3435176319205248</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3896756533676329</v>
+        <v>0.3823714107828452</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3684724416934421</v>
+        <v>0.3616264468180383</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5326253927344151</v>
+        <v>0.5261927823127682</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4448334497955047</v>
+        <v>0.441997107079971</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3960441600488505</v>
+        <v>0.3934991594526069</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2906101140192583</v>
+        <v>0.2849570389199365</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.359377709199482</v>
+        <v>0.3558654344054911</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5866865374405409</v>
+        <v>0.5816727349403208</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>15</v>
       </c>
       <c r="C58">
-        <v>0.3387049529650369</v>
+        <v>0.3304942310832242</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.418040944778058</v>
+        <v>0.4023510367548296</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.2802636851558155</v>
+        <v>0.2761861902523435</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3465987220348992</v>
+        <v>0.3428988857524589</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3554827409459266</v>
+        <v>0.3455134135112166</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.377822842625364</v>
+        <v>0.3715722676211589</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2411085964039868</v>
+        <v>0.2369168953961513</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3380481255559311</v>
+        <v>0.3340518525879855</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3326191692625839</v>
+        <v>0.3305173626011721</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3670901745753551</v>
+        <v>0.3624983250487309</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2662243770271415</v>
+        <v>0.2562574243338254</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>79</v>
       </c>
       <c r="C69">
-        <v>0.5752178585727976</v>
+        <v>0.6303965300737046</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>79</v>
       </c>
       <c r="C70">
-        <v>0.5139168238589952</v>
+        <v>0.5617303980475821</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.5105534951542032</v>
+        <v>0.480411174447221</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3741996669766918</v>
+        <v>0.3616993955647609</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.545060761004782</v>
+        <v>0.5357651501135829</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4999662791352072</v>
+        <v>0.4845437728885268</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2566796673355865</v>
+        <v>0.2541955445262615</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3861670199087062</v>
+        <v>0.3809370408374679</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3507708557075714</v>
+        <v>0.3488099600822705</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4321583143919466</v>
+        <v>0.4317646871450993</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>0.2536855763458504</v>
+        <v>0.2500509288923488</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3780323775834545</v>
+        <v>0.3763295152472192</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.3250940696668205</v>
+        <v>0.318127218475848</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4345841003048698</v>
+        <v>0.4312318788542558</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3996691271634397</v>
+        <v>0.396635457080874</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>15</v>
       </c>
       <c r="C84">
-        <v>0.3039098653722838</v>
+        <v>0.2999412811216872</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3511342050494848</v>
+        <v>0.3471447810830471</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.2942281260880815</v>
+        <v>0.2891873074079594</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2654540862652238</v>
+        <v>0.262716332460824</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>79</v>
       </c>
       <c r="C88">
-        <v>0.3175290193067311</v>
+        <v>0.3586697590136387</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3091833187353051</v>
+        <v>0.304093917974551</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2941001741876766</v>
+        <v>0.2887036086633403</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>15</v>
       </c>
       <c r="C91">
-        <v>0.2707349989006477</v>
+        <v>0.2666599847064514</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.3390803863832717</v>
+        <v>0.339259539149075</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.4067607070222479</v>
+        <v>0.4025063195184892</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.2681426861307242</v>
+        <v>0.2634342665085479</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3313015334207891</v>
+        <v>0.3249173539227785</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3916184379003206</v>
+        <v>0.3847829847262648</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3636423743697733</v>
+        <v>0.3621818003696727</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3674296938775312</v>
+        <v>0.3663540130078058</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4408367175454333</v>
+        <v>0.4344227560630397</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.4035193228528987</v>
+        <v>0.40043261148049</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.4567652865107409</v>
+        <v>0.4581797797144687</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4613246281683068</v>
+        <v>0.455724614425064</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.350512790711995</v>
+        <v>0.3498833412686107</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3704359969894747</v>
+        <v>0.3633097905611046</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3496659789409031</v>
+        <v>0.3507620203388998</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.4111007953503558</v>
+        <v>0.4055375610684723</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3509383947208228</v>
+        <v>0.3508890499335309</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4065108007481238</v>
+        <v>0.4049777632437482</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>90</v>
       </c>
       <c r="C109">
-        <v>0.2649498884738904</v>
+        <v>0.264161745185849</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2945735820979558</v>
+        <v>0.2915435292569892</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.5353796735510493</v>
+        <v>0.5329921238719034</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3905223239457118</v>
+        <v>0.3848545588968632</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.5285800306227033</v>
+        <v>0.525927124703529</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6859572483384525</v>
+        <v>0.668061393160153</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3139025483315097</v>
+        <v>0.3090130497852639</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4426836698890262</v>
+        <v>0.4423518019096727</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>10</v>
       </c>
       <c r="C117">
-        <v>0.2761325587972868</v>
+        <v>0.2733264992622443</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.4078913507053042</v>
+        <v>0.4049727985965608</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3763142611007187</v>
+        <v>0.3753697405417786</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3740157215264653</v>
+        <v>0.3715785922883789</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.3189678581175269</v>
+        <v>0.3113720368055873</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3546441343707352</v>
+        <v>0.3472863770556365</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.3020082664986499</v>
+        <v>0.2977328383852423</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3915947795650886</v>
+        <v>0.3863200256804191</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="C125">
-        <v>0.2880372858423364</v>
+        <v>0.2845880307006517</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3805236719469925</v>
+        <v>0.3780114004616743</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.5089749539855166</v>
+        <v>0.5035276801037192</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4504933725224523</v>
+        <v>0.4409548223810976</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="C129">
-        <v>0.3023225262410847</v>
+        <v>0.2981279624026634</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.4644546663652233</v>
+        <v>0.4607930045110125</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2830431694334888</v>
+        <v>0.2795737786263787</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3645834761611966</v>
+        <v>0.3606924208088326</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3527482372664351</v>
+        <v>0.3469232179208231</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3180921283532087</v>
+        <v>0.3178345101267935</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3552984565744476</v>
+        <v>0.3498487195078078</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3531851695055268</v>
+        <v>0.3499424984851879</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3992815295665175</v>
+        <v>0.3933209787178658</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>15</v>
       </c>
       <c r="C138">
-        <v>0.3227998878422417</v>
+        <v>0.3179710458229442</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4427156640453834</v>
+        <v>0.4402757647939984</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.4056683410752389</v>
+        <v>0.4070122175367404</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3464714192787845</v>
+        <v>0.3439640069237996</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.4059302073110285</v>
+        <v>0.4055534461997542</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>15</v>
       </c>
       <c r="C143">
-        <v>0.3121103410919873</v>
+        <v>0.304135463461537</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5876306152288507</v>
+        <v>0.564188157039164</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2698367060463446</v>
+        <v>0.2655238711819132</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4436468803715153</v>
+        <v>0.4406535218267651</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4430331727848163</v>
+        <v>0.4394390304887004</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3410568608326927</v>
+        <v>0.3331830173678353</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3934490642266766</v>
+        <v>0.385596584360534</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3507126082059528</v>
+        <v>0.3428805136849269</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2554218915426055</v>
+        <v>0.2503822374398392</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.7114191000189132</v>
+        <v>0.6930778180921288</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3501963425533418</v>
+        <v>0.3507530793377277</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="C154">
-        <v>0.3407134977412515</v>
+        <v>0.3395075839022036</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="C155">
-        <v>0.2854371134548503</v>
+        <v>0.2794920407605136</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3539525694085282</v>
+        <v>0.352570586076865</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3625942292439459</v>
+        <v>0.357644811223298</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3798322416946763</v>
+        <v>0.3807980325274031</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.4019867013544833</v>
+        <v>0.4000028116210905</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.4053565284969917</v>
+        <v>0.4006571610081797</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3719536093618472</v>
+        <v>0.3679085899314681</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5725432951507149</v>
+        <v>0.5715720690848046</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4744984356189673</v>
+        <v>0.470761276594728</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3050193227252472</v>
+        <v>0.2983781177782549</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3650739699344572</v>
+        <v>0.3593796570380079</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>44</v>
       </c>
       <c r="C166">
-        <v>0.3470995012544706</v>
+        <v>0.3464142876319796</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3544724057355421</v>
+        <v>0.3516283424368871</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.614115150250741</v>
+        <v>0.6064224652096507</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.368090560040471</v>
+        <v>0.3674487581508515</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3705491472245697</v>
+        <v>0.3617511012569462</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>44</v>
       </c>
       <c r="C171">
-        <v>0.2636412962725487</v>
+        <v>0.2601095847181945</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4507377688796738</v>
+        <v>0.4515780879960856</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3610347389161275</v>
+        <v>0.359205679040503</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3081199017600114</v>
+        <v>0.3063556428707638</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.3361432062887905</v>
+        <v>0.3298362489438225</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4076225954532831</v>
+        <v>0.4026629395948165</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.575313154034593</v>
+        <v>0.5729334375544368</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.4206166336705622</v>
+        <v>0.4151225514301349</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3219155427982095</v>
+        <v>0.3175111760158237</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3860290995248083</v>
+        <v>0.3842450177261314</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3343575362767849</v>
+        <v>0.3328027511991101</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.3149893672484506</v>
+        <v>0.3128997364994713</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.3228210668523822</v>
+        <v>0.317009547615681</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3375247279803752</v>
+        <v>0.3334635355415005</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>15</v>
       </c>
       <c r="C185">
-        <v>0.3493140845936578</v>
+        <v>0.3448198751628412</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4322765039583277</v>
+        <v>0.429923516445045</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2413737410871</v>
+        <v>0.2370057393918104</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4859491608544575</v>
+        <v>0.4833369826390967</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3438749075360664</v>
+        <v>0.3394078900131983</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C190">
-        <v>0.2785476024702784</v>
+        <v>0.2677358374063779</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3624031903689905</v>
+        <v>0.3597245379122828</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4356359928017999</v>
+        <v>0.4319641396559481</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4739236572872539</v>
+        <v>0.4698853659521273</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3557742961409078</v>
+        <v>0.3551230224930279</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>90</v>
       </c>
       <c r="C195">
-        <v>0.3635426152846116</v>
+        <v>0.3674265355705121</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7655,10 +7655,10 @@
         <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C196">
-        <v>0.3414954242128251</v>
+        <v>0.3427007098638066</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3266679327406622</v>
+        <v>0.3242680080605463</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5623044250432531</v>
+        <v>0.5412766256287408</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6125430051275563</v>
+        <v>0.584160523273034</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>10</v>
       </c>
       <c r="C200">
-        <v>0.3387073719857271</v>
+        <v>0.3360508935521485</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3457962986129706</v>
+        <v>0.3390423572818747</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3743517246921917</v>
+        <v>0.3730451833340153</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5429971199338652</v>
+        <v>0.530071513386964</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.5186862375199359</v>
+        <v>0.5109337459889992</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4508976631949783</v>
+        <v>0.4498727134251197</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3782220559035051</v>
+        <v>0.3725712597622816</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5539401568102398</v>
+        <v>0.5522480487094877</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.4102780853458416</v>
+        <v>0.4086149538192547</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5413927187876494</v>
+        <v>0.535358365259141</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4534345217955247</v>
+        <v>0.4474591770575177</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.439416666741628</v>
+        <v>0.4342493238860198</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>10</v>
       </c>
       <c r="C212">
-        <v>0.2881211563689072</v>
+        <v>0.2851874218556277</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3691045762980391</v>
+        <v>0.3639106047434822</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3751914000070358</v>
+        <v>0.3704971027327663</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.6266573508386495</v>
+        <v>0.6239477689806501</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3377949474695567</v>
+        <v>0.3340860985100582</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3286159680771591</v>
+        <v>0.325039987078386</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3741361653400642</v>
+        <v>0.3708071697491942</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4855048758879948</v>
+        <v>0.4834469237090166</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="C220">
-        <v>0.3039043475760219</v>
+        <v>0.3012901202413699</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3668190301943769</v>
+        <v>0.3631648356356301</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>10</v>
       </c>
       <c r="C222">
-        <v>0.3039675129177595</v>
+        <v>0.2986984381783132</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.559145004915129</v>
+        <v>0.5585470800076302</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3828430335216658</v>
+        <v>0.379625970341352</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3733838150041052</v>
+        <v>0.367593854615648</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4959513437609812</v>
+        <v>0.4889632742355976</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3574968832743508</v>
+        <v>0.3541105401469736</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4816183600183679</v>
+        <v>0.4801042691536525</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5367738379176054</v>
+        <v>0.514823022013033</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3785288301989626</v>
+        <v>0.3796636330794332</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3069538930674262</v>
+        <v>0.3040984725755093</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.6497386231481003</v>
+        <v>0.6396213446286138</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.468236039387981</v>
+        <v>0.463881140870176</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4104949323252272</v>
+        <v>0.407299630991789</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5393772623810018</v>
+        <v>0.5265604752104807</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2612702022392781</v>
+        <v>0.2544151984046321</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3543692429051519</v>
+        <v>0.3515060660423022</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3222078940091243</v>
+        <v>0.3187454843865296</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4077159947115215</v>
+        <v>0.4053937802998382</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>90</v>
       </c>
       <c r="C240">
-        <v>0.3721774718566679</v>
+        <v>0.3659828005382771</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C241">
-        <v>0.2433747260458472</v>
+        <v>0.2365797828062899</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3066572761382347</v>
+        <v>0.3029198380470375</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.467528112104981</v>
+        <v>0.4615145136969455</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>90</v>
       </c>
       <c r="C244">
-        <v>0.3659217696377142</v>
+        <v>0.3609764216052976</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6713804484255201</v>
+        <v>0.6556996063224717</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4619845478485745</v>
+        <v>0.4524579893186171</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4460376994763179</v>
+        <v>0.4421069067664105</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.376431345408876</v>
+        <v>0.3730227980393712</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4769308951287688</v>
+        <v>0.4673892891495007</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3797564451442427</v>
+        <v>0.3747267412857377</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4917488824495321</v>
+        <v>0.4893986464751204</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4621345194059519</v>
+        <v>0.4610894773248488</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3672623700275011</v>
+        <v>0.3624809435957666</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4745440679804606</v>
+        <v>0.4740045897596761</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4467230938139757</v>
+        <v>0.4400104588754182</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5808962699141962</v>
+        <v>0.5727272073393423</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3972305702805617</v>
+        <v>0.3911678407612567</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.5401195914597928</v>
+        <v>0.5158455728760613</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3187354885186393</v>
+        <v>0.3121121637966094</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4082505245598554</v>
+        <v>0.4016680948012837</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4343187889360684</v>
+        <v>0.4304294965720206</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4248047082751661</v>
+        <v>0.4098832143033049</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4914265973220349</v>
+        <v>0.4868200829764714</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4195553335894438</v>
+        <v>0.4115130751747961</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3201101819094134</v>
+        <v>0.3098950655347125</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>90</v>
       </c>
       <c r="C266">
-        <v>0.3360797308459521</v>
+        <v>0.3335881192565437</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2876181657059387</v>
+        <v>0.2832379905339202</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4586770186223819</v>
+        <v>0.4563057573110308</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3777765555733613</v>
+        <v>0.3755121927242653</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5510074061370909</v>
+        <v>0.5357467880290233</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5752194339335136</v>
+        <v>0.5472665090953376</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3393085749834798</v>
+        <v>0.329767416137605</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5484497548144663</v>
+        <v>0.5391828427496783</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3566305204150331</v>
+        <v>0.3534318317217603</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2602235164734286</v>
+        <v>0.2552834466407648</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3356125217906785</v>
+        <v>0.3334980963961576</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C277">
-        <v>0.3833036982855891</v>
+        <v>0.4086115522892595</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4511810914535584</v>
+        <v>0.4463123214762043</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5819364180795003</v>
+        <v>0.5657360423902152</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4698542271897259</v>
+        <v>0.4637155656716211</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3703746920095099</v>
+        <v>0.3670883107884595</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3789099141469114</v>
+        <v>0.3750075222928968</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.39274494688999</v>
+        <v>0.3901365448432866</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3263026243309614</v>
+        <v>0.3199304532095547</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2933204873692673</v>
+        <v>0.2873051152788437</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3133903807423313</v>
+        <v>0.3094181449471252</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.5020866422744739</v>
+        <v>0.5016708193685903</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>15</v>
       </c>
       <c r="C288">
-        <v>0.2518567574199793</v>
+        <v>0.2465732638561469</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3692506217142567</v>
+        <v>0.3675150456401096</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3857685525049637</v>
+        <v>0.3826014220099081</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.479888109000133</v>
+        <v>0.4602268929723713</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>79</v>
       </c>
       <c r="C292">
-        <v>0.4370979051100437</v>
+        <v>0.486746206063516</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6394420513558626</v>
+        <v>0.6198957533641464</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.4152711526580308</v>
+        <v>0.409690806421421</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3767584980418999</v>
+        <v>0.3737032247404276</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.2807865678957987</v>
+        <v>0.2771847055905297</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.5165195832041586</v>
+        <v>0.5173973655729445</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3996531629557994</v>
+        <v>0.3948333682134985</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.3217930581193317</v>
+        <v>0.3145355796124201</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3588216202846792</v>
+        <v>0.3549704427854145</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3651607757176786</v>
+        <v>0.3620484599316319</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.5140415001731807</v>
+        <v>0.5138289255297454</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.341016039496665</v>
+        <v>0.3390941480594509</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2862679774029669</v>
+        <v>0.2805110979544425</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4642279452496298</v>
+        <v>0.4635582706491105</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4202644499284598</v>
+        <v>0.4145996241731137</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4527634361577014</v>
+        <v>0.4516763150970041</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.363707626036357</v>
+        <v>0.3597115626734285</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>10</v>
       </c>
       <c r="C309">
-        <v>0.2699507709782042</v>
+        <v>0.2673465951161779</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.4188825687795267</v>
+        <v>0.408232967534265</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3531006745579697</v>
+        <v>0.3487404067218108</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>10</v>
       </c>
       <c r="C312">
-        <v>0.3073322112340575</v>
+        <v>0.3052686911174595</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>10</v>
       </c>
       <c r="C313">
-        <v>0.2847734851528541</v>
+        <v>0.2837778384697631</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3379436281896377</v>
+        <v>0.3324916428543011</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.5112185816367065</v>
+        <v>0.5077009515781277</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.4071636140258336</v>
+        <v>0.399814116398546</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5199076383421941</v>
+        <v>0.5107413486164124</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5742442027706895</v>
+        <v>0.5665695687972865</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3142549239722319</v>
+        <v>0.3104931238537325</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2712017216778262</v>
+        <v>0.2684752809125104</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.309562728182086</v>
+        <v>0.3077015350180304</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.4335211909117278</v>
+        <v>0.4309639870595725</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.4058365174089516</v>
+        <v>0.4037207406727693</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.4210085744395568</v>
+        <v>0.4207316562536017</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>10</v>
       </c>
       <c r="C325">
-        <v>0.2749540226592071</v>
+        <v>0.2721439245213856</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>10</v>
       </c>
       <c r="C326">
-        <v>0.3629440808977026</v>
+        <v>0.3611334511097342</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3473699753843887</v>
+        <v>0.3479601964053797</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2955943871396476</v>
+        <v>0.2898840323285728</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>15</v>
       </c>
       <c r="C329">
-        <v>0.3210191544958206</v>
+        <v>0.3169055634290532</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3044819590833273</v>
+        <v>0.2993400318562207</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3621789566677379</v>
+        <v>0.3603501067594256</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3960756227371886</v>
+        <v>0.3929297893005765</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4711440114121606</v>
+        <v>0.4630761966751208</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.3027920816593779</v>
+        <v>0.2964159475548304</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3384357220007716</v>
+        <v>0.336588340599565</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.2955520573676881</v>
+        <v>0.291518623335303</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.5083904485963793</v>
+        <v>0.5085666676479978</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.3076671657252991</v>
+        <v>0.3026176483141224</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4866788728278647</v>
+        <v>0.4835737570254297</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3319224649693254</v>
+        <v>0.3250763958305026</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2562049710781969</v>
+        <v>0.2515527063979699</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2788386902775188</v>
+        <v>0.274153613802874</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4068537796651799</v>
+        <v>0.4042415201152397</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.3075110764991976</v>
+        <v>0.3045205345537625</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3635797524737669</v>
+        <v>0.3594762029946419</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3807348232669976</v>
+        <v>0.3753648305355839</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3513732134382796</v>
+        <v>0.3455718804031652</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3180399291509251</v>
+        <v>0.3074432875627549</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5355330991510647</v>
+        <v>0.5135677795918249</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3884437293359401</v>
+        <v>0.380637944351854</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>79</v>
       </c>
       <c r="C351">
-        <v>0.269424734642764</v>
+        <v>0.30767120650532</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.4332365231767719</v>
+        <v>0.4273081739045716</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3907395632429125</v>
+        <v>0.3880168246785771</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2650705888120313</v>
+        <v>0.2613237021323689</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3380656660017344</v>
+        <v>0.3301968908866532</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="C356">
-        <v>0.3253388590616574</v>
+        <v>0.3212158321852635</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4344200158129855</v>
+        <v>0.4308434270464221</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3703488318211703</v>
+        <v>0.3566295155066911</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4818351331819922</v>
+        <v>0.479474326432445</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.5018564300612518</v>
+        <v>0.4711771538299555</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3179286888901702</v>
+        <v>0.3135592526234125</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3343850199301769</v>
+        <v>0.331745313631599</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2988635787777628</v>
+        <v>0.2952343981726941</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3078490298728246</v>
+        <v>0.3017420958173301</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3155836159118277</v>
+        <v>0.3112286518482177</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2730510265689933</v>
+        <v>0.2670219647749826</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>15</v>
       </c>
       <c r="C367">
-        <v>0.3001816188839767</v>
+        <v>0.2915402487343922</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.34326543587904</v>
+        <v>0.3393718398705277</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4752978901289066</v>
+        <v>0.4648663500347679</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3677059874788612</v>
+        <v>0.3633709134090088</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.5099768483985874</v>
+        <v>0.5026088737105343</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3304779804596841</v>
+        <v>0.3251152316613581</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4283493391246398</v>
+        <v>0.4230300016133531</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.5050129438518015</v>
+        <v>0.486606835038531</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4432111578560545</v>
+        <v>0.437340702820295</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.400880816374967</v>
+        <v>0.3986313446715231</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.5222064043234128</v>
+        <v>0.5134256545794209</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.282460825437609</v>
+        <v>0.2789083149529728</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>10</v>
       </c>
       <c r="C379">
-        <v>0.3150026215436118</v>
+        <v>0.310003296042193</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3497363192872168</v>
+        <v>0.3466933329521261</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4740058115104633</v>
+        <v>0.4700892345997365</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.346764465547226</v>
+        <v>0.3454313504928811</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.373563559915764</v>
+        <v>0.37126231603825</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4919147384049176</v>
+        <v>0.4902124071192181</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3896018325778609</v>
+        <v>0.3874539757875712</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3133180531837769</v>
+        <v>0.3083202079019423</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4679781380932894</v>
+        <v>0.4659513775184309</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3572038526890338</v>
+        <v>0.3557603004203539</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3780470899693529</v>
+        <v>0.375143083036504</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3579556075963025</v>
+        <v>0.3526840368731656</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3785658851539945</v>
+        <v>0.370976101544301</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.355741699612033</v>
+        <v>0.3521032507962491</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4561117874847074</v>
+        <v>0.4557230412036504</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3828111969087217</v>
+        <v>0.3769314186539973</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4161448850851163</v>
+        <v>0.4135788296296223</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.4136607867095036</v>
+        <v>0.4122318510693349</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3900709117182337</v>
+        <v>0.3861222079851723</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.5166344469058195</v>
+        <v>0.4959586570802403</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3469227574063841</v>
+        <v>0.3438489741318798</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.317476785210755</v>
+        <v>0.3163980762472792</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4587751895135407</v>
+        <v>0.455643904593342</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.4019140610892505</v>
+        <v>0.3985413710809583</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2931894169464963</v>
+        <v>0.2910514201427636</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>44</v>
       </c>
       <c r="C404">
-        <v>0.3173854687910198</v>
+        <v>0.3136715325395758</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4205301903818507</v>
+        <v>0.411603161002154</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C406">
-        <v>0.4916167964759152</v>
+        <v>0.4921401167383042</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3817202312977135</v>
+        <v>0.3789773875830229</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4734426073990602</v>
+        <v>0.4646872914404461</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.5130959572438536</v>
+        <v>0.5082064286438356</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3302831339563063</v>
+        <v>0.3254759838537029</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3241466270282546</v>
+        <v>0.3197946781767519</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4785869478502672</v>
+        <v>0.4757372637002838</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2810957467636199</v>
+        <v>0.2762991480379078</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>10</v>
       </c>
       <c r="C414">
-        <v>0.3566670128553855</v>
+        <v>0.3541782583901451</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3420937850526287</v>
+        <v>0.338694149857548</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3742353273248115</v>
+        <v>0.3664711590326702</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.3198840271206917</v>
+        <v>0.3120896296653531</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>44</v>
       </c>
       <c r="C418">
-        <v>0.3181847601448357</v>
+        <v>0.3172456188776043</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.4143289756792773</v>
+        <v>0.409642998810138</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4528897926210088</v>
+        <v>0.4511014777436628</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4006252975805643</v>
+        <v>0.3967291701518157</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3735265231332319</v>
+        <v>0.3711147863654267</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4640165755358109</v>
+        <v>0.4649017336919584</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3325229993088122</v>
+        <v>0.3296969371904548</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3247809281701205</v>
+        <v>0.3227609808474454</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3772309142513167</v>
+        <v>0.3742120209534412</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2608351460719957</v>
+        <v>0.2566696528212971</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2793402396159717</v>
+        <v>0.2747590284037176</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3836820575179162</v>
+        <v>0.3781873244582644</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3160536192646429</v>
+        <v>0.3118507017086689</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>15</v>
       </c>
       <c r="C431">
-        <v>0.2998975711920567</v>
+        <v>0.2928670506584419</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.331597973018401</v>
+        <v>0.3286567825375022</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3185244884909684</v>
+        <v>0.3173235009287645</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3616339994183591</v>
+        <v>0.3585622753600495</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.426279773788339</v>
+        <v>0.4251448969871074</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3591371610925511</v>
+        <v>0.3539190868136093</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3331881383000567</v>
+        <v>0.3307273956499053</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3953120153372238</v>
+        <v>0.387522960156024</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3424144269501241</v>
+        <v>0.3305297324265407</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3412019405599855</v>
+        <v>0.337231621835752</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>15</v>
       </c>
       <c r="C441">
-        <v>0.3039308640375215</v>
+        <v>0.298044032831654</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3635243741334956</v>
+        <v>0.356901196531142</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3113812451305115</v>
+        <v>0.307011368204434</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3377911189301578</v>
+        <v>0.3373965553600082</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3497565401390224</v>
+        <v>0.345558195433679</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3922462912833353</v>
+        <v>0.3885195372491845</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.3041494228845325</v>
+        <v>0.3005308970286985</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3988597409304627</v>
+        <v>0.3927395997134802</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3762184921137278</v>
+        <v>0.373596095360096</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3703665128163428</v>
+        <v>0.3703940658628674</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4568756961313837</v>
+        <v>0.4546029615767068</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2827762978712109</v>
+        <v>0.2793662839734509</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3941841036599131</v>
+        <v>0.3918001031817109</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2947473069018948</v>
+        <v>0.2880072373896687</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3309425170789219</v>
+        <v>0.3265079782558651</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3505895778151284</v>
+        <v>0.3368104496784967</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3872018054345991</v>
+        <v>0.3813446338888398</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3357582341024452</v>
+        <v>0.3342329174955648</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3507381635844327</v>
+        <v>0.3434806358538459</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>15</v>
       </c>
       <c r="C460">
-        <v>0.3898248151995047</v>
+        <v>0.3818033641680585</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3292635202021108</v>
+        <v>0.3259337062344202</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>10</v>
       </c>
       <c r="C462">
-        <v>0.3020884787026801</v>
+        <v>0.2984958893624328</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3290988686133663</v>
+        <v>0.3243299808650127</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4401225507382625</v>
+        <v>0.4231239800959847</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.4056166773141336</v>
+        <v>0.4056076483756846</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5711362775788509</v>
+        <v>0.5596277970509876</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4615192046468659</v>
+        <v>0.4521557149116521</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.4069828858218998</v>
+        <v>0.4019611026499396</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.3018741319553296</v>
+        <v>0.2973591291999924</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.337776417518129</v>
+        <v>0.3317357216997716</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3351166778175548</v>
+        <v>0.3337370101010737</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3616106943071908</v>
+        <v>0.3591736066826279</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3561869227662535</v>
+        <v>0.3533643581800312</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3880470330068618</v>
+        <v>0.3847727530628554</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3742631477366594</v>
+        <v>0.3698874186053104</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3166353472815191</v>
+        <v>0.3131162654506845</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>15</v>
       </c>
       <c r="C477">
-        <v>0.3534526540337829</v>
+        <v>0.3491023713723275</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4223264987054359</v>
+        <v>0.4213605830994959</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4200488163297086</v>
+        <v>0.4180003837685235</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4514351849346507</v>
+        <v>0.4453502421266167</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3811394420795335</v>
+        <v>0.3792799669648689</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3288384918364493</v>
+        <v>0.3261032386568871</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3446280567111195</v>
+        <v>0.3425985754053199</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3820042284062229</v>
+        <v>0.3787477239025471</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.4024708034122653</v>
+        <v>0.3950721030284169</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.4226357280140805</v>
+        <v>0.416995168831459</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4509265078934047</v>
+        <v>0.4492242609525252</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3837807891370171</v>
+        <v>0.3779315381115447</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4968743394763223</v>
+        <v>0.484355452486484</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3428082574731809</v>
+        <v>0.3395734071927177</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>15</v>
       </c>
       <c r="C491">
-        <v>0.281045675292399</v>
+        <v>0.276806746553911</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.5304550786594751</v>
+        <v>0.4999140627748311</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3295031102426207</v>
+        <v>0.3261759260719906</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>44</v>
       </c>
       <c r="C494">
-        <v>0.3193176679625419</v>
+        <v>0.3144698561178459</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5471474828345227</v>
+        <v>0.5464291554632484</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4905229698219487</v>
+        <v>0.4871059457615867</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3751617727867874</v>
+        <v>0.369356228360872</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.7208180903680157</v>
+        <v>0.6990401241405413</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.4164872252154111</v>
+        <v>0.4114278043485819</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3943267507387416</v>
+        <v>0.3886298683993562</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3728521907159971</v>
+        <v>0.3664631868487004</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.6301891065138235</v>
+        <v>0.615994367220091</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3821492204497333</v>
+        <v>0.3737009139590765</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3123464980621902</v>
+        <v>0.306685729211892</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4573156491572166</v>
+        <v>0.4533850176780899</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4966510128918018</v>
+        <v>0.4906347149838955</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.3226515520479352</v>
+        <v>0.318034494234029</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3581285198657512</v>
+        <v>0.3499279547098815</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4868700420546586</v>
+        <v>0.4871169910017538</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3832140657500053</v>
+        <v>0.3791164715424325</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.4002956522463696</v>
+        <v>0.3984104313729391</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2945093231863476</v>
+        <v>0.2927760512283072</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.389275447609536</v>
+        <v>0.3819438445224634</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.4245501843823383</v>
+        <v>0.4249131398562046</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5617419992367746</v>
+        <v>0.5480627802357901</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3103045015107687</v>
+        <v>0.308006647019007</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3360781606157007</v>
+        <v>0.3317361866030943</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3342259312229136</v>
+        <v>0.3310945920211142</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.481233076827528</v>
+        <v>0.4801018212364839</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3477510435961427</v>
+        <v>0.3423448541208454</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3332957457588769</v>
+        <v>0.3287231787463962</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3739859518526156</v>
+        <v>0.3684477926033294</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4547305845510159</v>
+        <v>0.4522050526536761</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2949141063007796</v>
+        <v>0.2876506084706189</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4526918593537551</v>
+        <v>0.4459967989335649</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.452569278729548</v>
+        <v>0.4485744324122278</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3761839404766265</v>
+        <v>0.3722775368526367</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4737974547594956</v>
+        <v>0.4676748415016272</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3481609487251634</v>
+        <v>0.3461130979107216</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.5070412521509874</v>
+        <v>0.5044745212910274</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.6060838145642971</v>
+        <v>0.6030733673507404</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>44</v>
       </c>
       <c r="C532">
-        <v>0.3157390365205732</v>
+        <v>0.3132517331555756</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4727195100380562</v>
+        <v>0.4656702283479625</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3199035927362817</v>
+        <v>0.3114998073613152</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3023043600393073</v>
+        <v>0.3001928280825698</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3221586764954804</v>
+        <v>0.3171837533315937</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.4222813201451429</v>
+        <v>0.4152060755926826</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2949399381791736</v>
+        <v>0.2907657776595584</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3095952973161565</v>
+        <v>0.3060678668152193</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2881023938442137</v>
+        <v>0.283939379391095</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4452570861377024</v>
+        <v>0.4416864847108284</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.4030427253243088</v>
+        <v>0.4003353632535511</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.4522944302958911</v>
+        <v>0.4343917864809401</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3765856908900599</v>
+        <v>0.3728560145159255</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15387,7 +15387,7 @@
         <v>79</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -77,6 +77,9 @@
     <t>ashfield</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>E14001068</t>
   </si>
   <si>
@@ -285,9 +288,6 @@
   </si>
   <si>
     <t>blackburn</t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>E14001102</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2707688023253016</v>
+        <v>0.2732395136851172</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4273550040153515</v>
+        <v>0.3993823086053072</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3721229598856683</v>
+        <v>0.3666681949988029</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3557925576187628</v>
+        <v>0.3333148689926222</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3941300358670415</v>
+        <v>0.3510355070779581</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4442,588 +4442,588 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>0.2830914975431358</v>
+        <v>0.2832283208693455</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3653476068513238</v>
+        <v>0.3465683265117847</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3412451391907707</v>
+        <v>0.3109956190612335</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3464507969288235</v>
+        <v>0.3222205598462528</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2539011792253815</v>
+        <v>0.2476629360983871</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4147227394802035</v>
+        <v>0.4111456985443812</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3247670644942205</v>
+        <v>0.2962053799676988</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.4307827381421535</v>
+        <v>0.3855110348463691</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3553771857214677</v>
+        <v>0.3338585957311285</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.2933009965118885</v>
+        <v>0.2836049670263135</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2753778203808029</v>
+        <v>0.2728312828792824</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2947385930946325</v>
+        <v>0.2795082447941284</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19">
-        <v>0.4360049105756226</v>
+        <v>0.4194729223340706</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4189960882201127</v>
+        <v>0.3933161990023065</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4361717024392023</v>
+        <v>0.3867408118256472</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.327776106359753</v>
+        <v>0.3186303566815537</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3969006339241101</v>
+        <v>0.3816454654806094</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3439240076363249</v>
+        <v>0.3158250984910693</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6223155428152148</v>
+        <v>0.5705131187879788</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3073101306719332</v>
+        <v>0.3069946589709277</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2844572302731646</v>
+        <v>0.2706583924026896</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3176173211194649</v>
+        <v>0.2998420790755987</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C29">
-        <v>0.4788310853692099</v>
+        <v>0.4643350221357704</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.378042005269581</v>
+        <v>0.352512239710294</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4242921960687304</v>
+        <v>0.4055323808440809</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4226553042105923</v>
+        <v>0.3926119523985971</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3901552397622838</v>
+        <v>0.3555112152011001</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3312561804615002</v>
+        <v>0.3090915708881617</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4669123446346876</v>
+        <v>0.4287422943562835</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36">
-        <v>0.2625399423195997</v>
+        <v>0.2549795254211109</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.2991815861609693</v>
+        <v>0.2834463060736293</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3375690440010488</v>
+        <v>0.3253392066303707</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3678491486038083</v>
+        <v>0.3407688887049003</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4606636025130146</v>
+        <v>0.4436582056613935</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C41">
-        <v>0.2721692936521675</v>
+        <v>0.2749760614344846</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5414220825177557</v>
+        <v>0.5191910470472684</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.4060875385124043</v>
+        <v>0.3867159166450228</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.411634669568714</v>
+        <v>0.3871284132921279</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.39770654985971</v>
+        <v>0.3774297046853012</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4339180874155192</v>
+        <v>0.4156876074399146</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2915652766643496</v>
+        <v>0.2861443703421916</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4233680717804375</v>
+        <v>0.397489707599648</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3435176319205248</v>
+        <v>0.3292253863156944</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3823714107828452</v>
+        <v>0.3563386933955707</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3616264468180383</v>
+        <v>0.3343999921068679</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5261927823127682</v>
+        <v>0.5028252942314915</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.441997107079971</v>
+        <v>0.4170155739579671</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3934991594526069</v>
+        <v>0.3840835386522008</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2849570389199365</v>
+        <v>0.2680288583156998</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3558654344054911</v>
+        <v>0.3310817579738206</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5816727349403208</v>
+        <v>0.5382685942049356</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>15</v>
       </c>
       <c r="C58">
-        <v>0.3304942310832242</v>
+        <v>0.3063925062734232</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.4023510367548296</v>
+        <v>0.3630166565500669</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.2761861902523435</v>
+        <v>0.28034462940937</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3428988857524589</v>
+        <v>0.3343190539378091</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3455134135112166</v>
+        <v>0.3132311139192334</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3715722676211589</v>
+        <v>0.3563511504840943</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5411,10 +5411,10 @@
         <v>136</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C64">
-        <v>0.2369168953961513</v>
+        <v>0.2313794876144904</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3340518525879855</v>
+        <v>0.3218859423546621</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3305173626011721</v>
+        <v>0.3202592974782623</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3624983250487309</v>
+        <v>0.3436566611342001</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2562574243338254</v>
+        <v>0.2494182359711944</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5496,10 +5496,10 @@
         <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C69">
-        <v>0.6303965300737046</v>
+        <v>0.5672836486833495</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5513,10 +5513,10 @@
         <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C70">
-        <v>0.5617303980475821</v>
+        <v>0.5225325306877003</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.480411174447221</v>
+        <v>0.4330225069301216</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3616993955647609</v>
+        <v>0.3360167606023098</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.5357651501135829</v>
+        <v>0.4896640890778335</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4845437728885268</v>
+        <v>0.4371959091734038</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2541955445262615</v>
+        <v>0.2428192051911606</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3809370408374679</v>
+        <v>0.3477989834865634</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3488099600822705</v>
+        <v>0.320795777391552</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4317646871450993</v>
+        <v>0.4031862397350496</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>0.2500509288923488</v>
+        <v>0.2535830912134504</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3763295152472192</v>
+        <v>0.3449869704744172</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.318127218475848</v>
+        <v>0.2965520408900267</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4312318788542558</v>
+        <v>0.3993035234758795</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.396635457080874</v>
+        <v>0.3865852541764806</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>15</v>
       </c>
       <c r="C84">
-        <v>0.2999412811216872</v>
+        <v>0.2949678120888177</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3471447810830471</v>
+        <v>0.3304689942792156</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.2891873074079594</v>
+        <v>0.2801835306101984</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.262716332460824</v>
+        <v>0.2617267840375349</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5819,10 +5819,10 @@
         <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C88">
-        <v>0.3586697590136387</v>
+        <v>0.3316067571380222</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5836,10 +5836,10 @@
         <v>186</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C89">
-        <v>0.304093917974551</v>
+        <v>0.2937954515916378</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2887036086633403</v>
+        <v>0.2678799846485569</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5870,10 +5870,10 @@
         <v>190</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2666599847064514</v>
+        <v>0.2683314013744097</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5887,10 +5887,10 @@
         <v>192</v>
       </c>
       <c r="B92" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C92">
-        <v>0.339259539149075</v>
+        <v>0.3375133441215455</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.4025063195184892</v>
+        <v>0.3834210818534879</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.2634342665085479</v>
+        <v>0.2567264356363955</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3249173539227785</v>
+        <v>0.3158378124719264</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3847829847262648</v>
+        <v>0.3615994437072197</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5972,10 +5972,10 @@
         <v>202</v>
       </c>
       <c r="B97" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C97">
-        <v>0.3621818003696727</v>
+        <v>0.3578729993117989</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5989,10 +5989,10 @@
         <v>204</v>
       </c>
       <c r="B98" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C98">
-        <v>0.3663540130078058</v>
+        <v>0.3623239501331408</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4344227560630397</v>
+        <v>0.4056975187596664</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6023,10 +6023,10 @@
         <v>208</v>
       </c>
       <c r="B100" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C100">
-        <v>0.40043261148049</v>
+        <v>0.3918375627670607</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6040,10 +6040,10 @@
         <v>210</v>
       </c>
       <c r="B101" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C101">
-        <v>0.4581797797144687</v>
+        <v>0.4519795971934741</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.455724614425064</v>
+        <v>0.4290823611102275</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3498833412686107</v>
+        <v>0.3389445254708947</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3633097905611046</v>
+        <v>0.3402615552965701</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6108,10 +6108,10 @@
         <v>218</v>
       </c>
       <c r="B105" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C105">
-        <v>0.3507620203388998</v>
+        <v>0.3512033665479103</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.4055375610684723</v>
+        <v>0.3713434697734791</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6142,10 +6142,10 @@
         <v>222</v>
       </c>
       <c r="B107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C107">
-        <v>0.3508890499335309</v>
+        <v>0.3503301116799097</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4049777632437482</v>
+        <v>0.396813674338575</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6176,10 +6176,10 @@
         <v>226</v>
       </c>
       <c r="B109" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C109">
-        <v>0.264161745185849</v>
+        <v>0.2623724599497705</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2915435292569892</v>
+        <v>0.2839820020161116</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.5329921238719034</v>
+        <v>0.490884790317633</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3848545588968632</v>
+        <v>0.3604755931247435</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.525927124703529</v>
+        <v>0.4856537038614581</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.668061393160153</v>
+        <v>0.5949318974436387</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3090130497852639</v>
+        <v>0.3025276460356449</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4423518019096727</v>
+        <v>0.4317564378425923</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6312,10 +6312,10 @@
         <v>242</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2733264992622443</v>
+        <v>0.2644812967283403</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.4049727985965608</v>
+        <v>0.3748404086447688</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3753697405417786</v>
+        <v>0.3652763938157373</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3715785922883789</v>
+        <v>0.3439644831100909</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.3113720368055873</v>
+        <v>0.2910252931523665</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3472863770556365</v>
+        <v>0.3274030589132348</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2977328383852423</v>
+        <v>0.2900734829936261</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3863200256804191</v>
+        <v>0.367631298368318</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C125">
-        <v>0.2845880307006517</v>
+        <v>0.2780558536637699</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3780114004616743</v>
+        <v>0.367713448233465</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.5035276801037192</v>
+        <v>0.4769618159002622</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4409548223810976</v>
+        <v>0.3963609585658288</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="C129">
-        <v>0.2981279624026634</v>
+        <v>0.2855799310364898</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.4607930045110125</v>
+        <v>0.433125564990629</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2795737786263787</v>
+        <v>0.2650142077228216</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3606924208088326</v>
+        <v>0.3572959683556816</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3469232179208231</v>
+        <v>0.3222891266486957</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3178345101267935</v>
+        <v>0.3194544706754181</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3498487195078078</v>
+        <v>0.3274551342623792</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6635,10 +6635,10 @@
         <v>280</v>
       </c>
       <c r="B136" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C136">
-        <v>0.3499424984851879</v>
+        <v>0.3393765780999465</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3933209787178658</v>
+        <v>0.3748268378382502</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>15</v>
       </c>
       <c r="C138">
-        <v>0.3179710458229442</v>
+        <v>0.3098970714053071</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4402757647939984</v>
+        <v>0.4194437970379778</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6703,10 +6703,10 @@
         <v>288</v>
       </c>
       <c r="B140" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C140">
-        <v>0.4070122175367404</v>
+        <v>0.4064580817836484</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3439640069237996</v>
+        <v>0.3369089305648181</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.4055534461997542</v>
+        <v>0.3720076633968321</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>15</v>
       </c>
       <c r="C143">
-        <v>0.304135463461537</v>
+        <v>0.2871559190517126</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.564188157039164</v>
+        <v>0.515024418052678</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2655238711819132</v>
+        <v>0.266984799425953</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4406535218267651</v>
+        <v>0.4134114368788093</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4394390304887004</v>
+        <v>0.4191708620130175</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3331830173678353</v>
+        <v>0.320675297926122</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.385596584360534</v>
+        <v>0.3497384917362218</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3428805136849269</v>
+        <v>0.3144011441009629</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2503822374398392</v>
+        <v>0.2334886221640672</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6930778180921288</v>
+        <v>0.6192215421305959</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3507530793377277</v>
+        <v>0.3218681128533195</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="C154">
-        <v>0.3395075839022036</v>
+        <v>0.3113456447159945</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="C155">
-        <v>0.2794920407605136</v>
+        <v>0.2696032734794893</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.352570586076865</v>
+        <v>0.3289693694554722</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.357644811223298</v>
+        <v>0.3512362884190388</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7009,10 +7009,10 @@
         <v>324</v>
       </c>
       <c r="B158" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C158">
-        <v>0.3807980325274031</v>
+        <v>0.3771225999672054</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7026,10 +7026,10 @@
         <v>326</v>
       </c>
       <c r="B159" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C159">
-        <v>0.4000028116210905</v>
+        <v>0.3882265911025024</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.4006571610081797</v>
+        <v>0.3831075266295019</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3679085899314681</v>
+        <v>0.3564391503642897</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5715720690848046</v>
+        <v>0.5391323946831142</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7094,10 +7094,10 @@
         <v>334</v>
       </c>
       <c r="B163" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C163">
-        <v>0.470761276594728</v>
+        <v>0.4495152484915196</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.2983781177782549</v>
+        <v>0.2833621580266551</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3593796570380079</v>
+        <v>0.3337881873494717</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C166">
-        <v>0.3464142876319796</v>
+        <v>0.3456002432341783</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3516283424368871</v>
+        <v>0.3421101258309006</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.6064224652096507</v>
+        <v>0.5572880857822303</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7196,10 +7196,10 @@
         <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C169">
-        <v>0.3674487581508515</v>
+        <v>0.3657992064474962</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3617511012569462</v>
+        <v>0.3458474452844516</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C171">
-        <v>0.2601095847181945</v>
+        <v>0.2551874296601972</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4515780879960856</v>
+        <v>0.4211231823575422</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.359205679040503</v>
+        <v>0.3247734659088505</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3063556428707638</v>
+        <v>0.3073607236787221</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.3298362489438225</v>
+        <v>0.3047444451293809</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4026629395948165</v>
+        <v>0.3876622383107603</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5729334375544368</v>
+        <v>0.5318517134163941</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.4151225514301349</v>
+        <v>0.3893141370280193</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3175111760158237</v>
+        <v>0.3080403558816855</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7383,10 +7383,10 @@
         <v>368</v>
       </c>
       <c r="B180" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C180">
-        <v>0.3842450177261314</v>
+        <v>0.3744440790336231</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3328027511991101</v>
+        <v>0.3318277701772704</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.3128997364994713</v>
+        <v>0.2934839507389534</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.317009547615681</v>
+        <v>0.305558146972186</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3334635355415005</v>
+        <v>0.3257687424554845</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>15</v>
       </c>
       <c r="C185">
-        <v>0.3448198751628412</v>
+        <v>0.3350558984248939</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7485,10 +7485,10 @@
         <v>380</v>
       </c>
       <c r="B186" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C186">
-        <v>0.429923516445045</v>
+        <v>0.4310029511697319</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2370057393918104</v>
+        <v>0.2372961787880213</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4833369826390967</v>
+        <v>0.4390984212272475</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3394078900131983</v>
+        <v>0.316496737199386</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2677358374063779</v>
+        <v>0.2577324375382284</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3597245379122828</v>
+        <v>0.333135099914439</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4319641396559481</v>
+        <v>0.4063638862920527</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4698853659521273</v>
+        <v>0.4291584686892414</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3551230224930279</v>
+        <v>0.3553428603335652</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7638,10 +7638,10 @@
         <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C195">
-        <v>0.3674265355705121</v>
+        <v>0.3686992557310674</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7655,10 +7655,10 @@
         <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C196">
-        <v>0.3427007098638066</v>
+        <v>0.3196407977631342</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3242680080605463</v>
+        <v>0.2975237827880578</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5412766256287408</v>
+        <v>0.4832734482567372</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.584160523273034</v>
+        <v>0.536530830944757</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>10</v>
       </c>
       <c r="C200">
-        <v>0.3360508935521485</v>
+        <v>0.3189990371125813</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3390423572818747</v>
+        <v>0.3091005831135611</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3730451833340153</v>
+        <v>0.3415345227041416</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.530071513386964</v>
+        <v>0.4820322905126632</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.5109337459889992</v>
+        <v>0.4720492890699459</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4498727134251197</v>
+        <v>0.4079002439392426</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3725712597622816</v>
+        <v>0.3509326760882177</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7842,10 +7842,10 @@
         <v>422</v>
       </c>
       <c r="B207" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C207">
-        <v>0.5522480487094877</v>
+        <v>0.5253263102563502</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7859,10 +7859,10 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C208">
-        <v>0.4086149538192547</v>
+        <v>0.415897979195919</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.535358365259141</v>
+        <v>0.47682645304833</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4474591770575177</v>
+        <v>0.4197551789507116</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4342493238860198</v>
+        <v>0.4057323684344987</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2851874218556277</v>
+        <v>0.2772820745388682</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3639106047434822</v>
+        <v>0.3474177839772552</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3704971027327663</v>
+        <v>0.358323130545646</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.6239477689806501</v>
+        <v>0.5678678779039124</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3340860985100582</v>
+        <v>0.3180583156170301</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.325039987078386</v>
+        <v>0.3148534232701697</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3708071697491942</v>
+        <v>0.3635582730744681</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8046,10 +8046,10 @@
         <v>446</v>
       </c>
       <c r="B219" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C219">
-        <v>0.4834469237090166</v>
+        <v>0.4787128209948535</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="C220">
-        <v>0.3012901202413699</v>
+        <v>0.2848139868626538</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3631648356356301</v>
+        <v>0.3485697389467239</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C222">
-        <v>0.2986984381783132</v>
+        <v>0.2947821968570619</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5585470800076302</v>
+        <v>0.513523819121123</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.379625970341352</v>
+        <v>0.3482339833248665</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.367593854615648</v>
+        <v>0.3465018811394917</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4889632742355976</v>
+        <v>0.4522929765223401</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3541105401469736</v>
+        <v>0.3261427236224995</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4801042691536525</v>
+        <v>0.4478647876220882</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.514823022013033</v>
+        <v>0.4679499655967116</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8233,10 +8233,10 @@
         <v>468</v>
       </c>
       <c r="B230" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C230">
-        <v>0.3796636330794332</v>
+        <v>0.3793067223448619</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3040984725755093</v>
+        <v>0.3087760857063826</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.6396213446286138</v>
+        <v>0.5738775021817857</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8284,10 +8284,10 @@
         <v>474</v>
       </c>
       <c r="B233" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C233">
-        <v>0.463881140870176</v>
+        <v>0.4604257737646199</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.407299630991789</v>
+        <v>0.3898769720030905</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5265604752104807</v>
+        <v>0.4775875319625823</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2544151984046321</v>
+        <v>0.2507865641714971</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3515060660423022</v>
+        <v>0.3243289094624282</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3187454843865296</v>
+        <v>0.3089225347785897</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4053937802998382</v>
+        <v>0.3910619808032776</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8403,10 +8403,10 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C240">
-        <v>0.3659828005382771</v>
+        <v>0.3511545042527324</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C241">
-        <v>0.2365797828062899</v>
+        <v>0.2319251259728439</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3029198380470375</v>
+        <v>0.3043682882542799</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4615145136969455</v>
+        <v>0.4257755907431912</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8471,10 +8471,10 @@
         <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C244">
-        <v>0.3609764216052976</v>
+        <v>0.3514922078411835</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6556996063224717</v>
+        <v>0.5871540315280875</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4524579893186171</v>
+        <v>0.4339542752247665</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4421069067664105</v>
+        <v>0.4258583993765638</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3730227980393712</v>
+        <v>0.3365203208521267</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4673892891495007</v>
+        <v>0.4327909918464454</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3747267412857377</v>
+        <v>0.3536651453158876</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8590,10 +8590,10 @@
         <v>510</v>
       </c>
       <c r="B251" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C251">
-        <v>0.4893986464751204</v>
+        <v>0.4719406442989078</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4610894773248488</v>
+        <v>0.4330290601764087</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3624809435957666</v>
+        <v>0.3482805964284796</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4740045897596761</v>
+        <v>0.453590307584794</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4400104588754182</v>
+        <v>0.4082341301306797</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5727272073393423</v>
+        <v>0.5312402467327827</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3911678407612567</v>
+        <v>0.369037843466496</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.5158455728760613</v>
+        <v>0.4804646438274022</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3121121637966094</v>
+        <v>0.3045076943275314</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4016680948012837</v>
+        <v>0.3872407740974299</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4304294965720206</v>
+        <v>0.4103948820437387</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4098832143033049</v>
+        <v>0.371407847685944</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4868200829764714</v>
+        <v>0.458901369758199</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4115130751747961</v>
+        <v>0.3877591326375837</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3098950655347125</v>
+        <v>0.2934466826849581</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="C266">
-        <v>0.3335881192565437</v>
+        <v>0.3288719298568865</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2832379905339202</v>
+        <v>0.2780323813965551</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4563057573110308</v>
+        <v>0.4266915723281238</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8896,10 +8896,10 @@
         <v>546</v>
       </c>
       <c r="B269" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C269">
-        <v>0.3755121927242653</v>
+        <v>0.3652960342650693</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5357467880290233</v>
+        <v>0.4885303441501425</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5472665090953376</v>
+        <v>0.4884026929138592</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.329767416137605</v>
+        <v>0.3159308800354828</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5391828427496783</v>
+        <v>0.4946677818070228</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3534318317217603</v>
+        <v>0.3410156712608597</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2552834466407648</v>
+        <v>0.2506895755622416</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3334980963961576</v>
+        <v>0.3201052333980147</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C277">
-        <v>0.4086115522892595</v>
+        <v>0.3981536929910262</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4463123214762043</v>
+        <v>0.4372629958065475</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5657360423902152</v>
+        <v>0.5282563737210509</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4637155656716211</v>
+        <v>0.4468697236387886</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3670883107884595</v>
+        <v>0.3602800968706564</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3750075222928968</v>
+        <v>0.3590048688977155</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3901365448432866</v>
+        <v>0.3791757417003581</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3199304532095547</v>
+        <v>0.3074120796310096</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2873051152788437</v>
+        <v>0.2757887573314627</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3094181449471252</v>
+        <v>0.3063422548835616</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9202,10 +9202,10 @@
         <v>582</v>
       </c>
       <c r="B287" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C287">
-        <v>0.5016708193685903</v>
+        <v>0.4878842402089424</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>15</v>
       </c>
       <c r="C288">
-        <v>0.2465732638561469</v>
+        <v>0.2464437791351542</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3675150456401096</v>
+        <v>0.3569184580174412</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3826014220099081</v>
+        <v>0.3595185772025217</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4602268929723713</v>
+        <v>0.4291926544740748</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C292">
-        <v>0.486746206063516</v>
+        <v>0.4680035070011875</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6198957533641464</v>
+        <v>0.5707380766841614</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.409690806421421</v>
+        <v>0.3844822960153834</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3737032247404276</v>
+        <v>0.3509829337434293</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.2771847055905297</v>
+        <v>0.2742862509406211</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.5173973655729445</v>
+        <v>0.4752656084850989</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3948333682134985</v>
+        <v>0.3651811968577741</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9406,10 +9406,10 @@
         <v>606</v>
       </c>
       <c r="B299" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C299">
-        <v>0.3145355796124201</v>
+        <v>0.3017454308359744</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3549704427854145</v>
+        <v>0.328607104605971</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3620484599316319</v>
+        <v>0.3520854427446481</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9457,10 +9457,10 @@
         <v>612</v>
       </c>
       <c r="B302" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C302">
-        <v>0.5138289255297454</v>
+        <v>0.4977970281073916</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3390941480594509</v>
+        <v>0.3209774210827143</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C304">
-        <v>0.2805110979544425</v>
+        <v>0.2717254781879639</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9508,10 +9508,10 @@
         <v>618</v>
       </c>
       <c r="B305" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C305">
-        <v>0.4635582706491105</v>
+        <v>0.449829688823387</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4145996241731137</v>
+        <v>0.3821715932856783</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4516763150970041</v>
+        <v>0.438812873605348</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3597115626734285</v>
+        <v>0.3537888278641893</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>10</v>
       </c>
       <c r="C309">
-        <v>0.2673465951161779</v>
+        <v>0.2542405840586017</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.408232967534265</v>
+        <v>0.3714737845246933</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3487404067218108</v>
+        <v>0.3343371802313397</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>10</v>
       </c>
       <c r="C312">
-        <v>0.3052686911174595</v>
+        <v>0.2861827833800425</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9644,10 +9644,10 @@
         <v>634</v>
       </c>
       <c r="B313" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C313">
-        <v>0.2837778384697631</v>
+        <v>0.2662489440577941</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3324916428543011</v>
+        <v>0.3079549116179478</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9678,10 +9678,10 @@
         <v>638</v>
       </c>
       <c r="B315" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C315">
-        <v>0.5077009515781277</v>
+        <v>0.4828283379038344</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.399814116398546</v>
+        <v>0.3746650958547679</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5107413486164124</v>
+        <v>0.468304007361598</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5665695687972865</v>
+        <v>0.5176790857026109</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3104931238537325</v>
+        <v>0.3048266776722032</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2684752809125104</v>
+        <v>0.2632994408666604</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3077015350180304</v>
+        <v>0.3099762972793331</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.4309639870595725</v>
+        <v>0.410326911998559</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.4037207406727693</v>
+        <v>0.370316961873501</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9831,10 +9831,10 @@
         <v>656</v>
       </c>
       <c r="B324" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C324">
-        <v>0.4207316562536017</v>
+        <v>0.4105986791850854</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>10</v>
       </c>
       <c r="C325">
-        <v>0.2721439245213856</v>
+        <v>0.2547994001785602</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9865,10 +9865,10 @@
         <v>660</v>
       </c>
       <c r="B326" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C326">
-        <v>0.3611334511097342</v>
+        <v>0.3614333388584811</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9882,10 +9882,10 @@
         <v>662</v>
       </c>
       <c r="B327" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C327">
-        <v>0.3479601964053797</v>
+        <v>0.3486507738444576</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2898840323285728</v>
+        <v>0.2721056644938017</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>15</v>
       </c>
       <c r="C329">
-        <v>0.3169055634290532</v>
+        <v>0.3028255571915233</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C330">
-        <v>0.2993400318562207</v>
+        <v>0.295131447797671</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3603501067594256</v>
+        <v>0.3404296569513102</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3929297893005765</v>
+        <v>0.3573375418612609</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4630761966751208</v>
+        <v>0.4341160489667888</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C334">
-        <v>0.2964159475548304</v>
+        <v>0.2854775989190521</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.336588340599565</v>
+        <v>0.3168912580287356</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.291518623335303</v>
+        <v>0.2774996633904437</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10052,10 +10052,10 @@
         <v>682</v>
       </c>
       <c r="B337" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C337">
-        <v>0.5085666676479978</v>
+        <v>0.4889199285138132</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.3026176483141224</v>
+        <v>0.2795102268385413</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4835737570254297</v>
+        <v>0.4561556155866121</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3250763958305026</v>
+        <v>0.3095445296297069</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2515527063979699</v>
+        <v>0.2487223303728552</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.274153613802874</v>
+        <v>0.258480564928115</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4042415201152397</v>
+        <v>0.3749100899428632</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.3045205345537625</v>
+        <v>0.2931209066013535</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3594762029946419</v>
+        <v>0.3497374609188618</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3753648305355839</v>
+        <v>0.3479384373158478</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3455718804031652</v>
+        <v>0.3258704387773306</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3074432875627549</v>
+        <v>0.2921907284093073</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5135677795918249</v>
+        <v>0.4806258351266455</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.380637944351854</v>
+        <v>0.3547018272596593</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C351">
-        <v>0.30767120650532</v>
+        <v>0.2903366521035799</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.4273081739045716</v>
+        <v>0.3969695416588596</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3880168246785771</v>
+        <v>0.3637719562022336</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2613237021323689</v>
+        <v>0.2607843142586349</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3301968908866532</v>
+        <v>0.3152838223407323</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="C356">
-        <v>0.3212158321852635</v>
+        <v>0.3016488005168317</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4308434270464221</v>
+        <v>0.4088642502362704</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3566295155066911</v>
+        <v>0.3262332819466302</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10426,10 +10426,10 @@
         <v>726</v>
       </c>
       <c r="B359" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C359">
-        <v>0.479474326432445</v>
+        <v>0.4625614990377774</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4711771538299555</v>
+        <v>0.4380897720356673</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3135592526234125</v>
+        <v>0.3042809108881442</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.331745313631599</v>
+        <v>0.3235028717685948</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2952343981726941</v>
+        <v>0.2810243734241137</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3017420958173301</v>
+        <v>0.2809045886549856</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3112286518482177</v>
+        <v>0.3038825354732409</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2670219647749826</v>
+        <v>0.2591150616191807</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>15</v>
       </c>
       <c r="C367">
-        <v>0.2915402487343922</v>
+        <v>0.27871374350084</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3393718398705277</v>
+        <v>0.3214172811427258</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4648663500347679</v>
+        <v>0.4252675330797375</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3633709134090088</v>
+        <v>0.34454180083186</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.5026088737105343</v>
+        <v>0.4586015513210037</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3251152316613581</v>
+        <v>0.3104425016267333</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4230300016133531</v>
+        <v>0.3973124680360511</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.486606835038531</v>
+        <v>0.4342764392813563</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.437340702820295</v>
+        <v>0.4138096697532855</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3986313446715231</v>
+        <v>0.3814901269075194</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.5134256545794209</v>
+        <v>0.4627443205341789</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.2789083149529728</v>
+        <v>0.2790264548815291</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10766,10 +10766,10 @@
         <v>766</v>
       </c>
       <c r="B379" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C379">
-        <v>0.310003296042193</v>
+        <v>0.30402367151835</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3466933329521261</v>
+        <v>0.3398330080369503</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4700892345997365</v>
+        <v>0.4245001583495382</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3454313504928811</v>
+        <v>0.3369444667297006</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.37126231603825</v>
+        <v>0.345562983344772</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10851,10 +10851,10 @@
         <v>776</v>
       </c>
       <c r="B384" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C384">
-        <v>0.4902124071192181</v>
+        <v>0.4742303476598229</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3874539757875712</v>
+        <v>0.3720829383935021</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3083202079019423</v>
+        <v>0.2994732272138844</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4659513775184309</v>
+        <v>0.4346799178935959</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10919,10 +10919,10 @@
         <v>784</v>
       </c>
       <c r="B388" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C388">
-        <v>0.3557603004203539</v>
+        <v>0.3498885679269799</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.375143083036504</v>
+        <v>0.363277109307553</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3526840368731656</v>
+        <v>0.3378144772658636</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.370976101544301</v>
+        <v>0.339498613701158</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3521032507962491</v>
+        <v>0.3275957562094902</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4557230412036504</v>
+        <v>0.4084781932188881</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3769314186539973</v>
+        <v>0.352631639915378</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4135788296296223</v>
+        <v>0.3776899193248638</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.4122318510693349</v>
+        <v>0.3962803967435647</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3861222079851723</v>
+        <v>0.3512364645341589</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4959586570802403</v>
+        <v>0.4682400225829401</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3438489741318798</v>
+        <v>0.3234851725768356</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3163980762472792</v>
+        <v>0.3186550814509799</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.455643904593342</v>
+        <v>0.424869773517303</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3985413710809583</v>
+        <v>0.3730426564933626</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2910514201427636</v>
+        <v>0.2900061356713853</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C404">
-        <v>0.3136715325395758</v>
+        <v>0.3175047775126165</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.411603161002154</v>
+        <v>0.3930068838017378</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C406">
-        <v>0.4921401167383042</v>
+        <v>0.4777576219765692</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3789773875830229</v>
+        <v>0.3511848215070617</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4646872914404461</v>
+        <v>0.4281911595605447</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.5082064286438356</v>
+        <v>0.4718092660774478</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3254759838537029</v>
+        <v>0.3131463525423306</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3197946781767519</v>
+        <v>0.3038333958684844</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4757372637002838</v>
+        <v>0.4396536440173752</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2762991480379078</v>
+        <v>0.2680321768169744</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>10</v>
       </c>
       <c r="C414">
-        <v>0.3541782583901451</v>
+        <v>0.3300139068429414</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.338694149857548</v>
+        <v>0.3251022796321989</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3664711590326702</v>
+        <v>0.3491456602088209</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.3120896296653531</v>
+        <v>0.296997496060187</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C418">
-        <v>0.3172456188776043</v>
+        <v>0.3176574167317129</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.409642998810138</v>
+        <v>0.386350975168991</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11463,10 +11463,10 @@
         <v>848</v>
       </c>
       <c r="B420" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C420">
-        <v>0.4511014777436628</v>
+        <v>0.4608689377848685</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11480,10 +11480,10 @@
         <v>850</v>
       </c>
       <c r="B421" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C421">
-        <v>0.3967291701518157</v>
+        <v>0.404295877684205</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3711147863654267</v>
+        <v>0.3592656733860785</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11514,10 +11514,10 @@
         <v>854</v>
       </c>
       <c r="B423" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C423">
-        <v>0.4649017336919584</v>
+        <v>0.4535415408882609</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3296969371904548</v>
+        <v>0.309980467554482</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3227609808474454</v>
+        <v>0.3187488620258687</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3742120209534412</v>
+        <v>0.3572497867053049</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2566696528212971</v>
+        <v>0.2525429651535341</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2747590284037176</v>
+        <v>0.2667113496632</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3781873244582644</v>
+        <v>0.34578574689476</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3118507017086689</v>
+        <v>0.3087587518325001</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>15</v>
       </c>
       <c r="C431">
-        <v>0.2928670506584419</v>
+        <v>0.2732319736441867</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3286567825375022</v>
+        <v>0.3130740852039834</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3173235009287645</v>
+        <v>0.3144539071726312</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3585622753600495</v>
+        <v>0.3448981490687766</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.4251448969871074</v>
+        <v>0.3833303388778149</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3539190868136093</v>
+        <v>0.3291678491517077</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3307273956499053</v>
+        <v>0.3087414162107683</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.387522960156024</v>
+        <v>0.3593586250155537</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3305297324265407</v>
+        <v>0.3092861619335975</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.337231621835752</v>
+        <v>0.3152268174336217</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11820,10 +11820,10 @@
         <v>890</v>
       </c>
       <c r="B441" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C441">
-        <v>0.298044032831654</v>
+        <v>0.2929149629839986</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.356901196531142</v>
+        <v>0.3412531768204681</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.307011368204434</v>
+        <v>0.2936629451592391</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3373965553600082</v>
+        <v>0.3115485263037371</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.345558195433679</v>
+        <v>0.3412926217680126</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11905,10 +11905,10 @@
         <v>900</v>
       </c>
       <c r="B446" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C446">
-        <v>0.3885195372491845</v>
+        <v>0.3783879839679469</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.3005308970286985</v>
+        <v>0.2951059101837285</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3927395997134802</v>
+        <v>0.3723544020935158</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.373596095360096</v>
+        <v>0.3559505358576879</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11973,10 +11973,10 @@
         <v>908</v>
       </c>
       <c r="B450" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C450">
-        <v>0.3703940658628674</v>
+        <v>0.365474779067582</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11990,10 +11990,10 @@
         <v>910</v>
       </c>
       <c r="B451" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C451">
-        <v>0.4546029615767068</v>
+        <v>0.4400500772761061</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2793662839734509</v>
+        <v>0.2824861686700084</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3918001031817109</v>
+        <v>0.3632755683280363</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2880072373896687</v>
+        <v>0.2736101857591355</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3265079782558651</v>
+        <v>0.3067977522613501</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3368104496784967</v>
+        <v>0.3116611202772487</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3813446338888398</v>
+        <v>0.3546982688267348</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3342329174955648</v>
+        <v>0.3360690518820298</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3434806358538459</v>
+        <v>0.3310730955708794</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>15</v>
       </c>
       <c r="C460">
-        <v>0.3818033641680585</v>
+        <v>0.3499631456090554</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3259337062344202</v>
+        <v>0.3100110353866648</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12177,10 +12177,10 @@
         <v>932</v>
       </c>
       <c r="B462" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C462">
-        <v>0.2984958893624328</v>
+        <v>0.295174729525442</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3243299808650127</v>
+        <v>0.3175972829084052</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4231239800959847</v>
+        <v>0.3803593095550749</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12228,10 +12228,10 @@
         <v>938</v>
       </c>
       <c r="B465" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C465">
-        <v>0.4056076483756846</v>
+        <v>0.401848341780075</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5596277970509876</v>
+        <v>0.5119715410173421</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4521557149116521</v>
+        <v>0.4178900427106604</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.4019611026499396</v>
+        <v>0.3800209737120411</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2973591291999924</v>
+        <v>0.2859813324560533</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3317357216997716</v>
+        <v>0.3167320259142452</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3337370101010737</v>
+        <v>0.3052732161253165</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3591736066826279</v>
+        <v>0.3397955771318765</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C473">
-        <v>0.3533643581800312</v>
+        <v>0.3346019209651814</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3847727530628554</v>
+        <v>0.3570939901372787</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3698874186053104</v>
+        <v>0.3609458767807003</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3131162654506845</v>
+        <v>0.3078561077645003</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>15</v>
       </c>
       <c r="C477">
-        <v>0.3491023713723275</v>
+        <v>0.341373910096145</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4213605830994959</v>
+        <v>0.4032154620318777</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12466,10 +12466,10 @@
         <v>966</v>
       </c>
       <c r="B479" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C479">
-        <v>0.4180003837685235</v>
+        <v>0.4096218086848217</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4453502421266167</v>
+        <v>0.4177116025701006</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12500,10 +12500,10 @@
         <v>970</v>
       </c>
       <c r="B481" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C481">
-        <v>0.3792799669648689</v>
+        <v>0.3920043524892423</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3261032386568871</v>
+        <v>0.3069549661471149</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3425985754053199</v>
+        <v>0.3181125204381248</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12551,10 +12551,10 @@
         <v>976</v>
       </c>
       <c r="B484" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C484">
-        <v>0.3787477239025471</v>
+        <v>0.3839439192267289</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3950721030284169</v>
+        <v>0.3647104049921775</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.416995168831459</v>
+        <v>0.3880836418657497</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12602,10 +12602,10 @@
         <v>982</v>
       </c>
       <c r="B487" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C487">
-        <v>0.4492242609525252</v>
+        <v>0.4571329494434789</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3779315381115447</v>
+        <v>0.3461764371795718</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.484355452486484</v>
+        <v>0.4488900411480692</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3395734071927177</v>
+        <v>0.3125676863827651</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>15</v>
       </c>
       <c r="C491">
-        <v>0.276806746553911</v>
+        <v>0.2702317397813721</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4999140627748311</v>
+        <v>0.4605097769083669</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3261759260719906</v>
+        <v>0.3156631474744012</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12721,10 +12721,10 @@
         <v>996</v>
       </c>
       <c r="B494" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C494">
-        <v>0.3144698561178459</v>
+        <v>0.3236467553169627</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12738,10 +12738,10 @@
         <v>998</v>
       </c>
       <c r="B495" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C495">
-        <v>0.5464291554632484</v>
+        <v>0.5257538416676516</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4871059457615867</v>
+        <v>0.4501307833104078</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.369356228360872</v>
+        <v>0.3425926930428181</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6990401241405413</v>
+        <v>0.6485183690510853</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.4114278043485819</v>
+        <v>0.3803376324250616</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3886298683993562</v>
+        <v>0.3740153777530699</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3664631868487004</v>
+        <v>0.3437097675858076</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.615994367220091</v>
+        <v>0.560434457098564</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3737009139590765</v>
+        <v>0.3459257073283095</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C504">
-        <v>0.306685729211892</v>
+        <v>0.3049182984917297</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4533850176780899</v>
+        <v>0.4306666964679278</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4906347149838955</v>
+        <v>0.4408388963492982</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.318034494234029</v>
+        <v>0.2951637635330851</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3499279547098815</v>
+        <v>0.3209172014053107</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4871169910017538</v>
+        <v>0.4511486904392834</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3791164715424325</v>
+        <v>0.3557855732294958</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13010,10 +13010,10 @@
         <v>1030</v>
       </c>
       <c r="B511" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C511">
-        <v>0.3984104313729391</v>
+        <v>0.3863145991535313</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2927760512283072</v>
+        <v>0.2946641230139691</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3819438445224634</v>
+        <v>0.368466973796776</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13061,10 +13061,10 @@
         <v>1036</v>
       </c>
       <c r="B514" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C514">
-        <v>0.4249131398562046</v>
+        <v>0.4181624379822251</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5480627802357901</v>
+        <v>0.4945404362711351</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>6</v>
       </c>
       <c r="C516">
-        <v>0.308006647019007</v>
+        <v>0.3020976047696739</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3317361866030943</v>
+        <v>0.3226831921033473</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3310945920211142</v>
+        <v>0.3078510445682313</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13146,10 +13146,10 @@
         <v>1046</v>
       </c>
       <c r="B519" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C519">
-        <v>0.4801018212364839</v>
+        <v>0.4765268093148343</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3423448541208454</v>
+        <v>0.3228192833179416</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3287231787463962</v>
+        <v>0.3043788115361888</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3684477926033294</v>
+        <v>0.3525434807607541</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4522050526536761</v>
+        <v>0.4225060152790976</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2876506084706189</v>
+        <v>0.278719157569129</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13248,10 +13248,10 @@
         <v>1058</v>
       </c>
       <c r="B525" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C525">
-        <v>0.4459967989335649</v>
+        <v>0.421629657580746</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13265,10 +13265,10 @@
         <v>1060</v>
       </c>
       <c r="B526" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C526">
-        <v>0.4485744324122278</v>
+        <v>0.445179887881905</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3722775368526367</v>
+        <v>0.3441377489813401</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4676748415016272</v>
+        <v>0.4411598781177027</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3461130979107216</v>
+        <v>0.3269008076616604</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13333,10 +13333,10 @@
         <v>1068</v>
       </c>
       <c r="B530" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C530">
-        <v>0.5044745212910274</v>
+        <v>0.4929330277132449</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13350,10 +13350,10 @@
         <v>1070</v>
       </c>
       <c r="B531" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C531">
-        <v>0.6030733673507404</v>
+        <v>0.5833429767900368</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C532">
-        <v>0.3132517331555756</v>
+        <v>0.3100812541067824</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4656702283479625</v>
+        <v>0.4164658704403154</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C534">
-        <v>0.3114998073613152</v>
+        <v>0.2989847875203512</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3001928280825698</v>
+        <v>0.3006994393991956</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3171837533315937</v>
+        <v>0.3085481987455175</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.4152060755926826</v>
+        <v>0.3870501913061548</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2907657776595584</v>
+        <v>0.2874451359749816</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3060678668152193</v>
+        <v>0.3044960961690293</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.283939379391095</v>
+        <v>0.275037541003478</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4416864847108284</v>
+        <v>0.4164425633531035</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13537,10 +13537,10 @@
         <v>1092</v>
       </c>
       <c r="B542" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C542">
-        <v>0.4003353632535511</v>
+        <v>0.4075016138918661</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.4343917864809401</v>
+        <v>0.3940702808069877</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3728560145159255</v>
+        <v>0.3572967985831095</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -14027,7 +14027,7 @@
         <v>1166</v>
       </c>
       <c r="B574" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C574">
         <v>0.3227511442277982</v>
@@ -14282,7 +14282,7 @@
         <v>1196</v>
       </c>
       <c r="B589" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C589">
         <v>0.3456207620168386</v>
@@ -14554,7 +14554,7 @@
         <v>1228</v>
       </c>
       <c r="B605" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C605">
         <v>0.2957363704839646</v>
@@ -14656,7 +14656,7 @@
         <v>1240</v>
       </c>
       <c r="B611" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C611">
         <v>0.4846106870503183</v>
@@ -14673,7 +14673,7 @@
         <v>1242</v>
       </c>
       <c r="B612" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C612">
         <v>0.4297736490016794</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,12 +15379,12 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -15395,23 +15395,23 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.3032762648047834</v>
+        <v>0.2778510537375036</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3531039416695648</v>
+        <v>0.3278804824240203</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.3076666390457057</v>
+        <v>0.2751971003895707</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.4907216867804695</v>
+        <v>0.4574381408777259</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4238249431858235</v>
+        <v>0.3954275260752005</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3684223588301463</v>
+        <v>0.3429164531248907</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.3066190561849952</v>
+        <v>0.2807094492642338</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13959,10 +13959,10 @@
         <v>1158</v>
       </c>
       <c r="B570" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C570">
-        <v>0.3098005487786876</v>
+        <v>0.2961480648555327</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.3025596542441778</v>
+        <v>0.2767573836990959</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.3597870223807797</v>
+        <v>0.3324425591822937</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3050634886121578</v>
+        <v>0.2811055033079313</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>45</v>
       </c>
       <c r="C574">
-        <v>0.3227511442277982</v>
+        <v>0.335414871319458</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3371033177670684</v>
+        <v>0.3071793543488098</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3897751160083814</v>
+        <v>0.3604746859907967</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14078,10 +14078,10 @@
         <v>1172</v>
       </c>
       <c r="B577" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2841597472232418</v>
+        <v>0.3033545451788696</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3890065758143285</v>
+        <v>0.3596182830515524</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3281385619552016</v>
+        <v>0.3015362942315583</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3685731822947451</v>
+        <v>0.3692136422589501</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4449098081558612</v>
+        <v>0.4129505501857075</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14163,10 +14163,10 @@
         <v>1182</v>
       </c>
       <c r="B582" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C582">
-        <v>0.3118414788894101</v>
+        <v>0.3029006331683956</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>6</v>
       </c>
       <c r="C583">
-        <v>0.3676439037715044</v>
+        <v>0.3929266122330919</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14197,10 +14197,10 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C584">
-        <v>0.3041133165010727</v>
+        <v>0.2932849087433811</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.3921049488558505</v>
+        <v>0.363708684858251</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.3110312942285105</v>
+        <v>0.2854320270876021</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3292717537634981</v>
+        <v>0.3453653431796098</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14265,10 +14265,10 @@
         <v>1194</v>
       </c>
       <c r="B588" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C588">
-        <v>0.2915438760173306</v>
+        <v>0.2735817841992918</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>45</v>
       </c>
       <c r="C589">
-        <v>0.3456207620168386</v>
+        <v>0.357462837887167</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4030196804948968</v>
+        <v>0.4251514422423212</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.4704354123402085</v>
+        <v>0.4383068928645414</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3851910777979292</v>
+        <v>0.3542111829477864</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.5418925974074438</v>
+        <v>0.5112859425084417</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4222690750438409</v>
+        <v>0.3946718449923842</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14384,10 +14384,10 @@
         <v>1208</v>
       </c>
       <c r="B595" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3346530825625604</v>
+        <v>0.3497580567706906</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4327481944721272</v>
+        <v>0.4051188448878583</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3741442853546899</v>
+        <v>0.3473858265553106</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2849978342499468</v>
+        <v>0.2782432998597438</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.3218449368484785</v>
+        <v>0.2952111168057661</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.3039958818503642</v>
+        <v>0.2776591372914131</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.3155177535017599</v>
+        <v>0.2901105183098396</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3967551010112958</v>
+        <v>0.3649148793048337</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.3240206318110657</v>
+        <v>0.2968127707577324</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.2969274373347594</v>
+        <v>0.3186467881333611</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>45</v>
       </c>
       <c r="C605">
-        <v>0.2957363704839646</v>
+        <v>0.2992967032903776</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3656187619977456</v>
+        <v>0.3875941813405891</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C607">
-        <v>0.317704705795591</v>
+        <v>0.3000683811756371</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>1143</v>
       </c>
       <c r="C608">
-        <v>0.3221291059284625</v>
+        <v>0.2937333620891303</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.3294718102079252</v>
+        <v>0.3049127584107788</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.268710503691466</v>
+        <v>0.2443450113787726</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>45</v>
       </c>
       <c r="C611">
-        <v>0.4846106870503183</v>
+        <v>0.4973402187105948</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>45</v>
       </c>
       <c r="C612">
-        <v>0.4297736490016794</v>
+        <v>0.4323010177825921</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3518523567980054</v>
+        <v>0.3229712387563671</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.3913391249140533</v>
+        <v>0.3636035455794478</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3579411795091575</v>
+        <v>0.333638255468842</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3924376116817266</v>
+        <v>0.3643448636617475</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3580591422994894</v>
+        <v>0.3342648823405743</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3179779610056626</v>
+        <v>0.311023473183448</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4310891558384365</v>
+        <v>0.403612761275682</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14812,7 +14812,7 @@
         <v>15</v>
       </c>
       <c r="C620">
-        <v>0.2890539426284621</v>
+        <v>0.2891314228241091</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3264652590983719</v>
+        <v>0.3268663846519788</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>15</v>
       </c>
       <c r="C622">
-        <v>0.2274980912335571</v>
+        <v>0.2275404253202313</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2429884473956745</v>
+        <v>0.2392847862985188</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2690408351901146</v>
+        <v>0.2722995902607807</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14894,10 +14894,10 @@
         <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>1266</v>
+        <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2504897389124233</v>
+        <v>0.2521530024585635</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3024316527710464</v>
+        <v>0.3027961559975631</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.3259183667833081</v>
+        <v>0.3217575982867497</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2870318579605975</v>
+        <v>0.2830052487288737</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>1266</v>
       </c>
       <c r="C629">
-        <v>0.2223251664995292</v>
+        <v>0.2188305089201392</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3930299238157548</v>
+        <v>0.3895353849245772</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.4040703574019626</v>
+        <v>0.3997078850171333</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.4557776174784538</v>
+        <v>0.4518529565287717</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.265804185567516</v>
+        <v>0.2662182419519051</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.3325964414456429</v>
+        <v>0.3330863011539898</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4695927819330701</v>
+        <v>0.4650725858900553</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3618594904497027</v>
+        <v>0.3621577104358017</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>1266</v>
       </c>
       <c r="C637">
-        <v>0.3234625111819353</v>
+        <v>0.3193161758528884</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4903627901137151</v>
+        <v>0.487291006358283</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3080109935756575</v>
+        <v>0.3113728459237843</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2600392705901694</v>
+        <v>0.263217694231395</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>1266</v>
       </c>
       <c r="C641">
-        <v>0.2878169316923523</v>
+        <v>0.2837883937185025</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.3355545985743619</v>
+        <v>0.3311501451174218</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3026071747601911</v>
+        <v>0.302798518075402</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2912869579012972</v>
+        <v>0.2919865086088561</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>1266</v>
       </c>
       <c r="C645">
-        <v>0.2499418303546379</v>
+        <v>0.2458327937744067</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3302226417810288</v>
+        <v>0.3305884568402281</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>1266</v>
       </c>
       <c r="C647">
-        <v>0.3296166688505361</v>
+        <v>0.3255603298081895</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2697526705414868</v>
+        <v>0.2702503401802666</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.2930271360542232</v>
+        <v>0.2934592544460942</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>1266</v>
       </c>
       <c r="C650">
-        <v>0.2818298737363125</v>
+        <v>0.2780759251476082</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.301028925047235</v>
+        <v>0.3014870811565031</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15419,7 +15419,7 @@
         <v>1266</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2778510537375036</v>
+        <v>0.2754534067785577</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3278804824240203</v>
+        <v>0.3217552589307947</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2751971003895707</v>
+        <v>0.2712719546541894</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.4574381408777259</v>
+        <v>0.4599578364420591</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.3954275260752005</v>
+        <v>0.4095146333369669</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3429164531248907</v>
+        <v>0.3468779710443464</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2807094492642338</v>
+        <v>0.2819164947080606</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>10</v>
       </c>
       <c r="C570">
-        <v>0.2961480648555327</v>
+        <v>0.2922538829959456</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2767573836990959</v>
+        <v>0.2799547040370936</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.3324425591822937</v>
+        <v>0.3300073093208997</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.2811055033079313</v>
+        <v>0.2805324853412571</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>45</v>
       </c>
       <c r="C574">
-        <v>0.335414871319458</v>
+        <v>0.3687604786717376</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3071793543488098</v>
+        <v>0.3015709519450364</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3604746859907967</v>
+        <v>0.3674308555554007</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3033545451788696</v>
+        <v>0.2966752447379611</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3596182830515524</v>
+        <v>0.3631428679854594</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3015362942315583</v>
+        <v>0.3054834405529114</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3692136422589501</v>
+        <v>0.357103663493369</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4129505501857075</v>
+        <v>0.4010937252652034</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>6</v>
       </c>
       <c r="C582">
-        <v>0.3029006331683956</v>
+        <v>0.296311647312829</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>6</v>
       </c>
       <c r="C583">
-        <v>0.3929266122330919</v>
+        <v>0.3877448800199075</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14197,10 +14197,10 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.2932849087433811</v>
+        <v>0.2887079332281093</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.363708684858251</v>
+        <v>0.3693780743037599</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2854320270876021</v>
+        <v>0.2801336688646776</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3453653431796098</v>
+        <v>0.3287710800260244</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14265,10 +14265,10 @@
         <v>1194</v>
       </c>
       <c r="B588" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.2735817841992918</v>
+        <v>0.2681818349557712</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>45</v>
       </c>
       <c r="C589">
-        <v>0.357462837887167</v>
+        <v>0.3916150747493796</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4251514422423212</v>
+        <v>0.410420021121837</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.4383068928645414</v>
+        <v>0.4219222946389186</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3542111829477864</v>
+        <v>0.3270613617209647</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.5112859425084417</v>
+        <v>0.5173383757395047</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.3946718449923842</v>
+        <v>0.3887938758872745</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3497580567706906</v>
+        <v>0.337543487651305</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4051188448878583</v>
+        <v>0.3936227625512888</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3473858265553106</v>
+        <v>0.3632435099993138</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2782432998597438</v>
+        <v>0.266914164262071</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2952111168057661</v>
+        <v>0.3042814912995248</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2776591372914131</v>
+        <v>0.2781088630637019</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14486,10 +14486,10 @@
         <v>1220</v>
       </c>
       <c r="B601" t="s">
-        <v>1143</v>
+        <v>45</v>
       </c>
       <c r="C601">
-        <v>0.2901105183098396</v>
+        <v>0.2916491957457273</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3649148793048337</v>
+        <v>0.36987647682363</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2968127707577324</v>
+        <v>0.298544854354126</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3186467881333611</v>
+        <v>0.3132720927243448</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>45</v>
       </c>
       <c r="C605">
-        <v>0.2992967032903776</v>
+        <v>0.3288100647079791</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3875941813405891</v>
+        <v>0.3756896859321552</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>10</v>
       </c>
       <c r="C607">
-        <v>0.3000683811756371</v>
+        <v>0.2873044081796143</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>1143</v>
       </c>
       <c r="C608">
-        <v>0.2937333620891303</v>
+        <v>0.2954830322571341</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.3049127584107788</v>
+        <v>0.3012841560274029</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2443450113787726</v>
+        <v>0.2499979097946463</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>45</v>
       </c>
       <c r="C611">
-        <v>0.4973402187105948</v>
+        <v>0.5301410827809822</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>45</v>
       </c>
       <c r="C612">
-        <v>0.4323010177825921</v>
+        <v>0.4702653401107232</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3229712387563671</v>
+        <v>0.3263467065741318</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.3636035455794478</v>
+        <v>0.3780567462472258</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.333638255468842</v>
+        <v>0.3337172300066883</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3643448636617475</v>
+        <v>0.3762573196510252</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3342648823405743</v>
+        <v>0.3446620184954829</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.311023473183448</v>
+        <v>0.2983525383218857</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.403612761275682</v>
+        <v>0.4187231771809876</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2754534067785577</v>
+        <v>0.2690105680143081</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3217552589307947</v>
+        <v>0.3177251028942784</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2712719546541894</v>
+        <v>0.2612073347443773</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.4599578364420591</v>
+        <v>0.4692636361466231</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4095146333369669</v>
+        <v>0.4067040151987543</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3468779710443464</v>
+        <v>0.3265702287762656</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2819164947080606</v>
+        <v>0.2725871796309934</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>10</v>
       </c>
       <c r="C570">
-        <v>0.2922538829959456</v>
+        <v>0.2973980033569115</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2799547040370936</v>
+        <v>0.2785945084718467</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.3300073093208997</v>
+        <v>0.3339394241823059</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.2805324853412571</v>
+        <v>0.2742210821650125</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>45</v>
       </c>
       <c r="C574">
-        <v>0.3687604786717376</v>
+        <v>0.3028456434777809</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3015709519450364</v>
+        <v>0.3119341197899996</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3674308555554007</v>
+        <v>0.3698231117449726</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2966752447379611</v>
+        <v>0.2919594411842059</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3631428679854594</v>
+        <v>0.3539930473586655</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3054834405529114</v>
+        <v>0.2940333724000349</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.357103663493369</v>
+        <v>0.3509493963487059</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4010937252652034</v>
+        <v>0.4147576516194132</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14163,10 +14163,10 @@
         <v>1182</v>
       </c>
       <c r="B582" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.296311647312829</v>
+        <v>0.2893096138868425</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>6</v>
       </c>
       <c r="C583">
-        <v>0.3877448800199075</v>
+        <v>0.377930850660432</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14197,10 +14197,10 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C584">
-        <v>0.2887079332281093</v>
+        <v>0.2909773104359007</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.3693780743037599</v>
+        <v>0.3590663072187273</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2801336688646776</v>
+        <v>0.2805660414157179</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3287710800260244</v>
+        <v>0.3109198236844402</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.2681818349557712</v>
+        <v>0.2658543187802467</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>45</v>
       </c>
       <c r="C589">
-        <v>0.3916150747493796</v>
+        <v>0.334880147352805</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.410420021121837</v>
+        <v>0.4162449782215457</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.4219222946389186</v>
+        <v>0.4498428338083647</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3270613617209647</v>
+        <v>0.3616150735580669</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.5173383757395047</v>
+        <v>0.5284429984532093</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.3887938758872745</v>
+        <v>0.4029520642890408</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.337543487651305</v>
+        <v>0.3381832858024464</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.3936227625512888</v>
+        <v>0.4199716629659814</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3632435099993138</v>
+        <v>0.3512890035148448</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.266914164262071</v>
+        <v>0.2581521998596382</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.3042814912995248</v>
+        <v>0.3027521919912147</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2781088630637019</v>
+        <v>0.2791350443565828</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14486,10 +14486,10 @@
         <v>1220</v>
       </c>
       <c r="B601" t="s">
-        <v>45</v>
+        <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2916491957457273</v>
+        <v>0.2807495838551311</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.36987647682363</v>
+        <v>0.3673640637629877</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.298544854354126</v>
+        <v>0.2923137433218961</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3132720927243448</v>
+        <v>0.3036732982785109</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>45</v>
       </c>
       <c r="C605">
-        <v>0.3288100647079791</v>
+        <v>0.280490914003508</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3756896859321552</v>
+        <v>0.3717057904590055</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.2873044081796143</v>
+        <v>0.2846142319580898</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>1143</v>
       </c>
       <c r="C608">
-        <v>0.2954830322571341</v>
+        <v>0.2988339006103424</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.3012841560274029</v>
+        <v>0.3152593720728452</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2499979097946463</v>
+        <v>0.2442559023413335</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>45</v>
       </c>
       <c r="C611">
-        <v>0.5301410827809822</v>
+        <v>0.4649064157757105</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>45</v>
       </c>
       <c r="C612">
-        <v>0.4702653401107232</v>
+        <v>0.3840648677724066</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3263467065741318</v>
+        <v>0.3265343579132391</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.3780567462472258</v>
+        <v>0.3710125022602774</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3337172300066883</v>
+        <v>0.31410023344431</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3762573196510252</v>
+        <v>0.3696786189294876</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3446620184954829</v>
+        <v>0.3260999878488807</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.2983525383218857</v>
+        <v>0.2893262440264847</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4187231771809876</v>
+        <v>0.4169620502023828</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2732395136851172</v>
+        <v>0.2731890869974225</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3993823086053072</v>
+        <v>0.3996834850583485</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3666681949988029</v>
+        <v>0.3666158421547488</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3333148689926222</v>
+        <v>0.3330553881030072</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3510355070779581</v>
+        <v>0.3512736284212313</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>0.2832283208693455</v>
+        <v>0.2832193906265477</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3465683265117847</v>
+        <v>0.3463004079274083</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3109956190612335</v>
+        <v>0.3107449472632849</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3222205598462528</v>
+        <v>0.3224864117201496</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2476629360983871</v>
+        <v>0.2474386313360999</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4111456985443812</v>
+        <v>0.4111173766481203</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.2962053799676988</v>
+        <v>0.2959813806281669</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3855110348463691</v>
+        <v>0.3852372276325588</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3338585957311285</v>
+        <v>0.3341340164338367</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.2836049670263135</v>
+        <v>0.2835704948855043</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2728312828792824</v>
+        <v>0.2725952644456928</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2795082447941284</v>
+        <v>0.2797663816875068</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>45</v>
       </c>
       <c r="C19">
-        <v>0.4194729223340706</v>
+        <v>0.419510256107003</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3933161990023065</v>
+        <v>0.3932511050718077</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3867408118256472</v>
+        <v>0.3869801342194137</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3186303566815537</v>
+        <v>0.3185825831063429</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3816454654806094</v>
+        <v>0.3815955855164153</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3158250984910693</v>
+        <v>0.3157665784601392</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.5705131187879788</v>
+        <v>0.5704637043601798</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3069946589709277</v>
+        <v>0.3069507129881807</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2706583924026896</v>
+        <v>0.2709107066038902</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.2998420790755987</v>
+        <v>0.3001056267093883</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>45</v>
       </c>
       <c r="C29">
-        <v>0.4643350221357704</v>
+        <v>0.4643788553261233</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.352512239710294</v>
+        <v>0.3524755763214208</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4055323808440809</v>
+        <v>0.4054963817441615</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.3926119523985971</v>
+        <v>0.392343809092573</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3555112152011001</v>
+        <v>0.3554751668963511</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3090915708881617</v>
+        <v>0.3088500834847635</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4287422943562835</v>
+        <v>0.4286937672550652</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>0.2549795254211109</v>
+        <v>0.2550133214175332</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.2834463060736293</v>
+        <v>0.2832173390723448</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3253392066303707</v>
+        <v>0.3252837826892754</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3407688887049003</v>
+        <v>0.3405052023869318</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4436582056613935</v>
+        <v>0.4436113799021176</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>20</v>
       </c>
       <c r="C41">
-        <v>0.2749760614344846</v>
+        <v>0.2749489028880143</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5191910470472684</v>
+        <v>0.5191525591553324</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3867159166450228</v>
+        <v>0.3864296393144396</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.3871284132921279</v>
+        <v>0.3868478511515707</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3774297046853012</v>
+        <v>0.377389347326093</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4156876074399146</v>
+        <v>0.4156455140660558</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2861443703421916</v>
+        <v>0.2859036433056031</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.397489707599648</v>
+        <v>0.3972113653587483</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3292253863156944</v>
+        <v>0.3289744295912151</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3563386933955707</v>
+        <v>0.3560624745818616</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3343999921068679</v>
+        <v>0.3341336222149231</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5028252942314915</v>
+        <v>0.5027855543387127</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4170155739579671</v>
+        <v>0.4167395478851277</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3840835386522008</v>
+        <v>0.3840286303150024</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2680288583156998</v>
+        <v>0.2682772373281074</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3310817579738206</v>
+        <v>0.3313508524095074</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5382685942049356</v>
+        <v>0.5382174061133613</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>15</v>
       </c>
       <c r="C58">
-        <v>0.3063925062734232</v>
+        <v>0.3061467871207842</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3630166565500669</v>
+        <v>0.3629804924296078</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.28034462940937</v>
+        <v>0.2802973014917337</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3343190539378091</v>
+        <v>0.3342690694464948</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3132311139192334</v>
+        <v>0.3134754634905552</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3563511504840943</v>
+        <v>0.3562992507308759</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>45</v>
       </c>
       <c r="C64">
-        <v>0.2313794876144904</v>
+        <v>0.2314080513790949</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3218859423546621</v>
+        <v>0.3216310557878241</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5448,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3202592974782623</v>
+        <v>0.3200119056826832</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3436566611342001</v>
+        <v>0.3433872272009656</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2494182359711944</v>
+        <v>0.2493718781804786</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>80</v>
       </c>
       <c r="C69">
-        <v>0.5672836486833495</v>
+        <v>0.5673409809461826</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>80</v>
       </c>
       <c r="C70">
-        <v>0.5225325306877003</v>
+        <v>0.5225906468163186</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4330225069301216</v>
+        <v>0.4329657255888861</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3360167606023098</v>
+        <v>0.3359700793452768</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4896640890778335</v>
+        <v>0.4896129678501382</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4371959091734038</v>
+        <v>0.4371402473826764</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2428192051911606</v>
+        <v>0.2430594694832757</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3477989834865634</v>
+        <v>0.3480667918786327</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.320795777391552</v>
+        <v>0.3210524072079386</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4031862397350496</v>
+        <v>0.4034850417811271</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>0.2535830912134504</v>
+        <v>0.2535355540043076</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3449869704744172</v>
+        <v>0.3452511609485241</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2965520408900267</v>
+        <v>0.2963153071352545</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.3993035234758795</v>
+        <v>0.3995996470451474</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3865852541764806</v>
+        <v>0.3865333897570747</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>15</v>
       </c>
       <c r="C84">
-        <v>0.2949678120888177</v>
+        <v>0.2947200753351377</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3304689942792156</v>
+        <v>0.3302062294006716</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.2801835306101984</v>
+        <v>0.2801413141255369</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2617267840375349</v>
+        <v>0.2616954020069883</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>80</v>
       </c>
       <c r="C88">
-        <v>0.3316067571380222</v>
+        <v>0.3316401168222959</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>15</v>
       </c>
       <c r="C89">
-        <v>0.2937954515916378</v>
+        <v>0.2935480096965258</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2678799846485569</v>
+        <v>0.2681237132932035</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2683314013744097</v>
+        <v>0.2682838134905657</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>45</v>
       </c>
       <c r="C92">
-        <v>0.3375133441215455</v>
+        <v>0.3375502674426004</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3834210818534879</v>
+        <v>0.3831431819939581</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.2567264356363955</v>
+        <v>0.2566762142793432</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3158378124719264</v>
+        <v>0.3155769849718266</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3615994437072197</v>
+        <v>0.3613328234785266</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>45</v>
       </c>
       <c r="C97">
-        <v>0.3578729993117989</v>
+        <v>0.3579073122107756</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>45</v>
       </c>
       <c r="C98">
-        <v>0.3623239501331408</v>
+        <v>0.362355413675806</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4056975187596664</v>
+        <v>0.4056270083741218</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>45</v>
       </c>
       <c r="C100">
-        <v>0.3918375627670607</v>
+        <v>0.3918610032818315</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>45</v>
       </c>
       <c r="C101">
-        <v>0.4519795971934741</v>
+        <v>0.4520140331017552</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4290823611102275</v>
+        <v>0.4290283937516334</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3389445254708947</v>
+        <v>0.3389035021198932</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3402615552965701</v>
+        <v>0.3399918177168225</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>45</v>
       </c>
       <c r="C105">
-        <v>0.3512033665479103</v>
+        <v>0.3512409063442349</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3713434697734791</v>
+        <v>0.3716112746163084</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>45</v>
       </c>
       <c r="C107">
-        <v>0.3503301116799097</v>
+        <v>0.350361397399039</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.396813674338575</v>
+        <v>0.3967617859296316</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>20</v>
       </c>
       <c r="C109">
-        <v>0.2623724599497705</v>
+        <v>0.262348792225695</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2839820020161116</v>
+        <v>0.2837484941430751</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.490884790317633</v>
+        <v>0.4908208050650105</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3604755931247435</v>
+        <v>0.3604239711781717</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4856537038614581</v>
+        <v>0.4853549816241357</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.5949318974436387</v>
+        <v>0.5948801515847653</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3025276460356449</v>
+        <v>0.3024819137950779</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4317564378425923</v>
+        <v>0.4317233836289813</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2644812967283403</v>
+        <v>0.264429409158885</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3748404086447688</v>
+        <v>0.375123270396285</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3652763938157373</v>
+        <v>0.365248637322291</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3439644831100909</v>
+        <v>0.3442355975778208</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.2910252931523665</v>
+        <v>0.2909929612483907</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3274030589132348</v>
+        <v>0.3271348927052412</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2900734829936261</v>
+        <v>0.2898320457208974</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.367631298368318</v>
+        <v>0.3673590101132331</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>15</v>
       </c>
       <c r="C125">
-        <v>0.2780558536637699</v>
+        <v>0.2778180066829818</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.367713448233465</v>
+        <v>0.3676490201203153</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4769618159002622</v>
+        <v>0.4768950402409398</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.3963609585658288</v>
+        <v>0.3960828688266318</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="C129">
-        <v>0.2855799310364898</v>
+        <v>0.2858458600248156</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.433125564990629</v>
+        <v>0.4328389197864882</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2650142077228216</v>
+        <v>0.2652639144731969</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3572959683556816</v>
+        <v>0.3572433362744091</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3222891266486957</v>
+        <v>0.3220400117619798</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3194544706754181</v>
+        <v>0.3194050868779635</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3274551342623792</v>
+        <v>0.3274243279902584</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>45</v>
       </c>
       <c r="C136">
-        <v>0.3393765780999465</v>
+        <v>0.3394150540333496</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3748268378382502</v>
+        <v>0.3747907404981838</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>15</v>
       </c>
       <c r="C138">
-        <v>0.3098970714053071</v>
+        <v>0.3096466562439349</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4194437970379778</v>
+        <v>0.4194043211696282</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>45</v>
       </c>
       <c r="C140">
-        <v>0.4064580817836484</v>
+        <v>0.4064874472953158</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3369089305648181</v>
+        <v>0.3368634750840982</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3720076633968321</v>
+        <v>0.3722744168110607</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>15</v>
       </c>
       <c r="C143">
-        <v>0.2871559190517126</v>
+        <v>0.2869107338664426</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.515024418052678</v>
+        <v>0.5149677915139416</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.266984799425953</v>
+        <v>0.2669363237969181</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4134114368788093</v>
+        <v>0.4133607212816991</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4191708620130175</v>
+        <v>0.4191184101559514</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.320675297926122</v>
+        <v>0.3206143323126642</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3497384917362218</v>
+        <v>0.3499922889641674</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3144011441009629</v>
+        <v>0.3141607593121649</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2334886221640672</v>
+        <v>0.2337148206909468</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6192215421305959</v>
+        <v>0.6191715869715585</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3218681128533195</v>
+        <v>0.3221201557399923</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="C154">
-        <v>0.3113456447159945</v>
+        <v>0.3115919685370324</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="C155">
-        <v>0.2696032734794893</v>
+        <v>0.2693786834207951</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3289693694554722</v>
+        <v>0.3292372399788503</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3512362884190388</v>
+        <v>0.3511878239339409</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>45</v>
       </c>
       <c r="C158">
-        <v>0.3771225999672054</v>
+        <v>0.377163934698311</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>45</v>
       </c>
       <c r="C159">
-        <v>0.3882265911025024</v>
+        <v>0.3882680721506582</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3831075266295019</v>
+        <v>0.3830576544558822</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3564391503642897</v>
+        <v>0.3563898414903429</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5391323946831142</v>
+        <v>0.5390843779034344</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>45</v>
       </c>
       <c r="C163">
-        <v>0.4495152484915196</v>
+        <v>0.4495592387784004</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.2833621580266551</v>
+        <v>0.2836279654067483</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3337881873494717</v>
+        <v>0.3340615422191347</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>45</v>
       </c>
       <c r="C166">
-        <v>0.3456002432341783</v>
+        <v>0.3456292448323147</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3421101258309006</v>
+        <v>0.3420638171893551</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5572880857822303</v>
+        <v>0.5572434298283805</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>45</v>
       </c>
       <c r="C169">
-        <v>0.3657992064474962</v>
+        <v>0.3658267336996434</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3458474452844516</v>
+        <v>0.3458037588315381</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>45</v>
       </c>
       <c r="C171">
-        <v>0.2551874296601972</v>
+        <v>0.2552191194763097</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4211231823575422</v>
+        <v>0.4214224271971195</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3247734659088505</v>
+        <v>0.3250215889553364</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3073607236787221</v>
+        <v>0.3073061334381291</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.3047444451293809</v>
+        <v>0.3045112797055867</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3876622383107603</v>
+        <v>0.3876166275523616</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5318517134163941</v>
+        <v>0.5317942719584017</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3893141370280193</v>
+        <v>0.3890424501513491</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3080403558816855</v>
+        <v>0.3077994733057124</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>45</v>
       </c>
       <c r="C180">
-        <v>0.3744440790336231</v>
+        <v>0.3744852979436264</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3318277701772704</v>
+        <v>0.3317751252262934</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2934839507389534</v>
+        <v>0.2937394359514823</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.305558146972186</v>
+        <v>0.3055180009122466</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3257687424554845</v>
+        <v>0.3257185816808302</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>15</v>
       </c>
       <c r="C185">
-        <v>0.3350558984248939</v>
+        <v>0.334806713715348</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>45</v>
       </c>
       <c r="C186">
-        <v>0.4310029511697319</v>
+        <v>0.4310428784265809</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2372961787880213</v>
+        <v>0.2370730021299846</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4390984212272475</v>
+        <v>0.4393136638376079</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.316496737199386</v>
+        <v>0.3167608604941766</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2577324375382284</v>
+        <v>0.2577027297614452</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.333135099914439</v>
+        <v>0.3334029902697402</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4063638862920527</v>
+        <v>0.4060737389959426</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4291584686892414</v>
+        <v>0.4288973490129452</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3553428603335652</v>
+        <v>0.3553090877817893</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>20</v>
       </c>
       <c r="C195">
-        <v>0.3686992557310674</v>
+        <v>0.3686909631656248</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>80</v>
       </c>
       <c r="C196">
-        <v>0.3196407977631342</v>
+        <v>0.3196754825406789</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.2975237827880578</v>
+        <v>0.2977718532422716</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.4832734482567372</v>
+        <v>0.483215803592919</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.536530830944757</v>
+        <v>0.5364745120522867</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>10</v>
       </c>
       <c r="C200">
-        <v>0.3189990371125813</v>
+        <v>0.3192753998027191</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3091005831135611</v>
+        <v>0.3088662619119187</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3415345227041416</v>
+        <v>0.3417927567244875</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.4820322905126632</v>
+        <v>0.4819795799699422</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4720492890699459</v>
+        <v>0.471996931039137</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4079002439392426</v>
+        <v>0.4081681575437077</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3509326760882177</v>
+        <v>0.3506673342981533</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>45</v>
       </c>
       <c r="C207">
-        <v>0.5253263102563502</v>
+        <v>0.525377427715866</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>45</v>
       </c>
       <c r="C208">
-        <v>0.415897979195919</v>
+        <v>0.4159290211631522</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.47682645304833</v>
+        <v>0.4771214598363571</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4197551789507116</v>
+        <v>0.4196906013430968</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4057323684344987</v>
+        <v>0.4054458940749395</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2772820745388682</v>
+        <v>0.2770432360761396</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3474177839772552</v>
+        <v>0.3471492587017801</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.358323130545646</v>
+        <v>0.3580584042005969</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5678678779039124</v>
+        <v>0.5681837258049387</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3180583156170301</v>
+        <v>0.317796369664284</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3148534232701697</v>
+        <v>0.3145959139908964</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3635582730744681</v>
+        <v>0.3634906118826228</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>45</v>
       </c>
       <c r="C219">
-        <v>0.4787128209948535</v>
+        <v>0.4787458774152446</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="C220">
-        <v>0.2848139868626538</v>
+        <v>0.2850727480217654</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3485697389467239</v>
+        <v>0.348313587766664</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.2947821968570619</v>
+        <v>0.2947309021696987</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.513523819121123</v>
+        <v>0.5138256242946968</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3482339833248665</v>
+        <v>0.3485000033367506</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3465018811394917</v>
+        <v>0.3462422056144061</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4522929765223401</v>
+        <v>0.4522405644416394</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3261427236224995</v>
+        <v>0.3264004124808472</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4478647876220882</v>
+        <v>0.4478216478033977</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.4679499655967116</v>
+        <v>0.4678918457256477</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>45</v>
       </c>
       <c r="C230">
-        <v>0.3793067223448619</v>
+        <v>0.3793382882223059</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3087760857063826</v>
+        <v>0.3087256087437703</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5738775021817857</v>
+        <v>0.5738205589844051</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>45</v>
       </c>
       <c r="C233">
-        <v>0.4604257737646199</v>
+        <v>0.4604664658368461</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.3898769720030905</v>
+        <v>0.3898425522259859</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4775875319625823</v>
+        <v>0.4775298713028546</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2507865641714971</v>
+        <v>0.250736309301051</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3243289094624282</v>
+        <v>0.324584554707784</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3089225347785897</v>
+        <v>0.3088967176865974</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.3910619808032776</v>
+        <v>0.3910097506279728</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>20</v>
       </c>
       <c r="C240">
-        <v>0.3511545042527324</v>
+        <v>0.3511075332953673</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>6</v>
       </c>
       <c r="C241">
-        <v>0.2319251259728439</v>
+        <v>0.2318719746343891</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3043682882542799</v>
+        <v>0.3043280350926076</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4257755907431912</v>
+        <v>0.4254749719038978</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>20</v>
       </c>
       <c r="C244">
-        <v>0.3514922078411835</v>
+        <v>0.3514556541208051</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.5871540315280875</v>
+        <v>0.5871050413590594</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4339542752247665</v>
+        <v>0.433911799138176</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4258583993765638</v>
+        <v>0.4258013029650813</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3365203208521267</v>
+        <v>0.3367735403128483</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4327909918464454</v>
+        <v>0.4327332674582867</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3536651453158876</v>
+        <v>0.3533989992026901</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>45</v>
       </c>
       <c r="C251">
-        <v>0.4719406442989078</v>
+        <v>0.4719735323699444</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4330290601764087</v>
+        <v>0.432984028102927</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3482805964284796</v>
+        <v>0.3482440105139347</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.453590307584794</v>
+        <v>0.4535440136190794</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4082341301306797</v>
+        <v>0.4079307460070048</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5312402467327827</v>
+        <v>0.5311997363979404</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.369037843466496</v>
+        <v>0.3689910548685303</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4804646438274022</v>
+        <v>0.4804122228917141</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3045076943275314</v>
+        <v>0.3044799909263223</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.3872407740974299</v>
+        <v>0.3871905807816949</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4103948820437387</v>
+        <v>0.4103418820567779</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.371407847685944</v>
+        <v>0.3713599096231524</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.458901369758199</v>
+        <v>0.4588543582388119</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.3877591326375837</v>
+        <v>0.3877159049571143</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.2934466826849581</v>
+        <v>0.2934057693299821</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>20</v>
       </c>
       <c r="C266">
-        <v>0.3288719298568865</v>
+        <v>0.3288429271148609</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2780323813965551</v>
+        <v>0.2779969860574772</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4266915723281238</v>
+        <v>0.426647378164651</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>45</v>
       </c>
       <c r="C269">
-        <v>0.3652960342650693</v>
+        <v>0.3653446707330477</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.4885303441501425</v>
+        <v>0.4884721181987628</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.4884026929138592</v>
+        <v>0.4883434608466046</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3159308800354828</v>
+        <v>0.3158766514614303</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.4946677818070228</v>
+        <v>0.494624265201998</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3410156712608597</v>
+        <v>0.340755564582454</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2506895755622416</v>
+        <v>0.2504757139292913</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3201052333980147</v>
+        <v>0.3200707782842176</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>80</v>
       </c>
       <c r="C277">
-        <v>0.3981536929910262</v>
+        <v>0.3982061271880902</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4372629958065475</v>
+        <v>0.437240806033782</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5282563737210509</v>
+        <v>0.5283035154184802</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4468697236387886</v>
+        <v>0.4469222428389935</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3602800968706564</v>
+        <v>0.3602211135781793</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3590048688977155</v>
+        <v>0.3587412775477272</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3791757417003581</v>
+        <v>0.3791386734222417</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3074120796310096</v>
+        <v>0.3073622089724057</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2757887573314627</v>
+        <v>0.2755665554647973</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3063422548835616</v>
+        <v>0.3062977007842542</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>45</v>
       </c>
       <c r="C287">
-        <v>0.4878842402089424</v>
+        <v>0.4879194143501602</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>15</v>
       </c>
       <c r="C288">
-        <v>0.2464437791351542</v>
+        <v>0.2462084765180149</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3569184580174412</v>
+        <v>0.3568848064644838</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3595185772025217</v>
+        <v>0.3592466875392143</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4291926544740748</v>
+        <v>0.4292197120521462</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>80</v>
       </c>
       <c r="C292">
-        <v>0.4680035070011875</v>
+        <v>0.4681486220271456</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5707380766841614</v>
+        <v>0.5706848977293811</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3844822960153834</v>
+        <v>0.3842133909407972</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3509829337434293</v>
+        <v>0.3512250406166735</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.2742862509406211</v>
+        <v>0.2740468942383446</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4752656084850989</v>
+        <v>0.4755721378536933</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3651811968577741</v>
+        <v>0.3654642758490134</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>45</v>
       </c>
       <c r="C299">
-        <v>0.3017454308359744</v>
+        <v>0.3017739344916547</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.328607104605971</v>
+        <v>0.3288729509461174</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3520854427446481</v>
+        <v>0.3520330426124753</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>45</v>
       </c>
       <c r="C302">
-        <v>0.4977970281073916</v>
+        <v>0.4978343125737101</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3209774210827143</v>
+        <v>0.3212517778903816</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>15</v>
       </c>
       <c r="C304">
-        <v>0.2717254781879639</v>
+        <v>0.2714871244027537</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>45</v>
       </c>
       <c r="C305">
-        <v>0.449829688823387</v>
+        <v>0.4498735258259645</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.3821715932856783</v>
+        <v>0.3819191565054057</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.438812873605348</v>
+        <v>0.4387604731025528</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3537888278641893</v>
+        <v>0.3537353469374516</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>10</v>
       </c>
       <c r="C309">
-        <v>0.2542405840586017</v>
+        <v>0.2544837670412075</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3714737845246933</v>
+        <v>0.3714180537966165</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3343371802313397</v>
+        <v>0.3340876911856222</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>10</v>
       </c>
       <c r="C312">
-        <v>0.2861827833800425</v>
+        <v>0.2864367306694399</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9644,10 +9644,10 @@
         <v>634</v>
       </c>
       <c r="B313" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C313">
-        <v>0.2662489440577941</v>
+        <v>0.266321782050805</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3079549116179478</v>
+        <v>0.3082145877865801</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>45</v>
       </c>
       <c r="C315">
-        <v>0.4828283379038344</v>
+        <v>0.4828745173921967</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3746650958547679</v>
+        <v>0.3746232108410319</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.468304007361598</v>
+        <v>0.4682629238684478</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5176790857026109</v>
+        <v>0.517634975343646</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3048266776722032</v>
+        <v>0.3047787475696113</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2632994408666604</v>
+        <v>0.263065575801109</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3099762972793331</v>
+        <v>0.3099371458527243</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.410326911998559</v>
+        <v>0.4102891906644293</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.370316961873501</v>
+        <v>0.370586220374662</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>45</v>
       </c>
       <c r="C324">
-        <v>0.4105986791850854</v>
+        <v>0.4106432547008605</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>10</v>
       </c>
       <c r="C325">
-        <v>0.2547994001785602</v>
+        <v>0.2550363643046866</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>45</v>
       </c>
       <c r="C326">
-        <v>0.3614333388584811</v>
+        <v>0.3614667433397781</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>45</v>
       </c>
       <c r="C327">
-        <v>0.3486507738444576</v>
+        <v>0.3486826232840337</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2721056644938017</v>
+        <v>0.2718691318663946</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>15</v>
       </c>
       <c r="C329">
-        <v>0.3028255571915233</v>
+        <v>0.3025914194022289</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>6</v>
       </c>
       <c r="C330">
-        <v>0.295131447797671</v>
+        <v>0.2950881982799907</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3404296569513102</v>
+        <v>0.3406703505292503</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3573375418612609</v>
+        <v>0.3576042797254165</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4341160489667888</v>
+        <v>0.4340673012680558</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>80</v>
       </c>
       <c r="C334">
-        <v>0.2854775989190521</v>
+        <v>0.2855087264895134</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3168912580287356</v>
+        <v>0.3166324402235866</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.2774996633904437</v>
+        <v>0.2777595715094676</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>45</v>
       </c>
       <c r="C337">
-        <v>0.4889199285138132</v>
+        <v>0.4889653749591809</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.2795102268385413</v>
+        <v>0.2797481395861633</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4561556155866121</v>
+        <v>0.455855209767033</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3095445296297069</v>
+        <v>0.3092846985137886</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2487223303728552</v>
+        <v>0.2486665028937088</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.258480564928115</v>
+        <v>0.258725458660699</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3749100899428632</v>
+        <v>0.375196727501278</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2931209066013535</v>
+        <v>0.2928898509991285</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3497374609188618</v>
+        <v>0.349696905411865</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3479384373158478</v>
+        <v>0.3482110117609485</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3258704387773306</v>
+        <v>0.3256175281595101</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.2921907284093073</v>
+        <v>0.2921458422993574</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4806258351266455</v>
+        <v>0.4806617609397184</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3547018272596593</v>
+        <v>0.354437716107102</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>80</v>
       </c>
       <c r="C351">
-        <v>0.2903366521035799</v>
+        <v>0.2903704478950631</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3969695416588596</v>
+        <v>0.3966817000459791</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3637719562022336</v>
+        <v>0.3640582765304966</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2607843142586349</v>
+        <v>0.260749237328832</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3152838223407323</v>
+        <v>0.3152511859641568</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="C356">
-        <v>0.3016488005168317</v>
+        <v>0.3019120855194085</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4088642502362704</v>
+        <v>0.4088172729982106</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3262332819466302</v>
+        <v>0.3261792320868157</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>45</v>
       </c>
       <c r="C359">
-        <v>0.4625614990377774</v>
+        <v>0.462600463127239</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4380897720356673</v>
+        <v>0.438034179262234</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3042809108881442</v>
+        <v>0.3040363766121623</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3235028717685948</v>
+        <v>0.3234537836751084</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2810243734241137</v>
+        <v>0.2812847576172484</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.2809045886549856</v>
+        <v>0.2811558048351003</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3038825354732409</v>
+        <v>0.3036345293068745</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2591150616191807</v>
+        <v>0.2588864554974043</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>15</v>
       </c>
       <c r="C367">
-        <v>0.27871374350084</v>
+        <v>0.2784782110246684</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3214172811427258</v>
+        <v>0.3211603788095643</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4252675330797375</v>
+        <v>0.4252213482780369</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.34454180083186</v>
+        <v>0.3442870820604507</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4586015513210037</v>
+        <v>0.4585465982962904</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3104425016267333</v>
+        <v>0.3104077173927295</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.3973124680360511</v>
+        <v>0.3972459430383062</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4342764392813563</v>
+        <v>0.4342171728926152</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4138096697532855</v>
+        <v>0.413764114571708</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3814901269075194</v>
+        <v>0.381215197787105</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4627443205341789</v>
+        <v>0.4626898176105343</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.2790264548815291</v>
+        <v>0.2789791402286035</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.30402367151835</v>
+        <v>0.3039714469196432</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3398330080369503</v>
+        <v>0.3397803270561676</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4245001583495382</v>
+        <v>0.4247732133574574</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3369444667297006</v>
+        <v>0.3369022315284393</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.345562983344772</v>
+        <v>0.3458374502083499</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>45</v>
       </c>
       <c r="C384">
-        <v>0.4742303476598229</v>
+        <v>0.4742699130294302</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3720829383935021</v>
+        <v>0.3720468539888261</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.2994732272138844</v>
+        <v>0.299227291373138</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4346799178935959</v>
+        <v>0.4349819731556097</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>45</v>
       </c>
       <c r="C388">
-        <v>0.3498885679269799</v>
+        <v>0.3499308599251187</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.363277109307553</v>
+        <v>0.3632316566683695</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3378144772658636</v>
+        <v>0.3375580826284844</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.339498613701158</v>
+        <v>0.3392437563907716</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3275957562094902</v>
+        <v>0.327865141090202</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4084781932188881</v>
+        <v>0.4087309088243788</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.352631639915378</v>
+        <v>0.3523692138956416</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3776899193248638</v>
+        <v>0.3779538974631316</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3962803967435647</v>
+        <v>0.3962251172181989</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3512364645341589</v>
+        <v>0.3514910748964758</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4682400225829401</v>
+        <v>0.4682776065793735</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3234851725768356</v>
+        <v>0.3232363401939202</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3186550814509799</v>
+        <v>0.3186083559741433</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.424869773517303</v>
+        <v>0.4246020579587555</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3730426564933626</v>
+        <v>0.3729903858041885</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2900061356713853</v>
+        <v>0.2899675167461703</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>45</v>
       </c>
       <c r="C404">
-        <v>0.3175047775126165</v>
+        <v>0.3175360773966646</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.3930068838017378</v>
+        <v>0.3929794712241717</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>80</v>
       </c>
       <c r="C406">
-        <v>0.4777576219765692</v>
+        <v>0.4779122023011237</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3511848215070617</v>
+        <v>0.3511229843719513</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4281911595605447</v>
+        <v>0.4281430937149495</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4718092660774478</v>
+        <v>0.4717704640621001</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3131463525423306</v>
+        <v>0.312897823165637</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3038333958684844</v>
+        <v>0.304105233267457</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4396536440173752</v>
+        <v>0.4396043747850718</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2680321768169744</v>
+        <v>0.2678124782510752</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>10</v>
       </c>
       <c r="C414">
-        <v>0.3300139068429414</v>
+        <v>0.3302848933546773</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3251022796321989</v>
+        <v>0.3248559088024955</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3491456602088209</v>
+        <v>0.3488926485295074</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.296997496060187</v>
+        <v>0.2969600129055217</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>45</v>
       </c>
       <c r="C418">
-        <v>0.3176574167317129</v>
+        <v>0.3176846158634196</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.386350975168991</v>
+        <v>0.3860757411455151</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>45</v>
       </c>
       <c r="C420">
-        <v>0.4608689377848685</v>
+        <v>0.460892573458606</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>45</v>
       </c>
       <c r="C421">
-        <v>0.404295877684205</v>
+        <v>0.4043262313625419</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3592656733860785</v>
+        <v>0.3592126343553975</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>45</v>
       </c>
       <c r="C423">
-        <v>0.4535415408882609</v>
+        <v>0.4535858936439449</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.309980467554482</v>
+        <v>0.3102485711038153</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3187488620258687</v>
+        <v>0.3187065280614216</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3572497867053049</v>
+        <v>0.3569991256457595</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2525429651535341</v>
+        <v>0.2523091313360108</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2667113496632</v>
+        <v>0.266472001642879</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.34578574689476</v>
+        <v>0.3460536530396763</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3087587518325001</v>
+        <v>0.3087184337994641</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>15</v>
       </c>
       <c r="C431">
-        <v>0.2732319736441867</v>
+        <v>0.2730144141879683</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3130740852039834</v>
+        <v>0.3128234465667463</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3144539071726312</v>
+        <v>0.3144001315645454</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3448981490687766</v>
+        <v>0.3446352925363452</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3833303388778149</v>
+        <v>0.3835964988557198</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3291678491517077</v>
+        <v>0.3289273114921393</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3087414162107683</v>
+        <v>0.3090034667935982</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3593586250155537</v>
+        <v>0.3590759443003201</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3092861619335975</v>
+        <v>0.3092426214085327</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3152268174336217</v>
+        <v>0.3154957992333819</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.2929149629839986</v>
+        <v>0.2928671164994046</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3412531768204681</v>
+        <v>0.3412034971226596</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.2936629451592391</v>
+        <v>0.2934183642409439</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3115485263037371</v>
+        <v>0.3118020936745044</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3412926217680126</v>
+        <v>0.3412490950689892</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>45</v>
       </c>
       <c r="C446">
-        <v>0.3783879839679469</v>
+        <v>0.3784220243083811</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2951059101837285</v>
+        <v>0.2948615553283793</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3723544020935158</v>
+        <v>0.3723081887705632</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3559505358576879</v>
+        <v>0.3559054211844607</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>45</v>
       </c>
       <c r="C450">
-        <v>0.365474779067582</v>
+        <v>0.3655168497891842</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>45</v>
       </c>
       <c r="C451">
-        <v>0.4400500772761061</v>
+        <v>0.4400868062943886</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2824861686700084</v>
+        <v>0.2824384626014126</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3632755683280363</v>
+        <v>0.3635547378570189</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2736101857591355</v>
+        <v>0.273380818902087</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3067977522613501</v>
+        <v>0.3070673128793995</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3116611202772487</v>
+        <v>0.3116086119303234</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3546982688267348</v>
+        <v>0.3544537814016951</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3360690518820298</v>
+        <v>0.3360217151294216</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3310730955708794</v>
+        <v>0.3310306265179507</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>15</v>
       </c>
       <c r="C460">
-        <v>0.3499631456090554</v>
+        <v>0.3497113575459847</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3100110353866648</v>
+        <v>0.3102832058768457</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.295174729525442</v>
+        <v>0.2951199538253073</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3175972829084052</v>
+        <v>0.3173431389469031</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3803593095550749</v>
+        <v>0.3803018377096156</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>45</v>
       </c>
       <c r="C465">
-        <v>0.401848341780075</v>
+        <v>0.4018791292073734</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5119715410173421</v>
+        <v>0.5119195926104859</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4178900427106604</v>
+        <v>0.4178461864262614</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3800209737120411</v>
+        <v>0.3799689470259686</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2859813324560533</v>
+        <v>0.2857347491897689</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3167320259142452</v>
+        <v>0.3166975806255047</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3052732161253165</v>
+        <v>0.3055173586380364</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3397955771318765</v>
+        <v>0.3395395474993761</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>45</v>
       </c>
       <c r="C473">
-        <v>0.3346019209651814</v>
+        <v>0.3346231905573269</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3570939901372787</v>
+        <v>0.3573655536432784</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3609458767807003</v>
+        <v>0.3608943004400553</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3078561077645003</v>
+        <v>0.3078145205904246</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>15</v>
       </c>
       <c r="C477">
-        <v>0.341373910096145</v>
+        <v>0.3411111539300127</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4032154620318777</v>
+        <v>0.4031610562392523</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>45</v>
       </c>
       <c r="C479">
-        <v>0.4096218086848217</v>
+        <v>0.4096583070766168</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4177116025701006</v>
+        <v>0.4176589919714969</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>45</v>
       </c>
       <c r="C481">
-        <v>0.3920043524892423</v>
+        <v>0.3920328299605533</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3069549661471149</v>
+        <v>0.3072209500829088</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3181125204381248</v>
+        <v>0.3183757520177675</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>45</v>
       </c>
       <c r="C484">
-        <v>0.3839439192267289</v>
+        <v>0.3839812346456542</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3647104049921775</v>
+        <v>0.3644352232714033</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3880836418657497</v>
+        <v>0.3878187269546011</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>45</v>
       </c>
       <c r="C487">
-        <v>0.4571329494434789</v>
+        <v>0.4571624583650462</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3461764371795718</v>
+        <v>0.3464487816362369</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4488900411480692</v>
+        <v>0.4488287808389586</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3125676863827651</v>
+        <v>0.3123205056904071</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>15</v>
       </c>
       <c r="C491">
-        <v>0.2702317397813721</v>
+        <v>0.2699936106665689</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4605097769083669</v>
+        <v>0.4604490214633638</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3156631474744012</v>
+        <v>0.3156058146594751</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>45</v>
       </c>
       <c r="C494">
-        <v>0.3236467553169627</v>
+        <v>0.3236602796368406</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>45</v>
       </c>
       <c r="C495">
-        <v>0.5257538416676516</v>
+        <v>0.5257919783482017</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4501307833104078</v>
+        <v>0.4500822896704332</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3425926930428181</v>
+        <v>0.3428617281783524</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6485183690510853</v>
+        <v>0.6485841497303375</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3803376324250616</v>
+        <v>0.3800529150632701</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3740153777530699</v>
+        <v>0.3739727180763645</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3437097675858076</v>
+        <v>0.3434609828490527</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.560434457098564</v>
+        <v>0.5603885213652796</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3459257073283095</v>
+        <v>0.3456531269009137</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>6</v>
       </c>
       <c r="C504">
-        <v>0.3049182984917297</v>
+        <v>0.3048737075202556</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4306666964679278</v>
+        <v>0.4306132850563954</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4408388963492982</v>
+        <v>0.4405395140540376</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.2951637635330851</v>
+        <v>0.2954113908457857</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3209172014053107</v>
+        <v>0.3206610557174391</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4511486904392834</v>
+        <v>0.45144873441758</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3557855732294958</v>
+        <v>0.3560733241318851</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>45</v>
       </c>
       <c r="C511">
-        <v>0.3863145991535313</v>
+        <v>0.3863620365984127</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2946641230139691</v>
+        <v>0.2946165867730811</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.368466973796776</v>
+        <v>0.3684162798228464</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>45</v>
       </c>
       <c r="C514">
-        <v>0.4181624379822251</v>
+        <v>0.4182068038522778</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4945404362711351</v>
+        <v>0.4944843562883525</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3020976047696739</v>
+        <v>0.3020567498364609</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3226831921033473</v>
+        <v>0.3224291017452579</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3078510445682313</v>
+        <v>0.3081129393686016</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>45</v>
       </c>
       <c r="C519">
-        <v>0.4765268093148343</v>
+        <v>0.476560053872467</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3228192833179416</v>
+        <v>0.3225684008917846</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3043788115361888</v>
+        <v>0.3046348215894539</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3525434807607541</v>
+        <v>0.3522748255461715</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4225060152790976</v>
+        <v>0.4224709535229624</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.278719157569129</v>
+        <v>0.2786874139910143</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>45</v>
       </c>
       <c r="C525">
-        <v>0.421629657580746</v>
+        <v>0.4216786834081071</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>45</v>
       </c>
       <c r="C526">
-        <v>0.445179887881905</v>
+        <v>0.4452199730585119</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3441377489813401</v>
+        <v>0.3444100447361247</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4411598781177027</v>
+        <v>0.4411019114616536</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3269008076616604</v>
+        <v>0.3271773838563044</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>45</v>
       </c>
       <c r="C530">
-        <v>0.4929330277132449</v>
+        <v>0.492976533625236</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>45</v>
       </c>
       <c r="C531">
-        <v>0.5833429767900368</v>
+        <v>0.5833798369907374</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>45</v>
       </c>
       <c r="C532">
-        <v>0.3100812541067824</v>
+        <v>0.310109125748361</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4164658704403154</v>
+        <v>0.4162028254093524</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>6</v>
       </c>
       <c r="C534">
-        <v>0.2989847875203512</v>
+        <v>0.2989483751934589</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3006994393991956</v>
+        <v>0.3006574452968384</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3085481987455175</v>
+        <v>0.308293012824479</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3870501913061548</v>
+        <v>0.3870033492852393</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2874451359749816</v>
+        <v>0.2872057028707105</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3044960961690293</v>
+        <v>0.3044511430348754</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.275037541003478</v>
+        <v>0.2748156901785596</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4164425633531035</v>
+        <v>0.4164073368832348</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>45</v>
       </c>
       <c r="C542">
-        <v>0.4075016138918661</v>
+        <v>0.4075407361454353</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3940702808069877</v>
+        <v>0.3940105915362205</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3572967985831095</v>
+        <v>0.3572389267949311</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2690105680143081</v>
+        <v>0.2690105680143082</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3177251028942784</v>
+        <v>0.3177251028942785</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2612073347443773</v>
+        <v>0.2612073347443774</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4067040151987543</v>
+        <v>0.4067040151987542</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3265702287762656</v>
+        <v>0.3265702287762658</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>45</v>
       </c>
       <c r="C574">
-        <v>0.3028456434777809</v>
+        <v>0.3028456434777808</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3698231117449726</v>
+        <v>0.3698231117449727</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2919594411842059</v>
+        <v>0.291959441184206</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3539930473586655</v>
+        <v>0.3539930473586654</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.2940333724000349</v>
+        <v>0.294033372400035</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3509493963487059</v>
+        <v>0.350949396348706</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4147576516194132</v>
+        <v>0.4147576516194134</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.2893096138868425</v>
+        <v>0.2893096138868426</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>6</v>
       </c>
       <c r="C583">
-        <v>0.377930850660432</v>
+        <v>0.3779308506604319</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2805660414157179</v>
+        <v>0.2805660414157181</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3109198236844402</v>
+        <v>0.3109198236844404</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>45</v>
       </c>
       <c r="C589">
-        <v>0.334880147352805</v>
+        <v>0.3348801473528051</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.4498428338083647</v>
+        <v>0.4498428338083648</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3616150735580669</v>
+        <v>0.3616150735580671</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.5284429984532093</v>
+        <v>0.5284429984532094</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4029520642890408</v>
+        <v>0.402952064289041</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2581521998596382</v>
+        <v>0.2581521998596381</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.3027521919912147</v>
+        <v>0.3027521919912148</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2791350443565828</v>
+        <v>0.2791350443565827</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2807495838551311</v>
+        <v>0.2807495838551312</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>45</v>
       </c>
       <c r="C605">
-        <v>0.280490914003508</v>
+        <v>0.2804909140035079</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.2846142319580898</v>
+        <v>0.2846142319580899</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.3152593720728452</v>
+        <v>0.3152593720728451</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2442559023413335</v>
+        <v>0.2442559023413333</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>45</v>
       </c>
       <c r="C612">
-        <v>0.3840648677724066</v>
+        <v>0.3840648677724065</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3265343579132391</v>
+        <v>0.326534357913239</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3696786189294876</v>
+        <v>0.3696786189294877</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3260999878488807</v>
+        <v>0.3260999878488808</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3268663846519788</v>
+        <v>0.3268663846519787</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>15</v>
       </c>
       <c r="C622">
-        <v>0.2275404253202313</v>
+        <v>0.2275404253202314</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2722995902607807</v>
+        <v>0.2722995902607805</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14897,7 +14897,7 @@
         <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2521530024585635</v>
+        <v>0.2521530024585636</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3027961559975631</v>
+        <v>0.3027961559975632</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.3217575982867497</v>
+        <v>0.3217575982867499</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2830052487288737</v>
+        <v>0.2830052487288738</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3895353849245772</v>
+        <v>0.3895353849245771</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.4518529565287717</v>
+        <v>0.4518529565287715</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.3330863011539898</v>
+        <v>0.33308630115399</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3621577104358017</v>
+        <v>0.3621577104358016</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.487291006358283</v>
+        <v>0.4872910063582829</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3113728459237843</v>
+        <v>0.3113728459237841</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.263217694231395</v>
+        <v>0.2632176942313951</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.3311501451174218</v>
+        <v>0.331150145117422</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.302798518075402</v>
+        <v>0.3027985180754022</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2919865086088561</v>
+        <v>0.291986508608856</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>1266</v>
       </c>
       <c r="C645">
-        <v>0.2458327937744067</v>
+        <v>0.2458327937744069</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2702503401802666</v>
+        <v>0.2702503401802665</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>1266</v>
       </c>
       <c r="C650">
-        <v>0.2780759251476082</v>
+        <v>0.2780759251476083</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2731890869974225</v>
+        <v>0.277291960996215</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3996834850583485</v>
+        <v>0.4017809619558773</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3666158421547488</v>
+        <v>0.3710835749703816</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3330553881030072</v>
+        <v>0.325693636209995</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3512736284212313</v>
+        <v>0.3527181556040812</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>0.2832193906265477</v>
+        <v>0.2829471913172449</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3463004079274083</v>
+        <v>0.3388295362794972</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3107449472632849</v>
+        <v>0.3037905169621366</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3224864117201496</v>
+        <v>0.3241388560586246</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2474386313360999</v>
+        <v>0.2412925284624479</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4111173766481203</v>
+        <v>0.4158601184407265</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.2959813806281669</v>
+        <v>0.2896267458522633</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3852372276325588</v>
+        <v>0.377488457846987</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3341340164338367</v>
+        <v>0.3354955623367066</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.2835704948855043</v>
+        <v>0.2875605519184178</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2725952644456928</v>
+        <v>0.2660459029862736</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2797663816875068</v>
+        <v>0.2812433224745551</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>45</v>
       </c>
       <c r="C19">
-        <v>0.419510256107003</v>
+        <v>0.4202213481675295</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3932511050718077</v>
+        <v>0.3971974227949642</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3869801342194137</v>
+        <v>0.3888208401337501</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3185825831063429</v>
+        <v>0.3227110001827531</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3815955855164153</v>
+        <v>0.3860354357600342</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3157665784601392</v>
+        <v>0.3191548387559736</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.5704637043601798</v>
+        <v>0.5743141739353725</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3069507129881807</v>
+        <v>0.3114631707037078</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2709107066038902</v>
+        <v>0.2723048590122926</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3001056267093883</v>
+        <v>0.3014949849082639</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>45</v>
       </c>
       <c r="C29">
-        <v>0.4643788553261233</v>
+        <v>0.4651798586891095</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3524755763214208</v>
+        <v>0.356695542765499</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4054963817441615</v>
+        <v>0.4100131313464024</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.392343809092573</v>
+        <v>0.3848892144690036</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3554751668963511</v>
+        <v>0.3592883849903489</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3088500834847635</v>
+        <v>0.302160703933691</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4286937672550652</v>
+        <v>0.432755986537848</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>0.2550133214175332</v>
+        <v>0.2557193200123898</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.2832173390723448</v>
+        <v>0.2768630291831764</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3252837826892754</v>
+        <v>0.3294563660282523</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3405052023869318</v>
+        <v>0.3331067277415553</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4436113799021176</v>
+        <v>0.4484244083930765</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>20</v>
       </c>
       <c r="C41">
-        <v>0.2749489028880143</v>
+        <v>0.2749006737382146</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5191525591553324</v>
+        <v>0.5239597048583693</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3864296393144396</v>
+        <v>0.3782900003883791</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.3868478511515707</v>
+        <v>0.3788535576445727</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.377389347326093</v>
+        <v>0.3819795417038943</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4156455140660558</v>
+        <v>0.4204233259507213</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2859036433056031</v>
+        <v>0.2792832465157536</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.3972113653587483</v>
+        <v>0.389518457022661</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3289744295912151</v>
+        <v>0.321838447650258</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3560624745818616</v>
+        <v>0.3483327518968981</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3341336222149231</v>
+        <v>0.326696332635863</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5027855543387127</v>
+        <v>0.5075778804396623</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4167395478851277</v>
+        <v>0.4088284132604432</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3840286303150024</v>
+        <v>0.3885704916729709</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2682772373281074</v>
+        <v>0.269712092552892</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3313508524095074</v>
+        <v>0.3327649566829699</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5382174061133613</v>
+        <v>0.5430601702948123</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5309,10 +5309,10 @@
         <v>124</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3061467871207842</v>
+        <v>0.2995603745816332</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3629804924296078</v>
+        <v>0.3667991629573439</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.2802973014917337</v>
+        <v>0.2845651245932449</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3342690694464948</v>
+        <v>0.3383097441934277</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3134754634905552</v>
+        <v>0.3143794180279573</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3562992507308759</v>
+        <v>0.3604317701040795</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>45</v>
       </c>
       <c r="C64">
-        <v>0.2314080513790949</v>
+        <v>0.2317780434557803</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3216310557878241</v>
+        <v>0.3145467382446507</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3200119056826832</v>
+        <v>0.3140075611946589</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3433872272009656</v>
+        <v>0.335995165847114</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2493718781804786</v>
+        <v>0.2529904103978803</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>80</v>
       </c>
       <c r="C69">
-        <v>0.5673409809461826</v>
+        <v>0.5681350769138535</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>80</v>
       </c>
       <c r="C70">
-        <v>0.5225906468163186</v>
+        <v>0.5230315216805278</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4329657255888861</v>
+        <v>0.4366888513299752</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3359700793452768</v>
+        <v>0.340025415873439</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4896129678501382</v>
+        <v>0.4938071866142983</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4371402473826764</v>
+        <v>0.4414208252369139</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2430594694832757</v>
+        <v>0.2445420285701944</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3480667918786327</v>
+        <v>0.3494713852516239</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3210524072079386</v>
+        <v>0.3226312855109078</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4034850417811271</v>
+        <v>0.4055139613377092</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>0.2535355540043076</v>
+        <v>0.2575392674698221</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3452511609485241</v>
+        <v>0.3468955473093625</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2963153071352545</v>
+        <v>0.2896323871986439</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.3995996470451474</v>
+        <v>0.4014068373854037</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3865333897570747</v>
+        <v>0.391197642755533</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>15</v>
       </c>
       <c r="C84">
-        <v>0.2947200753351377</v>
+        <v>0.2878808673494411</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3302062294006716</v>
+        <v>0.3231066606261061</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.2801413141255369</v>
+        <v>0.2841309202946985</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2616954020069883</v>
+        <v>0.2656654894988665</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>80</v>
       </c>
       <c r="C88">
-        <v>0.3316401168222959</v>
+        <v>0.3322477383776872</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5836,10 +5836,10 @@
         <v>186</v>
       </c>
       <c r="B89" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C89">
-        <v>0.2935480096965258</v>
+        <v>0.2930080755317967</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2681237132932035</v>
+        <v>0.2696209654485522</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2682838134905657</v>
+        <v>0.2724540279196571</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>45</v>
       </c>
       <c r="C92">
-        <v>0.3375502674426004</v>
+        <v>0.3384823377590137</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3831431819939581</v>
+        <v>0.375243219678766</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.2566762142793432</v>
+        <v>0.2605004077350938</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3155769849718266</v>
+        <v>0.3085380115312084</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3613328234785266</v>
+        <v>0.3538085345484305</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>45</v>
       </c>
       <c r="C97">
-        <v>0.3579073122107756</v>
+        <v>0.358307094175879</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>45</v>
       </c>
       <c r="C98">
-        <v>0.362355413675806</v>
+        <v>0.3632411423462268</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4056270083741218</v>
+        <v>0.4094178154975308</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>45</v>
       </c>
       <c r="C100">
-        <v>0.3918610032818315</v>
+        <v>0.3924874870830619</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>45</v>
       </c>
       <c r="C101">
-        <v>0.4520140331017552</v>
+        <v>0.4530944165148593</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4290283937516334</v>
+        <v>0.4335988527571005</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3389035021198932</v>
+        <v>0.3431186438463646</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3399918177168225</v>
+        <v>0.3324262657918919</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>45</v>
       </c>
       <c r="C105">
-        <v>0.3512409063442349</v>
+        <v>0.3523585762491924</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3716112746163084</v>
+        <v>0.3728496237244538</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>45</v>
       </c>
       <c r="C107">
-        <v>0.350361397399039</v>
+        <v>0.3512941948442386</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.3967617859296316</v>
+        <v>0.4014123262372644</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>20</v>
       </c>
       <c r="C109">
-        <v>0.262348792225695</v>
+        <v>0.2618702089372352</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2837484941430751</v>
+        <v>0.2773342358844454</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4908208050650105</v>
+        <v>0.4948072090346822</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3604239711781717</v>
+        <v>0.3646465599876872</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4853549816241357</v>
+        <v>0.4771602710975908</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.5948801515847653</v>
+        <v>0.5987124899824117</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3024819137950779</v>
+        <v>0.3068153155508778</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4317233836289813</v>
+        <v>0.4368404122929329</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.264429409158885</v>
+        <v>0.2685832698732843</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.375123270396285</v>
+        <v>0.3771528924170043</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.365248637322291</v>
+        <v>0.3698595221932544</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3442355975778208</v>
+        <v>0.3458514917514542</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.2909929612483907</v>
+        <v>0.2946558140383462</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3271348927052412</v>
+        <v>0.3196527477037641</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2898320457208974</v>
+        <v>0.2831442728979647</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3673590101132331</v>
+        <v>0.3596055240996618</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>0.2778180066829818</v>
+        <v>0.2748374508949051</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3676490201203153</v>
+        <v>0.3717638796130566</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4768950402409398</v>
+        <v>0.4810307074093857</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.3960828688266318</v>
+        <v>0.3882641934082985</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="C129">
-        <v>0.2858458600248156</v>
+        <v>0.2873854746955893</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.4328389197864882</v>
+        <v>0.4249165816425359</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2652639144731969</v>
+        <v>0.2667082917349382</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3572433362744091</v>
+        <v>0.3617561412845595</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3220400117619798</v>
+        <v>0.3150682957562712</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3194050868779635</v>
+        <v>0.3239100101054236</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3274243279902584</v>
+        <v>0.331368668426456</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>45</v>
       </c>
       <c r="C136">
-        <v>0.3394150540333496</v>
+        <v>0.3399293735978097</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3747907404981838</v>
+        <v>0.37938566905307</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6669,10 +6669,10 @@
         <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3096466562439349</v>
+        <v>0.3100402915988685</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4194043211696282</v>
+        <v>0.4240733014658604</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>45</v>
       </c>
       <c r="C140">
-        <v>0.4064874472953158</v>
+        <v>0.4075723110787083</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3368634750840982</v>
+        <v>0.3413761355735224</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3722744168110607</v>
+        <v>0.3741068861943159</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6754,10 +6754,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>0.2869107338664426</v>
+        <v>0.2889248274958582</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5149677915139416</v>
+        <v>0.5186635228892565</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2669363237969181</v>
+        <v>0.2709557160432653</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4133607212816991</v>
+        <v>0.4177353957915003</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4191184101559514</v>
+        <v>0.4237028565344638</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3206143323126642</v>
+        <v>0.3245141256233538</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3499922889641674</v>
+        <v>0.3510296992650069</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3141607593121649</v>
+        <v>0.3073164682201561</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2337148206909468</v>
+        <v>0.2351022332184243</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6191715869715585</v>
+        <v>0.6230243282100028</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3221201557399923</v>
+        <v>0.3242000934408787</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="C154">
-        <v>0.3115919685370324</v>
+        <v>0.3133321159909714</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="C155">
-        <v>0.2693786834207951</v>
+        <v>0.263040830071073</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3292372399788503</v>
+        <v>0.3308733850661563</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3511878239339409</v>
+        <v>0.3557865154370302</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>45</v>
       </c>
       <c r="C158">
-        <v>0.377163934698311</v>
+        <v>0.3781116583976198</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>45</v>
       </c>
       <c r="C159">
-        <v>0.3882680721506582</v>
+        <v>0.3890632046707608</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3830576544558822</v>
+        <v>0.3874586538536944</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3563898414903429</v>
+        <v>0.3608362966177567</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5390843779034344</v>
+        <v>0.5436893692227475</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>45</v>
       </c>
       <c r="C163">
-        <v>0.4495592387784004</v>
+        <v>0.4501588788523025</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.2836279654067483</v>
+        <v>0.2849902542909545</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3340615422191347</v>
+        <v>0.3354136654900866</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>45</v>
       </c>
       <c r="C166">
-        <v>0.3456292448323147</v>
+        <v>0.3463274192293989</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3420638171893551</v>
+        <v>0.3464174819242861</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5572434298283805</v>
+        <v>0.5616352356863005</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>45</v>
       </c>
       <c r="C169">
-        <v>0.3658267336996434</v>
+        <v>0.3663340657502953</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3458037588315381</v>
+        <v>0.3501864806486128</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>45</v>
       </c>
       <c r="C171">
-        <v>0.2552191194763097</v>
+        <v>0.2555349685967502</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4214224271971195</v>
+        <v>0.4236981170823603</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3250215889553364</v>
+        <v>0.326624021552459</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3073061334381291</v>
+        <v>0.3115887840849396</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.3045112797055867</v>
+        <v>0.2979201659838987</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3876166275523616</v>
+        <v>0.3921658809274778</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5317942719584017</v>
+        <v>0.5360103851174605</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3890424501513491</v>
+        <v>0.3815424456865568</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3077994733057124</v>
+        <v>0.3010052822122408</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>45</v>
       </c>
       <c r="C180">
-        <v>0.3744852979436264</v>
+        <v>0.3752028634175426</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3317751252262934</v>
+        <v>0.3361446697774799</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2937394359514823</v>
+        <v>0.2952601946455822</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.3055180009122466</v>
+        <v>0.3097136537911451</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3257185816808302</v>
+        <v>0.3300233392030066</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>15</v>
       </c>
       <c r="C185">
-        <v>0.334806713715348</v>
+        <v>0.3278388094753844</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>45</v>
       </c>
       <c r="C186">
-        <v>0.4310428784265809</v>
+        <v>0.4320761652301892</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2370730021299846</v>
+        <v>0.231007283111277</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4393136638376079</v>
+        <v>0.442084104692801</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3167608604941766</v>
+        <v>0.3179871212097052</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2577027297614452</v>
+        <v>0.2616029424297667</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3334029902697402</v>
+        <v>0.3350290495269639</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4060737389959426</v>
+        <v>0.3979537503172871</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4288973490129452</v>
+        <v>0.4215307216301454</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3553090877817893</v>
+        <v>0.3603240033893292</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>20</v>
       </c>
       <c r="C195">
-        <v>0.3686909631656248</v>
+        <v>0.3688223113206409</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>80</v>
       </c>
       <c r="C196">
-        <v>0.3196754825406789</v>
+        <v>0.3203120942695679</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.2977718532422716</v>
+        <v>0.2994483539546928</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.483215803592919</v>
+        <v>0.4874742021368957</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.5364745120522867</v>
+        <v>0.5400634293918212</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>10</v>
       </c>
       <c r="C200">
-        <v>0.3192753998027191</v>
+        <v>0.3208654469122219</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3088662619119187</v>
+        <v>0.3022549731793827</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3417927567244875</v>
+        <v>0.3436256196281622</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.4819795799699422</v>
+        <v>0.486100618262633</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.471996931039137</v>
+        <v>0.4765709183980956</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4081681575437077</v>
+        <v>0.4099608331539586</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3506673342981533</v>
+        <v>0.3431691051287138</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>45</v>
       </c>
       <c r="C207">
-        <v>0.525377427715866</v>
+        <v>0.5257864629336464</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>45</v>
       </c>
       <c r="C208">
-        <v>0.4159290211631522</v>
+        <v>0.4171586625539604</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.4771214598363571</v>
+        <v>0.4785430830961167</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4196906013430968</v>
+        <v>0.4237199909478739</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4054458940749395</v>
+        <v>0.3972698264409871</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C212">
-        <v>0.2770432360761396</v>
+        <v>0.2740289804326873</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3471492587017801</v>
+        <v>0.3396337834580604</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3580584042005969</v>
+        <v>0.3507449423606132</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5681837258049387</v>
+        <v>0.5701128583943172</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.317796369664284</v>
+        <v>0.3109298788208324</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3145959139908964</v>
+        <v>0.3075601597399387</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3634906118826228</v>
+        <v>0.3676111452401755</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>45</v>
       </c>
       <c r="C219">
-        <v>0.4787458774152446</v>
+        <v>0.4798826307046511</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="C220">
-        <v>0.2850727480217654</v>
+        <v>0.2867515966916249</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.348313587766664</v>
+        <v>0.3410826064410246</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.2947309021696987</v>
+        <v>0.2991430352570507</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5138256242946968</v>
+        <v>0.5155791578417225</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3485000033367506</v>
+        <v>0.3498881342464662</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3462422056144061</v>
+        <v>0.338816765902476</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4522405644416394</v>
+        <v>0.4565001253588584</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3264004124808472</v>
+        <v>0.3279544733910626</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4478216478033977</v>
+        <v>0.4521574469348577</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.4678918457256477</v>
+        <v>0.471581950707535</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>45</v>
       </c>
       <c r="C230">
-        <v>0.3793382882223059</v>
+        <v>0.380470539605373</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3087256087437703</v>
+        <v>0.3132254384288745</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5738205589844051</v>
+        <v>0.5776804013256243</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>45</v>
       </c>
       <c r="C233">
-        <v>0.4604664658368461</v>
+        <v>0.4614600841334983</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.3898425522259859</v>
+        <v>0.3945482863766444</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4775298713028546</v>
+        <v>0.4819213206206003</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.250736309301051</v>
+        <v>0.2545992379391297</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.324584554707784</v>
+        <v>0.3260232153200676</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3088967176865974</v>
+        <v>0.3130644441459473</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.3910097506279728</v>
+        <v>0.3955478573732865</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>20</v>
       </c>
       <c r="C240">
-        <v>0.3511075332953673</v>
+        <v>0.3500979120477359</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>6</v>
       </c>
       <c r="C241">
-        <v>0.2318719746343891</v>
+        <v>0.2355784603363169</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3043280350926076</v>
+        <v>0.3087671403174517</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4254749719038978</v>
+        <v>0.4169426309053272</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>20</v>
       </c>
       <c r="C244">
-        <v>0.3514556541208051</v>
+        <v>0.35018566440908</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.5871050413590594</v>
+        <v>0.5910653690153199</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.433911799138176</v>
+        <v>0.4384855067957416</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4258013029650813</v>
+        <v>0.4302230095290447</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3367735403128483</v>
+        <v>0.3382662521730595</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4327332674582867</v>
+        <v>0.4368373220145094</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3533989992026901</v>
+        <v>0.3459375683137258</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>45</v>
       </c>
       <c r="C251">
-        <v>0.4719735323699444</v>
+        <v>0.4726481668997234</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.432984028102927</v>
+        <v>0.437721630572028</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3482440105139347</v>
+        <v>0.3527337862798675</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4535440136190794</v>
+        <v>0.4585393230707982</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4079307460070048</v>
+        <v>0.3993139622512582</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5311997363979404</v>
+        <v>0.5359580768488581</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3689910548685303</v>
+        <v>0.3733077330397593</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4804122228917141</v>
+        <v>0.4841923190710162</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3044799909263223</v>
+        <v>0.3089421826869821</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.3871905807816949</v>
+        <v>0.3916683369733749</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4103418820567779</v>
+        <v>0.4149038117888028</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3713599096231524</v>
+        <v>0.3753556126825288</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4588543582388119</v>
+        <v>0.4636229925812994</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.3877159049571143</v>
+        <v>0.3921855313471398</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.2934057693299821</v>
+        <v>0.29715281260065</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>20</v>
       </c>
       <c r="C266">
-        <v>0.3288429271148609</v>
+        <v>0.3278720975990084</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2779969860574772</v>
+        <v>0.2820952046300608</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.426647378164651</v>
+        <v>0.431326290603933</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>45</v>
       </c>
       <c r="C269">
-        <v>0.3653446707330477</v>
+        <v>0.3659251290449079</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.4884721181987628</v>
+        <v>0.4924824397013896</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.4883434608466046</v>
+        <v>0.4919810945287419</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3158766514614303</v>
+        <v>0.3199072075731652</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.494624265201998</v>
+        <v>0.4990321493362934</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.340755564582454</v>
+        <v>0.3336204859195055</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2504757139292913</v>
+        <v>0.2444746411034004</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3200707782842176</v>
+        <v>0.3240914381090479</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>80</v>
       </c>
       <c r="C277">
-        <v>0.3982061271880902</v>
+        <v>0.3988610541023275</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.437240806033782</v>
+        <v>0.4423500932063502</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5283035154184802</v>
+        <v>0.5329314260189301</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4469222428389935</v>
+        <v>0.4515145485671911</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3602211135781793</v>
+        <v>0.364529687605446</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3587412775477272</v>
+        <v>0.351275819481941</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3791386734222417</v>
+        <v>0.3838496866425183</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3073622089724057</v>
+        <v>0.3115129416854884</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2755665554647973</v>
+        <v>0.2692380759929583</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3062977007842542</v>
+        <v>0.310563062799866</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>45</v>
       </c>
       <c r="C287">
-        <v>0.4879194143501602</v>
+        <v>0.4884095551780621</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>15</v>
       </c>
       <c r="C288">
-        <v>0.2462084765180149</v>
+        <v>0.2399096094749317</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3568848064644838</v>
+        <v>0.3615715243612877</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3592466875392143</v>
+        <v>0.351809048982891</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4292197120521462</v>
+        <v>0.4338594263291719</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>80</v>
       </c>
       <c r="C292">
-        <v>0.4681486220271456</v>
+        <v>0.4696692108610314</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5706848977293811</v>
+        <v>0.5744371495905708</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3842133909407972</v>
+        <v>0.3766765159898068</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3512250406166735</v>
+        <v>0.3539739059448383</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.2740468942383446</v>
+        <v>0.2675896757638208</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4755721378536933</v>
+        <v>0.4775596559480303</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3654642758490134</v>
+        <v>0.3674983412053532</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>45</v>
       </c>
       <c r="C299">
-        <v>0.3017739344916547</v>
+        <v>0.3020090223226491</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3288729509461174</v>
+        <v>0.3303052125424228</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3520330426124753</v>
+        <v>0.3564498051697897</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>45</v>
       </c>
       <c r="C302">
-        <v>0.4978343125737101</v>
+        <v>0.4986288064249219</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3212517778903816</v>
+        <v>0.3229253090326237</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2714871244027537</v>
+        <v>0.2709389151991752</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>45</v>
       </c>
       <c r="C305">
-        <v>0.4498735258259645</v>
+        <v>0.450729377726961</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.3819191565054057</v>
+        <v>0.3746533167598236</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4387604731025528</v>
+        <v>0.4434172880034892</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3537353469374516</v>
+        <v>0.3581203591657898</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>10</v>
       </c>
       <c r="C309">
-        <v>0.2544837670412075</v>
+        <v>0.2558718910863761</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3714180537966165</v>
+        <v>0.3752411087102203</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3340876911856222</v>
+        <v>0.3269638798501616</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>10</v>
       </c>
       <c r="C312">
-        <v>0.2864367306694399</v>
+        <v>0.2881087426473353</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>10</v>
       </c>
       <c r="C313">
-        <v>0.266321782050805</v>
+        <v>0.2679211443864666</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3082145877865801</v>
+        <v>0.3095210068996197</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>45</v>
       </c>
       <c r="C315">
-        <v>0.4828745173921967</v>
+        <v>0.4834717639422403</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3746232108410319</v>
+        <v>0.3790368120707346</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.4682629238684478</v>
+        <v>0.4727172405783263</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.517634975343646</v>
+        <v>0.5220223769537663</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3047787475696113</v>
+        <v>0.3090175909746784</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C320">
-        <v>0.263065575801109</v>
+        <v>0.2587175828117153</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3099371458527243</v>
+        <v>0.314416842904029</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.4102891906644293</v>
+        <v>0.415100718520075</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.370586220374662</v>
+        <v>0.3723753377303713</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>45</v>
       </c>
       <c r="C324">
-        <v>0.4106432547008605</v>
+        <v>0.4114272619533969</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>10</v>
       </c>
       <c r="C325">
-        <v>0.2550363643046866</v>
+        <v>0.2565182251464185</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>45</v>
       </c>
       <c r="C326">
-        <v>0.3614667433397781</v>
+        <v>0.3624184060642561</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>45</v>
       </c>
       <c r="C327">
-        <v>0.3486826232840337</v>
+        <v>0.349721246851055</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2718691318663946</v>
+        <v>0.2654456922944198</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>15</v>
       </c>
       <c r="C329">
-        <v>0.3025914194022289</v>
+        <v>0.2960485435774149</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>6</v>
       </c>
       <c r="C330">
-        <v>0.2950881982799907</v>
+        <v>0.2995196980837722</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3406703505292503</v>
+        <v>0.3434198622238294</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3576042797254165</v>
+        <v>0.3592174018268457</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4340673012680558</v>
+        <v>0.4384543168411817</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>80</v>
       </c>
       <c r="C334">
-        <v>0.2855087264895134</v>
+        <v>0.2865086842392086</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10018,10 +10018,10 @@
         <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C335">
-        <v>0.3166324402235866</v>
+        <v>0.309863688019859</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.2777595715094676</v>
+        <v>0.2792390948016764</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>45</v>
       </c>
       <c r="C337">
-        <v>0.4889653749591809</v>
+        <v>0.4898436393891951</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.2797481395861633</v>
+        <v>0.2809994186155283</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.455855209767033</v>
+        <v>0.4475836547174362</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3092846985137886</v>
+        <v>0.3020833329962566</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2486665028937088</v>
+        <v>0.2523775570707018</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.258725458660699</v>
+        <v>0.2602494742184292</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.375196727501278</v>
+        <v>0.3769768372132268</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2928898509991285</v>
+        <v>0.2865002122099738</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.349696905411865</v>
+        <v>0.3541646842914932</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3482110117609485</v>
+        <v>0.3496939172797643</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3256175281595101</v>
+        <v>0.3184946854592572</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.2921458422993574</v>
+        <v>0.2960681263398671</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4806617609397184</v>
+        <v>0.4856454162022395</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.354437716107102</v>
+        <v>0.3470613729871183</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>80</v>
       </c>
       <c r="C351">
-        <v>0.2903704478950631</v>
+        <v>0.2910754050075383</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3966817000459791</v>
+        <v>0.3885548376602089</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3640582765304966</v>
+        <v>0.3659139353875432</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.260749237328832</v>
+        <v>0.2647419760749157</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3152511859641568</v>
+        <v>0.3195065331597545</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="C356">
-        <v>0.3019120855194085</v>
+        <v>0.303316890461082</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4088172729982106</v>
+        <v>0.4135479302749116</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3261792320868157</v>
+        <v>0.3299288974408745</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>45</v>
       </c>
       <c r="C359">
-        <v>0.462600463127239</v>
+        <v>0.4629420136262139</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.438034179262234</v>
+        <v>0.4416527569335458</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3040363766121623</v>
+        <v>0.2971738671476444</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3234537836751084</v>
+        <v>0.3277016792076467</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2812847576172484</v>
+        <v>0.2827200326117318</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.2811558048351003</v>
+        <v>0.2824575918422693</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3036345293068745</v>
+        <v>0.2967050911398446</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2588864554974043</v>
+        <v>0.2525502273137183</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10562,10 +10562,10 @@
         <v>742</v>
       </c>
       <c r="B367" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C367">
-        <v>0.2784782110246684</v>
+        <v>0.2723037803156916</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3211603788095643</v>
+        <v>0.3142037327672038</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4252213482780369</v>
+        <v>0.429414793399188</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3442870820604507</v>
+        <v>0.3371145782456617</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4585465982962904</v>
+        <v>0.4629743857896418</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3104077173927295</v>
+        <v>0.3144478707048167</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.3972459430383062</v>
+        <v>0.40114860510031</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4342171728926152</v>
+        <v>0.4379748016287689</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.413764114571708</v>
+        <v>0.4184248078585152</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.381215197787105</v>
+        <v>0.373869867445445</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4626898176105343</v>
+        <v>0.4670040039292218</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.2789791402286035</v>
+        <v>0.28310490529727</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3039714469196432</v>
+        <v>0.3081660454430948</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3397803270561676</v>
+        <v>0.3442018604964464</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4247732133574574</v>
+        <v>0.4266445562278698</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3369022315284393</v>
+        <v>0.3411695782886216</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3458374502083499</v>
+        <v>0.3474225780730816</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>45</v>
       </c>
       <c r="C384">
-        <v>0.4742699130294302</v>
+        <v>0.4745462581422086</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3720468539888261</v>
+        <v>0.3766536223414527</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.299227291373138</v>
+        <v>0.2923503590834966</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4349819731556097</v>
+        <v>0.4372699146866955</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>45</v>
       </c>
       <c r="C388">
-        <v>0.3499308599251187</v>
+        <v>0.3505015468906392</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3632316566683695</v>
+        <v>0.3677501905407636</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3375580826284844</v>
+        <v>0.3302637110418306</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3392437563907716</v>
+        <v>0.3319418742973394</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.327865141090202</v>
+        <v>0.3293873442559936</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4087309088243788</v>
+        <v>0.4103863393148087</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3523692138956416</v>
+        <v>0.3449410757278949</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3779538974631316</v>
+        <v>0.3793649570919138</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3962251172181989</v>
+        <v>0.4005985402935572</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3514910748964758</v>
+        <v>0.3528821061359603</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4682776065793735</v>
+        <v>0.4733335726810887</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3232363401939202</v>
+        <v>0.3164281944466554</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3186083559741433</v>
+        <v>0.3230835526823926</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4246020579587555</v>
+        <v>0.4171649416923944</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3729903858041885</v>
+        <v>0.377282825248878</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2899675167461703</v>
+        <v>0.2941656995871747</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>45</v>
       </c>
       <c r="C404">
-        <v>0.3175360773966646</v>
+        <v>0.3184663552365998</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.3929794712241717</v>
+        <v>0.3972744641373062</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>80</v>
       </c>
       <c r="C406">
-        <v>0.4779122023011237</v>
+        <v>0.4786835792895225</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3511229843719513</v>
+        <v>0.3548728081165048</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4281430937149495</v>
+        <v>0.4325350414011197</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4717704640621001</v>
+        <v>0.4762639970655455</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.312897823165637</v>
+        <v>0.3059435171753339</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.304105233267457</v>
+        <v>0.3055349675280697</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4396043747850718</v>
+        <v>0.4439001792022268</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2678124782510752</v>
+        <v>0.2616238480458306</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>10</v>
       </c>
       <c r="C414">
-        <v>0.3302848933546773</v>
+        <v>0.3322028337083728</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3248559088024955</v>
+        <v>0.3180036414694134</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3488926485295074</v>
+        <v>0.3429023522555896</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2969600129055217</v>
+        <v>0.3010091416705902</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>45</v>
       </c>
       <c r="C418">
-        <v>0.3176846158634196</v>
+        <v>0.3183270158257336</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3860757411455151</v>
+        <v>0.3781941881842809</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>45</v>
       </c>
       <c r="C420">
-        <v>0.460892573458606</v>
+        <v>0.4620336078718866</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>45</v>
       </c>
       <c r="C421">
-        <v>0.4043262313625419</v>
+        <v>0.4055160433640661</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3592126343553975</v>
+        <v>0.3636388955830344</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>45</v>
       </c>
       <c r="C423">
-        <v>0.4535858936439449</v>
+        <v>0.4545191892506971</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3102485711038153</v>
+        <v>0.3120172005161264</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3187065280614216</v>
+        <v>0.3230724255538148</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3569991256457595</v>
+        <v>0.3498573600558611</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2523091313360108</v>
+        <v>0.2460393379224394</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C428">
-        <v>0.266472001642879</v>
+        <v>0.2700969062804695</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3460536530396763</v>
+        <v>0.3474108201773781</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3087184337994641</v>
+        <v>0.3132532266495295</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C431">
-        <v>0.2730144141879683</v>
+        <v>0.2748729040028564</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3128234465667463</v>
+        <v>0.3060274865104196</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3144001315645454</v>
+        <v>0.3186732405924446</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3446352925363452</v>
+        <v>0.3373466868904968</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3835964988557198</v>
+        <v>0.3852617998327044</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3289273114921393</v>
+        <v>0.3220833788651397</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3090034667935982</v>
+        <v>0.3106362505225571</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3590759443003201</v>
+        <v>0.351169294440441</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3092426214085327</v>
+        <v>0.3131753255671202</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3154957992333819</v>
+        <v>0.317134981094663</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.2928671164994046</v>
+        <v>0.2972414995446891</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3412034971226596</v>
+        <v>0.3453137129592652</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.2934183642409439</v>
+        <v>0.2867036838190634</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3118020936745044</v>
+        <v>0.3137782831279604</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3412490950689892</v>
+        <v>0.345834848277266</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>45</v>
       </c>
       <c r="C446">
-        <v>0.3784220243083811</v>
+        <v>0.3785289480037506</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2948615553283793</v>
+        <v>0.2881666702173092</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3723081887705632</v>
+        <v>0.376723459288349</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3559054211844607</v>
+        <v>0.3601744681825012</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>45</v>
       </c>
       <c r="C450">
-        <v>0.3655168497891842</v>
+        <v>0.3664088430415279</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>45</v>
       </c>
       <c r="C451">
-        <v>0.4400868062943886</v>
+        <v>0.4407641946958372</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2824384626014126</v>
+        <v>0.2866858111613779</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3635547378570189</v>
+        <v>0.3651022977518647</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.273380818902087</v>
+        <v>0.2669624114769655</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3070673128793995</v>
+        <v>0.3087096552940747</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3116086119303234</v>
+        <v>0.3155622961375231</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3544537814016951</v>
+        <v>0.3475035424027257</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3360217151294216</v>
+        <v>0.3406566143441734</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3310306265179507</v>
+        <v>0.3353703585495569</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>15</v>
       </c>
       <c r="C460">
-        <v>0.3497113575459847</v>
+        <v>0.3425766693463171</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>10</v>
       </c>
       <c r="C461">
-        <v>0.3102832058768457</v>
+        <v>0.3116468945325233</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.2951199538253073</v>
+        <v>0.2994078204392774</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3173431389469031</v>
+        <v>0.3101755928075769</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3803018377096156</v>
+        <v>0.3840395642888844</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>45</v>
       </c>
       <c r="C465">
-        <v>0.4018791292073734</v>
+        <v>0.4026821035950487</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5119195926104859</v>
+        <v>0.5161018045694561</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4178461864262614</v>
+        <v>0.4222744692507661</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3799689470259686</v>
+        <v>0.3842154652771341</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2857347491897689</v>
+        <v>0.2790199845567272</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3166975806255047</v>
+        <v>0.3209814357831016</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3055173586380364</v>
+        <v>0.3073434647802239</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3395395474993761</v>
+        <v>0.3325692050017597</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>45</v>
       </c>
       <c r="C473">
-        <v>0.3346231905573269</v>
+        <v>0.3352903727882012</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3573655536432784</v>
+        <v>0.3586947193186428</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3608943004400553</v>
+        <v>0.3653365143937059</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3078145205904246</v>
+        <v>0.3120970750947351</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>15</v>
       </c>
       <c r="C477">
-        <v>0.3411111539300127</v>
+        <v>0.3336580408276894</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4031610562392523</v>
+        <v>0.4076271510058423</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>45</v>
       </c>
       <c r="C479">
-        <v>0.4096583070766168</v>
+        <v>0.410756360741184</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4176589919714969</v>
+        <v>0.422176247125554</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>45</v>
       </c>
       <c r="C481">
-        <v>0.3920328299605533</v>
+        <v>0.3932830990450652</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3072209500829088</v>
+        <v>0.3087935148353653</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3183757520177675</v>
+        <v>0.3201030425586805</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>45</v>
       </c>
       <c r="C484">
-        <v>0.3839812346456542</v>
+        <v>0.3849910990851387</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3644352232714033</v>
+        <v>0.3565968438526058</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3878187269546011</v>
+        <v>0.3803440033606869</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>45</v>
       </c>
       <c r="C487">
-        <v>0.4571624583650462</v>
+        <v>0.4596973381527554</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3464487816362369</v>
+        <v>0.3479902991743904</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4488287808389586</v>
+        <v>0.4528445507502809</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3123205056904071</v>
+        <v>0.3057248460364979</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C491">
-        <v>0.2699936106665689</v>
+        <v>0.2700364001431496</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4604490214633638</v>
+        <v>0.4643982343281005</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3156058146594751</v>
+        <v>0.3196722459638836</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>45</v>
       </c>
       <c r="C494">
-        <v>0.3236602796368406</v>
+        <v>0.3255500522930692</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>45</v>
       </c>
       <c r="C495">
-        <v>0.5257919783482017</v>
+        <v>0.5263708231095314</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4500822896704332</v>
+        <v>0.4546448090615399</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3428617281783524</v>
+        <v>0.3439887447962816</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6485841497303375</v>
+        <v>0.6529372709790503</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3800529150632701</v>
+        <v>0.3721421040923648</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3739727180763645</v>
+        <v>0.3785948026573989</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3434609828490527</v>
+        <v>0.3365322211992172</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5603885213652796</v>
+        <v>0.5649367716553365</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3456531269009137</v>
+        <v>0.3379278517207226</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>6</v>
       </c>
       <c r="C504">
-        <v>0.3048737075202556</v>
+        <v>0.3093470222975075</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4306132850563954</v>
+        <v>0.4351850562919998</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4405395140540376</v>
+        <v>0.4320379480198651</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.2954113908457857</v>
+        <v>0.2965976575778214</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3206610557174391</v>
+        <v>0.3135532883475335</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.45144873441758</v>
+        <v>0.4535606866084286</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3560733241318851</v>
+        <v>0.3576391947205351</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>45</v>
       </c>
       <c r="C511">
-        <v>0.3863620365984127</v>
+        <v>0.3868570171274341</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2946165867730811</v>
+        <v>0.2988427347380892</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3684162798228464</v>
+        <v>0.3729420822509257</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>45</v>
       </c>
       <c r="C514">
-        <v>0.4182068038522778</v>
+        <v>0.4190796921455509</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4944843562883525</v>
+        <v>0.4989634992548926</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3020567498364609</v>
+        <v>0.3064041944755737</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3224291017452579</v>
+        <v>0.3152642974889923</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3081129393686016</v>
+        <v>0.3098214425539756</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>45</v>
       </c>
       <c r="C519">
-        <v>0.476560053872467</v>
+        <v>0.4777256569481673</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3225684008917846</v>
+        <v>0.3155312759530808</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3046348215894539</v>
+        <v>0.3059610024273849</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3522748255461715</v>
+        <v>0.3446577071981979</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4224709535229624</v>
+        <v>0.4270836437030606</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2786874139910143</v>
+        <v>0.2827607193916583</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>45</v>
       </c>
       <c r="C525">
-        <v>0.4216786834081071</v>
+        <v>0.421700703873447</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>45</v>
       </c>
       <c r="C526">
-        <v>0.4452199730585119</v>
+        <v>0.4462036721239022</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3444100447361247</v>
+        <v>0.3459097410701322</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4411019114616536</v>
+        <v>0.4453467291936897</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3271773838563044</v>
+        <v>0.3289504736585668</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>45</v>
       </c>
       <c r="C530">
-        <v>0.492976533625236</v>
+        <v>0.4942098281033007</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>45</v>
       </c>
       <c r="C531">
-        <v>0.5833798369907374</v>
+        <v>0.584471035209375</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>45</v>
       </c>
       <c r="C532">
-        <v>0.310109125748361</v>
+        <v>0.3106880948031883</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4162028254093524</v>
+        <v>0.408829373950657</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>6</v>
       </c>
       <c r="C534">
-        <v>0.2989483751934589</v>
+        <v>0.3034647749776237</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3006574452968384</v>
+        <v>0.3049756203074195</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.308293012824479</v>
+        <v>0.3011798312148798</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3870033492852393</v>
+        <v>0.391460884122098</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2872057028707105</v>
+        <v>0.2805109289657787</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3044511430348754</v>
+        <v>0.3088453722825179</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2748156901785596</v>
+        <v>0.26858108181721</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4164073368832348</v>
+        <v>0.4210628199284728</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>45</v>
       </c>
       <c r="C542">
-        <v>0.4075407361454353</v>
+        <v>0.4085957965086758</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3940105915362205</v>
+        <v>0.3977722119155333</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3572389267949311</v>
+        <v>0.3613517905243049</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2690105680143082</v>
+        <v>0.2687491782204811</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3177251028942785</v>
+        <v>0.3174200962617724</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2612073347443774</v>
+        <v>0.2609468159772826</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.4692636361466231</v>
+        <v>0.4689585749377365</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4067040151987542</v>
+        <v>0.4064407691361006</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3265702287762658</v>
+        <v>0.3262609241334073</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2725871796309934</v>
+        <v>0.2723285899309967</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>10</v>
       </c>
       <c r="C570">
-        <v>0.2973980033569115</v>
+        <v>0.297638705894047</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2785945084718467</v>
+        <v>0.2783329881035538</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.3339394241823059</v>
+        <v>0.3336282744655584</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.2742210821650125</v>
+        <v>0.2739596044066941</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>45</v>
       </c>
       <c r="C574">
-        <v>0.3028456434777808</v>
+        <v>0.3031163294349688</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3119341197899996</v>
+        <v>0.3116261532872319</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3698231117449727</v>
+        <v>0.3696645876640704</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.291959441184206</v>
+        <v>0.291972577903216</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3539930473586654</v>
+        <v>0.3537495593721368</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.294033372400035</v>
+        <v>0.2937586287526299</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.350949396348706</v>
+        <v>0.3511510509625057</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4147576516194134</v>
+        <v>0.4144750607440022</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.2893096138868426</v>
+        <v>0.2890492946307441</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>6</v>
       </c>
       <c r="C583">
-        <v>0.3779308506604319</v>
+        <v>0.3779613341863146</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>6</v>
       </c>
       <c r="C584">
-        <v>0.2909773104359007</v>
+        <v>0.2910273262447091</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.3590663072187273</v>
+        <v>0.3588303807374129</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2805660414157181</v>
+        <v>0.2803573330566558</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3109198236844404</v>
+        <v>0.3108448138838268</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.2658543187802467</v>
+        <v>0.2656055159295865</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>45</v>
       </c>
       <c r="C589">
-        <v>0.3348801473528051</v>
+        <v>0.3351631571203056</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4162449782215457</v>
+        <v>0.4162409695654517</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.4498428338083648</v>
+        <v>0.4495712298772098</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3616150735580671</v>
+        <v>0.3613645465870011</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.5284429984532094</v>
+        <v>0.5281591379743067</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.402952064289041</v>
+        <v>0.4025995554958594</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3381832858024464</v>
+        <v>0.3382808696188604</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4199716629659814</v>
+        <v>0.4196925604624839</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3512890035148448</v>
+        <v>0.3509917650253619</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2581521998596381</v>
+        <v>0.2583308293230095</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.3027521919912148</v>
+        <v>0.3024776969982798</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2791350443565827</v>
+        <v>0.2788689286067543</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2807495838551312</v>
+        <v>0.280471957453105</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3673640637629877</v>
+        <v>0.3670262886535851</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2923137433218961</v>
+        <v>0.2920402053359418</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3036732982785109</v>
+        <v>0.3036730259752044</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>45</v>
       </c>
       <c r="C605">
-        <v>0.2804909140035079</v>
+        <v>0.2807425528234912</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3717057904590055</v>
+        <v>0.3718096722167662</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C607">
-        <v>0.2846142319580899</v>
+        <v>0.2847287438273493</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>1143</v>
       </c>
       <c r="C608">
-        <v>0.2988339006103424</v>
+        <v>0.2986111272197359</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.3152593720728451</v>
+        <v>0.3150170046836258</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2442559023413333</v>
+        <v>0.2440280549437927</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>45</v>
       </c>
       <c r="C611">
-        <v>0.4649064157757105</v>
+        <v>0.465181748047462</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>45</v>
       </c>
       <c r="C612">
-        <v>0.3840648677724065</v>
+        <v>0.3843419185298139</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.326534357913239</v>
+        <v>0.3262375992790741</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.3710125022602774</v>
+        <v>0.3706956699174769</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.31410023344431</v>
+        <v>0.3138007677597047</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3696786189294877</v>
+        <v>0.3694378370629566</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3260999878488808</v>
+        <v>0.3258111964955274</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.2893262440264847</v>
+        <v>0.2895310426859918</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4169620502023828</v>
+        <v>0.4167038922543281</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14812,7 +14812,7 @@
         <v>15</v>
       </c>
       <c r="C620">
-        <v>0.2891314228241091</v>
+        <v>0.2889662860768512</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3268663846519787</v>
+        <v>0.3266220389769623</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>15</v>
       </c>
       <c r="C622">
-        <v>0.2275404253202314</v>
+        <v>0.2273802750458805</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2392847862985188</v>
+        <v>0.2394313482187342</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2722995902607805</v>
+        <v>0.272456806265866</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14897,7 +14897,7 @@
         <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2521530024585636</v>
+        <v>0.2523072595955246</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3027961559975632</v>
+        <v>0.3026200783138855</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.3217575982867499</v>
+        <v>0.3219157821145738</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2830052487288738</v>
+        <v>0.2831941595741423</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>1266</v>
       </c>
       <c r="C629">
-        <v>0.2188305089201392</v>
+        <v>0.2189670077823594</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3895353849245771</v>
+        <v>0.3899090965408467</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3997078850171333</v>
+        <v>0.3998742661564533</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.4518529565287715</v>
+        <v>0.4520557764339608</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2662182419519051</v>
+        <v>0.2660185554471572</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.33308630115399</v>
+        <v>0.332863950609976</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4650725858900553</v>
+        <v>0.4653730445461359</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3621577104358016</v>
+        <v>0.3621924257108051</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>1266</v>
       </c>
       <c r="C637">
-        <v>0.3193161758528884</v>
+        <v>0.3194798369458868</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4872910063582829</v>
+        <v>0.4874907647329959</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3113728459237841</v>
+        <v>0.3115543259320968</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2632176942313951</v>
+        <v>0.2633706030578041</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>1266</v>
       </c>
       <c r="C641">
-        <v>0.2837883937185025</v>
+        <v>0.2839373345498962</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.331150145117422</v>
+        <v>0.3313296667827375</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3027985180754022</v>
+        <v>0.3025607103381028</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.291986508608856</v>
+        <v>0.2917902069776948</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>1266</v>
       </c>
       <c r="C645">
-        <v>0.2458327937744069</v>
+        <v>0.2459961474814001</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3305884568402281</v>
+        <v>0.3304333469519075</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>1266</v>
       </c>
       <c r="C647">
-        <v>0.3255603298081895</v>
+        <v>0.3257265599129234</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2702503401802665</v>
+        <v>0.270084975954196</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.2934592544460942</v>
+        <v>0.2932684585158645</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>1266</v>
       </c>
       <c r="C650">
-        <v>0.2780759251476083</v>
+        <v>0.2782071676581046</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.3014870811565031</v>
+        <v>0.3012697990966122</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>45</v>
       </c>
       <c r="B6">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.277291960996215</v>
+        <v>0.2783397162352091</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4017809619558773</v>
+        <v>0.3908213891285116</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3710835749703816</v>
+        <v>0.3741141682964865</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.325693636209995</v>
+        <v>0.3270360202658594</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3527181556040812</v>
+        <v>0.3447481455512441</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>20</v>
       </c>
       <c r="C7">
-        <v>0.2829471913172449</v>
+        <v>0.2841931363389094</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3388295362794972</v>
+        <v>0.3309140702054094</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3037905169621366</v>
+        <v>0.3035155513653607</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3241388560586246</v>
+        <v>0.3345826706538367</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2412925284624479</v>
+        <v>0.2428555332887804</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4158601184407265</v>
+        <v>0.4118165766805206</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.2896267458522633</v>
+        <v>0.2866908482065674</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.377488457846987</v>
+        <v>0.3740957354290101</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3354955623367066</v>
+        <v>0.33807311999948</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.2875605519184178</v>
+        <v>0.2956265659523648</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2660459029862736</v>
+        <v>0.2632905748378498</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2812433224745551</v>
+        <v>0.2815656349927556</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>45</v>
       </c>
       <c r="C19">
-        <v>0.4202213481675295</v>
+        <v>0.4368047353234267</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3971974227949642</v>
+        <v>0.396904736777948</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3888208401337501</v>
+        <v>0.3920179347903796</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3227110001827531</v>
+        <v>0.3220923365675588</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3860354357600342</v>
+        <v>0.3846485913484996</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3191548387559736</v>
+        <v>0.3186984306764079</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.5743141739353725</v>
+        <v>0.5857831564645877</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3114631707037078</v>
+        <v>0.306924912249611</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4782,10 +4782,10 @@
         <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>0.2723048590122926</v>
+        <v>0.2687802255744351</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3014949849082639</v>
+        <v>0.2973430767280314</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>45</v>
       </c>
       <c r="C29">
-        <v>0.4651798586891095</v>
+        <v>0.4648008849306461</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.356695542765499</v>
+        <v>0.357204969062116</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4100131313464024</v>
+        <v>0.4117154087621919</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.3848892144690036</v>
+        <v>0.3857904546143509</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3592883849903489</v>
+        <v>0.3678105251400186</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.302160703933691</v>
+        <v>0.3091699304959967</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.432755986537848</v>
+        <v>0.4280752045529344</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>80</v>
       </c>
       <c r="C36">
-        <v>0.2557193200123898</v>
+        <v>0.248397557007654</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.2768630291831764</v>
+        <v>0.2868247712126806</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3294563660282523</v>
+        <v>0.33456155359148</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3331067277415553</v>
+        <v>0.3372073511408544</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4484244083930765</v>
+        <v>0.4494455651839437</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>20</v>
       </c>
       <c r="C41">
-        <v>0.2749006737382146</v>
+        <v>0.27969354789309</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5239597048583693</v>
+        <v>0.5250718319371045</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3782900003883791</v>
+        <v>0.3799198219069162</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.3788535576445727</v>
+        <v>0.3756747451551119</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3819795417038943</v>
+        <v>0.3840271067620474</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4204233259507213</v>
+        <v>0.4211556963159843</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2792832465157536</v>
+        <v>0.283447987864051</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.389518457022661</v>
+        <v>0.3851976622050953</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.321838447650258</v>
+        <v>0.3254333406148167</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3483327518968981</v>
+        <v>0.3487720543865165</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5190,10 +5190,10 @@
         <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C51">
-        <v>0.326696332635863</v>
+        <v>0.3280506797283821</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.5075778804396623</v>
+        <v>0.5084372435141645</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4088284132604432</v>
+        <v>0.4105320412923439</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3885704916729709</v>
+        <v>0.3776635194473141</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.269712092552892</v>
+        <v>0.2787148517751213</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3327649566829699</v>
+        <v>0.3362478358228546</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5430601702948123</v>
+        <v>0.5433779507405758</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.2995603745816332</v>
+        <v>0.30033283189373</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3667991629573439</v>
+        <v>0.3647772723092726</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.2845651245932449</v>
+        <v>0.2831074009107585</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3383097441934277</v>
+        <v>0.3368065293766908</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3143794180279573</v>
+        <v>0.3166152470789659</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3604317701040795</v>
+        <v>0.3580902463359339</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>45</v>
       </c>
       <c r="C64">
-        <v>0.2317780434557803</v>
+        <v>0.2245166136552385</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3145467382446507</v>
+        <v>0.3119823433013833</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3140075611946589</v>
+        <v>0.3155414206277927</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.335995165847114</v>
+        <v>0.3337399643999885</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2529904103978803</v>
+        <v>0.2529596440842589</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>80</v>
       </c>
       <c r="C69">
-        <v>0.5681350769138535</v>
+        <v>0.5664889531204741</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>80</v>
       </c>
       <c r="C70">
-        <v>0.5230315216805278</v>
+        <v>0.5268502924471444</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4366888513299752</v>
+        <v>0.4362797626795313</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.340025415873439</v>
+        <v>0.3414218313787895</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4938071866142983</v>
+        <v>0.4978382199716783</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4414208252369139</v>
+        <v>0.4476031330612863</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2445420285701944</v>
+        <v>0.2416529502251306</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3494713852516239</v>
+        <v>0.3585913257101458</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3226312855109078</v>
+        <v>0.3180372917572961</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4055139613377092</v>
+        <v>0.4145123140844902</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>6</v>
       </c>
       <c r="C79">
-        <v>0.2575392674698221</v>
+        <v>0.2542548238941606</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3468955473093625</v>
+        <v>0.3489374617501155</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2896323871986439</v>
+        <v>0.285739011902557</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4014068373854037</v>
+        <v>0.4021364387411479</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.391197642755533</v>
+        <v>0.3946498553831562</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5751,10 +5751,10 @@
         <v>176</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C84">
-        <v>0.2878808673494411</v>
+        <v>0.2911070707805467</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3231066606261061</v>
+        <v>0.3231846468947362</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.2841309202946985</v>
+        <v>0.2855697574256493</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2656654894988665</v>
+        <v>0.266898051142975</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>80</v>
       </c>
       <c r="C88">
-        <v>0.3322477383776872</v>
+        <v>0.3249859967764583</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.2930080755317967</v>
+        <v>0.2941247265956287</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2696209654485522</v>
+        <v>0.2726298306066811</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>6</v>
       </c>
       <c r="C91">
-        <v>0.2724540279196571</v>
+        <v>0.2710729350706333</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>45</v>
       </c>
       <c r="C92">
-        <v>0.3384823377590137</v>
+        <v>0.3137335093446783</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.375243219678766</v>
+        <v>0.3774582313033601</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>6</v>
       </c>
       <c r="C94">
-        <v>0.2605004077350938</v>
+        <v>0.2615840943483706</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3085380115312084</v>
+        <v>0.3111086631906604</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3538085345484305</v>
+        <v>0.3452306938457549</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>45</v>
       </c>
       <c r="C97">
-        <v>0.358307094175879</v>
+        <v>0.3526337295442307</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>45</v>
       </c>
       <c r="C98">
-        <v>0.3632411423462268</v>
+        <v>0.3616224791005015</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4094178154975308</v>
+        <v>0.4131779409124166</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>45</v>
       </c>
       <c r="C100">
-        <v>0.3924874870830619</v>
+        <v>0.3898807164242571</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>45</v>
       </c>
       <c r="C101">
-        <v>0.4530944165148593</v>
+        <v>0.4468083565307387</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4335988527571005</v>
+        <v>0.4287889024774094</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3431186438463646</v>
+        <v>0.3438954592691309</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3324262657918919</v>
+        <v>0.3352564968874661</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>45</v>
       </c>
       <c r="C105">
-        <v>0.3523585762491924</v>
+        <v>0.3663789219529934</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3728496237244538</v>
+        <v>0.3729088405903878</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>45</v>
       </c>
       <c r="C107">
-        <v>0.3512941948442386</v>
+        <v>0.3528267658574491</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4014123262372644</v>
+        <v>0.4006373148734787</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>20</v>
       </c>
       <c r="C109">
-        <v>0.2618702089372352</v>
+        <v>0.2661405541436977</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2773342358844454</v>
+        <v>0.2865739358698661</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4948072090346822</v>
+        <v>0.4786420083584983</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3646465599876872</v>
+        <v>0.3605094813587421</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4771602710975908</v>
+        <v>0.4916011738613081</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.5987124899824117</v>
+        <v>0.6072892346160425</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3068153155508778</v>
+        <v>0.3015864972684584</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4368404122929329</v>
+        <v>0.4331117028485081</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2685832698732843</v>
+        <v>0.271345088870486</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3771528924170043</v>
+        <v>0.3928449874997194</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3698595221932544</v>
+        <v>0.3705309861067657</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3458514917514542</v>
+        <v>0.3542835903882562</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.2946558140383462</v>
+        <v>0.292275555831002</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3196527477037641</v>
+        <v>0.3172092618583013</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2831442728979647</v>
+        <v>0.279836772460911</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3596055240996618</v>
+        <v>0.3583740257847175</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C125">
-        <v>0.2748374508949051</v>
+        <v>0.2758427591569181</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3717638796130566</v>
+        <v>0.3746323351072266</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4810307074093857</v>
+        <v>0.4739349460992593</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.3882641934082985</v>
+        <v>0.3688115184596596</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="C129">
-        <v>0.2873854746955893</v>
+        <v>0.2960566504884973</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.4249165816425359</v>
+        <v>0.4048481612357133</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2667082917349382</v>
+        <v>0.2692374941307293</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3617561412845595</v>
+        <v>0.3636908778773366</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3150682957562712</v>
+        <v>0.3159163000335873</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3239100101054236</v>
+        <v>0.3240641925436202</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.331368668426456</v>
+        <v>0.3331713829789615</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>45</v>
       </c>
       <c r="C136">
-        <v>0.3399293735978097</v>
+        <v>0.3316245908287139</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.37938566905307</v>
+        <v>0.3755358506196073</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3100402915988685</v>
+        <v>0.3111588431595431</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4240733014658604</v>
+        <v>0.4227334566780049</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>45</v>
       </c>
       <c r="C140">
-        <v>0.4075723110787083</v>
+        <v>0.4044737009914344</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3413761355735224</v>
+        <v>0.3393266458559356</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3741068861943159</v>
+        <v>0.3685179173589958</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.2889248274958582</v>
+        <v>0.2918280548797931</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5186635228892565</v>
+        <v>0.5273450574132679</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2709557160432653</v>
+        <v>0.2721995698689382</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4177353957915003</v>
+        <v>0.4113452825246861</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4237028565344638</v>
+        <v>0.4241776172112502</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3245141256233538</v>
+        <v>0.3225298987295805</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3510296992650069</v>
+        <v>0.3553524299869851</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3073164682201561</v>
+        <v>0.3063939351318757</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2351022332184243</v>
+        <v>0.2427757885437097</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6230243282100028</v>
+        <v>0.6177216660645984</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3242000934408787</v>
+        <v>0.3189446434510047</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>10</v>
       </c>
       <c r="C154">
-        <v>0.3133321159909714</v>
+        <v>0.321223956360034</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="C155">
-        <v>0.263040830071073</v>
+        <v>0.2610802127860333</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3308733850661563</v>
+        <v>0.3337332961301803</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3557865154370302</v>
+        <v>0.3524182010413938</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>45</v>
       </c>
       <c r="C158">
-        <v>0.3781116583976198</v>
+        <v>0.3811697946091416</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>45</v>
       </c>
       <c r="C159">
-        <v>0.3890632046707608</v>
+        <v>0.3868815088971703</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3874586538536944</v>
+        <v>0.3855129779545766</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3608362966177567</v>
+        <v>0.3633970518590632</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5436893692227475</v>
+        <v>0.5516020643119978</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>45</v>
       </c>
       <c r="C163">
-        <v>0.4501588788523025</v>
+        <v>0.4520364912778011</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.2849902542909545</v>
+        <v>0.2957157313577768</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3354136654900866</v>
+        <v>0.3381607684906451</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>45</v>
       </c>
       <c r="C166">
-        <v>0.3463274192293989</v>
+        <v>0.334986085477665</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3464174819242861</v>
+        <v>0.3463686200010235</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5616352356863005</v>
+        <v>0.5636992295108407</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>45</v>
       </c>
       <c r="C169">
-        <v>0.3663340657502953</v>
+        <v>0.3452725842164662</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3501864806486128</v>
+        <v>0.3353252212608033</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>45</v>
       </c>
       <c r="C171">
-        <v>0.2555349685967502</v>
+        <v>0.2610419418775379</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4236981170823603</v>
+        <v>0.4146880456346468</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.326624021552459</v>
+        <v>0.3281972394036274</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3115887840849396</v>
+        <v>0.3146334687471917</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2979201659838987</v>
+        <v>0.2909061668969898</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3921658809274778</v>
+        <v>0.385827795596797</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5360103851174605</v>
+        <v>0.5233416736052642</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3815424456865568</v>
+        <v>0.3823957247986784</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3010052822122408</v>
+        <v>0.3060120047891445</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>45</v>
       </c>
       <c r="C180">
-        <v>0.3752028634175426</v>
+        <v>0.3752666688007331</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3361446697774799</v>
+        <v>0.3302469047977956</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2952601946455822</v>
+        <v>0.2967174246354413</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.3097136537911451</v>
+        <v>0.3107710956362992</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3300233392030066</v>
+        <v>0.3276613567672378</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>15</v>
       </c>
       <c r="C185">
-        <v>0.3278388094753844</v>
+        <v>0.3246294319614887</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>45</v>
       </c>
       <c r="C186">
-        <v>0.4320761652301892</v>
+        <v>0.4396145741454752</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.231007283111277</v>
+        <v>0.2296039201069449</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.442084104692801</v>
+        <v>0.4452537888677324</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3179871212097052</v>
+        <v>0.3220307115223564</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2616029424297667</v>
+        <v>0.2622628610489271</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3350290495269639</v>
+        <v>0.3333252385826292</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.3979537503172871</v>
+        <v>0.3953171212648308</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4215307216301454</v>
+        <v>0.4142990556844292</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3603240033893292</v>
+        <v>0.3569450039810287</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>20</v>
       </c>
       <c r="C195">
-        <v>0.3688223113206409</v>
+        <v>0.3677333428185096</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>80</v>
       </c>
       <c r="C196">
-        <v>0.3203120942695679</v>
+        <v>0.3158192546457703</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.2994483539546928</v>
+        <v>0.3003930436653268</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.4874742021368957</v>
+        <v>0.5032201000276119</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.5400634293918212</v>
+        <v>0.5557183513315729</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3208654469122219</v>
+        <v>0.3138752153470565</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3022549731793827</v>
+        <v>0.3011058155208427</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3436256196281622</v>
+        <v>0.3507927789568595</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.486100618262633</v>
+        <v>0.4882460455334763</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4765709183980956</v>
+        <v>0.4710726074455408</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4099608331539586</v>
+        <v>0.4074143844744552</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3431691051287138</v>
+        <v>0.3359423640635127</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>45</v>
       </c>
       <c r="C207">
-        <v>0.5257864629336464</v>
+        <v>0.5124411532458947</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>45</v>
       </c>
       <c r="C208">
-        <v>0.4171586625539604</v>
+        <v>0.4206667233040177</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.4785430830961167</v>
+        <v>0.4805478641198995</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4237199909478739</v>
+        <v>0.4164910399310606</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.3972698264409871</v>
+        <v>0.3904900932185079</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>10</v>
       </c>
       <c r="C212">
-        <v>0.2740289804326873</v>
+        <v>0.2775985254159323</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3396337834580604</v>
+        <v>0.3374114915382355</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3507449423606132</v>
+        <v>0.3534065708921878</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5701128583943172</v>
+        <v>0.5829765613662623</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3109298788208324</v>
+        <v>0.3160778824113379</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3075601597399387</v>
+        <v>0.3041674405349387</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3676111452401755</v>
+        <v>0.3627764803280363</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>45</v>
       </c>
       <c r="C219">
-        <v>0.4798826307046511</v>
+        <v>0.4840476611212454</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="C220">
-        <v>0.2867515966916249</v>
+        <v>0.2800038508064276</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3410826064410246</v>
+        <v>0.3429394203915165</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.2991430352570507</v>
+        <v>0.2969033206547682</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5155791578417225</v>
+        <v>0.5211882451545831</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3498881342464662</v>
+        <v>0.3391564456217657</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.338816765902476</v>
+        <v>0.3347958353221741</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4565001253588584</v>
+        <v>0.4569601697709951</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3279544733910626</v>
+        <v>0.3329415063551348</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4521574469348577</v>
+        <v>0.454710585444606</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.471581950707535</v>
+        <v>0.4785770189281114</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>45</v>
       </c>
       <c r="C230">
-        <v>0.380470539605373</v>
+        <v>0.3992034358241452</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3132254384288745</v>
+        <v>0.3220934218649285</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5776804013256243</v>
+        <v>0.5731847073553561</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>45</v>
       </c>
       <c r="C233">
-        <v>0.4614600841334983</v>
+        <v>0.46070615730883</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.3945482863766444</v>
+        <v>0.3992088512804117</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4819213206206003</v>
+        <v>0.4744003064770025</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2545992379391297</v>
+        <v>0.2539989439437317</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3260232153200676</v>
+        <v>0.3298333245475181</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3130644441459473</v>
+        <v>0.313136943671959</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.3955478573732865</v>
+        <v>0.3950856623596029</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>20</v>
       </c>
       <c r="C240">
-        <v>0.3500979120477359</v>
+        <v>0.3387607104648244</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>6</v>
       </c>
       <c r="C241">
-        <v>0.2355784603363169</v>
+        <v>0.2317456401915947</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3087671403174517</v>
+        <v>0.3037707415967317</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4169426309053272</v>
+        <v>0.4199849511162295</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>20</v>
       </c>
       <c r="C244">
-        <v>0.35018566440908</v>
+        <v>0.3595552647259219</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.5910653690153199</v>
+        <v>0.6051890758740173</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4384855067957416</v>
+        <v>0.4415377699548766</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4302230095290447</v>
+        <v>0.4284964013699248</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3382662521730595</v>
+        <v>0.334069363782976</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4368373220145094</v>
+        <v>0.4323562402776086</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3459375683137258</v>
+        <v>0.3412990949705821</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>45</v>
       </c>
       <c r="C251">
-        <v>0.4726481668997234</v>
+        <v>0.4575800210305982</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.437721630572028</v>
+        <v>0.4405201560590839</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3527337862798675</v>
+        <v>0.3510436048324433</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4585393230707982</v>
+        <v>0.4567762488332016</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.3993139622512582</v>
+        <v>0.4027300830793713</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5359580768488581</v>
+        <v>0.5408642224119784</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3733077330397593</v>
+        <v>0.3691613163335336</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4841923190710162</v>
+        <v>0.4508551697112859</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3089421826869821</v>
+        <v>0.3107624456015211</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.3916683369733749</v>
+        <v>0.3959873174187641</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4149038117888028</v>
+        <v>0.4176503118410154</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3753556126825288</v>
+        <v>0.3677797873936203</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4636229925812994</v>
+        <v>0.4638396331595597</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.3921855313471398</v>
+        <v>0.3925096063611809</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.29715281260065</v>
+        <v>0.3005700121310368</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>20</v>
       </c>
       <c r="C266">
-        <v>0.3278720975990084</v>
+        <v>0.3134127432889699</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2820952046300608</v>
+        <v>0.2799338332805154</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.431326290603933</v>
+        <v>0.4340644049733743</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>45</v>
       </c>
       <c r="C269">
-        <v>0.3659251290449079</v>
+        <v>0.3726080628573989</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.4924824397013896</v>
+        <v>0.4984236563451751</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.4919810945287419</v>
+        <v>0.4956716748544643</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3199072075731652</v>
+        <v>0.3265757290334707</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.4990321493362934</v>
+        <v>0.4939168908470985</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3336204859195055</v>
+        <v>0.3370438725192193</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2444746411034004</v>
+        <v>0.242848586448791</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3240914381090479</v>
+        <v>0.3287771108937658</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>80</v>
       </c>
       <c r="C277">
-        <v>0.3988610541023275</v>
+        <v>0.3986484165491903</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4423500932063502</v>
+        <v>0.4442108405517486</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5329314260189301</v>
+        <v>0.5222189641152256</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4515145485671911</v>
+        <v>0.4556678899667322</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.364529687605446</v>
+        <v>0.355217477962789</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.351275819481941</v>
+        <v>0.3563740472403016</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3838496866425183</v>
+        <v>0.3811991410588477</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3115129416854884</v>
+        <v>0.3184993508819693</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2692380759929583</v>
+        <v>0.2652211606589704</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.310563062799866</v>
+        <v>0.3119246358672181</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>45</v>
       </c>
       <c r="C287">
-        <v>0.4884095551780621</v>
+        <v>0.4804577118728801</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C288">
-        <v>0.2399096094749317</v>
+        <v>0.2373935039379387</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3615715243612877</v>
+        <v>0.3632875699328729</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.351809048982891</v>
+        <v>0.3542864061773519</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4338594263291719</v>
+        <v>0.4226088052917317</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>80</v>
       </c>
       <c r="C292">
-        <v>0.4696692108610314</v>
+        <v>0.4640854373558982</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5744371495905708</v>
+        <v>0.5675649386173612</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3766765159898068</v>
+        <v>0.3727348390891146</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3539739059448383</v>
+        <v>0.3486649656121441</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C296">
-        <v>0.2675896757638208</v>
+        <v>0.2688590157602789</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4775596559480303</v>
+        <v>0.4722928449377478</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3674983412053532</v>
+        <v>0.3771692232579172</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>45</v>
       </c>
       <c r="C299">
-        <v>0.3020090223226491</v>
+        <v>0.2894454737161057</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3303052125424228</v>
+        <v>0.3352277829528975</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3564498051697897</v>
+        <v>0.3545397630454251</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>45</v>
       </c>
       <c r="C302">
-        <v>0.4986288064249219</v>
+        <v>0.5066608218355024</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3229253090326237</v>
+        <v>0.326654952648398</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2709389151991752</v>
+        <v>0.2695210676715539</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>45</v>
       </c>
       <c r="C305">
-        <v>0.450729377726961</v>
+        <v>0.4459836434887848</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.3746533167598236</v>
+        <v>0.3706423484553656</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4434172880034892</v>
+        <v>0.4511128956350159</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3581203591657898</v>
+        <v>0.3542294494552481</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>10</v>
       </c>
       <c r="C309">
-        <v>0.2558718910863761</v>
+        <v>0.2607006726274055</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3752411087102203</v>
+        <v>0.3772726025638357</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3269638798501616</v>
+        <v>0.3328383562750326</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>10</v>
       </c>
       <c r="C312">
-        <v>0.2881087426473353</v>
+        <v>0.2839138586220505</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9644,10 +9644,10 @@
         <v>634</v>
       </c>
       <c r="B313" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C313">
-        <v>0.2679211443864666</v>
+        <v>0.2876277501215084</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3095210068996197</v>
+        <v>0.3048262668382279</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>45</v>
       </c>
       <c r="C315">
-        <v>0.4834717639422403</v>
+        <v>0.4854472674533629</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3790368120707346</v>
+        <v>0.3778233278909814</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.4727172405783263</v>
+        <v>0.4771626656903982</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5220223769537663</v>
+        <v>0.519186076437425</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3090175909746784</v>
+        <v>0.310131942789811</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>45</v>
       </c>
       <c r="C320">
-        <v>0.2587175828117153</v>
+        <v>0.2640039290780005</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.314416842904029</v>
+        <v>0.3160150965791196</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.415100718520075</v>
+        <v>0.4163937400582384</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3723753377303713</v>
+        <v>0.3794874612390233</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>45</v>
       </c>
       <c r="C324">
-        <v>0.4114272619533969</v>
+        <v>0.4200607447816606</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>10</v>
       </c>
       <c r="C325">
-        <v>0.2565182251464185</v>
+        <v>0.2555714119321391</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>45</v>
       </c>
       <c r="C326">
-        <v>0.3624184060642561</v>
+        <v>0.3688386645089898</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>45</v>
       </c>
       <c r="C327">
-        <v>0.349721246851055</v>
+        <v>0.3601290312485365</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2654456922944198</v>
+        <v>0.2668302370347232</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>15</v>
       </c>
       <c r="C329">
-        <v>0.2960485435774149</v>
+        <v>0.293510677131512</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>6</v>
       </c>
       <c r="C330">
-        <v>0.2995196980837722</v>
+        <v>0.3017220957770312</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3434198622238294</v>
+        <v>0.3493531240495946</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3592174018268457</v>
+        <v>0.3512256151244637</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4384543168411817</v>
+        <v>0.4375394647594506</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>80</v>
       </c>
       <c r="C334">
-        <v>0.2865086842392086</v>
+        <v>0.2914621540629993</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>45</v>
       </c>
       <c r="C335">
-        <v>0.309863688019859</v>
+        <v>0.3316577693526703</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C336">
-        <v>0.2792390948016764</v>
+        <v>0.2733770562721901</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>45</v>
       </c>
       <c r="C337">
-        <v>0.4898436393891951</v>
+        <v>0.4949392360812387</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.2809994186155283</v>
+        <v>0.2772698589991967</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4475836547174362</v>
+        <v>0.444113147349091</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3020833329962566</v>
+        <v>0.2940259544421459</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2523775570707018</v>
+        <v>0.2533194421469254</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2602494742184292</v>
+        <v>0.2673253646195596</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3769768372132268</v>
+        <v>0.3752601836895709</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2865002122099738</v>
+        <v>0.2883440109293667</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3541646842914932</v>
+        <v>0.3503368161918288</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3496939172797643</v>
+        <v>0.3594581375815226</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3184946854592572</v>
+        <v>0.3233114713158131</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.2960681263398671</v>
+        <v>0.2890978900775688</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4856454162022395</v>
+        <v>0.4730147866183658</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3470613729871183</v>
+        <v>0.3473803148925736</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>80</v>
       </c>
       <c r="C351">
-        <v>0.2910754050075383</v>
+        <v>0.2882281248141371</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3885548376602089</v>
+        <v>0.3837232641275561</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3659139353875432</v>
+        <v>0.3665473402099665</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2647419760749157</v>
+        <v>0.2682162658675827</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3195065331597545</v>
+        <v>0.3232259989513972</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>10</v>
       </c>
       <c r="C356">
-        <v>0.303316890461082</v>
+        <v>0.2982058207074127</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4135479302749116</v>
+        <v>0.4131283162287204</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3299288974408745</v>
+        <v>0.3277095170544023</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>45</v>
       </c>
       <c r="C359">
-        <v>0.4629420136262139</v>
+        <v>0.4743359912660757</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4416527569335458</v>
+        <v>0.4531798907452236</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.2971738671476444</v>
+        <v>0.2949997850720203</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3277016792076467</v>
+        <v>0.3293717115019485</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10494,10 +10494,10 @@
         <v>734</v>
       </c>
       <c r="B363" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C363">
-        <v>0.2827200326117318</v>
+        <v>0.2692207180508231</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.2824575918422693</v>
+        <v>0.2880721941643493</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.2967050911398446</v>
+        <v>0.298408705347951</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2525502273137183</v>
+        <v>0.2497957348604209</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.2723037803156916</v>
+        <v>0.2744112015704843</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3142037327672038</v>
+        <v>0.3146379352323028</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.429414793399188</v>
+        <v>0.4311833279013857</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3371145782456617</v>
+        <v>0.3339321997632673</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4629743857896418</v>
+        <v>0.457000547776179</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3144478707048167</v>
+        <v>0.3139244690612099</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.40114860510031</v>
+        <v>0.4016998679538646</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4379748016287689</v>
+        <v>0.4508932740026436</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4184248078585152</v>
+        <v>0.4205472376102995</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.373869867445445</v>
+        <v>0.3744315707517908</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4670040039292218</v>
+        <v>0.4575110359523363</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.28310490529727</v>
+        <v>0.2854427505294029</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3081660454430948</v>
+        <v>0.3109881567761955</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3442018604964464</v>
+        <v>0.3498400064800496</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4266445562278698</v>
+        <v>0.4325416029236621</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3411695782886216</v>
+        <v>0.342979563882755</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3474225780730816</v>
+        <v>0.340819917336656</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>45</v>
       </c>
       <c r="C384">
-        <v>0.4745462581422086</v>
+        <v>0.4623059257031458</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3766536223414527</v>
+        <v>0.3794127790788834</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.2923503590834966</v>
+        <v>0.2861634175048328</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4372699146866955</v>
+        <v>0.4348209184989677</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>45</v>
       </c>
       <c r="C388">
-        <v>0.3505015468906392</v>
+        <v>0.3581176470082595</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3677501905407636</v>
+        <v>0.3699890517086399</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3302637110418306</v>
+        <v>0.3285157443166593</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3319418742973394</v>
+        <v>0.3291343280109355</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3293873442559936</v>
+        <v>0.3338912746419109</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4103863393148087</v>
+        <v>0.411106741502532</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3449410757278949</v>
+        <v>0.3487632027536919</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3793649570919138</v>
+        <v>0.3879275141055887</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.4005985402935572</v>
+        <v>0.4011359812125906</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3528821061359603</v>
+        <v>0.3476166044921737</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4733335726810887</v>
+        <v>0.4613370369560668</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3164281944466554</v>
+        <v>0.3182278888153661</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3230835526823926</v>
+        <v>0.3210529260378626</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4171649416923944</v>
+        <v>0.4156225416643691</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.377282825248878</v>
+        <v>0.3731333959319046</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2941656995871747</v>
+        <v>0.2941077965417614</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>45</v>
       </c>
       <c r="C404">
-        <v>0.3184663552365998</v>
+        <v>0.3081539976859192</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.3972744641373062</v>
+        <v>0.3996983382055906</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>80</v>
       </c>
       <c r="C406">
-        <v>0.4786835792895225</v>
+        <v>0.4859412585291888</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3548728081165048</v>
+        <v>0.3584082504198747</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4325350414011197</v>
+        <v>0.4401228139827381</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4762639970655455</v>
+        <v>0.4804340754604554</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3059435171753339</v>
+        <v>0.3049262793484668</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3055349675280697</v>
+        <v>0.3095732616923019</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4439001792022268</v>
+        <v>0.4443657507582527</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2616238480458306</v>
+        <v>0.2576482081479453</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>10</v>
       </c>
       <c r="C414">
-        <v>0.3322028337083728</v>
+        <v>0.3234955829063349</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C415">
-        <v>0.3180036414694134</v>
+        <v>0.3193477744298099</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3429023522555896</v>
+        <v>0.3355325127139998</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.3010091416705902</v>
+        <v>0.3027813455024205</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>45</v>
       </c>
       <c r="C418">
-        <v>0.3183270158257336</v>
+        <v>0.3094023530280534</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3781941881842809</v>
+        <v>0.3694267767677678</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>45</v>
       </c>
       <c r="C420">
-        <v>0.4620336078718866</v>
+        <v>0.4688166000705382</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>45</v>
       </c>
       <c r="C421">
-        <v>0.4055160433640661</v>
+        <v>0.4117752185081852</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3636388955830344</v>
+        <v>0.366038851921885</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>45</v>
       </c>
       <c r="C423">
-        <v>0.4545191892506971</v>
+        <v>0.463977077392135</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3120172005161264</v>
+        <v>0.303403817122771</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3230724255538148</v>
+        <v>0.3249436074402846</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3498573600558611</v>
+        <v>0.3496751802417434</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2460393379224394</v>
+        <v>0.2455558197983442</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2700969062804695</v>
+        <v>0.2684000043121693</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3474108201773781</v>
+        <v>0.3537708066663069</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3132532266495295</v>
+        <v>0.316864507443803</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.2748729040028564</v>
+        <v>0.2767977092770992</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3060274865104196</v>
+        <v>0.3114669533368716</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3186732405924446</v>
+        <v>0.3132443831320026</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3373466868904968</v>
+        <v>0.3395972375597331</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3852617998327044</v>
+        <v>0.3836244789145654</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3220833788651397</v>
+        <v>0.3249588538413754</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3106362505225571</v>
+        <v>0.3148141271372883</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.351169294440441</v>
+        <v>0.3482049558521511</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3131753255671202</v>
+        <v>0.308606027367922</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.317134981094663</v>
+        <v>0.3326482589953794</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.2972414995446891</v>
+        <v>0.2956892125158121</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3453137129592652</v>
+        <v>0.3414386405964547</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.2867036838190634</v>
+        <v>0.2915133326156629</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3137782831279604</v>
+        <v>0.3219259453633753</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.345834848277266</v>
+        <v>0.3457842390289156</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>45</v>
       </c>
       <c r="C446">
-        <v>0.3785289480037506</v>
+        <v>0.3658239778448735</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2881666702173092</v>
+        <v>0.2870762860558245</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.376723459288349</v>
+        <v>0.3805403522123703</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3601744681825012</v>
+        <v>0.3613014331518368</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>45</v>
       </c>
       <c r="C450">
-        <v>0.3664088430415279</v>
+        <v>0.3761121892726185</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>45</v>
       </c>
       <c r="C451">
-        <v>0.4407641946958372</v>
+        <v>0.4356342754321482</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2866858111613779</v>
+        <v>0.2863924951842754</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3651022977518647</v>
+        <v>0.3545003771340144</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2669624114769655</v>
+        <v>0.2654534476965363</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3087096552940747</v>
+        <v>0.3059385034928689</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3155622961375231</v>
+        <v>0.3257217433655537</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3475035424027257</v>
+        <v>0.3395838144923476</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3406566143441734</v>
+        <v>0.3419400172423726</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3353703585495569</v>
+        <v>0.3325064306929535</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>15</v>
       </c>
       <c r="C460">
-        <v>0.3425766693463171</v>
+        <v>0.3389510423598189</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3116468945325233</v>
+        <v>0.3104779930363459</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.2994078204392774</v>
+        <v>0.300345614963857</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3101755928075769</v>
+        <v>0.3132067386031935</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3840395642888844</v>
+        <v>0.3813996972495141</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>45</v>
       </c>
       <c r="C465">
-        <v>0.4026821035950487</v>
+        <v>0.4116032161601315</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5161018045694561</v>
+        <v>0.5141352885291609</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4222744692507661</v>
+        <v>0.4254270178505236</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3842154652771341</v>
+        <v>0.3879884817252552</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2790199845567272</v>
+        <v>0.2858926998373261</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>6</v>
       </c>
       <c r="C470">
-        <v>0.3209814357831016</v>
+        <v>0.3228493182258328</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3073434647802239</v>
+        <v>0.3121708259884814</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3325692050017597</v>
+        <v>0.3363111132947602</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3352903727882012</v>
+        <v>0.3236829314396276</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3586947193186428</v>
+        <v>0.357124202015469</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3653365143937059</v>
+        <v>0.3661208237765902</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3120970750947351</v>
+        <v>0.3106348040797658</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>15</v>
       </c>
       <c r="C477">
-        <v>0.3336580408276894</v>
+        <v>0.3322557425407986</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4076271510058423</v>
+        <v>0.4069233744245945</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>45</v>
       </c>
       <c r="C479">
-        <v>0.410756360741184</v>
+        <v>0.4087343913159378</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.422176247125554</v>
+        <v>0.4239593908579146</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>45</v>
       </c>
       <c r="C481">
-        <v>0.3932830990450652</v>
+        <v>0.3976130475311022</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3087935148353653</v>
+        <v>0.3144277293149703</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3201030425586805</v>
+        <v>0.3087636382678662</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>45</v>
       </c>
       <c r="C484">
-        <v>0.3849910990851387</v>
+        <v>0.3867133918182866</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3565968438526058</v>
+        <v>0.3361460032930892</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3803440033606869</v>
+        <v>0.3800434720651185</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>45</v>
       </c>
       <c r="C487">
-        <v>0.4596973381527554</v>
+        <v>0.4666963679205031</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3479902991743904</v>
+        <v>0.3440194683773689</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4528445507502809</v>
+        <v>0.448707656909423</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3057248460364979</v>
+        <v>0.307320212582097</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.2700364001431496</v>
+        <v>0.2682393889321275</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4643982343281005</v>
+        <v>0.4656222467138824</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3196722459638836</v>
+        <v>0.3126613475336949</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>45</v>
       </c>
       <c r="C494">
-        <v>0.3255500522930692</v>
+        <v>0.3222878577681964</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>45</v>
       </c>
       <c r="C495">
-        <v>0.5263708231095314</v>
+        <v>0.5103703485795215</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4546448090615399</v>
+        <v>0.4566742329129653</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3439887447962816</v>
+        <v>0.348478062330174</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6529372709790503</v>
+        <v>0.6634938074911064</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3721421040923648</v>
+        <v>0.3699123497946487</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3785948026573989</v>
+        <v>0.3779933756920962</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3365322211992172</v>
+        <v>0.3375835989361704</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5649367716553365</v>
+        <v>0.5647288494257764</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3379278517207226</v>
+        <v>0.3389985622684376</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>6</v>
       </c>
       <c r="C504">
-        <v>0.3093470222975075</v>
+        <v>0.3071333654379391</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4351850562919998</v>
+        <v>0.4348699633109686</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4320379480198651</v>
+        <v>0.4315807374220208</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.2965976575778214</v>
+        <v>0.3051695206860697</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3135532883475335</v>
+        <v>0.3227982277770536</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4535606866084286</v>
+        <v>0.4497241463186884</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3576391947205351</v>
+        <v>0.3623329891027147</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>45</v>
       </c>
       <c r="C511">
-        <v>0.3868570171274341</v>
+        <v>0.3946681385755655</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2988427347380892</v>
+        <v>0.3003913493664003</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3729420822509257</v>
+        <v>0.3757929829421549</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>45</v>
       </c>
       <c r="C514">
-        <v>0.4190796921455509</v>
+        <v>0.4373115180680894</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4989634992548926</v>
+        <v>0.4886350202033946</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>6</v>
       </c>
       <c r="C516">
-        <v>0.3064041944755737</v>
+        <v>0.3056982759068027</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3152642974889923</v>
+        <v>0.3116078091599512</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3098214425539756</v>
+        <v>0.2941454757882516</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>45</v>
       </c>
       <c r="C519">
-        <v>0.4777256569481673</v>
+        <v>0.498270569268045</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3155312759530808</v>
+        <v>0.3124745575050306</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3059610024273849</v>
+        <v>0.301417612709649</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3446577071981979</v>
+        <v>0.3478848743648147</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4270836437030606</v>
+        <v>0.4307467071309138</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2827607193916583</v>
+        <v>0.2863429778799398</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>45</v>
       </c>
       <c r="C525">
-        <v>0.421700703873447</v>
+        <v>0.4097413954941316</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>45</v>
       </c>
       <c r="C526">
-        <v>0.4462036721239022</v>
+        <v>0.4508613177695499</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3459097410701322</v>
+        <v>0.3552238796663157</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4453467291936897</v>
+        <v>0.4446194726687943</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3289504736585668</v>
+        <v>0.3353912256631994</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>45</v>
       </c>
       <c r="C530">
-        <v>0.4942098281033007</v>
+        <v>0.4980139469894899</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>45</v>
       </c>
       <c r="C531">
-        <v>0.584471035209375</v>
+        <v>0.5731371479519929</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>45</v>
       </c>
       <c r="C532">
-        <v>0.3106880948031883</v>
+        <v>0.2974068552537372</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.408829373950657</v>
+        <v>0.4054317276840516</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>6</v>
       </c>
       <c r="C534">
-        <v>0.3034647749776237</v>
+        <v>0.3059107523746352</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3049756203074195</v>
+        <v>0.3070947420535514</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3011798312148798</v>
+        <v>0.3009313791253835</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.391460884122098</v>
+        <v>0.3951853156407599</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2805109289657787</v>
+        <v>0.2841611680661826</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3088453722825179</v>
+        <v>0.3123750966785598</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.26858108181721</v>
+        <v>0.2699914685758585</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4210628199284728</v>
+        <v>0.4279963729279818</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>45</v>
       </c>
       <c r="C542">
-        <v>0.4085957965086758</v>
+        <v>0.4124676454941053</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3977722119155333</v>
+        <v>0.3852204945794201</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3613517905243049</v>
+        <v>0.3595741347269353</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2687491782204811</v>
+        <v>0.2620874355404834</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3174200962617724</v>
+        <v>0.3374719779447966</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2609468159772826</v>
+        <v>0.2633908789781597</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.4689585749377365</v>
+        <v>0.4763852464108229</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4064407691361006</v>
+        <v>0.3993771569905746</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3262609241334073</v>
+        <v>0.3293661791462943</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2723285899309967</v>
+        <v>0.2740642347368503</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>10</v>
       </c>
       <c r="C570">
-        <v>0.297638705894047</v>
+        <v>0.2918862040351888</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2783329881035538</v>
+        <v>0.2791307549672933</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.3336282744655584</v>
+        <v>0.3276306167407494</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.2739596044066941</v>
+        <v>0.2734433106409772</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>45</v>
       </c>
       <c r="C574">
-        <v>0.3031163294349688</v>
+        <v>0.3144858145232893</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3116261532872319</v>
+        <v>0.316446731985193</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3696645876640704</v>
+        <v>0.3779853893220506</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.291972577903216</v>
+        <v>0.2873615817589585</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3537495593721368</v>
+        <v>0.3661427605043753</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.2937586287526299</v>
+        <v>0.3026029316309243</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3511510509625057</v>
+        <v>0.3527830670218301</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4144750607440022</v>
+        <v>0.4483751640247601</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.2890492946307441</v>
+        <v>0.2977054365978619</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14180,10 +14180,10 @@
         <v>1184</v>
       </c>
       <c r="B583" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3779613341863146</v>
+        <v>0.3385987720676739</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>6</v>
       </c>
       <c r="C584">
-        <v>0.2910273262447091</v>
+        <v>0.3095734456437048</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.3588303807374129</v>
+        <v>0.382286176167086</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2803573330566558</v>
+        <v>0.2877378989150525</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3108448138838268</v>
+        <v>0.2927306938321464</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.2656055159295865</v>
+        <v>0.2762020549455292</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>45</v>
       </c>
       <c r="C589">
-        <v>0.3351631571203056</v>
+        <v>0.3297268961496782</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4162409695654517</v>
+        <v>0.4304208327062033</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.4495712298772098</v>
+        <v>0.4459454025124768</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3613645465870011</v>
+        <v>0.3529844979502992</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.5281591379743067</v>
+        <v>0.509544815769169</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4025995554958594</v>
+        <v>0.3993588829939644</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3382808696188604</v>
+        <v>0.3516706212735022</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4196925604624839</v>
+        <v>0.3911934330228708</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3509917650253619</v>
+        <v>0.3605433099045404</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2583308293230095</v>
+        <v>0.2609674210650417</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.3024776969982798</v>
+        <v>0.320459367920903</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2788689286067543</v>
+        <v>0.2818074552975855</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.280471957453105</v>
+        <v>0.2780841627919294</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3670262886535851</v>
+        <v>0.3740736997754755</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2920402053359418</v>
+        <v>0.2987208912610551</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3036730259752044</v>
+        <v>0.3472135920546724</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>45</v>
       </c>
       <c r="C605">
-        <v>0.2807425528234912</v>
+        <v>0.2799055671201063</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3718096722167662</v>
+        <v>0.3837870891755099</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14588,10 +14588,10 @@
         <v>1232</v>
       </c>
       <c r="B607" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.2847287438273493</v>
+        <v>0.2908990956206018</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14605,10 +14605,10 @@
         <v>1234</v>
       </c>
       <c r="B608" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C608">
-        <v>0.2986111272197359</v>
+        <v>0.2998826696600439</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.3150170046836258</v>
+        <v>0.2810675698488048</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2440280549437927</v>
+        <v>0.238967290585352</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>45</v>
       </c>
       <c r="C611">
-        <v>0.465181748047462</v>
+        <v>0.4635796867450719</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>45</v>
       </c>
       <c r="C612">
-        <v>0.3843419185298139</v>
+        <v>0.3760980985884191</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3262375992790741</v>
+        <v>0.3393845087228324</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.3706956699174769</v>
+        <v>0.3785676708399713</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3138007677597047</v>
+        <v>0.314302555760871</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3694378370629566</v>
+        <v>0.3800180563950039</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3258111964955274</v>
+        <v>0.3120663679917381</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.2895310426859918</v>
+        <v>0.2852479809450488</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4167038922543281</v>
+        <v>0.397268705897574</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14812,7 +14812,7 @@
         <v>15</v>
       </c>
       <c r="C620">
-        <v>0.2889662860768512</v>
+        <v>0.286077132805149</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3266220389769623</v>
+        <v>0.3354485076469418</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>15</v>
       </c>
       <c r="C622">
-        <v>0.2273802750458805</v>
+        <v>0.2272256174360431</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2394313482187342</v>
+        <v>0.228096792612476</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.272456806265866</v>
+        <v>0.2800959684707632</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14894,10 +14894,10 @@
         <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>10</v>
+        <v>1266</v>
       </c>
       <c r="C625">
-        <v>0.2523072595955246</v>
+        <v>0.257152478242327</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3026200783138855</v>
+        <v>0.3029059441613101</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.3219157821145738</v>
+        <v>0.3213496953851631</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2831941595741423</v>
+        <v>0.2738081875390032</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>1266</v>
       </c>
       <c r="C629">
-        <v>0.2189670077823594</v>
+        <v>0.225043147235599</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3899090965408467</v>
+        <v>0.3584233611975108</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3998742661564533</v>
+        <v>0.4038523107483728</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.4520557764339608</v>
+        <v>0.456433072002846</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2660185554471572</v>
+        <v>0.2697796536135059</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.332863950609976</v>
+        <v>0.3396989488839469</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4653730445461359</v>
+        <v>0.457670954351715</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3621924257108051</v>
+        <v>0.3543499519479846</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>1266</v>
       </c>
       <c r="C637">
-        <v>0.3194798369458868</v>
+        <v>0.3233945927853522</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4874907647329959</v>
+        <v>0.4910339184352084</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3115543259320968</v>
+        <v>0.3211994718242165</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2633706030578041</v>
+        <v>0.2688851536684454</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>1266</v>
       </c>
       <c r="C641">
-        <v>0.2839373345498962</v>
+        <v>0.2783340923618423</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.3313296667827375</v>
+        <v>0.3315345025644301</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3025607103381028</v>
+        <v>0.3054083075764442</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2917902069776948</v>
+        <v>0.2927384534707999</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>1266</v>
       </c>
       <c r="C645">
-        <v>0.2459961474814001</v>
+        <v>0.2533652032340521</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3304333469519075</v>
+        <v>0.3415006417050697</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>1266</v>
       </c>
       <c r="C647">
-        <v>0.3257265599129234</v>
+        <v>0.3096016695968161</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.270084975954196</v>
+        <v>0.2542895437904842</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.2932684585158645</v>
+        <v>0.3032723156267034</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>1266</v>
       </c>
       <c r="C650">
-        <v>0.2782071676581046</v>
+        <v>0.2721296242891634</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.3012697990966122</v>
+        <v>0.3001977580702927</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15419,7 +15419,7 @@
         <v>1266</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -77,627 +77,627 @@
     <t>ashfield</t>
   </si>
   <si>
+    <t>E14001068</t>
+  </si>
+  <si>
+    <t>ashford</t>
+  </si>
+  <si>
+    <t>E14001069</t>
+  </si>
+  <si>
+    <t>ashton-under-lyne</t>
+  </si>
+  <si>
+    <t>E14001070</t>
+  </si>
+  <si>
+    <t>aylesbury</t>
+  </si>
+  <si>
+    <t>E14001071</t>
+  </si>
+  <si>
+    <t>banbury</t>
+  </si>
+  <si>
+    <t>E14001072</t>
+  </si>
+  <si>
+    <t>barking</t>
+  </si>
+  <si>
+    <t>E14001073</t>
+  </si>
+  <si>
+    <t>barnsley north</t>
+  </si>
+  <si>
+    <t>E14001074</t>
+  </si>
+  <si>
+    <t>barnsley south</t>
+  </si>
+  <si>
+    <t>E14001075</t>
+  </si>
+  <si>
+    <t>barrow and furness</t>
+  </si>
+  <si>
+    <t>E14001076</t>
+  </si>
+  <si>
+    <t>basildon and billericay</t>
+  </si>
+  <si>
+    <t>E14001077</t>
+  </si>
+  <si>
+    <t>basingstoke</t>
+  </si>
+  <si>
+    <t>E14001078</t>
+  </si>
+  <si>
+    <t>bassetlaw</t>
+  </si>
+  <si>
+    <t>E14001079</t>
+  </si>
+  <si>
+    <t>bath</t>
+  </si>
+  <si>
+    <t>Liberal Democrat</t>
+  </si>
+  <si>
+    <t>E14001080</t>
+  </si>
+  <si>
+    <t>battersea</t>
+  </si>
+  <si>
+    <t>E14001081</t>
+  </si>
+  <si>
+    <t>beaconsfield</t>
+  </si>
+  <si>
+    <t>E14001082</t>
+  </si>
+  <si>
+    <t>beckenham and penge</t>
+  </si>
+  <si>
+    <t>E14001083</t>
+  </si>
+  <si>
+    <t>bedford</t>
+  </si>
+  <si>
+    <t>E14001084</t>
+  </si>
+  <si>
+    <t>bermondsey and old southwark</t>
+  </si>
+  <si>
+    <t>E14001085</t>
+  </si>
+  <si>
+    <t>bethnal green and stepney</t>
+  </si>
+  <si>
+    <t>E14001086</t>
+  </si>
+  <si>
+    <t>beverley and holderness</t>
+  </si>
+  <si>
+    <t>E14001087</t>
+  </si>
+  <si>
+    <t>bexhill and battle</t>
+  </si>
+  <si>
+    <t>E14001088</t>
+  </si>
+  <si>
+    <t>bexleyheath and crayford</t>
+  </si>
+  <si>
+    <t>E14001089</t>
+  </si>
+  <si>
+    <t>bicester and woodstock</t>
+  </si>
+  <si>
+    <t>E14001090</t>
+  </si>
+  <si>
+    <t>birkenhead</t>
+  </si>
+  <si>
+    <t>E14001091</t>
+  </si>
+  <si>
+    <t>birmingham edgbaston</t>
+  </si>
+  <si>
+    <t>E14001092</t>
+  </si>
+  <si>
+    <t>birmingham erdington</t>
+  </si>
+  <si>
+    <t>E14001093</t>
+  </si>
+  <si>
+    <t>birmingham hall green and moseley</t>
+  </si>
+  <si>
+    <t>E14001094</t>
+  </si>
+  <si>
+    <t>birmingham hodge hill and solihull north</t>
+  </si>
+  <si>
+    <t>E14001095</t>
+  </si>
+  <si>
+    <t>birmingham ladywood</t>
+  </si>
+  <si>
+    <t>E14001096</t>
+  </si>
+  <si>
+    <t>birmingham northfield</t>
+  </si>
+  <si>
+    <t>Green Party</t>
+  </si>
+  <si>
+    <t>E14001097</t>
+  </si>
+  <si>
+    <t>birmingham perry barr</t>
+  </si>
+  <si>
+    <t>E14001098</t>
+  </si>
+  <si>
+    <t>birmingham selly oak</t>
+  </si>
+  <si>
+    <t>E14001099</t>
+  </si>
+  <si>
+    <t>birmingham yardley</t>
+  </si>
+  <si>
+    <t>E14001100</t>
+  </si>
+  <si>
+    <t>bishop auckland</t>
+  </si>
+  <si>
+    <t>E14001101</t>
+  </si>
+  <si>
+    <t>blackburn</t>
+  </si>
+  <si>
+    <t>E14001102</t>
+  </si>
+  <si>
+    <t>blackley and middleton south</t>
+  </si>
+  <si>
+    <t>E14001103</t>
+  </si>
+  <si>
+    <t>blackpool north and fleetwood</t>
+  </si>
+  <si>
+    <t>E14001104</t>
+  </si>
+  <si>
+    <t>blackpool south</t>
+  </si>
+  <si>
+    <t>E14001105</t>
+  </si>
+  <si>
+    <t>blaydon and consett</t>
+  </si>
+  <si>
+    <t>E14001106</t>
+  </si>
+  <si>
+    <t>blyth and ashington</t>
+  </si>
+  <si>
+    <t>E14001107</t>
+  </si>
+  <si>
+    <t>bognor regis and littlehampton</t>
+  </si>
+  <si>
+    <t>E14001108</t>
+  </si>
+  <si>
+    <t>bolsover</t>
+  </si>
+  <si>
+    <t>E14001109</t>
+  </si>
+  <si>
+    <t>bolton north east</t>
+  </si>
+  <si>
+    <t>E14001110</t>
+  </si>
+  <si>
+    <t>bolton south and walkden</t>
+  </si>
+  <si>
+    <t>E14001111</t>
+  </si>
+  <si>
+    <t>bolton west</t>
+  </si>
+  <si>
+    <t>E14001112</t>
+  </si>
+  <si>
+    <t>bootle</t>
+  </si>
+  <si>
+    <t>E14001113</t>
+  </si>
+  <si>
+    <t>boston and skegness</t>
+  </si>
+  <si>
+    <t>E14001114</t>
+  </si>
+  <si>
+    <t>bournemouth east</t>
+  </si>
+  <si>
+    <t>E14001115</t>
+  </si>
+  <si>
+    <t>bournemouth west</t>
+  </si>
+  <si>
+    <t>E14001116</t>
+  </si>
+  <si>
+    <t>bracknell</t>
+  </si>
+  <si>
+    <t>E14001117</t>
+  </si>
+  <si>
+    <t>bradford east</t>
+  </si>
+  <si>
+    <t>E14001118</t>
+  </si>
+  <si>
+    <t>bradford south</t>
+  </si>
+  <si>
+    <t>E14001119</t>
+  </si>
+  <si>
+    <t>bradford west</t>
+  </si>
+  <si>
+    <t>E14001120</t>
+  </si>
+  <si>
+    <t>braintree</t>
+  </si>
+  <si>
+    <t>E14001121</t>
+  </si>
+  <si>
+    <t>brent east</t>
+  </si>
+  <si>
+    <t>E14001122</t>
+  </si>
+  <si>
+    <t>brent west</t>
+  </si>
+  <si>
+    <t>E14001123</t>
+  </si>
+  <si>
+    <t>brentford and isleworth</t>
+  </si>
+  <si>
+    <t>E14001124</t>
+  </si>
+  <si>
+    <t>brentwood and ongar</t>
+  </si>
+  <si>
+    <t>E14001125</t>
+  </si>
+  <si>
+    <t>bridgwater</t>
+  </si>
+  <si>
+    <t>E14001126</t>
+  </si>
+  <si>
+    <t>bridlington and the wolds</t>
+  </si>
+  <si>
+    <t>E14001127</t>
+  </si>
+  <si>
+    <t>brigg and immingham</t>
+  </si>
+  <si>
+    <t>E14001128</t>
+  </si>
+  <si>
+    <t>brighton kemptown and peacehaven</t>
+  </si>
+  <si>
+    <t>E14001129</t>
+  </si>
+  <si>
+    <t>brighton pavilion</t>
+  </si>
+  <si>
+    <t>E14001130</t>
+  </si>
+  <si>
+    <t>bristol central</t>
+  </si>
+  <si>
+    <t>E14001131</t>
+  </si>
+  <si>
+    <t>bristol east</t>
+  </si>
+  <si>
+    <t>E14001132</t>
+  </si>
+  <si>
+    <t>bristol north east</t>
+  </si>
+  <si>
+    <t>E14001133</t>
+  </si>
+  <si>
+    <t>bristol north west</t>
+  </si>
+  <si>
+    <t>E14001134</t>
+  </si>
+  <si>
+    <t>bristol south</t>
+  </si>
+  <si>
+    <t>E14001135</t>
+  </si>
+  <si>
+    <t>broadland and fakenham</t>
+  </si>
+  <si>
+    <t>E14001136</t>
+  </si>
+  <si>
+    <t>bromley and biggin hill</t>
+  </si>
+  <si>
+    <t>E14001137</t>
+  </si>
+  <si>
+    <t>bromsgrove</t>
+  </si>
+  <si>
+    <t>E14001138</t>
+  </si>
+  <si>
+    <t>broxbourne</t>
+  </si>
+  <si>
+    <t>E14001139</t>
+  </si>
+  <si>
+    <t>broxtowe</t>
+  </si>
+  <si>
+    <t>E14001140</t>
+  </si>
+  <si>
+    <t>buckingham and bletchley</t>
+  </si>
+  <si>
+    <t>E14001141</t>
+  </si>
+  <si>
+    <t>burnley</t>
+  </si>
+  <si>
+    <t>E14001142</t>
+  </si>
+  <si>
+    <t>burton and uttoxeter</t>
+  </si>
+  <si>
+    <t>E14001143</t>
+  </si>
+  <si>
+    <t>bury north</t>
+  </si>
+  <si>
+    <t>E14001144</t>
+  </si>
+  <si>
+    <t>bury south</t>
+  </si>
+  <si>
+    <t>E14001145</t>
+  </si>
+  <si>
+    <t>bury st edmunds and stowmarket</t>
+  </si>
+  <si>
+    <t>E14001146</t>
+  </si>
+  <si>
+    <t>calder valley</t>
+  </si>
+  <si>
+    <t>E14001147</t>
+  </si>
+  <si>
+    <t>camborne and redruth</t>
+  </si>
+  <si>
+    <t>E14001148</t>
+  </si>
+  <si>
+    <t>cambridge</t>
+  </si>
+  <si>
+    <t>E14001149</t>
+  </si>
+  <si>
+    <t>cannock chase</t>
+  </si>
+  <si>
+    <t>E14001150</t>
+  </si>
+  <si>
+    <t>canterbury</t>
+  </si>
+  <si>
+    <t>E14001151</t>
+  </si>
+  <si>
+    <t>carlisle</t>
+  </si>
+  <si>
+    <t>E14001152</t>
+  </si>
+  <si>
+    <t>carshalton and wallington</t>
+  </si>
+  <si>
+    <t>E14001153</t>
+  </si>
+  <si>
+    <t>castle point</t>
+  </si>
+  <si>
+    <t>E14001154</t>
+  </si>
+  <si>
+    <t>central devon</t>
+  </si>
+  <si>
+    <t>E14001155</t>
+  </si>
+  <si>
+    <t>central suffolk and north ipswich</t>
+  </si>
+  <si>
+    <t>E14001156</t>
+  </si>
+  <si>
+    <t>chatham and aylesford</t>
+  </si>
+  <si>
+    <t>E14001157</t>
+  </si>
+  <si>
+    <t>cheadle</t>
+  </si>
+  <si>
+    <t>E14001158</t>
+  </si>
+  <si>
+    <t>chelmsford</t>
+  </si>
+  <si>
+    <t>E14001159</t>
+  </si>
+  <si>
+    <t>chelsea and fulham</t>
+  </si>
+  <si>
+    <t>E14001160</t>
+  </si>
+  <si>
+    <t>cheltenham</t>
+  </si>
+  <si>
+    <t>E14001161</t>
+  </si>
+  <si>
+    <t>chesham and amersham</t>
+  </si>
+  <si>
+    <t>E14001162</t>
+  </si>
+  <si>
+    <t>chester north and neston</t>
+  </si>
+  <si>
+    <t>E14001163</t>
+  </si>
+  <si>
+    <t>chester south and eddisbury</t>
+  </si>
+  <si>
+    <t>E14001164</t>
+  </si>
+  <si>
+    <t>chesterfield</t>
+  </si>
+  <si>
+    <t>E14001165</t>
+  </si>
+  <si>
+    <t>chichester</t>
+  </si>
+  <si>
+    <t>E14001166</t>
+  </si>
+  <si>
+    <t>chingford and woodford green</t>
+  </si>
+  <si>
+    <t>E14001167</t>
+  </si>
+  <si>
+    <t>chippenham</t>
+  </si>
+  <si>
+    <t>E14001168</t>
+  </si>
+  <si>
+    <t>chipping barnet</t>
+  </si>
+  <si>
+    <t>E14001169</t>
+  </si>
+  <si>
+    <t>chorley</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
-    <t>E14001068</t>
-  </si>
-  <si>
-    <t>ashford</t>
-  </si>
-  <si>
-    <t>E14001069</t>
-  </si>
-  <si>
-    <t>ashton-under-lyne</t>
-  </si>
-  <si>
-    <t>E14001070</t>
-  </si>
-  <si>
-    <t>aylesbury</t>
-  </si>
-  <si>
-    <t>E14001071</t>
-  </si>
-  <si>
-    <t>banbury</t>
-  </si>
-  <si>
-    <t>E14001072</t>
-  </si>
-  <si>
-    <t>barking</t>
-  </si>
-  <si>
-    <t>E14001073</t>
-  </si>
-  <si>
-    <t>barnsley north</t>
-  </si>
-  <si>
-    <t>E14001074</t>
-  </si>
-  <si>
-    <t>barnsley south</t>
-  </si>
-  <si>
-    <t>E14001075</t>
-  </si>
-  <si>
-    <t>barrow and furness</t>
-  </si>
-  <si>
-    <t>E14001076</t>
-  </si>
-  <si>
-    <t>basildon and billericay</t>
-  </si>
-  <si>
-    <t>E14001077</t>
-  </si>
-  <si>
-    <t>basingstoke</t>
-  </si>
-  <si>
-    <t>E14001078</t>
-  </si>
-  <si>
-    <t>bassetlaw</t>
-  </si>
-  <si>
-    <t>E14001079</t>
-  </si>
-  <si>
-    <t>bath</t>
-  </si>
-  <si>
-    <t>Liberal Democrat</t>
-  </si>
-  <si>
-    <t>E14001080</t>
-  </si>
-  <si>
-    <t>battersea</t>
-  </si>
-  <si>
-    <t>E14001081</t>
-  </si>
-  <si>
-    <t>beaconsfield</t>
-  </si>
-  <si>
-    <t>E14001082</t>
-  </si>
-  <si>
-    <t>beckenham and penge</t>
-  </si>
-  <si>
-    <t>E14001083</t>
-  </si>
-  <si>
-    <t>bedford</t>
-  </si>
-  <si>
-    <t>E14001084</t>
-  </si>
-  <si>
-    <t>bermondsey and old southwark</t>
-  </si>
-  <si>
-    <t>E14001085</t>
-  </si>
-  <si>
-    <t>bethnal green and stepney</t>
-  </si>
-  <si>
-    <t>E14001086</t>
-  </si>
-  <si>
-    <t>beverley and holderness</t>
-  </si>
-  <si>
-    <t>E14001087</t>
-  </si>
-  <si>
-    <t>bexhill and battle</t>
-  </si>
-  <si>
-    <t>E14001088</t>
-  </si>
-  <si>
-    <t>bexleyheath and crayford</t>
-  </si>
-  <si>
-    <t>E14001089</t>
-  </si>
-  <si>
-    <t>bicester and woodstock</t>
-  </si>
-  <si>
-    <t>E14001090</t>
-  </si>
-  <si>
-    <t>birkenhead</t>
-  </si>
-  <si>
-    <t>E14001091</t>
-  </si>
-  <si>
-    <t>birmingham edgbaston</t>
-  </si>
-  <si>
-    <t>E14001092</t>
-  </si>
-  <si>
-    <t>birmingham erdington</t>
-  </si>
-  <si>
-    <t>E14001093</t>
-  </si>
-  <si>
-    <t>birmingham hall green and moseley</t>
-  </si>
-  <si>
-    <t>E14001094</t>
-  </si>
-  <si>
-    <t>birmingham hodge hill and solihull north</t>
-  </si>
-  <si>
-    <t>E14001095</t>
-  </si>
-  <si>
-    <t>birmingham ladywood</t>
-  </si>
-  <si>
-    <t>E14001096</t>
-  </si>
-  <si>
-    <t>birmingham northfield</t>
-  </si>
-  <si>
-    <t>Green Party</t>
-  </si>
-  <si>
-    <t>E14001097</t>
-  </si>
-  <si>
-    <t>birmingham perry barr</t>
-  </si>
-  <si>
-    <t>E14001098</t>
-  </si>
-  <si>
-    <t>birmingham selly oak</t>
-  </si>
-  <si>
-    <t>E14001099</t>
-  </si>
-  <si>
-    <t>birmingham yardley</t>
-  </si>
-  <si>
-    <t>E14001100</t>
-  </si>
-  <si>
-    <t>bishop auckland</t>
-  </si>
-  <si>
-    <t>E14001101</t>
-  </si>
-  <si>
-    <t>blackburn</t>
-  </si>
-  <si>
-    <t>E14001102</t>
-  </si>
-  <si>
-    <t>blackley and middleton south</t>
-  </si>
-  <si>
-    <t>E14001103</t>
-  </si>
-  <si>
-    <t>blackpool north and fleetwood</t>
-  </si>
-  <si>
-    <t>E14001104</t>
-  </si>
-  <si>
-    <t>blackpool south</t>
-  </si>
-  <si>
-    <t>E14001105</t>
-  </si>
-  <si>
-    <t>blaydon and consett</t>
-  </si>
-  <si>
-    <t>E14001106</t>
-  </si>
-  <si>
-    <t>blyth and ashington</t>
-  </si>
-  <si>
-    <t>E14001107</t>
-  </si>
-  <si>
-    <t>bognor regis and littlehampton</t>
-  </si>
-  <si>
-    <t>E14001108</t>
-  </si>
-  <si>
-    <t>bolsover</t>
-  </si>
-  <si>
-    <t>E14001109</t>
-  </si>
-  <si>
-    <t>bolton north east</t>
-  </si>
-  <si>
-    <t>E14001110</t>
-  </si>
-  <si>
-    <t>bolton south and walkden</t>
-  </si>
-  <si>
-    <t>E14001111</t>
-  </si>
-  <si>
-    <t>bolton west</t>
-  </si>
-  <si>
-    <t>E14001112</t>
-  </si>
-  <si>
-    <t>bootle</t>
-  </si>
-  <si>
-    <t>E14001113</t>
-  </si>
-  <si>
-    <t>boston and skegness</t>
-  </si>
-  <si>
-    <t>E14001114</t>
-  </si>
-  <si>
-    <t>bournemouth east</t>
-  </si>
-  <si>
-    <t>E14001115</t>
-  </si>
-  <si>
-    <t>bournemouth west</t>
-  </si>
-  <si>
-    <t>E14001116</t>
-  </si>
-  <si>
-    <t>bracknell</t>
-  </si>
-  <si>
-    <t>E14001117</t>
-  </si>
-  <si>
-    <t>bradford east</t>
-  </si>
-  <si>
-    <t>E14001118</t>
-  </si>
-  <si>
-    <t>bradford south</t>
-  </si>
-  <si>
-    <t>E14001119</t>
-  </si>
-  <si>
-    <t>bradford west</t>
-  </si>
-  <si>
-    <t>E14001120</t>
-  </si>
-  <si>
-    <t>braintree</t>
-  </si>
-  <si>
-    <t>E14001121</t>
-  </si>
-  <si>
-    <t>brent east</t>
-  </si>
-  <si>
-    <t>E14001122</t>
-  </si>
-  <si>
-    <t>brent west</t>
-  </si>
-  <si>
-    <t>E14001123</t>
-  </si>
-  <si>
-    <t>brentford and isleworth</t>
-  </si>
-  <si>
-    <t>E14001124</t>
-  </si>
-  <si>
-    <t>brentwood and ongar</t>
-  </si>
-  <si>
-    <t>E14001125</t>
-  </si>
-  <si>
-    <t>bridgwater</t>
-  </si>
-  <si>
-    <t>E14001126</t>
-  </si>
-  <si>
-    <t>bridlington and the wolds</t>
-  </si>
-  <si>
-    <t>E14001127</t>
-  </si>
-  <si>
-    <t>brigg and immingham</t>
-  </si>
-  <si>
-    <t>E14001128</t>
-  </si>
-  <si>
-    <t>brighton kemptown and peacehaven</t>
-  </si>
-  <si>
-    <t>E14001129</t>
-  </si>
-  <si>
-    <t>brighton pavilion</t>
-  </si>
-  <si>
-    <t>E14001130</t>
-  </si>
-  <si>
-    <t>bristol central</t>
-  </si>
-  <si>
-    <t>E14001131</t>
-  </si>
-  <si>
-    <t>bristol east</t>
-  </si>
-  <si>
-    <t>E14001132</t>
-  </si>
-  <si>
-    <t>bristol north east</t>
-  </si>
-  <si>
-    <t>E14001133</t>
-  </si>
-  <si>
-    <t>bristol north west</t>
-  </si>
-  <si>
-    <t>E14001134</t>
-  </si>
-  <si>
-    <t>bristol south</t>
-  </si>
-  <si>
-    <t>E14001135</t>
-  </si>
-  <si>
-    <t>broadland and fakenham</t>
-  </si>
-  <si>
-    <t>E14001136</t>
-  </si>
-  <si>
-    <t>bromley and biggin hill</t>
-  </si>
-  <si>
-    <t>E14001137</t>
-  </si>
-  <si>
-    <t>bromsgrove</t>
-  </si>
-  <si>
-    <t>E14001138</t>
-  </si>
-  <si>
-    <t>broxbourne</t>
-  </si>
-  <si>
-    <t>E14001139</t>
-  </si>
-  <si>
-    <t>broxtowe</t>
-  </si>
-  <si>
-    <t>E14001140</t>
-  </si>
-  <si>
-    <t>buckingham and bletchley</t>
-  </si>
-  <si>
-    <t>E14001141</t>
-  </si>
-  <si>
-    <t>burnley</t>
-  </si>
-  <si>
-    <t>E14001142</t>
-  </si>
-  <si>
-    <t>burton and uttoxeter</t>
-  </si>
-  <si>
-    <t>E14001143</t>
-  </si>
-  <si>
-    <t>bury north</t>
-  </si>
-  <si>
-    <t>E14001144</t>
-  </si>
-  <si>
-    <t>bury south</t>
-  </si>
-  <si>
-    <t>E14001145</t>
-  </si>
-  <si>
-    <t>bury st edmunds and stowmarket</t>
-  </si>
-  <si>
-    <t>E14001146</t>
-  </si>
-  <si>
-    <t>calder valley</t>
-  </si>
-  <si>
-    <t>E14001147</t>
-  </si>
-  <si>
-    <t>camborne and redruth</t>
-  </si>
-  <si>
-    <t>E14001148</t>
-  </si>
-  <si>
-    <t>cambridge</t>
-  </si>
-  <si>
-    <t>E14001149</t>
-  </si>
-  <si>
-    <t>cannock chase</t>
-  </si>
-  <si>
-    <t>E14001150</t>
-  </si>
-  <si>
-    <t>canterbury</t>
-  </si>
-  <si>
-    <t>E14001151</t>
-  </si>
-  <si>
-    <t>carlisle</t>
-  </si>
-  <si>
-    <t>E14001152</t>
-  </si>
-  <si>
-    <t>carshalton and wallington</t>
-  </si>
-  <si>
-    <t>E14001153</t>
-  </si>
-  <si>
-    <t>castle point</t>
-  </si>
-  <si>
-    <t>E14001154</t>
-  </si>
-  <si>
-    <t>central devon</t>
-  </si>
-  <si>
-    <t>E14001155</t>
-  </si>
-  <si>
-    <t>central suffolk and north ipswich</t>
-  </si>
-  <si>
-    <t>E14001156</t>
-  </si>
-  <si>
-    <t>chatham and aylesford</t>
-  </si>
-  <si>
-    <t>E14001157</t>
-  </si>
-  <si>
-    <t>cheadle</t>
-  </si>
-  <si>
-    <t>E14001158</t>
-  </si>
-  <si>
-    <t>chelmsford</t>
-  </si>
-  <si>
-    <t>E14001159</t>
-  </si>
-  <si>
-    <t>chelsea and fulham</t>
-  </si>
-  <si>
-    <t>E14001160</t>
-  </si>
-  <si>
-    <t>cheltenham</t>
-  </si>
-  <si>
-    <t>E14001161</t>
-  </si>
-  <si>
-    <t>chesham and amersham</t>
-  </si>
-  <si>
-    <t>E14001162</t>
-  </si>
-  <si>
-    <t>chester north and neston</t>
-  </si>
-  <si>
-    <t>E14001163</t>
-  </si>
-  <si>
-    <t>chester south and eddisbury</t>
-  </si>
-  <si>
-    <t>E14001164</t>
-  </si>
-  <si>
-    <t>chesterfield</t>
-  </si>
-  <si>
-    <t>E14001165</t>
-  </si>
-  <si>
-    <t>chichester</t>
-  </si>
-  <si>
-    <t>E14001166</t>
-  </si>
-  <si>
-    <t>chingford and woodford green</t>
-  </si>
-  <si>
-    <t>E14001167</t>
-  </si>
-  <si>
-    <t>chippenham</t>
-  </si>
-  <si>
-    <t>E14001168</t>
-  </si>
-  <si>
-    <t>chipping barnet</t>
-  </si>
-  <si>
-    <t>E14001169</t>
-  </si>
-  <si>
-    <t>chorley</t>
-  </si>
-  <si>
     <t>E14001170</t>
   </si>
   <si>
@@ -3815,31 +3815,31 @@
     <t>blaenau gwent and rhymney</t>
   </si>
   <si>
+    <t>W07000084</t>
+  </si>
+  <si>
+    <t>brecon, radnor and cwm tawe</t>
+  </si>
+  <si>
+    <t>W07000085</t>
+  </si>
+  <si>
+    <t>bridgend</t>
+  </si>
+  <si>
+    <t>W07000086</t>
+  </si>
+  <si>
+    <t>caerfyrddin</t>
+  </si>
+  <si>
+    <t>W07000087</t>
+  </si>
+  <si>
+    <t>caerphilly</t>
+  </si>
+  <si>
     <t>Plaid Cymru</t>
-  </si>
-  <si>
-    <t>W07000084</t>
-  </si>
-  <si>
-    <t>brecon, radnor and cwm tawe</t>
-  </si>
-  <si>
-    <t>W07000085</t>
-  </si>
-  <si>
-    <t>bridgend</t>
-  </si>
-  <si>
-    <t>W07000086</t>
-  </si>
-  <si>
-    <t>caerfyrddin</t>
-  </si>
-  <si>
-    <t>W07000087</t>
-  </si>
-  <si>
-    <t>caerphilly</t>
   </si>
   <si>
     <t>W07000088</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2783397162352091</v>
+        <v>0.2861136619684696</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.3908213891285116</v>
+        <v>0.4244600019068437</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3741141682964865</v>
+        <v>0.3883263223309518</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3270360202658594</v>
+        <v>0.3203165626118626</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3447481455512441</v>
+        <v>0.3672823498225658</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4442,1744 +4442,1744 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0.2894188262842786</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
         <v>20</v>
-      </c>
-      <c r="C7">
-        <v>0.2841931363389094</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3309140702054094</v>
+        <v>0.3436478907024805</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3035155513653607</v>
+        <v>0.3068564098264016</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3345826706538367</v>
+        <v>0.3419190169819784</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2428555332887804</v>
+        <v>0.2365624300929078</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>0.3863311756245</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12">
-        <v>0.4118165766805206</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.2866908482065674</v>
+        <v>0.2849147063794257</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3740957354290101</v>
+        <v>0.3629465736558813</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.33807311999948</v>
+        <v>0.3482010779662978</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>0.3181361481180126</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s">
         <v>38</v>
-      </c>
-      <c r="B16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>0.2956265659523648</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>0.2828756880254554</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
         <v>40</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17">
-        <v>0.2632905748378498</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.2815656349927556</v>
+        <v>0.3144865619517914</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19">
+        <v>0.4385165461202119</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
         <v>45</v>
-      </c>
-      <c r="C19">
-        <v>0.4368047353234267</v>
-      </c>
-      <c r="D19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20">
+        <v>0.3983236681891718</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s">
         <v>47</v>
-      </c>
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20">
-        <v>0.396904736777948</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.3920179347903796</v>
+        <v>0.4275915522253093</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>0.3189457939618349</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
         <v>51</v>
-      </c>
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22">
-        <v>0.3220923365675588</v>
-      </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>0.38233403747561</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
         <v>53</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>0.3846485913484996</v>
-      </c>
-      <c r="D23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>0.3296308344864835</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
         <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24">
-        <v>0.3186984306764079</v>
-      </c>
-      <c r="D24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>0.5914225481423456</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
         <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25">
-        <v>0.5857831564645877</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>0.3213711217749676</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
         <v>59</v>
-      </c>
-      <c r="B26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26">
-        <v>0.306924912249611</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>0.2853612406948791</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
         <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27">
-        <v>0.2687802255744351</v>
-      </c>
-      <c r="D27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.2973430767280314</v>
+        <v>0.3166711537639034</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29">
+        <v>0.4723371418438614</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
         <v>65</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29">
-        <v>0.4648008849306461</v>
-      </c>
-      <c r="D29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>0.3791339473693786</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30">
-        <v>0.357204969062116</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>0.4332990973851951</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
         <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31">
-        <v>0.4117154087621919</v>
-      </c>
-      <c r="D31" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.3857904546143509</v>
+        <v>0.3930012298671672</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>0.3851622492261616</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
         <v>73</v>
-      </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33">
-        <v>0.3678105251400186</v>
-      </c>
-      <c r="D33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3091699304959967</v>
+        <v>0.3256855921164982</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>0.4367476546473292</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
         <v>77</v>
-      </c>
-      <c r="B35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35">
-        <v>0.4280752045529344</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
         <v>79</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36">
+        <v>0.2275722004655827</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" t="s">
         <v>80</v>
-      </c>
-      <c r="C36">
-        <v>0.248397557007654</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.2868247712126806</v>
+        <v>0.272876092351075</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
+        <v>83</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>0.3113558885968452</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s">
         <v>84</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38">
-        <v>0.33456155359148</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3372073511408544</v>
+        <v>0.3094237980949825</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0.4718995208209228</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
         <v>88</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>0.4494455651839437</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41">
+        <v>0.2558844780521347</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" t="s">
         <v>90</v>
-      </c>
-      <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41">
-        <v>0.27969354789309</v>
-      </c>
-      <c r="D41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>0.5267119988322035</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
         <v>92</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42">
-        <v>0.5250718319371045</v>
-      </c>
-      <c r="D42" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3799198219069162</v>
+        <v>0.3948497229958553</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.3756747451551119</v>
+        <v>0.4045289947652131</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>0.3841009784678219</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
         <v>98</v>
-      </c>
-      <c r="B45" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45">
-        <v>0.3840271067620474</v>
-      </c>
-      <c r="D45" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>0.4245622161495508</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" t="s">
         <v>100</v>
-      </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46">
-        <v>0.4211556963159843</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.283447987864051</v>
+        <v>0.2959512301138466</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.3851976622050953</v>
+        <v>0.3934902795124471</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3254333406148167</v>
+        <v>0.3427760256573618</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3487720543865165</v>
+        <v>0.36516290637235</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
+        <v>109</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>0.3502851354946415</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" t="s">
         <v>110</v>
-      </c>
-      <c r="B51" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51">
-        <v>0.3280506797283821</v>
-      </c>
-      <c r="D51" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>0.4827612216876414</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
         <v>112</v>
-      </c>
-      <c r="B52" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52">
-        <v>0.5084372435141645</v>
-      </c>
-      <c r="D52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4105320412923439</v>
+        <v>0.4106643150911294</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
+        <v>115</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>0.3670068017848328</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
         <v>116</v>
-      </c>
-      <c r="B54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54">
-        <v>0.3776635194473141</v>
-      </c>
-      <c r="D54" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2787148517751213</v>
+        <v>0.2643365648169991</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3362478358228546</v>
+        <v>0.3584650885406817</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
+        <v>121</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>0.5694327585605388</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
         <v>122</v>
-      </c>
-      <c r="B57" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57">
-        <v>0.5433779507405758</v>
-      </c>
-      <c r="D57" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>0.3085390677888586</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
         <v>124</v>
-      </c>
-      <c r="B58" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58">
-        <v>0.30033283189373</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>0.3501096805573429</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
         <v>126</v>
-      </c>
-      <c r="B59" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59">
-        <v>0.3647772723092726</v>
-      </c>
-      <c r="D59" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
+        <v>127</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60">
+        <v>0.2983347184269911</v>
+      </c>
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
         <v>128</v>
-      </c>
-      <c r="B60" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60">
-        <v>0.2831074009107585</v>
-      </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
+        <v>129</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61">
+        <v>0.3808066766348976</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
         <v>130</v>
-      </c>
-      <c r="B61" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61">
-        <v>0.3368065293766908</v>
-      </c>
-      <c r="D61" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3166152470789659</v>
+        <v>0.3214507429466437</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <v>0.3670005025939267</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
         <v>134</v>
-      </c>
-      <c r="B63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63">
-        <v>0.3580902463359339</v>
-      </c>
-      <c r="D63" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C64">
+        <v>0.230033736577176</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" t="s">
         <v>136</v>
-      </c>
-      <c r="B64" t="s">
-        <v>45</v>
-      </c>
-      <c r="C64">
-        <v>0.2245166136552385</v>
-      </c>
-      <c r="D64" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3119823433013833</v>
+        <v>0.312110818327202</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3155414206277927</v>
+        <v>0.3056722322614504</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3337399643999885</v>
+        <v>0.3279944714071562</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68">
+        <v>0.2719312918361165</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" t="s">
         <v>144</v>
-      </c>
-      <c r="B68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68">
-        <v>0.2529596440842589</v>
-      </c>
-      <c r="D68" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C69">
+        <v>0.5375813134285388</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" t="s">
         <v>146</v>
-      </c>
-      <c r="B69" t="s">
-        <v>80</v>
-      </c>
-      <c r="C69">
-        <v>0.5664889531204741</v>
-      </c>
-      <c r="D69" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70">
+        <v>0.5068866895159087</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
         <v>148</v>
-      </c>
-      <c r="B70" t="s">
-        <v>80</v>
-      </c>
-      <c r="C70">
-        <v>0.5268502924471444</v>
-      </c>
-      <c r="D70" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71">
+        <v>0.4647428572850165</v>
+      </c>
+      <c r="D71" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
         <v>150</v>
-      </c>
-      <c r="B71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71">
-        <v>0.4362797626795313</v>
-      </c>
-      <c r="D71" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72">
+        <v>0.3547631793790447</v>
+      </c>
+      <c r="D72" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" t="s">
         <v>152</v>
-      </c>
-      <c r="B72" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72">
-        <v>0.3414218313787895</v>
-      </c>
-      <c r="D72" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73">
+        <v>0.4755248056365441</v>
+      </c>
+      <c r="D73" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" t="s">
         <v>154</v>
-      </c>
-      <c r="B73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73">
-        <v>0.4978382199716783</v>
-      </c>
-      <c r="D73" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74">
+        <v>0.469921047381363</v>
+      </c>
+      <c r="D74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" t="s">
         <v>156</v>
-      </c>
-      <c r="B74" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74">
-        <v>0.4476031330612863</v>
-      </c>
-      <c r="D74" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2416529502251306</v>
+        <v>0.2659975113984998</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B76" t="s">
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3585913257101458</v>
+        <v>0.3473077768408801</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
       </c>
       <c r="E76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3180372917572961</v>
+        <v>0.2826879145789996</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
       </c>
       <c r="E77" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4145123140844902</v>
+        <v>0.415729232435863</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
       </c>
       <c r="E78" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79">
+        <v>0.2487705462943092</v>
+      </c>
+      <c r="D79" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" t="s">
         <v>166</v>
-      </c>
-      <c r="B79" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79">
-        <v>0.2542548238941606</v>
-      </c>
-      <c r="D79" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3489374617501155</v>
+        <v>0.3584070635167842</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B81" t="s">
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.285739011902557</v>
+        <v>0.2841801853337769</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
       </c>
       <c r="E81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B82" t="s">
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4021364387411479</v>
+        <v>0.4014896921890105</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83">
+        <v>0.3705370513929325</v>
+      </c>
+      <c r="D83" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" t="s">
         <v>174</v>
-      </c>
-      <c r="B83" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83">
-        <v>0.3946498553831562</v>
-      </c>
-      <c r="D83" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
       </c>
       <c r="C84">
-        <v>0.2911070707805467</v>
+        <v>0.2917098742282421</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
       </c>
       <c r="E84" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B85" t="s">
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3231846468947362</v>
+        <v>0.3051074371779726</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
       </c>
       <c r="E85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
+        <v>179</v>
+      </c>
+      <c r="B86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86">
+        <v>0.304240865705958</v>
+      </c>
+      <c r="D86" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" t="s">
         <v>180</v>
-      </c>
-      <c r="B86" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86">
-        <v>0.2855697574256493</v>
-      </c>
-      <c r="D86" t="s">
-        <v>7</v>
-      </c>
-      <c r="E86" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87">
+        <v>0.2739612573104298</v>
+      </c>
+      <c r="D87" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" t="s">
         <v>182</v>
-      </c>
-      <c r="B87" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87">
-        <v>0.266898051142975</v>
-      </c>
-      <c r="D87" t="s">
-        <v>7</v>
-      </c>
-      <c r="E87" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88">
+        <v>0.3150632622683961</v>
+      </c>
+      <c r="D88" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" t="s">
         <v>184</v>
-      </c>
-      <c r="B88" t="s">
-        <v>80</v>
-      </c>
-      <c r="C88">
-        <v>0.3249859967764583</v>
-      </c>
-      <c r="D88" t="s">
-        <v>7</v>
-      </c>
-      <c r="E88" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B89" t="s">
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.2941247265956287</v>
+        <v>0.3178494778473476</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
       </c>
       <c r="E89" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B90" t="s">
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2726298306066811</v>
+        <v>0.2850336665976755</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
       </c>
       <c r="E90" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
+        <v>189</v>
+      </c>
+      <c r="B91" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91">
+        <v>0.2840658945572561</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" t="s">
         <v>190</v>
-      </c>
-      <c r="B91" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91">
-        <v>0.2710729350706333</v>
-      </c>
-      <c r="D91" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
+        <v>191</v>
+      </c>
+      <c r="B92" t="s">
+        <v>44</v>
+      </c>
+      <c r="C92">
+        <v>0.2985353951302683</v>
+      </c>
+      <c r="D92" t="s">
+        <v>7</v>
+      </c>
+      <c r="E92" t="s">
         <v>192</v>
-      </c>
-      <c r="B92" t="s">
-        <v>45</v>
-      </c>
-      <c r="C92">
-        <v>0.3137335093446783</v>
-      </c>
-      <c r="D92" t="s">
-        <v>7</v>
-      </c>
-      <c r="E92" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3774582313033601</v>
+        <v>0.3688740251464059</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
+        <v>195</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94">
+        <v>0.2859199590467616</v>
+      </c>
+      <c r="D94" t="s">
+        <v>7</v>
+      </c>
+      <c r="E94" t="s">
         <v>196</v>
-      </c>
-      <c r="B94" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94">
-        <v>0.2615840943483706</v>
-      </c>
-      <c r="D94" t="s">
-        <v>7</v>
-      </c>
-      <c r="E94" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B95" t="s">
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3111086631906604</v>
+        <v>0.3318529712939059</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3452306938457549</v>
+        <v>0.3416291724766912</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
       </c>
       <c r="E96" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
+        <v>201</v>
+      </c>
+      <c r="B97" t="s">
+        <v>44</v>
+      </c>
+      <c r="C97">
+        <v>0.3351494207084505</v>
+      </c>
+      <c r="D97" t="s">
+        <v>7</v>
+      </c>
+      <c r="E97" t="s">
         <v>202</v>
-      </c>
-      <c r="B97" t="s">
-        <v>45</v>
-      </c>
-      <c r="C97">
-        <v>0.3526337295442307</v>
-      </c>
-      <c r="D97" t="s">
-        <v>7</v>
-      </c>
-      <c r="E97" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
+        <v>203</v>
+      </c>
+      <c r="B98" t="s">
+        <v>44</v>
+      </c>
+      <c r="C98">
+        <v>0.3573993703475558</v>
+      </c>
+      <c r="D98" t="s">
+        <v>7</v>
+      </c>
+      <c r="E98" t="s">
         <v>204</v>
-      </c>
-      <c r="B98" t="s">
-        <v>45</v>
-      </c>
-      <c r="C98">
-        <v>0.3616224791005015</v>
-      </c>
-      <c r="D98" t="s">
-        <v>7</v>
-      </c>
-      <c r="E98" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
+        <v>205</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99">
+        <v>0.4095402429565683</v>
+      </c>
+      <c r="D99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" t="s">
         <v>206</v>
-      </c>
-      <c r="B99" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99">
-        <v>0.4131779409124166</v>
-      </c>
-      <c r="D99" t="s">
-        <v>7</v>
-      </c>
-      <c r="E99" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
+        <v>207</v>
+      </c>
+      <c r="B100" t="s">
+        <v>44</v>
+      </c>
+      <c r="C100">
+        <v>0.3685449830735972</v>
+      </c>
+      <c r="D100" t="s">
+        <v>7</v>
+      </c>
+      <c r="E100" t="s">
         <v>208</v>
-      </c>
-      <c r="B100" t="s">
-        <v>45</v>
-      </c>
-      <c r="C100">
-        <v>0.3898807164242571</v>
-      </c>
-      <c r="D100" t="s">
-        <v>7</v>
-      </c>
-      <c r="E100" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
+        <v>209</v>
+      </c>
+      <c r="B101" t="s">
+        <v>44</v>
+      </c>
+      <c r="C101">
+        <v>0.4381067533284311</v>
+      </c>
+      <c r="D101" t="s">
+        <v>7</v>
+      </c>
+      <c r="E101" t="s">
         <v>210</v>
-      </c>
-      <c r="B101" t="s">
-        <v>45</v>
-      </c>
-      <c r="C101">
-        <v>0.4468083565307387</v>
-      </c>
-      <c r="D101" t="s">
-        <v>7</v>
-      </c>
-      <c r="E101" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
+        <v>211</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102">
+        <v>0.4446168524928911</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" t="s">
         <v>212</v>
-      </c>
-      <c r="B102" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102">
-        <v>0.4287889024774094</v>
-      </c>
-      <c r="D102" t="s">
-        <v>7</v>
-      </c>
-      <c r="E102" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
+        <v>213</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103">
+        <v>0.3355966270539834</v>
+      </c>
+      <c r="D103" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" t="s">
         <v>214</v>
-      </c>
-      <c r="B103" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103">
-        <v>0.3438954592691309</v>
-      </c>
-      <c r="D103" t="s">
-        <v>7</v>
-      </c>
-      <c r="E103" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B104" t="s">
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3352564968874661</v>
+        <v>0.3613003794214308</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
       </c>
       <c r="E104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
+        <v>217</v>
+      </c>
+      <c r="B105" t="s">
+        <v>44</v>
+      </c>
+      <c r="C105">
+        <v>0.347696117307507</v>
+      </c>
+      <c r="D105" t="s">
+        <v>7</v>
+      </c>
+      <c r="E105" t="s">
         <v>218</v>
-      </c>
-      <c r="B105" t="s">
-        <v>45</v>
-      </c>
-      <c r="C105">
-        <v>0.3663789219529934</v>
-      </c>
-      <c r="D105" t="s">
-        <v>7</v>
-      </c>
-      <c r="E105" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B106" t="s">
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3729088405903878</v>
+        <v>0.3629771428920042</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
       </c>
       <c r="E106" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
+        <v>221</v>
+      </c>
+      <c r="B107" t="s">
+        <v>44</v>
+      </c>
+      <c r="C107">
+        <v>0.3573134005318049</v>
+      </c>
+      <c r="D107" t="s">
+        <v>7</v>
+      </c>
+      <c r="E107" t="s">
         <v>222</v>
-      </c>
-      <c r="B107" t="s">
-        <v>45</v>
-      </c>
-      <c r="C107">
-        <v>0.3528267658574491</v>
-      </c>
-      <c r="D107" t="s">
-        <v>7</v>
-      </c>
-      <c r="E107" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
+        <v>223</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108">
+        <v>0.387397570016406</v>
+      </c>
+      <c r="D108" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" t="s">
         <v>224</v>
-      </c>
-      <c r="B108" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108">
-        <v>0.4006373148734787</v>
-      </c>
-      <c r="D108" t="s">
-        <v>7</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
+        <v>225</v>
+      </c>
+      <c r="B109" t="s">
         <v>226</v>
       </c>
-      <c r="B109" t="s">
-        <v>20</v>
-      </c>
       <c r="C109">
-        <v>0.2661405541436977</v>
+        <v>0.2732875398744341</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2865739358698661</v>
+        <v>0.293645532886323</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4786420083584983</v>
+        <v>0.4870710258599482</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3605094813587421</v>
+        <v>0.3776683175939995</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4916011738613081</v>
+        <v>0.4907773194083301</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6072892346160425</v>
+        <v>0.6172606299007736</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3015864972684584</v>
+        <v>0.2958022654649784</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4331117028485081</v>
+        <v>0.4425244458387717</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.271345088870486</v>
+        <v>0.29147529640192</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3928449874997194</v>
+        <v>0.3715870178840825</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3705309861067657</v>
+        <v>0.3656998806715763</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3542835903882562</v>
+        <v>0.3536123643868399</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.292275555831002</v>
+        <v>0.2491215870181868</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3172092618583013</v>
+        <v>0.3016808408980547</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.279836772460911</v>
+        <v>0.2918652595570721</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3583740257847175</v>
+        <v>0.3877516581358044</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>0.2758427591569181</v>
+        <v>0.3071461346081928</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3746323351072266</v>
+        <v>0.3468645070321281</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4739349460992593</v>
+        <v>0.4864466149757284</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.3688115184596596</v>
+        <v>0.3925288989113198</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C129">
-        <v>0.2960566504884973</v>
+        <v>0.3022755427149115</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.4048481612357133</v>
+        <v>0.3811545999044016</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2692374941307293</v>
+        <v>0.2744174015479982</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3636908778773366</v>
+        <v>0.3855046340838106</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3159163000335873</v>
+        <v>0.3255400822712893</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3240641925436202</v>
+        <v>0.3148347790422202</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3331713829789615</v>
+        <v>0.3043210902916059</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6635,10 +6635,10 @@
         <v>280</v>
       </c>
       <c r="B136" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3316245908287139</v>
+        <v>0.3220976321552211</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3755358506196073</v>
+        <v>0.4084715136538806</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3111588431595431</v>
+        <v>0.3286231651545216</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4227334566780049</v>
+        <v>0.3643812157744238</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6703,10 +6703,10 @@
         <v>288</v>
       </c>
       <c r="B140" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C140">
-        <v>0.4044737009914344</v>
+        <v>0.3929183936180154</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3393266458559356</v>
+        <v>0.3352164929228912</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3685179173589958</v>
+        <v>0.3751992665385492</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.2918280548797931</v>
+        <v>0.3304794353894058</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5273450574132679</v>
+        <v>0.5910626312735524</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2721995698689382</v>
+        <v>0.2830210551373179</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4113452825246861</v>
+        <v>0.3922599697988504</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4241776172112502</v>
+        <v>0.4444133285047434</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3225298987295805</v>
+        <v>0.2882112860032878</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3553524299869851</v>
+        <v>0.3651088418394173</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6873,10 +6873,10 @@
         <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3063939351318757</v>
+        <v>0.3252114125162771</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2427757885437097</v>
+        <v>0.2456400076795973</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6177216660645984</v>
+        <v>0.6614707942934493</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3189446434510047</v>
+        <v>0.3195086499242815</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6941,10 +6941,10 @@
         <v>316</v>
       </c>
       <c r="B154" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C154">
-        <v>0.321223956360034</v>
+        <v>0.3230786337460085</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6958,10 +6958,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C155">
-        <v>0.2610802127860333</v>
+        <v>0.2746712802077314</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3337332961301803</v>
+        <v>0.3278961858593225</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3524182010413938</v>
+        <v>0.3461333624692499</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7009,10 +7009,10 @@
         <v>324</v>
       </c>
       <c r="B158" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3811697946091416</v>
+        <v>0.387975869225308</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7026,10 +7026,10 @@
         <v>326</v>
       </c>
       <c r="B159" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3868815088971703</v>
+        <v>0.3986600693219532</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3855129779545766</v>
+        <v>0.3720802176222696</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3633970518590632</v>
+        <v>0.3821963615354673</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5516020643119978</v>
+        <v>0.5557076652017821</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7094,10 +7094,10 @@
         <v>334</v>
       </c>
       <c r="B163" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4520364912778011</v>
+        <v>0.441378620513883</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.2957157313577768</v>
+        <v>0.3385024982098514</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3381607684906451</v>
+        <v>0.3436757666890416</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C166">
-        <v>0.334986085477665</v>
+        <v>0.3002813757688143</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3463686200010235</v>
+        <v>0.352472341708571</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5636992295108407</v>
+        <v>0.5859808257434195</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7196,10 +7196,10 @@
         <v>346</v>
       </c>
       <c r="B169" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3452725842164662</v>
+        <v>0.3328898646405973</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3353252212608033</v>
+        <v>0.348418422339315</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C171">
-        <v>0.2610419418775379</v>
+        <v>0.2557727318901526</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4146880456346468</v>
+        <v>0.3884262915422832</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3281972394036274</v>
+        <v>0.3077930511540957</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3146334687471917</v>
+        <v>0.324173304810476</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2909061668969898</v>
+        <v>0.2890034745699111</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.385827795596797</v>
+        <v>0.3998196260908056</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5233416736052642</v>
+        <v>0.4872823077045053</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3823957247986784</v>
+        <v>0.3799014623378668</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3060120047891445</v>
+        <v>0.3075092302693504</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7383,10 +7383,10 @@
         <v>368</v>
       </c>
       <c r="B180" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3752666688007331</v>
+        <v>0.3446208516607657</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3302469047977956</v>
+        <v>0.3379546425352769</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2967174246354413</v>
+        <v>0.2887110450891056</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.3107710956362992</v>
+        <v>0.2865262983478146</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3276613567672378</v>
+        <v>0.3442634014050478</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3246294319614887</v>
+        <v>0.3381117622468598</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7485,10 +7485,10 @@
         <v>380</v>
       </c>
       <c r="B186" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4396145741454752</v>
+        <v>0.4064502625726111</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2296039201069449</v>
+        <v>0.24603566901833</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4452537888677324</v>
+        <v>0.4584906538229266</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3220307115223564</v>
+        <v>0.3139973782775285</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2622628610489271</v>
+        <v>0.281335484188852</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3333252385826292</v>
+        <v>0.345813406846774</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.3953171212648308</v>
+        <v>0.3854822063742863</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4142990556844292</v>
+        <v>0.3979648363933358</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3569450039810287</v>
+        <v>0.3961917596704624</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7638,10 +7638,10 @@
         <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="C195">
-        <v>0.3677333428185096</v>
+        <v>0.3633286648295007</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7655,10 +7655,10 @@
         <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3158192546457703</v>
+        <v>0.3412543813085424</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3003930436653268</v>
+        <v>0.3300905661803299</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5032201000276119</v>
+        <v>0.5106179860619076</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.5557183513315729</v>
+        <v>0.6024647285942177</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3138752153470565</v>
+        <v>0.3281337551964315</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3011058155208427</v>
+        <v>0.2975151923723954</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3507927789568595</v>
+        <v>0.3830219380458117</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.4882460455334763</v>
+        <v>0.5091313939773168</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4710726074455408</v>
+        <v>0.4400202280826854</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4074143844744552</v>
+        <v>0.4387146506373419</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3359423640635127</v>
+        <v>0.3485623958037571</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7842,10 +7842,10 @@
         <v>422</v>
       </c>
       <c r="B207" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5124411532458947</v>
+        <v>0.5493183803966396</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7859,10 +7859,10 @@
         <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C208">
-        <v>0.4206667233040177</v>
+        <v>0.4014993222981846</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.4805478641198995</v>
+        <v>0.4974066534283145</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4164910399310606</v>
+        <v>0.4023849857227825</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.3904900932185079</v>
+        <v>0.422486441792542</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2775985254159323</v>
+        <v>0.2844904508398324</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3374114915382355</v>
+        <v>0.3069363372457801</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3534065708921878</v>
+        <v>0.3715109353969295</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.5829765613662623</v>
+        <v>0.4695602739803728</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3160778824113379</v>
+        <v>0.3303962231774788</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3041674405349387</v>
+        <v>0.3309954884278163</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3627764803280363</v>
+        <v>0.3393313364482444</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8046,10 +8046,10 @@
         <v>446</v>
       </c>
       <c r="B219" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4840476611212454</v>
+        <v>0.4749381041309967</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C220">
-        <v>0.2800038508064276</v>
+        <v>0.2759039799104047</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3429394203915165</v>
+        <v>0.3434825805390539</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.2969033206547682</v>
+        <v>0.3221244140886136</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5211882451545831</v>
+        <v>0.5026533316330004</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3391564456217657</v>
+        <v>0.318543486025801</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3347958353221741</v>
+        <v>0.3571377201531903</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4569601697709951</v>
+        <v>0.4625394882512806</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3329415063551348</v>
+        <v>0.3421718150002956</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.454710585444606</v>
+        <v>0.4725965166364404</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.4785770189281114</v>
+        <v>0.5374742290205313</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8233,10 +8233,10 @@
         <v>468</v>
       </c>
       <c r="B230" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3992034358241452</v>
+        <v>0.362570256718442</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3220934218649285</v>
+        <v>0.3144445449822922</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5731847073553561</v>
+        <v>0.573128077869523</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8284,10 +8284,10 @@
         <v>474</v>
       </c>
       <c r="B233" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C233">
-        <v>0.46070615730883</v>
+        <v>0.4122899558576995</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.3992088512804117</v>
+        <v>0.403162589641927</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4744003064770025</v>
+        <v>0.4667672588807263</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2539989439437317</v>
+        <v>0.2778828590983202</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3298333245475181</v>
+        <v>0.3318729052493475</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.313136943671959</v>
+        <v>0.3454350553362527</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.3950856623596029</v>
+        <v>0.4247478415374827</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8403,10 +8403,10 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3387607104648244</v>
+        <v>0.3412431936718611</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C241">
-        <v>0.2317456401915947</v>
+        <v>0.2278970121759742</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C242">
-        <v>0.3037707415967317</v>
+        <v>0.3042664378137436</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4199849511162295</v>
+        <v>0.4531329967499129</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8471,10 +8471,10 @@
         <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="C244">
-        <v>0.3595552647259219</v>
+        <v>0.3910050155526176</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6051890758740173</v>
+        <v>0.614956823890439</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4415377699548766</v>
+        <v>0.4321984134741917</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4284964013699248</v>
+        <v>0.4271611287638611</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.334069363782976</v>
+        <v>0.3552541102064895</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4323562402776086</v>
+        <v>0.3981172533417957</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3412990949705821</v>
+        <v>0.3086396571898459</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8590,10 +8590,10 @@
         <v>510</v>
       </c>
       <c r="B251" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4575800210305982</v>
+        <v>0.4264267007295922</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4405201560590839</v>
+        <v>0.4192741280351067</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3510436048324433</v>
+        <v>0.3803293146780267</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4567762488332016</v>
+        <v>0.4922778295813283</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.4027300830793713</v>
+        <v>0.3917395486891489</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5408642224119784</v>
+        <v>0.5805217858631857</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3691613163335336</v>
+        <v>0.4081194277633916</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4508551697112859</v>
+        <v>0.4868422699681493</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C259">
-        <v>0.3107624456015211</v>
+        <v>0.3042888148706895</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.3959873174187641</v>
+        <v>0.4102531545018706</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4176503118410154</v>
+        <v>0.45332776386311</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3677797873936203</v>
+        <v>0.3941811725233179</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4638396331595597</v>
+        <v>0.4417794197665414</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.3925096063611809</v>
+        <v>0.41845336798642</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3005700121310368</v>
+        <v>0.3241523528530911</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="C266">
-        <v>0.3134127432889699</v>
+        <v>0.3188021047888844</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
         <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C267">
-        <v>0.2799338332805154</v>
+        <v>0.2738064946696965</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4340644049733743</v>
+        <v>0.4266256405287925</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8896,10 +8896,10 @@
         <v>546</v>
       </c>
       <c r="B269" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3726080628573989</v>
+        <v>0.3868149843878536</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.4984236563451751</v>
+        <v>0.5114512725554951</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.4956716748544643</v>
+        <v>0.5313857195606858</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3265757290334707</v>
+        <v>0.3365842375308938</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.4939168908470985</v>
+        <v>0.497058117166766</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3370438725192193</v>
+        <v>0.3341229387900291</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.242848586448791</v>
+        <v>0.2441260186234964</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3287771108937658</v>
+        <v>0.3290318299206622</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C277">
-        <v>0.3986484165491903</v>
+        <v>0.3734936930587524</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4442108405517486</v>
+        <v>0.4442457709807539</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5222189641152256</v>
+        <v>0.5514500946871475</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4556678899667322</v>
+        <v>0.4584004138033197</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.355217477962789</v>
+        <v>0.3826132256959259</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3563740472403016</v>
+        <v>0.3674224481796012</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3811991410588477</v>
+        <v>0.3628335381347704</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3184993508819693</v>
+        <v>0.3078922262259856</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2652211606589704</v>
+        <v>0.2605911206430679</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3119246358672181</v>
+        <v>0.2819693786390272</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9202,10 +9202,10 @@
         <v>582</v>
       </c>
       <c r="B287" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4804577118728801</v>
+        <v>0.4523776974636924</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C288">
-        <v>0.2373935039379387</v>
+        <v>0.237906226626616</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3632875699328729</v>
+        <v>0.344618153287586</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3542864061773519</v>
+        <v>0.3141716480633512</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4226088052917317</v>
+        <v>0.4020321308598012</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C292">
-        <v>0.4640854373558982</v>
+        <v>0.4579627585556948</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5675649386173612</v>
+        <v>0.5934857220745682</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3727348390891146</v>
+        <v>0.3756162335947532</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3486649656121441</v>
+        <v>0.348815527396435</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C296">
-        <v>0.2688590157602789</v>
+        <v>0.3144724749476119</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4722928449377478</v>
+        <v>0.4510379228470904</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3771692232579172</v>
+        <v>0.3876331248097032</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9406,10 +9406,10 @@
         <v>606</v>
       </c>
       <c r="B299" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2894454737161057</v>
+        <v>0.2869509816327896</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3352277829528975</v>
+        <v>0.335797806610426</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3545397630454251</v>
+        <v>0.3426963298292768</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9457,10 +9457,10 @@
         <v>612</v>
       </c>
       <c r="B302" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C302">
-        <v>0.5066608218355024</v>
+        <v>0.527957238164429</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.326654952648398</v>
+        <v>0.3039403432114322</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2695210676715539</v>
+        <v>0.2870774828283357</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9508,10 +9508,10 @@
         <v>618</v>
       </c>
       <c r="B305" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4459836434887848</v>
+        <v>0.4396259546149008</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.3706423484553656</v>
+        <v>0.3894052996752283</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4511128956350159</v>
+        <v>0.4429290259968005</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3542294494552481</v>
+        <v>0.3905900028850289</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9576,10 +9576,10 @@
         <v>626</v>
       </c>
       <c r="B309" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2607006726274055</v>
+        <v>0.268938655762435</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3772726025638357</v>
+        <v>0.384064243631789</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3328383562750326</v>
+        <v>0.3443241195802385</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9627,10 +9627,10 @@
         <v>632</v>
       </c>
       <c r="B312" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2839138586220505</v>
+        <v>0.2774239647709135</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9644,10 +9644,10 @@
         <v>634</v>
       </c>
       <c r="B313" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C313">
-        <v>0.2876277501215084</v>
+        <v>0.3255699158339491</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3048262668382279</v>
+        <v>0.3149834400035742</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9678,10 +9678,10 @@
         <v>638</v>
       </c>
       <c r="B315" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4854472674533629</v>
+        <v>0.487274352810498</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3778233278909814</v>
+        <v>0.3880297541837925</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.4771626656903982</v>
+        <v>0.5217389717569033</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.519186076437425</v>
+        <v>0.5272114726866903</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.310131942789811</v>
+        <v>0.3365627344387399</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C320">
-        <v>0.2640039290780005</v>
+        <v>0.2651441355563188</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3160150965791196</v>
+        <v>0.3282764486548599</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.4163937400582384</v>
+        <v>0.3535080478340162</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3794874612390233</v>
+        <v>0.3782953871258739</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9831,10 +9831,10 @@
         <v>656</v>
       </c>
       <c r="B324" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C324">
-        <v>0.4200607447816606</v>
+        <v>0.3885097540543505</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9848,10 +9848,10 @@
         <v>658</v>
       </c>
       <c r="B325" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C325">
-        <v>0.2555714119321391</v>
+        <v>0.2335660182229677</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9865,10 +9865,10 @@
         <v>660</v>
       </c>
       <c r="B326" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3688386645089898</v>
+        <v>0.3679684382793482</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9882,10 +9882,10 @@
         <v>662</v>
       </c>
       <c r="B327" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3601290312485365</v>
+        <v>0.3389036850708688</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2668302370347232</v>
+        <v>0.2797956038308701</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C329">
-        <v>0.293510677131512</v>
+        <v>0.3045917571674812</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>6</v>
       </c>
       <c r="C330">
-        <v>0.3017220957770312</v>
+        <v>0.3025549529733922</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3493531240495946</v>
+        <v>0.3872855742511495</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3512256151244637</v>
+        <v>0.3509833118276986</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4375394647594506</v>
+        <v>0.4677073517174425</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="C334">
-        <v>0.2914621540629993</v>
+        <v>0.28399218385652</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10018,10 +10018,10 @@
         <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C335">
-        <v>0.3316577693526703</v>
+        <v>0.3427864273599877</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>15</v>
       </c>
       <c r="C336">
-        <v>0.2733770562721901</v>
+        <v>0.297622436162364</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10052,10 +10052,10 @@
         <v>682</v>
       </c>
       <c r="B337" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4949392360812387</v>
+        <v>0.4655091770048483</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.2772698589991967</v>
+        <v>0.281652527267989</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.444113147349091</v>
+        <v>0.4437454581333809</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.2940259544421459</v>
+        <v>0.307751368870076</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2533194421469254</v>
+        <v>0.2939067461866287</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2673253646195596</v>
+        <v>0.2591863580363889</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3752601836895709</v>
+        <v>0.3952269558639611</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2883440109293667</v>
+        <v>0.2887671597103184</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3503368161918288</v>
+        <v>0.3545688155610214</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3594581375815226</v>
+        <v>0.330005477404774</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3233114713158131</v>
+        <v>0.3364481960584361</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.2890978900775688</v>
+        <v>0.3134115301868616</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4730147866183658</v>
+        <v>0.4732114638791179</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3473803148925736</v>
+        <v>0.3576303575126556</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C351">
-        <v>0.2882281248141371</v>
+        <v>0.2658039462359348</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3837232641275561</v>
+        <v>0.3926118972002886</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3665473402099665</v>
+        <v>0.3875947563155628</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2682162658675827</v>
+        <v>0.2790484086711113</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3232259989513972</v>
+        <v>0.353049637805116</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10375,10 +10375,10 @@
         <v>720</v>
       </c>
       <c r="B356" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C356">
-        <v>0.2982058207074127</v>
+        <v>0.3058475359999432</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4131283162287204</v>
+        <v>0.3918903345497604</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3277095170544023</v>
+        <v>0.3104777775224267</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10426,10 +10426,10 @@
         <v>726</v>
       </c>
       <c r="B359" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4743359912660757</v>
+        <v>0.472149610386606</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4531798907452236</v>
+        <v>0.471449863300955</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.2949997850720203</v>
+        <v>0.3106907591643868</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3293717115019485</v>
+        <v>0.354304262375831</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10494,10 +10494,10 @@
         <v>734</v>
       </c>
       <c r="B363" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2692207180508231</v>
+        <v>0.2913408036337486</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.2880721941643493</v>
+        <v>0.3185117735673548</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.298408705347951</v>
+        <v>0.3010255724690242</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2497957348604209</v>
+        <v>0.2626800854961652</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.2744112015704843</v>
+        <v>0.3019769509201753</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3146379352323028</v>
+        <v>0.3085227585951494</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4311833279013857</v>
+        <v>0.4850916583793015</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3339321997632673</v>
+        <v>0.3304459402927414</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.457000547776179</v>
+        <v>0.4432694298194241</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3139244690612099</v>
+        <v>0.351787070270293</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4016998679538646</v>
+        <v>0.4238707963363504</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4508932740026436</v>
+        <v>0.46944822956528</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4205472376102995</v>
+        <v>0.4532035521879832</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3744315707517908</v>
+        <v>0.3620914139994278</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4575110359523363</v>
+        <v>0.4542538021769481</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.2854427505294029</v>
+        <v>0.305977767600755</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3109881567761955</v>
+        <v>0.3519148065633409</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3498400064800496</v>
+        <v>0.3497739963191122</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4325416029236621</v>
+        <v>0.435494050603664</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.342979563882755</v>
+        <v>0.320779217011703</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.340819917336656</v>
+        <v>0.3760724212485425</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10851,10 +10851,10 @@
         <v>776</v>
       </c>
       <c r="B384" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4623059257031458</v>
+        <v>0.4316680878241635</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3794127790788834</v>
+        <v>0.3894961149701471</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.2861634175048328</v>
+        <v>0.3097982030072141</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4348209184989677</v>
+        <v>0.4236598681346773</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10919,10 +10919,10 @@
         <v>784</v>
       </c>
       <c r="B388" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3581176470082595</v>
+        <v>0.3543217471293787</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3699890517086399</v>
+        <v>0.3397174970538442</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3285157443166593</v>
+        <v>0.3213167795007851</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3291343280109355</v>
+        <v>0.3403698392516281</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3338912746419109</v>
+        <v>0.302369767306986</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.411106741502532</v>
+        <v>0.400876409051463</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3487632027536919</v>
+        <v>0.3618649629551463</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3879275141055887</v>
+        <v>0.3947114518435716</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.4011359812125906</v>
+        <v>0.3884287749037924</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3476166044921737</v>
+        <v>0.3630286146464676</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4613370369560668</v>
+        <v>0.4718054196047277</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3182278888153661</v>
+        <v>0.3468307600215131</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3210529260378626</v>
+        <v>0.3341573878869074</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4156225416643691</v>
+        <v>0.4218735818236939</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3731333959319046</v>
+        <v>0.389886371807409</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2941077965417614</v>
+        <v>0.2750616846604813</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C404">
-        <v>0.3081539976859192</v>
+        <v>0.2980664116693748</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.3996983382055906</v>
+        <v>0.4176963758067991</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C406">
-        <v>0.4859412585291888</v>
+        <v>0.4769835319568453</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3584082504198747</v>
+        <v>0.3660565556394468</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4401228139827381</v>
+        <v>0.4723920170558493</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4804340754604554</v>
+        <v>0.46530098832342</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3049262793484668</v>
+        <v>0.3132977543183315</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3095732616923019</v>
+        <v>0.3146291275862148</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4443657507582527</v>
+        <v>0.4516732496113741</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2576482081479453</v>
+        <v>0.2582808251676272</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11361,10 +11361,10 @@
         <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3234955829063349</v>
+        <v>0.3122905600521406</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3193477744298099</v>
+        <v>0.3411223656042475</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3355325127139998</v>
+        <v>0.3778326212318529</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.3027813455024205</v>
+        <v>0.2567095463434271</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C418">
-        <v>0.3094023530280534</v>
+        <v>0.2991045422511011</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3694267767677678</v>
+        <v>0.3450264823743769</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11463,10 +11463,10 @@
         <v>848</v>
       </c>
       <c r="B420" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4688166000705382</v>
+        <v>0.3976939238497436</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11480,10 +11480,10 @@
         <v>850</v>
       </c>
       <c r="B421" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C421">
-        <v>0.4117752185081852</v>
+        <v>0.3959417500801545</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.366038851921885</v>
+        <v>0.3520281861243801</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11514,10 +11514,10 @@
         <v>854</v>
       </c>
       <c r="B423" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C423">
-        <v>0.463977077392135</v>
+        <v>0.463445543909917</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.303403817122771</v>
+        <v>0.3088808598099239</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3249436074402846</v>
+        <v>0.3305754523857272</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3496751802417434</v>
+        <v>0.3476568381440197</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2455558197983442</v>
+        <v>0.2702570428058927</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2684000043121693</v>
+        <v>0.2737844691622493</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3537708066663069</v>
+        <v>0.3213524049202692</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.316864507443803</v>
+        <v>0.3437893019589151</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.2767977092770992</v>
+        <v>0.2773257841111456</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3114669533368716</v>
+        <v>0.3237906981070713</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3132443831320026</v>
+        <v>0.3214009798989462</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3395972375597331</v>
+        <v>0.350769242946087</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3836244789145654</v>
+        <v>0.3543430364029925</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3249588538413754</v>
+        <v>0.335449257588734</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3148141271372883</v>
+        <v>0.3057093412304472</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3482049558521511</v>
+        <v>0.3427196684623486</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.308606027367922</v>
+        <v>0.3485307435733862</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3326482589953794</v>
+        <v>0.3460633612664038</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.2956892125158121</v>
+        <v>0.303448409949237</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3414386405964547</v>
+        <v>0.2820971349507029</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.2915133326156629</v>
+        <v>0.292127574809511</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3219259453633753</v>
+        <v>0.3283232639413382</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3457842390289156</v>
+        <v>0.3466993842650783</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11905,10 +11905,10 @@
         <v>900</v>
       </c>
       <c r="B446" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3658239778448735</v>
+        <v>0.346493750452994</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2870762860558245</v>
+        <v>0.2868521198350029</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3805403522123703</v>
+        <v>0.3546227763538569</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3613014331518368</v>
+        <v>0.3842232596575464</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11973,10 +11973,10 @@
         <v>908</v>
       </c>
       <c r="B450" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3761121892726185</v>
+        <v>0.3767835943069194</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11990,10 +11990,10 @@
         <v>910</v>
       </c>
       <c r="B451" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4356342754321482</v>
+        <v>0.4103124187310438</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2863924951842754</v>
+        <v>0.2751670480136385</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3545003771340144</v>
+        <v>0.3407868291735076</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2654534476965363</v>
+        <v>0.2848192834126454</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3059385034928689</v>
+        <v>0.328420313232577</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3257217433655537</v>
+        <v>0.3491408372236749</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3395838144923476</v>
+        <v>0.3382818591695884</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3419400172423726</v>
+        <v>0.3896068589898339</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3325064306929535</v>
+        <v>0.3619765032418573</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12143,10 +12143,10 @@
         <v>928</v>
       </c>
       <c r="B460" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3389510423598189</v>
+        <v>0.3337461099955391</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3104779930363459</v>
+        <v>0.3191972529567833</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.300345614963857</v>
+        <v>0.3412032567324592</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3132067386031935</v>
+        <v>0.2932224969267514</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3813996972495141</v>
+        <v>0.3924267232886226</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12228,10 +12228,10 @@
         <v>938</v>
       </c>
       <c r="B465" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C465">
-        <v>0.4116032161601315</v>
+        <v>0.4021937469954971</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5141352885291609</v>
+        <v>0.5172983609306038</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4254270178505236</v>
+        <v>0.4577163204936925</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3879884817252552</v>
+        <v>0.3875823234592799</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2858926998373261</v>
+        <v>0.2921053081342213</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C470">
-        <v>0.3228493182258328</v>
+        <v>0.2962871945685051</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12330,10 +12330,10 @@
         <v>950</v>
       </c>
       <c r="B471" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C471">
-        <v>0.3121708259884814</v>
+        <v>0.3029646007919119</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3363111132947602</v>
+        <v>0.3331765481242102</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C473">
-        <v>0.3236829314396276</v>
+        <v>0.3114185478835853</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.357124202015469</v>
+        <v>0.3688594187369839</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3661208237765902</v>
+        <v>0.3338236873195197</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3106348040797658</v>
+        <v>0.3466765930692349</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3322557425407986</v>
+        <v>0.3468983487851426</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4069233744245945</v>
+        <v>0.3871306997051409</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12466,10 +12466,10 @@
         <v>966</v>
       </c>
       <c r="B479" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4087343913159378</v>
+        <v>0.4144432164146241</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4239593908579146</v>
+        <v>0.4495823453134792</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12500,10 +12500,10 @@
         <v>970</v>
       </c>
       <c r="B481" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3976130475311022</v>
+        <v>0.4028693007571467</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3144277293149703</v>
+        <v>0.305922610474118</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3087636382678662</v>
+        <v>0.2968746017856752</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12551,10 +12551,10 @@
         <v>976</v>
       </c>
       <c r="B484" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3867133918182866</v>
+        <v>0.3863191907966307</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3361460032930892</v>
+        <v>0.350926851453511</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3800434720651185</v>
+        <v>0.3862391353445343</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12602,10 +12602,10 @@
         <v>982</v>
       </c>
       <c r="B487" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4666963679205031</v>
+        <v>0.477858653985512</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3440194683773689</v>
+        <v>0.3148118363945324</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.448707656909423</v>
+        <v>0.474211819429071</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.307320212582097</v>
+        <v>0.3075769661170859</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C491">
-        <v>0.2682393889321275</v>
+        <v>0.2735333442169051</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4656222467138824</v>
+        <v>0.4860642964324082</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.3126613475336949</v>
+        <v>0.2859439464256592</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12721,10 +12721,10 @@
         <v>996</v>
       </c>
       <c r="B494" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3222878577681964</v>
+        <v>0.3353173709054332</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12738,10 +12738,10 @@
         <v>998</v>
       </c>
       <c r="B495" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5103703485795215</v>
+        <v>0.5249105308162485</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4566742329129653</v>
+        <v>0.4703896512579094</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.348478062330174</v>
+        <v>0.3314449921645754</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6634938074911064</v>
+        <v>0.670178350950892</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3699123497946487</v>
+        <v>0.3393934588214377</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3779933756920962</v>
+        <v>0.4110912622229522</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3375835989361704</v>
+        <v>0.3840866600840658</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5647288494257764</v>
+        <v>0.5769007238637928</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3389985622684376</v>
+        <v>0.3560337852103868</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3071333654379391</v>
+        <v>0.3244722825324076</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4348699633109686</v>
+        <v>0.4287695454022775</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4315807374220208</v>
+        <v>0.5003604898679385</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.3051695206860697</v>
+        <v>0.3052769719659477</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3227982277770536</v>
+        <v>0.3131230861719746</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4497241463186884</v>
+        <v>0.4869926786296521</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3623329891027147</v>
+        <v>0.3653134116272648</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13010,10 +13010,10 @@
         <v>1030</v>
       </c>
       <c r="B511" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3946681385755655</v>
+        <v>0.3499345335998894</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3003913493664003</v>
+        <v>0.299222119551234</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3757929829421549</v>
+        <v>0.3636631098991319</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13061,10 +13061,10 @@
         <v>1036</v>
       </c>
       <c r="B514" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C514">
-        <v>0.4373115180680894</v>
+        <v>0.4202816710201673</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4886350202033946</v>
+        <v>0.4635218890724219</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C516">
-        <v>0.3056982759068027</v>
+        <v>0.315897184415829</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3116078091599512</v>
+        <v>0.3355218515279798</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.2941454757882516</v>
+        <v>0.3258557514945978</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13146,10 +13146,10 @@
         <v>1046</v>
       </c>
       <c r="B519" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C519">
-        <v>0.498270569268045</v>
+        <v>0.5065692616865147</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3124745575050306</v>
+        <v>0.3249111220567935</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.301417612709649</v>
+        <v>0.2998178029324541</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3478848743648147</v>
+        <v>0.3599507269450423</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4307467071309138</v>
+        <v>0.4290743312332251</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2863429778799398</v>
+        <v>0.2780579738100629</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13248,10 +13248,10 @@
         <v>1058</v>
       </c>
       <c r="B525" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4097413954941316</v>
+        <v>0.4074768608786564</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13265,10 +13265,10 @@
         <v>1060</v>
       </c>
       <c r="B526" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4508613177695499</v>
+        <v>0.4235319999220581</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3552238796663157</v>
+        <v>0.3622294388898334</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4446194726687943</v>
+        <v>0.4344373080305042</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3353912256631994</v>
+        <v>0.3361369759692363</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13333,10 +13333,10 @@
         <v>1068</v>
       </c>
       <c r="B530" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4980139469894899</v>
+        <v>0.4928787779482044</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13350,10 +13350,10 @@
         <v>1070</v>
       </c>
       <c r="B531" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5731371479519929</v>
+        <v>0.5608389947140966</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C532">
-        <v>0.2974068552537372</v>
+        <v>0.27397455944736</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4054317276840516</v>
+        <v>0.4325451622544554</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3059107523746352</v>
+        <v>0.3212987078058976</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3070947420535514</v>
+        <v>0.3108902729732357</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3009313791253835</v>
+        <v>0.3042023064884808</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3951853156407599</v>
+        <v>0.3649253928754086</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2841611680661826</v>
+        <v>0.2818816105329868</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3123750966785598</v>
+        <v>0.2897339696083849</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2699914685758585</v>
+        <v>0.283673563131618</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4279963729279818</v>
+        <v>0.4312447391153837</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13537,10 +13537,10 @@
         <v>1092</v>
       </c>
       <c r="B542" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C542">
-        <v>0.4124676454941053</v>
+        <v>0.3943205444889283</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3852204945794201</v>
+        <v>0.3980498065640394</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3595741347269353</v>
+        <v>0.3337048740611942</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2620874355404834</v>
+        <v>0.2731384927042435</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3374719779447966</v>
+        <v>0.3103410940075775</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2633908789781597</v>
+        <v>0.2723393751093193</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.4763852464108229</v>
+        <v>0.3593415375718323</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.3993771569905746</v>
+        <v>0.37954399391003</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3293661791462943</v>
+        <v>0.354406958014482</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2740642347368503</v>
+        <v>0.2549143642234157</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13959,10 +13959,10 @@
         <v>1158</v>
       </c>
       <c r="B570" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2918862040351888</v>
+        <v>0.2768943425168894</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2791307549672933</v>
+        <v>0.2725979073406502</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.3276306167407494</v>
+        <v>0.2640958695870804</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.2734433106409772</v>
+        <v>0.3084875238406498</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14027,10 +14027,10 @@
         <v>1166</v>
       </c>
       <c r="B574" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3144858145232893</v>
+        <v>0.3091201595645839</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.316446731985193</v>
+        <v>0.3458893287699538</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3779853893220506</v>
+        <v>0.3815270814863027</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2873615817589585</v>
+        <v>0.2632726086524325</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3661427605043753</v>
+        <v>0.3691893160583841</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3026029316309243</v>
+        <v>0.3030609013061132</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3527830670218301</v>
+        <v>0.3439847634047299</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4483751640247601</v>
+        <v>0.4650310118704535</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.2977054365978619</v>
+        <v>0.2988089748829916</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3385987720676739</v>
+        <v>0.3541261172558095</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14197,10 +14197,10 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3095734456437048</v>
+        <v>0.2928596265571694</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.382286176167086</v>
+        <v>0.404041178651959</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2877378989150525</v>
+        <v>0.2912235811596577</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2927306938321464</v>
+        <v>0.2602665155854976</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.2762020549455292</v>
+        <v>0.3076361250384443</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14282,10 +14282,10 @@
         <v>1196</v>
       </c>
       <c r="B589" t="s">
-        <v>45</v>
+        <v>1143</v>
       </c>
       <c r="C589">
-        <v>0.3297268961496782</v>
+        <v>0.3185058920204895</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4304208327062033</v>
+        <v>0.3584194851952392</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.4459454025124768</v>
+        <v>0.5386527158750367</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3529844979502992</v>
+        <v>0.4147764446980161</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.509544815769169</v>
+        <v>0.6600179068529647</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.3993588829939644</v>
+        <v>0.4162173221884855</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14384,10 +14384,10 @@
         <v>1208</v>
       </c>
       <c r="B595" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C595">
-        <v>0.3516706212735022</v>
+        <v>0.2886170017664208</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.3911934330228708</v>
+        <v>0.4125627567941312</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3605433099045404</v>
+        <v>0.2927833821005742</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2609674210650417</v>
+        <v>0.2713603587303414</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.320459367920903</v>
+        <v>0.2573108571855422</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14469,10 +14469,10 @@
         <v>1218</v>
       </c>
       <c r="B600" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C600">
-        <v>0.2818074552975855</v>
+        <v>0.280536158939665</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2780841627919294</v>
+        <v>0.2378708110856944</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3740736997754755</v>
+        <v>0.3519809046128113</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2987208912610551</v>
+        <v>0.2803754239084807</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3472135920546724</v>
+        <v>0.2773048816442821</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14554,10 +14554,10 @@
         <v>1228</v>
       </c>
       <c r="B605" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2799055671201063</v>
+        <v>0.2694091324479843</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14571,10 +14571,10 @@
         <v>1230</v>
       </c>
       <c r="B606" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3837870891755099</v>
+        <v>0.3423979308474982</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.2908990956206018</v>
+        <v>0.3083839977314169</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.2998826696600439</v>
+        <v>0.269707207180606</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2810675698488048</v>
+        <v>0.2724715047043063</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C610">
-        <v>0.238967290585352</v>
+        <v>0.2637866490650348</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14656,10 +14656,10 @@
         <v>1240</v>
       </c>
       <c r="B611" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4635796867450719</v>
+        <v>0.4503016244124671</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14673,10 +14673,10 @@
         <v>1242</v>
       </c>
       <c r="B612" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3760980985884191</v>
+        <v>0.2991934768493403</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3393845087228324</v>
+        <v>0.3305955627735175</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.3785676708399713</v>
+        <v>0.4051956473138253</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14724,10 +14724,10 @@
         <v>1248</v>
       </c>
       <c r="B615" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C615">
-        <v>0.314302555760871</v>
+        <v>0.314369305794523</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.3800180563950039</v>
+        <v>0.4170232544888506</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3120663679917381</v>
+        <v>0.3177706232780887</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.2852479809450488</v>
+        <v>0.3466168647459811</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.397268705897574</v>
+        <v>0.4401220170979919</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C620">
-        <v>0.286077132805149</v>
+        <v>0.3159239752156625</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3354485076469418</v>
+        <v>0.3429331846675638</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C622">
-        <v>0.2272256174360431</v>
+        <v>0.2711593240056192</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14860,78 +14860,78 @@
         <v>1265</v>
       </c>
       <c r="B623" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C623">
-        <v>0.228096792612476</v>
+        <v>0.2019897684965157</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
       </c>
       <c r="E623" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="624" spans="1:5">
       <c r="A624" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B624" t="s">
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2800959684707632</v>
+        <v>0.2924823598400101</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
       </c>
       <c r="E624" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="625" spans="1:5">
       <c r="A625" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B625" t="s">
-        <v>1266</v>
+        <v>10</v>
       </c>
       <c r="C625">
-        <v>0.257152478242327</v>
+        <v>0.2491159187758467</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
       </c>
       <c r="E625" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="626" spans="1:5">
       <c r="A626" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B626" t="s">
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3029059441613101</v>
+        <v>0.3192464625487216</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
       </c>
       <c r="E626" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="627" spans="1:5">
       <c r="A627" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B627" t="s">
         <v>1274</v>
       </c>
-      <c r="B627" t="s">
-        <v>1266</v>
-      </c>
       <c r="C627">
-        <v>0.3213496953851631</v>
+        <v>0.281101446020071</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C628">
-        <v>0.2738081875390032</v>
+        <v>0.2287450870632596</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C629">
-        <v>0.225043147235599</v>
+        <v>0.2683592160592963</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14979,10 +14979,10 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C630">
-        <v>0.3584233611975108</v>
+        <v>0.3242185529796044</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14996,10 +14996,10 @@
         <v>1282</v>
       </c>
       <c r="B631" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C631">
-        <v>0.4038523107483728</v>
+        <v>0.3081328527891776</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15013,10 +15013,10 @@
         <v>1284</v>
       </c>
       <c r="B632" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C632">
-        <v>0.456433072002846</v>
+        <v>0.3832346088366407</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2697796536135059</v>
+        <v>0.2636495911136129</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.3396989488839469</v>
+        <v>0.3807730747996486</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15064,10 +15064,10 @@
         <v>1290</v>
       </c>
       <c r="B635" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C635">
-        <v>0.457670954351715</v>
+        <v>0.4133253740157806</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3543499519479846</v>
+        <v>0.39247961345539</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C637">
-        <v>0.3233945927853522</v>
+        <v>0.2787830016665964</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15115,10 +15115,10 @@
         <v>1296</v>
       </c>
       <c r="B638" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C638">
-        <v>0.4910339184352084</v>
+        <v>0.4054888617340373</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3211994718242165</v>
+        <v>0.3568549897621376</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2688851536684454</v>
+        <v>0.2883214564347477</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C641">
-        <v>0.2783340923618423</v>
+        <v>0.2633567289020611</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15183,10 +15183,10 @@
         <v>1304</v>
       </c>
       <c r="B642" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C642">
-        <v>0.3315345025644301</v>
+        <v>0.2741080245293495</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3054083075764442</v>
+        <v>0.2967292024074723</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2927384534707999</v>
+        <v>0.2732174525992443</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15234,10 +15234,10 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2533652032340521</v>
+        <v>0.2520746588551162</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3415006417050697</v>
+        <v>0.35307879544014</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C647">
-        <v>0.3096016695968161</v>
+        <v>0.292104403395063</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2542895437904842</v>
+        <v>0.2685648215429726</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.3032723156267034</v>
+        <v>0.3106981120762746</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C650">
-        <v>0.2721296242891634</v>
+        <v>0.2585534164255819</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.3001977580702927</v>
+        <v>0.2948235921724291</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,15 +15379,15 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,31 +15395,31 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="B8">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2731384927042435</v>
+        <v>0.2888287818295125</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3103410940075775</v>
+        <v>0.3322795898775816</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2723393751093193</v>
+        <v>0.2764596601169398</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3593415375718323</v>
+        <v>0.3719705089548241</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.37954399391003</v>
+        <v>0.4012424141887613</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.354406958014482</v>
+        <v>0.3701706072983576</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2549143642234157</v>
+        <v>0.2627581182322579</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2768943425168894</v>
+        <v>0.2891033100775696</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2725979073406502</v>
+        <v>0.2821519833076478</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.2640958695870804</v>
+        <v>0.2769815524308674</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3084875238406498</v>
+        <v>0.3260040773520119</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3091201595645839</v>
+        <v>0.3226331502921406</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3458893287699538</v>
+        <v>0.3648558626033117</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3815270814863027</v>
+        <v>0.3913235884134174</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2632726086524325</v>
+        <v>0.2842886423110846</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3691893160583841</v>
+        <v>0.3872165915096974</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3030609013061132</v>
+        <v>0.3182743592282397</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3439847634047299</v>
+        <v>0.3198066122624188</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4650310118704535</v>
+        <v>0.4902760428457153</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.2988089748829916</v>
+        <v>0.3098994519649725</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3541261172558095</v>
+        <v>0.3733645298496815</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.2928596265571694</v>
+        <v>0.304587911814411</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.404041178651959</v>
+        <v>0.4237076938251195</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2912235811596577</v>
+        <v>0.3155585383051112</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2602665155854976</v>
+        <v>0.2580066296735423</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3076361250384443</v>
+        <v>0.3361781406209469</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>1143</v>
       </c>
       <c r="C589">
-        <v>0.3185058920204895</v>
+        <v>0.336044880369905</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.3584194851952392</v>
+        <v>0.3663674537166403</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5386527158750367</v>
+        <v>0.5416924648469769</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.4147764446980161</v>
+        <v>0.4123993579551783</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6600179068529647</v>
+        <v>0.6555197834409716</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4162173221884855</v>
+        <v>0.4378460535704081</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>1143</v>
       </c>
       <c r="C595">
-        <v>0.2886170017664208</v>
+        <v>0.304238741536642</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4125627567941312</v>
+        <v>0.4481575699686549</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.2927833821005742</v>
+        <v>0.3078256921596347</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2713603587303414</v>
+        <v>0.2404176243974193</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2573108571855422</v>
+        <v>0.2645273749686199</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14469,10 +14469,10 @@
         <v>1218</v>
       </c>
       <c r="B600" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.280536158939665</v>
+        <v>0.2770134524450406</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2378708110856944</v>
+        <v>0.2474132824246504</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3519809046128113</v>
+        <v>0.3607201683666747</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2803754239084807</v>
+        <v>0.2865655447165862</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.2773048816442821</v>
+        <v>0.2938105524513625</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2694091324479843</v>
+        <v>0.27907788077766</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3423979308474982</v>
+        <v>0.3580318771814169</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3083839977314169</v>
+        <v>0.3256800730901381</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.269707207180606</v>
+        <v>0.2937079130823276</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2724715047043063</v>
+        <v>0.2856797297946881</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2637866490650348</v>
+        <v>0.2429642091301902</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4503016244124671</v>
+        <v>0.4577466515440454</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.2991934768493403</v>
+        <v>0.3032056080094967</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3305955627735175</v>
+        <v>0.3445324914796333</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4051956473138253</v>
+        <v>0.4273298483406441</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14724,10 +14724,10 @@
         <v>1248</v>
       </c>
       <c r="B615" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.314369305794523</v>
+        <v>0.3302704028439839</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4170232544888506</v>
+        <v>0.4388612038367041</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3177706232780887</v>
+        <v>0.3387636535336066</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3466168647459811</v>
+        <v>0.3215542996688102</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4401220170979919</v>
+        <v>0.4575209350394632</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14812,7 +14812,7 @@
         <v>6</v>
       </c>
       <c r="C620">
-        <v>0.3159239752156625</v>
+        <v>0.3104029982406734</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3429331846675638</v>
+        <v>0.3344987369481774</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>6</v>
       </c>
       <c r="C622">
-        <v>0.2711593240056192</v>
+        <v>0.2711105195139781</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14863,7 +14863,7 @@
         <v>15</v>
       </c>
       <c r="C623">
-        <v>0.2019897684965157</v>
+        <v>0.1998650128147459</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2924823598400101</v>
+        <v>0.2897594197377535</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14897,7 +14897,7 @@
         <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2491159187758467</v>
+        <v>0.2436249891084367</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3192464625487216</v>
+        <v>0.3103934258040722</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1274</v>
       </c>
       <c r="C627">
-        <v>0.281101446020071</v>
+        <v>0.2811903929356518</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>6</v>
       </c>
       <c r="C628">
-        <v>0.2287450870632596</v>
+        <v>0.2167647871252837</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>6</v>
       </c>
       <c r="C629">
-        <v>0.2683592160592963</v>
+        <v>0.265397913992652</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1274</v>
       </c>
       <c r="C630">
-        <v>0.3242185529796044</v>
+        <v>0.293666246412662</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1274</v>
       </c>
       <c r="C631">
-        <v>0.3081328527891776</v>
+        <v>0.3052227366862181</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1274</v>
       </c>
       <c r="C632">
-        <v>0.3832346088366407</v>
+        <v>0.3789411780583819</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2636495911136129</v>
+        <v>0.2604602991478561</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.3807730747996486</v>
+        <v>0.3733070460900481</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1274</v>
       </c>
       <c r="C635">
-        <v>0.4133253740157806</v>
+        <v>0.401939843668326</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.39247961345539</v>
+        <v>0.384706885807842</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>15</v>
       </c>
       <c r="C637">
-        <v>0.2787830016665964</v>
+        <v>0.2688666004105387</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1274</v>
       </c>
       <c r="C638">
-        <v>0.4054888617340373</v>
+        <v>0.4059303674170687</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3568549897621376</v>
+        <v>0.3509843947032604</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2883214564347477</v>
+        <v>0.2825080544759188</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>15</v>
       </c>
       <c r="C641">
-        <v>0.2633567289020611</v>
+        <v>0.2549091824216865</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1274</v>
       </c>
       <c r="C642">
-        <v>0.2741080245293495</v>
+        <v>0.2719646899842941</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.2967292024074723</v>
+        <v>0.2914348283479374</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2732174525992443</v>
+        <v>0.264832382107491</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2520746588551162</v>
+        <v>0.2484083793559056</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.35307879544014</v>
+        <v>0.3365939816540054</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>6</v>
       </c>
       <c r="C647">
-        <v>0.292104403395063</v>
+        <v>0.2877847868598161</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2685648215429726</v>
+        <v>0.2607515713142328</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.3106981120762746</v>
+        <v>0.3028602240440963</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>6</v>
       </c>
       <c r="C650">
-        <v>0.2585534164255819</v>
+        <v>0.2571398045357967</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.2948235921724291</v>
+        <v>0.2892728605372195</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2861136619684696</v>
+        <v>0.2882140268243685</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4244600019068437</v>
+        <v>0.424925600778397</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3883263223309518</v>
+        <v>0.3903625944507353</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3203165626118626</v>
+        <v>0.3222960531988727</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3672823498225658</v>
+        <v>0.3684935791535398</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.2894188262842786</v>
+        <v>0.2914272737455451</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3436478907024805</v>
+        <v>0.3457033830922796</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3068564098264016</v>
+        <v>0.3085658486491382</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3419190169819784</v>
+        <v>0.3440359754793982</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2365624300929078</v>
+        <v>0.2381712079908356</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.3863311756245</v>
+        <v>0.3880716049425764</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.2849147063794257</v>
+        <v>0.2863195390203992</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3629465736558813</v>
+        <v>0.3647212543954171</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3482010779662978</v>
+        <v>0.3490478363797349</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3181361481180126</v>
+        <v>0.3202655669676484</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>0.2828756880254554</v>
+        <v>0.2849520976585044</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3144865619517914</v>
+        <v>0.3155553211841251</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4385165461202119</v>
+        <v>0.4354140120157834</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3983236681891718</v>
+        <v>0.3995861048217506</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4275915522253093</v>
+        <v>0.4286775218518142</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3189457939618349</v>
+        <v>0.3210682702968278</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.38233403747561</v>
+        <v>0.3833120166834394</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3296308344864835</v>
+        <v>0.3316736935417304</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.5914225481423456</v>
+        <v>0.5925807421895093</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3213711217749676</v>
+        <v>0.3224958666040308</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2853612406948791</v>
+        <v>0.287334125573678</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3166711537639034</v>
+        <v>0.3176816154208367</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4723371418438614</v>
+        <v>0.4682545718556896</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3791339473693786</v>
+        <v>0.3815463568095588</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4332990973851951</v>
+        <v>0.4353340428419675</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.3930012298671672</v>
+        <v>0.3944016743903546</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3851622492261616</v>
+        <v>0.3874284500984028</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3256855921164982</v>
+        <v>0.3270369982420012</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4367476546473292</v>
+        <v>0.4395368105678893</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="C36">
-        <v>0.2275722004655827</v>
+        <v>0.2261854244905496</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.272876092351075</v>
+        <v>0.2742291808267222</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3113558885968452</v>
+        <v>0.3137481329967758</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3094237980949825</v>
+        <v>0.3113523599699435</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4718995208209228</v>
+        <v>0.4740079886932574</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2558844780521347</v>
+        <v>0.2570137347181923</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5267119988322035</v>
+        <v>0.529078647342869</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3948497229958553</v>
+        <v>0.3971599776892091</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4045289947652131</v>
+        <v>0.4067259090042875</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3841009784678219</v>
+        <v>0.3863899802957136</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4245622161495508</v>
+        <v>0.4267608162803143</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2959512301138466</v>
+        <v>0.2978389234686477</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.3934902795124471</v>
+        <v>0.3949275571570278</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3427760256573618</v>
+        <v>0.3447633378344794</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.36516290637235</v>
+        <v>0.3672726862313744</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>6</v>
       </c>
       <c r="C51">
-        <v>0.3502851354946415</v>
+        <v>0.3524795422109075</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.4827612216876414</v>
+        <v>0.4851418265095178</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4106643150911294</v>
+        <v>0.411946923431699</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3670068017848328</v>
+        <v>0.3678864394133576</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2643365648169991</v>
+        <v>0.2656676985671237</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3584650885406817</v>
+        <v>0.3605617537818656</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5694327585605388</v>
+        <v>0.5699133414365929</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3085390677888586</v>
+        <v>0.3108378283557524</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3501096805573429</v>
+        <v>0.3525125680870577</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.2983347184269911</v>
+        <v>0.3004320410730447</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3808066766348976</v>
+        <v>0.3828258243143364</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3214507429466437</v>
+        <v>0.3226785017772814</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3670005025939267</v>
+        <v>0.3691652420386064</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.230033736577176</v>
+        <v>0.2276820869097179</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.312110818327202</v>
+        <v>0.3140797446024887</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5448,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3056722322614504</v>
+        <v>0.3075502675020678</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3279944714071562</v>
+        <v>0.3299565071490183</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2719312918361165</v>
+        <v>0.2742728184424301</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>79</v>
       </c>
       <c r="C69">
-        <v>0.5375813134285388</v>
+        <v>0.5338092040241297</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>79</v>
       </c>
       <c r="C70">
-        <v>0.5068866895159087</v>
+        <v>0.5033393006600457</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4647428572850165</v>
+        <v>0.4664030814497084</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3547631793790447</v>
+        <v>0.3563818992499542</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4755248056365441</v>
+        <v>0.4765869395975676</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.469921047381363</v>
+        <v>0.4726182049388693</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2659975113984998</v>
+        <v>0.2671969134741759</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3473077768408801</v>
+        <v>0.3494787463609104</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.2826879145789996</v>
+        <v>0.2839501828007703</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.415729232435863</v>
+        <v>0.4179497500244117</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>15</v>
       </c>
       <c r="C79">
-        <v>0.2487705462943092</v>
+        <v>0.2505115300689811</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3584070635167842</v>
+        <v>0.3604801592798837</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2841801853337769</v>
+        <v>0.2858519828132473</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4014896921890105</v>
+        <v>0.4037916430214358</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3705370513929325</v>
+        <v>0.3726277958745841</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="C84">
-        <v>0.2917098742282421</v>
+        <v>0.2938142666043369</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3051074371779726</v>
+        <v>0.3061070288855319</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.304240865705958</v>
+        <v>0.3064880922806075</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2739612573104298</v>
+        <v>0.2759699469130661</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>79</v>
       </c>
       <c r="C88">
-        <v>0.3150632622683961</v>
+        <v>0.3126527415639566</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3178494778473476</v>
+        <v>0.3199727384602273</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2850336665976755</v>
+        <v>0.2870226029215515</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>10</v>
       </c>
       <c r="C91">
-        <v>0.2840658945572561</v>
+        <v>0.2860945379264104</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.2985353951302683</v>
+        <v>0.2957791468104679</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3688740251464059</v>
+        <v>0.3710417397776693</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>44</v>
       </c>
       <c r="C94">
-        <v>0.2859199590467616</v>
+        <v>0.2833245748337881</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.3318529712939059</v>
+        <v>0.332904336103729</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3416291724766912</v>
+        <v>0.3430589394073549</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3351494207084505</v>
+        <v>0.3315191741440189</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3573993703475558</v>
+        <v>0.353707910294004</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4095402429565683</v>
+        <v>0.4107763706010319</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3685449830735972</v>
+        <v>0.36493657587214</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.4381067533284311</v>
+        <v>0.4340065843050927</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4446168524928911</v>
+        <v>0.4455942929998226</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3355966270539834</v>
+        <v>0.3375836380185827</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3613003794214308</v>
+        <v>0.3634379539474923</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.347696117307507</v>
+        <v>0.3437572122321753</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3629771428920042</v>
+        <v>0.3639092296462842</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3573134005318049</v>
+        <v>0.3534327181095303</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.387397570016406</v>
+        <v>0.3894483883652824</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>226</v>
       </c>
       <c r="C109">
-        <v>0.2732875398744341</v>
+        <v>0.2702951382015362</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.293645532886323</v>
+        <v>0.2953929560348129</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4870710258599482</v>
+        <v>0.488027808135202</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3776683175939995</v>
+        <v>0.380002799229847</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4907773194083301</v>
+        <v>0.4920414145702919</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6172606299007736</v>
+        <v>0.6182618871767068</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.2958022654649784</v>
+        <v>0.2980839628149102</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4425244458387717</v>
+        <v>0.443065038961885</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.29147529640192</v>
+        <v>0.2926470442439431</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3715870178840825</v>
+        <v>0.3730202636751062</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3656998806715763</v>
+        <v>0.3671108119200195</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3536123643868399</v>
+        <v>0.3556517491031541</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.2491215870181868</v>
+        <v>0.2513529726846762</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3016808408980547</v>
+        <v>0.303702515802753</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2918652595570721</v>
+        <v>0.2938138776426843</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3877516581358044</v>
+        <v>0.3892239998973958</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="C125">
-        <v>0.3071461346081928</v>
+        <v>0.3092099680832417</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3468645070321281</v>
+        <v>0.3478329241177317</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4864466149757284</v>
+        <v>0.4871377865604617</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.3925288989113198</v>
+        <v>0.3938525194351277</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="C129">
-        <v>0.3022755427149115</v>
+        <v>0.3037042938748347</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3811545999044016</v>
+        <v>0.3825613425359978</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2744174015479982</v>
+        <v>0.2764383959962752</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3855046340838106</v>
+        <v>0.3863073099175786</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3255400822712893</v>
+        <v>0.3273585691828883</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3148347790422202</v>
+        <v>0.3158443759614415</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3043210902916059</v>
+        <v>0.3064693984337917</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3220976321552211</v>
+        <v>0.3194130051012417</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.4084715136538806</v>
+        <v>0.4108235170374376</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3286231651545216</v>
+        <v>0.3306564441748294</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.3643812157744238</v>
+        <v>0.3664598368705302</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3929183936180154</v>
+        <v>0.3888902046034365</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3352164929228912</v>
+        <v>0.3373697855360028</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3751992665385492</v>
+        <v>0.376195420254807</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3304794353894058</v>
+        <v>0.3327852545043795</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5910626312735524</v>
+        <v>0.5923083898115646</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2830210551373179</v>
+        <v>0.2851289363188913</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.3922599697988504</v>
+        <v>0.3944225923653825</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4444133285047434</v>
+        <v>0.4466487631144404</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.2882112860032878</v>
+        <v>0.290478239670413</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3651088418394173</v>
+        <v>0.3661664212865041</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3252114125162771</v>
+        <v>0.3273724880019563</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2456400076795973</v>
+        <v>0.2476178741233664</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6614707942934493</v>
+        <v>0.6622364804109311</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3195086499242815</v>
+        <v>0.3207570989630888</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3230786337460085</v>
+        <v>0.319483447116808</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.2746712802077314</v>
+        <v>0.276795942865707</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3278961858593225</v>
+        <v>0.3299654188759196</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3461333624692499</v>
+        <v>0.3478579814426823</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.387975869225308</v>
+        <v>0.3848739392250294</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3986600693219532</v>
+        <v>0.3958228888096297</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3720802176222696</v>
+        <v>0.3742579644925902</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3821963615354673</v>
+        <v>0.3844444028034739</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5557076652017821</v>
+        <v>0.5578617441402903</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.441378620513883</v>
+        <v>0.437468459814245</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3385024982098514</v>
+        <v>0.3394461641114359</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3436757666890416</v>
+        <v>0.3458118161371394</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.3002813757688143</v>
+        <v>0.3015967922198849</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.352472341708571</v>
+        <v>0.3545857029046301</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5859808257434195</v>
+        <v>0.5865171673888198</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3328898646405973</v>
+        <v>0.3292977106415327</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.348418422339315</v>
+        <v>0.3496732318784683</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>44</v>
       </c>
       <c r="C171">
-        <v>0.2557727318901526</v>
+        <v>0.2532682627418967</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.3884262915422832</v>
+        <v>0.3891790661130516</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3077930511540957</v>
+        <v>0.3098926011244216</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.324173304810476</v>
+        <v>0.3262293288415183</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2890034745699111</v>
+        <v>0.2905378882138326</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3998196260908056</v>
+        <v>0.4007310745244856</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.4872823077045053</v>
+        <v>0.4880322165440201</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3799014623378668</v>
+        <v>0.3812958509394732</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3075092302693504</v>
+        <v>0.3094030487953465</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3446208516607657</v>
+        <v>0.341906149937274</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3379546425352769</v>
+        <v>0.3399685674897125</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2887110450891056</v>
+        <v>0.2906770573649118</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.2865262983478146</v>
+        <v>0.2887940055993771</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3442634014050478</v>
+        <v>0.346426329186201</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3381117622468598</v>
+        <v>0.3395315796822979</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4064502625726111</v>
+        <v>0.4032745040960193</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.24603566901833</v>
+        <v>0.2477524961627114</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4584906538229266</v>
+        <v>0.4595780273978522</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.3139973782775285</v>
+        <v>0.316018828380405</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.281335484188852</v>
+        <v>0.2833018681818847</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.345813406846774</v>
+        <v>0.3479394978446018</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.3854822063742863</v>
+        <v>0.3876274641869539</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.3979648363933358</v>
+        <v>0.399182120208396</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3961917596704624</v>
+        <v>0.39752728431582</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.3633286648295007</v>
+        <v>0.3600212761833992</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3412543813085424</v>
+        <v>0.3439613157861746</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3300905661803299</v>
+        <v>0.3322801107875567</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5106179860619076</v>
+        <v>0.5126754755234557</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6024647285942177</v>
+        <v>0.6046759640194266</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3281337551964315</v>
+        <v>0.3301886570454581</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.2975151923723954</v>
+        <v>0.2990827759577149</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3830219380458117</v>
+        <v>0.3844562944043112</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5091313939773168</v>
+        <v>0.5101673751808098</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4400202280826854</v>
+        <v>0.442422647973388</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4387146506373419</v>
+        <v>0.439494729714679</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3485623958037571</v>
+        <v>0.350566121644655</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5493183803966396</v>
+        <v>0.5451189948970628</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.4014993222981846</v>
+        <v>0.3974589327752635</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.4974066534283145</v>
+        <v>0.4996830047302218</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4023849857227825</v>
+        <v>0.4036334744276726</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.422486441792542</v>
+        <v>0.4238697948950082</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2844904508398324</v>
+        <v>0.2863985220557114</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3069363372457801</v>
+        <v>0.3090209911637161</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3715109353969295</v>
+        <v>0.3729547114374185</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.4695602739803728</v>
+        <v>0.4708686385505227</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3303962231774788</v>
+        <v>0.3322574301249487</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3309954884278163</v>
+        <v>0.3330062402439348</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3393313364482444</v>
+        <v>0.3403415096227051</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4749381041309967</v>
+        <v>0.4707173427875729</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="C220">
-        <v>0.2759039799104047</v>
+        <v>0.2777223826223104</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3434825805390539</v>
+        <v>0.3454744959447322</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3221244140886136</v>
+        <v>0.3230181423588571</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5026533316330004</v>
+        <v>0.502981806641476</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.318543486025801</v>
+        <v>0.3205299613974936</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3571377201531903</v>
+        <v>0.3591964308192276</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4625394882512806</v>
+        <v>0.4648967792406267</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3421718150002956</v>
+        <v>0.3432363197673307</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4725965166364404</v>
+        <v>0.4737498489644217</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5374742290205313</v>
+        <v>0.5388739733429568</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.362570256718442</v>
+        <v>0.3586142767157708</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3144445449822922</v>
+        <v>0.3156491705087305</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.573128077869523</v>
+        <v>0.5740347038466673</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4122899558576995</v>
+        <v>0.4092306073881415</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.403162589641927</v>
+        <v>0.4053326350604912</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4667672588807263</v>
+        <v>0.4693287290260539</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2778828590983202</v>
+        <v>0.2802811215348538</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3318729052493475</v>
+        <v>0.3329239407327334</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3454350553362527</v>
+        <v>0.3475044459383709</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4247478415374827</v>
+        <v>0.4269128912951971</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3412431936718611</v>
+        <v>0.338906794620614</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>15</v>
       </c>
       <c r="C241">
-        <v>0.2278970121759742</v>
+        <v>0.2290757654048104</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>15</v>
       </c>
       <c r="C242">
-        <v>0.3042664378137436</v>
+        <v>0.3062284219268624</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4531329967499129</v>
+        <v>0.454885612229877</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.3910050155526176</v>
+        <v>0.3883656686066478</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.614956823890439</v>
+        <v>0.6158344150167538</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4321984134741917</v>
+        <v>0.4346313479450927</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4271611287638611</v>
+        <v>0.427887507238831</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3552541102064895</v>
+        <v>0.3573974051655957</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.3981172533417957</v>
+        <v>0.4004619134804884</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3086396571898459</v>
+        <v>0.3106250975140731</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4264267007295922</v>
+        <v>0.4226090106454818</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4192741280351067</v>
+        <v>0.4215225194747155</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3803293146780267</v>
+        <v>0.382588554371605</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4922778295813283</v>
+        <v>0.4927231359650153</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.3917395486891489</v>
+        <v>0.394000685078693</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5805217858631857</v>
+        <v>0.5829025628513484</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4081194277633916</v>
+        <v>0.4104448442511122</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4868422699681493</v>
+        <v>0.4884385667344533</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>15</v>
       </c>
       <c r="C259">
-        <v>0.3042888148706895</v>
+        <v>0.3056783576451451</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4102531545018706</v>
+        <v>0.4111296134823114</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.45332776386311</v>
+        <v>0.4541304462055147</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3941811725233179</v>
+        <v>0.3967896419225956</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4417794197665414</v>
+        <v>0.4440850037294227</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.41845336798642</v>
+        <v>0.4208350352009756</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3241523528530911</v>
+        <v>0.3264423564968075</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>226</v>
       </c>
       <c r="C266">
-        <v>0.3188021047888844</v>
+        <v>0.3159430829103052</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>15</v>
       </c>
       <c r="C267">
-        <v>0.2738064946696965</v>
+        <v>0.2755089011156285</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4266256405287925</v>
+        <v>0.4289243882485121</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3868149843878536</v>
+        <v>0.3829002918592759</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5114512725554951</v>
+        <v>0.5125832658286531</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5313857195606858</v>
+        <v>0.5328330953346908</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3365842375308938</v>
+        <v>0.3390245819778576</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.497058117166766</v>
+        <v>0.4980316616646574</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3341229387900291</v>
+        <v>0.3350354293870675</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2441260186234964</v>
+        <v>0.2457986712639984</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3290318299206622</v>
+        <v>0.331007249055735</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>79</v>
       </c>
       <c r="C277">
-        <v>0.3734936930587524</v>
+        <v>0.3714441004726534</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4442457709807539</v>
+        <v>0.4457316547043956</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5514500946871475</v>
+        <v>0.5531072871100657</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4584004138033197</v>
+        <v>0.4606821497330063</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3826132256959259</v>
+        <v>0.3834631976205587</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3674224481796012</v>
+        <v>0.3694842448143066</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3628335381347704</v>
+        <v>0.3649579858652059</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3078922262259856</v>
+        <v>0.3102315635695568</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2605911206430679</v>
+        <v>0.2622238231942537</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.2819693786390272</v>
+        <v>0.2840748879584387</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4523776974636924</v>
+        <v>0.4484137505863382</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>6</v>
       </c>
       <c r="C288">
-        <v>0.237906226626616</v>
+        <v>0.2395450966119924</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.344618153287586</v>
+        <v>0.3467634249732602</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3141716480633512</v>
+        <v>0.3160528852547545</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4020321308598012</v>
+        <v>0.4049112517298866</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>79</v>
       </c>
       <c r="C292">
-        <v>0.4579627585556948</v>
+        <v>0.4555937686836316</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5934857220745682</v>
+        <v>0.5947141170621938</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3756162335947532</v>
+        <v>0.3770069112290163</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.348815527396435</v>
+        <v>0.3510224826235235</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.3144724749476119</v>
+        <v>0.3164229121591852</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4510379228470904</v>
+        <v>0.4532617242888282</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3876331248097032</v>
+        <v>0.3886282450458986</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2869509816327896</v>
+        <v>0.2838580747866252</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.335797806610426</v>
+        <v>0.3377928600746522</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3426963298292768</v>
+        <v>0.3448694472501815</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.527957238164429</v>
+        <v>0.5237186359847206</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3039403432114322</v>
+        <v>0.3049412782764863</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2870774828283357</v>
+        <v>0.2892028396466185</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4396259546149008</v>
+        <v>0.4365431123856792</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.3894052996752283</v>
+        <v>0.3906402045818572</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4429290259968005</v>
+        <v>0.4434502204524501</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3905900028850289</v>
+        <v>0.3927262352596316</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.268938655762435</v>
+        <v>0.2710282464200494</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.384064243631789</v>
+        <v>0.3856299578454766</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3443241195802385</v>
+        <v>0.3463238132394398</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2774239647709135</v>
+        <v>0.2791512116982955</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3255699158339491</v>
+        <v>0.3227659119270788</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3149834400035742</v>
+        <v>0.3170739480860267</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.487274352810498</v>
+        <v>0.4832729498218137</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3880297541837925</v>
+        <v>0.3903918854702347</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5217389717569033</v>
+        <v>0.5236021619857196</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5272114726866903</v>
+        <v>0.5281783017229182</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3365627344387399</v>
+        <v>0.338739356253855</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2651441355563188</v>
+        <v>0.266675277045067</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3282764486548599</v>
+        <v>0.3302699833478307</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3535080478340162</v>
+        <v>0.355723976874564</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3782953871258739</v>
+        <v>0.3792491882813597</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3885097540543505</v>
+        <v>0.3854939415710883</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>15</v>
       </c>
       <c r="C325">
-        <v>0.2335660182229677</v>
+        <v>0.2351247216248196</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3679684382793482</v>
+        <v>0.3649674143512009</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3389036850708688</v>
+        <v>0.3350646562693455</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2797956038308701</v>
+        <v>0.2814648529342331</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>10</v>
       </c>
       <c r="C329">
-        <v>0.3045917571674812</v>
+        <v>0.3067171671764445</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>6</v>
       </c>
       <c r="C330">
-        <v>0.3025549529733922</v>
+        <v>0.30456355615769</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3872855742511495</v>
+        <v>0.390226283809365</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3509833118276986</v>
+        <v>0.3531535793098539</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4677073517174425</v>
+        <v>0.4686948107645164</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.28399218385652</v>
+        <v>0.2859218236294512</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>44</v>
       </c>
       <c r="C335">
-        <v>0.3427864273599877</v>
+        <v>0.3397541620791251</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>15</v>
       </c>
       <c r="C336">
-        <v>0.297622436162364</v>
+        <v>0.2995931612904237</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4655091770048483</v>
+        <v>0.4622755374091589</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.281652527267989</v>
+        <v>0.2829203600550356</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4437454581333809</v>
+        <v>0.4451447727149642</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.307751368870076</v>
+        <v>0.3097723982115085</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2939067461866287</v>
+        <v>0.2953885194297042</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2591863580363889</v>
+        <v>0.2605321285832493</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.3952269558639611</v>
+        <v>0.397371588119501</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2887671597103184</v>
+        <v>0.2904355291377471</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3545688155610214</v>
+        <v>0.356710221420408</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.330005477404774</v>
+        <v>0.3309951433400266</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3364481960584361</v>
+        <v>0.338436784754342</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3134115301868616</v>
+        <v>0.3158212808649553</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4732114638791179</v>
+        <v>0.47487676323518</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3576303575126556</v>
+        <v>0.3590971146178216</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>79</v>
       </c>
       <c r="C351">
-        <v>0.2658039462359348</v>
+        <v>0.2642247922079262</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3926118972002886</v>
+        <v>0.3948016985990453</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3875947563155628</v>
+        <v>0.3883712924044244</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2790484086711113</v>
+        <v>0.2810902780901962</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.353049637805116</v>
+        <v>0.3554152826388386</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3058475359999432</v>
+        <v>0.307968115270974</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.3918903345497604</v>
+        <v>0.3941943956467352</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3104777775224267</v>
+        <v>0.3130519577402617</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.472149610386606</v>
+        <v>0.4681872248103757</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.471449863300955</v>
+        <v>0.4737435417093092</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3106907591643868</v>
+        <v>0.3126132300093546</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.354304262375831</v>
+        <v>0.3564113051451503</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2913408036337486</v>
+        <v>0.2933808753130011</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3185117735673548</v>
+        <v>0.3205808864731204</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3010255724690242</v>
+        <v>0.3030301700961534</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2626800854961652</v>
+        <v>0.2644699477838249</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3019769509201753</v>
+        <v>0.304365124184993</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3085227585951494</v>
+        <v>0.3095336448450537</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4850916583793015</v>
+        <v>0.4875867554097122</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3304459402927414</v>
+        <v>0.3323845458652118</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4432694298194241</v>
+        <v>0.4457141240823744</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.351787070270293</v>
+        <v>0.3539352682045122</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4238707963363504</v>
+        <v>0.4249374376961623</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.46944822956528</v>
+        <v>0.4720798375874312</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4532035521879832</v>
+        <v>0.4555900853427389</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3620914139994278</v>
+        <v>0.3629999778968403</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4542538021769481</v>
+        <v>0.4567448039682038</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.305977767600755</v>
+        <v>0.3080633197555632</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3519148065633409</v>
+        <v>0.3539615283412253</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3497739963191122</v>
+        <v>0.3519325756600939</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.435494050603664</v>
+        <v>0.4364045521835532</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.320779217011703</v>
+        <v>0.3227728322867317</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3760724212485425</v>
+        <v>0.3781197802708273</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4316680878241635</v>
+        <v>0.4278170493529366</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3894961149701471</v>
+        <v>0.391686640606782</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3097982030072141</v>
+        <v>0.3117778107417683</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4236598681346773</v>
+        <v>0.4234018069345032</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3543217471293787</v>
+        <v>0.351608630271677</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3397174970538442</v>
+        <v>0.3418725369184407</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3213167795007851</v>
+        <v>0.3233872560716411</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3403698392516281</v>
+        <v>0.3421651791768209</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.302369767306986</v>
+        <v>0.3044480552241149</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.400876409051463</v>
+        <v>0.4019075218317986</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3618649629551463</v>
+        <v>0.3638669385070762</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3947114518435716</v>
+        <v>0.3955520565672337</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3884287749037924</v>
+        <v>0.389436224968346</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3630286146464676</v>
+        <v>0.3640764523006944</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4718054196047277</v>
+        <v>0.4747689325169223</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3468307600215131</v>
+        <v>0.3485785717725723</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3341573878869074</v>
+        <v>0.3361622375198715</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4218735818236939</v>
+        <v>0.4231039616552564</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.389886371807409</v>
+        <v>0.3922014588102881</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2750616846604813</v>
+        <v>0.2770738323044247</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.2980664116693748</v>
+        <v>0.3002834904502956</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4176963758067991</v>
+        <v>0.4199772982213539</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>79</v>
       </c>
       <c r="C406">
-        <v>0.4769835319568453</v>
+        <v>0.4734865417259063</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3660565556394468</v>
+        <v>0.3675237083027506</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4723920170558493</v>
+        <v>0.4747755596788322</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.46530098832342</v>
+        <v>0.4676092643078792</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3132977543183315</v>
+        <v>0.3152442754679363</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3146291275862148</v>
+        <v>0.3167146835907402</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4516732496113741</v>
+        <v>0.4527464665662591</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2582808251676272</v>
+        <v>0.2599746949428018</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3122905600521406</v>
+        <v>0.3141888283889567</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3411223656042475</v>
+        <v>0.3430009230556839</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3778326212318529</v>
+        <v>0.3801289341864169</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2567095463434271</v>
+        <v>0.2590455939838325</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.2991045422511011</v>
+        <v>0.3004076177008029</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3450264823743769</v>
+        <v>0.3470532152511466</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.3976939238497436</v>
+        <v>0.3936758419397943</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.3959417500801545</v>
+        <v>0.3919434692621153</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3520281861243801</v>
+        <v>0.3542078614588216</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.463445543909917</v>
+        <v>0.4602221205321659</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3088808598099239</v>
+        <v>0.3099895462329984</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3305754523857272</v>
+        <v>0.3326728646212059</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3476568381440197</v>
+        <v>0.3495550067949087</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2702570428058927</v>
+        <v>0.2713080241959008</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2737844691622493</v>
+        <v>0.2755651830629051</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3213524049202692</v>
+        <v>0.3234327562281284</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3437893019589151</v>
+        <v>0.3449146338308048</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.2773257841111456</v>
+        <v>0.2794464705462866</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3237906981070713</v>
+        <v>0.3255604607681911</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3214009798989462</v>
+        <v>0.3234099485347198</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.350769242946087</v>
+        <v>0.3528339415900539</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3543430364029925</v>
+        <v>0.3564235975220453</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.335449257588734</v>
+        <v>0.3371713243751752</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3057093412304472</v>
+        <v>0.3077869001319014</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3427196684623486</v>
+        <v>0.344855973103392</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3485307435733862</v>
+        <v>0.3510371931809452</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3460633612664038</v>
+        <v>0.3481769249373199</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.303448409949237</v>
+        <v>0.305397406661855</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.2820971349507029</v>
+        <v>0.2843055716602412</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.292127574809511</v>
+        <v>0.2939120166081285</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3283232639413382</v>
+        <v>0.3295198968480662</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3466993842650783</v>
+        <v>0.3488796534375608</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.346493750452994</v>
+        <v>0.3430065172344442</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2868521198350029</v>
+        <v>0.2878841212500933</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3546227763538569</v>
+        <v>0.356883572169119</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3842232596575464</v>
+        <v>0.386391610807334</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3767835943069194</v>
+        <v>0.373787798640506</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4103124187310438</v>
+        <v>0.4064917566947878</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2751670480136385</v>
+        <v>0.2772465867589065</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3407868291735076</v>
+        <v>0.3428880998762383</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2848192834126454</v>
+        <v>0.2865574560430217</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.328420313232577</v>
+        <v>0.3305630826868569</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3491408372236749</v>
+        <v>0.3514285972298866</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3382818591695884</v>
+        <v>0.339539929715512</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3896068589898339</v>
+        <v>0.3902649138715188</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3619765032418573</v>
+        <v>0.3642761759508351</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3337461099955391</v>
+        <v>0.3359747315219174</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3191972529567833</v>
+        <v>0.3211590344645533</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3412032567324592</v>
+        <v>0.3421489117750018</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.2932224969267514</v>
+        <v>0.2952972286515756</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3924267232886226</v>
+        <v>0.39519309835755</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.4021937469954971</v>
+        <v>0.3983016953197909</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5172983609306038</v>
+        <v>0.5182765213271876</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4577163204936925</v>
+        <v>0.460207570424539</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3875823234592799</v>
+        <v>0.3887450159520556</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2921053081342213</v>
+        <v>0.2939305525172114</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>15</v>
       </c>
       <c r="C470">
-        <v>0.2962871945685051</v>
+        <v>0.2980702644970674</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12330,10 +12330,10 @@
         <v>950</v>
       </c>
       <c r="B471" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3029646007919119</v>
+        <v>0.3027872227097334</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3331765481242102</v>
+        <v>0.3350077017411019</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>44</v>
       </c>
       <c r="C473">
-        <v>0.3114185478835853</v>
+        <v>0.3079533124722368</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3688594187369839</v>
+        <v>0.3696583106595751</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3338236873195197</v>
+        <v>0.3347417781595635</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3466765930692349</v>
+        <v>0.3488151157305164</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3468983487851426</v>
+        <v>0.3490191662915159</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.3871306997051409</v>
+        <v>0.3891752972780927</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4144432164146241</v>
+        <v>0.4105088128207801</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4495823453134792</v>
+        <v>0.4518703500201768</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.4028693007571467</v>
+        <v>0.3988185960222921</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.305922610474118</v>
+        <v>0.3079810461872419</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.2968746017856752</v>
+        <v>0.2989840889879922</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3863191907966307</v>
+        <v>0.3832534438453517</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.350926851453511</v>
+        <v>0.3523074986335054</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3862391353445343</v>
+        <v>0.3875622742744171</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.477858653985512</v>
+        <v>0.4734990530217132</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3148118363945324</v>
+        <v>0.3169522766883882</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.474211819429071</v>
+        <v>0.4753256113258356</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3075769661170859</v>
+        <v>0.3091738458265771</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>15</v>
       </c>
       <c r="C491">
-        <v>0.2735333442169051</v>
+        <v>0.2753347359873742</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4860642964324082</v>
+        <v>0.4891186703771651</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.2859439464256592</v>
+        <v>0.2873029181160376</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3353173709054332</v>
+        <v>0.3368046333476345</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5249105308162485</v>
+        <v>0.5208070855259753</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4703896512579094</v>
+        <v>0.4726417802072567</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3314449921645754</v>
+        <v>0.3335268738161581</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.670178350950892</v>
+        <v>0.6720556089840504</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3393934588214377</v>
+        <v>0.3413748214154109</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4110912622229522</v>
+        <v>0.4134403431038555</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3840866600840658</v>
+        <v>0.3853670661997149</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5769007238637928</v>
+        <v>0.579504169074729</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3560337852103868</v>
+        <v>0.3581376405870803</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3244722825324076</v>
+        <v>0.3265430554458331</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4287695454022775</v>
+        <v>0.4309685790691669</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.5003604898679385</v>
+        <v>0.501627331864519</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.3052769719659477</v>
+        <v>0.3063911894040673</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3131230861719746</v>
+        <v>0.3150349927072103</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4869926786296521</v>
+        <v>0.4879475914876307</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3653134116272648</v>
+        <v>0.3674597275003224</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3499345335998894</v>
+        <v>0.3471727741807976</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.299222119551234</v>
+        <v>0.3012306087707559</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3636631098991319</v>
+        <v>0.3659541671924843</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.4202816710201673</v>
+        <v>0.4172677685947335</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4635218890724219</v>
+        <v>0.4662328629128423</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>15</v>
       </c>
       <c r="C516">
-        <v>0.315897184415829</v>
+        <v>0.317777724825319</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3355218515279798</v>
+        <v>0.3375680428680898</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3258557514945978</v>
+        <v>0.3279940135209331</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5065692616865147</v>
+        <v>0.5022944620691857</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3249111220567935</v>
+        <v>0.3268076278569762</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.2998178029324541</v>
+        <v>0.3018259789239875</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3599507269450423</v>
+        <v>0.3614240135696991</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4290743312332251</v>
+        <v>0.4312593037773295</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2780579738100629</v>
+        <v>0.2802994338107743</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4074768608786564</v>
+        <v>0.4039219142030415</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4235319999220581</v>
+        <v>0.4203911405725111</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3622294388898334</v>
+        <v>0.3643174094899185</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4344373080305042</v>
+        <v>0.4353645014248509</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3361369759692363</v>
+        <v>0.337058088201249</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4928787779482044</v>
+        <v>0.4886113406620538</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5608389947140966</v>
+        <v>0.5565225666240617</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>44</v>
       </c>
       <c r="C532">
-        <v>0.27397455944736</v>
+        <v>0.270607236292422</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4325451622544554</v>
+        <v>0.433769218353064</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3212987078058976</v>
+        <v>0.3227670431782358</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3108902729732357</v>
+        <v>0.3129376842292733</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3042023064884808</v>
+        <v>0.30624507450543</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3649253928754086</v>
+        <v>0.3673641661712518</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2818816105329868</v>
+        <v>0.2838229755638133</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.2897339696083849</v>
+        <v>0.2918867662571139</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.283673563131618</v>
+        <v>0.2853133402803443</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4312447391153837</v>
+        <v>0.4334289341446497</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3943205444889283</v>
+        <v>0.3911553019170018</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3980498065640394</v>
+        <v>0.3996966038360104</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3337048740611942</v>
+        <v>0.3349311356381527</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2888287818295125</v>
+        <v>0.2885933316994441</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3322795898775816</v>
+        <v>0.3315649768845428</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2764596601169398</v>
+        <v>0.2768116298207039</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3719705089548241</v>
+        <v>0.3721600528440104</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4012424141887613</v>
+        <v>0.4010091839065414</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3701706072983576</v>
+        <v>0.3700802454722817</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2627581182322579</v>
+        <v>0.2628339130924623</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2891033100775696</v>
+        <v>0.2889453147854109</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2821519833076478</v>
+        <v>0.2821704816738212</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.2769815524308674</v>
+        <v>0.2769585454267521</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3260040773520119</v>
+        <v>0.3257372872698618</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3226331502921406</v>
+        <v>0.3217147710987504</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3648558626033117</v>
+        <v>0.3642658739486872</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3913235884134174</v>
+        <v>0.3912054249005278</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2842886423110846</v>
+        <v>0.2824751051595559</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3872165915096974</v>
+        <v>0.3871865325510653</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3182743592282397</v>
+        <v>0.3181505328096915</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3198066122624188</v>
+        <v>0.3190705384117182</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4902760428457153</v>
+        <v>0.48917132173675</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3098994519649725</v>
+        <v>0.3099314973130384</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3733645298496815</v>
+        <v>0.3731458113232022</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.304587911814411</v>
+        <v>0.3045504532604373</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.4237076938251195</v>
+        <v>0.423057064225317</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.3155585383051112</v>
+        <v>0.3148847258125221</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2580066296735423</v>
+        <v>0.257455862911814</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3361781406209469</v>
+        <v>0.3355688626607655</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>1143</v>
       </c>
       <c r="C589">
-        <v>0.336044880369905</v>
+        <v>0.3355929001299688</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.3663674537166403</v>
+        <v>0.3649957749395182</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5416924648469769</v>
+        <v>0.5402657598545296</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.4123993579551783</v>
+        <v>0.4115766548785516</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6555197834409716</v>
+        <v>0.654280612673072</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4378460535704081</v>
+        <v>0.4377516740103888</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>1143</v>
       </c>
       <c r="C595">
-        <v>0.304238741536642</v>
+        <v>0.3039499742554594</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4481575699686549</v>
+        <v>0.4475317175746929</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3078256921596347</v>
+        <v>0.3076705088026271</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14438,7 +14438,7 @@
         <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2404176243974193</v>
+        <v>0.2402471877693405</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2645273749686199</v>
+        <v>0.2646379319913028</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2770134524450406</v>
+        <v>0.2771610247900749</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2474132824246504</v>
+        <v>0.2473401347347008</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3607201683666747</v>
+        <v>0.3611239408328594</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2865655447165862</v>
+        <v>0.2868291575936334</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.2938105524513625</v>
+        <v>0.292357712634558</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.27907788077766</v>
+        <v>0.2787428681373357</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3580318771814169</v>
+        <v>0.3580562574496187</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3256800730901381</v>
+        <v>0.3251581885714173</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.2937079130823276</v>
+        <v>0.2917836836437709</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2856797297946881</v>
+        <v>0.2855123348673395</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2429642091301902</v>
+        <v>0.2430071427574336</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4577466515440454</v>
+        <v>0.4573981080354651</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3032056080094967</v>
+        <v>0.3030608734483931</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3445324914796333</v>
+        <v>0.3446206779189034</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4273298483406441</v>
+        <v>0.4271669901480344</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3302704028439839</v>
+        <v>0.3296201299049334</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4388612038367041</v>
+        <v>0.4387138791988515</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3387636535336066</v>
+        <v>0.3383794303861106</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3215542996688102</v>
+        <v>0.320709550861998</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4575209350394632</v>
+        <v>0.4569990307010543</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2882140268243685</v>
+        <v>0.2831631561603731</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.424925600778397</v>
+        <v>0.4255039485586797</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3903625944507353</v>
+        <v>0.3849360667180776</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3222960531988727</v>
+        <v>0.3299913011840191</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3684935791535398</v>
+        <v>0.3722587302327848</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.2914272737455451</v>
+        <v>0.286097669215153</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3457033830922796</v>
+        <v>0.3537542732443177</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3085658486491382</v>
+        <v>0.3153965919011218</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3440359754793982</v>
+        <v>0.348302985884026</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2381712079908356</v>
+        <v>0.2441976559018879</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.3880716049425764</v>
+        <v>0.3807933956799462</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.2863195390203992</v>
+        <v>0.2924257318055369</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3647212543954171</v>
+        <v>0.3724020136284033</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3490478363797349</v>
+        <v>0.3527526482159136</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3202655669676484</v>
+        <v>0.3157230916017902</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>0.2849520976585044</v>
+        <v>0.2889991461956005</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3155553211841251</v>
+        <v>0.3190272882201634</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4354140120157834</v>
+        <v>0.4282823283126049</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3995861048217506</v>
+        <v>0.3933085454703231</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4286775218518142</v>
+        <v>0.4325828180667278</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3210682702968278</v>
+        <v>0.3159965669313618</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3833120166834394</v>
+        <v>0.3774524060599008</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3316736935417304</v>
+        <v>0.3266501086132437</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.5925807421895093</v>
+        <v>0.585586191500625</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3224958666040308</v>
+        <v>0.3165085863857585</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.287334125573678</v>
+        <v>0.2914192935357017</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3176816154208367</v>
+        <v>0.3211089555251925</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4682545718556896</v>
+        <v>0.4616204380008559</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3815463568095588</v>
+        <v>0.3758300111980035</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4353340428419675</v>
+        <v>0.4298340179147914</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.3944016743903546</v>
+        <v>0.4011294782529491</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3874284500984028</v>
+        <v>0.3827605339726079</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3270369982420012</v>
+        <v>0.3328375424616308</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4395368105678893</v>
+        <v>0.4331634072929274</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="C36">
-        <v>0.2261854244905496</v>
+        <v>0.2288984667648479</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.2742291808267222</v>
+        <v>0.2796787759611737</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3137481329967758</v>
+        <v>0.3078807545776337</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3113523599699435</v>
+        <v>0.3187046927433971</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4740079886932574</v>
+        <v>0.4682014197891373</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2570137347181923</v>
+        <v>0.2621143902451977</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.529078647342869</v>
+        <v>0.5229127188476864</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3971599776892091</v>
+        <v>0.4058826873607149</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4067259090042875</v>
+        <v>0.4142104769579736</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3863899802957136</v>
+        <v>0.3809191306591311</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4267608162803143</v>
+        <v>0.420819761508451</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.2978389234686477</v>
+        <v>0.3051903147736814</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.3949275571570278</v>
+        <v>0.4017841447006284</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3447633378344794</v>
+        <v>0.3527546153493197</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3672726862313744</v>
+        <v>0.3748390959162642</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>6</v>
       </c>
       <c r="C51">
-        <v>0.3524795422109075</v>
+        <v>0.3470957663728896</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.4851418265095178</v>
+        <v>0.4790042973483321</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.411946923431699</v>
+        <v>0.4188656618217351</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3678864394133576</v>
+        <v>0.3617461145168955</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2656676985671237</v>
+        <v>0.2690113072572358</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3605617537818656</v>
+        <v>0.3649543691659294</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5699133414365929</v>
+        <v>0.5633531625012963</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3108378283557524</v>
+        <v>0.3039819240183771</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3525125680870577</v>
+        <v>0.347176682933209</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3004320410730447</v>
+        <v>0.2949400729606396</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3828258243143364</v>
+        <v>0.377504955829631</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3226785017772814</v>
+        <v>0.3262054237416919</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3691652420386064</v>
+        <v>0.3636450607989149</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5411,10 +5411,10 @@
         <v>135</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C64">
-        <v>0.2276820869097179</v>
+        <v>0.2282511805135438</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3140797446024887</v>
+        <v>0.3217954788224316</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5448,7 +5448,7 @@
         <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3075502675020678</v>
+        <v>0.3150536984757487</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3299565071490183</v>
+        <v>0.337600519773778</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2742728184424301</v>
+        <v>0.2690918078289161</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5499,7 +5499,7 @@
         <v>79</v>
       </c>
       <c r="C69">
-        <v>0.5338092040241297</v>
+        <v>0.5378684651415885</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5516,7 +5516,7 @@
         <v>79</v>
       </c>
       <c r="C70">
-        <v>0.5033393006600457</v>
+        <v>0.507725383253298</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4664030814497084</v>
+        <v>0.458917112330169</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3563818992499542</v>
+        <v>0.3504311949938821</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4765869395975676</v>
+        <v>0.4703847858808292</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4726182049388693</v>
+        <v>0.4661665283294252</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2671969134741759</v>
+        <v>0.2708495252926101</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3494787463609104</v>
+        <v>0.3537513405999169</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.2839501828007703</v>
+        <v>0.2876926449450477</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4179497500244117</v>
+        <v>0.4223251536409405</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>15</v>
       </c>
       <c r="C79">
-        <v>0.2505115300689811</v>
+        <v>0.257024573522678</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3604801592798837</v>
+        <v>0.3646921171518739</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.2858519828132473</v>
+        <v>0.2924174791700816</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4037916430214358</v>
+        <v>0.4079366676095699</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3726277958745841</v>
+        <v>0.3668245146044376</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="C84">
-        <v>0.2938142666043369</v>
+        <v>0.2979195868252322</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3061070288855319</v>
+        <v>0.3128222531563299</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3064880922806075</v>
+        <v>0.3015863499162146</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2759699469130661</v>
+        <v>0.2712144926881904</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5822,7 +5822,7 @@
         <v>79</v>
       </c>
       <c r="C88">
-        <v>0.3126527415639566</v>
+        <v>0.3161456522855082</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3199727384602273</v>
+        <v>0.3241543614608279</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2870226029215515</v>
+        <v>0.2904902217660849</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>10</v>
       </c>
       <c r="C91">
-        <v>0.2860945379264104</v>
+        <v>0.2901514381247962</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.2957791468104679</v>
+        <v>0.2893865335774943</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.3710417397776693</v>
+        <v>0.3797981205321461</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>44</v>
       </c>
       <c r="C94">
-        <v>0.2833245748337881</v>
+        <v>0.2776021258820446</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.332904336103729</v>
+        <v>0.3398135499806118</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.3430589394073549</v>
+        <v>0.3496225032225199</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3315191741440189</v>
+        <v>0.3255453799630212</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.353707910294004</v>
+        <v>0.3469486923934018</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4107763706010319</v>
+        <v>0.4055000257738264</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.36493657587214</v>
+        <v>0.3581757131127667</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.4340065843050927</v>
+        <v>0.426993236688255</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4455942929998226</v>
+        <v>0.4392743475825197</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3375836380185827</v>
+        <v>0.3328985838614494</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.3634379539474923</v>
+        <v>0.3716836355424765</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3437572122321753</v>
+        <v>0.3367252208528693</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3639092296462842</v>
+        <v>0.367642934071217</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3534327181095303</v>
+        <v>0.3462037589081145</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.3894483883652824</v>
+        <v>0.3837630929577617</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>226</v>
       </c>
       <c r="C109">
-        <v>0.2702951382015362</v>
+        <v>0.2690628218329628</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2953929560348129</v>
+        <v>0.3024767883538066</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.488027808135202</v>
+        <v>0.4828334013834791</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.380002799229847</v>
+        <v>0.3749429978400496</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.4920414145702919</v>
+        <v>0.499547821794505</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6182618871767068</v>
+        <v>0.6116095379798064</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>0.2980839628149102</v>
+        <v>0.294142674768749</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.443065038961885</v>
+        <v>0.4361210000983498</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2926470442439431</v>
+        <v>0.2874801423660134</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3730202636751062</v>
+        <v>0.3751821617515811</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3671108119200195</v>
+        <v>0.3603116155790395</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3556517491031541</v>
+        <v>0.359689239088871</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.2513529726846762</v>
+        <v>0.2468797323861577</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.303702515802753</v>
+        <v>0.3111429213684392</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.2938138776426843</v>
+        <v>0.3011907011408936</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3892239998973958</v>
+        <v>0.3961654856937492</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="C125">
-        <v>0.3092099680832417</v>
+        <v>0.3134466182148659</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3478329241177317</v>
+        <v>0.342136734862397</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4871377865604617</v>
+        <v>0.4807451899551782</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.3938525194351277</v>
+        <v>0.4001678970928536</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="C129">
-        <v>0.3037042938748347</v>
+        <v>0.3099125998636751</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3825613425359978</v>
+        <v>0.3894469532112544</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2764383959962752</v>
+        <v>0.2804274186520376</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3863073099175786</v>
+        <v>0.3796173357941848</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3273585691828883</v>
+        <v>0.3347696416893302</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3158443759614415</v>
+        <v>0.3102427312947497</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3064693984337917</v>
+        <v>0.3019062146639315</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3194130051012417</v>
+        <v>0.3133064625156143</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.4108235170374376</v>
+        <v>0.4047841665743758</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3306564441748294</v>
+        <v>0.325159506303079</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.3664598368705302</v>
+        <v>0.3609386980011886</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3888902046034365</v>
+        <v>0.3815871912847953</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3373697855360028</v>
+        <v>0.3321424374849355</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.376195420254807</v>
+        <v>0.3799615107181262</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3327852545043795</v>
+        <v>0.3271386092600252</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5923083898115646</v>
+        <v>0.5852317188309035</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2851289363188913</v>
+        <v>0.279846014169359</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.3944225923653825</v>
+        <v>0.3893087622887993</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4466487631144404</v>
+        <v>0.4409106181453628</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.290478239670413</v>
+        <v>0.2854098544408822</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3661664212865041</v>
+        <v>0.3696742862894959</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3273724880019563</v>
+        <v>0.3221654973565646</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2476178741233664</v>
+        <v>0.2510026320419595</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6622364804109311</v>
+        <v>0.6554846203592137</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3207570989630888</v>
+        <v>0.324322320390241</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.319483447116808</v>
+        <v>0.3131579978616129</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.276795942865707</v>
+        <v>0.2716387829653236</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3299654188759196</v>
+        <v>0.3343982140637777</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3478579814426823</v>
+        <v>0.3410712640749947</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3848739392250294</v>
+        <v>0.378125301788326</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3958228888096297</v>
+        <v>0.3893192389652128</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3742579644925902</v>
+        <v>0.3687596551317665</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3844444028034739</v>
+        <v>0.3788222234331667</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5578617441402903</v>
+        <v>0.5520622311757521</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.437468459814245</v>
+        <v>0.4306190174323301</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3394461641114359</v>
+        <v>0.3414001082646069</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3458118161371394</v>
+        <v>0.3500149032101144</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.3015967922198849</v>
+        <v>0.3054266314348868</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3545857029046301</v>
+        <v>0.3493770005398228</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5865171673888198</v>
+        <v>0.5800565300469009</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3292977106415327</v>
+        <v>0.3233029034981408</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3496732318784683</v>
+        <v>0.3435238417671229</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7233,7 +7233,7 @@
         <v>44</v>
       </c>
       <c r="C171">
-        <v>0.2532682627418967</v>
+        <v>0.2476626259747402</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.3891790661130516</v>
+        <v>0.3924492019252033</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3098926011244216</v>
+        <v>0.3140708002491386</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3262293288415183</v>
+        <v>0.3210729778298571</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.2905378882138326</v>
+        <v>0.296954372556306</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4007310745244856</v>
+        <v>0.3941697577586928</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.4880322165440201</v>
+        <v>0.4824116306850783</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.3812958509394732</v>
+        <v>0.3878949427505825</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3094030487953465</v>
+        <v>0.3168185681181563</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.341906149937274</v>
+        <v>0.3356929787088834</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3399685674897125</v>
+        <v>0.3347165172461587</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2906770573649118</v>
+        <v>0.2946515649595063</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.2887940055993771</v>
+        <v>0.2837595402332083</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.346426329186201</v>
+        <v>0.3410738888098478</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C185">
-        <v>0.3395315796822979</v>
+        <v>0.3435449026792091</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4032745040960193</v>
+        <v>0.396317050062198</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7505,7 +7505,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2477524961627114</v>
+        <v>0.2541479087104608</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4595780273978522</v>
+        <v>0.4635175332613636</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>10</v>
       </c>
       <c r="C189">
-        <v>0.316018828380405</v>
+        <v>0.3203882589807177</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C190">
-        <v>0.2833018681818847</v>
+        <v>0.2822831693109872</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3479394978446018</v>
+        <v>0.3521507434061753</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.3876274641869539</v>
+        <v>0.3964902438274911</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.399182120208396</v>
+        <v>0.4057296019642586</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.39752728431582</v>
+        <v>0.3899892602319676</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>226</v>
       </c>
       <c r="C195">
-        <v>0.3600212761833992</v>
+        <v>0.3585941378119894</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3439613157861746</v>
+        <v>0.3385529158672433</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3322801107875567</v>
+        <v>0.3362082974653619</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5126754755234557</v>
+        <v>0.5039466792828622</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6046759640194266</v>
+        <v>0.5979674237113757</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3301886570454581</v>
+        <v>0.3382920026221902</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.2990827759577149</v>
+        <v>0.3055768465827172</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3844562944043112</v>
+        <v>0.3879781815218642</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5101673751808098</v>
+        <v>0.503496390786096</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.442422647973388</v>
+        <v>0.4365420742182027</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.439494729714679</v>
+        <v>0.4430512086441332</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.350566121644655</v>
+        <v>0.3585961924944634</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5451189948970628</v>
+        <v>0.5391393915789693</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.3974589327752635</v>
+        <v>0.390215131283338</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.4996830047302218</v>
+        <v>0.5043738416409609</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4036334744276726</v>
+        <v>0.3979926575964651</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.4238697948950082</v>
+        <v>0.4309242946516876</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2863985220557114</v>
+        <v>0.2936996755247407</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3090209911637161</v>
+        <v>0.3167432844714032</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3729547114374185</v>
+        <v>0.3798779038408905</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.4708686385505227</v>
+        <v>0.47371737243909</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3322574301249487</v>
+        <v>0.3399333300571322</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3330062402439348</v>
+        <v>0.3409377732428506</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3403415096227051</v>
+        <v>0.3345165290369346</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4707173427875729</v>
+        <v>0.4635132593149746</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="C220">
-        <v>0.2777223826223104</v>
+        <v>0.2844687352973168</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3454744959447322</v>
+        <v>0.3534901965821448</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3230181423588571</v>
+        <v>0.3166881788281863</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.502981806641476</v>
+        <v>0.5065550126125432</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3205299613974936</v>
+        <v>0.3247016069781652</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3591964308192276</v>
+        <v>0.3675134004405882</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4648967792406267</v>
+        <v>0.4590820578088414</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3432363197673307</v>
+        <v>0.3468517755414227</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4737498489644217</v>
+        <v>0.4691063688641451</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5388739733429568</v>
+        <v>0.5324891763411769</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3586142767157708</v>
+        <v>0.3514037815775791</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3156491705087305</v>
+        <v>0.3092415943072838</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5740347038466673</v>
+        <v>0.5685684322450046</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4092306073881415</v>
+        <v>0.4022266110461384</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4053326350604912</v>
+        <v>0.3995360063711544</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4693287290260539</v>
+        <v>0.4630821156035323</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2802811215348538</v>
+        <v>0.2754530551415825</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3329239407327334</v>
+        <v>0.3367439816201492</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3475044459383709</v>
+        <v>0.3422501839935803</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4269128912951971</v>
+        <v>0.4213089021892727</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.338906794620614</v>
+        <v>0.3380889784946238</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8423,7 +8423,7 @@
         <v>15</v>
       </c>
       <c r="C241">
-        <v>0.2290757654048104</v>
+        <v>0.2348796927206666</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>15</v>
       </c>
       <c r="C242">
-        <v>0.3062284219268624</v>
+        <v>0.3137102454633882</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.454885612229877</v>
+        <v>0.4620882915670713</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.3883656686066478</v>
+        <v>0.3877550658633636</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6158344150167538</v>
+        <v>0.6092195075716241</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4346313479450927</v>
+        <v>0.4286571878236593</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.427887507238831</v>
+        <v>0.4214140907996652</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3573974051655957</v>
+        <v>0.3616567416322681</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4004619134804884</v>
+        <v>0.3948716223250202</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3106250975140731</v>
+        <v>0.3181698845820534</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4226090106454818</v>
+        <v>0.4158658249132765</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4215225194747155</v>
+        <v>0.4163941534667894</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.382588554371605</v>
+        <v>0.3769929265987764</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4927231359650153</v>
+        <v>0.4858114474023756</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.394000685078693</v>
+        <v>0.4031501118849217</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5829025628513484</v>
+        <v>0.5767132258489583</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4104448442511122</v>
+        <v>0.4048790429025711</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4884385667344533</v>
+        <v>0.4817586628290036</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>15</v>
       </c>
       <c r="C259">
-        <v>0.3056783576451451</v>
+        <v>0.3115158620605481</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4111296134823114</v>
+        <v>0.4043464541818809</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4541304462055147</v>
+        <v>0.4478240740533708</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3967896419225956</v>
+        <v>0.3908440583535145</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4440850037294227</v>
+        <v>0.4380200799178905</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4208350352009756</v>
+        <v>0.4146698275273329</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3264423564968075</v>
+        <v>0.3210564140443634</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>226</v>
       </c>
       <c r="C266">
-        <v>0.3159430829103052</v>
+        <v>0.3154284227464472</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>15</v>
       </c>
       <c r="C267">
-        <v>0.2755089011156285</v>
+        <v>0.2821449805332264</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4289243882485121</v>
+        <v>0.4236188547365166</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3829002918592759</v>
+        <v>0.3761356164081675</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5125832658286531</v>
+        <v>0.5055666693844568</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5328330953346908</v>
+        <v>0.5258900442808085</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3390245819778576</v>
+        <v>0.3333166013220894</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.4980316616646574</v>
+        <v>0.4916092655907554</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3350354293870675</v>
+        <v>0.3422731935713</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2457986712639984</v>
+        <v>0.2520881477710521</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.331007249055735</v>
+        <v>0.3263897088562931</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9035,7 +9035,7 @@
         <v>79</v>
       </c>
       <c r="C277">
-        <v>0.3714441004726534</v>
+        <v>0.3756258098929685</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4457316547043956</v>
+        <v>0.4378077956420742</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5531072871100657</v>
+        <v>0.5473617164154592</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4606821497330063</v>
+        <v>0.4551015212523561</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3834631976205587</v>
+        <v>0.3774335549562516</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3694842448143066</v>
+        <v>0.3780005656069831</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3649579858652059</v>
+        <v>0.3592295196951494</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3102315635695568</v>
+        <v>0.3049301971743907</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2622238231942537</v>
+        <v>0.2676159767290468</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.2840748879584387</v>
+        <v>0.2788504355936055</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4484137505863382</v>
+        <v>0.4423559828411552</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C288">
-        <v>0.2395450966119924</v>
+        <v>0.2422591955700356</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>6</v>
       </c>
       <c r="C289">
-        <v>0.3467634249732602</v>
+        <v>0.3413457518537069</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3160528852547545</v>
+        <v>0.323610437904996</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4049112517298866</v>
+        <v>0.3987297717071052</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9290,7 +9290,7 @@
         <v>79</v>
       </c>
       <c r="C292">
-        <v>0.4555937686836316</v>
+        <v>0.4603820717038807</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5947141170621938</v>
+        <v>0.5884672169145735</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3770069112290163</v>
+        <v>0.3837673620139996</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3510224826235235</v>
+        <v>0.3552569073940873</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.3164229121591852</v>
+        <v>0.324109133052759</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4532617242888282</v>
+        <v>0.458063770466769</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3886282450458986</v>
+        <v>0.391474455695329</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2838580747866252</v>
+        <v>0.2777329682249277</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3377928600746522</v>
+        <v>0.3418429157854573</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3448694472501815</v>
+        <v>0.3396276119341169</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.5237186359847206</v>
+        <v>0.5167856765101565</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3049412782764863</v>
+        <v>0.3084731889800953</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2892028396466185</v>
+        <v>0.2931651265117198</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4365431123856792</v>
+        <v>0.4297559983785948</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.3906402045818572</v>
+        <v>0.397253827593232</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4434502204524501</v>
+        <v>0.4368927892552605</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3927262352596316</v>
+        <v>0.3869954761823061</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2710282464200494</v>
+        <v>0.2665399812237024</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3856299578454766</v>
+        <v>0.3807286001723058</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3463238132394398</v>
+        <v>0.3544954915466785</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2791512116982955</v>
+        <v>0.2860042120013992</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3227659119270788</v>
+        <v>0.3168578844143411</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3170739480860267</v>
+        <v>0.3213343623006783</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4832729498218137</v>
+        <v>0.4765424041988413</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3903918854702347</v>
+        <v>0.3847335900309929</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5236021619857196</v>
+        <v>0.5169264641012745</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5281783017229182</v>
+        <v>0.5218847405781213</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.338739356253855</v>
+        <v>0.3334447854042586</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.266675277045067</v>
+        <v>0.2733212584176998</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3302699833478307</v>
+        <v>0.3247656424633246</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.355723976874564</v>
+        <v>0.3501588402622776</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3792491882813597</v>
+        <v>0.382704521098798</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3854939415710883</v>
+        <v>0.3789307710748647</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>15</v>
       </c>
       <c r="C325">
-        <v>0.2351247216248196</v>
+        <v>0.241169899326524</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3649674143512009</v>
+        <v>0.358322435786918</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3350646562693455</v>
+        <v>0.3280471108953001</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2814648529342331</v>
+        <v>0.2880889412741522</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>10</v>
       </c>
       <c r="C329">
-        <v>0.3067171671764445</v>
+        <v>0.3103389307610689</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C330">
-        <v>0.30456355615769</v>
+        <v>0.303564513364857</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.390226283809365</v>
+        <v>0.3932657363250261</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3531535793098539</v>
+        <v>0.3574191259163707</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.4686948107645164</v>
+        <v>0.462212422289032</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>15</v>
       </c>
       <c r="C334">
-        <v>0.2859218236294512</v>
+        <v>0.2928893048029497</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>44</v>
       </c>
       <c r="C335">
-        <v>0.3397541620791251</v>
+        <v>0.3330036444689364</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>15</v>
       </c>
       <c r="C336">
-        <v>0.2995931612904237</v>
+        <v>0.3071478944191704</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4622755374091589</v>
+        <v>0.4551811233548003</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.2829203600550356</v>
+        <v>0.2866229274394441</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4451447727149642</v>
+        <v>0.4527299190962443</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3097723982115085</v>
+        <v>0.3172044835941235</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2953885194297042</v>
+        <v>0.2909474539248448</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2605321285832493</v>
+        <v>0.2640161055162293</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.397371588119501</v>
+        <v>0.4014942219396792</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2904355291377471</v>
+        <v>0.2973272729459644</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.356710221420408</v>
+        <v>0.3510444333269421</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3309951433400266</v>
+        <v>0.3344138609692857</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.338436784754342</v>
+        <v>0.3463258315754877</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3158212808649553</v>
+        <v>0.3105467991993697</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.47487676323518</v>
+        <v>0.4675978952908086</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3590971146178216</v>
+        <v>0.3655787079079476</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10293,7 +10293,7 @@
         <v>79</v>
       </c>
       <c r="C351">
-        <v>0.2642247922079262</v>
+        <v>0.2672546550963665</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.3948016985990453</v>
+        <v>0.4029182461032711</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3883712924044244</v>
+        <v>0.3916219437852297</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2810902780901962</v>
+        <v>0.2760623433361764</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3554152826388386</v>
+        <v>0.3496721059499771</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.307968115270974</v>
+        <v>0.3027760850048895</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.3941943956467352</v>
+        <v>0.3885803887096927</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3130519577402617</v>
+        <v>0.3078186310040785</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4681872248103757</v>
+        <v>0.4620735949476567</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4737435417093092</v>
+        <v>0.4662677113038008</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3126132300093546</v>
+        <v>0.3202243543843178</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3564113051451503</v>
+        <v>0.3513529340615593</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2933808753130011</v>
+        <v>0.2975540643573028</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3205808864731204</v>
+        <v>0.3244242504063273</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3030301700961534</v>
+        <v>0.3106792268827239</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2644699477838249</v>
+        <v>0.2710777081263618</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.304365124184993</v>
+        <v>0.2991471949989479</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3095336448450537</v>
+        <v>0.3163943049112177</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4875867554097122</v>
+        <v>0.4814917834201249</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3323845458652118</v>
+        <v>0.3401530633547369</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4457141240823744</v>
+        <v>0.4402213555880974</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3539352682045122</v>
+        <v>0.3486823641823614</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4249374376961623</v>
+        <v>0.4195367561618498</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4720798375874312</v>
+        <v>0.4661529301689115</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4555900853427389</v>
+        <v>0.4494777979918227</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.3629999778968403</v>
+        <v>0.3704033598968718</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4567448039682038</v>
+        <v>0.4514120548242644</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3080633197555632</v>
+        <v>0.3030019399182439</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3539615283412253</v>
+        <v>0.348710111280798</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3519325756600939</v>
+        <v>0.3465548934510516</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4364045521835532</v>
+        <v>0.4394520384681703</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3227728322867317</v>
+        <v>0.3178486358672271</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3781197802708273</v>
+        <v>0.3822499461468807</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4278170493529366</v>
+        <v>0.4220068403288894</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.391686640606782</v>
+        <v>0.3863572902023372</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3117778107417683</v>
+        <v>0.3193511470050998</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4234018069345032</v>
+        <v>0.4245822183945224</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.351608630271677</v>
+        <v>0.3458505371143464</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3418725369184407</v>
+        <v>0.3364639549806435</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3233872560716411</v>
+        <v>0.3302825115908661</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3421651791768209</v>
+        <v>0.3496649885373304</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3044480552241149</v>
+        <v>0.3086080280739411</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4019075218317986</v>
+        <v>0.4058114419028353</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3638669385070762</v>
+        <v>0.3719664544311484</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3955520565672337</v>
+        <v>0.3993610759333287</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.389436224968346</v>
+        <v>0.3838517209448933</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3640764523006944</v>
+        <v>0.3678178017036466</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4747689325169223</v>
+        <v>0.4678478171813533</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3485785717725723</v>
+        <v>0.3562322581521316</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3361622375198715</v>
+        <v>0.3307841127960584</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4231039616552564</v>
+        <v>0.4298958506327907</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3922014588102881</v>
+        <v>0.387466841213626</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2770738323044247</v>
+        <v>0.2721518461063179</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.3002834904502956</v>
+        <v>0.3041318444700312</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4199772982213539</v>
+        <v>0.4143354707773915</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>79</v>
       </c>
       <c r="C406">
-        <v>0.4734865417259063</v>
+        <v>0.4780519663820634</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3675237083027506</v>
+        <v>0.3635896423577388</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4747755596788322</v>
+        <v>0.4689042637472415</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4676092643078792</v>
+        <v>0.4623873146350835</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3152442754679363</v>
+        <v>0.3227983731472718</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3167146835907402</v>
+        <v>0.3209494341528195</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4527464665662591</v>
+        <v>0.4476124404305162</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>15</v>
       </c>
       <c r="C413">
-        <v>0.2599746949428018</v>
+        <v>0.2665056905398744</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3141888283889567</v>
+        <v>0.3216727816378716</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3430009230556839</v>
+        <v>0.3508259138972202</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.3801289341864169</v>
+        <v>0.386406248961731</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11412,10 +11412,10 @@
         <v>842</v>
       </c>
       <c r="B417" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C417">
-        <v>0.2590455939838325</v>
+        <v>0.2559579210457664</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.3004076177008029</v>
+        <v>0.304150820593802</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.3470532152511466</v>
+        <v>0.3552474690476196</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.3936758419397943</v>
+        <v>0.3865356817302836</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.3919434692621153</v>
+        <v>0.3844685121873515</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3542078614588216</v>
+        <v>0.3490246516184218</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4602221205321659</v>
+        <v>0.4532970583205719</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3099895462329984</v>
+        <v>0.3134398456111477</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3326728646212059</v>
+        <v>0.3274565535126261</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3495550067949087</v>
+        <v>0.3575729222747163</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.2713080241959008</v>
+        <v>0.2777244064448509</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2755651830629051</v>
+        <v>0.2824056548021234</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3234327562281284</v>
+        <v>0.3275507350530543</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3449146338308048</v>
+        <v>0.3389406708068116</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C431">
-        <v>0.2794464705462866</v>
+        <v>0.279490772283341</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3255604607681911</v>
+        <v>0.3329611991718113</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3234099485347198</v>
+        <v>0.3181164198473584</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3528339415900539</v>
+        <v>0.3612015824491683</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3564235975220453</v>
+        <v>0.3607037075468528</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3371713243751752</v>
+        <v>0.3445444600613159</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3077869001319014</v>
+        <v>0.3118456619154692</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.344855973103392</v>
+        <v>0.3527890693549495</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3510371931809452</v>
+        <v>0.3453402183559093</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3481769249373199</v>
+        <v>0.3521124251633238</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.305397406661855</v>
+        <v>0.2990966219178311</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.2843055716602412</v>
+        <v>0.2790203966326534</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.2939120166081285</v>
+        <v>0.3010060331429905</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3295198968480662</v>
+        <v>0.3330649073930068</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3488796534375608</v>
+        <v>0.3420418272584687</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3430065172344442</v>
+        <v>0.3374788685406973</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2878841212500933</v>
+        <v>0.2946069281150356</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.356883572169119</v>
+        <v>0.3514065575855496</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.386391610807334</v>
+        <v>0.3814441365244088</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.373787798640506</v>
+        <v>0.3670632739717443</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4064917566947878</v>
+        <v>0.3997611545192093</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12007,10 +12007,10 @@
         <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C452">
-        <v>0.2772465867589065</v>
+        <v>0.2830767658448352</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3428880998762383</v>
+        <v>0.347298784867131</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.2865574560430217</v>
+        <v>0.2932673916038284</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3305630826868569</v>
+        <v>0.3346701683202167</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3514285972298866</v>
+        <v>0.3453306582763442</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.339539929715512</v>
+        <v>0.3456525199507995</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3902649138715188</v>
+        <v>0.3837823924339293</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3642761759508351</v>
+        <v>0.3584356564984703</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3359747315219174</v>
+        <v>0.3296617447507984</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3211590344645533</v>
+        <v>0.3156494145243769</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3421489117750018</v>
+        <v>0.3366276449093441</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.2952972286515756</v>
+        <v>0.3029294804444634</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.39519309835755</v>
+        <v>0.3892238615395494</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3983016953197909</v>
+        <v>0.3917201964158781</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5182765213271876</v>
+        <v>0.5113761309580195</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.460207570424539</v>
+        <v>0.4540924880878452</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3887450159520556</v>
+        <v>0.3832203061706804</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2939305525172114</v>
+        <v>0.3010656078365986</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>15</v>
       </c>
       <c r="C470">
-        <v>0.2980702644970674</v>
+        <v>0.30492009899508</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3027872227097334</v>
+        <v>0.3063868743444489</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3350077017411019</v>
+        <v>0.3426464218707992</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3079533124722368</v>
+        <v>0.3079660108313291</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3696583106595751</v>
+        <v>0.3734213557773237</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3347417781595635</v>
+        <v>0.3285555596860554</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3488151157305164</v>
+        <v>0.3433783177219141</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3490191662915159</v>
+        <v>0.3527828011257783</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.3891752972780927</v>
+        <v>0.3842315650982783</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4105088128207801</v>
+        <v>0.4031350724137019</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4518703500201768</v>
+        <v>0.4462113965058892</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3988185960222921</v>
+        <v>0.3914443569133633</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3079810461872419</v>
+        <v>0.3121202415180426</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.2989840889879922</v>
+        <v>0.3030245569257389</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3832534438453517</v>
+        <v>0.3762491509180237</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3523074986335054</v>
+        <v>0.3586316417074126</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.3875622742744171</v>
+        <v>0.3942896434549302</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4734990530217132</v>
+        <v>0.4659008229636533</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3169522766883882</v>
+        <v>0.3207534955055301</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4753256113258356</v>
+        <v>0.4684696547005462</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3091738458265771</v>
+        <v>0.3160122513869029</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>15</v>
       </c>
       <c r="C491">
-        <v>0.2753347359873742</v>
+        <v>0.282229769632438</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4891186703771651</v>
+        <v>0.4816447216897343</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.2873029181160376</v>
+        <v>0.2824388482274733</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3368046333476345</v>
+        <v>0.3395742808273076</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5208070855259753</v>
+        <v>0.5145593817434271</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4726417802072567</v>
+        <v>0.4673355685218653</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3335268738161581</v>
+        <v>0.3377770064857819</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6720556089840504</v>
+        <v>0.6674392708877078</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3413748214154109</v>
+        <v>0.3493457199681903</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4134403431038555</v>
+        <v>0.4073105319107444</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.3853670661997149</v>
+        <v>0.39172055353376</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.579504169074729</v>
+        <v>0.5730408842705578</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3581376405870803</v>
+        <v>0.3655606524778894</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3265430554458331</v>
+        <v>0.3344878559947604</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4309685790691669</v>
+        <v>0.4253265646279834</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.501627331864519</v>
+        <v>0.5090580303004499</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.3063911894040673</v>
+        <v>0.3101365078886263</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3150349927072103</v>
+        <v>0.3221276633204012</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4879475914876307</v>
+        <v>0.4910548432855799</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3674597275003224</v>
+        <v>0.3719342359686852</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3471727741807976</v>
+        <v>0.3413627463145065</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3012306087707559</v>
+        <v>0.2962241248477734</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3659541671924843</v>
+        <v>0.3590441069850307</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.4172677685947335</v>
+        <v>0.410842507587753</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4662328629128423</v>
+        <v>0.4596814451374978</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>15</v>
       </c>
       <c r="C516">
-        <v>0.317777724825319</v>
+        <v>0.3252376641704987</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3375680428680898</v>
+        <v>0.3457148110068663</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3279940135209331</v>
+        <v>0.3319665751069916</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5022944620691857</v>
+        <v>0.4952779844488593</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3268076278569762</v>
+        <v>0.3343675507887386</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3018259789239875</v>
+        <v>0.3057240332272759</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3614240135696991</v>
+        <v>0.3681208330858352</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4312593037773295</v>
+        <v>0.4259041796993562</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2802994338107743</v>
+        <v>0.2751776470461191</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4039219142030415</v>
+        <v>0.397757105537638</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4203911405725111</v>
+        <v>0.4133676839611221</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3643174094899185</v>
+        <v>0.3686957927585725</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4353645014248509</v>
+        <v>0.4292171306739597</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.337058088201249</v>
+        <v>0.3405249283261827</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4886113406620538</v>
+        <v>0.4812428778763264</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5565225666240617</v>
+        <v>0.5495625495065581</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C532">
-        <v>0.270607236292422</v>
+        <v>0.2678548310596582</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.433769218353064</v>
+        <v>0.4401964306260909</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.3227670431782358</v>
+        <v>0.3289110514158071</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3129376842292733</v>
+        <v>0.3077034159069985</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.30624507450543</v>
+        <v>0.3139258601880067</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3673641661712518</v>
+        <v>0.3617746537448041</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2838229755638133</v>
+        <v>0.2911083821747393</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
         <v>1086</v>
       </c>
       <c r="B539" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C539">
-        <v>0.2918867662571139</v>
+        <v>0.2890131001803555</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2853133402803443</v>
+        <v>0.2920627763083262</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4334289341446497</v>
+        <v>0.4276600833826822</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3911553019170018</v>
+        <v>0.3840765342049579</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3996966038360104</v>
+        <v>0.3933153211076005</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3349311356381527</v>
+        <v>0.3296046400563991</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2885933316994441</v>
+        <v>0.2825145550332216</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3315649768845428</v>
+        <v>0.3326470726566873</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2768116298207039</v>
+        <v>0.2767102227383172</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3721600528440104</v>
+        <v>0.3696006753066093</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4010091839065414</v>
+        <v>0.3932226175754304</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3700802454722817</v>
+        <v>0.3660396986876603</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2628339130924623</v>
+        <v>0.2597804062544701</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2889453147854109</v>
+        <v>0.2847694407499272</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2821704816738212</v>
+        <v>0.279111681997177</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.2769585454267521</v>
+        <v>0.2719369941301639</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3257372872698618</v>
+        <v>0.3199991504770234</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3217147710987504</v>
+        <v>0.3107302264252313</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3642658739486872</v>
+        <v>0.3669250325358958</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3912054249005278</v>
+        <v>0.3785058952717061</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2824751051595559</v>
+        <v>0.3015655661956503</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3871865325510653</v>
+        <v>0.3819813955196033</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3181505328096915</v>
+        <v>0.3138353810690899</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3190705384117182</v>
+        <v>0.3178558726104788</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.48917132173675</v>
+        <v>0.4898225043811229</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3099314973130384</v>
+        <v>0.3069733337969863</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3731458113232022</v>
+        <v>0.3683584748256013</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3045504532604373</v>
+        <v>0.3013351697430424</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.423057064225317</v>
+        <v>0.4083327607031286</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.3148847258125221</v>
+        <v>0.3008054465892636</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.257455862911814</v>
+        <v>0.2858500642732822</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3355688626607655</v>
+        <v>0.325171024990202</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>1143</v>
       </c>
       <c r="C589">
-        <v>0.3355929001299688</v>
+        <v>0.3393589443667762</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.3649957749395182</v>
+        <v>0.385366737919478</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5402657598545296</v>
+        <v>0.5393213376485435</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.4115766548785516</v>
+        <v>0.4159838557158766</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.654280612673072</v>
+        <v>0.6558457689044063</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4377516740103888</v>
+        <v>0.4323160193782327</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14384,10 +14384,10 @@
         <v>1208</v>
       </c>
       <c r="B595" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3039499742554594</v>
+        <v>0.3007109193839573</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4475317175746929</v>
+        <v>0.436002935663695</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14418,10 +14418,10 @@
         <v>1212</v>
       </c>
       <c r="B597" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3076705088026271</v>
+        <v>0.320323679383744</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C598">
-        <v>0.2402471877693405</v>
+        <v>0.2369305280610853</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2646379319913028</v>
+        <v>0.262048740484529</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2771610247900749</v>
+        <v>0.2742453351379144</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>1143</v>
       </c>
       <c r="C601">
-        <v>0.2473401347347008</v>
+        <v>0.242944303401476</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3611239408328594</v>
+        <v>0.3603223615600438</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2868291575936334</v>
+        <v>0.2845776645230053</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.292357712634558</v>
+        <v>0.3130848833601909</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2787428681373357</v>
+        <v>0.2652879260965629</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3580562574496187</v>
+        <v>0.3546178559487202</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3251581885714173</v>
+        <v>0.3243076920493616</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.2917836836437709</v>
+        <v>0.3067845256022596</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2855123348673395</v>
+        <v>0.2809127536694294</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14642,7 +14642,7 @@
         <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2430071427574336</v>
+        <v>0.2405645277382739</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4573981080354651</v>
+        <v>0.4448754641887904</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3030608734483931</v>
+        <v>0.2889917162793297</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3446206779189034</v>
+        <v>0.3414667532788234</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4271669901480344</v>
+        <v>0.4221697187448215</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3296201299049334</v>
+        <v>0.3295598156334839</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4387138791988515</v>
+        <v>0.4306697553469792</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3383794303861106</v>
+        <v>0.3319983589359958</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.320709550861998</v>
+        <v>0.3182352833574913</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4569990307010543</v>
+        <v>0.4403718284674818</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>149</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2825145550332216</v>
+        <v>0.2884541338878192</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3326470726566873</v>
+        <v>0.3172809661289639</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2767102227383172</v>
+        <v>0.2773377677243735</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3696006753066093</v>
+        <v>0.368342835975275</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.3932226175754304</v>
+        <v>0.3884101799882506</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3660396986876603</v>
+        <v>0.379371034479448</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2597804062544701</v>
+        <v>0.2600739576711865</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2847694407499272</v>
+        <v>0.2905986252948766</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.279111681997177</v>
+        <v>0.2806108459847001</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13996,7 +13996,7 @@
         <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.2719369941301639</v>
+        <v>0.2605653666914444</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3199991504770234</v>
+        <v>0.3248891226638706</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3107302264252313</v>
+        <v>0.3334316793337581</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3669250325358958</v>
+        <v>0.3508593410760105</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3785058952717061</v>
+        <v>0.3744840800853754</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3015655661956503</v>
+        <v>0.2778650220807022</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3819813955196033</v>
+        <v>0.3722366567780488</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3138353810690899</v>
+        <v>0.314444678161674</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3178558726104788</v>
+        <v>0.3351580348578205</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4898225043811229</v>
+        <v>0.446050854412754</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3069733337969863</v>
+        <v>0.3078860993807473</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3683584748256013</v>
+        <v>0.3653731380049468</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3013351697430424</v>
+        <v>0.3014934763097268</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.4083327607031286</v>
+        <v>0.4162026741118093</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.3008054465892636</v>
+        <v>0.2950762094740955</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2858500642732822</v>
+        <v>0.2645086405681463</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.325171024990202</v>
+        <v>0.3199422265530663</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14282,10 +14282,10 @@
         <v>1196</v>
       </c>
       <c r="B589" t="s">
-        <v>1143</v>
+        <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3393589443667762</v>
+        <v>0.3390551340189545</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.385366737919478</v>
+        <v>0.3763925756754392</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5393213376485435</v>
+        <v>0.5095298202222793</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.4159838557158766</v>
+        <v>0.3989612299461182</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6558457689044063</v>
+        <v>0.6582965010277916</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4323160193782327</v>
+        <v>0.4221439994881752</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3007109193839573</v>
+        <v>0.2918106303385109</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.436002935663695</v>
+        <v>0.4301576463632634</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="C597">
-        <v>0.320323679383744</v>
+        <v>0.3044024203225391</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2369305280610853</v>
+        <v>0.2643341994591614</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.262048740484529</v>
+        <v>0.2648504330079637</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2742453351379144</v>
+        <v>0.2761861474128283</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14486,10 +14486,10 @@
         <v>1220</v>
       </c>
       <c r="B601" t="s">
-        <v>1143</v>
+        <v>44</v>
       </c>
       <c r="C601">
-        <v>0.242944303401476</v>
+        <v>0.2572228456529158</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3603223615600438</v>
+        <v>0.3613122234337758</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2845776645230053</v>
+        <v>0.2855076528078401</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3130848833601909</v>
+        <v>0.2956557260375929</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2652879260965629</v>
+        <v>0.2914120289876425</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3546178559487202</v>
+        <v>0.3451617870106473</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3243076920493616</v>
+        <v>0.31832864658203</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.3067845256022596</v>
+        <v>0.2832507191971311</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14625,7 +14625,7 @@
         <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2809127536694294</v>
+        <v>0.2805570156583798</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C610">
-        <v>0.2405645277382739</v>
+        <v>0.2582097621665965</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4448754641887904</v>
+        <v>0.4919645159808907</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.2889917162793297</v>
+        <v>0.3151492916956965</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3414667532788234</v>
+        <v>0.3360888701446423</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4221697187448215</v>
+        <v>0.4207979427071842</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3295598156334839</v>
+        <v>0.3222503224022803</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4306697553469792</v>
+        <v>0.4158551996754468</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3319983589359958</v>
+        <v>0.3297967013232817</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3182352833574913</v>
+        <v>0.3389721578373202</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4403718284674818</v>
+        <v>0.4461214753089645</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14812,7 +14812,7 @@
         <v>6</v>
       </c>
       <c r="C620">
-        <v>0.3104029982406734</v>
+        <v>0.3125307121551915</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3344987369481774</v>
+        <v>0.3507400549922038</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14846,7 +14846,7 @@
         <v>6</v>
       </c>
       <c r="C622">
-        <v>0.2711105195139781</v>
+        <v>0.2761082774659481</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14860,10 +14860,10 @@
         <v>1265</v>
       </c>
       <c r="B623" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C623">
-        <v>0.1998650128147459</v>
+        <v>0.2000750633796806</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
@@ -14880,7 +14880,7 @@
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2897594197377535</v>
+        <v>0.2883252241547618</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
@@ -14897,7 +14897,7 @@
         <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2436249891084367</v>
+        <v>0.2396158513481142</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
@@ -14914,7 +14914,7 @@
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3103934258040722</v>
+        <v>0.3273877094251895</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
@@ -14931,7 +14931,7 @@
         <v>1274</v>
       </c>
       <c r="C627">
-        <v>0.2811903929356518</v>
+        <v>0.2907155384419668</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14948,7 +14948,7 @@
         <v>6</v>
       </c>
       <c r="C628">
-        <v>0.2167647871252837</v>
+        <v>0.2316826523207751</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14965,7 +14965,7 @@
         <v>6</v>
       </c>
       <c r="C629">
-        <v>0.265397913992652</v>
+        <v>0.2740322105859919</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14982,7 +14982,7 @@
         <v>1274</v>
       </c>
       <c r="C630">
-        <v>0.293666246412662</v>
+        <v>0.3249190296566286</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14999,7 +14999,7 @@
         <v>1274</v>
       </c>
       <c r="C631">
-        <v>0.3052227366862181</v>
+        <v>0.3213592118476376</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15016,7 +15016,7 @@
         <v>1274</v>
       </c>
       <c r="C632">
-        <v>0.3789411780583819</v>
+        <v>0.3899411003422587</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2604602991478561</v>
+        <v>0.2754347631658899</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.3733070460900481</v>
+        <v>0.4043783090255618</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15067,7 +15067,7 @@
         <v>1274</v>
       </c>
       <c r="C635">
-        <v>0.401939843668326</v>
+        <v>0.4224469967081615</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.384706885807842</v>
+        <v>0.395115115047224</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15101,7 +15101,7 @@
         <v>15</v>
       </c>
       <c r="C637">
-        <v>0.2688666004105387</v>
+        <v>0.2847717563531478</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15118,7 +15118,7 @@
         <v>1274</v>
       </c>
       <c r="C638">
-        <v>0.4059303674170687</v>
+        <v>0.423901360193371</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3509843947032604</v>
+        <v>0.3465188860892308</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2825080544759188</v>
+        <v>0.2833597484023196</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15169,7 +15169,7 @@
         <v>15</v>
       </c>
       <c r="C641">
-        <v>0.2549091824216865</v>
+        <v>0.2671652083472434</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15186,7 +15186,7 @@
         <v>1274</v>
       </c>
       <c r="C642">
-        <v>0.2719646899842941</v>
+        <v>0.2829886519524138</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.2914348283479374</v>
+        <v>0.3012074692481571</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.264832382107491</v>
+        <v>0.2812053685863024</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2484083793559056</v>
+        <v>0.2554459886194498</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3365939816540054</v>
+        <v>0.3645766184623316</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15271,7 +15271,7 @@
         <v>6</v>
       </c>
       <c r="C647">
-        <v>0.2877847868598161</v>
+        <v>0.2909655313496472</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2607515713142328</v>
+        <v>0.2818035307281975</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.3028602240440963</v>
+        <v>0.3285805759841801</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15322,7 +15322,7 @@
         <v>6</v>
       </c>
       <c r="C650">
-        <v>0.2571398045357967</v>
+        <v>0.2635631244085863</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.2892728605372195</v>
+        <v>0.3081560486231352</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,7 +15371,7 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,7 +15379,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -62,27 +62,27 @@
     <t>amber valley</t>
   </si>
   <si>
+    <t>E14001066</t>
+  </si>
+  <si>
+    <t>arundel and south downs</t>
+  </si>
+  <si>
+    <t>E14001067</t>
+  </si>
+  <si>
+    <t>ashfield</t>
+  </si>
+  <si>
+    <t>E14001068</t>
+  </si>
+  <si>
+    <t>ashford</t>
+  </si>
+  <si>
     <t>Brexit Party/Reform UK</t>
   </si>
   <si>
-    <t>E14001066</t>
-  </si>
-  <si>
-    <t>arundel and south downs</t>
-  </si>
-  <si>
-    <t>E14001067</t>
-  </si>
-  <si>
-    <t>ashfield</t>
-  </si>
-  <si>
-    <t>E14001068</t>
-  </si>
-  <si>
-    <t>ashford</t>
-  </si>
-  <si>
     <t>E14001069</t>
   </si>
   <si>
@@ -254,207 +254,210 @@
     <t>birmingham northfield</t>
   </si>
   <si>
+    <t>E14001097</t>
+  </si>
+  <si>
+    <t>birmingham perry barr</t>
+  </si>
+  <si>
+    <t>E14001098</t>
+  </si>
+  <si>
+    <t>birmingham selly oak</t>
+  </si>
+  <si>
+    <t>E14001099</t>
+  </si>
+  <si>
+    <t>birmingham yardley</t>
+  </si>
+  <si>
+    <t>E14001100</t>
+  </si>
+  <si>
+    <t>bishop auckland</t>
+  </si>
+  <si>
+    <t>E14001101</t>
+  </si>
+  <si>
+    <t>blackburn</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>E14001102</t>
+  </si>
+  <si>
+    <t>blackley and middleton south</t>
+  </si>
+  <si>
+    <t>E14001103</t>
+  </si>
+  <si>
+    <t>blackpool north and fleetwood</t>
+  </si>
+  <si>
+    <t>E14001104</t>
+  </si>
+  <si>
+    <t>blackpool south</t>
+  </si>
+  <si>
+    <t>E14001105</t>
+  </si>
+  <si>
+    <t>blaydon and consett</t>
+  </si>
+  <si>
+    <t>E14001106</t>
+  </si>
+  <si>
+    <t>blyth and ashington</t>
+  </si>
+  <si>
+    <t>E14001107</t>
+  </si>
+  <si>
+    <t>bognor regis and littlehampton</t>
+  </si>
+  <si>
+    <t>E14001108</t>
+  </si>
+  <si>
+    <t>bolsover</t>
+  </si>
+  <si>
+    <t>E14001109</t>
+  </si>
+  <si>
+    <t>bolton north east</t>
+  </si>
+  <si>
+    <t>E14001110</t>
+  </si>
+  <si>
+    <t>bolton south and walkden</t>
+  </si>
+  <si>
+    <t>E14001111</t>
+  </si>
+  <si>
+    <t>bolton west</t>
+  </si>
+  <si>
+    <t>E14001112</t>
+  </si>
+  <si>
+    <t>bootle</t>
+  </si>
+  <si>
+    <t>E14001113</t>
+  </si>
+  <si>
+    <t>boston and skegness</t>
+  </si>
+  <si>
+    <t>E14001114</t>
+  </si>
+  <si>
+    <t>bournemouth east</t>
+  </si>
+  <si>
+    <t>E14001115</t>
+  </si>
+  <si>
+    <t>bournemouth west</t>
+  </si>
+  <si>
+    <t>E14001116</t>
+  </si>
+  <si>
+    <t>bracknell</t>
+  </si>
+  <si>
+    <t>E14001117</t>
+  </si>
+  <si>
+    <t>bradford east</t>
+  </si>
+  <si>
+    <t>E14001118</t>
+  </si>
+  <si>
+    <t>bradford south</t>
+  </si>
+  <si>
+    <t>E14001119</t>
+  </si>
+  <si>
+    <t>bradford west</t>
+  </si>
+  <si>
+    <t>E14001120</t>
+  </si>
+  <si>
+    <t>braintree</t>
+  </si>
+  <si>
+    <t>E14001121</t>
+  </si>
+  <si>
+    <t>brent east</t>
+  </si>
+  <si>
+    <t>E14001122</t>
+  </si>
+  <si>
+    <t>brent west</t>
+  </si>
+  <si>
+    <t>E14001123</t>
+  </si>
+  <si>
+    <t>brentford and isleworth</t>
+  </si>
+  <si>
+    <t>E14001124</t>
+  </si>
+  <si>
+    <t>brentwood and ongar</t>
+  </si>
+  <si>
+    <t>E14001125</t>
+  </si>
+  <si>
+    <t>bridgwater</t>
+  </si>
+  <si>
+    <t>E14001126</t>
+  </si>
+  <si>
+    <t>bridlington and the wolds</t>
+  </si>
+  <si>
+    <t>E14001127</t>
+  </si>
+  <si>
+    <t>brigg and immingham</t>
+  </si>
+  <si>
+    <t>E14001128</t>
+  </si>
+  <si>
+    <t>brighton kemptown and peacehaven</t>
+  </si>
+  <si>
+    <t>E14001129</t>
+  </si>
+  <si>
+    <t>brighton pavilion</t>
+  </si>
+  <si>
     <t>Green Party</t>
   </si>
   <si>
-    <t>E14001097</t>
-  </si>
-  <si>
-    <t>birmingham perry barr</t>
-  </si>
-  <si>
-    <t>E14001098</t>
-  </si>
-  <si>
-    <t>birmingham selly oak</t>
-  </si>
-  <si>
-    <t>E14001099</t>
-  </si>
-  <si>
-    <t>birmingham yardley</t>
-  </si>
-  <si>
-    <t>E14001100</t>
-  </si>
-  <si>
-    <t>bishop auckland</t>
-  </si>
-  <si>
-    <t>E14001101</t>
-  </si>
-  <si>
-    <t>blackburn</t>
-  </si>
-  <si>
-    <t>E14001102</t>
-  </si>
-  <si>
-    <t>blackley and middleton south</t>
-  </si>
-  <si>
-    <t>E14001103</t>
-  </si>
-  <si>
-    <t>blackpool north and fleetwood</t>
-  </si>
-  <si>
-    <t>E14001104</t>
-  </si>
-  <si>
-    <t>blackpool south</t>
-  </si>
-  <si>
-    <t>E14001105</t>
-  </si>
-  <si>
-    <t>blaydon and consett</t>
-  </si>
-  <si>
-    <t>E14001106</t>
-  </si>
-  <si>
-    <t>blyth and ashington</t>
-  </si>
-  <si>
-    <t>E14001107</t>
-  </si>
-  <si>
-    <t>bognor regis and littlehampton</t>
-  </si>
-  <si>
-    <t>E14001108</t>
-  </si>
-  <si>
-    <t>bolsover</t>
-  </si>
-  <si>
-    <t>E14001109</t>
-  </si>
-  <si>
-    <t>bolton north east</t>
-  </si>
-  <si>
-    <t>E14001110</t>
-  </si>
-  <si>
-    <t>bolton south and walkden</t>
-  </si>
-  <si>
-    <t>E14001111</t>
-  </si>
-  <si>
-    <t>bolton west</t>
-  </si>
-  <si>
-    <t>E14001112</t>
-  </si>
-  <si>
-    <t>bootle</t>
-  </si>
-  <si>
-    <t>E14001113</t>
-  </si>
-  <si>
-    <t>boston and skegness</t>
-  </si>
-  <si>
-    <t>E14001114</t>
-  </si>
-  <si>
-    <t>bournemouth east</t>
-  </si>
-  <si>
-    <t>E14001115</t>
-  </si>
-  <si>
-    <t>bournemouth west</t>
-  </si>
-  <si>
-    <t>E14001116</t>
-  </si>
-  <si>
-    <t>bracknell</t>
-  </si>
-  <si>
-    <t>E14001117</t>
-  </si>
-  <si>
-    <t>bradford east</t>
-  </si>
-  <si>
-    <t>E14001118</t>
-  </si>
-  <si>
-    <t>bradford south</t>
-  </si>
-  <si>
-    <t>E14001119</t>
-  </si>
-  <si>
-    <t>bradford west</t>
-  </si>
-  <si>
-    <t>E14001120</t>
-  </si>
-  <si>
-    <t>braintree</t>
-  </si>
-  <si>
-    <t>E14001121</t>
-  </si>
-  <si>
-    <t>brent east</t>
-  </si>
-  <si>
-    <t>E14001122</t>
-  </si>
-  <si>
-    <t>brent west</t>
-  </si>
-  <si>
-    <t>E14001123</t>
-  </si>
-  <si>
-    <t>brentford and isleworth</t>
-  </si>
-  <si>
-    <t>E14001124</t>
-  </si>
-  <si>
-    <t>brentwood and ongar</t>
-  </si>
-  <si>
-    <t>E14001125</t>
-  </si>
-  <si>
-    <t>bridgwater</t>
-  </si>
-  <si>
-    <t>E14001126</t>
-  </si>
-  <si>
-    <t>bridlington and the wolds</t>
-  </si>
-  <si>
-    <t>E14001127</t>
-  </si>
-  <si>
-    <t>brigg and immingham</t>
-  </si>
-  <si>
-    <t>E14001128</t>
-  </si>
-  <si>
-    <t>brighton kemptown and peacehaven</t>
-  </si>
-  <si>
-    <t>E14001129</t>
-  </si>
-  <si>
-    <t>brighton pavilion</t>
-  </si>
-  <si>
     <t>E14001130</t>
   </si>
   <si>
@@ -695,9 +698,6 @@
     <t>chorley</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>E14001170</t>
   </si>
   <si>
@@ -3815,6 +3815,9 @@
     <t>blaenau gwent and rhymney</t>
   </si>
   <si>
+    <t>Plaid Cymru</t>
+  </si>
+  <si>
     <t>W07000084</t>
   </si>
   <si>
@@ -3837,9 +3840,6 @@
   </si>
   <si>
     <t>caerphilly</t>
-  </si>
-  <si>
-    <t>Plaid Cymru</t>
   </si>
   <si>
     <t>W07000088</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2831631561603731</v>
+        <v>0.3045662209153074</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4255039485586797</v>
+        <v>0.4481544392485535</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3849360667180776</v>
+        <v>0.4084450589291873</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4408,61 +4408,61 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>0.3096046846301769</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
-      </c>
-      <c r="C5">
-        <v>0.3299913011840191</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3722587302327848</v>
+        <v>0.3908512141516383</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0.2949077704014985</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>0.286097669215153</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
       <c r="C8">
-        <v>0.3537542732443177</v>
+        <v>0.2991732117520275</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4476,10 +4476,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>0.3153965919011218</v>
+        <v>0.2855002914434173</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.348302985884026</v>
+        <v>0.3678572957083865</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4510,10 +4510,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>0.2441976559018879</v>
+        <v>0.2531080098871682</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.3807933956799462</v>
+        <v>0.4094676683429365</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4544,10 +4544,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>0.2924257318055369</v>
+        <v>0.2892153888162617</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4561,10 +4561,10 @@
         <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C14">
-        <v>0.3724020136284033</v>
+        <v>0.3494829314903982</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3527526482159136</v>
+        <v>0.353842545080053</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3157230916017902</v>
+        <v>0.3154570374236534</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>0.2889991461956005</v>
+        <v>0.3110359644877596</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3190272882201634</v>
+        <v>0.3397917422810864</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4282823283126049</v>
+        <v>0.4466376346849855</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3933085454703231</v>
+        <v>0.4194416148124586</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4325828180667278</v>
+        <v>0.4428372217925839</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3159965669313618</v>
+        <v>0.3387807910262845</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3774524060599008</v>
+        <v>0.4002047301400665</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3266501086132437</v>
+        <v>0.3416615919121777</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.585586191500625</v>
+        <v>0.5932999398290189</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3165085863857585</v>
+        <v>0.3348970075727914</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.2914192935357017</v>
+        <v>0.302128511336643</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3211089555251925</v>
+        <v>0.3300397115394119</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4616204380008559</v>
+        <v>0.4735506312811599</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3758300111980035</v>
+        <v>0.4022755860601706</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4298340179147914</v>
+        <v>0.447046706581018</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4867,10 +4867,10 @@
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C32">
-        <v>0.4011294782529491</v>
+        <v>0.3853443151076201</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.3827605339726079</v>
+        <v>0.3988207793409055</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4901,10 +4901,10 @@
         <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C34">
-        <v>0.3328375424616308</v>
+        <v>0.3486375633880249</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4331634072929274</v>
+        <v>0.4590311036291592</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4935,95 +4935,95 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>0.2553270228005215</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" t="s">
         <v>79</v>
-      </c>
-      <c r="C36">
-        <v>0.2288984667648479</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37">
+        <v>0.2723330354892966</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
         <v>81</v>
-      </c>
-      <c r="B37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37">
-        <v>0.2796787759611737</v>
-      </c>
-      <c r="D37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>0.3434286077370375</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s">
         <v>83</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38">
-        <v>0.3078807545776337</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39">
+        <v>0.3173162633652878</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s">
         <v>85</v>
-      </c>
-      <c r="B39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39">
-        <v>0.3187046927433971</v>
-      </c>
-      <c r="D39" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0.4983272714257007</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
         <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>0.4682014197891373</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" t="s">
         <v>89</v>
       </c>
-      <c r="B41" t="s">
-        <v>15</v>
-      </c>
       <c r="C41">
-        <v>0.2621143902451977</v>
+        <v>0.2368728034740736</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5040,7 +5040,7 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5229127188476864</v>
+        <v>0.5256407239845938</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5054,10 +5054,10 @@
         <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C43">
-        <v>0.4058826873607149</v>
+        <v>0.3762891066431306</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5071,10 +5071,10 @@
         <v>95</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C44">
-        <v>0.4142104769579736</v>
+        <v>0.3815912662184281</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5091,7 +5091,7 @@
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3809191306591311</v>
+        <v>0.4219180451609132</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5108,7 +5108,7 @@
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.420819761508451</v>
+        <v>0.4265000027253761</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5122,10 +5122,10 @@
         <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C47">
-        <v>0.3051903147736814</v>
+        <v>0.301205872984333</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5139,10 +5139,10 @@
         <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C48">
-        <v>0.4017841447006284</v>
+        <v>0.3887915237839455</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5156,10 +5156,10 @@
         <v>105</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C49">
-        <v>0.3527546153493197</v>
+        <v>0.3686114303195336</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5173,10 +5173,10 @@
         <v>107</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C50">
-        <v>0.3748390959162642</v>
+        <v>0.3241403930504687</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>6</v>
       </c>
       <c r="C51">
-        <v>0.3470957663728896</v>
+        <v>0.3374240775073768</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5210,7 +5210,7 @@
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.4790042973483321</v>
+        <v>0.4981768537252985</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5224,10 +5224,10 @@
         <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C53">
-        <v>0.4188656618217351</v>
+        <v>0.4055175427362857</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3617461145168955</v>
+        <v>0.3808032713650149</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5261,7 +5261,7 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2690113072572358</v>
+        <v>0.2908716782078624</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5278,7 +5278,7 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3649543691659294</v>
+        <v>0.3906543060157131</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5633531625012963</v>
+        <v>0.5644528510147101</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5312,7 +5312,7 @@
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3039819240183771</v>
+        <v>0.3306589049930568</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5329,7 +5329,7 @@
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.347176682933209</v>
+        <v>0.3839472339778317</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5346,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.2949400729606396</v>
+        <v>0.3193817868246915</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5363,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.377504955829631</v>
+        <v>0.3869092048793438</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5380,7 +5380,7 @@
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3262054237416919</v>
+        <v>0.3440410835695087</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5397,7 +5397,7 @@
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3636450607989149</v>
+        <v>0.3944869357543939</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5411,10 +5411,10 @@
         <v>135</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2282511805135438</v>
+        <v>0.2314259305044633</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5428,10 +5428,10 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C65">
-        <v>0.3217954788224316</v>
+        <v>0.3127869851834417</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3150536984757487</v>
+        <v>0.3197758401127539</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5462,10 +5462,10 @@
         <v>141</v>
       </c>
       <c r="B67" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C67">
-        <v>0.337600519773778</v>
+        <v>0.3028629444396335</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5482,7 +5482,7 @@
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2690918078289161</v>
+        <v>0.2941451364148224</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5496,690 +5496,690 @@
         <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C69">
-        <v>0.5378684651415885</v>
+        <v>0.5017975801290956</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C70">
-        <v>0.507725383253298</v>
+        <v>0.4654360405405868</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.458917112330169</v>
+        <v>0.4796720450750187</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
       </c>
       <c r="E71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3504311949938821</v>
+        <v>0.3732842688466002</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4703847858808292</v>
+        <v>0.5073789464113158</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4661665283294252</v>
+        <v>0.5061932669480189</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2708495252926101</v>
+        <v>0.2862247180660402</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3537513405999169</v>
+        <v>0.3784404811457866</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
       </c>
       <c r="E76" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.2876926449450477</v>
+        <v>0.3116942331266189</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
       </c>
       <c r="E77" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4223251536409405</v>
+        <v>0.4145535775998789</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
       </c>
       <c r="E78" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>0.257024573522678</v>
+        <v>0.2628628062198392</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
       </c>
       <c r="E79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3646921171518739</v>
+        <v>0.3729964423603974</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C81">
-        <v>0.2924174791700816</v>
+        <v>0.285899685497323</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
       </c>
       <c r="E81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B82" t="s">
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4079366676095699</v>
+        <v>0.4406779717359944</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B83" t="s">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3668245146044376</v>
+        <v>0.3890493260349111</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
       </c>
       <c r="C84">
-        <v>0.2979195868252322</v>
+        <v>0.3132639288702744</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C85">
-        <v>0.3128222531563299</v>
+        <v>0.3161451929337294</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
       </c>
       <c r="E85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3015863499162146</v>
+        <v>0.315594535528159</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
       </c>
       <c r="E86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2712144926881904</v>
+        <v>0.2844102711772702</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
       </c>
       <c r="E87" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C88">
-        <v>0.3161456522855082</v>
+        <v>0.2888672689455881</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
       </c>
       <c r="E88" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s">
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3241543614608279</v>
+        <v>0.3428719566161287</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
       </c>
       <c r="E89" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B90" t="s">
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.2904902217660849</v>
+        <v>0.3164855123553829</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
       </c>
       <c r="E90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91">
-        <v>0.2901514381247962</v>
+        <v>0.3125589937984551</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
       </c>
       <c r="E91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B92" t="s">
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.2893865335774943</v>
+        <v>0.2865791611095113</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C93">
-        <v>0.3797981205321461</v>
+        <v>0.3550430032039424</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
         <v>44</v>
       </c>
       <c r="C94">
-        <v>0.2776021258820446</v>
+        <v>0.2599462551503132</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
       </c>
       <c r="E94" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C95">
-        <v>0.3398135499806118</v>
+        <v>0.3303789388838115</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C96">
-        <v>0.3496225032225199</v>
+        <v>0.3430321306581801</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
       </c>
       <c r="E96" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B97" t="s">
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3255453799630212</v>
+        <v>0.3340273911373995</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B98" t="s">
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3469486923934018</v>
+        <v>0.358046805363488</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B99" t="s">
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4055000257738264</v>
+        <v>0.42547094924343</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
       </c>
       <c r="E99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B100" t="s">
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3581757131127667</v>
+        <v>0.357528750930159</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B101" t="s">
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.426993236688255</v>
+        <v>0.4221704499426024</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
       </c>
       <c r="E101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B102" t="s">
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4392743475825197</v>
+        <v>0.472192057352865</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3328985838614494</v>
+        <v>0.3494325328675375</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
       </c>
       <c r="E103" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C104">
-        <v>0.3716836355424765</v>
+        <v>0.3821380598357436</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
       </c>
       <c r="E104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B105" t="s">
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3367252208528693</v>
+        <v>0.346732362314895</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s">
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.367642934071217</v>
+        <v>0.376689413346808</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
       </c>
       <c r="E106" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B107" t="s">
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3462037589081145</v>
+        <v>0.3371398118811238</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
       </c>
       <c r="E107" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B108" t="s">
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.3837630929577617</v>
+        <v>0.4076950197056768</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B109" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="C109">
-        <v>0.2690628218329628</v>
+        <v>0.292278686654382</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6193,10 +6193,10 @@
         <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C110">
-        <v>0.3024767883538066</v>
+        <v>0.2709299302559546</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4828334013834791</v>
+        <v>0.4904953349217805</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3749429978400496</v>
+        <v>0.391843479014723</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6244,10 +6244,10 @@
         <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C113">
-        <v>0.499547821794505</v>
+        <v>0.476152823296633</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6116095379798064</v>
+        <v>0.6163039471233949</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>0.294142674768749</v>
+        <v>0.3077204583833777</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4361210000983498</v>
+        <v>0.4422124266048388</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2874801423660134</v>
+        <v>0.2980800505660757</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3751821617515811</v>
+        <v>0.3980467567935082</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3603116155790395</v>
+        <v>0.3792290972214342</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.359689239088871</v>
+        <v>0.3665539554545157</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.2468797323861577</v>
+        <v>0.2741970447512193</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6397,10 +6397,10 @@
         <v>252</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C122">
-        <v>0.3111429213684392</v>
+        <v>0.3016955745667039</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6414,10 +6414,10 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C123">
-        <v>0.3011907011408936</v>
+        <v>0.3041478413447269</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6431,10 +6431,10 @@
         <v>256</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C124">
-        <v>0.3961654856937492</v>
+        <v>0.3787026154112434</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="C125">
-        <v>0.3134466182148659</v>
+        <v>0.3208978170715764</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.342136734862397</v>
+        <v>0.3476412468039597</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4807451899551782</v>
+        <v>0.4953523051731307</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6499,10 +6499,10 @@
         <v>264</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C128">
-        <v>0.4001678970928536</v>
+        <v>0.4127349667662925</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C129">
-        <v>0.3099125998636751</v>
+        <v>0.3012573767111855</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6533,10 +6533,10 @@
         <v>268</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C130">
-        <v>0.3894469532112544</v>
+        <v>0.3362366995935229</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2804274186520376</v>
+        <v>0.2964939894568442</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.3796173357941848</v>
+        <v>0.3960962784766259</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6584,10 +6584,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C133">
-        <v>0.3347696416893302</v>
+        <v>0.3120065160548884</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3102427312947497</v>
+        <v>0.3331659933734045</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.3019062146639315</v>
+        <v>0.3377551277078729</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3133064625156143</v>
+        <v>0.3217749581865522</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.4047841665743758</v>
+        <v>0.4197616569093698</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.325159506303079</v>
+        <v>0.3167666689446598</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.3609386980011886</v>
+        <v>0.37468417251184</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3815871912847953</v>
+        <v>0.3967013929014711</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3321424374849355</v>
+        <v>0.3515722740874809</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3799615107181262</v>
+        <v>0.4015876151992491</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3271386092600252</v>
+        <v>0.3441872110192552</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5852317188309035</v>
+        <v>0.5929923162364147</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.279846014169359</v>
+        <v>0.3121167136086777</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.3893087622887993</v>
+        <v>0.3911794982342401</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.4409106181453628</v>
+        <v>0.4748135629458538</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.2854098544408822</v>
+        <v>0.3092623646117814</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3696742862894959</v>
+        <v>0.3904671048619432</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3221654973565646</v>
+        <v>0.3167900724343132</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2510026320419595</v>
+        <v>0.2732379423263704</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6554846203592137</v>
+        <v>0.6520421776922417</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.324322320390241</v>
+        <v>0.3339790037606728</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3131579978616129</v>
+        <v>0.3242321514653067</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.2716387829653236</v>
+        <v>0.2800004752573139</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3343982140637777</v>
+        <v>0.3752679410168647</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3410712640749947</v>
+        <v>0.365947784227799</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.378125301788326</v>
+        <v>0.3707898383548707</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.3893192389652128</v>
+        <v>0.4095056792580791</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3687596551317665</v>
+        <v>0.3968579561645934</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.3788222234331667</v>
+        <v>0.3931165979285502</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.5520622311757521</v>
+        <v>0.5545910855462384</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4306190174323301</v>
+        <v>0.4478359585507252</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3414001082646069</v>
+        <v>0.3491962528841059</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3500149032101144</v>
+        <v>0.380408505547995</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.3054266314348868</v>
+        <v>0.3167461091860118</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.3493770005398228</v>
+        <v>0.3676414872231386</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5800565300469009</v>
+        <v>0.597830723973946</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3233029034981408</v>
+        <v>0.3236216932380601</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3435238417671229</v>
+        <v>0.3766276623837551</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2476626259747402</v>
+        <v>0.2487394058702326</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.3924492019252033</v>
+        <v>0.3964605098752181</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3140708002491386</v>
+        <v>0.3339570538678298</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3210729778298571</v>
+        <v>0.3434136734919773</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7298,10 +7298,10 @@
         <v>358</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C175">
-        <v>0.296954372556306</v>
+        <v>0.25076150678887</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3941697577586928</v>
+        <v>0.4207252473443582</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.4824116306850783</v>
+        <v>0.4849292680437667</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7349,10 +7349,10 @@
         <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C178">
-        <v>0.3878949427505825</v>
+        <v>0.4215262727670255</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7366,10 +7366,10 @@
         <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C179">
-        <v>0.3168185681181563</v>
+        <v>0.3148587475498274</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3356929787088834</v>
+        <v>0.3522284386433004</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3347165172461587</v>
+        <v>0.3422367252128425</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.2946515649595063</v>
+        <v>0.3157021273867006</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.2837595402332083</v>
+        <v>0.3145458245517296</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.3410738888098478</v>
+        <v>0.3615648060818098</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3435449026792091</v>
+        <v>0.3468899910650011</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.396317050062198</v>
+        <v>0.4211161116574755</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C187">
-        <v>0.2541479087104608</v>
+        <v>0.2503493668894138</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4635175332613636</v>
+        <v>0.4673946388935998</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7536,10 +7536,10 @@
         <v>386</v>
       </c>
       <c r="B189" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3203882589807177</v>
+        <v>0.3414139838521207</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C190">
-        <v>0.2822831693109872</v>
+        <v>0.2946375365955958</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3521507434061753</v>
+        <v>0.3644840206112219</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7587,10 +7587,10 @@
         <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C192">
-        <v>0.3964902438274911</v>
+        <v>0.374552141083195</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7604,10 +7604,10 @@
         <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C193">
-        <v>0.4057296019642586</v>
+        <v>0.4432750810320481</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.3899892602319676</v>
+        <v>0.3902776861629508</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7638,10 +7638,10 @@
         <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="C195">
-        <v>0.3585941378119894</v>
+        <v>0.3453270556581568</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3385529158672433</v>
+        <v>0.3603477954063979</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3362082974653619</v>
+        <v>0.352076744301615</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5039466792828622</v>
+        <v>0.5327714066262805</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.5979674237113757</v>
+        <v>0.5956393195859917</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C200">
-        <v>0.3382920026221902</v>
+        <v>0.3400205350761787</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7740,10 +7740,10 @@
         <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C201">
-        <v>0.3055768465827172</v>
+        <v>0.3040819775222374</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.3879781815218642</v>
+        <v>0.4243055205978848</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.503496390786096</v>
+        <v>0.5329222814533608</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.4365420742182027</v>
+        <v>0.4621664773108676</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4430512086441332</v>
+        <v>0.4871876817812261</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7825,10 +7825,10 @@
         <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C206">
-        <v>0.3585961924944634</v>
+        <v>0.3593038159651081</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5391393915789693</v>
+        <v>0.5564168477814087</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.390215131283338</v>
+        <v>0.3783720298916468</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5043738416409609</v>
+        <v>0.5385972138023822</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.3979926575964651</v>
+        <v>0.4273974038248865</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7910,10 +7910,10 @@
         <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C211">
-        <v>0.4309242946516876</v>
+        <v>0.431361920088507</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C212">
-        <v>0.2936996755247407</v>
+        <v>0.2917264812457533</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C213">
-        <v>0.3167432844714032</v>
+        <v>0.3138742805834103</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7961,10 +7961,10 @@
         <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C214">
-        <v>0.3798779038408905</v>
+        <v>0.3659730270226195</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.47371737243909</v>
+        <v>0.4543193494753476</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7995,10 +7995,10 @@
         <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C216">
-        <v>0.3399333300571322</v>
+        <v>0.3085109392651217</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C217">
-        <v>0.3409377732428506</v>
+        <v>0.3426504456698292</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3345165290369346</v>
+        <v>0.3462381733932525</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4635132593149746</v>
+        <v>0.4846126145260455</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C220">
-        <v>0.2844687352973168</v>
+        <v>0.2539338583012547</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8080,10 +8080,10 @@
         <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C221">
-        <v>0.3534901965821448</v>
+        <v>0.3384668714334471</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3166881788281863</v>
+        <v>0.321291573612932</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5065550126125432</v>
+        <v>0.516312677067991</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3247016069781652</v>
+        <v>0.3459251653438432</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8148,10 +8148,10 @@
         <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C225">
-        <v>0.3675134004405882</v>
+        <v>0.3331664437939075</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4590820578088414</v>
+        <v>0.4933916584817199</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3468517755414227</v>
+        <v>0.3674406570641466</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4691063688641451</v>
+        <v>0.4740671064855538</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5324891763411769</v>
+        <v>0.5414075408119848</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3514037815775791</v>
+        <v>0.3466307955223518</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3092415943072838</v>
+        <v>0.3074923174918969</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5685684322450046</v>
+        <v>0.5757970877399116</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4022266110461384</v>
+        <v>0.4166327780722927</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.3995360063711544</v>
+        <v>0.4300151521451824</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4630821156035323</v>
+        <v>0.491783743588743</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2754530551415825</v>
+        <v>0.2871229186963779</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3367439816201492</v>
+        <v>0.3502686235155923</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.3422501839935803</v>
+        <v>0.3765417504241466</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4213089021892727</v>
+        <v>0.4021149981103511</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8403,10 +8403,10 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="C240">
-        <v>0.3380889784946238</v>
+        <v>0.359081098369969</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C241">
-        <v>0.2348796927206666</v>
+        <v>0.2373421429384271</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3137102454633882</v>
+        <v>0.3097228446452674</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8454,10 +8454,10 @@
         <v>494</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C243">
-        <v>0.4620882915670713</v>
+        <v>0.4761722246503817</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8471,10 +8471,10 @@
         <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="C244">
-        <v>0.3877550658633636</v>
+        <v>0.3913510886563449</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6092195075716241</v>
+        <v>0.6167316358264125</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4286571878236593</v>
+        <v>0.4444899475059202</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.4214140907996652</v>
+        <v>0.4285989532771451</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3616567416322681</v>
+        <v>0.3862045892219038</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.3948716223250202</v>
+        <v>0.4205149735535716</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8573,10 +8573,10 @@
         <v>508</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C250">
-        <v>0.3181698845820534</v>
+        <v>0.2761279042441301</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4158658249132765</v>
+        <v>0.4312215216228205</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.4163941534667894</v>
+        <v>0.4387977701650266</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3769929265987764</v>
+        <v>0.3929082253459785</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.4858114474023756</v>
+        <v>0.4835198515806392</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8658,10 +8658,10 @@
         <v>518</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C255">
-        <v>0.4031501118849217</v>
+        <v>0.39122151418524</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5767132258489583</v>
+        <v>0.591050279575541</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4048790429025711</v>
+        <v>0.4412099133333313</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4817586628290036</v>
+        <v>0.5027170971497459</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3115158620605481</v>
+        <v>0.3057700321589019</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4043464541818809</v>
+        <v>0.443982999701498</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.4478240740533708</v>
+        <v>0.4659876901018064</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3908440583535145</v>
+        <v>0.4227964258889865</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4380200799178905</v>
+        <v>0.4544066496852124</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4146698275273329</v>
+        <v>0.4568591242957185</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3210564140443634</v>
+        <v>0.3607496542593642</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="C266">
-        <v>0.3154284227464472</v>
+        <v>0.326551862579202</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
         <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C267">
-        <v>0.2821449805332264</v>
+        <v>0.2873292161155256</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4236188547365166</v>
+        <v>0.4297559732300851</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3761356164081675</v>
+        <v>0.3638245148740752</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5055666693844568</v>
+        <v>0.5254307612331567</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5258900442808085</v>
+        <v>0.5397518913966814</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3333166013220894</v>
+        <v>0.3787472253228006</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.4916092655907554</v>
+        <v>0.5267583133616188</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8981,10 +8981,10 @@
         <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C274">
-        <v>0.3422731935713</v>
+        <v>0.3292749467741282</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C275">
-        <v>0.2520881477710521</v>
+        <v>0.2592395619025692</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3263897088562931</v>
+        <v>0.3228610064462192</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C277">
-        <v>0.3756258098929685</v>
+        <v>0.380080886061899</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4378077956420742</v>
+        <v>0.4265596516480366</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.5473617164154592</v>
+        <v>0.5512423673939065</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4551015212523561</v>
+        <v>0.48420214824229</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3774335549562516</v>
+        <v>0.4066044172165793</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9117,10 +9117,10 @@
         <v>572</v>
       </c>
       <c r="B282" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C282">
-        <v>0.3780005656069831</v>
+        <v>0.3970256469242343</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3592295196951494</v>
+        <v>0.3736794764193132</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3049301971743907</v>
+        <v>0.3242885898818839</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C285">
-        <v>0.2676159767290468</v>
+        <v>0.2551415358942214</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.2788504355936055</v>
+        <v>0.2939193638088055</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4423559828411552</v>
+        <v>0.4601916380877823</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C288">
-        <v>0.2422591955700356</v>
+        <v>0.2534148333944155</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9236,10 +9236,10 @@
         <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C289">
-        <v>0.3413457518537069</v>
+        <v>0.3412961849311597</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9253,10 +9253,10 @@
         <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C290">
-        <v>0.323610437904996</v>
+        <v>0.283698878383284</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.3987297717071052</v>
+        <v>0.4189728379316511</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C292">
-        <v>0.4603820717038807</v>
+        <v>0.4267907566618528</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5884672169145735</v>
+        <v>0.5989746747883173</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9321,10 +9321,10 @@
         <v>596</v>
       </c>
       <c r="B294" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C294">
-        <v>0.3837673620139996</v>
+        <v>0.3611743368077697</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3552569073940873</v>
+        <v>0.3667747879979016</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C296">
-        <v>0.324109133052759</v>
+        <v>0.2894713989543</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.458063770466769</v>
+        <v>0.4704549575627175</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.391474455695329</v>
+        <v>0.4124084135388045</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2777329682249277</v>
+        <v>0.2713640289352758</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3418429157854573</v>
+        <v>0.363583962491223</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3396276119341169</v>
+        <v>0.3704202316569088</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.5167856765101565</v>
+        <v>0.5294143647341687</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3084731889800953</v>
+        <v>0.3245359222366417</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.2931651265117198</v>
+        <v>0.3203842635161764</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4297559983785948</v>
+        <v>0.4464662486517647</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9525,10 +9525,10 @@
         <v>620</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C306">
-        <v>0.397253827593232</v>
+        <v>0.3652121822473804</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.4368927892552605</v>
+        <v>0.4550807680031991</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3869954761823061</v>
+        <v>0.4053220897911998</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2665399812237024</v>
+        <v>0.291279916626478</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3807286001723058</v>
+        <v>0.3993922455995887</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9610,10 +9610,10 @@
         <v>630</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C311">
-        <v>0.3544954915466785</v>
+        <v>0.3358307348860017</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9627,10 +9627,10 @@
         <v>632</v>
       </c>
       <c r="B312" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C312">
-        <v>0.2860042120013992</v>
+        <v>0.2812620291193779</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3168578844143411</v>
+        <v>0.3055676365224455</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3213343623006783</v>
+        <v>0.3439551170758134</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4765424041988413</v>
+        <v>0.4966969155763854</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3847335900309929</v>
+        <v>0.4103647864530215</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5169264641012745</v>
+        <v>0.5316533356365678</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.5218847405781213</v>
+        <v>0.5493662568276458</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3334447854042586</v>
+        <v>0.3670801229641468</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C320">
-        <v>0.2733212584176998</v>
+        <v>0.2727251036549035</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3247656424633246</v>
+        <v>0.3510224409142203</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3501588402622776</v>
+        <v>0.3754361384320462</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.382704521098798</v>
+        <v>0.3979525829273354</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3789307710748647</v>
+        <v>0.3733039306047221</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9848,10 +9848,10 @@
         <v>658</v>
       </c>
       <c r="B325" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C325">
-        <v>0.241169899326524</v>
+        <v>0.2481850646054373</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9865,10 +9865,10 @@
         <v>660</v>
       </c>
       <c r="B326" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C326">
-        <v>0.358322435786918</v>
+        <v>0.3504757066485311</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3280471108953001</v>
+        <v>0.3230640204435239</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C328">
-        <v>0.2880889412741522</v>
+        <v>0.2688174336111492</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>10</v>
       </c>
       <c r="C329">
-        <v>0.3103389307610689</v>
+        <v>0.32741026318025</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C330">
-        <v>0.303564513364857</v>
+        <v>0.2963130927172308</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3932657363250261</v>
+        <v>0.4094231845338929</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3574191259163707</v>
+        <v>0.374082020147678</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.462212422289032</v>
+        <v>0.4892548293162943</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C334">
-        <v>0.2928893048029497</v>
+        <v>0.2974319773293228</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>44</v>
       </c>
       <c r="C335">
-        <v>0.3330036444689364</v>
+        <v>0.3186082231370499</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3071478944191704</v>
+        <v>0.310984741789172</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4551811233548003</v>
+        <v>0.4634225262358527</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.2866229274394441</v>
+        <v>0.3045355807775115</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10086,10 +10086,10 @@
         <v>686</v>
       </c>
       <c r="B339" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C339">
-        <v>0.4527299190962443</v>
+        <v>0.4247743495127151</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10103,10 +10103,10 @@
         <v>688</v>
       </c>
       <c r="B340" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C340">
-        <v>0.3172044835941235</v>
+        <v>0.3027873298954217</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2909474539248448</v>
+        <v>0.3099381151964136</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2640161055162293</v>
+        <v>0.2720322087163045</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4014942219396792</v>
+        <v>0.424763103422661</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C344">
-        <v>0.2973272729459644</v>
+        <v>0.2736441817800995</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.3510444333269421</v>
+        <v>0.3787786366375068</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3344138609692857</v>
+        <v>0.3513548372890778</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10222,10 +10222,10 @@
         <v>702</v>
       </c>
       <c r="B347" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C347">
-        <v>0.3463258315754877</v>
+        <v>0.3062791885084924</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3105467991993697</v>
+        <v>0.3384409514802589</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4675978952908086</v>
+        <v>0.488084550198791</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10273,10 +10273,10 @@
         <v>708</v>
       </c>
       <c r="B350" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C350">
-        <v>0.3655787079079476</v>
+        <v>0.3565010186469181</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C351">
-        <v>0.2672546550963665</v>
+        <v>0.2439094400617322</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10307,10 +10307,10 @@
         <v>712</v>
       </c>
       <c r="B352" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C352">
-        <v>0.4029182461032711</v>
+        <v>0.4056019596244076</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3916219437852297</v>
+        <v>0.3935586596025323</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.2760623433361764</v>
+        <v>0.2911160258368046</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.3496721059499771</v>
+        <v>0.3776230286358142</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3027760850048895</v>
+        <v>0.3423834660717359</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.3885803887096927</v>
+        <v>0.4053848969827728</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3078186310040785</v>
+        <v>0.340499239330625</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4620735949476567</v>
+        <v>0.4787493949281007</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4662677113038008</v>
+        <v>0.482874716038117</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10460,10 +10460,10 @@
         <v>730</v>
       </c>
       <c r="B361" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C361">
-        <v>0.3202243543843178</v>
+        <v>0.3057261052694391</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3513529340615593</v>
+        <v>0.3593817479086274</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.2975540643573028</v>
+        <v>0.3135367474708399</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3244242504063273</v>
+        <v>0.3485105306367041</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10528,10 +10528,10 @@
         <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C365">
-        <v>0.3106792268827239</v>
+        <v>0.3030814083584488</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10545,10 +10545,10 @@
         <v>740</v>
       </c>
       <c r="B366" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C366">
-        <v>0.2710777081263618</v>
+        <v>0.2498127249746581</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.2991471949989479</v>
+        <v>0.3225803122161974</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10579,10 +10579,10 @@
         <v>744</v>
       </c>
       <c r="B368" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C368">
-        <v>0.3163943049112177</v>
+        <v>0.2778289159575764</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4814917834201249</v>
+        <v>0.5070628502286457</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10613,10 +10613,10 @@
         <v>748</v>
       </c>
       <c r="B370" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C370">
-        <v>0.3401530633547369</v>
+        <v>0.3226429437291963</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.4402213555880974</v>
+        <v>0.473414105434951</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3486823641823614</v>
+        <v>0.3845210664602465</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.4195367561618498</v>
+        <v>0.4407791383706006</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4661529301689115</v>
+        <v>0.5051157965012489</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.4494777979918227</v>
+        <v>0.4966345232081801</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10715,10 +10715,10 @@
         <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C376">
-        <v>0.3704033598968718</v>
+        <v>0.34785348190755</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.4514120548242644</v>
+        <v>0.4727253875865513</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3030019399182439</v>
+        <v>0.3388704616711796</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.348710111280798</v>
+        <v>0.3531624530548816</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3465548934510516</v>
+        <v>0.367013700839659</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4394520384681703</v>
+        <v>0.482561096435849</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3178486358672271</v>
+        <v>0.3483262967288834</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3822499461468807</v>
+        <v>0.4013649484129872</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4220068403288894</v>
+        <v>0.4325006669733273</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3863572902023372</v>
+        <v>0.4037620546250527</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C386">
-        <v>0.3193511470050998</v>
+        <v>0.3077834039783328</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4245822183945224</v>
+        <v>0.4326294215640941</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3458505371143464</v>
+        <v>0.3384434455649635</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3364639549806435</v>
+        <v>0.3473219016142112</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10953,10 +10953,10 @@
         <v>788</v>
       </c>
       <c r="B390" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C390">
-        <v>0.3302825115908661</v>
+        <v>0.311226641833374</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10970,10 +10970,10 @@
         <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C391">
-        <v>0.3496649885373304</v>
+        <v>0.3281339909041506</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3086080280739411</v>
+        <v>0.3127889719477722</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4058114419028353</v>
+        <v>0.4289064897451685</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11021,10 +11021,10 @@
         <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C394">
-        <v>0.3719664544311484</v>
+        <v>0.3457209710589936</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.3993610759333287</v>
+        <v>0.423487880847166</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3838517209448933</v>
+        <v>0.4009308469098222</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3678178017036466</v>
+        <v>0.3801726646296298</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4678478171813533</v>
+        <v>0.4922621613195413</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11106,10 +11106,10 @@
         <v>806</v>
       </c>
       <c r="B399" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C399">
-        <v>0.3562322581521316</v>
+        <v>0.3712242931009684</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3307841127960584</v>
+        <v>0.3582789432867072</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11140,10 +11140,10 @@
         <v>810</v>
       </c>
       <c r="B401" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C401">
-        <v>0.4298958506327907</v>
+        <v>0.4306268340462955</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.387466841213626</v>
+        <v>0.4099504404221152</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2721518461063179</v>
+        <v>0.2812999025878103</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.3041318444700312</v>
+        <v>0.3314861853585954</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4143354707773915</v>
+        <v>0.4057880875464539</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="C406">
-        <v>0.4780519663820634</v>
+        <v>0.4310370935190977</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.3635896423577388</v>
+        <v>0.3777149561166234</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.4689042637472415</v>
+        <v>0.4904185861053884</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4623873146350835</v>
+        <v>0.4879487748474435</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11293,10 +11293,10 @@
         <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C410">
-        <v>0.3227983731472718</v>
+        <v>0.2926165443165696</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3209494341528195</v>
+        <v>0.3498514796781526</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.4476124404305162</v>
+        <v>0.462808576076613</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11344,10 +11344,10 @@
         <v>834</v>
       </c>
       <c r="B413" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C413">
-        <v>0.2665056905398744</v>
+        <v>0.262395456813332</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11361,10 +11361,10 @@
         <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C414">
-        <v>0.3216727816378716</v>
+        <v>0.3215743714000109</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C415">
-        <v>0.3508259138972202</v>
+        <v>0.3547104929653703</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11395,10 +11395,10 @@
         <v>840</v>
       </c>
       <c r="B416" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C416">
-        <v>0.386406248961731</v>
+        <v>0.4262056500825738</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11412,10 +11412,10 @@
         <v>842</v>
       </c>
       <c r="B417" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2559579210457664</v>
+        <v>0.2755574304610836</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.304150820593802</v>
+        <v>0.3016985051150668</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11446,10 +11446,10 @@
         <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C419">
-        <v>0.3552474690476196</v>
+        <v>0.2977486125484571</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.3865356817302836</v>
+        <v>0.3826282081906937</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.3844685121873515</v>
+        <v>0.3897236305171813</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.3490246516184218</v>
+        <v>0.3761520327417773</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4532970583205719</v>
+        <v>0.4629102731348608</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3134398456111477</v>
+        <v>0.3322489021763431</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3274565535126261</v>
+        <v>0.3506354662280581</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11565,10 +11565,10 @@
         <v>860</v>
       </c>
       <c r="B426" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C426">
-        <v>0.3575729222747163</v>
+        <v>0.3364547213196367</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11582,10 +11582,10 @@
         <v>862</v>
       </c>
       <c r="B427" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C427">
-        <v>0.2777244064448509</v>
+        <v>0.27089322326954</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2824056548021234</v>
+        <v>0.2874198743095294</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3275507350530543</v>
+        <v>0.3616010517391045</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3389406708068116</v>
+        <v>0.3436637411069952</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C431">
-        <v>0.279490772283341</v>
+        <v>0.2963546878881709</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11667,10 +11667,10 @@
         <v>872</v>
       </c>
       <c r="B432" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C432">
-        <v>0.3329611991718113</v>
+        <v>0.3183933194157216</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3181164198473584</v>
+        <v>0.3308828066130786</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11701,10 +11701,10 @@
         <v>876</v>
       </c>
       <c r="B434" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C434">
-        <v>0.3612015824491683</v>
+        <v>0.3324871782151275</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3607037075468528</v>
+        <v>0.3863446408067679</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11735,10 +11735,10 @@
         <v>880</v>
       </c>
       <c r="B436" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C436">
-        <v>0.3445444600613159</v>
+        <v>0.2933078834835189</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3118456619154692</v>
+        <v>0.3273027889224993</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11769,10 +11769,10 @@
         <v>884</v>
       </c>
       <c r="B438" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C438">
-        <v>0.3527890693549495</v>
+        <v>0.3349378445443585</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.3453402183559093</v>
+        <v>0.3855406523205607</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3521124251633238</v>
+        <v>0.3874116577542206</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>6</v>
       </c>
       <c r="C441">
-        <v>0.2990966219178311</v>
+        <v>0.3028599414345913</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.2790203966326534</v>
+        <v>0.310079020617442</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11854,10 +11854,10 @@
         <v>894</v>
       </c>
       <c r="B443" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C443">
-        <v>0.3010060331429905</v>
+        <v>0.2899955170565146</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3330649073930068</v>
+        <v>0.3405096017860576</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3420418272584687</v>
+        <v>0.3566343886820209</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3374788685406973</v>
+        <v>0.3407350324121086</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11922,10 +11922,10 @@
         <v>902</v>
       </c>
       <c r="B447" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C447">
-        <v>0.2946069281150356</v>
+        <v>0.2976246601603867</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.3514065575855496</v>
+        <v>0.3709286840890514</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.3814441365244088</v>
+        <v>0.4038636462698424</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3670632739717443</v>
+        <v>0.3645265941550396</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.3997611545192093</v>
+        <v>0.4150089593822529</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12007,10 +12007,10 @@
         <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C452">
-        <v>0.2830767658448352</v>
+        <v>0.3026187208650171</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.347298784867131</v>
+        <v>0.3555114938107093</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12041,10 +12041,10 @@
         <v>916</v>
       </c>
       <c r="B454" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C454">
-        <v>0.2932673916038284</v>
+        <v>0.265521999651412</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3346701683202167</v>
+        <v>0.3450171950279035</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3453306582763442</v>
+        <v>0.3810183688920446</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12092,10 +12092,10 @@
         <v>922</v>
       </c>
       <c r="B457" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C457">
-        <v>0.3456525199507995</v>
+        <v>0.3202535553220538</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3837823924339293</v>
+        <v>0.376912779878956</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3584356564984703</v>
+        <v>0.3763088593793559</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3296617447507984</v>
+        <v>0.3384596165863307</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3156494145243769</v>
+        <v>0.3127140313371691</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3366276449093441</v>
+        <v>0.3426132983414376</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12194,10 +12194,10 @@
         <v>934</v>
       </c>
       <c r="B463" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C463">
-        <v>0.3029294804444634</v>
+        <v>0.2981564474242959</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3892238615395494</v>
+        <v>0.4172919692070367</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3917201964158781</v>
+        <v>0.3964852606540288</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5113761309580195</v>
+        <v>0.5321956374630411</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.4540924880878452</v>
+        <v>0.4794895419341528</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3832203061706804</v>
+        <v>0.4165707144577219</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
         <v>946</v>
       </c>
       <c r="B469" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C469">
-        <v>0.3010656078365986</v>
+        <v>0.2708199322921215</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C470">
-        <v>0.30492009899508</v>
+        <v>0.3049941308464052</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3063868743444489</v>
+        <v>0.3285628256448819</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12347,10 +12347,10 @@
         <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C472">
-        <v>0.3426464218707992</v>
+        <v>0.3219414088519146</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3079660108313291</v>
+        <v>0.3241875266198842</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.3734213557773237</v>
+        <v>0.4049619231649815</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3285555596860554</v>
+        <v>0.3518282071397129</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3433783177219141</v>
+        <v>0.3439393956719564</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3527828011257783</v>
+        <v>0.3471361247132734</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.3842315650982783</v>
+        <v>0.3906801551762827</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4031350724137019</v>
+        <v>0.4208874962429768</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.4462113965058892</v>
+        <v>0.4832210796063616</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3914443569133633</v>
+        <v>0.3849396438279146</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3121202415180426</v>
+        <v>0.3332317507714258</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3030245569257389</v>
+        <v>0.3178356022948433</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3762491509180237</v>
+        <v>0.3863543261632468</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12568,10 +12568,10 @@
         <v>978</v>
       </c>
       <c r="B485" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C485">
-        <v>0.3586316417074126</v>
+        <v>0.3830300920138719</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12585,10 +12585,10 @@
         <v>980</v>
       </c>
       <c r="B486" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C486">
-        <v>0.3942896434549302</v>
+        <v>0.4154579509028183</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4659008229636533</v>
+        <v>0.4694663894259216</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3207534955055301</v>
+        <v>0.3450043433223682</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4684696547005462</v>
+        <v>0.4976728413024931</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12653,10 +12653,10 @@
         <v>988</v>
       </c>
       <c r="B490" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C490">
-        <v>0.3160122513869029</v>
+        <v>0.2950238063819532</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C491">
-        <v>0.282229769632438</v>
+        <v>0.2803319378608051</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4816447216897343</v>
+        <v>0.4850240682782722</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.2824388482274733</v>
+        <v>0.286838231678684</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3395742808273076</v>
+        <v>0.3726342064442006</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5145593817434271</v>
+        <v>0.5293756061525527</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.4673355685218653</v>
+        <v>0.4858568165445143</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3377770064857819</v>
+        <v>0.3530928462773465</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6674392708877078</v>
+        <v>0.6583497536513089</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12806,10 +12806,10 @@
         <v>1006</v>
       </c>
       <c r="B499" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C499">
-        <v>0.3493457199681903</v>
+        <v>0.3210333801657367</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4073105319107444</v>
+        <v>0.4366511975978077</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12840,10 +12840,10 @@
         <v>1010</v>
       </c>
       <c r="B501" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C501">
-        <v>0.39172055353376</v>
+        <v>0.383773192261028</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5730408842705578</v>
+        <v>0.5929342065366617</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12874,10 +12874,10 @@
         <v>1014</v>
       </c>
       <c r="B503" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C503">
-        <v>0.3655606524778894</v>
+        <v>0.3623648649715543</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C504">
-        <v>0.3344878559947604</v>
+        <v>0.2914191492295475</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.4253265646279834</v>
+        <v>0.4518757505867036</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12925,10 +12925,10 @@
         <v>1020</v>
       </c>
       <c r="B506" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C506">
-        <v>0.5090580303004499</v>
+        <v>0.4860886737329657</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.3101365078886263</v>
+        <v>0.3278726639355394</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12959,10 +12959,10 @@
         <v>1024</v>
       </c>
       <c r="B508" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C508">
-        <v>0.3221276633204012</v>
+        <v>0.307957081418648</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.4910548432855799</v>
+        <v>0.5328019951181769</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3719342359686852</v>
+        <v>0.3709250950699248</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3413627463145065</v>
+        <v>0.3473818763869019</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2962241248477734</v>
+        <v>0.3294091918170668</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3590441069850307</v>
+        <v>0.4008859727396674</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.410842507587753</v>
+        <v>0.4213836765987584</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.4596814451374978</v>
+        <v>0.4881077892246497</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C516">
-        <v>0.3252376641704987</v>
+        <v>0.2995998661882726</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13112,10 +13112,10 @@
         <v>1042</v>
       </c>
       <c r="B517" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C517">
-        <v>0.3457148110068663</v>
+        <v>0.3009941115055448</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3319665751069916</v>
+        <v>0.3523772609379261</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.4952779844488593</v>
+        <v>0.4953406796987408</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13163,10 +13163,10 @@
         <v>1048</v>
       </c>
       <c r="B520" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C520">
-        <v>0.3343675507887386</v>
+        <v>0.3268704953363349</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3057240332272759</v>
+        <v>0.3179794504368292</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13197,10 +13197,10 @@
         <v>1052</v>
       </c>
       <c r="B522" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C522">
-        <v>0.3681208330858352</v>
+        <v>0.3578309866850056</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.4259041796993562</v>
+        <v>0.4685559491460675</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.2751776470461191</v>
+        <v>0.2976674628639938</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.397757105537638</v>
+        <v>0.4089689182139154</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4133676839611221</v>
+        <v>0.4361796283851705</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3686957927585725</v>
+        <v>0.3669779457062384</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4292171306739597</v>
+        <v>0.4466842162926879</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3405249283261827</v>
+        <v>0.3437183164751437</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.4812428778763264</v>
+        <v>0.5006519707312975</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5495625495065581</v>
+        <v>0.5597454870003309</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>10</v>
       </c>
       <c r="C532">
-        <v>0.2678548310596582</v>
+        <v>0.2757630171027494</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13384,10 +13384,10 @@
         <v>1074</v>
       </c>
       <c r="B533" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C533">
-        <v>0.4401964306260909</v>
+        <v>0.4466448406053867</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C534">
-        <v>0.3289110514158071</v>
+        <v>0.33412391378609</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3077034159069985</v>
+        <v>0.3216059339608368</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C536">
-        <v>0.3139258601880067</v>
+        <v>0.2915434332528509</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.3617746537448041</v>
+        <v>0.3881360446219309</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C538">
-        <v>0.2911083821747393</v>
+        <v>0.2877180787466358</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
         <v>1086</v>
       </c>
       <c r="B539" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C539">
-        <v>0.2890131001803555</v>
+        <v>0.3115406704265408</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C540">
-        <v>0.2920627763083262</v>
+        <v>0.2538354791818599</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.4276600833826822</v>
+        <v>0.4459444941311597</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3840765342049579</v>
+        <v>0.3544844617763684</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3933153211076005</v>
+        <v>0.4107825878025874</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3296046400563991</v>
+        <v>0.3593941474044878</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2884541338878192</v>
+        <v>0.283012119932313</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3172809661289639</v>
+        <v>0.3275173474677737</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2773377677243735</v>
+        <v>0.2829119876573445</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.368342835975275</v>
+        <v>0.3717273565574627</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.3884101799882506</v>
+        <v>0.4035982543587803</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.379371034479448</v>
+        <v>0.3777938155865279</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2600739576711865</v>
+        <v>0.2575601488208817</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2905986252948766</v>
+        <v>0.2848172563192416</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2806108459847001</v>
+        <v>0.2801909702983088</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13993,10 +13993,10 @@
         <v>1162</v>
       </c>
       <c r="B572" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C572">
-        <v>0.2605653666914444</v>
+        <v>0.2676369516133467</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3248891226638706</v>
+        <v>0.3259079353246845</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3334316793337581</v>
+        <v>0.3515558081292249</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3508593410760105</v>
+        <v>0.3668406274872268</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3744840800853754</v>
+        <v>0.3703408010713912</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2778650220807022</v>
+        <v>0.3205612130677405</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3722366567780488</v>
+        <v>0.3842701487381203</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.314444678161674</v>
+        <v>0.3182666076686037</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3351580348578205</v>
+        <v>0.3316527745391962</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.446050854412754</v>
+        <v>0.465033400836241</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3078860993807473</v>
+        <v>0.3050114573861465</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3653731380049468</v>
+        <v>0.3759156938395272</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3014934763097268</v>
+        <v>0.2994125297183951</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.4162026741118093</v>
+        <v>0.4060144053853142</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2950762094740955</v>
+        <v>0.2894958706986879</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2645086405681463</v>
+        <v>0.3046889247084006</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3199422265530663</v>
+        <v>0.3222872701305645</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3390551340189545</v>
+        <v>0.3541766684858648</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.3763925756754392</v>
+        <v>0.4127624764155563</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5095298202222793</v>
+        <v>0.5231825777729124</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3989612299461182</v>
+        <v>0.3928007896202946</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6582965010277916</v>
+        <v>0.6547194721030339</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4221439994881752</v>
+        <v>0.4353205036174386</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.2918106303385109</v>
+        <v>0.3157856425047901</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4301576463632634</v>
+        <v>0.4366779505562012</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3044024203225391</v>
+        <v>0.3453946434769294</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>10</v>
+        <v>1143</v>
       </c>
       <c r="C598">
-        <v>0.2643341994591614</v>
+        <v>0.2378964756737056</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2648504330079637</v>
+        <v>0.2617276414805471</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2761861474128283</v>
+        <v>0.2712784126573458</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>44</v>
       </c>
       <c r="C601">
-        <v>0.2572228456529158</v>
+        <v>0.2570790704722975</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3613122234337758</v>
+        <v>0.3623921652382751</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2855076528078401</v>
+        <v>0.2833590310900423</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.2956557260375929</v>
+        <v>0.3367488276794558</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2914120289876425</v>
+        <v>0.2940767271796472</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3451617870106473</v>
+        <v>0.3476698567846861</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.31832864658203</v>
+        <v>0.3266271424184538</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.2832507191971311</v>
+        <v>0.3203677908490863</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14622,10 +14622,10 @@
         <v>1236</v>
       </c>
       <c r="B609" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C609">
-        <v>0.2805570156583798</v>
+        <v>0.2821835440968321</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C610">
-        <v>0.2582097621665965</v>
+        <v>0.2500050842218875</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4919645159808907</v>
+        <v>0.5156950117625676</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3151492916956965</v>
+        <v>0.3172798802247047</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3360888701446423</v>
+        <v>0.339290729911238</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4207979427071842</v>
+        <v>0.4400498055589998</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3222503224022803</v>
+        <v>0.3331020518883558</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4158551996754468</v>
+        <v>0.4391882392708466</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3297967013232817</v>
+        <v>0.3378867020085848</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3389721578373202</v>
+        <v>0.3303376973272643</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4461214753089645</v>
+        <v>0.4563187446497999</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C620">
-        <v>0.3125307121551915</v>
+        <v>0.2741042909118989</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14826,10 +14826,10 @@
         <v>1261</v>
       </c>
       <c r="B621" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C621">
-        <v>0.3507400549922038</v>
+        <v>0.3442496769108165</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C622">
-        <v>0.2761082774659481</v>
+        <v>0.2415765256537446</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14860,78 +14860,78 @@
         <v>1265</v>
       </c>
       <c r="B623" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2000750633796806</v>
+        <v>0.252487081765725</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
       </c>
       <c r="E623" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="624" spans="1:5">
       <c r="A624" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B624" t="s">
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2883252241547618</v>
+        <v>0.2798941737012071</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
       </c>
       <c r="E624" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="625" spans="1:5">
       <c r="A625" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>10</v>
+        <v>1266</v>
       </c>
       <c r="C625">
-        <v>0.2396158513481142</v>
+        <v>0.2670406397923298</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
       </c>
       <c r="E625" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="626" spans="1:5">
       <c r="A626" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B626" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C626">
-        <v>0.3273877094251895</v>
+        <v>0.3166733413150922</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
       </c>
       <c r="E626" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="627" spans="1:5">
       <c r="A627" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B627" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.2907155384419668</v>
+        <v>0.3518394968681734</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2316826523207751</v>
+        <v>0.2564085526816159</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C629">
-        <v>0.2740322105859919</v>
+        <v>0.2396958430685907</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14979,10 +14979,10 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3249190296566286</v>
+        <v>0.3708925254401351</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14996,10 +14996,10 @@
         <v>1282</v>
       </c>
       <c r="B631" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3213592118476376</v>
+        <v>0.3819348915873846</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15013,10 +15013,10 @@
         <v>1284</v>
       </c>
       <c r="B632" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.3899411003422587</v>
+        <v>0.4517125214338317</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15030,10 +15030,10 @@
         <v>1286</v>
       </c>
       <c r="B633" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C633">
-        <v>0.2754347631658899</v>
+        <v>0.2641238770905688</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15047,10 +15047,10 @@
         <v>1288</v>
       </c>
       <c r="B634" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C634">
-        <v>0.4043783090255618</v>
+        <v>0.4075726957754266</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15064,10 +15064,10 @@
         <v>1290</v>
       </c>
       <c r="B635" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4224469967081615</v>
+        <v>0.4507954410402215</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.395115115047224</v>
+        <v>0.3394815279150748</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C637">
-        <v>0.2847717563531478</v>
+        <v>0.3353207749233857</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15115,10 +15115,10 @@
         <v>1296</v>
       </c>
       <c r="B638" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.423901360193371</v>
+        <v>0.4657188915026288</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3465188860892308</v>
+        <v>0.3530728189893109</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2833597484023196</v>
+        <v>0.2813370363292744</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C641">
-        <v>0.2671652083472434</v>
+        <v>0.273005565930221</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15183,10 +15183,10 @@
         <v>1304</v>
       </c>
       <c r="B642" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.2829886519524138</v>
+        <v>0.3473587485169741</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15200,10 +15200,10 @@
         <v>1306</v>
       </c>
       <c r="B643" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C643">
-        <v>0.3012074692481571</v>
+        <v>0.2908470979609751</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15217,10 +15217,10 @@
         <v>1308</v>
       </c>
       <c r="B644" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C644">
-        <v>0.2812053685863024</v>
+        <v>0.2712434656734149</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15234,10 +15234,10 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C645">
-        <v>0.2554459886194498</v>
+        <v>0.2413129036593048</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15251,10 +15251,10 @@
         <v>1312</v>
       </c>
       <c r="B646" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C646">
-        <v>0.3645766184623316</v>
+        <v>0.359637859074117</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C647">
-        <v>0.2909655313496472</v>
+        <v>0.2799393225128359</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15285,10 +15285,10 @@
         <v>1316</v>
       </c>
       <c r="B648" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C648">
-        <v>0.2818035307281975</v>
+        <v>0.2702794633290554</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15302,10 +15302,10 @@
         <v>1318</v>
       </c>
       <c r="B649" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C649">
-        <v>0.3285805759841801</v>
+        <v>0.321389799642084</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C650">
-        <v>0.2635631244085863</v>
+        <v>0.2940131372512635</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15336,10 +15336,10 @@
         <v>1322</v>
       </c>
       <c r="B651" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C651">
-        <v>0.3081560486231352</v>
+        <v>0.2994570594935365</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15368,10 +15368,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>159</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,15 +15379,15 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>235</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,23 +15403,23 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -35,33 +35,36 @@
     <t>aldershot</t>
   </si>
   <si>
+    <t>Conservative</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>E14001063</t>
+  </si>
+  <si>
+    <t>aldridge-brownhills</t>
+  </si>
+  <si>
+    <t>E14001064</t>
+  </si>
+  <si>
+    <t>altrincham and sale west</t>
+  </si>
+  <si>
     <t>Labour</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>E14001063</t>
-  </si>
-  <si>
-    <t>aldridge-brownhills</t>
-  </si>
-  <si>
-    <t>Conservative</t>
-  </si>
-  <si>
-    <t>E14001064</t>
-  </si>
-  <si>
-    <t>altrincham and sale west</t>
-  </si>
-  <si>
     <t>E14001065</t>
   </si>
   <si>
     <t>amber valley</t>
   </si>
   <si>
+    <t>Brexit Party/Reform UK</t>
+  </si>
+  <si>
     <t>E14001066</t>
   </si>
   <si>
@@ -80,9 +83,6 @@
     <t>ashford</t>
   </si>
   <si>
-    <t>Brexit Party/Reform UK</t>
-  </si>
-  <si>
     <t>E14001069</t>
   </si>
   <si>
@@ -182,6 +182,9 @@
     <t>bermondsey and old southwark</t>
   </si>
   <si>
+    <t>Green Party</t>
+  </si>
+  <si>
     <t>E14001085</t>
   </si>
   <si>
@@ -284,420 +287,417 @@
     <t>blackburn</t>
   </si>
   <si>
+    <t>E14001102</t>
+  </si>
+  <si>
+    <t>blackley and middleton south</t>
+  </si>
+  <si>
+    <t>E14001103</t>
+  </si>
+  <si>
+    <t>blackpool north and fleetwood</t>
+  </si>
+  <si>
+    <t>E14001104</t>
+  </si>
+  <si>
+    <t>blackpool south</t>
+  </si>
+  <si>
+    <t>E14001105</t>
+  </si>
+  <si>
+    <t>blaydon and consett</t>
+  </si>
+  <si>
+    <t>E14001106</t>
+  </si>
+  <si>
+    <t>blyth and ashington</t>
+  </si>
+  <si>
+    <t>E14001107</t>
+  </si>
+  <si>
+    <t>bognor regis and littlehampton</t>
+  </si>
+  <si>
+    <t>E14001108</t>
+  </si>
+  <si>
+    <t>bolsover</t>
+  </si>
+  <si>
+    <t>E14001109</t>
+  </si>
+  <si>
+    <t>bolton north east</t>
+  </si>
+  <si>
+    <t>E14001110</t>
+  </si>
+  <si>
+    <t>bolton south and walkden</t>
+  </si>
+  <si>
+    <t>E14001111</t>
+  </si>
+  <si>
+    <t>bolton west</t>
+  </si>
+  <si>
+    <t>E14001112</t>
+  </si>
+  <si>
+    <t>bootle</t>
+  </si>
+  <si>
+    <t>E14001113</t>
+  </si>
+  <si>
+    <t>boston and skegness</t>
+  </si>
+  <si>
+    <t>E14001114</t>
+  </si>
+  <si>
+    <t>bournemouth east</t>
+  </si>
+  <si>
+    <t>E14001115</t>
+  </si>
+  <si>
+    <t>bournemouth west</t>
+  </si>
+  <si>
+    <t>E14001116</t>
+  </si>
+  <si>
+    <t>bracknell</t>
+  </si>
+  <si>
+    <t>E14001117</t>
+  </si>
+  <si>
+    <t>bradford east</t>
+  </si>
+  <si>
+    <t>E14001118</t>
+  </si>
+  <si>
+    <t>bradford south</t>
+  </si>
+  <si>
+    <t>E14001119</t>
+  </si>
+  <si>
+    <t>bradford west</t>
+  </si>
+  <si>
+    <t>E14001120</t>
+  </si>
+  <si>
+    <t>braintree</t>
+  </si>
+  <si>
+    <t>E14001121</t>
+  </si>
+  <si>
+    <t>brent east</t>
+  </si>
+  <si>
+    <t>E14001122</t>
+  </si>
+  <si>
+    <t>brent west</t>
+  </si>
+  <si>
+    <t>E14001123</t>
+  </si>
+  <si>
+    <t>brentford and isleworth</t>
+  </si>
+  <si>
+    <t>E14001124</t>
+  </si>
+  <si>
+    <t>brentwood and ongar</t>
+  </si>
+  <si>
+    <t>E14001125</t>
+  </si>
+  <si>
+    <t>bridgwater</t>
+  </si>
+  <si>
+    <t>E14001126</t>
+  </si>
+  <si>
+    <t>bridlington and the wolds</t>
+  </si>
+  <si>
+    <t>E14001127</t>
+  </si>
+  <si>
+    <t>brigg and immingham</t>
+  </si>
+  <si>
+    <t>E14001128</t>
+  </si>
+  <si>
+    <t>brighton kemptown and peacehaven</t>
+  </si>
+  <si>
+    <t>E14001129</t>
+  </si>
+  <si>
+    <t>brighton pavilion</t>
+  </si>
+  <si>
+    <t>E14001130</t>
+  </si>
+  <si>
+    <t>bristol central</t>
+  </si>
+  <si>
+    <t>E14001131</t>
+  </si>
+  <si>
+    <t>bristol east</t>
+  </si>
+  <si>
+    <t>E14001132</t>
+  </si>
+  <si>
+    <t>bristol north east</t>
+  </si>
+  <si>
+    <t>E14001133</t>
+  </si>
+  <si>
+    <t>bristol north west</t>
+  </si>
+  <si>
+    <t>E14001134</t>
+  </si>
+  <si>
+    <t>bristol south</t>
+  </si>
+  <si>
+    <t>E14001135</t>
+  </si>
+  <si>
+    <t>broadland and fakenham</t>
+  </si>
+  <si>
+    <t>E14001136</t>
+  </si>
+  <si>
+    <t>bromley and biggin hill</t>
+  </si>
+  <si>
+    <t>E14001137</t>
+  </si>
+  <si>
+    <t>bromsgrove</t>
+  </si>
+  <si>
+    <t>E14001138</t>
+  </si>
+  <si>
+    <t>broxbourne</t>
+  </si>
+  <si>
+    <t>E14001139</t>
+  </si>
+  <si>
+    <t>broxtowe</t>
+  </si>
+  <si>
+    <t>E14001140</t>
+  </si>
+  <si>
+    <t>buckingham and bletchley</t>
+  </si>
+  <si>
+    <t>E14001141</t>
+  </si>
+  <si>
+    <t>burnley</t>
+  </si>
+  <si>
+    <t>E14001142</t>
+  </si>
+  <si>
+    <t>burton and uttoxeter</t>
+  </si>
+  <si>
+    <t>E14001143</t>
+  </si>
+  <si>
+    <t>bury north</t>
+  </si>
+  <si>
+    <t>E14001144</t>
+  </si>
+  <si>
+    <t>bury south</t>
+  </si>
+  <si>
+    <t>E14001145</t>
+  </si>
+  <si>
+    <t>bury st edmunds and stowmarket</t>
+  </si>
+  <si>
+    <t>E14001146</t>
+  </si>
+  <si>
+    <t>calder valley</t>
+  </si>
+  <si>
+    <t>E14001147</t>
+  </si>
+  <si>
+    <t>camborne and redruth</t>
+  </si>
+  <si>
+    <t>E14001148</t>
+  </si>
+  <si>
+    <t>cambridge</t>
+  </si>
+  <si>
+    <t>E14001149</t>
+  </si>
+  <si>
+    <t>cannock chase</t>
+  </si>
+  <si>
+    <t>E14001150</t>
+  </si>
+  <si>
+    <t>canterbury</t>
+  </si>
+  <si>
+    <t>E14001151</t>
+  </si>
+  <si>
+    <t>carlisle</t>
+  </si>
+  <si>
+    <t>E14001152</t>
+  </si>
+  <si>
+    <t>carshalton and wallington</t>
+  </si>
+  <si>
+    <t>E14001153</t>
+  </si>
+  <si>
+    <t>castle point</t>
+  </si>
+  <si>
+    <t>E14001154</t>
+  </si>
+  <si>
+    <t>central devon</t>
+  </si>
+  <si>
+    <t>E14001155</t>
+  </si>
+  <si>
+    <t>central suffolk and north ipswich</t>
+  </si>
+  <si>
+    <t>E14001156</t>
+  </si>
+  <si>
+    <t>chatham and aylesford</t>
+  </si>
+  <si>
+    <t>E14001157</t>
+  </si>
+  <si>
+    <t>cheadle</t>
+  </si>
+  <si>
+    <t>E14001158</t>
+  </si>
+  <si>
+    <t>chelmsford</t>
+  </si>
+  <si>
+    <t>E14001159</t>
+  </si>
+  <si>
+    <t>chelsea and fulham</t>
+  </si>
+  <si>
+    <t>E14001160</t>
+  </si>
+  <si>
+    <t>cheltenham</t>
+  </si>
+  <si>
+    <t>E14001161</t>
+  </si>
+  <si>
+    <t>chesham and amersham</t>
+  </si>
+  <si>
+    <t>E14001162</t>
+  </si>
+  <si>
+    <t>chester north and neston</t>
+  </si>
+  <si>
+    <t>E14001163</t>
+  </si>
+  <si>
+    <t>chester south and eddisbury</t>
+  </si>
+  <si>
+    <t>E14001164</t>
+  </si>
+  <si>
+    <t>chesterfield</t>
+  </si>
+  <si>
+    <t>E14001165</t>
+  </si>
+  <si>
+    <t>chichester</t>
+  </si>
+  <si>
+    <t>E14001166</t>
+  </si>
+  <si>
+    <t>chingford and woodford green</t>
+  </si>
+  <si>
+    <t>E14001167</t>
+  </si>
+  <si>
+    <t>chippenham</t>
+  </si>
+  <si>
+    <t>E14001168</t>
+  </si>
+  <si>
+    <t>chipping barnet</t>
+  </si>
+  <si>
+    <t>E14001169</t>
+  </si>
+  <si>
+    <t>chorley</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
-    <t>E14001102</t>
-  </si>
-  <si>
-    <t>blackley and middleton south</t>
-  </si>
-  <si>
-    <t>E14001103</t>
-  </si>
-  <si>
-    <t>blackpool north and fleetwood</t>
-  </si>
-  <si>
-    <t>E14001104</t>
-  </si>
-  <si>
-    <t>blackpool south</t>
-  </si>
-  <si>
-    <t>E14001105</t>
-  </si>
-  <si>
-    <t>blaydon and consett</t>
-  </si>
-  <si>
-    <t>E14001106</t>
-  </si>
-  <si>
-    <t>blyth and ashington</t>
-  </si>
-  <si>
-    <t>E14001107</t>
-  </si>
-  <si>
-    <t>bognor regis and littlehampton</t>
-  </si>
-  <si>
-    <t>E14001108</t>
-  </si>
-  <si>
-    <t>bolsover</t>
-  </si>
-  <si>
-    <t>E14001109</t>
-  </si>
-  <si>
-    <t>bolton north east</t>
-  </si>
-  <si>
-    <t>E14001110</t>
-  </si>
-  <si>
-    <t>bolton south and walkden</t>
-  </si>
-  <si>
-    <t>E14001111</t>
-  </si>
-  <si>
-    <t>bolton west</t>
-  </si>
-  <si>
-    <t>E14001112</t>
-  </si>
-  <si>
-    <t>bootle</t>
-  </si>
-  <si>
-    <t>E14001113</t>
-  </si>
-  <si>
-    <t>boston and skegness</t>
-  </si>
-  <si>
-    <t>E14001114</t>
-  </si>
-  <si>
-    <t>bournemouth east</t>
-  </si>
-  <si>
-    <t>E14001115</t>
-  </si>
-  <si>
-    <t>bournemouth west</t>
-  </si>
-  <si>
-    <t>E14001116</t>
-  </si>
-  <si>
-    <t>bracknell</t>
-  </si>
-  <si>
-    <t>E14001117</t>
-  </si>
-  <si>
-    <t>bradford east</t>
-  </si>
-  <si>
-    <t>E14001118</t>
-  </si>
-  <si>
-    <t>bradford south</t>
-  </si>
-  <si>
-    <t>E14001119</t>
-  </si>
-  <si>
-    <t>bradford west</t>
-  </si>
-  <si>
-    <t>E14001120</t>
-  </si>
-  <si>
-    <t>braintree</t>
-  </si>
-  <si>
-    <t>E14001121</t>
-  </si>
-  <si>
-    <t>brent east</t>
-  </si>
-  <si>
-    <t>E14001122</t>
-  </si>
-  <si>
-    <t>brent west</t>
-  </si>
-  <si>
-    <t>E14001123</t>
-  </si>
-  <si>
-    <t>brentford and isleworth</t>
-  </si>
-  <si>
-    <t>E14001124</t>
-  </si>
-  <si>
-    <t>brentwood and ongar</t>
-  </si>
-  <si>
-    <t>E14001125</t>
-  </si>
-  <si>
-    <t>bridgwater</t>
-  </si>
-  <si>
-    <t>E14001126</t>
-  </si>
-  <si>
-    <t>bridlington and the wolds</t>
-  </si>
-  <si>
-    <t>E14001127</t>
-  </si>
-  <si>
-    <t>brigg and immingham</t>
-  </si>
-  <si>
-    <t>E14001128</t>
-  </si>
-  <si>
-    <t>brighton kemptown and peacehaven</t>
-  </si>
-  <si>
-    <t>E14001129</t>
-  </si>
-  <si>
-    <t>brighton pavilion</t>
-  </si>
-  <si>
-    <t>Green Party</t>
-  </si>
-  <si>
-    <t>E14001130</t>
-  </si>
-  <si>
-    <t>bristol central</t>
-  </si>
-  <si>
-    <t>E14001131</t>
-  </si>
-  <si>
-    <t>bristol east</t>
-  </si>
-  <si>
-    <t>E14001132</t>
-  </si>
-  <si>
-    <t>bristol north east</t>
-  </si>
-  <si>
-    <t>E14001133</t>
-  </si>
-  <si>
-    <t>bristol north west</t>
-  </si>
-  <si>
-    <t>E14001134</t>
-  </si>
-  <si>
-    <t>bristol south</t>
-  </si>
-  <si>
-    <t>E14001135</t>
-  </si>
-  <si>
-    <t>broadland and fakenham</t>
-  </si>
-  <si>
-    <t>E14001136</t>
-  </si>
-  <si>
-    <t>bromley and biggin hill</t>
-  </si>
-  <si>
-    <t>E14001137</t>
-  </si>
-  <si>
-    <t>bromsgrove</t>
-  </si>
-  <si>
-    <t>E14001138</t>
-  </si>
-  <si>
-    <t>broxbourne</t>
-  </si>
-  <si>
-    <t>E14001139</t>
-  </si>
-  <si>
-    <t>broxtowe</t>
-  </si>
-  <si>
-    <t>E14001140</t>
-  </si>
-  <si>
-    <t>buckingham and bletchley</t>
-  </si>
-  <si>
-    <t>E14001141</t>
-  </si>
-  <si>
-    <t>burnley</t>
-  </si>
-  <si>
-    <t>E14001142</t>
-  </si>
-  <si>
-    <t>burton and uttoxeter</t>
-  </si>
-  <si>
-    <t>E14001143</t>
-  </si>
-  <si>
-    <t>bury north</t>
-  </si>
-  <si>
-    <t>E14001144</t>
-  </si>
-  <si>
-    <t>bury south</t>
-  </si>
-  <si>
-    <t>E14001145</t>
-  </si>
-  <si>
-    <t>bury st edmunds and stowmarket</t>
-  </si>
-  <si>
-    <t>E14001146</t>
-  </si>
-  <si>
-    <t>calder valley</t>
-  </si>
-  <si>
-    <t>E14001147</t>
-  </si>
-  <si>
-    <t>camborne and redruth</t>
-  </si>
-  <si>
-    <t>E14001148</t>
-  </si>
-  <si>
-    <t>cambridge</t>
-  </si>
-  <si>
-    <t>E14001149</t>
-  </si>
-  <si>
-    <t>cannock chase</t>
-  </si>
-  <si>
-    <t>E14001150</t>
-  </si>
-  <si>
-    <t>canterbury</t>
-  </si>
-  <si>
-    <t>E14001151</t>
-  </si>
-  <si>
-    <t>carlisle</t>
-  </si>
-  <si>
-    <t>E14001152</t>
-  </si>
-  <si>
-    <t>carshalton and wallington</t>
-  </si>
-  <si>
-    <t>E14001153</t>
-  </si>
-  <si>
-    <t>castle point</t>
-  </si>
-  <si>
-    <t>E14001154</t>
-  </si>
-  <si>
-    <t>central devon</t>
-  </si>
-  <si>
-    <t>E14001155</t>
-  </si>
-  <si>
-    <t>central suffolk and north ipswich</t>
-  </si>
-  <si>
-    <t>E14001156</t>
-  </si>
-  <si>
-    <t>chatham and aylesford</t>
-  </si>
-  <si>
-    <t>E14001157</t>
-  </si>
-  <si>
-    <t>cheadle</t>
-  </si>
-  <si>
-    <t>E14001158</t>
-  </si>
-  <si>
-    <t>chelmsford</t>
-  </si>
-  <si>
-    <t>E14001159</t>
-  </si>
-  <si>
-    <t>chelsea and fulham</t>
-  </si>
-  <si>
-    <t>E14001160</t>
-  </si>
-  <si>
-    <t>cheltenham</t>
-  </si>
-  <si>
-    <t>E14001161</t>
-  </si>
-  <si>
-    <t>chesham and amersham</t>
-  </si>
-  <si>
-    <t>E14001162</t>
-  </si>
-  <si>
-    <t>chester north and neston</t>
-  </si>
-  <si>
-    <t>E14001163</t>
-  </si>
-  <si>
-    <t>chester south and eddisbury</t>
-  </si>
-  <si>
-    <t>E14001164</t>
-  </si>
-  <si>
-    <t>chesterfield</t>
-  </si>
-  <si>
-    <t>E14001165</t>
-  </si>
-  <si>
-    <t>chichester</t>
-  </si>
-  <si>
-    <t>E14001166</t>
-  </si>
-  <si>
-    <t>chingford and woodford green</t>
-  </si>
-  <si>
-    <t>E14001167</t>
-  </si>
-  <si>
-    <t>chippenham</t>
-  </si>
-  <si>
-    <t>E14001168</t>
-  </si>
-  <si>
-    <t>chipping barnet</t>
-  </si>
-  <si>
-    <t>E14001169</t>
-  </si>
-  <si>
-    <t>chorley</t>
-  </si>
-  <si>
     <t>E14001170</t>
   </si>
   <si>
@@ -3815,31 +3815,31 @@
     <t>blaenau gwent and rhymney</t>
   </si>
   <si>
+    <t>W07000084</t>
+  </si>
+  <si>
+    <t>brecon, radnor and cwm tawe</t>
+  </si>
+  <si>
+    <t>W07000085</t>
+  </si>
+  <si>
+    <t>bridgend</t>
+  </si>
+  <si>
+    <t>W07000086</t>
+  </si>
+  <si>
+    <t>caerfyrddin</t>
+  </si>
+  <si>
+    <t>W07000087</t>
+  </si>
+  <si>
+    <t>caerphilly</t>
+  </si>
+  <si>
     <t>Plaid Cymru</t>
-  </si>
-  <si>
-    <t>W07000084</t>
-  </si>
-  <si>
-    <t>brecon, radnor and cwm tawe</t>
-  </si>
-  <si>
-    <t>W07000085</t>
-  </si>
-  <si>
-    <t>bridgend</t>
-  </si>
-  <si>
-    <t>W07000086</t>
-  </si>
-  <si>
-    <t>caerfyrddin</t>
-  </si>
-  <si>
-    <t>W07000087</t>
-  </si>
-  <si>
-    <t>caerphilly</t>
   </si>
   <si>
     <t>W07000088</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3045662209153074</v>
+        <v>0.2695912896455576</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4374,27 +4374,27 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>0.4307430611125232</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
-      </c>
-      <c r="C3">
-        <v>0.4481544392485535</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
       <c r="C4">
-        <v>0.4084450589291873</v>
+        <v>0.3330515784854231</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4408,61 +4408,61 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3096046846301769</v>
+        <v>0.3772632696606538</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0.3908512141516383</v>
+        <v>0.3873939564605757</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>0.2949077704014985</v>
+        <v>0.3324741338813946</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C8">
-        <v>0.2991732117520275</v>
+        <v>0.3740070599523287</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4476,10 +4476,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>0.2855002914434173</v>
+        <v>0.3565595338359154</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4493,10 +4493,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>0.3678572957083865</v>
+        <v>0.3514805769782894</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4510,10 +4510,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>0.2531080098871682</v>
+        <v>0.2236287249150227</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4527,10 +4527,10 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>0.4094676683429365</v>
+        <v>0.3521334037116561</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4544,10 +4544,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C13">
-        <v>0.2892153888162617</v>
+        <v>0.3633361938972649</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4561,10 +4561,10 @@
         <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>0.3494829314903982</v>
+        <v>0.4290885235723687</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>0.353842545080053</v>
+        <v>0.353324383285011</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4595,10 +4595,10 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C16">
-        <v>0.3154570374236534</v>
+        <v>0.2806153481092007</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C17">
-        <v>0.3110359644877596</v>
+        <v>0.3266824432675457</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4629,10 +4629,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>0.3397917422810864</v>
+        <v>0.329507534340949</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4466376346849855</v>
+        <v>0.4627953001029372</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4663,10 +4663,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>0.4194416148124586</v>
+        <v>0.3439760643204102</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4680,10 +4680,10 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>0.4428372217925839</v>
+        <v>0.4324207993855941</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4697,10 +4697,10 @@
         <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C22">
-        <v>0.3387807910262845</v>
+        <v>0.256332233086707</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4714,10 +4714,10 @@
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C23">
-        <v>0.4002047301400665</v>
+        <v>0.312955303873579</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4731,299 +4731,299 @@
         <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C24">
-        <v>0.3416615919121777</v>
+        <v>0.3381185475937113</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C25">
-        <v>0.5932999398290189</v>
+        <v>0.539693270102466</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C26">
-        <v>0.3348970075727914</v>
+        <v>0.3510680436411081</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C27">
-        <v>0.302128511336643</v>
+        <v>0.3000115018164868</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>0.3300397115394119</v>
+        <v>0.3256191895678688</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4735506312811599</v>
+        <v>0.4917580624636897</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C30">
-        <v>0.4022755860601706</v>
+        <v>0.3087715362186574</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C31">
-        <v>0.447046706581018</v>
+        <v>0.3699456888044048</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>0.3853443151076201</v>
+        <v>0.4670783955132038</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>0.3988207793409055</v>
+        <v>0.3331607793541906</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>0.3486375633880249</v>
+        <v>0.4206889240196939</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C35">
-        <v>0.4590311036291592</v>
+        <v>0.3880019310666975</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C36">
-        <v>0.2553270228005215</v>
+        <v>0.2636128251047856</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>0.2723330354892966</v>
+        <v>0.3393665326163298</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C38">
-        <v>0.3434286077370375</v>
+        <v>0.2582251391515031</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
       </c>
       <c r="E38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3173162633652878</v>
+        <v>0.3945858852089007</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C40">
-        <v>0.4983272714257007</v>
+        <v>0.4164687525165971</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2368728034740736</v>
+        <v>0.2991056328049332</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5037,10 +5037,10 @@
         <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>0.5256407239845938</v>
+        <v>0.4361658578700387</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5054,10 +5054,10 @@
         <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C43">
-        <v>0.3762891066431306</v>
+        <v>0.4710571238933087</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5071,10 +5071,10 @@
         <v>95</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C44">
-        <v>0.3815912662184281</v>
+        <v>0.4730106822444252</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5088,10 +5088,10 @@
         <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C45">
-        <v>0.4219180451609132</v>
+        <v>0.3250550843313242</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5105,10 +5105,10 @@
         <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C46">
-        <v>0.4265000027253761</v>
+        <v>0.3514914463431822</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5122,10 +5122,10 @@
         <v>101</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C47">
-        <v>0.301205872984333</v>
+        <v>0.3799821256260187</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5139,10 +5139,10 @@
         <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C48">
-        <v>0.3887915237839455</v>
+        <v>0.4743878510226539</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5156,10 +5156,10 @@
         <v>105</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C49">
-        <v>0.3686114303195336</v>
+        <v>0.4550104394131985</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5173,10 +5173,10 @@
         <v>107</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C50">
-        <v>0.3241403930504687</v>
+        <v>0.4005637214017976</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5190,10 +5190,10 @@
         <v>109</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C51">
-        <v>0.3374240775073768</v>
+        <v>0.4070851620222515</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5207,10 +5207,10 @@
         <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C52">
-        <v>0.4981768537252985</v>
+        <v>0.4033590285922248</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5224,10 +5224,10 @@
         <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4055175427362857</v>
+        <v>0.4994948405730678</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3808032713650149</v>
+        <v>0.3119459087255811</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5258,10 +5258,10 @@
         <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C55">
-        <v>0.2908716782078624</v>
+        <v>0.2791423321810907</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5275,10 +5275,10 @@
         <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C56">
-        <v>0.3906543060157131</v>
+        <v>0.3801593554683973</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5292,10 +5292,10 @@
         <v>121</v>
       </c>
       <c r="B57" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C57">
-        <v>0.5644528510147101</v>
+        <v>0.4791024189087837</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5309,10 +5309,10 @@
         <v>123</v>
       </c>
       <c r="B58" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C58">
-        <v>0.3306589049930568</v>
+        <v>0.3332809151423174</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5326,10 +5326,10 @@
         <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C59">
-        <v>0.3839472339778317</v>
+        <v>0.3169292471897748</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5343,10 +5343,10 @@
         <v>127</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C60">
-        <v>0.3193817868246915</v>
+        <v>0.2916707872983467</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5360,10 +5360,10 @@
         <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C61">
-        <v>0.3869092048793438</v>
+        <v>0.3280241701111944</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5377,10 +5377,10 @@
         <v>131</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C62">
-        <v>0.3440410835695087</v>
+        <v>0.3469117265610153</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5394,10 +5394,10 @@
         <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C63">
-        <v>0.3944869357543939</v>
+        <v>0.3244957774337724</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2314259305044633</v>
+        <v>0.2539087047533717</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5428,10 +5428,10 @@
         <v>137</v>
       </c>
       <c r="B65" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3127869851834417</v>
+        <v>0.3885605876053833</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C66">
-        <v>0.3197758401127539</v>
+        <v>0.3644380538284632</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5462,10 +5462,10 @@
         <v>141</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3028629444396335</v>
+        <v>0.3747142348305812</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5479,10 +5479,10 @@
         <v>143</v>
       </c>
       <c r="B68" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C68">
-        <v>0.2941451364148224</v>
+        <v>0.2548464223926452</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5496,690 +5496,690 @@
         <v>145</v>
       </c>
       <c r="B69" t="s">
+        <v>55</v>
+      </c>
+      <c r="C69">
+        <v>0.6170484987692131</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" t="s">
         <v>146</v>
-      </c>
-      <c r="C69">
-        <v>0.5017975801290956</v>
-      </c>
-      <c r="D69" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
+        <v>147</v>
+      </c>
+      <c r="B70" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70">
+        <v>0.5888217068563716</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
         <v>148</v>
-      </c>
-      <c r="B70" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70">
-        <v>0.4654360405405868</v>
-      </c>
-      <c r="D70" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
+        <v>149</v>
+      </c>
+      <c r="B71" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71">
+        <v>0.4362970152235134</v>
+      </c>
+      <c r="D71" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" t="s">
         <v>150</v>
-      </c>
-      <c r="B71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71">
-        <v>0.4796720450750187</v>
-      </c>
-      <c r="D71" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
+        <v>151</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72">
+        <v>0.2748369782435519</v>
+      </c>
+      <c r="D72" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" t="s">
         <v>152</v>
-      </c>
-      <c r="B72" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72">
-        <v>0.3732842688466002</v>
-      </c>
-      <c r="D72" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73">
+        <v>0.4243073427386303</v>
+      </c>
+      <c r="D73" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" t="s">
         <v>154</v>
-      </c>
-      <c r="B73" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73">
-        <v>0.5073789464113158</v>
-      </c>
-      <c r="D73" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
+        <v>155</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74">
+        <v>0.4230515768148378</v>
+      </c>
+      <c r="D74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" t="s">
         <v>156</v>
-      </c>
-      <c r="B74" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74">
-        <v>0.5061932669480189</v>
-      </c>
-      <c r="D74" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75">
+        <v>0.3072539083618881</v>
+      </c>
+      <c r="D75" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" t="s">
         <v>158</v>
-      </c>
-      <c r="B75" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75">
-        <v>0.2862247180660402</v>
-      </c>
-      <c r="D75" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76">
+        <v>0.3691422440755467</v>
+      </c>
+      <c r="D76" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" t="s">
         <v>160</v>
-      </c>
-      <c r="B76" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76">
-        <v>0.3784404811457866</v>
-      </c>
-      <c r="D76" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
+        <v>161</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>0.3073974205391639</v>
+      </c>
+      <c r="D77" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" t="s">
         <v>162</v>
-      </c>
-      <c r="B77" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77">
-        <v>0.3116942331266189</v>
-      </c>
-      <c r="D77" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
+        <v>163</v>
+      </c>
+      <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78">
+        <v>0.4448840927486005</v>
+      </c>
+      <c r="D78" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" t="s">
         <v>164</v>
-      </c>
-      <c r="B78" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78">
-        <v>0.4145535775998789</v>
-      </c>
-      <c r="D78" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
+        <v>165</v>
+      </c>
+      <c r="B79" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79">
+        <v>0.2944645328520163</v>
+      </c>
+      <c r="D79" t="s">
+        <v>7</v>
+      </c>
+      <c r="E79" t="s">
         <v>166</v>
-      </c>
-      <c r="B79" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79">
-        <v>0.2628628062198392</v>
-      </c>
-      <c r="D79" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
+        <v>167</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80">
+        <v>0.3580749520416043</v>
+      </c>
+      <c r="D80" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" t="s">
         <v>168</v>
-      </c>
-      <c r="B80" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80">
-        <v>0.3729964423603974</v>
-      </c>
-      <c r="D80" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
+        <v>169</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81">
+        <v>0.3583587302265745</v>
+      </c>
+      <c r="D81" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" t="s">
         <v>170</v>
-      </c>
-      <c r="B81" t="s">
-        <v>21</v>
-      </c>
-      <c r="C81">
-        <v>0.285899685497323</v>
-      </c>
-      <c r="D81" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82">
+        <v>0.418192543564155</v>
+      </c>
+      <c r="D82" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" t="s">
         <v>172</v>
-      </c>
-      <c r="B82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82">
-        <v>0.4406779717359944</v>
-      </c>
-      <c r="D82" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
+        <v>173</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83">
+        <v>0.3039815445594078</v>
+      </c>
+      <c r="D83" t="s">
+        <v>7</v>
+      </c>
+      <c r="E83" t="s">
         <v>174</v>
-      </c>
-      <c r="B83" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83">
-        <v>0.3890493260349111</v>
-      </c>
-      <c r="D83" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
+        <v>175</v>
+      </c>
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84">
+        <v>0.3397572739119206</v>
+      </c>
+      <c r="D84" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" t="s">
         <v>176</v>
-      </c>
-      <c r="B84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84">
-        <v>0.3132639288702744</v>
-      </c>
-      <c r="D84" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
+        <v>177</v>
+      </c>
+      <c r="B85" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85">
+        <v>0.3927094908764024</v>
+      </c>
+      <c r="D85" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" t="s">
         <v>178</v>
-      </c>
-      <c r="B85" t="s">
-        <v>21</v>
-      </c>
-      <c r="C85">
-        <v>0.3161451929337294</v>
-      </c>
-      <c r="D85" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
+        <v>179</v>
+      </c>
+      <c r="B86" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86">
+        <v>0.2499413282739558</v>
+      </c>
+      <c r="D86" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" t="s">
         <v>180</v>
-      </c>
-      <c r="B86" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86">
-        <v>0.315594535528159</v>
-      </c>
-      <c r="D86" t="s">
-        <v>7</v>
-      </c>
-      <c r="E86" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87">
+        <v>0.2719271700995662</v>
+      </c>
+      <c r="D87" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" t="s">
         <v>182</v>
-      </c>
-      <c r="B87" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87">
-        <v>0.2844102711772702</v>
-      </c>
-      <c r="D87" t="s">
-        <v>7</v>
-      </c>
-      <c r="E87" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
+        <v>183</v>
+      </c>
+      <c r="B88" t="s">
+        <v>55</v>
+      </c>
+      <c r="C88">
+        <v>0.3686503676768417</v>
+      </c>
+      <c r="D88" t="s">
+        <v>7</v>
+      </c>
+      <c r="E88" t="s">
         <v>184</v>
-      </c>
-      <c r="B88" t="s">
-        <v>146</v>
-      </c>
-      <c r="C88">
-        <v>0.2888672689455881</v>
-      </c>
-      <c r="D88" t="s">
-        <v>7</v>
-      </c>
-      <c r="E88" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
+        <v>185</v>
+      </c>
+      <c r="B89" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89">
+        <v>0.3357447358727934</v>
+      </c>
+      <c r="D89" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" t="s">
         <v>186</v>
-      </c>
-      <c r="B89" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89">
-        <v>0.3428719566161287</v>
-      </c>
-      <c r="D89" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
+        <v>187</v>
+      </c>
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90">
+        <v>0.3023893754972292</v>
+      </c>
+      <c r="D90" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" t="s">
         <v>188</v>
-      </c>
-      <c r="B90" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90">
-        <v>0.3164855123553829</v>
-      </c>
-      <c r="D90" t="s">
-        <v>7</v>
-      </c>
-      <c r="E90" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
+        <v>189</v>
+      </c>
+      <c r="B91" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91">
+        <v>0.3143305166693383</v>
+      </c>
+      <c r="D91" t="s">
+        <v>7</v>
+      </c>
+      <c r="E91" t="s">
         <v>190</v>
-      </c>
-      <c r="B91" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91">
-        <v>0.3125589937984551</v>
-      </c>
-      <c r="D91" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
+        <v>191</v>
+      </c>
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92">
+        <v>0.3324663872827223</v>
+      </c>
+      <c r="D92" t="s">
+        <v>7</v>
+      </c>
+      <c r="E92" t="s">
         <v>192</v>
-      </c>
-      <c r="B92" t="s">
-        <v>44</v>
-      </c>
-      <c r="C92">
-        <v>0.2865791611095113</v>
-      </c>
-      <c r="D92" t="s">
-        <v>7</v>
-      </c>
-      <c r="E92" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
+        <v>193</v>
+      </c>
+      <c r="B93" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93">
+        <v>0.4471825103126185</v>
+      </c>
+      <c r="D93" t="s">
+        <v>7</v>
+      </c>
+      <c r="E93" t="s">
         <v>194</v>
-      </c>
-      <c r="B93" t="s">
-        <v>21</v>
-      </c>
-      <c r="C93">
-        <v>0.3550430032039424</v>
-      </c>
-      <c r="D93" t="s">
-        <v>7</v>
-      </c>
-      <c r="E93" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B94" t="s">
         <v>44</v>
       </c>
       <c r="C94">
-        <v>0.2599462551503132</v>
+        <v>0.2849527087563791</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
       </c>
       <c r="E94" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
+        <v>197</v>
+      </c>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95">
+        <v>0.4064200664411014</v>
+      </c>
+      <c r="D95" t="s">
+        <v>7</v>
+      </c>
+      <c r="E95" t="s">
         <v>198</v>
-      </c>
-      <c r="B95" t="s">
-        <v>21</v>
-      </c>
-      <c r="C95">
-        <v>0.3303789388838115</v>
-      </c>
-      <c r="D95" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
+        <v>199</v>
+      </c>
+      <c r="B96" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96">
+        <v>0.4291993324001527</v>
+      </c>
+      <c r="D96" t="s">
+        <v>7</v>
+      </c>
+      <c r="E96" t="s">
         <v>200</v>
-      </c>
-      <c r="B96" t="s">
-        <v>21</v>
-      </c>
-      <c r="C96">
-        <v>0.3430321306581801</v>
-      </c>
-      <c r="D96" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B97" t="s">
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3340273911373995</v>
+        <v>0.3682198067986875</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B98" t="s">
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.358046805363488</v>
+        <v>0.3837108264755988</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
+        <v>205</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99">
+        <v>0.3647340089764327</v>
+      </c>
+      <c r="D99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E99" t="s">
         <v>206</v>
-      </c>
-      <c r="B99" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99">
-        <v>0.42547094924343</v>
-      </c>
-      <c r="D99" t="s">
-        <v>7</v>
-      </c>
-      <c r="E99" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B100" t="s">
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.357528750930159</v>
+        <v>0.3834668350292765</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B101" t="s">
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.4221704499426024</v>
+        <v>0.4434874371029829</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
       </c>
       <c r="E101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
+        <v>211</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102">
+        <v>0.3822623482139353</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
+      <c r="E102" t="s">
         <v>212</v>
-      </c>
-      <c r="B102" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102">
-        <v>0.472192057352865</v>
-      </c>
-      <c r="D102" t="s">
-        <v>7</v>
-      </c>
-      <c r="E102" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
+        <v>213</v>
+      </c>
+      <c r="B103" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103">
+        <v>0.276686056809946</v>
+      </c>
+      <c r="D103" t="s">
+        <v>7</v>
+      </c>
+      <c r="E103" t="s">
         <v>214</v>
-      </c>
-      <c r="B103" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103">
-        <v>0.3494325328675375</v>
-      </c>
-      <c r="D103" t="s">
-        <v>7</v>
-      </c>
-      <c r="E103" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
+        <v>215</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104">
+        <v>0.4630438738578206</v>
+      </c>
+      <c r="D104" t="s">
+        <v>7</v>
+      </c>
+      <c r="E104" t="s">
         <v>216</v>
-      </c>
-      <c r="B104" t="s">
-        <v>21</v>
-      </c>
-      <c r="C104">
-        <v>0.3821380598357436</v>
-      </c>
-      <c r="D104" t="s">
-        <v>7</v>
-      </c>
-      <c r="E104" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B105" t="s">
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.346732362314895</v>
+        <v>0.3700315873225005</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
+        <v>219</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106">
+        <v>0.3747707596353598</v>
+      </c>
+      <c r="D106" t="s">
+        <v>7</v>
+      </c>
+      <c r="E106" t="s">
         <v>220</v>
-      </c>
-      <c r="B106" t="s">
-        <v>10</v>
-      </c>
-      <c r="C106">
-        <v>0.376689413346808</v>
-      </c>
-      <c r="D106" t="s">
-        <v>7</v>
-      </c>
-      <c r="E106" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B107" t="s">
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3371398118811238</v>
+        <v>0.3563271474404673</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
       </c>
       <c r="E107" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
+        <v>223</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108">
+        <v>0.3280848523608485</v>
+      </c>
+      <c r="D108" t="s">
+        <v>7</v>
+      </c>
+      <c r="E108" t="s">
         <v>224</v>
-      </c>
-      <c r="B108" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108">
-        <v>0.4076950197056768</v>
-      </c>
-      <c r="D108" t="s">
-        <v>7</v>
-      </c>
-      <c r="E108" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
+        <v>225</v>
+      </c>
+      <c r="B109" t="s">
         <v>226</v>
       </c>
-      <c r="B109" t="s">
-        <v>89</v>
-      </c>
       <c r="C109">
-        <v>0.292278686654382</v>
+        <v>0.2863687728244987</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6193,10 +6193,10 @@
         <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C110">
-        <v>0.2709299302559546</v>
+        <v>0.3453299224367379</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6210,10 +6210,10 @@
         <v>230</v>
       </c>
       <c r="B111" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C111">
-        <v>0.4904953349217805</v>
+        <v>0.4333526216020995</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6227,10 +6227,10 @@
         <v>232</v>
       </c>
       <c r="B112" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C112">
-        <v>0.391843479014723</v>
+        <v>0.2995782855055681</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6244,10 +6244,10 @@
         <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C113">
-        <v>0.476152823296633</v>
+        <v>0.5674471389314046</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6261,10 +6261,10 @@
         <v>236</v>
       </c>
       <c r="B114" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C114">
-        <v>0.6163039471233949</v>
+        <v>0.5775085722349664</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C115">
-        <v>0.3077204583833777</v>
+        <v>0.3519520636234045</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6295,10 +6295,10 @@
         <v>240</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C116">
-        <v>0.4422124266048388</v>
+        <v>0.3835333353129855</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2980800505660757</v>
+        <v>0.2704106631606569</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6329,10 +6329,10 @@
         <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C118">
-        <v>0.3980467567935082</v>
+        <v>0.3795463805879538</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6346,10 +6346,10 @@
         <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C119">
-        <v>0.3792290972214342</v>
+        <v>0.3277972434651102</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6363,10 +6363,10 @@
         <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C120">
-        <v>0.3665539554545157</v>
+        <v>0.3715406732307086</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6380,10 +6380,10 @@
         <v>250</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
       <c r="C121">
-        <v>0.2741970447512193</v>
+        <v>0.239415285955196</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6397,10 +6397,10 @@
         <v>252</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3016955745667039</v>
+        <v>0.3755655958716215</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6414,10 +6414,10 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C123">
-        <v>0.3041478413447269</v>
+        <v>0.3848056746309083</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6431,10 +6431,10 @@
         <v>256</v>
       </c>
       <c r="B124" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C124">
-        <v>0.3787026154112434</v>
+        <v>0.4674631814067407</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C125">
-        <v>0.3208978170715764</v>
+        <v>0.3135740271123884</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3476412468039597</v>
+        <v>0.3359538433229279</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6482,10 +6482,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C127">
-        <v>0.4953523051731307</v>
+        <v>0.4403270998480047</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6499,10 +6499,10 @@
         <v>264</v>
       </c>
       <c r="B128" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4127349667662925</v>
+        <v>0.4894701650933957</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C129">
-        <v>0.3012573767111855</v>
+        <v>0.3504960482119446</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6533,10 +6533,10 @@
         <v>268</v>
       </c>
       <c r="B130" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C130">
-        <v>0.3362366995935229</v>
+        <v>0.4253521710838636</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6550,10 +6550,10 @@
         <v>270</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C131">
-        <v>0.2964939894568442</v>
+        <v>0.2888133283613945</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6567,10 +6567,10 @@
         <v>272</v>
       </c>
       <c r="B132" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C132">
-        <v>0.3960962784766259</v>
+        <v>0.311598353834324</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6584,10 +6584,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3120065160548884</v>
+        <v>0.3879859581021927</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6601,10 +6601,10 @@
         <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C134">
-        <v>0.3331659933734045</v>
+        <v>0.2972778825484494</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6618,10 +6618,10 @@
         <v>278</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C135">
-        <v>0.3377551277078729</v>
+        <v>0.2671343512274562</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3217749581865522</v>
+        <v>0.341233866598735</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6652,10 +6652,10 @@
         <v>282</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C137">
-        <v>0.4197616569093698</v>
+        <v>0.3287164017415332</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6669,10 +6669,10 @@
         <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C138">
-        <v>0.3167666689446598</v>
+        <v>0.3555450359728415</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6686,10 +6686,10 @@
         <v>286</v>
       </c>
       <c r="B139" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C139">
-        <v>0.37468417251184</v>
+        <v>0.2896072803474994</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.3967013929014711</v>
+        <v>0.4158015597956838</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6720,10 +6720,10 @@
         <v>290</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C141">
-        <v>0.3515722740874809</v>
+        <v>0.31864586578441</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6737,10 +6737,10 @@
         <v>292</v>
       </c>
       <c r="B142" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C142">
-        <v>0.4015876151992491</v>
+        <v>0.3905905911649031</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6754,10 +6754,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C143">
-        <v>0.3441872110192552</v>
+        <v>0.2526701232872011</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6771,10 +6771,10 @@
         <v>296</v>
       </c>
       <c r="B144" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C144">
-        <v>0.5929923162364147</v>
+        <v>0.5567654981157845</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6788,10 +6788,10 @@
         <v>298</v>
       </c>
       <c r="B145" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C145">
-        <v>0.3121167136086777</v>
+        <v>0.2709702370890882</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6805,10 +6805,10 @@
         <v>300</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C146">
-        <v>0.3911794982342401</v>
+        <v>0.3099423244526024</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6822,10 +6822,10 @@
         <v>302</v>
       </c>
       <c r="B147" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C147">
-        <v>0.4748135629458538</v>
+        <v>0.3931354938230862</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3092623646117814</v>
+        <v>0.2788566726356119</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6856,10 +6856,10 @@
         <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C149">
-        <v>0.3904671048619432</v>
+        <v>0.3903741526733047</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6873,10 +6873,10 @@
         <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3167900724343132</v>
+        <v>0.3907623202764101</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6890,10 +6890,10 @@
         <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C151">
-        <v>0.2732379423263704</v>
+        <v>0.2621972704275675</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6907,10 +6907,10 @@
         <v>312</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C152">
-        <v>0.6520421776922417</v>
+        <v>0.6299201293985575</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6924,10 +6924,10 @@
         <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C153">
-        <v>0.3339790037606728</v>
+        <v>0.3417163011488755</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3242321514653067</v>
+        <v>0.3479533109407189</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6958,10 +6958,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C155">
-        <v>0.2800004752573139</v>
+        <v>0.3019135551083482</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6975,10 +6975,10 @@
         <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C156">
-        <v>0.3752679410168647</v>
+        <v>0.3614208497534631</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6992,10 +6992,10 @@
         <v>322</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C157">
-        <v>0.365947784227799</v>
+        <v>0.3337048597639303</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3707898383548707</v>
+        <v>0.3855105868615716</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.4095056792580791</v>
+        <v>0.4194627168373174</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7043,10 +7043,10 @@
         <v>328</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C160">
-        <v>0.3968579561645934</v>
+        <v>0.3097026907787334</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7060,10 +7060,10 @@
         <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C161">
-        <v>0.3931165979285502</v>
+        <v>0.2986012878097322</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7077,10 +7077,10 @@
         <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C162">
-        <v>0.5545910855462384</v>
+        <v>0.4806844210969549</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4478359585507252</v>
+        <v>0.4589934843225591</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7111,10 +7111,10 @@
         <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C164">
-        <v>0.3491962528841059</v>
+        <v>0.3486595216338215</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7128,10 +7128,10 @@
         <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C165">
-        <v>0.380408505547995</v>
+        <v>0.3692674179506623</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C166">
-        <v>0.3167461091860118</v>
+        <v>0.3163702718456224</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7162,10 +7162,10 @@
         <v>342</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C167">
-        <v>0.3676414872231386</v>
+        <v>0.2817044448974596</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7179,10 +7179,10 @@
         <v>344</v>
       </c>
       <c r="B168" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C168">
-        <v>0.597830723973946</v>
+        <v>0.5309955398317673</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3236216932380601</v>
+        <v>0.3650103176360437</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7213,10 +7213,10 @@
         <v>348</v>
       </c>
       <c r="B170" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C170">
-        <v>0.3766276623837551</v>
+        <v>0.2789412326352341</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C171">
-        <v>0.2487394058702326</v>
+        <v>0.2551351012690621</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7247,10 +7247,10 @@
         <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C172">
-        <v>0.3964605098752181</v>
+        <v>0.4543777854628477</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7264,10 +7264,10 @@
         <v>354</v>
       </c>
       <c r="B173" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C173">
-        <v>0.3339570538678298</v>
+        <v>0.3270012480761664</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3434136734919773</v>
+        <v>0.2918446203324322</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7298,10 +7298,10 @@
         <v>358</v>
       </c>
       <c r="B175" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C175">
-        <v>0.25076150678887</v>
+        <v>0.3168318726950732</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7315,10 +7315,10 @@
         <v>360</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C176">
-        <v>0.4207252473443582</v>
+        <v>0.3307283229937568</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7332,10 +7332,10 @@
         <v>362</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C177">
-        <v>0.4849292680437667</v>
+        <v>0.4235433947138919</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7349,10 +7349,10 @@
         <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C178">
-        <v>0.4215262727670255</v>
+        <v>0.5057947584512315</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7366,10 +7366,10 @@
         <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3148587475498274</v>
+        <v>0.3942899245266229</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3522284386433004</v>
+        <v>0.3705550272355669</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3422367252128425</v>
+        <v>0.2870018705889952</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7417,10 +7417,10 @@
         <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C182">
-        <v>0.3157021273867006</v>
+        <v>0.3064188896042878</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7434,10 +7434,10 @@
         <v>374</v>
       </c>
       <c r="B183" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C183">
-        <v>0.3145458245517296</v>
+        <v>0.2992371975654323</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7451,10 +7451,10 @@
         <v>376</v>
       </c>
       <c r="B184" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C184">
-        <v>0.3615648060818098</v>
+        <v>0.2788941430921827</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C185">
-        <v>0.3468899910650011</v>
+        <v>0.3982496687005311</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4211161116574755</v>
+        <v>0.4371673545777988</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C187">
-        <v>0.2503493668894138</v>
+        <v>0.2503043598115533</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7519,10 +7519,10 @@
         <v>384</v>
       </c>
       <c r="B188" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C188">
-        <v>0.4673946388935998</v>
+        <v>0.4509070339610649</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3414139838521207</v>
+        <v>0.3271105330459483</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C190">
-        <v>0.2946375365955958</v>
+        <v>0.3135900989133935</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7570,10 +7570,10 @@
         <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C191">
-        <v>0.3644840206112219</v>
+        <v>0.3478047716957799</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7587,10 +7587,10 @@
         <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C192">
-        <v>0.374552141083195</v>
+        <v>0.4635917570073048</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7604,10 +7604,10 @@
         <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C193">
-        <v>0.4432750810320481</v>
+        <v>0.5267265019044698</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7621,10 +7621,10 @@
         <v>396</v>
       </c>
       <c r="B194" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C194">
-        <v>0.3902776861629508</v>
+        <v>0.4094287844927014</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7638,10 +7638,10 @@
         <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C195">
-        <v>0.3453270556581568</v>
+        <v>0.3994397023921899</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7655,10 +7655,10 @@
         <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C196">
-        <v>0.3603477954063979</v>
+        <v>0.3267175072508403</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7672,10 +7672,10 @@
         <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C197">
-        <v>0.352076744301615</v>
+        <v>0.3358121387598624</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7689,10 +7689,10 @@
         <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C198">
-        <v>0.5327714066262805</v>
+        <v>0.4674657368173894</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7706,10 +7706,10 @@
         <v>406</v>
       </c>
       <c r="B199" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C199">
-        <v>0.5956393195859917</v>
+        <v>0.5696057759725685</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C200">
-        <v>0.3400205350761787</v>
+        <v>0.4304579739822558</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7740,10 +7740,10 @@
         <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3040819775222374</v>
+        <v>0.3764407087652451</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7757,10 +7757,10 @@
         <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C202">
-        <v>0.4243055205978848</v>
+        <v>0.4046168618572051</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7774,10 +7774,10 @@
         <v>414</v>
       </c>
       <c r="B203" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C203">
-        <v>0.5329222814533608</v>
+        <v>0.4568623066862512</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7791,10 +7791,10 @@
         <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C204">
-        <v>0.4621664773108676</v>
+        <v>0.3744618925309421</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7808,10 +7808,10 @@
         <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C205">
-        <v>0.4871876817812261</v>
+        <v>0.4698139367982812</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7825,10 +7825,10 @@
         <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C206">
-        <v>0.3593038159651081</v>
+        <v>0.4435262173293562</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5564168477814087</v>
+        <v>0.5813801968304581</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.3783720298916468</v>
+        <v>0.3925037138931228</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7876,10 +7876,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C209">
-        <v>0.5385972138023822</v>
+        <v>0.5376236004174237</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7893,10 +7893,10 @@
         <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C210">
-        <v>0.4273974038248865</v>
+        <v>0.3484496358644602</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7910,10 +7910,10 @@
         <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C211">
-        <v>0.431361920088507</v>
+        <v>0.5169148396657018</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C212">
-        <v>0.2917264812457533</v>
+        <v>0.3395397310825237</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C213">
-        <v>0.3138742805834103</v>
+        <v>0.3344726409472614</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7961,10 +7961,10 @@
         <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C214">
-        <v>0.3659730270226195</v>
+        <v>0.4594230837447755</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7978,10 +7978,10 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C215">
-        <v>0.4543193494753476</v>
+        <v>0.4488599873063641</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7995,10 +7995,10 @@
         <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3085109392651217</v>
+        <v>0.3708247953597161</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C217">
-        <v>0.3426504456698292</v>
+        <v>0.4227772601940245</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3462381733932525</v>
+        <v>0.349998453575616</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.4846126145260455</v>
+        <v>0.5053417032046279</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C220">
-        <v>0.2539338583012547</v>
+        <v>0.3035662356904427</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8080,10 +8080,10 @@
         <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C221">
-        <v>0.3384668714334471</v>
+        <v>0.4221274882600484</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C222">
-        <v>0.321291573612932</v>
+        <v>0.3285130587287675</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8114,10 +8114,10 @@
         <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C223">
-        <v>0.516312677067991</v>
+        <v>0.5193281645289345</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8131,10 +8131,10 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C224">
-        <v>0.3459251653438432</v>
+        <v>0.3397699092844189</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8148,10 +8148,10 @@
         <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C225">
-        <v>0.3331664437939075</v>
+        <v>0.4193031230753303</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8165,10 +8165,10 @@
         <v>460</v>
       </c>
       <c r="B226" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C226">
-        <v>0.4933916584817199</v>
+        <v>0.4067036337563059</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8182,10 +8182,10 @@
         <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C227">
-        <v>0.3674406570641466</v>
+        <v>0.3565522565355359</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8199,10 +8199,10 @@
         <v>464</v>
       </c>
       <c r="B228" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C228">
-        <v>0.4740671064855538</v>
+        <v>0.4072860987211013</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8216,10 +8216,10 @@
         <v>466</v>
       </c>
       <c r="B229" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C229">
-        <v>0.5414075408119848</v>
+        <v>0.478209274018106</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3466307955223518</v>
+        <v>0.3617160639822816</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8250,10 +8250,10 @@
         <v>470</v>
       </c>
       <c r="B231" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C231">
-        <v>0.3074923174918969</v>
+        <v>0.371540940688341</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8267,10 +8267,10 @@
         <v>472</v>
       </c>
       <c r="B232" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C232">
-        <v>0.5757970877399116</v>
+        <v>0.5359224265210301</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4166327780722927</v>
+        <v>0.4189746899217709</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8301,10 +8301,10 @@
         <v>476</v>
       </c>
       <c r="B234" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C234">
-        <v>0.4300151521451824</v>
+        <v>0.3399497554812264</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8318,10 +8318,10 @@
         <v>478</v>
       </c>
       <c r="B235" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C235">
-        <v>0.491783743588743</v>
+        <v>0.4179399422780793</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8335,10 +8335,10 @@
         <v>480</v>
       </c>
       <c r="B236" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C236">
-        <v>0.2871229186963779</v>
+        <v>0.3007215480949045</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8352,10 +8352,10 @@
         <v>482</v>
       </c>
       <c r="B237" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C237">
-        <v>0.3502686235155923</v>
+        <v>0.3487574684164745</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8369,10 +8369,10 @@
         <v>484</v>
       </c>
       <c r="B238" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C238">
-        <v>0.3765417504241466</v>
+        <v>0.2948267929467107</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8386,10 +8386,10 @@
         <v>486</v>
       </c>
       <c r="B239" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C239">
-        <v>0.4021149981103511</v>
+        <v>0.3171193034111763</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8403,10 +8403,10 @@
         <v>488</v>
       </c>
       <c r="B240" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="C240">
-        <v>0.359081098369969</v>
+        <v>0.3578991224779405</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C241">
-        <v>0.2373421429384271</v>
+        <v>0.2415280644063261</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C242">
-        <v>0.3097228446452674</v>
+        <v>0.3678689751000186</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8454,10 +8454,10 @@
         <v>494</v>
       </c>
       <c r="B243" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C243">
-        <v>0.4761722246503817</v>
+        <v>0.5631426894475878</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8471,10 +8471,10 @@
         <v>496</v>
       </c>
       <c r="B244" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="C244">
-        <v>0.3913510886563449</v>
+        <v>0.3967065205698253</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8488,10 +8488,10 @@
         <v>498</v>
       </c>
       <c r="B245" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C245">
-        <v>0.6167316358264125</v>
+        <v>0.5608969233781576</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8505,10 +8505,10 @@
         <v>500</v>
       </c>
       <c r="B246" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C246">
-        <v>0.4444899475059202</v>
+        <v>0.3469089661040908</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8522,10 +8522,10 @@
         <v>502</v>
       </c>
       <c r="B247" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C247">
-        <v>0.4285989532771451</v>
+        <v>0.3533167775091695</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8539,10 +8539,10 @@
         <v>504</v>
       </c>
       <c r="B248" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C248">
-        <v>0.3862045892219038</v>
+        <v>0.3746436646412047</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8556,10 +8556,10 @@
         <v>506</v>
       </c>
       <c r="B249" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C249">
-        <v>0.4205149735535716</v>
+        <v>0.3322106632872703</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8573,10 +8573,10 @@
         <v>508</v>
       </c>
       <c r="B250" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C250">
-        <v>0.2761279042441301</v>
+        <v>0.3476465022251459</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4312215216228205</v>
+        <v>0.4580880044379424</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8607,10 +8607,10 @@
         <v>512</v>
       </c>
       <c r="B252" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C252">
-        <v>0.4387977701650266</v>
+        <v>0.3492609486592563</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8624,10 +8624,10 @@
         <v>514</v>
       </c>
       <c r="B253" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C253">
-        <v>0.3929082253459785</v>
+        <v>0.3082576857216566</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8641,10 +8641,10 @@
         <v>516</v>
       </c>
       <c r="B254" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C254">
-        <v>0.4835198515806392</v>
+        <v>0.3934280770683309</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8658,10 +8658,10 @@
         <v>518</v>
       </c>
       <c r="B255" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C255">
-        <v>0.39122151418524</v>
+        <v>0.485778768901457</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8675,10 +8675,10 @@
         <v>520</v>
       </c>
       <c r="B256" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C256">
-        <v>0.591050279575541</v>
+        <v>0.5168415513385844</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8692,10 +8692,10 @@
         <v>522</v>
       </c>
       <c r="B257" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C257">
-        <v>0.4412099133333313</v>
+        <v>0.3483668542893446</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8709,10 +8709,10 @@
         <v>524</v>
       </c>
       <c r="B258" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C258">
-        <v>0.5027170971497459</v>
+        <v>0.4339177389936856</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C259">
-        <v>0.3057700321589019</v>
+        <v>0.3587561206044904</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8743,10 +8743,10 @@
         <v>528</v>
       </c>
       <c r="B260" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C260">
-        <v>0.443982999701498</v>
+        <v>0.3582434270719597</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8760,10 +8760,10 @@
         <v>530</v>
       </c>
       <c r="B261" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C261">
-        <v>0.4659876901018064</v>
+        <v>0.3836206909437639</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8777,10 +8777,10 @@
         <v>532</v>
       </c>
       <c r="B262" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C262">
-        <v>0.4227964258889865</v>
+        <v>0.3365263119405533</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8794,10 +8794,10 @@
         <v>534</v>
       </c>
       <c r="B263" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C263">
-        <v>0.4544066496852124</v>
+        <v>0.3572537917834441</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8811,10 +8811,10 @@
         <v>536</v>
       </c>
       <c r="B264" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C264">
-        <v>0.4568591242957185</v>
+        <v>0.3585207180058465</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8828,10 +8828,10 @@
         <v>538</v>
       </c>
       <c r="B265" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C265">
-        <v>0.3607496542593642</v>
+        <v>0.2768594029362588</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="C266">
-        <v>0.326551862579202</v>
+        <v>0.3303766985844671</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
         <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C267">
-        <v>0.2873292161155256</v>
+        <v>0.3426118127216689</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8879,10 +8879,10 @@
         <v>544</v>
       </c>
       <c r="B268" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C268">
-        <v>0.4297559732300851</v>
+        <v>0.3352435769684094</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3638245148740752</v>
+        <v>0.3773700750272198</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8913,10 +8913,10 @@
         <v>548</v>
       </c>
       <c r="B270" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C270">
-        <v>0.5254307612331567</v>
+        <v>0.4614377255765756</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8930,10 +8930,10 @@
         <v>550</v>
       </c>
       <c r="B271" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C271">
-        <v>0.5397518913966814</v>
+        <v>0.4912229656120447</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8947,10 +8947,10 @@
         <v>552</v>
       </c>
       <c r="B272" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C272">
-        <v>0.3787472253228006</v>
+        <v>0.2862940086565663</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8964,10 +8964,10 @@
         <v>554</v>
       </c>
       <c r="B273" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C273">
-        <v>0.5267583133616188</v>
+        <v>0.4432542996505917</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8981,10 +8981,10 @@
         <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C274">
-        <v>0.3292749467741282</v>
+        <v>0.41706910111738</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C275">
-        <v>0.2592395619025692</v>
+        <v>0.2740689471560268</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9015,10 +9015,10 @@
         <v>560</v>
       </c>
       <c r="B276" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C276">
-        <v>0.3228610064462192</v>
+        <v>0.2506042507634856</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C277">
-        <v>0.380080886061899</v>
+        <v>0.4237701615624012</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9049,10 +9049,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C278">
-        <v>0.4265596516480366</v>
+        <v>0.4399600377445592</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9066,10 +9066,10 @@
         <v>566</v>
       </c>
       <c r="B279" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C279">
-        <v>0.5512423673939065</v>
+        <v>0.4982760599505469</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9083,10 +9083,10 @@
         <v>568</v>
       </c>
       <c r="B280" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C280">
-        <v>0.48420214824229</v>
+        <v>0.4007271463144875</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9100,10 +9100,10 @@
         <v>570</v>
       </c>
       <c r="B281" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C281">
-        <v>0.4066044172165793</v>
+        <v>0.3302369026738208</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9117,10 +9117,10 @@
         <v>572</v>
       </c>
       <c r="B282" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C282">
-        <v>0.3970256469242343</v>
+        <v>0.4890454441875942</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9134,10 +9134,10 @@
         <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C283">
-        <v>0.3736794764193132</v>
+        <v>0.3694463647031994</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9151,10 +9151,10 @@
         <v>576</v>
       </c>
       <c r="B284" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C284">
-        <v>0.3242885898818839</v>
+        <v>0.2988544464669598</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C285">
-        <v>0.2551415358942214</v>
+        <v>0.2742069757022258</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9185,10 +9185,10 @@
         <v>580</v>
       </c>
       <c r="B286" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C286">
-        <v>0.2939193638088055</v>
+        <v>0.2850522212049605</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.4601916380877823</v>
+        <v>0.498932186824273</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C288">
-        <v>0.2534148333944155</v>
+        <v>0.3125620285813854</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9236,10 +9236,10 @@
         <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C289">
-        <v>0.3412961849311597</v>
+        <v>0.4261754810826845</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9253,10 +9253,10 @@
         <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C290">
-        <v>0.283698878383284</v>
+        <v>0.3600746087327519</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9270,10 +9270,10 @@
         <v>590</v>
       </c>
       <c r="B291" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C291">
-        <v>0.4189728379316511</v>
+        <v>0.4221360753703444</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="C292">
-        <v>0.4267907566618528</v>
+        <v>0.525653847638159</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9304,10 +9304,10 @@
         <v>594</v>
       </c>
       <c r="B293" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C293">
-        <v>0.5989746747883173</v>
+        <v>0.5635989722321237</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9321,10 +9321,10 @@
         <v>596</v>
       </c>
       <c r="B294" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C294">
-        <v>0.3611743368077697</v>
+        <v>0.4484213377608334</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9338,10 +9338,10 @@
         <v>598</v>
       </c>
       <c r="B295" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C295">
-        <v>0.3667747879979016</v>
+        <v>0.3377573281505317</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C296">
-        <v>0.2894713989543</v>
+        <v>0.3669232161612057</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9372,10 +9372,10 @@
         <v>602</v>
       </c>
       <c r="B297" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C297">
-        <v>0.4704549575627175</v>
+        <v>0.4516856472156731</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9389,10 +9389,10 @@
         <v>604</v>
       </c>
       <c r="B298" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C298">
-        <v>0.4124084135388045</v>
+        <v>0.3855597053387357</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2713640289352758</v>
+        <v>0.2954543515004676</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9423,10 +9423,10 @@
         <v>608</v>
       </c>
       <c r="B300" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C300">
-        <v>0.363583962491223</v>
+        <v>0.3582485477773821</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9440,10 +9440,10 @@
         <v>610</v>
       </c>
       <c r="B301" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C301">
-        <v>0.3704202316569088</v>
+        <v>0.280278534121455</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.5294143647341687</v>
+        <v>0.5468532580878058</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9474,10 +9474,10 @@
         <v>614</v>
       </c>
       <c r="B303" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C303">
-        <v>0.3245359222366417</v>
+        <v>0.3365266236897289</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C304">
-        <v>0.3203842635161764</v>
+        <v>0.3111280781943151</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4464662486517647</v>
+        <v>0.4588884454673973</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9525,10 +9525,10 @@
         <v>620</v>
       </c>
       <c r="B306" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C306">
-        <v>0.3652121822473804</v>
+        <v>0.4507992753924156</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9542,10 +9542,10 @@
         <v>622</v>
       </c>
       <c r="B307" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C307">
-        <v>0.4550807680031991</v>
+        <v>0.3869018250779983</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9559,10 +9559,10 @@
         <v>624</v>
       </c>
       <c r="B308" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C308">
-        <v>0.4053220897911998</v>
+        <v>0.3239502100185639</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9576,10 +9576,10 @@
         <v>626</v>
       </c>
       <c r="B309" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C309">
-        <v>0.291279916626478</v>
+        <v>0.2466967389272477</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9593,10 +9593,10 @@
         <v>628</v>
       </c>
       <c r="B310" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C310">
-        <v>0.3993922455995887</v>
+        <v>0.3270035817865354</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9610,10 +9610,10 @@
         <v>630</v>
       </c>
       <c r="B311" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C311">
-        <v>0.3358307348860017</v>
+        <v>0.4255272477999702</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9627,10 +9627,10 @@
         <v>632</v>
       </c>
       <c r="B312" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C312">
-        <v>0.2812620291193779</v>
+        <v>0.3076666153176793</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3055676365224455</v>
+        <v>0.3288652229941081</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C314">
-        <v>0.3439551170758134</v>
+        <v>0.3359803891311087</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.4966969155763854</v>
+        <v>0.5067952254691064</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9695,10 +9695,10 @@
         <v>640</v>
       </c>
       <c r="B316" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C316">
-        <v>0.4103647864530215</v>
+        <v>0.3126693134554198</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9712,10 +9712,10 @@
         <v>642</v>
       </c>
       <c r="B317" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C317">
-        <v>0.5316533356365678</v>
+        <v>0.4338054903265685</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9729,10 +9729,10 @@
         <v>644</v>
       </c>
       <c r="B318" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C318">
-        <v>0.5493662568276458</v>
+        <v>0.4639610887766684</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9746,10 +9746,10 @@
         <v>646</v>
       </c>
       <c r="B319" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C319">
-        <v>0.3670801229641468</v>
+        <v>0.281453691999594</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C320">
-        <v>0.2727251036549035</v>
+        <v>0.3369924117532813</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9780,10 +9780,10 @@
         <v>650</v>
       </c>
       <c r="B321" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C321">
-        <v>0.3510224409142203</v>
+        <v>0.297678638419612</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9797,10 +9797,10 @@
         <v>652</v>
       </c>
       <c r="B322" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C322">
-        <v>0.3754361384320462</v>
+        <v>0.3926419775056722</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9814,10 +9814,10 @@
         <v>654</v>
       </c>
       <c r="B323" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C323">
-        <v>0.3979525829273354</v>
+        <v>0.3827948295802887</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.3733039306047221</v>
+        <v>0.386645336999747</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9848,10 +9848,10 @@
         <v>658</v>
       </c>
       <c r="B325" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C325">
-        <v>0.2481850646054373</v>
+        <v>0.2617646563396065</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9865,10 +9865,10 @@
         <v>660</v>
       </c>
       <c r="B326" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3504757066485311</v>
+        <v>0.3623588153316062</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3230640204435239</v>
+        <v>0.3456963688617526</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C328">
-        <v>0.2688174336111492</v>
+        <v>0.3394269828848928</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C329">
-        <v>0.32741026318025</v>
+        <v>0.3557060564537073</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C330">
-        <v>0.2963130927172308</v>
+        <v>0.3741163403795813</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9950,10 +9950,10 @@
         <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C331">
-        <v>0.4094231845338929</v>
+        <v>0.3740057242197506</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9967,10 +9967,10 @@
         <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C332">
-        <v>0.374082020147678</v>
+        <v>0.3599478164147819</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9984,10 +9984,10 @@
         <v>674</v>
       </c>
       <c r="B333" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C333">
-        <v>0.4892548293162943</v>
+        <v>0.3976424051110828</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C334">
-        <v>0.2974319773293228</v>
+        <v>0.3228595902918182</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10018,10 +10018,10 @@
         <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3186082231370499</v>
+        <v>0.3832111665013808</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C336">
-        <v>0.310984741789172</v>
+        <v>0.3480340015611227</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4634225262358527</v>
+        <v>0.4646657926584409</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10069,10 +10069,10 @@
         <v>684</v>
       </c>
       <c r="B338" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C338">
-        <v>0.3045355807775115</v>
+        <v>0.3019914657634178</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10086,10 +10086,10 @@
         <v>686</v>
       </c>
       <c r="B339" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C339">
-        <v>0.4247743495127151</v>
+        <v>0.5229369383698881</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10103,10 +10103,10 @@
         <v>688</v>
       </c>
       <c r="B340" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3027873298954217</v>
+        <v>0.3727142685963155</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10120,10 +10120,10 @@
         <v>690</v>
       </c>
       <c r="B341" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C341">
-        <v>0.3099381151964136</v>
+        <v>0.2646404923226637</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10137,10 +10137,10 @@
         <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C342">
-        <v>0.2720322087163045</v>
+        <v>0.2629406080293007</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10154,10 +10154,10 @@
         <v>694</v>
       </c>
       <c r="B343" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C343">
-        <v>0.424763103422661</v>
+        <v>0.4061195241337882</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C344">
-        <v>0.2736441817800995</v>
+        <v>0.3485095970532197</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10188,10 +10188,10 @@
         <v>698</v>
       </c>
       <c r="B345" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C345">
-        <v>0.3787786366375068</v>
+        <v>0.295941188519612</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C346">
-        <v>0.3513548372890778</v>
+        <v>0.3436747931956213</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10222,10 +10222,10 @@
         <v>702</v>
       </c>
       <c r="B347" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3062791885084924</v>
+        <v>0.3854573395067151</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10239,10 +10239,10 @@
         <v>704</v>
       </c>
       <c r="B348" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C348">
-        <v>0.3384409514802589</v>
+        <v>0.2440883721265354</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10256,10 +10256,10 @@
         <v>706</v>
       </c>
       <c r="B349" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C349">
-        <v>0.488084550198791</v>
+        <v>0.4174471625982288</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10273,10 +10273,10 @@
         <v>708</v>
       </c>
       <c r="B350" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C350">
-        <v>0.3565010186469181</v>
+        <v>0.4362776183642587</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="C351">
-        <v>0.2439094400617322</v>
+        <v>0.2944602101397409</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10307,10 +10307,10 @@
         <v>712</v>
       </c>
       <c r="B352" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C352">
-        <v>0.4056019596244076</v>
+        <v>0.4914376101435488</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10324,10 +10324,10 @@
         <v>714</v>
       </c>
       <c r="B353" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C353">
-        <v>0.3935586596025323</v>
+        <v>0.3908412847950963</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10341,10 +10341,10 @@
         <v>716</v>
       </c>
       <c r="B354" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C354">
-        <v>0.2911160258368046</v>
+        <v>0.3084127843517361</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10358,10 +10358,10 @@
         <v>718</v>
       </c>
       <c r="B355" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C355">
-        <v>0.3776230286358142</v>
+        <v>0.2825768602525066</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10375,10 +10375,10 @@
         <v>720</v>
       </c>
       <c r="B356" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C356">
-        <v>0.3423834660717359</v>
+        <v>0.2561438461810645</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10392,10 +10392,10 @@
         <v>722</v>
       </c>
       <c r="B357" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C357">
-        <v>0.4053848969827728</v>
+        <v>0.364599628877601</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10409,10 +10409,10 @@
         <v>724</v>
       </c>
       <c r="B358" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C358">
-        <v>0.340499239330625</v>
+        <v>0.3327945676253314</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.4787493949281007</v>
+        <v>0.5083977086964667</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10443,10 +10443,10 @@
         <v>728</v>
       </c>
       <c r="B360" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C360">
-        <v>0.482874716038117</v>
+        <v>0.4480379910313607</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10460,10 +10460,10 @@
         <v>730</v>
       </c>
       <c r="B361" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3057261052694391</v>
+        <v>0.3880574026814158</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10477,10 +10477,10 @@
         <v>732</v>
       </c>
       <c r="B362" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C362">
-        <v>0.3593817479086274</v>
+        <v>0.2742447834431703</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10494,10 +10494,10 @@
         <v>734</v>
       </c>
       <c r="B363" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C363">
-        <v>0.3135367474708399</v>
+        <v>0.3197811244787069</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10511,10 +10511,10 @@
         <v>736</v>
       </c>
       <c r="B364" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C364">
-        <v>0.3485105306367041</v>
+        <v>0.3405263165985451</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10528,10 +10528,10 @@
         <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C365">
-        <v>0.3030814083584488</v>
+        <v>0.3419134375884932</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10545,10 +10545,10 @@
         <v>740</v>
       </c>
       <c r="B366" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C366">
-        <v>0.2498127249746581</v>
+        <v>0.3114978712436072</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10562,10 +10562,10 @@
         <v>742</v>
       </c>
       <c r="B367" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C367">
-        <v>0.3225803122161974</v>
+        <v>0.2799753187034235</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10579,10 +10579,10 @@
         <v>744</v>
       </c>
       <c r="B368" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C368">
-        <v>0.2778289159575764</v>
+        <v>0.3526720097001454</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10596,10 +10596,10 @@
         <v>746</v>
       </c>
       <c r="B369" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C369">
-        <v>0.5070628502286457</v>
+        <v>0.4364861098342026</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10613,10 +10613,10 @@
         <v>748</v>
       </c>
       <c r="B370" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C370">
-        <v>0.3226429437291963</v>
+        <v>0.3765858561750022</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10630,10 +10630,10 @@
         <v>750</v>
       </c>
       <c r="B371" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C371">
-        <v>0.473414105434951</v>
+        <v>0.3831973584660654</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10647,10 +10647,10 @@
         <v>752</v>
       </c>
       <c r="B372" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C372">
-        <v>0.3845210664602465</v>
+        <v>0.3009364624217767</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10664,10 +10664,10 @@
         <v>754</v>
       </c>
       <c r="B373" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C373">
-        <v>0.4407791383706006</v>
+        <v>0.3786489234139668</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10681,10 +10681,10 @@
         <v>756</v>
       </c>
       <c r="B374" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C374">
-        <v>0.5051157965012489</v>
+        <v>0.4291365026335516</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10698,10 +10698,10 @@
         <v>758</v>
       </c>
       <c r="B375" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C375">
-        <v>0.4966345232081801</v>
+        <v>0.3994720425483808</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10715,10 +10715,10 @@
         <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C376">
-        <v>0.34785348190755</v>
+        <v>0.4107425351251811</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10732,10 +10732,10 @@
         <v>762</v>
       </c>
       <c r="B377" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C377">
-        <v>0.4727253875865513</v>
+        <v>0.3950417342449342</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10749,10 +10749,10 @@
         <v>764</v>
       </c>
       <c r="B378" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C378">
-        <v>0.3388704616711796</v>
+        <v>0.2553231844164487</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10766,10 +10766,10 @@
         <v>766</v>
       </c>
       <c r="B379" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C379">
-        <v>0.3531624530548816</v>
+        <v>0.2738113043489911</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10783,10 +10783,10 @@
         <v>768</v>
       </c>
       <c r="B380" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C380">
-        <v>0.367013700839659</v>
+        <v>0.2835974480148041</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10800,10 +10800,10 @@
         <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C381">
-        <v>0.482561096435849</v>
+        <v>0.4585758727431198</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10817,10 +10817,10 @@
         <v>772</v>
       </c>
       <c r="B382" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C382">
-        <v>0.3483262967288834</v>
+        <v>0.2687904632194298</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10834,10 +10834,10 @@
         <v>774</v>
       </c>
       <c r="B383" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C383">
-        <v>0.4013649484129872</v>
+        <v>0.3861275542003516</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4325006669733273</v>
+        <v>0.4683436594737762</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10868,10 +10868,10 @@
         <v>778</v>
       </c>
       <c r="B385" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C385">
-        <v>0.4037620546250527</v>
+        <v>0.3133983599254345</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3077834039783328</v>
+        <v>0.3883974646645231</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10902,10 +10902,10 @@
         <v>782</v>
       </c>
       <c r="B387" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C387">
-        <v>0.4326294215640941</v>
+        <v>0.4256506166472542</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3384434455649635</v>
+        <v>0.3633809092216613</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10936,10 +10936,10 @@
         <v>786</v>
       </c>
       <c r="B389" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C389">
-        <v>0.3473219016142112</v>
+        <v>0.3165690713368335</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10953,10 +10953,10 @@
         <v>788</v>
       </c>
       <c r="B390" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C390">
-        <v>0.311226641833374</v>
+        <v>0.3934588920757937</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10970,10 +10970,10 @@
         <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C391">
-        <v>0.3281339909041506</v>
+        <v>0.4099835638488465</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10987,10 +10987,10 @@
         <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C392">
-        <v>0.3127889719477722</v>
+        <v>0.3106266818786358</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11004,10 +11004,10 @@
         <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C393">
-        <v>0.4289064897451685</v>
+        <v>0.4201246633925797</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11021,10 +11021,10 @@
         <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C394">
-        <v>0.3457209710589936</v>
+        <v>0.4270827565368991</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11038,10 +11038,10 @@
         <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C395">
-        <v>0.423487880847166</v>
+        <v>0.4162389037864443</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11055,10 +11055,10 @@
         <v>800</v>
       </c>
       <c r="B396" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C396">
-        <v>0.4009308469098222</v>
+        <v>0.3184925132274275</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11072,10 +11072,10 @@
         <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C397">
-        <v>0.3801726646296298</v>
+        <v>0.3725225600220212</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11089,10 +11089,10 @@
         <v>804</v>
       </c>
       <c r="B398" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C398">
-        <v>0.4922621613195413</v>
+        <v>0.4129044845583654</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11106,10 +11106,10 @@
         <v>806</v>
       </c>
       <c r="B399" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C399">
-        <v>0.3712242931009684</v>
+        <v>0.4532777624670984</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3582789432867072</v>
+        <v>0.2925780896705066</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11140,10 +11140,10 @@
         <v>810</v>
       </c>
       <c r="B401" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C401">
-        <v>0.4306268340462955</v>
+        <v>0.5164592358243356</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11157,10 +11157,10 @@
         <v>812</v>
       </c>
       <c r="B402" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C402">
-        <v>0.4099504404221152</v>
+        <v>0.3260109118842376</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11174,10 +11174,10 @@
         <v>814</v>
       </c>
       <c r="B403" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C403">
-        <v>0.2812999025878103</v>
+        <v>0.3118425906573278</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C404">
-        <v>0.3314861853585954</v>
+        <v>0.310312847030522</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11208,10 +11208,10 @@
         <v>818</v>
       </c>
       <c r="B405" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C405">
-        <v>0.4057880875464539</v>
+        <v>0.322214728226788</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="C406">
-        <v>0.4310370935190977</v>
+        <v>0.5641207116370761</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11242,10 +11242,10 @@
         <v>822</v>
       </c>
       <c r="B407" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C407">
-        <v>0.3777149561166234</v>
+        <v>0.35431604488359</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11259,10 +11259,10 @@
         <v>824</v>
       </c>
       <c r="B408" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C408">
-        <v>0.4904185861053884</v>
+        <v>0.3979601146302134</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11276,10 +11276,10 @@
         <v>826</v>
       </c>
       <c r="B409" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C409">
-        <v>0.4879487748474435</v>
+        <v>0.4073761270312487</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11293,10 +11293,10 @@
         <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C410">
-        <v>0.2926165443165696</v>
+        <v>0.3680662370116374</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11310,10 +11310,10 @@
         <v>830</v>
       </c>
       <c r="B411" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C411">
-        <v>0.3498514796781526</v>
+        <v>0.3446928305871058</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11327,10 +11327,10 @@
         <v>832</v>
       </c>
       <c r="B412" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C412">
-        <v>0.462808576076613</v>
+        <v>0.3837857829606339</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11344,10 +11344,10 @@
         <v>834</v>
       </c>
       <c r="B413" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C413">
-        <v>0.262395456813332</v>
+        <v>0.3015125354936323</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11361,10 +11361,10 @@
         <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3215743714000109</v>
+        <v>0.3998058006484279</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C415">
-        <v>0.3547104929653703</v>
+        <v>0.4120271617582045</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11395,10 +11395,10 @@
         <v>840</v>
       </c>
       <c r="B416" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4262056500825738</v>
+        <v>0.4755938697738304</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11412,10 +11412,10 @@
         <v>842</v>
       </c>
       <c r="B417" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C417">
-        <v>0.2755574304610836</v>
+        <v>0.2703469377164524</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C418">
-        <v>0.3016985051150668</v>
+        <v>0.2976644712293582</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11446,10 +11446,10 @@
         <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C419">
-        <v>0.2977486125484571</v>
+        <v>0.381695985427095</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.3826282081906937</v>
+        <v>0.409418471981977</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.3897236305171813</v>
+        <v>0.3948507639962782</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11497,10 +11497,10 @@
         <v>852</v>
       </c>
       <c r="B422" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C422">
-        <v>0.3761520327417773</v>
+        <v>0.2858022723371625</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4629102731348608</v>
+        <v>0.4695105045010427</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11531,10 +11531,10 @@
         <v>856</v>
       </c>
       <c r="B424" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C424">
-        <v>0.3322489021763431</v>
+        <v>0.3814442347106263</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11548,10 +11548,10 @@
         <v>858</v>
       </c>
       <c r="B425" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C425">
-        <v>0.3506354662280581</v>
+        <v>0.3066587097838216</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11565,10 +11565,10 @@
         <v>860</v>
       </c>
       <c r="B426" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C426">
-        <v>0.3364547213196367</v>
+        <v>0.4177088176906886</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11582,10 +11582,10 @@
         <v>862</v>
       </c>
       <c r="B427" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C427">
-        <v>0.27089322326954</v>
+        <v>0.3395386312667456</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C428">
-        <v>0.2874198743095294</v>
+        <v>0.3199939921473181</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11616,10 +11616,10 @@
         <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C429">
-        <v>0.3616010517391045</v>
+        <v>0.3501440395239063</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11633,10 +11633,10 @@
         <v>868</v>
       </c>
       <c r="B430" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C430">
-        <v>0.3436637411069952</v>
+        <v>0.3618644436681286</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C431">
-        <v>0.2963546878881709</v>
+        <v>0.3019614442246021</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11667,10 +11667,10 @@
         <v>872</v>
       </c>
       <c r="B432" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3183933194157216</v>
+        <v>0.3971218435022421</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11684,10 +11684,10 @@
         <v>874</v>
       </c>
       <c r="B433" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C433">
-        <v>0.3308828066130786</v>
+        <v>0.2744523528212764</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11701,10 +11701,10 @@
         <v>876</v>
       </c>
       <c r="B434" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C434">
-        <v>0.3324871782151275</v>
+        <v>0.4133916750746118</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11718,10 +11718,10 @@
         <v>878</v>
       </c>
       <c r="B435" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C435">
-        <v>0.3863446408067679</v>
+        <v>0.3725868197299252</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11735,10 +11735,10 @@
         <v>880</v>
       </c>
       <c r="B436" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C436">
-        <v>0.2933078834835189</v>
+        <v>0.3698186155623084</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11752,10 +11752,10 @@
         <v>882</v>
       </c>
       <c r="B437" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C437">
-        <v>0.3273027889224993</v>
+        <v>0.3477244773820562</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11769,10 +11769,10 @@
         <v>884</v>
       </c>
       <c r="B438" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C438">
-        <v>0.3349378445443585</v>
+        <v>0.4118026022837792</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11786,10 +11786,10 @@
         <v>886</v>
       </c>
       <c r="B439" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C439">
-        <v>0.3855406523205607</v>
+        <v>0.2914424827795816</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11803,10 +11803,10 @@
         <v>888</v>
       </c>
       <c r="B440" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C440">
-        <v>0.3874116577542206</v>
+        <v>0.3688189022536865</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11820,10 +11820,10 @@
         <v>890</v>
       </c>
       <c r="B441" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C441">
-        <v>0.3028599414345913</v>
+        <v>0.3541889529747193</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.310079020617442</v>
+        <v>0.2707250971886571</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11854,10 +11854,10 @@
         <v>894</v>
       </c>
       <c r="B443" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C443">
-        <v>0.2899955170565146</v>
+        <v>0.3671187207316316</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11871,10 +11871,10 @@
         <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C444">
-        <v>0.3405096017860576</v>
+        <v>0.3591762058619261</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11888,10 +11888,10 @@
         <v>898</v>
       </c>
       <c r="B445" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C445">
-        <v>0.3566343886820209</v>
+        <v>0.3350517697272739</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3407350324121086</v>
+        <v>0.3776776635644576</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11922,10 +11922,10 @@
         <v>902</v>
       </c>
       <c r="B447" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C447">
-        <v>0.2976246601603867</v>
+        <v>0.3088459719362907</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11939,10 +11939,10 @@
         <v>904</v>
       </c>
       <c r="B448" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C448">
-        <v>0.3709286840890514</v>
+        <v>0.2799042267780666</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11956,10 +11956,10 @@
         <v>906</v>
       </c>
       <c r="B449" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C449">
-        <v>0.4038636462698424</v>
+        <v>0.318901305314988</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3645265941550396</v>
+        <v>0.3746360297088294</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4150089593822529</v>
+        <v>0.4347537894028959</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12007,10 +12007,10 @@
         <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C452">
-        <v>0.3026187208650171</v>
+        <v>0.3020206087222677</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12024,10 +12024,10 @@
         <v>914</v>
       </c>
       <c r="B453" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C453">
-        <v>0.3555114938107093</v>
+        <v>0.3441971139667386</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12041,10 +12041,10 @@
         <v>916</v>
       </c>
       <c r="B454" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C454">
-        <v>0.265521999651412</v>
+        <v>0.3325863934261372</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12058,10 +12058,10 @@
         <v>918</v>
       </c>
       <c r="B455" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C455">
-        <v>0.3450171950279035</v>
+        <v>0.3863408103984265</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12075,10 +12075,10 @@
         <v>920</v>
       </c>
       <c r="B456" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C456">
-        <v>0.3810183688920446</v>
+        <v>0.3254868912418057</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12092,10 +12092,10 @@
         <v>922</v>
       </c>
       <c r="B457" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C457">
-        <v>0.3202535553220538</v>
+        <v>0.4009268209554514</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12109,10 +12109,10 @@
         <v>924</v>
       </c>
       <c r="B458" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C458">
-        <v>0.376912779878956</v>
+        <v>0.3088825760993496</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12126,10 +12126,10 @@
         <v>926</v>
       </c>
       <c r="B459" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C459">
-        <v>0.3763088593793559</v>
+        <v>0.3108700668526125</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12143,10 +12143,10 @@
         <v>928</v>
       </c>
       <c r="B460" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C460">
-        <v>0.3384596165863307</v>
+        <v>0.3536736657078028</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C461">
-        <v>0.3127140313371691</v>
+        <v>0.3563708934282608</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3426132983414376</v>
+        <v>0.2995325517870338</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12194,10 +12194,10 @@
         <v>934</v>
       </c>
       <c r="B463" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C463">
-        <v>0.2981564474242959</v>
+        <v>0.3798871801134601</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12211,10 +12211,10 @@
         <v>936</v>
       </c>
       <c r="B464" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C464">
-        <v>0.4172919692070367</v>
+        <v>0.3564478090290205</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.3964852606540288</v>
+        <v>0.4277749168777052</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12245,10 +12245,10 @@
         <v>940</v>
       </c>
       <c r="B466" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C466">
-        <v>0.5321956374630411</v>
+        <v>0.4511144921402336</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12262,10 +12262,10 @@
         <v>942</v>
       </c>
       <c r="B467" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C467">
-        <v>0.4794895419341528</v>
+        <v>0.3891052187924412</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12279,10 +12279,10 @@
         <v>944</v>
       </c>
       <c r="B468" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C468">
-        <v>0.4165707144577219</v>
+        <v>0.3284548633954094</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
         <v>946</v>
       </c>
       <c r="B469" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C469">
-        <v>0.2708199322921215</v>
+        <v>0.3356551994473588</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C470">
-        <v>0.3049941308464052</v>
+        <v>0.3782740154409732</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12330,10 +12330,10 @@
         <v>950</v>
       </c>
       <c r="B471" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C471">
-        <v>0.3285628256448819</v>
+        <v>0.3157999315899892</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12347,10 +12347,10 @@
         <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3219414088519146</v>
+        <v>0.3802117039941139</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C473">
-        <v>0.3241875266198842</v>
+        <v>0.3409707929840083</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C474">
-        <v>0.4049619231649815</v>
+        <v>0.4020511102922593</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3518282071397129</v>
+        <v>0.3026101191452168</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12415,10 +12415,10 @@
         <v>960</v>
       </c>
       <c r="B476" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C476">
-        <v>0.3439393956719564</v>
+        <v>0.3070723090427467</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C477">
-        <v>0.3471361247132734</v>
+        <v>0.4077250834957666</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12449,10 +12449,10 @@
         <v>964</v>
       </c>
       <c r="B478" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C478">
-        <v>0.3906801551762827</v>
+        <v>0.3143917557299255</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4208874962429768</v>
+        <v>0.4309009001904335</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12483,10 +12483,10 @@
         <v>968</v>
       </c>
       <c r="B480" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C480">
-        <v>0.4832210796063616</v>
+        <v>0.3906477929694617</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3849396438279146</v>
+        <v>0.3910646985745775</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C482">
-        <v>0.3332317507714258</v>
+        <v>0.3222552649716642</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C483">
-        <v>0.3178356022948433</v>
+        <v>0.3405219030309607</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3863543261632468</v>
+        <v>0.3893261865455211</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12568,10 +12568,10 @@
         <v>978</v>
       </c>
       <c r="B485" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C485">
-        <v>0.3830300920138719</v>
+        <v>0.465482771691472</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12585,10 +12585,10 @@
         <v>980</v>
       </c>
       <c r="B486" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C486">
-        <v>0.4154579509028183</v>
+        <v>0.5012992439081935</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4694663894259216</v>
+        <v>0.4656745115033811</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12619,10 +12619,10 @@
         <v>984</v>
       </c>
       <c r="B488" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C488">
-        <v>0.3450043433223682</v>
+        <v>0.3282074441747848</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12636,10 +12636,10 @@
         <v>986</v>
       </c>
       <c r="B489" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C489">
-        <v>0.4976728413024931</v>
+        <v>0.4348901340243421</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12653,10 +12653,10 @@
         <v>988</v>
       </c>
       <c r="B490" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C490">
-        <v>0.2950238063819532</v>
+        <v>0.3693157302918953</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C491">
-        <v>0.2803319378608051</v>
+        <v>0.3169514539775959</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12687,10 +12687,10 @@
         <v>992</v>
       </c>
       <c r="B492" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C492">
-        <v>0.4850240682782722</v>
+        <v>0.4721005399964329</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.286838231678684</v>
+        <v>0.240700802386998</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12721,10 +12721,10 @@
         <v>996</v>
       </c>
       <c r="B494" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C494">
-        <v>0.3726342064442006</v>
+        <v>0.3373599067775793</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5293756061525527</v>
+        <v>0.5558732734362113</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12755,10 +12755,10 @@
         <v>1000</v>
       </c>
       <c r="B496" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C496">
-        <v>0.4858568165445143</v>
+        <v>0.398616335930449</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
         <v>1002</v>
       </c>
       <c r="B497" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C497">
-        <v>0.3530928462773465</v>
+        <v>0.3528641663249694</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12789,10 +12789,10 @@
         <v>1004</v>
       </c>
       <c r="B498" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C498">
-        <v>0.6583497536513089</v>
+        <v>0.6503194805803054</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12806,10 +12806,10 @@
         <v>1006</v>
       </c>
       <c r="B499" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C499">
-        <v>0.3210333801657367</v>
+        <v>0.4023051882183194</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12823,10 +12823,10 @@
         <v>1008</v>
       </c>
       <c r="B500" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C500">
-        <v>0.4366511975978077</v>
+        <v>0.3361717238502174</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12840,10 +12840,10 @@
         <v>1010</v>
       </c>
       <c r="B501" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C501">
-        <v>0.383773192261028</v>
+        <v>0.4633154548725765</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12857,10 +12857,10 @@
         <v>1012</v>
       </c>
       <c r="B502" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C502">
-        <v>0.5929342065366617</v>
+        <v>0.5350378004405144</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12874,10 +12874,10 @@
         <v>1014</v>
       </c>
       <c r="B503" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C503">
-        <v>0.3623648649715543</v>
+        <v>0.4459506202331933</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C504">
-        <v>0.2914191492295475</v>
+        <v>0.3703143760164625</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12908,10 +12908,10 @@
         <v>1018</v>
       </c>
       <c r="B505" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C505">
-        <v>0.4518757505867036</v>
+        <v>0.3680598758451828</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12925,10 +12925,10 @@
         <v>1020</v>
       </c>
       <c r="B506" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C506">
-        <v>0.4860886737329657</v>
+        <v>0.5701753422348128</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12942,10 +12942,10 @@
         <v>1022</v>
       </c>
       <c r="B507" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C507">
-        <v>0.3278726639355394</v>
+        <v>0.3281661471836224</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12959,10 +12959,10 @@
         <v>1024</v>
       </c>
       <c r="B508" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C508">
-        <v>0.307957081418648</v>
+        <v>0.3737582962651139</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12976,10 +12976,10 @@
         <v>1026</v>
       </c>
       <c r="B509" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C509">
-        <v>0.5328019951181769</v>
+        <v>0.519965397010186</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12993,10 +12993,10 @@
         <v>1028</v>
       </c>
       <c r="B510" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C510">
-        <v>0.3709250950699248</v>
+        <v>0.3893996330862609</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3473818763869019</v>
+        <v>0.3659470108990784</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13027,10 +13027,10 @@
         <v>1032</v>
       </c>
       <c r="B512" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C512">
-        <v>0.3294091918170668</v>
+        <v>0.2601694086349136</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13044,10 +13044,10 @@
         <v>1034</v>
       </c>
       <c r="B513" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C513">
-        <v>0.4008859727396674</v>
+        <v>0.3212581426571081</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.4213836765987584</v>
+        <v>0.4384615825116663</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13078,10 +13078,10 @@
         <v>1038</v>
       </c>
       <c r="B515" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C515">
-        <v>0.4881077892246497</v>
+        <v>0.3994787096147158</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C516">
-        <v>0.2995998661882726</v>
+        <v>0.3774027809752907</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13112,10 +13112,10 @@
         <v>1042</v>
       </c>
       <c r="B517" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3009941115055448</v>
+        <v>0.3845912877462336</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13129,10 +13129,10 @@
         <v>1044</v>
       </c>
       <c r="B518" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C518">
-        <v>0.3523772609379261</v>
+        <v>0.3329239546592597</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.4953406796987408</v>
+        <v>0.5084396254520782</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13163,10 +13163,10 @@
         <v>1048</v>
       </c>
       <c r="B520" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C520">
-        <v>0.3268704953363349</v>
+        <v>0.4055890132978071</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13180,10 +13180,10 @@
         <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C521">
-        <v>0.3179794504368292</v>
+        <v>0.3082195966514678</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13197,10 +13197,10 @@
         <v>1052</v>
       </c>
       <c r="B522" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C522">
-        <v>0.3578309866850056</v>
+        <v>0.4445146552799638</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13214,10 +13214,10 @@
         <v>1054</v>
       </c>
       <c r="B523" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C523">
-        <v>0.4685559491460675</v>
+        <v>0.3804273023742613</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13231,10 +13231,10 @@
         <v>1056</v>
       </c>
       <c r="B524" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C524">
-        <v>0.2976674628639938</v>
+        <v>0.3227261473764709</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4089689182139154</v>
+        <v>0.4270105222575232</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4361796283851705</v>
+        <v>0.439717979034863</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13282,10 +13282,10 @@
         <v>1062</v>
       </c>
       <c r="B527" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C527">
-        <v>0.3669779457062384</v>
+        <v>0.3572038869138695</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13299,10 +13299,10 @@
         <v>1064</v>
       </c>
       <c r="B528" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C528">
-        <v>0.4466842162926879</v>
+        <v>0.3686435384006056</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13316,10 +13316,10 @@
         <v>1066</v>
       </c>
       <c r="B529" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C529">
-        <v>0.3437183164751437</v>
+        <v>0.3631274117265741</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.5006519707312975</v>
+        <v>0.5081235077128834</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5597454870003309</v>
+        <v>0.5709316525219272</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C532">
-        <v>0.2757630171027494</v>
+        <v>0.2968375096555584</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13384,10 +13384,10 @@
         <v>1074</v>
       </c>
       <c r="B533" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C533">
-        <v>0.4466448406053867</v>
+        <v>0.521722640126397</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C534">
-        <v>0.33412391378609</v>
+        <v>0.4109876378335323</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13418,10 +13418,10 @@
         <v>1078</v>
       </c>
       <c r="B535" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C535">
-        <v>0.3216059339608368</v>
+        <v>0.3312444347986639</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C536">
-        <v>0.2915434332528509</v>
+        <v>0.3595961750584842</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13452,10 +13452,10 @@
         <v>1082</v>
       </c>
       <c r="B537" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C537">
-        <v>0.3881360446219309</v>
+        <v>0.2996464531858647</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C538">
-        <v>0.2877180787466358</v>
+        <v>0.3601695227571301</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
         <v>1086</v>
       </c>
       <c r="B539" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C539">
-        <v>0.3115406704265408</v>
+        <v>0.3449746933628294</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C540">
-        <v>0.2538354791818599</v>
+        <v>0.3255735313830602</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13520,10 +13520,10 @@
         <v>1090</v>
       </c>
       <c r="B541" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C541">
-        <v>0.4459444941311597</v>
+        <v>0.3559235963886052</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13537,10 +13537,10 @@
         <v>1092</v>
       </c>
       <c r="B542" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C542">
-        <v>0.3544844617763684</v>
+        <v>0.3691282378324369</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13554,10 +13554,10 @@
         <v>1094</v>
       </c>
       <c r="B543" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C543">
-        <v>0.4107825878025874</v>
+        <v>0.3635620214796481</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13571,10 +13571,10 @@
         <v>1096</v>
       </c>
       <c r="B544" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C544">
-        <v>0.3593941474044878</v>
+        <v>0.2766618588564593</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.283012119932313</v>
+        <v>0.2999994045071486</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3275173474677737</v>
+        <v>0.328989687267506</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2829119876573445</v>
+        <v>0.2963471369460847</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3717273565574627</v>
+        <v>0.3843611636051328</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4035982543587803</v>
+        <v>0.4007170255023122</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3777938155865279</v>
+        <v>0.3941913582311795</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2575601488208817</v>
+        <v>0.2736554602593221</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2848172563192416</v>
+        <v>0.3023981135598851</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2801909702983088</v>
+        <v>0.2952959784196043</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13993,10 +13993,10 @@
         <v>1162</v>
       </c>
       <c r="B572" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.2676369516133467</v>
+        <v>0.2748615511995495</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3259079353246845</v>
+        <v>0.3366633488965735</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3515558081292249</v>
+        <v>0.3323513938903024</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3668406274872268</v>
+        <v>0.3684054628769579</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3703408010713912</v>
+        <v>0.3896978212034408</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14078,10 +14078,10 @@
         <v>1172</v>
       </c>
       <c r="B577" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C577">
-        <v>0.3205612130677405</v>
+        <v>0.2779873239329447</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3842701487381203</v>
+        <v>0.3863280550047151</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3182666076686037</v>
+        <v>0.3281212481422769</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14129,10 +14129,10 @@
         <v>1178</v>
       </c>
       <c r="B580" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C580">
-        <v>0.3316527745391962</v>
+        <v>0.3368065279147531</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.465033400836241</v>
+        <v>0.462381488726977</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.3050114573861465</v>
+        <v>0.320352604644586</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3759156938395272</v>
+        <v>0.3763642887219861</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14200,7 +14200,7 @@
         <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.2994125297183951</v>
+        <v>0.312962746913077</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.4060144053853142</v>
+        <v>0.417058081894219</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2894958706986879</v>
+        <v>0.2941710756449022</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14248,10 +14248,10 @@
         <v>1192</v>
       </c>
       <c r="B587" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C587">
-        <v>0.3046889247084006</v>
+        <v>0.2726400943341069</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3222872701305645</v>
+        <v>0.3241932149600917</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3541766684858648</v>
+        <v>0.3410659387717144</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14299,10 +14299,10 @@
         <v>1198</v>
       </c>
       <c r="B590" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C590">
-        <v>0.4127624764155563</v>
+        <v>0.3768187262167684</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5231825777729124</v>
+        <v>0.5332077891144843</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.3928007896202946</v>
+        <v>0.4164570829478551</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6547194721030339</v>
+        <v>0.6740383561868019</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4353205036174386</v>
+        <v>0.4361154723182727</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14384,10 +14384,10 @@
         <v>1208</v>
       </c>
       <c r="B595" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C595">
-        <v>0.3157856425047901</v>
+        <v>0.2985357949870052</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4366779505562012</v>
+        <v>0.4354430274448882</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14418,10 +14418,10 @@
         <v>1212</v>
       </c>
       <c r="B597" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C597">
-        <v>0.3453946434769294</v>
+        <v>0.3099043163761046</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C598">
-        <v>0.2378964756737056</v>
+        <v>0.2661957038483899</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2617276414805471</v>
+        <v>0.2785484394586231</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2712784126573458</v>
+        <v>0.2899810727880353</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>44</v>
       </c>
       <c r="C601">
-        <v>0.2570790704722975</v>
+        <v>0.2556804977422945</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3623921652382751</v>
+        <v>0.3791735127155921</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2833590310900423</v>
+        <v>0.3010717402804274</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14537,10 +14537,10 @@
         <v>1226</v>
       </c>
       <c r="B604" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C604">
-        <v>0.3367488276794558</v>
+        <v>0.2947551171956511</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2940767271796472</v>
+        <v>0.2887180869604026</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14574,7 +14574,7 @@
         <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3476698567846861</v>
+        <v>0.3571854771805912</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3266271424184538</v>
+        <v>0.3341553468731112</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14605,10 +14605,10 @@
         <v>1234</v>
       </c>
       <c r="B608" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C608">
-        <v>0.3203677908490863</v>
+        <v>0.2806722502206938</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14622,10 +14622,10 @@
         <v>1236</v>
       </c>
       <c r="B609" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2821835440968321</v>
+        <v>0.2948792353525946</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C610">
-        <v>0.2500050842218875</v>
+        <v>0.2593942047186719</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.5156950117625676</v>
+        <v>0.4915987013578978</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3172798802247047</v>
+        <v>0.3183899244029611</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.339290729911238</v>
+        <v>0.3501613141479245</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4400498055589998</v>
+        <v>0.4372233548824392</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3331020518883558</v>
+        <v>0.3351201939309388</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4391882392708466</v>
+        <v>0.433886948459429</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3378867020085848</v>
+        <v>0.3382879095145531</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14775,10 +14775,10 @@
         <v>1254</v>
       </c>
       <c r="B618" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C618">
-        <v>0.3303376973272643</v>
+        <v>0.3394351676987766</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4563187446497999</v>
+        <v>0.4590018723708016</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C620">
-        <v>0.2741042909118989</v>
+        <v>0.3011117285133565</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14826,10 +14826,10 @@
         <v>1261</v>
       </c>
       <c r="B621" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3442496769108165</v>
+        <v>0.3573007685329016</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C622">
-        <v>0.2415765256537446</v>
+        <v>0.2636743853122567</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14860,78 +14860,78 @@
         <v>1265</v>
       </c>
       <c r="B623" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C623">
-        <v>0.252487081765725</v>
+        <v>0.2006616320617115</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
       </c>
       <c r="E623" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="624" spans="1:5">
       <c r="A624" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B624" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C624">
-        <v>0.2798941737012071</v>
+        <v>0.2811709500222385</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
       </c>
       <c r="E624" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="625" spans="1:5">
       <c r="A625" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B625" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C625">
-        <v>0.2670406397923298</v>
+        <v>0.2393009594652543</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
       </c>
       <c r="E625" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="626" spans="1:5">
       <c r="A626" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B626" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3166733413150922</v>
+        <v>0.3360994622955937</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
       </c>
       <c r="E626" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="627" spans="1:5">
       <c r="A627" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B627" t="s">
         <v>1274</v>
       </c>
-      <c r="B627" t="s">
-        <v>1266</v>
-      </c>
       <c r="C627">
-        <v>0.3518394968681734</v>
+        <v>0.277902045501993</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>1266</v>
+        <v>12</v>
       </c>
       <c r="C628">
-        <v>0.2564085526816159</v>
+        <v>0.2201442313913202</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>1266</v>
+        <v>12</v>
       </c>
       <c r="C629">
-        <v>0.2396958430685907</v>
+        <v>0.2647707853853323</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14979,10 +14979,10 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C630">
-        <v>0.3708925254401351</v>
+        <v>0.3224246779272007</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14996,10 +14996,10 @@
         <v>1282</v>
       </c>
       <c r="B631" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C631">
-        <v>0.3819348915873846</v>
+        <v>0.3122155825898124</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15013,10 +15013,10 @@
         <v>1284</v>
       </c>
       <c r="B632" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C632">
-        <v>0.4517125214338317</v>
+        <v>0.3763977866427771</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15030,10 +15030,10 @@
         <v>1286</v>
       </c>
       <c r="B633" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2641238770905688</v>
+        <v>0.2783012340118505</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15047,10 +15047,10 @@
         <v>1288</v>
       </c>
       <c r="B634" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C634">
-        <v>0.4075726957754266</v>
+        <v>0.406261282910187</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15064,10 +15064,10 @@
         <v>1290</v>
       </c>
       <c r="B635" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C635">
-        <v>0.4507954410402215</v>
+        <v>0.4123250518416283</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15081,10 +15081,10 @@
         <v>1292</v>
       </c>
       <c r="B636" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C636">
-        <v>0.3394815279150748</v>
+        <v>0.3844111219214787</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C637">
-        <v>0.3353207749233857</v>
+        <v>0.2910499101309268</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15115,10 +15115,10 @@
         <v>1296</v>
       </c>
       <c r="B638" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C638">
-        <v>0.4657188915026288</v>
+        <v>0.4160095152808186</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15132,10 +15132,10 @@
         <v>1298</v>
       </c>
       <c r="B639" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C639">
-        <v>0.3530728189893109</v>
+        <v>0.3402489862981334</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15149,10 +15149,10 @@
         <v>1300</v>
       </c>
       <c r="B640" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C640">
-        <v>0.2813370363292744</v>
+        <v>0.2809680573390586</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>1266</v>
+        <v>15</v>
       </c>
       <c r="C641">
-        <v>0.273005565930221</v>
+        <v>0.2736206411762203</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15183,10 +15183,10 @@
         <v>1304</v>
       </c>
       <c r="B642" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C642">
-        <v>0.3473587485169741</v>
+        <v>0.270619711767387</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15200,10 +15200,10 @@
         <v>1306</v>
       </c>
       <c r="B643" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C643">
-        <v>0.2908470979609751</v>
+        <v>0.3067929832037643</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15217,10 +15217,10 @@
         <v>1308</v>
       </c>
       <c r="B644" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2712434656734149</v>
+        <v>0.2873032606701417</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15234,10 +15234,10 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2413129036593048</v>
+        <v>0.2581804464053325</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15251,10 +15251,10 @@
         <v>1312</v>
       </c>
       <c r="B646" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C646">
-        <v>0.359637859074117</v>
+        <v>0.3733794506170044</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>1266</v>
+        <v>12</v>
       </c>
       <c r="C647">
-        <v>0.2799393225128359</v>
+        <v>0.2786351838583878</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15285,10 +15285,10 @@
         <v>1316</v>
       </c>
       <c r="B648" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2702794633290554</v>
+        <v>0.2849348040639744</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15302,10 +15302,10 @@
         <v>1318</v>
       </c>
       <c r="B649" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C649">
-        <v>0.321389799642084</v>
+        <v>0.3321347580866019</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>1266</v>
+        <v>12</v>
       </c>
       <c r="C650">
-        <v>0.2940131372512635</v>
+        <v>0.2547230013139709</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15336,10 +15336,10 @@
         <v>1322</v>
       </c>
       <c r="B651" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C651">
-        <v>0.2994570594935365</v>
+        <v>0.3119758638387678</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15368,34 +15368,34 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B2">
-        <v>110</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B3">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,23 +15403,23 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -35,27 +35,27 @@
     <t>aldershot</t>
   </si>
   <si>
+    <t>Labour</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>E14001063</t>
+  </si>
+  <si>
+    <t>aldridge-brownhills</t>
+  </si>
+  <si>
     <t>Conservative</t>
   </si>
   <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>E14001063</t>
-  </si>
-  <si>
-    <t>aldridge-brownhills</t>
-  </si>
-  <si>
     <t>E14001064</t>
   </si>
   <si>
     <t>altrincham and sale west</t>
   </si>
   <si>
-    <t>Labour</t>
-  </si>
-  <si>
     <t>E14001065</t>
   </si>
   <si>
@@ -182,81 +182,81 @@
     <t>bermondsey and old southwark</t>
   </si>
   <si>
+    <t>E14001085</t>
+  </si>
+  <si>
+    <t>bethnal green and stepney</t>
+  </si>
+  <si>
+    <t>E14001086</t>
+  </si>
+  <si>
+    <t>beverley and holderness</t>
+  </si>
+  <si>
+    <t>E14001087</t>
+  </si>
+  <si>
+    <t>bexhill and battle</t>
+  </si>
+  <si>
+    <t>E14001088</t>
+  </si>
+  <si>
+    <t>bexleyheath and crayford</t>
+  </si>
+  <si>
+    <t>E14001089</t>
+  </si>
+  <si>
+    <t>bicester and woodstock</t>
+  </si>
+  <si>
+    <t>E14001090</t>
+  </si>
+  <si>
+    <t>birkenhead</t>
+  </si>
+  <si>
+    <t>E14001091</t>
+  </si>
+  <si>
+    <t>birmingham edgbaston</t>
+  </si>
+  <si>
+    <t>E14001092</t>
+  </si>
+  <si>
+    <t>birmingham erdington</t>
+  </si>
+  <si>
+    <t>E14001093</t>
+  </si>
+  <si>
+    <t>birmingham hall green and moseley</t>
+  </si>
+  <si>
+    <t>E14001094</t>
+  </si>
+  <si>
+    <t>birmingham hodge hill and solihull north</t>
+  </si>
+  <si>
+    <t>E14001095</t>
+  </si>
+  <si>
+    <t>birmingham ladywood</t>
+  </si>
+  <si>
+    <t>E14001096</t>
+  </si>
+  <si>
+    <t>birmingham northfield</t>
+  </si>
+  <si>
     <t>Green Party</t>
   </si>
   <si>
-    <t>E14001085</t>
-  </si>
-  <si>
-    <t>bethnal green and stepney</t>
-  </si>
-  <si>
-    <t>E14001086</t>
-  </si>
-  <si>
-    <t>beverley and holderness</t>
-  </si>
-  <si>
-    <t>E14001087</t>
-  </si>
-  <si>
-    <t>bexhill and battle</t>
-  </si>
-  <si>
-    <t>E14001088</t>
-  </si>
-  <si>
-    <t>bexleyheath and crayford</t>
-  </si>
-  <si>
-    <t>E14001089</t>
-  </si>
-  <si>
-    <t>bicester and woodstock</t>
-  </si>
-  <si>
-    <t>E14001090</t>
-  </si>
-  <si>
-    <t>birkenhead</t>
-  </si>
-  <si>
-    <t>E14001091</t>
-  </si>
-  <si>
-    <t>birmingham edgbaston</t>
-  </si>
-  <si>
-    <t>E14001092</t>
-  </si>
-  <si>
-    <t>birmingham erdington</t>
-  </si>
-  <si>
-    <t>E14001093</t>
-  </si>
-  <si>
-    <t>birmingham hall green and moseley</t>
-  </si>
-  <si>
-    <t>E14001094</t>
-  </si>
-  <si>
-    <t>birmingham hodge hill and solihull north</t>
-  </si>
-  <si>
-    <t>E14001095</t>
-  </si>
-  <si>
-    <t>birmingham ladywood</t>
-  </si>
-  <si>
-    <t>E14001096</t>
-  </si>
-  <si>
-    <t>birmingham northfield</t>
-  </si>
-  <si>
     <t>E14001097</t>
   </si>
   <si>
@@ -3815,6 +3815,9 @@
     <t>blaenau gwent and rhymney</t>
   </si>
   <si>
+    <t>Plaid Cymru</t>
+  </si>
+  <si>
     <t>W07000084</t>
   </si>
   <si>
@@ -3837,9 +3840,6 @@
   </si>
   <si>
     <t>caerphilly</t>
-  </si>
-  <si>
-    <t>Plaid Cymru</t>
   </si>
   <si>
     <t>W07000088</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.2695912896455576</v>
+        <v>0.3148799591978115</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4374,27 +4374,27 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4307430611125232</v>
+        <v>0.4889363734579543</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>0.3330515784854231</v>
+        <v>0.4588847465753229</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.3772632696606538</v>
+        <v>0.3329045509440046</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4425,10 +4425,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3873939564605757</v>
+        <v>0.4457269227235309</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4442,10 +4442,10 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>0.3324741338813946</v>
+        <v>0.3191198569972155</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>0.3740070599523287</v>
+        <v>0.3439871008118419</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>0.3565595338359154</v>
+        <v>0.3241899032902994</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4493,10 +4493,10 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3514805769782894</v>
+        <v>0.409372006019849</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4510,10 +4510,10 @@
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C11">
-        <v>0.2236287249150227</v>
+        <v>0.2578316307974798</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4527,10 +4527,10 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>0.3521334037116561</v>
+        <v>0.4449927539550906</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>0.3633361938972649</v>
+        <v>0.3358121897174547</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>0.4290885235723687</v>
+        <v>0.42165650768725</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4578,10 +4578,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15">
-        <v>0.353324383285011</v>
+        <v>0.3797925703831163</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4595,10 +4595,10 @@
         <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>0.2806153481092007</v>
+        <v>0.3508183375792192</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4612,10 +4612,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C17">
-        <v>0.3266824432675457</v>
+        <v>0.3313940396162245</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4629,10 +4629,10 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18">
-        <v>0.329507534340949</v>
+        <v>0.3661248249420669</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4627953001029372</v>
+        <v>0.523248742546236</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4663,10 +4663,10 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>0.3439760643204102</v>
+        <v>0.4577828542299923</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4680,10 +4680,10 @@
         <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4324207993855941</v>
+        <v>0.5143307530928638</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4697,10 +4697,10 @@
         <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>0.256332233086707</v>
+        <v>0.369693093144717</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4714,10 +4714,10 @@
         <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C23">
-        <v>0.312955303873579</v>
+        <v>0.4398849359991829</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4731,214 +4731,214 @@
         <v>54</v>
       </c>
       <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>0.3558323805497369</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
         <v>55</v>
-      </c>
-      <c r="C24">
-        <v>0.3381185475937113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25">
+        <v>0.6450119326050314</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
         <v>57</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25">
-        <v>0.539693270102466</v>
-      </c>
-      <c r="D25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>0.3429736389226613</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
         <v>59</v>
-      </c>
-      <c r="B26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26">
-        <v>0.3510680436411081</v>
-      </c>
-      <c r="D26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27">
+        <v>0.3273058236148824</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
         <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27">
-        <v>0.3000115018164868</v>
-      </c>
-      <c r="D27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>0.3498585663467955</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s">
         <v>63</v>
-      </c>
-      <c r="B28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28">
-        <v>0.3256191895678688</v>
-      </c>
-      <c r="D28" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4917580624636897</v>
+        <v>0.5550378767338562</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>0.4415380567087203</v>
+      </c>
+      <c r="D30" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30">
-        <v>0.3087715362186574</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>0.5181191661341904</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
         <v>69</v>
-      </c>
-      <c r="B31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31">
-        <v>0.3699456888044048</v>
-      </c>
-      <c r="D31" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32">
-        <v>0.4670783955132038</v>
+        <v>0.4667050692883329</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
       </c>
       <c r="E32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>0.468625925799224</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
         <v>73</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33">
-        <v>0.3331607793541906</v>
-      </c>
-      <c r="D33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34">
-        <v>0.4206889240196939</v>
+        <v>0.414947907346504</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
       </c>
       <c r="E34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
+        <v>76</v>
+      </c>
+      <c r="B35" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>0.4904876810172027</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
         <v>77</v>
-      </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35">
-        <v>0.3880019310666975</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" t="s">
         <v>79</v>
       </c>
-      <c r="B36" t="s">
-        <v>55</v>
-      </c>
       <c r="C36">
-        <v>0.2636128251047856</v>
+        <v>0.2840128056721649</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>0.3393665326163298</v>
+        <v>0.2995793658017566</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4969,10 +4969,10 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>0.2582251391515031</v>
+        <v>0.3451860156088423</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>0.3945858852089007</v>
+        <v>0.3645520217077515</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5003,10 +5003,10 @@
         <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>0.4164687525165971</v>
+        <v>0.5592018398856138</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5023,7 +5023,7 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>0.2991056328049332</v>
+        <v>0.2512736788206363</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
@@ -5037,10 +5037,10 @@
         <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>0.4361658578700387</v>
+        <v>0.5842200495081381</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
@@ -5057,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>0.4710571238933087</v>
+        <v>0.4408046842894297</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
@@ -5074,7 +5074,7 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>0.4730106822444252</v>
+        <v>0.4563504507689837</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
@@ -5088,10 +5088,10 @@
         <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>0.3250550843313242</v>
+        <v>0.4645302341573114</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
@@ -5105,10 +5105,10 @@
         <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C46">
-        <v>0.3514914463431822</v>
+        <v>0.4612671100533123</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
@@ -5125,7 +5125,7 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>0.3799821256260187</v>
+        <v>0.3511858139400525</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
@@ -5142,7 +5142,7 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>0.4743878510226539</v>
+        <v>0.4672940748369899</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
@@ -5159,7 +5159,7 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>0.4550104394131985</v>
+        <v>0.4472700694243915</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
@@ -5176,7 +5176,7 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>0.4005637214017976</v>
+        <v>0.3778978194474971</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
@@ -5193,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.4070851620222515</v>
+        <v>0.3718519630827773</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
@@ -5207,10 +5207,10 @@
         <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>0.4033590285922248</v>
+        <v>0.5477392293416247</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
@@ -5227,7 +5227,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>0.4994948405730678</v>
+        <v>0.5001351716944927</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
@@ -5244,7 +5244,7 @@
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3119459087255811</v>
+        <v>0.416025409162521</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -5258,10 +5258,10 @@
         <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2791423321810907</v>
+        <v>0.3068638416606324</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -5275,10 +5275,10 @@
         <v>119</v>
       </c>
       <c r="B56" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3801593554683973</v>
+        <v>0.4346604838844672</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -5292,10 +5292,10 @@
         <v>121</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C57">
-        <v>0.4791024189087837</v>
+        <v>0.6276776262089527</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -5309,10 +5309,10 @@
         <v>123</v>
       </c>
       <c r="B58" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3332809151423174</v>
+        <v>0.3448347187084835</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -5326,10 +5326,10 @@
         <v>125</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3169292471897748</v>
+        <v>0.4319717219435902</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -5343,10 +5343,10 @@
         <v>127</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C60">
-        <v>0.2916707872983467</v>
+        <v>0.3280239157444572</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -5360,10 +5360,10 @@
         <v>129</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C61">
-        <v>0.3280241701111944</v>
+        <v>0.4394226086032252</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -5377,10 +5377,10 @@
         <v>131</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3469117265610153</v>
+        <v>0.3705969153550849</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -5394,10 +5394,10 @@
         <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C63">
-        <v>0.3244957774337724</v>
+        <v>0.4415642302217197</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
@@ -5414,7 +5414,7 @@
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2539087047533717</v>
+        <v>0.2486445938311377</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
@@ -5431,7 +5431,7 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>0.3885605876053833</v>
+        <v>0.35632621927411</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
@@ -5445,10 +5445,10 @@
         <v>139</v>
       </c>
       <c r="B66" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3644380538284632</v>
+        <v>0.3468424172494392</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -5465,7 +5465,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>0.3747142348305812</v>
+        <v>0.3540074456109498</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
@@ -5479,10 +5479,10 @@
         <v>143</v>
       </c>
       <c r="B68" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2548464223926452</v>
+        <v>0.2984114582746857</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
@@ -5496,10 +5496,10 @@
         <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C69">
-        <v>0.6170484987692131</v>
+        <v>0.6700339591610287</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5513,10 +5513,10 @@
         <v>147</v>
       </c>
       <c r="B70" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C70">
-        <v>0.5888217068563716</v>
+        <v>0.61302003706103</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5530,10 +5530,10 @@
         <v>149</v>
       </c>
       <c r="B71" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C71">
-        <v>0.4362970152235134</v>
+        <v>0.5028644178028351</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5547,10 +5547,10 @@
         <v>151</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C72">
-        <v>0.2748369782435519</v>
+        <v>0.3875885374461754</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5564,10 +5564,10 @@
         <v>153</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C73">
-        <v>0.4243073427386303</v>
+        <v>0.5661518547675282</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5581,10 +5581,10 @@
         <v>155</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C74">
-        <v>0.4230515768148378</v>
+        <v>0.5414776872544211</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5598,10 +5598,10 @@
         <v>157</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C75">
-        <v>0.3072539083618881</v>
+        <v>0.3026320378679523</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5615,10 +5615,10 @@
         <v>159</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3691422440755467</v>
+        <v>0.4177123582204118</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5632,10 +5632,10 @@
         <v>161</v>
       </c>
       <c r="B77" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3073974205391639</v>
+        <v>0.3421539185019532</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5649,10 +5649,10 @@
         <v>163</v>
       </c>
       <c r="B78" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4448840927486005</v>
+        <v>0.4515158801495786</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5666,10 +5666,10 @@
         <v>165</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C79">
-        <v>0.2944645328520163</v>
+        <v>0.2769061896904103</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5683,10 +5683,10 @@
         <v>167</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3580749520416043</v>
+        <v>0.4239074146424086</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5703,7 +5703,7 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>0.3583587302265745</v>
+        <v>0.3236872879061882</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5717,10 +5717,10 @@
         <v>171</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C82">
-        <v>0.418192543564155</v>
+        <v>0.488734580621687</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5734,10 +5734,10 @@
         <v>173</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3039815445594078</v>
+        <v>0.415274350787541</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5751,10 +5751,10 @@
         <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C84">
-        <v>0.3397572739119206</v>
+        <v>0.3323810273136972</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5771,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>0.3927094908764024</v>
+        <v>0.3712286626404174</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5785,10 +5785,10 @@
         <v>179</v>
       </c>
       <c r="B86" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C86">
-        <v>0.2499413282739558</v>
+        <v>0.3365919085040002</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5802,10 +5802,10 @@
         <v>181</v>
       </c>
       <c r="B87" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2719271700995662</v>
+        <v>0.3085238807598942</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5819,10 +5819,10 @@
         <v>183</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C88">
-        <v>0.3686503676768417</v>
+        <v>0.3912397516953468</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5836,10 +5836,10 @@
         <v>185</v>
       </c>
       <c r="B89" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3357447358727934</v>
+        <v>0.3620262399644406</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5853,10 +5853,10 @@
         <v>187</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C90">
-        <v>0.3023893754972292</v>
+        <v>0.35485063225778</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5870,10 +5870,10 @@
         <v>189</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C91">
-        <v>0.3143305166693383</v>
+        <v>0.3348364448597098</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5887,10 +5887,10 @@
         <v>191</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C92">
-        <v>0.3324663872827223</v>
+        <v>0.3229386461239029</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5907,7 +5907,7 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>0.4471825103126185</v>
+        <v>0.4137627304841733</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>44</v>
       </c>
       <c r="C94">
-        <v>0.2849527087563791</v>
+        <v>0.2822035141944657</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5941,7 +5941,7 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>0.4064200664411014</v>
+        <v>0.378912442161157</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5958,7 +5958,7 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>0.4291993324001527</v>
+        <v>0.3957067788680715</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3682198067986875</v>
+        <v>0.3793260223073759</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.3837108264755988</v>
+        <v>0.4136094755713687</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6006,10 +6006,10 @@
         <v>205</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C99">
-        <v>0.3647340089764327</v>
+        <v>0.4829920136525135</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.3834668350292765</v>
+        <v>0.4121468304293552</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.4434874371029829</v>
+        <v>0.4953878656516765</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6057,10 +6057,10 @@
         <v>211</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C102">
-        <v>0.3822623482139353</v>
+        <v>0.5226709340403745</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6074,10 +6074,10 @@
         <v>213</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C103">
-        <v>0.276686056809946</v>
+        <v>0.4029856328323508</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6094,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>0.4630438738578206</v>
+        <v>0.4583916843047103</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3700315873225005</v>
+        <v>0.3980830901174558</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6125,10 +6125,10 @@
         <v>219</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3747707596353598</v>
+        <v>0.4096128781726479</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3563271474404673</v>
+        <v>0.3798070915112981</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6159,10 +6159,10 @@
         <v>223</v>
       </c>
       <c r="B108" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C108">
-        <v>0.3280848523608485</v>
+        <v>0.4455919608394198</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>226</v>
       </c>
       <c r="C109">
-        <v>0.2863687728244987</v>
+        <v>0.2788512891025846</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>0.3453299224367379</v>
+        <v>0.3107825444212622</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6210,10 +6210,10 @@
         <v>230</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C111">
-        <v>0.4333526216020995</v>
+        <v>0.5662023032273754</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6227,10 +6227,10 @@
         <v>232</v>
       </c>
       <c r="B112" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C112">
-        <v>0.2995782855055681</v>
+        <v>0.4316919304163817</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>0.5674471389314046</v>
+        <v>0.5958225042522152</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6261,10 +6261,10 @@
         <v>236</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C114">
-        <v>0.5775085722349664</v>
+        <v>0.6797493093260504</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>15</v>
       </c>
       <c r="C115">
-        <v>0.3519520636234045</v>
+        <v>0.3069434482897445</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6295,10 +6295,10 @@
         <v>240</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C116">
-        <v>0.3835333353129855</v>
+        <v>0.4722933488654157</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2704106631606569</v>
+        <v>0.3107342864137571</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6329,10 +6329,10 @@
         <v>244</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3795463805879538</v>
+        <v>0.4461973916848995</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6346,10 +6346,10 @@
         <v>246</v>
       </c>
       <c r="B119" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3277972434651102</v>
+        <v>0.4251087765807347</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6363,10 +6363,10 @@
         <v>248</v>
       </c>
       <c r="B120" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3715406732307086</v>
+        <v>0.4064908234339346</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6380,10 +6380,10 @@
         <v>250</v>
       </c>
       <c r="B121" t="s">
-        <v>226</v>
+        <v>6</v>
       </c>
       <c r="C121">
-        <v>0.239415285955196</v>
+        <v>0.2958834927935312</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="C122">
-        <v>0.3755655958716215</v>
+        <v>0.3375018036406633</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="C123">
-        <v>0.3848056746309083</v>
+        <v>0.3446735537192933</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6434,7 +6434,7 @@
         <v>15</v>
       </c>
       <c r="C124">
-        <v>0.4674631814067407</v>
+        <v>0.4504595818580544</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6448,10 +6448,10 @@
         <v>258</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C125">
-        <v>0.3135740271123884</v>
+        <v>0.3401806441062993</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3359538433229279</v>
+        <v>0.3751618625747613</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6482,10 +6482,10 @@
         <v>262</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C127">
-        <v>0.4403270998480047</v>
+        <v>0.5585547739560009</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6502,7 +6502,7 @@
         <v>15</v>
       </c>
       <c r="C128">
-        <v>0.4894701650933957</v>
+        <v>0.5022364335072822</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6516,10 +6516,10 @@
         <v>266</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C129">
-        <v>0.3504960482119446</v>
+        <v>0.3130801080338931</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6536,7 +6536,7 @@
         <v>15</v>
       </c>
       <c r="C130">
-        <v>0.4253521710838636</v>
+        <v>0.3922818003668597</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6550,10 +6550,10 @@
         <v>270</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C131">
-        <v>0.2888133283613945</v>
+        <v>0.3173325351774905</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6567,10 +6567,10 @@
         <v>272</v>
       </c>
       <c r="B132" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C132">
-        <v>0.311598353834324</v>
+        <v>0.4232562142004567</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6587,7 +6587,7 @@
         <v>15</v>
       </c>
       <c r="C133">
-        <v>0.3879859581021927</v>
+        <v>0.3732004014735105</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6601,10 +6601,10 @@
         <v>276</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C134">
-        <v>0.2972778825484494</v>
+        <v>0.3545338278061065</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6618,10 +6618,10 @@
         <v>278</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C135">
-        <v>0.2671343512274562</v>
+        <v>0.390734224189196</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.341233866598735</v>
+        <v>0.3635113258590155</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6652,10 +6652,10 @@
         <v>282</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C137">
-        <v>0.3287164017415332</v>
+        <v>0.4518193445814067</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6669,10 +6669,10 @@
         <v>284</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3555450359728415</v>
+        <v>0.3228199025592156</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6686,10 +6686,10 @@
         <v>286</v>
       </c>
       <c r="B139" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C139">
-        <v>0.2896072803474994</v>
+        <v>0.4150435435855106</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.4158015597956838</v>
+        <v>0.4520283408193798</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6720,10 +6720,10 @@
         <v>290</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C141">
-        <v>0.31864586578441</v>
+        <v>0.3753098620673169</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6737,10 +6737,10 @@
         <v>292</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>0.3905905911649031</v>
+        <v>0.457656182707546</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6754,10 +6754,10 @@
         <v>294</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C143">
-        <v>0.2526701232872011</v>
+        <v>0.3669082393334129</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6771,10 +6771,10 @@
         <v>296</v>
       </c>
       <c r="B144" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C144">
-        <v>0.5567654981157845</v>
+        <v>0.6420984002422625</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6788,10 +6788,10 @@
         <v>298</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C145">
-        <v>0.2709702370890882</v>
+        <v>0.3229198648707026</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6805,10 +6805,10 @@
         <v>300</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C146">
-        <v>0.3099423244526024</v>
+        <v>0.4450752203802713</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6822,10 +6822,10 @@
         <v>302</v>
       </c>
       <c r="B147" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C147">
-        <v>0.3931354938230862</v>
+        <v>0.5301223496059948</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.2788566726356119</v>
+        <v>0.3242344204018994</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6856,10 +6856,10 @@
         <v>306</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C149">
-        <v>0.3903741526733047</v>
+        <v>0.4287812370452211</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6876,7 +6876,7 @@
         <v>15</v>
       </c>
       <c r="C150">
-        <v>0.3907623202764101</v>
+        <v>0.3540805196932908</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6890,10 +6890,10 @@
         <v>310</v>
       </c>
       <c r="B151" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C151">
-        <v>0.2621972704275675</v>
+        <v>0.3036494445371418</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6907,10 +6907,10 @@
         <v>312</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C152">
-        <v>0.6299201293985575</v>
+        <v>0.7194980193172126</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6924,10 +6924,10 @@
         <v>314</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3417163011488755</v>
+        <v>0.3687832354087566</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3479533109407189</v>
+        <v>0.3665336396975648</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6958,10 +6958,10 @@
         <v>318</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C155">
-        <v>0.3019135551083482</v>
+        <v>0.2886388363929017</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6975,10 +6975,10 @@
         <v>320</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C156">
-        <v>0.3614208497534631</v>
+        <v>0.4149191407887769</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6992,10 +6992,10 @@
         <v>322</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3337048597639303</v>
+        <v>0.3781774175099467</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.3855105868615716</v>
+        <v>0.4247841476311267</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.4194627168373174</v>
+        <v>0.4880660984689396</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7043,10 +7043,10 @@
         <v>328</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C160">
-        <v>0.3097026907787334</v>
+        <v>0.4344939705175294</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7060,10 +7060,10 @@
         <v>330</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C161">
-        <v>0.2986012878097322</v>
+        <v>0.4237701809875523</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7077,10 +7077,10 @@
         <v>332</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C162">
-        <v>0.4806844210969549</v>
+        <v>0.6253478043579843</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.4589934843225591</v>
+        <v>0.5203867467563534</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7111,10 +7111,10 @@
         <v>336</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3486595216338215</v>
+        <v>0.3667776162333315</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7128,10 +7128,10 @@
         <v>338</v>
       </c>
       <c r="B165" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C165">
-        <v>0.3692674179506623</v>
+        <v>0.4139465031853306</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7145,10 +7145,10 @@
         <v>340</v>
       </c>
       <c r="B166" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C166">
-        <v>0.3163702718456224</v>
+        <v>0.3506003402743979</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7162,10 +7162,10 @@
         <v>342</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C167">
-        <v>0.2817044448974596</v>
+        <v>0.4058958770000176</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7179,10 +7179,10 @@
         <v>344</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C168">
-        <v>0.5309955398317673</v>
+        <v>0.6715046973729646</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3650103176360437</v>
+        <v>0.3702239800288876</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7213,10 +7213,10 @@
         <v>348</v>
       </c>
       <c r="B170" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C170">
-        <v>0.2789412326352341</v>
+        <v>0.3972913174396606</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C171">
-        <v>0.2551351012690621</v>
+        <v>0.2475211494785128</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7247,10 +7247,10 @@
         <v>352</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4543777854628477</v>
+        <v>0.4288610253432952</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7264,10 +7264,10 @@
         <v>354</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3270012480761664</v>
+        <v>0.3755574987664979</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.2918446203324322</v>
+        <v>0.3683316308674465</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7301,7 +7301,7 @@
         <v>15</v>
       </c>
       <c r="C175">
-        <v>0.3168318726950732</v>
+        <v>0.2831605654933195</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7315,10 +7315,10 @@
         <v>360</v>
       </c>
       <c r="B176" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C176">
-        <v>0.3307283229937568</v>
+        <v>0.4560397105674348</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7332,10 +7332,10 @@
         <v>362</v>
       </c>
       <c r="B177" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C177">
-        <v>0.4235433947138919</v>
+        <v>0.5573536239509664</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7352,7 +7352,7 @@
         <v>15</v>
       </c>
       <c r="C178">
-        <v>0.5057947584512315</v>
+        <v>0.5194681803627568</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7369,7 +7369,7 @@
         <v>15</v>
       </c>
       <c r="C179">
-        <v>0.3942899245266229</v>
+        <v>0.3712476881947506</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.3705550272355669</v>
+        <v>0.4109011642758376</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.2870018705889952</v>
+        <v>0.3670974558286617</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7417,10 +7417,10 @@
         <v>372</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C182">
-        <v>0.3064188896042878</v>
+        <v>0.3495164259588765</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7434,10 +7434,10 @@
         <v>374</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C183">
-        <v>0.2992371975654323</v>
+        <v>0.3296932462685482</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7451,10 +7451,10 @@
         <v>376</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C184">
-        <v>0.2788941430921827</v>
+        <v>0.386369315062284</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7468,10 +7468,10 @@
         <v>378</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3982496687005311</v>
+        <v>0.3660065707384407</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4371673545777988</v>
+        <v>0.4923662700232725</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C187">
-        <v>0.2503043598115533</v>
+        <v>0.2536763380919695</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7519,10 +7519,10 @@
         <v>384</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C188">
-        <v>0.4509070339610649</v>
+        <v>0.5294364134388408</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.3271105330459483</v>
+        <v>0.366259116385814</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7553,10 +7553,10 @@
         <v>388</v>
       </c>
       <c r="B190" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C190">
-        <v>0.3135900989133935</v>
+        <v>0.291764654005967</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7570,10 +7570,10 @@
         <v>390</v>
       </c>
       <c r="B191" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C191">
-        <v>0.3478047716957799</v>
+        <v>0.4079111204088721</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7590,7 +7590,7 @@
         <v>15</v>
       </c>
       <c r="C192">
-        <v>0.4635917570073048</v>
+        <v>0.4544734518780091</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7607,7 +7607,7 @@
         <v>15</v>
       </c>
       <c r="C193">
-        <v>0.5267265019044698</v>
+        <v>0.5533290782434391</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7621,10 +7621,10 @@
         <v>396</v>
       </c>
       <c r="B194" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C194">
-        <v>0.4094287844927014</v>
+        <v>0.4113183443586989</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7641,7 +7641,7 @@
         <v>15</v>
       </c>
       <c r="C195">
-        <v>0.3994397023921899</v>
+        <v>0.3818964047976229</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7655,10 +7655,10 @@
         <v>400</v>
       </c>
       <c r="B196" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3267175072508403</v>
+        <v>0.3701437612679536</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7672,10 +7672,10 @@
         <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C197">
-        <v>0.3358121387598624</v>
+        <v>0.393929099736922</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7689,10 +7689,10 @@
         <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C198">
-        <v>0.4674657368173894</v>
+        <v>0.5602173339661916</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7706,10 +7706,10 @@
         <v>406</v>
       </c>
       <c r="B199" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C199">
-        <v>0.5696057759725685</v>
+        <v>0.6411268072524422</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7726,7 +7726,7 @@
         <v>15</v>
       </c>
       <c r="C200">
-        <v>0.4304579739822558</v>
+        <v>0.3979679759681108</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7743,7 +7743,7 @@
         <v>15</v>
       </c>
       <c r="C201">
-        <v>0.3764407087652451</v>
+        <v>0.3594862802886198</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7757,10 +7757,10 @@
         <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C202">
-        <v>0.4046168618572051</v>
+        <v>0.4859608615094153</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7774,10 +7774,10 @@
         <v>414</v>
       </c>
       <c r="B203" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C203">
-        <v>0.4568623066862512</v>
+        <v>0.5885057356158224</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7791,10 +7791,10 @@
         <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C204">
-        <v>0.3744618925309421</v>
+        <v>0.514990341614148</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7808,10 +7808,10 @@
         <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C205">
-        <v>0.4698139367982812</v>
+        <v>0.5606446459729729</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7828,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="C206">
-        <v>0.4435262173293562</v>
+        <v>0.4321531024040908</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.5813801968304581</v>
+        <v>0.6457245344853824</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.3925037138931228</v>
+        <v>0.4232843147828974</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7876,10 +7876,10 @@
         <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C209">
-        <v>0.5376236004174237</v>
+        <v>0.6224917444577071</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7893,10 +7893,10 @@
         <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C210">
-        <v>0.3484496358644602</v>
+        <v>0.4752262753732715</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7913,7 +7913,7 @@
         <v>15</v>
       </c>
       <c r="C211">
-        <v>0.5169148396657018</v>
+        <v>0.5304033662789597</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7927,10 +7927,10 @@
         <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C212">
-        <v>0.3395397310825237</v>
+        <v>0.3067988768440789</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7944,10 +7944,10 @@
         <v>434</v>
       </c>
       <c r="B213" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C213">
-        <v>0.3344726409472614</v>
+        <v>0.3282363287816552</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7964,7 +7964,7 @@
         <v>15</v>
       </c>
       <c r="C214">
-        <v>0.4594230837447755</v>
+        <v>0.4289770989116624</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7978,10 +7978,10 @@
         <v>438</v>
       </c>
       <c r="B215" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C215">
-        <v>0.4488599873063641</v>
+        <v>0.4975163613379778</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7998,7 +7998,7 @@
         <v>15</v>
       </c>
       <c r="C216">
-        <v>0.3708247953597161</v>
+        <v>0.343019909018292</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8015,7 +8015,7 @@
         <v>15</v>
       </c>
       <c r="C217">
-        <v>0.4227772601940245</v>
+        <v>0.4059885729174929</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.349998453575616</v>
+        <v>0.3748648132808117</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.5053417032046279</v>
+        <v>0.5699754935105352</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8063,10 +8063,10 @@
         <v>448</v>
       </c>
       <c r="B220" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C220">
-        <v>0.3035662356904427</v>
+        <v>0.2633455436902431</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8083,7 +8083,7 @@
         <v>15</v>
       </c>
       <c r="C221">
-        <v>0.4221274882600484</v>
+        <v>0.4065939912058751</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8097,10 +8097,10 @@
         <v>452</v>
       </c>
       <c r="B222" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3285130587287675</v>
+        <v>0.3266754416488461</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8114,10 +8114,10 @@
         <v>454</v>
       </c>
       <c r="B223" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5193281645289345</v>
+        <v>0.5846821171643726</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8131,10 +8131,10 @@
         <v>456</v>
       </c>
       <c r="B224" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3397699092844189</v>
+        <v>0.3873435066455119</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8151,7 +8151,7 @@
         <v>15</v>
       </c>
       <c r="C225">
-        <v>0.4193031230753303</v>
+        <v>0.3865793400335491</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8165,10 +8165,10 @@
         <v>460</v>
       </c>
       <c r="B226" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C226">
-        <v>0.4067036337563059</v>
+        <v>0.5495094733382948</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8182,10 +8182,10 @@
         <v>462</v>
       </c>
       <c r="B227" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C227">
-        <v>0.3565522565355359</v>
+        <v>0.4096625199966866</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8199,10 +8199,10 @@
         <v>464</v>
       </c>
       <c r="B228" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C228">
-        <v>0.4072860987211013</v>
+        <v>0.543159346297543</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8216,10 +8216,10 @@
         <v>466</v>
       </c>
       <c r="B229" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C229">
-        <v>0.478209274018106</v>
+        <v>0.5919890348882643</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3617160639822816</v>
+        <v>0.3888956813624935</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8253,7 +8253,7 @@
         <v>15</v>
       </c>
       <c r="C231">
-        <v>0.371540940688341</v>
+        <v>0.3103171938753221</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8267,10 +8267,10 @@
         <v>472</v>
       </c>
       <c r="B232" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C232">
-        <v>0.5359224265210301</v>
+        <v>0.6602494169705571</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4189746899217709</v>
+        <v>0.4720639065520193</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8301,10 +8301,10 @@
         <v>476</v>
       </c>
       <c r="B234" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C234">
-        <v>0.3399497554812264</v>
+        <v>0.4807743771679945</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8318,10 +8318,10 @@
         <v>478</v>
       </c>
       <c r="B235" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C235">
-        <v>0.4179399422780793</v>
+        <v>0.5334318454755187</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8335,10 +8335,10 @@
         <v>480</v>
       </c>
       <c r="B236" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C236">
-        <v>0.3007215480949045</v>
+        <v>0.2849520656731544</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8352,10 +8352,10 @@
         <v>482</v>
       </c>
       <c r="B237" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3487574684164745</v>
+        <v>0.3866099720422553</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8369,10 +8369,10 @@
         <v>484</v>
       </c>
       <c r="B238" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C238">
-        <v>0.2948267929467107</v>
+        <v>0.4276325707467894</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8386,10 +8386,10 @@
         <v>486</v>
       </c>
       <c r="B239" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C239">
-        <v>0.3171193034111763</v>
+        <v>0.4415017158236738</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3578991224779405</v>
+        <v>0.3593678350003399</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="C241">
-        <v>0.2415280644063261</v>
+        <v>0.2416232088761105</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8440,7 +8440,7 @@
         <v>15</v>
       </c>
       <c r="C242">
-        <v>0.3678689751000186</v>
+        <v>0.3206150012883556</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8457,7 +8457,7 @@
         <v>15</v>
       </c>
       <c r="C243">
-        <v>0.5631426894475878</v>
+        <v>0.590349121725085</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.3967065205698253</v>
+        <v>0.3935414356253109</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8488,10 +8488,10 @@
         <v>498</v>
       </c>
       <c r="B245" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C245">
-        <v>0.5608969233781576</v>
+        <v>0.6812519073197484</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8505,10 +8505,10 @@
         <v>500</v>
       </c>
       <c r="B246" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C246">
-        <v>0.3469089661040908</v>
+        <v>0.4841341829048033</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8522,10 +8522,10 @@
         <v>502</v>
       </c>
       <c r="B247" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C247">
-        <v>0.3533167775091695</v>
+        <v>0.471992918627274</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8539,10 +8539,10 @@
         <v>504</v>
       </c>
       <c r="B248" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C248">
-        <v>0.3746436646412047</v>
+        <v>0.4432880242453651</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8556,10 +8556,10 @@
         <v>506</v>
       </c>
       <c r="B249" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C249">
-        <v>0.3322106632872703</v>
+        <v>0.4652247636394714</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8576,7 +8576,7 @@
         <v>15</v>
       </c>
       <c r="C250">
-        <v>0.3476465022251459</v>
+        <v>0.3066553452738644</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.4580880044379424</v>
+        <v>0.504985700716017</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8607,10 +8607,10 @@
         <v>512</v>
       </c>
       <c r="B252" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C252">
-        <v>0.3492609486592563</v>
+        <v>0.493634676836079</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8624,10 +8624,10 @@
         <v>514</v>
       </c>
       <c r="B253" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C253">
-        <v>0.3082576857216566</v>
+        <v>0.4286594418646705</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8641,10 +8641,10 @@
         <v>516</v>
       </c>
       <c r="B254" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C254">
-        <v>0.3934280770683309</v>
+        <v>0.5224333949561931</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8661,7 +8661,7 @@
         <v>15</v>
       </c>
       <c r="C255">
-        <v>0.485778768901457</v>
+        <v>0.4546943060107533</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8675,10 +8675,10 @@
         <v>520</v>
       </c>
       <c r="B256" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C256">
-        <v>0.5168415513385844</v>
+        <v>0.6655484318242186</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8692,10 +8692,10 @@
         <v>522</v>
       </c>
       <c r="B257" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C257">
-        <v>0.3483668542893446</v>
+        <v>0.4893867174435239</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8709,10 +8709,10 @@
         <v>524</v>
       </c>
       <c r="B258" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C258">
-        <v>0.4339177389936856</v>
+        <v>0.5402103190932995</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8729,7 +8729,7 @@
         <v>15</v>
       </c>
       <c r="C259">
-        <v>0.3587561206044904</v>
+        <v>0.3148979787459722</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8743,10 +8743,10 @@
         <v>528</v>
       </c>
       <c r="B260" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C260">
-        <v>0.3582434270719597</v>
+        <v>0.4855738878498426</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8760,10 +8760,10 @@
         <v>530</v>
       </c>
       <c r="B261" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C261">
-        <v>0.3836206909437639</v>
+        <v>0.5205245710657485</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8777,10 +8777,10 @@
         <v>532</v>
       </c>
       <c r="B262" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C262">
-        <v>0.3365263119405533</v>
+        <v>0.4570219375315318</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8794,10 +8794,10 @@
         <v>534</v>
       </c>
       <c r="B263" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C263">
-        <v>0.3572537917834441</v>
+        <v>0.4953872785709716</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8811,10 +8811,10 @@
         <v>536</v>
       </c>
       <c r="B264" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C264">
-        <v>0.3585207180058465</v>
+        <v>0.4953034622354727</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8828,10 +8828,10 @@
         <v>538</v>
       </c>
       <c r="B265" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C265">
-        <v>0.2768594029362588</v>
+        <v>0.3954076066997674</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8845,10 +8845,10 @@
         <v>540</v>
       </c>
       <c r="B266" t="s">
-        <v>226</v>
+        <v>6</v>
       </c>
       <c r="C266">
-        <v>0.3303766985844671</v>
+        <v>0.347149959750749</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8865,7 +8865,7 @@
         <v>15</v>
       </c>
       <c r="C267">
-        <v>0.3426118127216689</v>
+        <v>0.3034906037621761</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8879,10 +8879,10 @@
         <v>544</v>
       </c>
       <c r="B268" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C268">
-        <v>0.3352435769684094</v>
+        <v>0.4765174741092499</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.3773700750272198</v>
+        <v>0.4109838559146343</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8913,10 +8913,10 @@
         <v>548</v>
       </c>
       <c r="B270" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C270">
-        <v>0.4614377255765756</v>
+        <v>0.5733414035959792</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8930,10 +8930,10 @@
         <v>550</v>
       </c>
       <c r="B271" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C271">
-        <v>0.4912229656120447</v>
+        <v>0.5819489533095727</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8947,10 +8947,10 @@
         <v>552</v>
       </c>
       <c r="B272" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C272">
-        <v>0.2862940086565663</v>
+        <v>0.3956414237633554</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8964,10 +8964,10 @@
         <v>554</v>
       </c>
       <c r="B273" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C273">
-        <v>0.4432542996505917</v>
+        <v>0.5883161057218996</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8984,7 +8984,7 @@
         <v>15</v>
       </c>
       <c r="C274">
-        <v>0.41706910111738</v>
+        <v>0.3870232517150635</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -8998,10 +8998,10 @@
         <v>558</v>
       </c>
       <c r="B275" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C275">
-        <v>0.2740689471560268</v>
+        <v>0.276147618327698</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9015,10 +9015,10 @@
         <v>560</v>
       </c>
       <c r="B276" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C276">
-        <v>0.2506042507634856</v>
+        <v>0.3700233458753696</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C277">
-        <v>0.4237701615624012</v>
+        <v>0.4425856406980055</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9049,10 +9049,10 @@
         <v>564</v>
       </c>
       <c r="B278" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4399600377445592</v>
+        <v>0.4501446650235367</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9066,10 +9066,10 @@
         <v>566</v>
       </c>
       <c r="B279" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C279">
-        <v>0.4982760599505469</v>
+        <v>0.6172517291567656</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9083,10 +9083,10 @@
         <v>568</v>
       </c>
       <c r="B280" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C280">
-        <v>0.4007271463144875</v>
+        <v>0.559374990841964</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9100,10 +9100,10 @@
         <v>570</v>
       </c>
       <c r="B281" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C281">
-        <v>0.3302369026738208</v>
+        <v>0.4501158723344392</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9120,7 +9120,7 @@
         <v>15</v>
       </c>
       <c r="C282">
-        <v>0.4890454441875942</v>
+        <v>0.4871860668534409</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9134,10 +9134,10 @@
         <v>574</v>
       </c>
       <c r="B283" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3694463647031994</v>
+        <v>0.3996672548879696</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9151,10 +9151,10 @@
         <v>576</v>
       </c>
       <c r="B284" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C284">
-        <v>0.2988544464669598</v>
+        <v>0.3313043691007249</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9168,10 +9168,10 @@
         <v>578</v>
       </c>
       <c r="B285" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C285">
-        <v>0.2742069757022258</v>
+        <v>0.2685325952481217</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9185,10 +9185,10 @@
         <v>580</v>
       </c>
       <c r="B286" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C286">
-        <v>0.2850522212049605</v>
+        <v>0.3023755498559832</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.498932186824273</v>
+        <v>0.5402606774044334</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9222,7 +9222,7 @@
         <v>15</v>
       </c>
       <c r="C288">
-        <v>0.3125620285813854</v>
+        <v>0.2646625592040101</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9239,7 +9239,7 @@
         <v>15</v>
       </c>
       <c r="C289">
-        <v>0.4261754810826845</v>
+        <v>0.3979777332879673</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9256,7 +9256,7 @@
         <v>15</v>
       </c>
       <c r="C290">
-        <v>0.3600746087327519</v>
+        <v>0.3257138982138363</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9270,10 +9270,10 @@
         <v>590</v>
       </c>
       <c r="B291" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4221360753703444</v>
+        <v>0.4350455809450506</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C292">
-        <v>0.525653847638159</v>
+        <v>0.5555774605078838</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9304,10 +9304,10 @@
         <v>594</v>
       </c>
       <c r="B293" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C293">
-        <v>0.5635989722321237</v>
+        <v>0.6638494771105886</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9324,7 +9324,7 @@
         <v>15</v>
       </c>
       <c r="C294">
-        <v>0.4484213377608334</v>
+        <v>0.4264508034708075</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9338,10 +9338,10 @@
         <v>598</v>
       </c>
       <c r="B295" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3377573281505317</v>
+        <v>0.3938178430039411</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9358,7 +9358,7 @@
         <v>15</v>
       </c>
       <c r="C296">
-        <v>0.3669232161612057</v>
+        <v>0.3307264875601038</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9372,10 +9372,10 @@
         <v>602</v>
       </c>
       <c r="B297" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C297">
-        <v>0.4516856472156731</v>
+        <v>0.5329824183844382</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9389,10 +9389,10 @@
         <v>604</v>
       </c>
       <c r="B298" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C298">
-        <v>0.3855597053387357</v>
+        <v>0.4520976285773808</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2954543515004676</v>
+        <v>0.2946657986820778</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9423,10 +9423,10 @@
         <v>608</v>
       </c>
       <c r="B300" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C300">
-        <v>0.3582485477773821</v>
+        <v>0.4020209455314553</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9440,10 +9440,10 @@
         <v>610</v>
       </c>
       <c r="B301" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C301">
-        <v>0.280278534121455</v>
+        <v>0.3993576722841826</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.5468532580878058</v>
+        <v>0.6260995042798879</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9474,10 +9474,10 @@
         <v>614</v>
       </c>
       <c r="B303" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3365266236897289</v>
+        <v>0.3445595994125312</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9491,10 +9491,10 @@
         <v>616</v>
       </c>
       <c r="B304" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C304">
-        <v>0.3111280781943151</v>
+        <v>0.3334766024271276</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.4588884454673973</v>
+        <v>0.5268266027281194</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9528,7 +9528,7 @@
         <v>15</v>
       </c>
       <c r="C306">
-        <v>0.4507992753924156</v>
+        <v>0.4355333750783104</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9542,10 +9542,10 @@
         <v>622</v>
       </c>
       <c r="B307" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C307">
-        <v>0.3869018250779983</v>
+        <v>0.5082162097556689</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9559,10 +9559,10 @@
         <v>624</v>
       </c>
       <c r="B308" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C308">
-        <v>0.3239502100185639</v>
+        <v>0.4436456684074341</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9576,10 +9576,10 @@
         <v>626</v>
       </c>
       <c r="B309" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C309">
-        <v>0.2466967389272477</v>
+        <v>0.3071007711989771</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9593,10 +9593,10 @@
         <v>628</v>
       </c>
       <c r="B310" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C310">
-        <v>0.3270035817865354</v>
+        <v>0.444286373514984</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9613,7 +9613,7 @@
         <v>15</v>
       </c>
       <c r="C311">
-        <v>0.4255272477999702</v>
+        <v>0.3946737012853936</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9627,10 +9627,10 @@
         <v>632</v>
       </c>
       <c r="B312" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C312">
-        <v>0.3076666153176793</v>
+        <v>0.3056486793017745</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3288652229941081</v>
+        <v>0.3455016002167963</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9661,10 +9661,10 @@
         <v>636</v>
       </c>
       <c r="B314" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3359803891311087</v>
+        <v>0.3709597591379819</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.5067952254691064</v>
+        <v>0.5762635139434371</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9695,10 +9695,10 @@
         <v>640</v>
       </c>
       <c r="B316" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C316">
-        <v>0.3126693134554198</v>
+        <v>0.4500328376657746</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9712,10 +9712,10 @@
         <v>642</v>
       </c>
       <c r="B317" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C317">
-        <v>0.4338054903265685</v>
+        <v>0.5809218296654468</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9729,10 +9729,10 @@
         <v>644</v>
       </c>
       <c r="B318" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C318">
-        <v>0.4639610887766684</v>
+        <v>0.6111299901763236</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9746,10 +9746,10 @@
         <v>646</v>
       </c>
       <c r="B319" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C319">
-        <v>0.281453691999594</v>
+        <v>0.3986324333193592</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9766,7 +9766,7 @@
         <v>15</v>
       </c>
       <c r="C320">
-        <v>0.3369924117532813</v>
+        <v>0.3003941284664995</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9780,10 +9780,10 @@
         <v>650</v>
       </c>
       <c r="B321" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C321">
-        <v>0.297678638419612</v>
+        <v>0.3775111930003133</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9797,10 +9797,10 @@
         <v>652</v>
       </c>
       <c r="B322" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C322">
-        <v>0.3926419775056722</v>
+        <v>0.4022307914971617</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9814,10 +9814,10 @@
         <v>654</v>
       </c>
       <c r="B323" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C323">
-        <v>0.3827948295802887</v>
+        <v>0.4475370908943836</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.386645336999747</v>
+        <v>0.4330236076280478</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9848,10 +9848,10 @@
         <v>658</v>
       </c>
       <c r="B325" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C325">
-        <v>0.2617646563396065</v>
+        <v>0.2654002482317769</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9868,7 +9868,7 @@
         <v>44</v>
       </c>
       <c r="C326">
-        <v>0.3623588153316062</v>
+        <v>0.3841969017130468</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3456963688617526</v>
+        <v>0.3672088522889846</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9902,7 +9902,7 @@
         <v>15</v>
       </c>
       <c r="C328">
-        <v>0.3394269828848928</v>
+        <v>0.3065152119653884</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9916,10 +9916,10 @@
         <v>666</v>
       </c>
       <c r="B329" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C329">
-        <v>0.3557060564537073</v>
+        <v>0.361117062120934</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9936,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="C330">
-        <v>0.3741163403795813</v>
+        <v>0.3179824306503061</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9950,10 +9950,10 @@
         <v>670</v>
       </c>
       <c r="B331" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C331">
-        <v>0.3740057242197506</v>
+        <v>0.4341290661402167</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9967,10 +9967,10 @@
         <v>672</v>
       </c>
       <c r="B332" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C332">
-        <v>0.3599478164147819</v>
+        <v>0.4227280273905592</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9984,10 +9984,10 @@
         <v>674</v>
       </c>
       <c r="B333" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C333">
-        <v>0.3976424051110828</v>
+        <v>0.5393731395075825</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10001,10 +10001,10 @@
         <v>676</v>
       </c>
       <c r="B334" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C334">
-        <v>0.3228595902918182</v>
+        <v>0.3015225438733306</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10021,7 +10021,7 @@
         <v>15</v>
       </c>
       <c r="C335">
-        <v>0.3832111665013808</v>
+        <v>0.3568256808685825</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10035,10 +10035,10 @@
         <v>680</v>
       </c>
       <c r="B336" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3480340015611227</v>
+        <v>0.3280331998069908</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.4646657926584409</v>
+        <v>0.539270837835129</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10069,10 +10069,10 @@
         <v>684</v>
       </c>
       <c r="B338" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C338">
-        <v>0.3019914657634178</v>
+        <v>0.3286211366577315</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10089,7 +10089,7 @@
         <v>15</v>
       </c>
       <c r="C339">
-        <v>0.5229369383698881</v>
+        <v>0.5112997827743406</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10106,7 +10106,7 @@
         <v>15</v>
       </c>
       <c r="C340">
-        <v>0.3727142685963155</v>
+        <v>0.3424027020209376</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10120,10 +10120,10 @@
         <v>690</v>
       </c>
       <c r="B341" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C341">
-        <v>0.2646404923226637</v>
+        <v>0.3278080278950797</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10137,10 +10137,10 @@
         <v>692</v>
       </c>
       <c r="B342" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2629406080293007</v>
+        <v>0.2859927362249052</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10154,10 +10154,10 @@
         <v>694</v>
       </c>
       <c r="B343" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4061195241337882</v>
+        <v>0.4764177862651749</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10174,7 +10174,7 @@
         <v>15</v>
       </c>
       <c r="C344">
-        <v>0.3485095970532197</v>
+        <v>0.3197691413976114</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10188,10 +10188,10 @@
         <v>698</v>
       </c>
       <c r="B345" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C345">
-        <v>0.295941188519612</v>
+        <v>0.4082820347836064</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10205,10 +10205,10 @@
         <v>700</v>
       </c>
       <c r="B346" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3436747931956213</v>
+        <v>0.3753900425766254</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10225,7 +10225,7 @@
         <v>15</v>
       </c>
       <c r="C347">
-        <v>0.3854573395067151</v>
+        <v>0.35171916889072</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10239,10 +10239,10 @@
         <v>704</v>
       </c>
       <c r="B348" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C348">
-        <v>0.2440883721265354</v>
+        <v>0.3561779101284386</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10256,10 +10256,10 @@
         <v>706</v>
       </c>
       <c r="B349" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C349">
-        <v>0.4174471625982288</v>
+        <v>0.5125596723516849</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10276,7 +10276,7 @@
         <v>15</v>
       </c>
       <c r="C350">
-        <v>0.4362776183642587</v>
+        <v>0.4176005201693805</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C351">
-        <v>0.2944602101397409</v>
+        <v>0.3386502648128661</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10310,7 +10310,7 @@
         <v>15</v>
       </c>
       <c r="C352">
-        <v>0.4914376101435488</v>
+        <v>0.4925332154443695</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10324,10 +10324,10 @@
         <v>714</v>
       </c>
       <c r="B353" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C353">
-        <v>0.3908412847950963</v>
+        <v>0.4250114084902095</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10341,10 +10341,10 @@
         <v>716</v>
       </c>
       <c r="B354" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C354">
-        <v>0.3084127843517361</v>
+        <v>0.3082102407315919</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10358,10 +10358,10 @@
         <v>718</v>
       </c>
       <c r="B355" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C355">
-        <v>0.2825768602525066</v>
+        <v>0.4051264551520901</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10375,10 +10375,10 @@
         <v>720</v>
       </c>
       <c r="B356" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C356">
-        <v>0.2561438461810645</v>
+        <v>0.3629746782439219</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10392,10 +10392,10 @@
         <v>722</v>
       </c>
       <c r="B357" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C357">
-        <v>0.364599628877601</v>
+        <v>0.4301063011955147</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10409,10 +10409,10 @@
         <v>724</v>
       </c>
       <c r="B358" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3327945676253314</v>
+        <v>0.3562348696661759</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.5083977086964667</v>
+        <v>0.5581043837387906</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10443,10 +10443,10 @@
         <v>728</v>
       </c>
       <c r="B360" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C360">
-        <v>0.4480379910313607</v>
+        <v>0.5020662193034554</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10463,7 +10463,7 @@
         <v>15</v>
       </c>
       <c r="C361">
-        <v>0.3880574026814158</v>
+        <v>0.352668674335384</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10477,10 +10477,10 @@
         <v>732</v>
       </c>
       <c r="B362" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C362">
-        <v>0.2742447834431703</v>
+        <v>0.3944799399233535</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10494,10 +10494,10 @@
         <v>734</v>
       </c>
       <c r="B363" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C363">
-        <v>0.3197811244787069</v>
+        <v>0.330260588482478</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10511,10 +10511,10 @@
         <v>736</v>
       </c>
       <c r="B364" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3405263165985451</v>
+        <v>0.3836068712760068</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10528,10 +10528,10 @@
         <v>738</v>
       </c>
       <c r="B365" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C365">
-        <v>0.3419134375884932</v>
+        <v>0.3066676084409448</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10548,7 +10548,7 @@
         <v>15</v>
       </c>
       <c r="C366">
-        <v>0.3114978712436072</v>
+        <v>0.2675745882909432</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10562,10 +10562,10 @@
         <v>742</v>
       </c>
       <c r="B367" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C367">
-        <v>0.2799753187034235</v>
+        <v>0.3446768065429725</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10582,7 +10582,7 @@
         <v>15</v>
       </c>
       <c r="C368">
-        <v>0.3526720097001454</v>
+        <v>0.3118367685621168</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10596,10 +10596,10 @@
         <v>746</v>
       </c>
       <c r="B369" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C369">
-        <v>0.4364861098342026</v>
+        <v>0.5653072726311656</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10613,10 +10613,10 @@
         <v>748</v>
       </c>
       <c r="B370" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C370">
-        <v>0.3765858561750022</v>
+        <v>0.3507833967610343</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10630,10 +10630,10 @@
         <v>750</v>
       </c>
       <c r="B371" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C371">
-        <v>0.3831973584660654</v>
+        <v>0.5266404256995374</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10647,10 +10647,10 @@
         <v>752</v>
       </c>
       <c r="B372" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C372">
-        <v>0.3009364624217767</v>
+        <v>0.4393559502959843</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10664,10 +10664,10 @@
         <v>754</v>
       </c>
       <c r="B373" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C373">
-        <v>0.3786489234139668</v>
+        <v>0.5027858223896546</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10681,10 +10681,10 @@
         <v>756</v>
       </c>
       <c r="B374" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C374">
-        <v>0.4291365026335516</v>
+        <v>0.556090232358282</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10698,10 +10698,10 @@
         <v>758</v>
       </c>
       <c r="B375" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C375">
-        <v>0.3994720425483808</v>
+        <v>0.5474924861898719</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10718,7 +10718,7 @@
         <v>15</v>
       </c>
       <c r="C376">
-        <v>0.4107425351251811</v>
+        <v>0.3783123005122446</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10732,10 +10732,10 @@
         <v>762</v>
       </c>
       <c r="B377" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C377">
-        <v>0.3950417342449342</v>
+        <v>0.5320377168320795</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10749,10 +10749,10 @@
         <v>764</v>
       </c>
       <c r="B378" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C378">
-        <v>0.2553231844164487</v>
+        <v>0.3636683845002708</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10766,10 +10766,10 @@
         <v>766</v>
       </c>
       <c r="B379" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C379">
-        <v>0.2738113043489911</v>
+        <v>0.3872365221100981</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10783,10 +10783,10 @@
         <v>768</v>
       </c>
       <c r="B380" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C380">
-        <v>0.2835974480148041</v>
+        <v>0.3920990557933828</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10800,10 +10800,10 @@
         <v>770</v>
       </c>
       <c r="B381" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C381">
-        <v>0.4585758727431198</v>
+        <v>0.5496773919145983</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10817,10 +10817,10 @@
         <v>772</v>
       </c>
       <c r="B382" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C382">
-        <v>0.2687904632194298</v>
+        <v>0.3897021417822316</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10834,10 +10834,10 @@
         <v>774</v>
       </c>
       <c r="B383" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C383">
-        <v>0.3861275542003516</v>
+        <v>0.4548033795569768</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.4683436594737762</v>
+        <v>0.5008440643203851</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10868,10 +10868,10 @@
         <v>778</v>
       </c>
       <c r="B385" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C385">
-        <v>0.3133983599254345</v>
+        <v>0.4543443434414075</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10888,7 +10888,7 @@
         <v>15</v>
       </c>
       <c r="C386">
-        <v>0.3883974646645231</v>
+        <v>0.3525562300256839</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10902,10 +10902,10 @@
         <v>782</v>
       </c>
       <c r="B387" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4256506166472542</v>
+        <v>0.4718948461293332</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3633809092216613</v>
+        <v>0.3956299068587354</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10936,10 +10936,10 @@
         <v>786</v>
       </c>
       <c r="B389" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3165690713368335</v>
+        <v>0.3686062855597332</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10956,7 +10956,7 @@
         <v>15</v>
       </c>
       <c r="C390">
-        <v>0.3934588920757937</v>
+        <v>0.3528130909779427</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10973,7 +10973,7 @@
         <v>15</v>
       </c>
       <c r="C391">
-        <v>0.4099835638488465</v>
+        <v>0.3741367844867318</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10987,10 +10987,10 @@
         <v>792</v>
       </c>
       <c r="B392" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3106266818786358</v>
+        <v>0.3327162613760653</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11004,10 +11004,10 @@
         <v>794</v>
       </c>
       <c r="B393" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4201246633925797</v>
+        <v>0.4967507115150378</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11024,7 +11024,7 @@
         <v>15</v>
       </c>
       <c r="C394">
-        <v>0.4270827565368991</v>
+        <v>0.4146437537795883</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11038,10 +11038,10 @@
         <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4162389037864443</v>
+        <v>0.4778467014826863</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11055,10 +11055,10 @@
         <v>800</v>
       </c>
       <c r="B396" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C396">
-        <v>0.3184925132274275</v>
+        <v>0.4462539023599051</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11072,10 +11072,10 @@
         <v>802</v>
       </c>
       <c r="B397" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C397">
-        <v>0.3725225600220212</v>
+        <v>0.4283171153430735</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11089,10 +11089,10 @@
         <v>804</v>
       </c>
       <c r="B398" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C398">
-        <v>0.4129044845583654</v>
+        <v>0.509280183141702</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11109,7 +11109,7 @@
         <v>15</v>
       </c>
       <c r="C399">
-        <v>0.4532777624670984</v>
+        <v>0.4727110952455416</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.2925780896705066</v>
+        <v>0.3852298283222335</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11143,7 +11143,7 @@
         <v>15</v>
       </c>
       <c r="C401">
-        <v>0.5164592358243356</v>
+        <v>0.5382528709664383</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11157,10 +11157,10 @@
         <v>812</v>
       </c>
       <c r="B402" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C402">
-        <v>0.3260109118842376</v>
+        <v>0.4589390681050751</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11174,10 +11174,10 @@
         <v>814</v>
       </c>
       <c r="B403" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C403">
-        <v>0.3118425906573278</v>
+        <v>0.2944231781964758</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11191,10 +11191,10 @@
         <v>816</v>
       </c>
       <c r="B404" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C404">
-        <v>0.310312847030522</v>
+        <v>0.363180026181342</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11208,10 +11208,10 @@
         <v>818</v>
       </c>
       <c r="B405" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C405">
-        <v>0.322214728226788</v>
+        <v>0.4562746511666228</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C406">
-        <v>0.5641207116370761</v>
+        <v>0.5515217763636963</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11242,10 +11242,10 @@
         <v>822</v>
       </c>
       <c r="B407" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C407">
-        <v>0.35431604488359</v>
+        <v>0.4310088547781363</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11259,10 +11259,10 @@
         <v>824</v>
       </c>
       <c r="B408" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C408">
-        <v>0.3979601146302134</v>
+        <v>0.5479843496674669</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11276,10 +11276,10 @@
         <v>826</v>
       </c>
       <c r="B409" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C409">
-        <v>0.4073761270312487</v>
+        <v>0.56825765916293</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11296,7 +11296,7 @@
         <v>15</v>
       </c>
       <c r="C410">
-        <v>0.3680662370116374</v>
+        <v>0.333963899886761</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11310,10 +11310,10 @@
         <v>830</v>
       </c>
       <c r="B411" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3446928305871058</v>
+        <v>0.3718694704247643</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11327,10 +11327,10 @@
         <v>832</v>
       </c>
       <c r="B412" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C412">
-        <v>0.3837857829606339</v>
+        <v>0.5269174828656948</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11344,10 +11344,10 @@
         <v>834</v>
       </c>
       <c r="B413" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C413">
-        <v>0.3015125354936323</v>
+        <v>0.268753374498474</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11364,7 +11364,7 @@
         <v>15</v>
       </c>
       <c r="C414">
-        <v>0.3998058006484279</v>
+        <v>0.3835034714858351</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11381,7 +11381,7 @@
         <v>15</v>
       </c>
       <c r="C415">
-        <v>0.4120271617582045</v>
+        <v>0.3992113587275313</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11398,7 +11398,7 @@
         <v>15</v>
       </c>
       <c r="C416">
-        <v>0.4755938697738304</v>
+        <v>0.5091818949311835</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11412,10 +11412,10 @@
         <v>842</v>
       </c>
       <c r="B417" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2703469377164524</v>
+        <v>0.2815473203168448</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11429,10 +11429,10 @@
         <v>844</v>
       </c>
       <c r="B418" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C418">
-        <v>0.2976644712293582</v>
+        <v>0.3295765061099344</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11449,7 +11449,7 @@
         <v>15</v>
       </c>
       <c r="C419">
-        <v>0.381695985427095</v>
+        <v>0.3355905251906521</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.409418471981977</v>
+        <v>0.4330882946170404</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.3948507639962782</v>
+        <v>0.435229571691427</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11497,10 +11497,10 @@
         <v>852</v>
       </c>
       <c r="B422" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C422">
-        <v>0.2858022723371625</v>
+        <v>0.4086297737791083</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.4695105045010427</v>
+        <v>0.5436608511433112</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11531,10 +11531,10 @@
         <v>856</v>
       </c>
       <c r="B424" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3814442347106263</v>
+        <v>0.3561843979286954</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11548,10 +11548,10 @@
         <v>858</v>
       </c>
       <c r="B425" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3066587097838216</v>
+        <v>0.3780417541771915</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11568,7 +11568,7 @@
         <v>15</v>
       </c>
       <c r="C426">
-        <v>0.4177088176906886</v>
+        <v>0.3968591841209711</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11585,7 +11585,7 @@
         <v>15</v>
       </c>
       <c r="C427">
-        <v>0.3395386312667456</v>
+        <v>0.2927015597300543</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11599,10 +11599,10 @@
         <v>864</v>
       </c>
       <c r="B428" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C428">
-        <v>0.3199939921473181</v>
+        <v>0.2935762366250528</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11616,10 +11616,10 @@
         <v>866</v>
       </c>
       <c r="B429" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C429">
-        <v>0.3501440395239063</v>
+        <v>0.4017110859337001</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11633,10 +11633,10 @@
         <v>868</v>
       </c>
       <c r="B430" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3618644436681286</v>
+        <v>0.3522715490322337</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11650,10 +11650,10 @@
         <v>870</v>
       </c>
       <c r="B431" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C431">
-        <v>0.3019614442246021</v>
+        <v>0.319881605341448</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11670,7 +11670,7 @@
         <v>15</v>
       </c>
       <c r="C432">
-        <v>0.3971218435022421</v>
+        <v>0.3874688223223968</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11684,10 +11684,10 @@
         <v>874</v>
       </c>
       <c r="B433" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C433">
-        <v>0.2744523528212764</v>
+        <v>0.3528056575176793</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11704,7 +11704,7 @@
         <v>15</v>
       </c>
       <c r="C434">
-        <v>0.4133916750746118</v>
+        <v>0.3868562949051052</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11718,10 +11718,10 @@
         <v>878</v>
       </c>
       <c r="B435" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C435">
-        <v>0.3725868197299252</v>
+        <v>0.4450706155765732</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11738,7 +11738,7 @@
         <v>15</v>
       </c>
       <c r="C436">
-        <v>0.3698186155623084</v>
+        <v>0.3457844821966243</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11752,10 +11752,10 @@
         <v>882</v>
       </c>
       <c r="B437" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3477244773820562</v>
+        <v>0.3590717304185123</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11772,7 +11772,7 @@
         <v>15</v>
       </c>
       <c r="C438">
-        <v>0.4118026022837792</v>
+        <v>0.3786987201899532</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11786,10 +11786,10 @@
         <v>886</v>
       </c>
       <c r="B439" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C439">
-        <v>0.2914424827795816</v>
+        <v>0.4106590898760635</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11803,10 +11803,10 @@
         <v>888</v>
       </c>
       <c r="B440" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C440">
-        <v>0.3688189022536865</v>
+        <v>0.4365675765952921</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11823,7 +11823,7 @@
         <v>15</v>
       </c>
       <c r="C441">
-        <v>0.3541889529747193</v>
+        <v>0.3024182185664596</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.2707250971886571</v>
+        <v>0.3243218518696234</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11857,7 +11857,7 @@
         <v>15</v>
       </c>
       <c r="C443">
-        <v>0.3671187207316316</v>
+        <v>0.3356376753610104</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11871,10 +11871,10 @@
         <v>896</v>
       </c>
       <c r="B444" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3591762058619261</v>
+        <v>0.3743552451976403</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11888,10 +11888,10 @@
         <v>898</v>
       </c>
       <c r="B445" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3350517697272739</v>
+        <v>0.3673638301188544</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3776776635644576</v>
+        <v>0.3833124419691462</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11922,10 +11922,10 @@
         <v>902</v>
       </c>
       <c r="B447" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C447">
-        <v>0.3088459719362907</v>
+        <v>0.3136054766276056</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11939,10 +11939,10 @@
         <v>904</v>
       </c>
       <c r="B448" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C448">
-        <v>0.2799042267780666</v>
+        <v>0.40510798142858</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11956,10 +11956,10 @@
         <v>906</v>
       </c>
       <c r="B449" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C449">
-        <v>0.318901305314988</v>
+        <v>0.4587664465532609</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.3746360297088294</v>
+        <v>0.4179405662644137</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4347537894028959</v>
+        <v>0.4827849303102942</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12007,10 +12007,10 @@
         <v>912</v>
       </c>
       <c r="B452" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3020206087222677</v>
+        <v>0.3099747894866376</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12024,10 +12024,10 @@
         <v>914</v>
       </c>
       <c r="B453" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3441971139667386</v>
+        <v>0.3873199678874892</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12044,7 +12044,7 @@
         <v>15</v>
       </c>
       <c r="C454">
-        <v>0.3325863934261372</v>
+        <v>0.2964212206072519</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12058,10 +12058,10 @@
         <v>918</v>
       </c>
       <c r="B455" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3863408103984265</v>
+        <v>0.3689910127567897</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12075,10 +12075,10 @@
         <v>920</v>
       </c>
       <c r="B456" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3254868912418057</v>
+        <v>0.3938386295730035</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12095,7 +12095,7 @@
         <v>15</v>
       </c>
       <c r="C457">
-        <v>0.4009268209554514</v>
+        <v>0.3738768490827961</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12109,10 +12109,10 @@
         <v>924</v>
       </c>
       <c r="B458" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C458">
-        <v>0.3088825760993496</v>
+        <v>0.4007795957441858</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12126,10 +12126,10 @@
         <v>926</v>
       </c>
       <c r="B459" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3108700668526125</v>
+        <v>0.3948485405804614</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12143,10 +12143,10 @@
         <v>928</v>
       </c>
       <c r="B460" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C460">
-        <v>0.3536736657078028</v>
+        <v>0.358080728552195</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12160,10 +12160,10 @@
         <v>930</v>
       </c>
       <c r="B461" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3563708934282608</v>
+        <v>0.3187248964572302</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.2995325517870338</v>
+        <v>0.3708057923447027</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12197,7 +12197,7 @@
         <v>15</v>
       </c>
       <c r="C463">
-        <v>0.3798871801134601</v>
+        <v>0.3274994146027568</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12211,10 +12211,10 @@
         <v>936</v>
       </c>
       <c r="B464" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C464">
-        <v>0.3564478090290205</v>
+        <v>0.4364824348854913</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.4277749168777052</v>
+        <v>0.4627526096080364</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12245,10 +12245,10 @@
         <v>940</v>
       </c>
       <c r="B466" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C466">
-        <v>0.4511144921402336</v>
+        <v>0.5818093277334901</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12262,10 +12262,10 @@
         <v>942</v>
       </c>
       <c r="B467" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C467">
-        <v>0.3891052187924412</v>
+        <v>0.5318681052633515</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12279,10 +12279,10 @@
         <v>944</v>
       </c>
       <c r="B468" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C468">
-        <v>0.3284548633954094</v>
+        <v>0.4624796784844015</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12299,7 +12299,7 @@
         <v>15</v>
       </c>
       <c r="C469">
-        <v>0.3356551994473588</v>
+        <v>0.2909468644174008</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12316,7 +12316,7 @@
         <v>15</v>
       </c>
       <c r="C470">
-        <v>0.3782740154409732</v>
+        <v>0.3501024718936351</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12330,10 +12330,10 @@
         <v>950</v>
       </c>
       <c r="B471" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3157999315899892</v>
+        <v>0.3642365524218964</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12350,7 +12350,7 @@
         <v>15</v>
       </c>
       <c r="C472">
-        <v>0.3802117039941139</v>
+        <v>0.3641574848567489</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12364,10 +12364,10 @@
         <v>954</v>
       </c>
       <c r="B473" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3409707929840083</v>
+        <v>0.3601209059185533</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12381,10 +12381,10 @@
         <v>956</v>
       </c>
       <c r="B474" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C474">
-        <v>0.4020511102922593</v>
+        <v>0.4446015758913578</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3026101191452168</v>
+        <v>0.3737093745333434</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12415,10 +12415,10 @@
         <v>960</v>
       </c>
       <c r="B476" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3070723090427467</v>
+        <v>0.3650344834721148</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12432,10 +12432,10 @@
         <v>962</v>
       </c>
       <c r="B477" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C477">
-        <v>0.4077250834957666</v>
+        <v>0.3618452739323825</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12449,10 +12449,10 @@
         <v>964</v>
       </c>
       <c r="B478" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C478">
-        <v>0.3143917557299255</v>
+        <v>0.4423948961564615</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4309009001904335</v>
+        <v>0.4901674907761368</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12483,10 +12483,10 @@
         <v>968</v>
       </c>
       <c r="B480" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C480">
-        <v>0.3906477929694617</v>
+        <v>0.5381517481905375</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.3910646985745775</v>
+        <v>0.4275151226594582</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12517,10 +12517,10 @@
         <v>972</v>
       </c>
       <c r="B482" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3222552649716642</v>
+        <v>0.3617769502489039</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12534,10 +12534,10 @@
         <v>974</v>
       </c>
       <c r="B483" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3405219030309607</v>
+        <v>0.3480728379321548</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.3893261865455211</v>
+        <v>0.4320811055610588</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12571,7 +12571,7 @@
         <v>15</v>
       </c>
       <c r="C485">
-        <v>0.465482771691472</v>
+        <v>0.4577739372173761</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12588,7 +12588,7 @@
         <v>15</v>
       </c>
       <c r="C486">
-        <v>0.5012992439081935</v>
+        <v>0.5061829755067078</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.4656745115033811</v>
+        <v>0.5324847696946391</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12619,10 +12619,10 @@
         <v>984</v>
       </c>
       <c r="B488" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3282074441747848</v>
+        <v>0.3814103924333979</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12636,10 +12636,10 @@
         <v>986</v>
       </c>
       <c r="B489" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C489">
-        <v>0.4348901340243421</v>
+        <v>0.5472925921739843</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12656,7 +12656,7 @@
         <v>15</v>
       </c>
       <c r="C490">
-        <v>0.3693157302918953</v>
+        <v>0.3598376240194596</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12670,10 +12670,10 @@
         <v>990</v>
       </c>
       <c r="B491" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C491">
-        <v>0.3169514539775959</v>
+        <v>0.2847988295680832</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12687,10 +12687,10 @@
         <v>992</v>
       </c>
       <c r="B492" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4721005399964329</v>
+        <v>0.4968737095919299</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.240700802386998</v>
+        <v>0.2942361107541009</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12721,10 +12721,10 @@
         <v>996</v>
       </c>
       <c r="B494" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3373599067775793</v>
+        <v>0.3981123775930181</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.5558732734362113</v>
+        <v>0.6198801162548521</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12755,10 +12755,10 @@
         <v>1000</v>
       </c>
       <c r="B496" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C496">
-        <v>0.398616335930449</v>
+        <v>0.5552930372159036</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12772,10 +12772,10 @@
         <v>1002</v>
       </c>
       <c r="B497" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3528641663249694</v>
+        <v>0.3752465060328306</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12789,10 +12789,10 @@
         <v>1004</v>
       </c>
       <c r="B498" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C498">
-        <v>0.6503194805803054</v>
+        <v>0.7263049823731841</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12809,7 +12809,7 @@
         <v>15</v>
       </c>
       <c r="C499">
-        <v>0.4023051882183194</v>
+        <v>0.3738072432418988</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12823,10 +12823,10 @@
         <v>1008</v>
       </c>
       <c r="B500" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C500">
-        <v>0.3361717238502174</v>
+        <v>0.4665773114967099</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12843,7 +12843,7 @@
         <v>15</v>
       </c>
       <c r="C501">
-        <v>0.4633154548725765</v>
+        <v>0.4726646129905198</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12857,10 +12857,10 @@
         <v>1012</v>
       </c>
       <c r="B502" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C502">
-        <v>0.5350378004405144</v>
+        <v>0.654172813830409</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12877,7 +12877,7 @@
         <v>15</v>
       </c>
       <c r="C503">
-        <v>0.4459506202331933</v>
+        <v>0.4239101369256076</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12894,7 +12894,7 @@
         <v>15</v>
       </c>
       <c r="C504">
-        <v>0.3703143760164625</v>
+        <v>0.3236898762607828</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12908,10 +12908,10 @@
         <v>1018</v>
       </c>
       <c r="B505" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C505">
-        <v>0.3680598758451828</v>
+        <v>0.5053582193288489</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12928,7 +12928,7 @@
         <v>15</v>
       </c>
       <c r="C506">
-        <v>0.5701753422348128</v>
+        <v>0.606669037420546</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12942,10 +12942,10 @@
         <v>1022</v>
       </c>
       <c r="B507" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C507">
-        <v>0.3281661471836224</v>
+        <v>0.3534724180085382</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12962,7 +12962,7 @@
         <v>15</v>
       </c>
       <c r="C508">
-        <v>0.3737582962651139</v>
+        <v>0.3520312231605945</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12976,10 +12976,10 @@
         <v>1026</v>
       </c>
       <c r="B509" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C509">
-        <v>0.519965397010186</v>
+        <v>0.6126131705807644</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12993,10 +12993,10 @@
         <v>1028</v>
       </c>
       <c r="B510" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3893996330862609</v>
+        <v>0.3923450317469117</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.3659470108990784</v>
+        <v>0.4011121385046515</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13027,10 +13027,10 @@
         <v>1032</v>
       </c>
       <c r="B512" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C512">
-        <v>0.2601694086349136</v>
+        <v>0.3580543076495224</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13044,10 +13044,10 @@
         <v>1034</v>
       </c>
       <c r="B513" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C513">
-        <v>0.3212581426571081</v>
+        <v>0.4195153756560575</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.4384615825116663</v>
+        <v>0.5017602909299432</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13078,10 +13078,10 @@
         <v>1038</v>
       </c>
       <c r="B515" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C515">
-        <v>0.3994787096147158</v>
+        <v>0.5183877377188373</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13098,7 +13098,7 @@
         <v>15</v>
       </c>
       <c r="C516">
-        <v>0.3774027809752907</v>
+        <v>0.3442893827727207</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13115,7 +13115,7 @@
         <v>15</v>
       </c>
       <c r="C517">
-        <v>0.3845912877462336</v>
+        <v>0.3411001474694316</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13129,10 +13129,10 @@
         <v>1044</v>
       </c>
       <c r="B518" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3329239546592597</v>
+        <v>0.3948749226154879</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5084396254520782</v>
+        <v>0.5735250624980321</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13166,7 +13166,7 @@
         <v>15</v>
       </c>
       <c r="C520">
-        <v>0.4055890132978071</v>
+        <v>0.3908925393322007</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13180,10 +13180,10 @@
         <v>1050</v>
       </c>
       <c r="B521" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3082195966514678</v>
+        <v>0.3482588951200677</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13200,7 +13200,7 @@
         <v>15</v>
       </c>
       <c r="C522">
-        <v>0.4445146552799638</v>
+        <v>0.4184200415875385</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13214,10 +13214,10 @@
         <v>1054</v>
       </c>
       <c r="B523" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C523">
-        <v>0.3804273023742613</v>
+        <v>0.5372616215693192</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13231,10 +13231,10 @@
         <v>1056</v>
       </c>
       <c r="B524" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3227261473764709</v>
+        <v>0.3090968259362861</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4270105222575232</v>
+        <v>0.4613459989873869</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.439717979034863</v>
+        <v>0.4989851834853846</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13282,10 +13282,10 @@
         <v>1062</v>
       </c>
       <c r="B527" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C527">
-        <v>0.3572038869138695</v>
+        <v>0.396586754778305</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13299,10 +13299,10 @@
         <v>1064</v>
       </c>
       <c r="B528" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C528">
-        <v>0.3686435384006056</v>
+        <v>0.4987051665365487</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13316,10 +13316,10 @@
         <v>1066</v>
       </c>
       <c r="B529" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3631274117265741</v>
+        <v>0.3682801040755864</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.5081235077128834</v>
+        <v>0.587190397923504</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.5709316525219272</v>
+        <v>0.6516558743946289</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13370,7 +13370,7 @@
         <v>44</v>
       </c>
       <c r="C532">
-        <v>0.2968375096555584</v>
+        <v>0.2962295389728327</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13387,7 +13387,7 @@
         <v>15</v>
       </c>
       <c r="C533">
-        <v>0.521722640126397</v>
+        <v>0.5619238065575358</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13404,7 +13404,7 @@
         <v>15</v>
       </c>
       <c r="C534">
-        <v>0.4109876378335323</v>
+        <v>0.3800675063353964</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13418,10 +13418,10 @@
         <v>1078</v>
       </c>
       <c r="B535" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3312444347986639</v>
+        <v>0.3373762037480327</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13438,7 +13438,7 @@
         <v>15</v>
       </c>
       <c r="C536">
-        <v>0.3595961750584842</v>
+        <v>0.3080273742131366</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13452,10 +13452,10 @@
         <v>1082</v>
       </c>
       <c r="B537" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C537">
-        <v>0.2996464531858647</v>
+        <v>0.4131717664376138</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13472,7 +13472,7 @@
         <v>15</v>
       </c>
       <c r="C538">
-        <v>0.3601695227571301</v>
+        <v>0.3144315329354996</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13486,10 +13486,10 @@
         <v>1086</v>
       </c>
       <c r="B539" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3449746933628294</v>
+        <v>0.3138461162455821</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13506,7 +13506,7 @@
         <v>15</v>
       </c>
       <c r="C540">
-        <v>0.3255735313830602</v>
+        <v>0.2865130827840019</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13520,10 +13520,10 @@
         <v>1090</v>
       </c>
       <c r="B541" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C541">
-        <v>0.3559235963886052</v>
+        <v>0.5004709603666889</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13537,10 +13537,10 @@
         <v>1092</v>
       </c>
       <c r="B542" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3691282378324369</v>
+        <v>0.3798193010024841</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13554,10 +13554,10 @@
         <v>1094</v>
       </c>
       <c r="B543" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C543">
-        <v>0.3635620214796481</v>
+        <v>0.4348356654158654</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13571,10 +13571,10 @@
         <v>1096</v>
       </c>
       <c r="B544" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C544">
-        <v>0.2766618588564593</v>
+        <v>0.3914150402294408</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2999994045071486</v>
+        <v>0.2855484150813754</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.328989687267506</v>
+        <v>0.3262320650819759</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2963471369460847</v>
+        <v>0.2782669255799973</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3843611636051328</v>
+        <v>0.3940464698227714</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.4007170255023122</v>
+        <v>0.3988758093137</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.3941913582311795</v>
+        <v>0.4123188325914808</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2736554602593221</v>
+        <v>0.2575416750384958</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.3023981135598851</v>
+        <v>0.2927625854117862</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2952959784196043</v>
+        <v>0.2864544627275417</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13993,10 +13993,10 @@
         <v>1162</v>
       </c>
       <c r="B572" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C572">
-        <v>0.2748615511995495</v>
+        <v>0.2765638921388476</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3366633488965735</v>
+        <v>0.3414723130279372</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3323513938903024</v>
+        <v>0.3961806163165391</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3684054628769579</v>
+        <v>0.3732100493008802</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.3896978212034408</v>
+        <v>0.368156664991985</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14078,10 +14078,10 @@
         <v>1172</v>
       </c>
       <c r="B577" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C577">
-        <v>0.2779873239329447</v>
+        <v>0.3453925318550689</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3863280550047151</v>
+        <v>0.3793094642344827</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3281212481422769</v>
+        <v>0.3250164540827461</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14129,10 +14129,10 @@
         <v>1178</v>
       </c>
       <c r="B580" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3368065279147531</v>
+        <v>0.3218620878894965</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.462381488726977</v>
+        <v>0.4655952976822675</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.320352604644586</v>
+        <v>0.309400385416069</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3763642887219861</v>
+        <v>0.3658091273568222</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14197,10 +14197,10 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C584">
-        <v>0.312962746913077</v>
+        <v>0.3042246957161413</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.417058081894219</v>
+        <v>0.3964013693525566</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2941710756449022</v>
+        <v>0.2553361711698874</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14248,10 +14248,10 @@
         <v>1192</v>
       </c>
       <c r="B587" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C587">
-        <v>0.2726400943341069</v>
+        <v>0.3365768854851884</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3241932149600917</v>
+        <v>0.3095319197554634</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3410659387717144</v>
+        <v>0.3999095556206499</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14299,10 +14299,10 @@
         <v>1198</v>
       </c>
       <c r="B590" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C590">
-        <v>0.3768187262167684</v>
+        <v>0.4607922384138766</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5332077891144843</v>
+        <v>0.5345850890993862</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.4164570829478551</v>
+        <v>0.376006978002694</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.6740383561868019</v>
+        <v>0.688958893423898</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4361154723182727</v>
+        <v>0.4497991037722774</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14384,10 +14384,10 @@
         <v>1208</v>
       </c>
       <c r="B595" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C595">
-        <v>0.2985357949870052</v>
+        <v>0.3464765412091352</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4354430274448882</v>
+        <v>0.4341918946411915</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14418,10 +14418,10 @@
         <v>1212</v>
       </c>
       <c r="B597" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3099043163761046</v>
+        <v>0.3776594281121816</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C598">
-        <v>0.2661957038483899</v>
+        <v>0.2400237033279259</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2785484394586231</v>
+        <v>0.2601313329844225</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2899810727880353</v>
+        <v>0.2768379730721458</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>44</v>
       </c>
       <c r="C601">
-        <v>0.2556804977422945</v>
+        <v>0.2999115762177406</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3791735127155921</v>
+        <v>0.3822857762486591</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.3010717402804274</v>
+        <v>0.2948640674527304</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14537,10 +14537,10 @@
         <v>1226</v>
       </c>
       <c r="B604" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C604">
-        <v>0.2947551171956511</v>
+        <v>0.3686517808429063</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.2887180869604026</v>
+        <v>0.3373296272957552</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14571,10 +14571,10 @@
         <v>1230</v>
       </c>
       <c r="B606" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C606">
-        <v>0.3571854771805912</v>
+        <v>0.3422080186269025</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3341553468731112</v>
+        <v>0.3345403526847052</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14605,10 +14605,10 @@
         <v>1234</v>
       </c>
       <c r="B608" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C608">
-        <v>0.2806722502206938</v>
+        <v>0.3441064726401417</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14622,10 +14622,10 @@
         <v>1236</v>
       </c>
       <c r="B609" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C609">
-        <v>0.2948792353525946</v>
+        <v>0.2994096564544887</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>1143</v>
+        <v>6</v>
       </c>
       <c r="C610">
-        <v>0.2593942047186719</v>
+        <v>0.2556612526815089</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.4915987013578978</v>
+        <v>0.5878903570299606</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3183899244029611</v>
+        <v>0.3478722290239945</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3501613141479245</v>
+        <v>0.3441152500678243</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4372233548824392</v>
+        <v>0.4545700294234872</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3351201939309388</v>
+        <v>0.3388664958290554</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.433886948459429</v>
+        <v>0.4337485429436427</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3382879095145531</v>
+        <v>0.3324328559091356</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14775,10 +14775,10 @@
         <v>1254</v>
       </c>
       <c r="B618" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3394351676987766</v>
+        <v>0.3244921720352588</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4590018723708016</v>
+        <v>0.4443447212557739</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C620">
-        <v>0.3011117285133565</v>
+        <v>0.2795719529751234</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14829,7 +14829,7 @@
         <v>15</v>
       </c>
       <c r="C621">
-        <v>0.3573007685329016</v>
+        <v>0.3742407893655519</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C622">
-        <v>0.2636743853122567</v>
+        <v>0.2564627320476451</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14860,78 +14860,78 @@
         <v>1265</v>
       </c>
       <c r="B623" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C623">
-        <v>0.2006616320617115</v>
+        <v>0.2566706329475214</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
       </c>
       <c r="E623" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="624" spans="1:5">
       <c r="A624" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B624" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C624">
-        <v>0.2811709500222385</v>
+        <v>0.3128997512260232</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
       </c>
       <c r="E624" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="625" spans="1:5">
       <c r="A625" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B625" t="s">
-        <v>6</v>
+        <v>1266</v>
       </c>
       <c r="C625">
-        <v>0.2393009594652543</v>
+        <v>0.2748091567765434</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
       </c>
       <c r="E625" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="626" spans="1:5">
       <c r="A626" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B626" t="s">
         <v>15</v>
       </c>
       <c r="C626">
-        <v>0.3360994622955937</v>
+        <v>0.3112103199952198</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
       </c>
       <c r="E626" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="627" spans="1:5">
       <c r="A627" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B627" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C627">
-        <v>0.277902045501993</v>
+        <v>0.3819487650301643</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>12</v>
+        <v>1266</v>
       </c>
       <c r="C628">
-        <v>0.2201442313913202</v>
+        <v>0.2625010223874499</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>12</v>
+        <v>1266</v>
       </c>
       <c r="C629">
-        <v>0.2647707853853323</v>
+        <v>0.2453476357168148</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14979,10 +14979,10 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C630">
-        <v>0.3224246779272007</v>
+        <v>0.4029975429706738</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14996,10 +14996,10 @@
         <v>1282</v>
       </c>
       <c r="B631" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C631">
-        <v>0.3122155825898124</v>
+        <v>0.4256233767885871</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15013,10 +15013,10 @@
         <v>1284</v>
       </c>
       <c r="B632" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C632">
-        <v>0.3763977866427771</v>
+        <v>0.4787045911536497</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15033,7 +15033,7 @@
         <v>15</v>
       </c>
       <c r="C633">
-        <v>0.2783012340118505</v>
+        <v>0.264681346461473</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15050,7 +15050,7 @@
         <v>15</v>
       </c>
       <c r="C634">
-        <v>0.406261282910187</v>
+        <v>0.4505297611403773</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15064,10 +15064,10 @@
         <v>1290</v>
       </c>
       <c r="B635" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C635">
-        <v>0.4123250518416283</v>
+        <v>0.4931683103110366</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15081,10 +15081,10 @@
         <v>1292</v>
       </c>
       <c r="B636" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3844111219214787</v>
+        <v>0.3499541453003878</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C637">
-        <v>0.2910499101309268</v>
+        <v>0.360107153665462</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15115,10 +15115,10 @@
         <v>1296</v>
       </c>
       <c r="B638" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C638">
-        <v>0.4160095152808186</v>
+        <v>0.5425953501478241</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15132,10 +15132,10 @@
         <v>1298</v>
       </c>
       <c r="B639" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3402489862981334</v>
+        <v>0.3917239599328542</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15149,10 +15149,10 @@
         <v>1300</v>
       </c>
       <c r="B640" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C640">
-        <v>0.2809680573390586</v>
+        <v>0.3156642539070019</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>15</v>
+        <v>1266</v>
       </c>
       <c r="C641">
-        <v>0.2736206411762203</v>
+        <v>0.275282865843146</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15183,10 +15183,10 @@
         <v>1304</v>
       </c>
       <c r="B642" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C642">
-        <v>0.270619711767387</v>
+        <v>0.3678489336470355</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15203,7 +15203,7 @@
         <v>15</v>
       </c>
       <c r="C643">
-        <v>0.3067929832037643</v>
+        <v>0.3170130638659789</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15220,7 +15220,7 @@
         <v>15</v>
       </c>
       <c r="C644">
-        <v>0.2873032606701417</v>
+        <v>0.284441630395121</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15237,7 +15237,7 @@
         <v>15</v>
       </c>
       <c r="C645">
-        <v>0.2581804464053325</v>
+        <v>0.2344201201127299</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15254,7 +15254,7 @@
         <v>15</v>
       </c>
       <c r="C646">
-        <v>0.3733794506170044</v>
+        <v>0.3853974450695236</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>12</v>
+        <v>1266</v>
       </c>
       <c r="C647">
-        <v>0.2786351838583878</v>
+        <v>0.2963363725264956</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15288,7 +15288,7 @@
         <v>15</v>
       </c>
       <c r="C648">
-        <v>0.2849348040639744</v>
+        <v>0.2706524357275279</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15305,7 +15305,7 @@
         <v>15</v>
       </c>
       <c r="C649">
-        <v>0.3321347580866019</v>
+        <v>0.3503241214132245</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>12</v>
+        <v>1266</v>
       </c>
       <c r="C650">
-        <v>0.2547230013139709</v>
+        <v>0.31707139138557</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15339,7 +15339,7 @@
         <v>15</v>
       </c>
       <c r="C651">
-        <v>0.3119758638387678</v>
+        <v>0.2982426608190498</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15371,20 +15371,20 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -15392,10 +15392,10 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15416,10 +15416,10 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -62,27 +62,27 @@
     <t>amber valley</t>
   </si>
   <si>
+    <t>E14001066</t>
+  </si>
+  <si>
+    <t>arundel and south downs</t>
+  </si>
+  <si>
+    <t>E14001067</t>
+  </si>
+  <si>
+    <t>ashfield</t>
+  </si>
+  <si>
+    <t>E14001068</t>
+  </si>
+  <si>
+    <t>ashford</t>
+  </si>
+  <si>
     <t>Brexit Party/Reform UK</t>
   </si>
   <si>
-    <t>E14001066</t>
-  </si>
-  <si>
-    <t>arundel and south downs</t>
-  </si>
-  <si>
-    <t>E14001067</t>
-  </si>
-  <si>
-    <t>ashfield</t>
-  </si>
-  <si>
-    <t>E14001068</t>
-  </si>
-  <si>
-    <t>ashford</t>
-  </si>
-  <si>
     <t>E14001069</t>
   </si>
   <si>
@@ -254,207 +254,207 @@
     <t>birmingham northfield</t>
   </si>
   <si>
+    <t>E14001097</t>
+  </si>
+  <si>
+    <t>birmingham perry barr</t>
+  </si>
+  <si>
+    <t>E14001098</t>
+  </si>
+  <si>
+    <t>birmingham selly oak</t>
+  </si>
+  <si>
+    <t>E14001099</t>
+  </si>
+  <si>
+    <t>birmingham yardley</t>
+  </si>
+  <si>
+    <t>E14001100</t>
+  </si>
+  <si>
+    <t>bishop auckland</t>
+  </si>
+  <si>
+    <t>E14001101</t>
+  </si>
+  <si>
+    <t>blackburn</t>
+  </si>
+  <si>
+    <t>E14001102</t>
+  </si>
+  <si>
+    <t>blackley and middleton south</t>
+  </si>
+  <si>
+    <t>E14001103</t>
+  </si>
+  <si>
+    <t>blackpool north and fleetwood</t>
+  </si>
+  <si>
+    <t>E14001104</t>
+  </si>
+  <si>
+    <t>blackpool south</t>
+  </si>
+  <si>
+    <t>E14001105</t>
+  </si>
+  <si>
+    <t>blaydon and consett</t>
+  </si>
+  <si>
+    <t>E14001106</t>
+  </si>
+  <si>
+    <t>blyth and ashington</t>
+  </si>
+  <si>
+    <t>E14001107</t>
+  </si>
+  <si>
+    <t>bognor regis and littlehampton</t>
+  </si>
+  <si>
+    <t>E14001108</t>
+  </si>
+  <si>
+    <t>bolsover</t>
+  </si>
+  <si>
+    <t>E14001109</t>
+  </si>
+  <si>
+    <t>bolton north east</t>
+  </si>
+  <si>
+    <t>E14001110</t>
+  </si>
+  <si>
+    <t>bolton south and walkden</t>
+  </si>
+  <si>
+    <t>E14001111</t>
+  </si>
+  <si>
+    <t>bolton west</t>
+  </si>
+  <si>
+    <t>E14001112</t>
+  </si>
+  <si>
+    <t>bootle</t>
+  </si>
+  <si>
+    <t>E14001113</t>
+  </si>
+  <si>
+    <t>boston and skegness</t>
+  </si>
+  <si>
+    <t>E14001114</t>
+  </si>
+  <si>
+    <t>bournemouth east</t>
+  </si>
+  <si>
+    <t>E14001115</t>
+  </si>
+  <si>
+    <t>bournemouth west</t>
+  </si>
+  <si>
+    <t>E14001116</t>
+  </si>
+  <si>
+    <t>bracknell</t>
+  </si>
+  <si>
+    <t>E14001117</t>
+  </si>
+  <si>
+    <t>bradford east</t>
+  </si>
+  <si>
+    <t>E14001118</t>
+  </si>
+  <si>
+    <t>bradford south</t>
+  </si>
+  <si>
+    <t>E14001119</t>
+  </si>
+  <si>
+    <t>bradford west</t>
+  </si>
+  <si>
+    <t>E14001120</t>
+  </si>
+  <si>
+    <t>braintree</t>
+  </si>
+  <si>
+    <t>E14001121</t>
+  </si>
+  <si>
+    <t>brent east</t>
+  </si>
+  <si>
+    <t>E14001122</t>
+  </si>
+  <si>
+    <t>brent west</t>
+  </si>
+  <si>
+    <t>E14001123</t>
+  </si>
+  <si>
+    <t>brentford and isleworth</t>
+  </si>
+  <si>
+    <t>E14001124</t>
+  </si>
+  <si>
+    <t>brentwood and ongar</t>
+  </si>
+  <si>
+    <t>E14001125</t>
+  </si>
+  <si>
+    <t>bridgwater</t>
+  </si>
+  <si>
+    <t>E14001126</t>
+  </si>
+  <si>
+    <t>bridlington and the wolds</t>
+  </si>
+  <si>
+    <t>E14001127</t>
+  </si>
+  <si>
+    <t>brigg and immingham</t>
+  </si>
+  <si>
+    <t>E14001128</t>
+  </si>
+  <si>
+    <t>brighton kemptown and peacehaven</t>
+  </si>
+  <si>
+    <t>E14001129</t>
+  </si>
+  <si>
+    <t>brighton pavilion</t>
+  </si>
+  <si>
     <t>Green Party</t>
   </si>
   <si>
-    <t>E14001097</t>
-  </si>
-  <si>
-    <t>birmingham perry barr</t>
-  </si>
-  <si>
-    <t>E14001098</t>
-  </si>
-  <si>
-    <t>birmingham selly oak</t>
-  </si>
-  <si>
-    <t>E14001099</t>
-  </si>
-  <si>
-    <t>birmingham yardley</t>
-  </si>
-  <si>
-    <t>E14001100</t>
-  </si>
-  <si>
-    <t>bishop auckland</t>
-  </si>
-  <si>
-    <t>E14001101</t>
-  </si>
-  <si>
-    <t>blackburn</t>
-  </si>
-  <si>
-    <t>E14001102</t>
-  </si>
-  <si>
-    <t>blackley and middleton south</t>
-  </si>
-  <si>
-    <t>E14001103</t>
-  </si>
-  <si>
-    <t>blackpool north and fleetwood</t>
-  </si>
-  <si>
-    <t>E14001104</t>
-  </si>
-  <si>
-    <t>blackpool south</t>
-  </si>
-  <si>
-    <t>E14001105</t>
-  </si>
-  <si>
-    <t>blaydon and consett</t>
-  </si>
-  <si>
-    <t>E14001106</t>
-  </si>
-  <si>
-    <t>blyth and ashington</t>
-  </si>
-  <si>
-    <t>E14001107</t>
-  </si>
-  <si>
-    <t>bognor regis and littlehampton</t>
-  </si>
-  <si>
-    <t>E14001108</t>
-  </si>
-  <si>
-    <t>bolsover</t>
-  </si>
-  <si>
-    <t>E14001109</t>
-  </si>
-  <si>
-    <t>bolton north east</t>
-  </si>
-  <si>
-    <t>E14001110</t>
-  </si>
-  <si>
-    <t>bolton south and walkden</t>
-  </si>
-  <si>
-    <t>E14001111</t>
-  </si>
-  <si>
-    <t>bolton west</t>
-  </si>
-  <si>
-    <t>E14001112</t>
-  </si>
-  <si>
-    <t>bootle</t>
-  </si>
-  <si>
-    <t>E14001113</t>
-  </si>
-  <si>
-    <t>boston and skegness</t>
-  </si>
-  <si>
-    <t>E14001114</t>
-  </si>
-  <si>
-    <t>bournemouth east</t>
-  </si>
-  <si>
-    <t>E14001115</t>
-  </si>
-  <si>
-    <t>bournemouth west</t>
-  </si>
-  <si>
-    <t>E14001116</t>
-  </si>
-  <si>
-    <t>bracknell</t>
-  </si>
-  <si>
-    <t>E14001117</t>
-  </si>
-  <si>
-    <t>bradford east</t>
-  </si>
-  <si>
-    <t>E14001118</t>
-  </si>
-  <si>
-    <t>bradford south</t>
-  </si>
-  <si>
-    <t>E14001119</t>
-  </si>
-  <si>
-    <t>bradford west</t>
-  </si>
-  <si>
-    <t>E14001120</t>
-  </si>
-  <si>
-    <t>braintree</t>
-  </si>
-  <si>
-    <t>E14001121</t>
-  </si>
-  <si>
-    <t>brent east</t>
-  </si>
-  <si>
-    <t>E14001122</t>
-  </si>
-  <si>
-    <t>brent west</t>
-  </si>
-  <si>
-    <t>E14001123</t>
-  </si>
-  <si>
-    <t>brentford and isleworth</t>
-  </si>
-  <si>
-    <t>E14001124</t>
-  </si>
-  <si>
-    <t>brentwood and ongar</t>
-  </si>
-  <si>
-    <t>E14001125</t>
-  </si>
-  <si>
-    <t>bridgwater</t>
-  </si>
-  <si>
-    <t>E14001126</t>
-  </si>
-  <si>
-    <t>bridlington and the wolds</t>
-  </si>
-  <si>
-    <t>E14001127</t>
-  </si>
-  <si>
-    <t>brigg and immingham</t>
-  </si>
-  <si>
-    <t>E14001128</t>
-  </si>
-  <si>
-    <t>brighton kemptown and peacehaven</t>
-  </si>
-  <si>
-    <t>E14001129</t>
-  </si>
-  <si>
-    <t>brighton pavilion</t>
-  </si>
-  <si>
     <t>E14001130</t>
   </si>
   <si>
@@ -3815,31 +3815,31 @@
     <t>blaenau gwent and rhymney</t>
   </si>
   <si>
+    <t>W07000084</t>
+  </si>
+  <si>
+    <t>brecon, radnor and cwm tawe</t>
+  </si>
+  <si>
+    <t>W07000085</t>
+  </si>
+  <si>
+    <t>bridgend</t>
+  </si>
+  <si>
+    <t>W07000086</t>
+  </si>
+  <si>
+    <t>caerfyrddin</t>
+  </si>
+  <si>
+    <t>W07000087</t>
+  </si>
+  <si>
+    <t>caerphilly</t>
+  </si>
+  <si>
     <t>Plaid Cymru</t>
-  </si>
-  <si>
-    <t>W07000084</t>
-  </si>
-  <si>
-    <t>brecon, radnor and cwm tawe</t>
-  </si>
-  <si>
-    <t>W07000085</t>
-  </si>
-  <si>
-    <t>bridgend</t>
-  </si>
-  <si>
-    <t>W07000086</t>
-  </si>
-  <si>
-    <t>caerfyrddin</t>
-  </si>
-  <si>
-    <t>W07000087</t>
-  </si>
-  <si>
-    <t>caerphilly</t>
   </si>
   <si>
     <t>W07000088</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3148799591978115</v>
+        <v>0.3016269068473654</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4889363734579543</v>
+        <v>0.4401623243779999</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.4588847465753229</v>
+        <v>0.4167480359904406</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4408,61 +4408,61 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>0.3085380935059038</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
-      </c>
-      <c r="C5">
-        <v>0.3329045509440046</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.4457269227235309</v>
+        <v>0.3858216852295178</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0.2969903404013247</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>0.3191198569972155</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
       <c r="C8">
-        <v>0.3439871008118419</v>
+        <v>0.3069443243978868</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4476,10 +4476,10 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>0.3241899032902994</v>
+        <v>0.2903359951279176</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.409372006019849</v>
+        <v>0.3604244458439821</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>0.2578316307974798</v>
+        <v>0.2449683177961995</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4449927539550906</v>
+        <v>0.4058376615803914</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4544,10 +4544,10 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>0.3358121897174547</v>
+        <v>0.2970034344603001</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4561,10 +4561,10 @@
         <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C14">
-        <v>0.42165650768725</v>
+        <v>0.351900739544562</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.3797925703831163</v>
+        <v>0.352408713762176</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3508183375792192</v>
+        <v>0.3112351985615457</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>0.3313940396162245</v>
+        <v>0.3065976760963816</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.3661248249420669</v>
+        <v>0.333212898456059</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.523248742546236</v>
+        <v>0.4361284057590889</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4577828542299923</v>
+        <v>0.4204931814127174</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.5143307530928638</v>
+        <v>0.4405539608734234</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.369693093144717</v>
+        <v>0.3361489841799629</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.4398849359991829</v>
+        <v>0.3947483598439713</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3558323805497369</v>
+        <v>0.3466696064213628</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6450119326050314</v>
+        <v>0.6155356369540657</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3429736389226613</v>
+        <v>0.3295551908873148</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.3273058236148824</v>
+        <v>0.3012277515027705</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3498585663467955</v>
+        <v>0.3262327534250096</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.5550378767338562</v>
+        <v>0.4618654014443809</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.4415380567087203</v>
+        <v>0.3942316842809056</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.5181191661341904</v>
+        <v>0.4533077506566369</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4867,10 +4867,10 @@
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C32">
-        <v>0.4667050692883329</v>
+        <v>0.3854482013542957</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.468625925799224</v>
+        <v>0.4063664073262408</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4901,10 +4901,10 @@
         <v>74</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C34">
-        <v>0.414947907346504</v>
+        <v>0.3459156384426002</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4904876810172027</v>
+        <v>0.4717754394573599</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4935,571 +4935,571 @@
         <v>78</v>
       </c>
       <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>0.244986401557798</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" t="s">
         <v>79</v>
-      </c>
-      <c r="C36">
-        <v>0.2840128056721649</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37">
+        <v>0.2753666580754036</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
         <v>81</v>
-      </c>
-      <c r="B37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37">
-        <v>0.2995793658017566</v>
-      </c>
-      <c r="D37" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>0.3348008672778034</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s">
         <v>83</v>
-      </c>
-      <c r="B38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38">
-        <v>0.3451860156088423</v>
-      </c>
-      <c r="D38" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>21</v>
+      </c>
+      <c r="C39">
+        <v>0.3219178470779564</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s">
         <v>85</v>
-      </c>
-      <c r="B39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39">
-        <v>0.3645520217077515</v>
-      </c>
-      <c r="D39" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>0.5063553232724664</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
         <v>87</v>
-      </c>
-      <c r="B40" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40">
-        <v>0.5592018398856138</v>
-      </c>
-      <c r="D40" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41">
+        <v>0.2430329685497141</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" t="s">
         <v>89</v>
-      </c>
-      <c r="B41" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41">
-        <v>0.2512736788206363</v>
-      </c>
-      <c r="D41" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
+        <v>90</v>
+      </c>
+      <c r="B42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>0.5314891180116685</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
         <v>91</v>
-      </c>
-      <c r="B42" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42">
-        <v>0.5842200495081381</v>
-      </c>
-      <c r="D42" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C43">
+        <v>0.3869515198907192</v>
+      </c>
+      <c r="D43" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" t="s">
         <v>93</v>
-      </c>
-      <c r="B43" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43">
-        <v>0.4408046842894297</v>
-      </c>
-      <c r="D43" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" t="s">
+        <v>21</v>
+      </c>
+      <c r="C44">
+        <v>0.3892888345429857</v>
+      </c>
+      <c r="D44" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" t="s">
         <v>95</v>
-      </c>
-      <c r="B44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44">
-        <v>0.4563504507689837</v>
-      </c>
-      <c r="D44" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>0.4148548414642107</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
         <v>97</v>
-      </c>
-      <c r="B45" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45">
-        <v>0.4645302341573114</v>
-      </c>
-      <c r="D45" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>0.4256362711393673</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" t="s">
         <v>99</v>
-      </c>
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46">
-        <v>0.4612671100533123</v>
-      </c>
-      <c r="D46" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47">
+        <v>0.3117196430688026</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" t="s">
         <v>101</v>
-      </c>
-      <c r="B47" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47">
-        <v>0.3511858139400525</v>
-      </c>
-      <c r="D47" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48">
+        <v>0.3910441824895293</v>
+      </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" t="s">
         <v>103</v>
-      </c>
-      <c r="B48" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48">
-        <v>0.4672940748369899</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" t="s">
+        <v>21</v>
+      </c>
+      <c r="C49">
+        <v>0.3756637158880926</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
         <v>105</v>
-      </c>
-      <c r="B49" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49">
-        <v>0.4472700694243915</v>
-      </c>
-      <c r="D49" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" t="s">
+        <v>21</v>
+      </c>
+      <c r="C50">
+        <v>0.3289263434399722</v>
+      </c>
+      <c r="D50" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" t="s">
         <v>107</v>
-      </c>
-      <c r="B50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50">
-        <v>0.3778978194474971</v>
-      </c>
-      <c r="D50" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
+        <v>108</v>
+      </c>
+      <c r="B51" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51">
+        <v>0.3348965287860602</v>
+      </c>
+      <c r="D51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" t="s">
         <v>109</v>
-      </c>
-      <c r="B51" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51">
-        <v>0.3718519630827773</v>
-      </c>
-      <c r="D51" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
+        <v>110</v>
+      </c>
+      <c r="B52" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52">
+        <v>0.4985539416510877</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
         <v>111</v>
-      </c>
-      <c r="B52" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52">
-        <v>0.5477392293416247</v>
-      </c>
-      <c r="D52" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
+        <v>112</v>
+      </c>
+      <c r="B53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53">
+        <v>0.4130679180370659</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
         <v>113</v>
-      </c>
-      <c r="B53" t="s">
-        <v>15</v>
-      </c>
-      <c r="C53">
-        <v>0.5001351716944927</v>
-      </c>
-      <c r="D53" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54">
+        <v>0.3859700199665738</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
         <v>115</v>
-      </c>
-      <c r="B54" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54">
-        <v>0.416025409162521</v>
-      </c>
-      <c r="D54" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.3068638416606324</v>
+        <v>0.2839677029858616</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.4346604838844672</v>
+        <v>0.3840445098692734</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57">
+        <v>0.5692292577464846</v>
+      </c>
+      <c r="D57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" t="s">
         <v>121</v>
-      </c>
-      <c r="B57" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57">
-        <v>0.6276776262089527</v>
-      </c>
-      <c r="D57" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58">
+        <v>0.3229618445670541</v>
+      </c>
+      <c r="D58" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" t="s">
         <v>123</v>
-      </c>
-      <c r="B58" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58">
-        <v>0.3448347187084835</v>
-      </c>
-      <c r="D58" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59">
+        <v>0.3912685901161844</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
         <v>125</v>
-      </c>
-      <c r="B59" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59">
-        <v>0.4319717219435902</v>
-      </c>
-      <c r="D59" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60">
+        <v>0.3189254907421513</v>
+      </c>
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
         <v>127</v>
-      </c>
-      <c r="B60" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60">
-        <v>0.3280239157444572</v>
-      </c>
-      <c r="D60" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61">
+        <v>0.4050574537420344</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
         <v>129</v>
-      </c>
-      <c r="B61" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61">
-        <v>0.4394226086032252</v>
-      </c>
-      <c r="D61" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3705969153550849</v>
+        <v>0.3403123823237811</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <v>0.4035046155263314</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
         <v>133</v>
-      </c>
-      <c r="B63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63">
-        <v>0.4415642302217197</v>
-      </c>
-      <c r="D63" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B64" t="s">
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.2486445938311377</v>
+        <v>0.234224002238754</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65">
+        <v>0.31890047306172</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" t="s">
         <v>137</v>
-      </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65">
-        <v>0.35632621927411</v>
-      </c>
-      <c r="D65" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3468424172494392</v>
+        <v>0.3169432919486969</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
+        <v>140</v>
+      </c>
+      <c r="B67" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67">
+        <v>0.3077255338452973</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" t="s">
         <v>141</v>
-      </c>
-      <c r="B67" t="s">
-        <v>15</v>
-      </c>
-      <c r="C67">
-        <v>0.3540074456109498</v>
-      </c>
-      <c r="D67" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
+        <v>142</v>
+      </c>
+      <c r="B68" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68">
+        <v>0.2857336115773473</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" t="s">
         <v>143</v>
-      </c>
-      <c r="B68" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68">
-        <v>0.2984114582746857</v>
-      </c>
-      <c r="D68" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" t="s">
         <v>145</v>
       </c>
-      <c r="B69" t="s">
-        <v>79</v>
-      </c>
       <c r="C69">
-        <v>0.6700339591610287</v>
+        <v>0.5546153421658755</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
@@ -5513,10 +5513,10 @@
         <v>147</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C70">
-        <v>0.61302003706103</v>
+        <v>0.5230811004264685</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
@@ -5533,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.5028644178028351</v>
+        <v>0.5019592056601719</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
@@ -5550,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3875885374461754</v>
+        <v>0.3584282879379614</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
@@ -5567,7 +5567,7 @@
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.5661518547675282</v>
+        <v>0.5037426176914016</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
@@ -5584,7 +5584,7 @@
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.5414776872544211</v>
+        <v>0.5115694222808229</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
@@ -5601,7 +5601,7 @@
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.3026320378679523</v>
+        <v>0.2849954159121715</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
@@ -5618,7 +5618,7 @@
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.4177123582204118</v>
+        <v>0.3691329508663614</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
@@ -5635,7 +5635,7 @@
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3421539185019532</v>
+        <v>0.3107703785791928</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
@@ -5652,7 +5652,7 @@
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4515158801495786</v>
+        <v>0.4087340540975026</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
@@ -5669,7 +5669,7 @@
         <v>10</v>
       </c>
       <c r="C79">
-        <v>0.2769061896904103</v>
+        <v>0.2608309980184269</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
@@ -5686,7 +5686,7 @@
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.4239074146424086</v>
+        <v>0.3655552628102874</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
@@ -5700,10 +5700,10 @@
         <v>169</v>
       </c>
       <c r="B81" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C81">
-        <v>0.3236872879061882</v>
+        <v>0.2918808017793055</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
@@ -5720,7 +5720,7 @@
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.488734580621687</v>
+        <v>0.4269281090389851</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
@@ -5737,7 +5737,7 @@
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.415274350787541</v>
+        <v>0.3927810700698774</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
@@ -5754,7 +5754,7 @@
         <v>10</v>
       </c>
       <c r="C84">
-        <v>0.3323810273136972</v>
+        <v>0.3089532099622869</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
@@ -5768,10 +5768,10 @@
         <v>177</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C85">
-        <v>0.3712286626404174</v>
+        <v>0.3226022680599834</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
@@ -5788,7 +5788,7 @@
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3365919085040002</v>
+        <v>0.3062774014142624</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.3085238807598942</v>
+        <v>0.2830761858640501</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
@@ -5819,10 +5819,10 @@
         <v>183</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C88">
-        <v>0.3912397516953468</v>
+        <v>0.3289382328019479</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
@@ -5839,7 +5839,7 @@
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3620262399644406</v>
+        <v>0.3397001059854333</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
@@ -5856,7 +5856,7 @@
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.35485063225778</v>
+        <v>0.3097598455852941</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
@@ -5873,7 +5873,7 @@
         <v>10</v>
       </c>
       <c r="C91">
-        <v>0.3348364448597098</v>
+        <v>0.3105198274340028</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
@@ -5890,7 +5890,7 @@
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.3229386461239029</v>
+        <v>0.2913309921960212</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
@@ -5904,10 +5904,10 @@
         <v>193</v>
       </c>
       <c r="B93" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C93">
-        <v>0.4137627304841733</v>
+        <v>0.3668994210798103</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -5924,7 +5924,7 @@
         <v>44</v>
       </c>
       <c r="C94">
-        <v>0.2822035141944657</v>
+        <v>0.26292066563484</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -5938,10 +5938,10 @@
         <v>197</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C95">
-        <v>0.378912442161157</v>
+        <v>0.3343796937535661</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -5955,10 +5955,10 @@
         <v>199</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C96">
-        <v>0.3957067788680715</v>
+        <v>0.3489391872080709</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -5975,7 +5975,7 @@
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3793260223073759</v>
+        <v>0.3375203935277251</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -5992,7 +5992,7 @@
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.4136094755713687</v>
+        <v>0.359616784373201</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
@@ -6009,7 +6009,7 @@
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4829920136525135</v>
+        <v>0.4357319983163068</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
@@ -6026,7 +6026,7 @@
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.4121468304293552</v>
+        <v>0.359974636848084</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
@@ -6043,7 +6043,7 @@
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.4953878656516765</v>
+        <v>0.4214833441594282</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
@@ -6060,7 +6060,7 @@
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.5226709340403745</v>
+        <v>0.4652757612083137</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
@@ -6077,7 +6077,7 @@
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.4029856328323508</v>
+        <v>0.3530649482448727</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
@@ -6091,10 +6091,10 @@
         <v>215</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C104">
-        <v>0.4583916843047103</v>
+        <v>0.3821389719935503</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
@@ -6111,7 +6111,7 @@
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3980830901174558</v>
+        <v>0.3505029991496064</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.4096128781726479</v>
+        <v>0.3713441568876497</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
@@ -6145,7 +6145,7 @@
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3798070915112981</v>
+        <v>0.3445979453685457</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
@@ -6162,7 +6162,7 @@
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4455919608394198</v>
+        <v>0.4147911036405842</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
@@ -6179,7 +6179,7 @@
         <v>226</v>
       </c>
       <c r="C109">
-        <v>0.2788512891025846</v>
+        <v>0.2762897902410033</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6193,10 +6193,10 @@
         <v>228</v>
       </c>
       <c r="B110" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C110">
-        <v>0.3107825444212622</v>
+        <v>0.2822896167131076</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.5662023032273754</v>
+        <v>0.5044050663137096</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.4316919304163817</v>
+        <v>0.3838963550319209</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6244,10 +6244,10 @@
         <v>234</v>
       </c>
       <c r="B113" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C113">
-        <v>0.5958225042522152</v>
+        <v>0.4732395833986455</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6797493093260504</v>
+        <v>0.6474976021206573</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6278,10 +6278,10 @@
         <v>238</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>0.3069434482897445</v>
+        <v>0.2979308396707486</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4722933488654157</v>
+        <v>0.4457092750558775</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.3107342864137571</v>
+        <v>0.2973115484591263</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.4461973916848995</v>
+        <v>0.3879167096456849</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.4251087765807347</v>
+        <v>0.3830684436257644</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.4064908234339346</v>
+        <v>0.3625172705926554</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6383,7 +6383,7 @@
         <v>6</v>
       </c>
       <c r="C121">
-        <v>0.2958834927935312</v>
+        <v>0.2704350065374589</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6397,10 +6397,10 @@
         <v>252</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C122">
-        <v>0.3375018036406633</v>
+        <v>0.306793430295135</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6414,10 +6414,10 @@
         <v>254</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C123">
-        <v>0.3446735537192933</v>
+        <v>0.314174590373792</v>
       </c>
       <c r="D123" t="s">
         <v>7</v>
@@ -6431,10 +6431,10 @@
         <v>256</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C124">
-        <v>0.4504595818580544</v>
+        <v>0.3836021472842419</v>
       </c>
       <c r="D124" t="s">
         <v>7</v>
@@ -6451,7 +6451,7 @@
         <v>10</v>
       </c>
       <c r="C125">
-        <v>0.3401806441062993</v>
+        <v>0.3187042953230753</v>
       </c>
       <c r="D125" t="s">
         <v>7</v>
@@ -6468,7 +6468,7 @@
         <v>6</v>
       </c>
       <c r="C126">
-        <v>0.3751618625747613</v>
+        <v>0.3535246968528049</v>
       </c>
       <c r="D126" t="s">
         <v>7</v>
@@ -6485,7 +6485,7 @@
         <v>6</v>
       </c>
       <c r="C127">
-        <v>0.5585547739560009</v>
+        <v>0.5132235297205709</v>
       </c>
       <c r="D127" t="s">
         <v>7</v>
@@ -6499,10 +6499,10 @@
         <v>264</v>
       </c>
       <c r="B128" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C128">
-        <v>0.5022364335072822</v>
+        <v>0.4040430931785009</v>
       </c>
       <c r="D128" t="s">
         <v>7</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="C129">
-        <v>0.3130801080338931</v>
+        <v>0.2996628141434977</v>
       </c>
       <c r="D129" t="s">
         <v>7</v>
@@ -6533,10 +6533,10 @@
         <v>268</v>
       </c>
       <c r="B130" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C130">
-        <v>0.3922818003668597</v>
+        <v>0.3468295288607393</v>
       </c>
       <c r="D130" t="s">
         <v>7</v>
@@ -6553,7 +6553,7 @@
         <v>10</v>
       </c>
       <c r="C131">
-        <v>0.3173325351774905</v>
+        <v>0.2940464638628087</v>
       </c>
       <c r="D131" t="s">
         <v>7</v>
@@ -6570,7 +6570,7 @@
         <v>6</v>
       </c>
       <c r="C132">
-        <v>0.4232562142004567</v>
+        <v>0.3953086471581882</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -6584,10 +6584,10 @@
         <v>274</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C133">
-        <v>0.3732004014735105</v>
+        <v>0.3181654472417741</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -6604,7 +6604,7 @@
         <v>6</v>
       </c>
       <c r="C134">
-        <v>0.3545338278061065</v>
+        <v>0.333683601129651</v>
       </c>
       <c r="D134" t="s">
         <v>7</v>
@@ -6621,7 +6621,7 @@
         <v>6</v>
       </c>
       <c r="C135">
-        <v>0.390734224189196</v>
+        <v>0.3380369269657696</v>
       </c>
       <c r="D135" t="s">
         <v>7</v>
@@ -6638,7 +6638,7 @@
         <v>44</v>
       </c>
       <c r="C136">
-        <v>0.3635113258590155</v>
+        <v>0.3187200642763985</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
@@ -6655,7 +6655,7 @@
         <v>6</v>
       </c>
       <c r="C137">
-        <v>0.4518193445814067</v>
+        <v>0.4128850021820144</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
@@ -6672,7 +6672,7 @@
         <v>6</v>
       </c>
       <c r="C138">
-        <v>0.3228199025592156</v>
+        <v>0.3200397021214275</v>
       </c>
       <c r="D138" t="s">
         <v>7</v>
@@ -6689,7 +6689,7 @@
         <v>6</v>
       </c>
       <c r="C139">
-        <v>0.4150435435855106</v>
+        <v>0.3740164203214972</v>
       </c>
       <c r="D139" t="s">
         <v>7</v>
@@ -6706,7 +6706,7 @@
         <v>44</v>
       </c>
       <c r="C140">
-        <v>0.4520283408193798</v>
+        <v>0.4040544359592825</v>
       </c>
       <c r="D140" t="s">
         <v>7</v>
@@ -6723,7 +6723,7 @@
         <v>6</v>
       </c>
       <c r="C141">
-        <v>0.3753098620673169</v>
+        <v>0.3479822719014923</v>
       </c>
       <c r="D141" t="s">
         <v>7</v>
@@ -6740,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.457656182707546</v>
+        <v>0.3948972566677417</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
@@ -6757,7 +6757,7 @@
         <v>6</v>
       </c>
       <c r="C143">
-        <v>0.3669082393334129</v>
+        <v>0.3349965639286539</v>
       </c>
       <c r="D143" t="s">
         <v>7</v>
@@ -6774,7 +6774,7 @@
         <v>6</v>
       </c>
       <c r="C144">
-        <v>0.6420984002422625</v>
+        <v>0.6285804391911696</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
@@ -6791,7 +6791,7 @@
         <v>6</v>
       </c>
       <c r="C145">
-        <v>0.3229198648707026</v>
+        <v>0.308714813045275</v>
       </c>
       <c r="D145" t="s">
         <v>7</v>
@@ -6808,7 +6808,7 @@
         <v>6</v>
       </c>
       <c r="C146">
-        <v>0.4450752203802713</v>
+        <v>0.3905089559699357</v>
       </c>
       <c r="D146" t="s">
         <v>7</v>
@@ -6825,7 +6825,7 @@
         <v>6</v>
       </c>
       <c r="C147">
-        <v>0.5301223496059948</v>
+        <v>0.4779688579712267</v>
       </c>
       <c r="D147" t="s">
         <v>7</v>
@@ -6842,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="C148">
-        <v>0.3242344204018994</v>
+        <v>0.3118017690739986</v>
       </c>
       <c r="D148" t="s">
         <v>7</v>
@@ -6859,7 +6859,7 @@
         <v>10</v>
       </c>
       <c r="C149">
-        <v>0.4287812370452211</v>
+        <v>0.383093821088965</v>
       </c>
       <c r="D149" t="s">
         <v>7</v>
@@ -6873,10 +6873,10 @@
         <v>308</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C150">
-        <v>0.3540805196932908</v>
+        <v>0.3189820328482666</v>
       </c>
       <c r="D150" t="s">
         <v>7</v>
@@ -6893,7 +6893,7 @@
         <v>10</v>
       </c>
       <c r="C151">
-        <v>0.3036494445371418</v>
+        <v>0.2689019895694236</v>
       </c>
       <c r="D151" t="s">
         <v>7</v>
@@ -6910,7 +6910,7 @@
         <v>6</v>
       </c>
       <c r="C152">
-        <v>0.7194980193172126</v>
+        <v>0.6956433387619257</v>
       </c>
       <c r="D152" t="s">
         <v>7</v>
@@ -6927,7 +6927,7 @@
         <v>10</v>
       </c>
       <c r="C153">
-        <v>0.3687832354087566</v>
+        <v>0.3341660472775593</v>
       </c>
       <c r="D153" t="s">
         <v>7</v>
@@ -6944,7 +6944,7 @@
         <v>44</v>
       </c>
       <c r="C154">
-        <v>0.3665336396975648</v>
+        <v>0.323763700502917</v>
       </c>
       <c r="D154" t="s">
         <v>7</v>
@@ -6961,7 +6961,7 @@
         <v>6</v>
       </c>
       <c r="C155">
-        <v>0.2886388363929017</v>
+        <v>0.2749999238135038</v>
       </c>
       <c r="D155" t="s">
         <v>7</v>
@@ -6978,7 +6978,7 @@
         <v>10</v>
       </c>
       <c r="C156">
-        <v>0.4149191407887769</v>
+        <v>0.370283277542847</v>
       </c>
       <c r="D156" t="s">
         <v>7</v>
@@ -6995,7 +6995,7 @@
         <v>6</v>
       </c>
       <c r="C157">
-        <v>0.3781774175099467</v>
+        <v>0.3617281004598756</v>
       </c>
       <c r="D157" t="s">
         <v>7</v>
@@ -7012,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C158">
-        <v>0.4247841476311267</v>
+        <v>0.3696623940817696</v>
       </c>
       <c r="D158" t="s">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>44</v>
       </c>
       <c r="C159">
-        <v>0.4880660984689396</v>
+        <v>0.3979612677624669</v>
       </c>
       <c r="D159" t="s">
         <v>7</v>
@@ -7046,7 +7046,7 @@
         <v>6</v>
       </c>
       <c r="C160">
-        <v>0.4344939705175294</v>
+        <v>0.394502988165315</v>
       </c>
       <c r="D160" t="s">
         <v>7</v>
@@ -7063,7 +7063,7 @@
         <v>6</v>
       </c>
       <c r="C161">
-        <v>0.4237701809875523</v>
+        <v>0.3860876052902534</v>
       </c>
       <c r="D161" t="s">
         <v>7</v>
@@ -7080,7 +7080,7 @@
         <v>6</v>
       </c>
       <c r="C162">
-        <v>0.6253478043579843</v>
+        <v>0.5708041916131432</v>
       </c>
       <c r="D162" t="s">
         <v>7</v>
@@ -7097,7 +7097,7 @@
         <v>44</v>
       </c>
       <c r="C163">
-        <v>0.5203867467563534</v>
+        <v>0.4321479629608139</v>
       </c>
       <c r="D163" t="s">
         <v>7</v>
@@ -7114,7 +7114,7 @@
         <v>10</v>
       </c>
       <c r="C164">
-        <v>0.3667776162333315</v>
+        <v>0.3450313866048794</v>
       </c>
       <c r="D164" t="s">
         <v>7</v>
@@ -7131,7 +7131,7 @@
         <v>10</v>
       </c>
       <c r="C165">
-        <v>0.4139465031853306</v>
+        <v>0.3735955843381027</v>
       </c>
       <c r="D165" t="s">
         <v>7</v>
@@ -7148,7 +7148,7 @@
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.3506003402743979</v>
+        <v>0.3185695690950144</v>
       </c>
       <c r="D166" t="s">
         <v>7</v>
@@ -7165,7 +7165,7 @@
         <v>6</v>
       </c>
       <c r="C167">
-        <v>0.4058958770000176</v>
+        <v>0.3648955710755552</v>
       </c>
       <c r="D167" t="s">
         <v>7</v>
@@ -7182,7 +7182,7 @@
         <v>6</v>
       </c>
       <c r="C168">
-        <v>0.6715046973729646</v>
+        <v>0.608389445340746</v>
       </c>
       <c r="D168" t="s">
         <v>7</v>
@@ -7199,7 +7199,7 @@
         <v>44</v>
       </c>
       <c r="C169">
-        <v>0.3702239800288876</v>
+        <v>0.3349556627812932</v>
       </c>
       <c r="D169" t="s">
         <v>7</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="C170">
-        <v>0.3972913174396606</v>
+        <v>0.3626366275784824</v>
       </c>
       <c r="D170" t="s">
         <v>7</v>
@@ -7230,10 +7230,10 @@
         <v>350</v>
       </c>
       <c r="B171" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C171">
-        <v>0.2475211494785128</v>
+        <v>0.2426223168983042</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -7250,7 +7250,7 @@
         <v>10</v>
       </c>
       <c r="C172">
-        <v>0.4288610253432952</v>
+        <v>0.3973052957903009</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -7267,7 +7267,7 @@
         <v>10</v>
       </c>
       <c r="C173">
-        <v>0.3755574987664979</v>
+        <v>0.3337212926032734</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -7284,7 +7284,7 @@
         <v>6</v>
       </c>
       <c r="C174">
-        <v>0.3683316308674465</v>
+        <v>0.3459668997050944</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -7298,10 +7298,10 @@
         <v>358</v>
       </c>
       <c r="B175" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C175">
-        <v>0.2831605654933195</v>
+        <v>0.2583592742422158</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -7318,7 +7318,7 @@
         <v>6</v>
       </c>
       <c r="C176">
-        <v>0.4560397105674348</v>
+        <v>0.4138497412097857</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -7335,7 +7335,7 @@
         <v>6</v>
       </c>
       <c r="C177">
-        <v>0.5573536239509664</v>
+        <v>0.496852884292053</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -7349,10 +7349,10 @@
         <v>364</v>
       </c>
       <c r="B178" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C178">
-        <v>0.5194681803627568</v>
+        <v>0.4199717548739216</v>
       </c>
       <c r="D178" t="s">
         <v>7</v>
@@ -7366,10 +7366,10 @@
         <v>366</v>
       </c>
       <c r="B179" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C179">
-        <v>0.3712476881947506</v>
+        <v>0.3244161361069016</v>
       </c>
       <c r="D179" t="s">
         <v>7</v>
@@ -7386,7 +7386,7 @@
         <v>44</v>
       </c>
       <c r="C180">
-        <v>0.4109011642758376</v>
+        <v>0.3482466822046847</v>
       </c>
       <c r="D180" t="s">
         <v>7</v>
@@ -7403,7 +7403,7 @@
         <v>6</v>
       </c>
       <c r="C181">
-        <v>0.3670974558286617</v>
+        <v>0.3460692442499865</v>
       </c>
       <c r="D181" t="s">
         <v>7</v>
@@ -7420,7 +7420,7 @@
         <v>10</v>
       </c>
       <c r="C182">
-        <v>0.3495164259588765</v>
+        <v>0.3132315376553218</v>
       </c>
       <c r="D182" t="s">
         <v>7</v>
@@ -7437,7 +7437,7 @@
         <v>6</v>
       </c>
       <c r="C183">
-        <v>0.3296932462685482</v>
+        <v>0.3040972106267225</v>
       </c>
       <c r="D183" t="s">
         <v>7</v>
@@ -7454,7 +7454,7 @@
         <v>6</v>
       </c>
       <c r="C184">
-        <v>0.386369315062284</v>
+        <v>0.3565657922091811</v>
       </c>
       <c r="D184" t="s">
         <v>7</v>
@@ -7471,7 +7471,7 @@
         <v>10</v>
       </c>
       <c r="C185">
-        <v>0.3660065707384407</v>
+        <v>0.3443064569800522</v>
       </c>
       <c r="D185" t="s">
         <v>7</v>
@@ -7488,7 +7488,7 @@
         <v>44</v>
       </c>
       <c r="C186">
-        <v>0.4923662700232725</v>
+        <v>0.4169505391859726</v>
       </c>
       <c r="D186" t="s">
         <v>7</v>
@@ -7502,10 +7502,10 @@
         <v>382</v>
       </c>
       <c r="B187" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C187">
-        <v>0.2536763380919695</v>
+        <v>0.243675306287117</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -7522,7 +7522,7 @@
         <v>10</v>
       </c>
       <c r="C188">
-        <v>0.5294364134388408</v>
+        <v>0.4708528103990346</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -7539,7 +7539,7 @@
         <v>6</v>
       </c>
       <c r="C189">
-        <v>0.366259116385814</v>
+        <v>0.3476045711140358</v>
       </c>
       <c r="D189" t="s">
         <v>7</v>
@@ -7556,7 +7556,7 @@
         <v>6</v>
       </c>
       <c r="C190">
-        <v>0.291764654005967</v>
+        <v>0.2831611149174091</v>
       </c>
       <c r="D190" t="s">
         <v>7</v>
@@ -7573,7 +7573,7 @@
         <v>10</v>
       </c>
       <c r="C191">
-        <v>0.4079111204088721</v>
+        <v>0.3569040179479273</v>
       </c>
       <c r="D191" t="s">
         <v>7</v>
@@ -7587,10 +7587,10 @@
         <v>392</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C192">
-        <v>0.4544734518780091</v>
+        <v>0.3831267463512072</v>
       </c>
       <c r="D192" t="s">
         <v>7</v>
@@ -7604,10 +7604,10 @@
         <v>394</v>
       </c>
       <c r="B193" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C193">
-        <v>0.5533290782434391</v>
+        <v>0.4381324584970104</v>
       </c>
       <c r="D193" t="s">
         <v>7</v>
@@ -7624,7 +7624,7 @@
         <v>6</v>
       </c>
       <c r="C194">
-        <v>0.4113183443586989</v>
+        <v>0.3913708542743513</v>
       </c>
       <c r="D194" t="s">
         <v>7</v>
@@ -7638,10 +7638,10 @@
         <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="C195">
-        <v>0.3818964047976229</v>
+        <v>0.3414772854181009</v>
       </c>
       <c r="D195" t="s">
         <v>7</v>
@@ -7658,7 +7658,7 @@
         <v>6</v>
       </c>
       <c r="C196">
-        <v>0.3701437612679536</v>
+        <v>0.3530687492595427</v>
       </c>
       <c r="D196" t="s">
         <v>7</v>
@@ -7675,7 +7675,7 @@
         <v>10</v>
       </c>
       <c r="C197">
-        <v>0.393929099736922</v>
+        <v>0.3453343088104758</v>
       </c>
       <c r="D197" t="s">
         <v>7</v>
@@ -7692,7 +7692,7 @@
         <v>6</v>
       </c>
       <c r="C198">
-        <v>0.5602173339661916</v>
+        <v>0.5535891600789051</v>
       </c>
       <c r="D198" t="s">
         <v>7</v>
@@ -7709,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="C199">
-        <v>0.6411268072524422</v>
+        <v>0.6400813650683816</v>
       </c>
       <c r="D199" t="s">
         <v>7</v>
@@ -7723,10 +7723,10 @@
         <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C200">
-        <v>0.3979679759681108</v>
+        <v>0.3538732959175233</v>
       </c>
       <c r="D200" t="s">
         <v>7</v>
@@ -7740,10 +7740,10 @@
         <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C201">
-        <v>0.3594862802886198</v>
+        <v>0.3085313685267074</v>
       </c>
       <c r="D201" t="s">
         <v>7</v>
@@ -7760,7 +7760,7 @@
         <v>10</v>
       </c>
       <c r="C202">
-        <v>0.4859608615094153</v>
+        <v>0.4148594344770127</v>
       </c>
       <c r="D202" t="s">
         <v>7</v>
@@ -7777,7 +7777,7 @@
         <v>6</v>
       </c>
       <c r="C203">
-        <v>0.5885057356158224</v>
+        <v>0.5385071889564725</v>
       </c>
       <c r="D203" t="s">
         <v>7</v>
@@ -7794,7 +7794,7 @@
         <v>6</v>
       </c>
       <c r="C204">
-        <v>0.514990341614148</v>
+        <v>0.4602013064363989</v>
       </c>
       <c r="D204" t="s">
         <v>7</v>
@@ -7811,7 +7811,7 @@
         <v>10</v>
       </c>
       <c r="C205">
-        <v>0.5606446459729729</v>
+        <v>0.4760716769014413</v>
       </c>
       <c r="D205" t="s">
         <v>7</v>
@@ -7825,10 +7825,10 @@
         <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C206">
-        <v>0.4321531024040908</v>
+        <v>0.3648753236827028</v>
       </c>
       <c r="D206" t="s">
         <v>7</v>
@@ -7845,7 +7845,7 @@
         <v>44</v>
       </c>
       <c r="C207">
-        <v>0.6457245344853824</v>
+        <v>0.5423043687076559</v>
       </c>
       <c r="D207" t="s">
         <v>7</v>
@@ -7862,7 +7862,7 @@
         <v>44</v>
       </c>
       <c r="C208">
-        <v>0.4232843147828974</v>
+        <v>0.3869702943675387</v>
       </c>
       <c r="D208" t="s">
         <v>7</v>
@@ -7879,7 +7879,7 @@
         <v>10</v>
       </c>
       <c r="C209">
-        <v>0.6224917444577071</v>
+        <v>0.5316373269717012</v>
       </c>
       <c r="D209" t="s">
         <v>7</v>
@@ -7896,7 +7896,7 @@
         <v>6</v>
       </c>
       <c r="C210">
-        <v>0.4752262753732715</v>
+        <v>0.4283484090707507</v>
       </c>
       <c r="D210" t="s">
         <v>7</v>
@@ -7910,10 +7910,10 @@
         <v>430</v>
       </c>
       <c r="B211" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C211">
-        <v>0.5304033662789597</v>
+        <v>0.4287093133364632</v>
       </c>
       <c r="D211" t="s">
         <v>7</v>
@@ -7930,7 +7930,7 @@
         <v>10</v>
       </c>
       <c r="C212">
-        <v>0.3067988768440789</v>
+        <v>0.2911380717589603</v>
       </c>
       <c r="D212" t="s">
         <v>7</v>
@@ -7947,7 +7947,7 @@
         <v>10</v>
       </c>
       <c r="C213">
-        <v>0.3282363287816552</v>
+        <v>0.3078282914859491</v>
       </c>
       <c r="D213" t="s">
         <v>7</v>
@@ -7961,10 +7961,10 @@
         <v>436</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C214">
-        <v>0.4289770989116624</v>
+        <v>0.3774898369028911</v>
       </c>
       <c r="D214" t="s">
         <v>7</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="C215">
-        <v>0.4975163613379778</v>
+        <v>0.445104985915494</v>
       </c>
       <c r="D215" t="s">
         <v>7</v>
@@ -7995,10 +7995,10 @@
         <v>440</v>
       </c>
       <c r="B216" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C216">
-        <v>0.343019909018292</v>
+        <v>0.3095362697520602</v>
       </c>
       <c r="D216" t="s">
         <v>7</v>
@@ -8012,10 +8012,10 @@
         <v>442</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C217">
-        <v>0.4059885729174929</v>
+        <v>0.349603453768444</v>
       </c>
       <c r="D217" t="s">
         <v>7</v>
@@ -8032,7 +8032,7 @@
         <v>6</v>
       </c>
       <c r="C218">
-        <v>0.3748648132808117</v>
+        <v>0.3551829515345259</v>
       </c>
       <c r="D218" t="s">
         <v>7</v>
@@ -8049,7 +8049,7 @@
         <v>44</v>
       </c>
       <c r="C219">
-        <v>0.5699754935105352</v>
+        <v>0.4816158606460234</v>
       </c>
       <c r="D219" t="s">
         <v>7</v>
@@ -8066,7 +8066,7 @@
         <v>10</v>
       </c>
       <c r="C220">
-        <v>0.2633455436902431</v>
+        <v>0.2537531484533139</v>
       </c>
       <c r="D220" t="s">
         <v>7</v>
@@ -8080,10 +8080,10 @@
         <v>450</v>
       </c>
       <c r="B221" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C221">
-        <v>0.4065939912058751</v>
+        <v>0.348115699372351</v>
       </c>
       <c r="D221" t="s">
         <v>7</v>
@@ -8100,7 +8100,7 @@
         <v>6</v>
       </c>
       <c r="C222">
-        <v>0.3266754416488461</v>
+        <v>0.3234643015592814</v>
       </c>
       <c r="D222" t="s">
         <v>7</v>
@@ -8117,7 +8117,7 @@
         <v>10</v>
       </c>
       <c r="C223">
-        <v>0.5846821171643726</v>
+        <v>0.5141975964947965</v>
       </c>
       <c r="D223" t="s">
         <v>7</v>
@@ -8134,7 +8134,7 @@
         <v>10</v>
       </c>
       <c r="C224">
-        <v>0.3873435066455119</v>
+        <v>0.3423804691986876</v>
       </c>
       <c r="D224" t="s">
         <v>7</v>
@@ -8148,10 +8148,10 @@
         <v>458</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C225">
-        <v>0.3865793400335491</v>
+        <v>0.3426507088190909</v>
       </c>
       <c r="D225" t="s">
         <v>7</v>
@@ -8168,7 +8168,7 @@
         <v>6</v>
       </c>
       <c r="C226">
-        <v>0.5495094733382948</v>
+        <v>0.489644471536081</v>
       </c>
       <c r="D226" t="s">
         <v>7</v>
@@ -8185,7 +8185,7 @@
         <v>10</v>
       </c>
       <c r="C227">
-        <v>0.4096625199966866</v>
+        <v>0.3595648647682225</v>
       </c>
       <c r="D227" t="s">
         <v>7</v>
@@ -8202,7 +8202,7 @@
         <v>6</v>
       </c>
       <c r="C228">
-        <v>0.543159346297543</v>
+        <v>0.4853917859579996</v>
       </c>
       <c r="D228" t="s">
         <v>7</v>
@@ -8219,7 +8219,7 @@
         <v>6</v>
       </c>
       <c r="C229">
-        <v>0.5919890348882643</v>
+        <v>0.5593287162295242</v>
       </c>
       <c r="D229" t="s">
         <v>7</v>
@@ -8236,7 +8236,7 @@
         <v>44</v>
       </c>
       <c r="C230">
-        <v>0.3888956813624935</v>
+        <v>0.3529130621713715</v>
       </c>
       <c r="D230" t="s">
         <v>7</v>
@@ -8250,10 +8250,10 @@
         <v>470</v>
       </c>
       <c r="B231" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C231">
-        <v>0.3103171938753221</v>
+        <v>0.3098409737604076</v>
       </c>
       <c r="D231" t="s">
         <v>7</v>
@@ -8270,7 +8270,7 @@
         <v>6</v>
       </c>
       <c r="C232">
-        <v>0.6602494169705571</v>
+        <v>0.6028630092113024</v>
       </c>
       <c r="D232" t="s">
         <v>7</v>
@@ -8287,7 +8287,7 @@
         <v>44</v>
       </c>
       <c r="C233">
-        <v>0.4720639065520193</v>
+        <v>0.4099747576510495</v>
       </c>
       <c r="D233" t="s">
         <v>7</v>
@@ -8304,7 +8304,7 @@
         <v>6</v>
       </c>
       <c r="C234">
-        <v>0.4807743771679945</v>
+        <v>0.4291974318453313</v>
       </c>
       <c r="D234" t="s">
         <v>7</v>
@@ -8321,7 +8321,7 @@
         <v>6</v>
       </c>
       <c r="C235">
-        <v>0.5334318454755187</v>
+        <v>0.5029494043588981</v>
       </c>
       <c r="D235" t="s">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>6</v>
       </c>
       <c r="C236">
-        <v>0.2849520656731544</v>
+        <v>0.275526875044399</v>
       </c>
       <c r="D236" t="s">
         <v>7</v>
@@ -8355,7 +8355,7 @@
         <v>10</v>
       </c>
       <c r="C237">
-        <v>0.3866099720422553</v>
+        <v>0.3464677941609197</v>
       </c>
       <c r="D237" t="s">
         <v>7</v>
@@ -8372,7 +8372,7 @@
         <v>6</v>
       </c>
       <c r="C238">
-        <v>0.4276325707467894</v>
+        <v>0.3756151404680562</v>
       </c>
       <c r="D238" t="s">
         <v>7</v>
@@ -8389,7 +8389,7 @@
         <v>6</v>
       </c>
       <c r="C239">
-        <v>0.4415017158236738</v>
+        <v>0.4033936116252076</v>
       </c>
       <c r="D239" t="s">
         <v>7</v>
@@ -8406,7 +8406,7 @@
         <v>226</v>
       </c>
       <c r="C240">
-        <v>0.3593678350003399</v>
+        <v>0.340282483825649</v>
       </c>
       <c r="D240" t="s">
         <v>7</v>
@@ -8420,10 +8420,10 @@
         <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="C241">
-        <v>0.2416232088761105</v>
+        <v>0.2313768648010962</v>
       </c>
       <c r="D241" t="s">
         <v>7</v>
@@ -8437,10 +8437,10 @@
         <v>492</v>
       </c>
       <c r="B242" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C242">
-        <v>0.3206150012883556</v>
+        <v>0.307585130845003</v>
       </c>
       <c r="D242" t="s">
         <v>7</v>
@@ -8454,10 +8454,10 @@
         <v>494</v>
       </c>
       <c r="B243" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C243">
-        <v>0.590349121725085</v>
+        <v>0.4678081993648137</v>
       </c>
       <c r="D243" t="s">
         <v>7</v>
@@ -8474,7 +8474,7 @@
         <v>226</v>
       </c>
       <c r="C244">
-        <v>0.3935414356253109</v>
+        <v>0.3727355055526714</v>
       </c>
       <c r="D244" t="s">
         <v>7</v>
@@ -8491,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="C245">
-        <v>0.6812519073197484</v>
+        <v>0.635607047440584</v>
       </c>
       <c r="D245" t="s">
         <v>7</v>
@@ -8508,7 +8508,7 @@
         <v>6</v>
       </c>
       <c r="C246">
-        <v>0.4841341829048033</v>
+        <v>0.439230013082239</v>
       </c>
       <c r="D246" t="s">
         <v>7</v>
@@ -8525,7 +8525,7 @@
         <v>6</v>
       </c>
       <c r="C247">
-        <v>0.471992918627274</v>
+        <v>0.4334081874871188</v>
       </c>
       <c r="D247" t="s">
         <v>7</v>
@@ -8542,7 +8542,7 @@
         <v>10</v>
       </c>
       <c r="C248">
-        <v>0.4432880242453651</v>
+        <v>0.3790190802346144</v>
       </c>
       <c r="D248" t="s">
         <v>7</v>
@@ -8559,7 +8559,7 @@
         <v>6</v>
       </c>
       <c r="C249">
-        <v>0.4652247636394714</v>
+        <v>0.4161238340246184</v>
       </c>
       <c r="D249" t="s">
         <v>7</v>
@@ -8573,10 +8573,10 @@
         <v>508</v>
       </c>
       <c r="B250" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C250">
-        <v>0.3066553452738644</v>
+        <v>0.2838030769146059</v>
       </c>
       <c r="D250" t="s">
         <v>7</v>
@@ -8593,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="C251">
-        <v>0.504985700716017</v>
+        <v>0.4275642935296419</v>
       </c>
       <c r="D251" t="s">
         <v>7</v>
@@ -8610,7 +8610,7 @@
         <v>6</v>
       </c>
       <c r="C252">
-        <v>0.493634676836079</v>
+        <v>0.4380686917007066</v>
       </c>
       <c r="D252" t="s">
         <v>7</v>
@@ -8627,7 +8627,7 @@
         <v>6</v>
       </c>
       <c r="C253">
-        <v>0.4286594418646705</v>
+        <v>0.3852719491279851</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
@@ -8644,7 +8644,7 @@
         <v>6</v>
       </c>
       <c r="C254">
-        <v>0.5224333949561931</v>
+        <v>0.4878042225567453</v>
       </c>
       <c r="D254" t="s">
         <v>7</v>
@@ -8658,10 +8658,10 @@
         <v>518</v>
       </c>
       <c r="B255" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C255">
-        <v>0.4546943060107533</v>
+        <v>0.3974517232308627</v>
       </c>
       <c r="D255" t="s">
         <v>7</v>
@@ -8678,7 +8678,7 @@
         <v>6</v>
       </c>
       <c r="C256">
-        <v>0.6655484318242186</v>
+        <v>0.6064807253707537</v>
       </c>
       <c r="D256" t="s">
         <v>7</v>
@@ -8695,7 +8695,7 @@
         <v>6</v>
       </c>
       <c r="C257">
-        <v>0.4893867174435239</v>
+        <v>0.4350254005821838</v>
       </c>
       <c r="D257" t="s">
         <v>7</v>
@@ -8712,7 +8712,7 @@
         <v>6</v>
       </c>
       <c r="C258">
-        <v>0.5402103190932995</v>
+        <v>0.5132340094732739</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
@@ -8726,10 +8726,10 @@
         <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C259">
-        <v>0.3148979787459722</v>
+        <v>0.2967374287909085</v>
       </c>
       <c r="D259" t="s">
         <v>7</v>
@@ -8746,7 +8746,7 @@
         <v>6</v>
       </c>
       <c r="C260">
-        <v>0.4855738878498426</v>
+        <v>0.4411839720023771</v>
       </c>
       <c r="D260" t="s">
         <v>7</v>
@@ -8763,7 +8763,7 @@
         <v>6</v>
       </c>
       <c r="C261">
-        <v>0.5205245710657485</v>
+        <v>0.4640648139244544</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="C262">
-        <v>0.4570219375315318</v>
+        <v>0.4204276485757729</v>
       </c>
       <c r="D262" t="s">
         <v>7</v>
@@ -8797,7 +8797,7 @@
         <v>6</v>
       </c>
       <c r="C263">
-        <v>0.4953872785709716</v>
+        <v>0.4492263454485866</v>
       </c>
       <c r="D263" t="s">
         <v>7</v>
@@ -8814,7 +8814,7 @@
         <v>6</v>
       </c>
       <c r="C264">
-        <v>0.4953034622354727</v>
+        <v>0.4498656551505588</v>
       </c>
       <c r="D264" t="s">
         <v>7</v>
@@ -8831,7 +8831,7 @@
         <v>6</v>
       </c>
       <c r="C265">
-        <v>0.3954076066997674</v>
+        <v>0.355960484105498</v>
       </c>
       <c r="D265" t="s">
         <v>7</v>
@@ -8848,7 +8848,7 @@
         <v>6</v>
       </c>
       <c r="C266">
-        <v>0.347149959750749</v>
+        <v>0.3111021609241122</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
@@ -8862,10 +8862,10 @@
         <v>542</v>
       </c>
       <c r="B267" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C267">
-        <v>0.3034906037621761</v>
+        <v>0.2821454041530078</v>
       </c>
       <c r="D267" t="s">
         <v>7</v>
@@ -8882,7 +8882,7 @@
         <v>6</v>
       </c>
       <c r="C268">
-        <v>0.4765174741092499</v>
+        <v>0.425541817059029</v>
       </c>
       <c r="D268" t="s">
         <v>7</v>
@@ -8899,7 +8899,7 @@
         <v>44</v>
       </c>
       <c r="C269">
-        <v>0.4109838559146343</v>
+        <v>0.3594451136168667</v>
       </c>
       <c r="D269" t="s">
         <v>7</v>
@@ -8916,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="C270">
-        <v>0.5733414035959792</v>
+        <v>0.5377586593457597</v>
       </c>
       <c r="D270" t="s">
         <v>7</v>
@@ -8933,7 +8933,7 @@
         <v>6</v>
       </c>
       <c r="C271">
-        <v>0.5819489533095727</v>
+        <v>0.5658193046438081</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
@@ -8950,7 +8950,7 @@
         <v>6</v>
       </c>
       <c r="C272">
-        <v>0.3956414237633554</v>
+        <v>0.3711272510551955</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="C273">
-        <v>0.5883161057218996</v>
+        <v>0.5235714598739777</v>
       </c>
       <c r="D273" t="s">
         <v>7</v>
@@ -8981,10 +8981,10 @@
         <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C274">
-        <v>0.3870232517150635</v>
+        <v>0.3411803778411628</v>
       </c>
       <c r="D274" t="s">
         <v>7</v>
@@ -9001,7 +9001,7 @@
         <v>10</v>
       </c>
       <c r="C275">
-        <v>0.276147618327698</v>
+        <v>0.2560433155876313</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
@@ -9018,7 +9018,7 @@
         <v>6</v>
       </c>
       <c r="C276">
-        <v>0.3700233458753696</v>
+        <v>0.3251049371351671</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -9032,10 +9032,10 @@
         <v>562</v>
       </c>
       <c r="B277" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C277">
-        <v>0.4425856406980055</v>
+        <v>0.3848219599105739</v>
       </c>
       <c r="D277" t="s">
         <v>7</v>
@@ -9052,7 +9052,7 @@
         <v>6</v>
       </c>
       <c r="C278">
-        <v>0.4501446650235367</v>
+        <v>0.4290576339528186</v>
       </c>
       <c r="D278" t="s">
         <v>7</v>
@@ -9069,7 +9069,7 @@
         <v>6</v>
       </c>
       <c r="C279">
-        <v>0.6172517291567656</v>
+        <v>0.5713144005401215</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -9086,7 +9086,7 @@
         <v>6</v>
       </c>
       <c r="C280">
-        <v>0.559374990841964</v>
+        <v>0.4865459957212432</v>
       </c>
       <c r="D280" t="s">
         <v>7</v>
@@ -9103,7 +9103,7 @@
         <v>6</v>
       </c>
       <c r="C281">
-        <v>0.4501158723344392</v>
+        <v>0.4092057979265529</v>
       </c>
       <c r="D281" t="s">
         <v>7</v>
@@ -9117,10 +9117,10 @@
         <v>572</v>
       </c>
       <c r="B282" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C282">
-        <v>0.4871860668534409</v>
+        <v>0.4053577107267031</v>
       </c>
       <c r="D282" t="s">
         <v>7</v>
@@ -9137,7 +9137,7 @@
         <v>6</v>
       </c>
       <c r="C283">
-        <v>0.3996672548879696</v>
+        <v>0.3734951180800323</v>
       </c>
       <c r="D283" t="s">
         <v>7</v>
@@ -9154,7 +9154,7 @@
         <v>6</v>
       </c>
       <c r="C284">
-        <v>0.3313043691007249</v>
+        <v>0.3123080489705343</v>
       </c>
       <c r="D284" t="s">
         <v>7</v>
@@ -9171,7 +9171,7 @@
         <v>10</v>
       </c>
       <c r="C285">
-        <v>0.2685325952481217</v>
+        <v>0.2546950411937332</v>
       </c>
       <c r="D285" t="s">
         <v>7</v>
@@ -9188,7 +9188,7 @@
         <v>6</v>
       </c>
       <c r="C286">
-        <v>0.3023755498559832</v>
+        <v>0.2911982615506313</v>
       </c>
       <c r="D286" t="s">
         <v>7</v>
@@ -9205,7 +9205,7 @@
         <v>44</v>
       </c>
       <c r="C287">
-        <v>0.5402606774044334</v>
+        <v>0.4628158316658513</v>
       </c>
       <c r="D287" t="s">
         <v>7</v>
@@ -9219,10 +9219,10 @@
         <v>584</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C288">
-        <v>0.2646625592040101</v>
+        <v>0.2544898575622361</v>
       </c>
       <c r="D288" t="s">
         <v>7</v>
@@ -9236,10 +9236,10 @@
         <v>586</v>
       </c>
       <c r="B289" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C289">
-        <v>0.3979777332879673</v>
+        <v>0.3476148675840269</v>
       </c>
       <c r="D289" t="s">
         <v>7</v>
@@ -9253,10 +9253,10 @@
         <v>588</v>
       </c>
       <c r="B290" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C290">
-        <v>0.3257138982138363</v>
+        <v>0.2947965291919982</v>
       </c>
       <c r="D290" t="s">
         <v>7</v>
@@ -9273,7 +9273,7 @@
         <v>6</v>
       </c>
       <c r="C291">
-        <v>0.4350455809450506</v>
+        <v>0.4268898665383072</v>
       </c>
       <c r="D291" t="s">
         <v>7</v>
@@ -9287,10 +9287,10 @@
         <v>592</v>
       </c>
       <c r="B292" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C292">
-        <v>0.5555774605078838</v>
+        <v>0.4713913979534461</v>
       </c>
       <c r="D292" t="s">
         <v>7</v>
@@ -9307,7 +9307,7 @@
         <v>6</v>
       </c>
       <c r="C293">
-        <v>0.6638494771105886</v>
+        <v>0.6326729187180524</v>
       </c>
       <c r="D293" t="s">
         <v>7</v>
@@ -9321,10 +9321,10 @@
         <v>596</v>
       </c>
       <c r="B294" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C294">
-        <v>0.4264508034708075</v>
+        <v>0.3663936351258769</v>
       </c>
       <c r="D294" t="s">
         <v>7</v>
@@ -9341,7 +9341,7 @@
         <v>10</v>
       </c>
       <c r="C295">
-        <v>0.3938178430039411</v>
+        <v>0.3642841019876971</v>
       </c>
       <c r="D295" t="s">
         <v>7</v>
@@ -9355,10 +9355,10 @@
         <v>600</v>
       </c>
       <c r="B296" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C296">
-        <v>0.3307264875601038</v>
+        <v>0.300316462254311</v>
       </c>
       <c r="D296" t="s">
         <v>7</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="C297">
-        <v>0.5329824183844382</v>
+        <v>0.4631053192862904</v>
       </c>
       <c r="D297" t="s">
         <v>7</v>
@@ -9392,7 +9392,7 @@
         <v>10</v>
       </c>
       <c r="C298">
-        <v>0.4520976285773808</v>
+        <v>0.3979956944126165</v>
       </c>
       <c r="D298" t="s">
         <v>7</v>
@@ -9409,7 +9409,7 @@
         <v>44</v>
       </c>
       <c r="C299">
-        <v>0.2946657986820778</v>
+        <v>0.2710327401475281</v>
       </c>
       <c r="D299" t="s">
         <v>7</v>
@@ -9426,7 +9426,7 @@
         <v>10</v>
       </c>
       <c r="C300">
-        <v>0.4020209455314553</v>
+        <v>0.3603132966358548</v>
       </c>
       <c r="D300" t="s">
         <v>7</v>
@@ -9443,7 +9443,7 @@
         <v>6</v>
       </c>
       <c r="C301">
-        <v>0.3993576722841826</v>
+        <v>0.3655360038704389</v>
       </c>
       <c r="D301" t="s">
         <v>7</v>
@@ -9460,7 +9460,7 @@
         <v>44</v>
       </c>
       <c r="C302">
-        <v>0.6260995042798879</v>
+        <v>0.5192880017984473</v>
       </c>
       <c r="D302" t="s">
         <v>7</v>
@@ -9477,7 +9477,7 @@
         <v>10</v>
       </c>
       <c r="C303">
-        <v>0.3445595994125312</v>
+        <v>0.3231192130515977</v>
       </c>
       <c r="D303" t="s">
         <v>7</v>
@@ -9494,7 +9494,7 @@
         <v>10</v>
       </c>
       <c r="C304">
-        <v>0.3334766024271276</v>
+        <v>0.3151575680948271</v>
       </c>
       <c r="D304" t="s">
         <v>7</v>
@@ -9511,7 +9511,7 @@
         <v>44</v>
       </c>
       <c r="C305">
-        <v>0.5268266027281194</v>
+        <v>0.435464343366795</v>
       </c>
       <c r="D305" t="s">
         <v>7</v>
@@ -9525,10 +9525,10 @@
         <v>620</v>
       </c>
       <c r="B306" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C306">
-        <v>0.4355333750783104</v>
+        <v>0.3687143774011451</v>
       </c>
       <c r="D306" t="s">
         <v>7</v>
@@ -9545,7 +9545,7 @@
         <v>6</v>
       </c>
       <c r="C307">
-        <v>0.5082162097556689</v>
+        <v>0.4691417446979356</v>
       </c>
       <c r="D307" t="s">
         <v>7</v>
@@ -9562,7 +9562,7 @@
         <v>6</v>
       </c>
       <c r="C308">
-        <v>0.4436456684074341</v>
+        <v>0.4089673132346053</v>
       </c>
       <c r="D308" t="s">
         <v>7</v>
@@ -9579,7 +9579,7 @@
         <v>6</v>
       </c>
       <c r="C309">
-        <v>0.3071007711989771</v>
+        <v>0.2908834174621316</v>
       </c>
       <c r="D309" t="s">
         <v>7</v>
@@ -9596,7 +9596,7 @@
         <v>6</v>
       </c>
       <c r="C310">
-        <v>0.444286373514984</v>
+        <v>0.401762367364398</v>
       </c>
       <c r="D310" t="s">
         <v>7</v>
@@ -9610,10 +9610,10 @@
         <v>630</v>
       </c>
       <c r="B311" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C311">
-        <v>0.3946737012853936</v>
+        <v>0.349148740016899</v>
       </c>
       <c r="D311" t="s">
         <v>7</v>
@@ -9630,7 +9630,7 @@
         <v>10</v>
       </c>
       <c r="C312">
-        <v>0.3056486793017745</v>
+        <v>0.2794963669774947</v>
       </c>
       <c r="D312" t="s">
         <v>7</v>
@@ -9647,7 +9647,7 @@
         <v>44</v>
       </c>
       <c r="C313">
-        <v>0.3455016002167963</v>
+        <v>0.3084950069820853</v>
       </c>
       <c r="D313" t="s">
         <v>7</v>
@@ -9664,7 +9664,7 @@
         <v>10</v>
       </c>
       <c r="C314">
-        <v>0.3709597591379819</v>
+        <v>0.3394232163684426</v>
       </c>
       <c r="D314" t="s">
         <v>7</v>
@@ -9681,7 +9681,7 @@
         <v>44</v>
       </c>
       <c r="C315">
-        <v>0.5762635139434371</v>
+        <v>0.4766524267609801</v>
       </c>
       <c r="D315" t="s">
         <v>7</v>
@@ -9698,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C316">
-        <v>0.4500328376657746</v>
+        <v>0.4007391367597249</v>
       </c>
       <c r="D316" t="s">
         <v>7</v>
@@ -9715,7 +9715,7 @@
         <v>6</v>
       </c>
       <c r="C317">
-        <v>0.5809218296654468</v>
+        <v>0.5273529554397791</v>
       </c>
       <c r="D317" t="s">
         <v>7</v>
@@ -9732,7 +9732,7 @@
         <v>6</v>
       </c>
       <c r="C318">
-        <v>0.6111299901763236</v>
+        <v>0.5478588242795267</v>
       </c>
       <c r="D318" t="s">
         <v>7</v>
@@ -9749,7 +9749,7 @@
         <v>6</v>
       </c>
       <c r="C319">
-        <v>0.3986324333193592</v>
+        <v>0.3609183672334247</v>
       </c>
       <c r="D319" t="s">
         <v>7</v>
@@ -9763,10 +9763,10 @@
         <v>648</v>
       </c>
       <c r="B320" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C320">
-        <v>0.3003941284664995</v>
+        <v>0.2763711169031227</v>
       </c>
       <c r="D320" t="s">
         <v>7</v>
@@ -9783,7 +9783,7 @@
         <v>6</v>
       </c>
       <c r="C321">
-        <v>0.3775111930003133</v>
+        <v>0.3554978066794928</v>
       </c>
       <c r="D321" t="s">
         <v>7</v>
@@ -9800,7 +9800,7 @@
         <v>6</v>
       </c>
       <c r="C322">
-        <v>0.4022307914971617</v>
+        <v>0.3736340396195296</v>
       </c>
       <c r="D322" t="s">
         <v>7</v>
@@ -9817,7 +9817,7 @@
         <v>10</v>
       </c>
       <c r="C323">
-        <v>0.4475370908943836</v>
+        <v>0.3881683169708585</v>
       </c>
       <c r="D323" t="s">
         <v>7</v>
@@ -9834,7 +9834,7 @@
         <v>44</v>
       </c>
       <c r="C324">
-        <v>0.4330236076280478</v>
+        <v>0.3699842598633333</v>
       </c>
       <c r="D324" t="s">
         <v>7</v>
@@ -9851,7 +9851,7 @@
         <v>10</v>
       </c>
       <c r="C325">
-        <v>0.2654002482317769</v>
+        <v>0.2492254884839616</v>
       </c>
       <c r="D325" t="s">
         <v>7</v>
@@ -9865,10 +9865,10 @@
         <v>660</v>
       </c>
       <c r="B326" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C326">
-        <v>0.3841969017130468</v>
+        <v>0.3537392406200979</v>
       </c>
       <c r="D326" t="s">
         <v>7</v>
@@ -9885,7 +9885,7 @@
         <v>44</v>
       </c>
       <c r="C327">
-        <v>0.3672088522889846</v>
+        <v>0.3295765326542938</v>
       </c>
       <c r="D327" t="s">
         <v>7</v>
@@ -9899,10 +9899,10 @@
         <v>664</v>
       </c>
       <c r="B328" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C328">
-        <v>0.3065152119653884</v>
+        <v>0.276306236467173</v>
       </c>
       <c r="D328" t="s">
         <v>7</v>
@@ -9919,7 +9919,7 @@
         <v>10</v>
       </c>
       <c r="C329">
-        <v>0.361117062120934</v>
+        <v>0.3189488321832795</v>
       </c>
       <c r="D329" t="s">
         <v>7</v>
@@ -9933,10 +9933,10 @@
         <v>668</v>
       </c>
       <c r="B330" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C330">
-        <v>0.3179824306503061</v>
+        <v>0.3045827000715247</v>
       </c>
       <c r="D330" t="s">
         <v>7</v>
@@ -9953,7 +9953,7 @@
         <v>10</v>
       </c>
       <c r="C331">
-        <v>0.4341290661402167</v>
+        <v>0.4036025257709573</v>
       </c>
       <c r="D331" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
         <v>10</v>
       </c>
       <c r="C332">
-        <v>0.4227280273905592</v>
+        <v>0.3658271181230813</v>
       </c>
       <c r="D332" t="s">
         <v>7</v>
@@ -9987,7 +9987,7 @@
         <v>6</v>
       </c>
       <c r="C333">
-        <v>0.5393731395075825</v>
+        <v>0.480780459616064</v>
       </c>
       <c r="D333" t="s">
         <v>7</v>
@@ -10004,7 +10004,7 @@
         <v>10</v>
       </c>
       <c r="C334">
-        <v>0.3015225438733306</v>
+        <v>0.2854769243739197</v>
       </c>
       <c r="D334" t="s">
         <v>7</v>
@@ -10018,10 +10018,10 @@
         <v>678</v>
       </c>
       <c r="B335" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C335">
-        <v>0.3568256808685825</v>
+        <v>0.3258617055487849</v>
       </c>
       <c r="D335" t="s">
         <v>7</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="C336">
-        <v>0.3280331998069908</v>
+        <v>0.3105931123336523</v>
       </c>
       <c r="D336" t="s">
         <v>7</v>
@@ -10055,7 +10055,7 @@
         <v>44</v>
       </c>
       <c r="C337">
-        <v>0.539270837835129</v>
+        <v>0.4489427609966606</v>
       </c>
       <c r="D337" t="s">
         <v>7</v>
@@ -10072,7 +10072,7 @@
         <v>10</v>
       </c>
       <c r="C338">
-        <v>0.3286211366577315</v>
+        <v>0.3017872060013799</v>
       </c>
       <c r="D338" t="s">
         <v>7</v>
@@ -10086,10 +10086,10 @@
         <v>686</v>
       </c>
       <c r="B339" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C339">
-        <v>0.5112997827743406</v>
+        <v>0.4322036681461732</v>
       </c>
       <c r="D339" t="s">
         <v>7</v>
@@ -10103,10 +10103,10 @@
         <v>688</v>
       </c>
       <c r="B340" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C340">
-        <v>0.3424027020209376</v>
+        <v>0.3056609275303168</v>
       </c>
       <c r="D340" t="s">
         <v>7</v>
@@ -10123,7 +10123,7 @@
         <v>6</v>
       </c>
       <c r="C341">
-        <v>0.3278080278950797</v>
+        <v>0.3059172963428671</v>
       </c>
       <c r="D341" t="s">
         <v>7</v>
@@ -10140,7 +10140,7 @@
         <v>10</v>
       </c>
       <c r="C342">
-        <v>0.2859927362249052</v>
+        <v>0.2684881749951602</v>
       </c>
       <c r="D342" t="s">
         <v>7</v>
@@ -10157,7 +10157,7 @@
         <v>10</v>
       </c>
       <c r="C343">
-        <v>0.4764177862651749</v>
+        <v>0.414799993250563</v>
       </c>
       <c r="D343" t="s">
         <v>7</v>
@@ -10171,10 +10171,10 @@
         <v>696</v>
       </c>
       <c r="B344" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C344">
-        <v>0.3197691413976114</v>
+        <v>0.2854383117401438</v>
       </c>
       <c r="D344" t="s">
         <v>7</v>
@@ -10191,7 +10191,7 @@
         <v>6</v>
       </c>
       <c r="C345">
-        <v>0.4082820347836064</v>
+        <v>0.3752619304581581</v>
       </c>
       <c r="D345" t="s">
         <v>7</v>
@@ -10208,7 +10208,7 @@
         <v>10</v>
       </c>
       <c r="C346">
-        <v>0.3753900425766254</v>
+        <v>0.3457924988882654</v>
       </c>
       <c r="D346" t="s">
         <v>7</v>
@@ -10222,10 +10222,10 @@
         <v>702</v>
       </c>
       <c r="B347" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C347">
-        <v>0.35171916889072</v>
+        <v>0.3148709022324958</v>
       </c>
       <c r="D347" t="s">
         <v>7</v>
@@ -10242,7 +10242,7 @@
         <v>6</v>
       </c>
       <c r="C348">
-        <v>0.3561779101284386</v>
+        <v>0.3261972194076635</v>
       </c>
       <c r="D348" t="s">
         <v>7</v>
@@ -10259,7 +10259,7 @@
         <v>6</v>
       </c>
       <c r="C349">
-        <v>0.5125596723516849</v>
+        <v>0.5006106278600735</v>
       </c>
       <c r="D349" t="s">
         <v>7</v>
@@ -10273,10 +10273,10 @@
         <v>708</v>
       </c>
       <c r="B350" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C350">
-        <v>0.4176005201693805</v>
+        <v>0.3568669925768695</v>
       </c>
       <c r="D350" t="s">
         <v>7</v>
@@ -10290,10 +10290,10 @@
         <v>710</v>
       </c>
       <c r="B351" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C351">
-        <v>0.3386502648128661</v>
+        <v>0.2706738944316612</v>
       </c>
       <c r="D351" t="s">
         <v>7</v>
@@ -10307,10 +10307,10 @@
         <v>712</v>
       </c>
       <c r="B352" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C352">
-        <v>0.4925332154443695</v>
+        <v>0.4057761037583621</v>
       </c>
       <c r="D352" t="s">
         <v>7</v>
@@ -10327,7 +10327,7 @@
         <v>10</v>
       </c>
       <c r="C353">
-        <v>0.4250114084902095</v>
+        <v>0.3893378778070289</v>
       </c>
       <c r="D353" t="s">
         <v>7</v>
@@ -10344,7 +10344,7 @@
         <v>6</v>
       </c>
       <c r="C354">
-        <v>0.3082102407315919</v>
+        <v>0.2896903943308037</v>
       </c>
       <c r="D354" t="s">
         <v>7</v>
@@ -10361,7 +10361,7 @@
         <v>6</v>
       </c>
       <c r="C355">
-        <v>0.4051264551520901</v>
+        <v>0.3670683827240634</v>
       </c>
       <c r="D355" t="s">
         <v>7</v>
@@ -10378,7 +10378,7 @@
         <v>6</v>
       </c>
       <c r="C356">
-        <v>0.3629746782439219</v>
+        <v>0.3396611551153086</v>
       </c>
       <c r="D356" t="s">
         <v>7</v>
@@ -10395,7 +10395,7 @@
         <v>6</v>
       </c>
       <c r="C357">
-        <v>0.4301063011955147</v>
+        <v>0.3989442962479933</v>
       </c>
       <c r="D357" t="s">
         <v>7</v>
@@ -10412,7 +10412,7 @@
         <v>6</v>
       </c>
       <c r="C358">
-        <v>0.3562348696661759</v>
+        <v>0.3381358868610471</v>
       </c>
       <c r="D358" t="s">
         <v>7</v>
@@ -10429,7 +10429,7 @@
         <v>44</v>
       </c>
       <c r="C359">
-        <v>0.5581043837387906</v>
+        <v>0.4708992337439087</v>
       </c>
       <c r="D359" t="s">
         <v>7</v>
@@ -10446,7 +10446,7 @@
         <v>6</v>
       </c>
       <c r="C360">
-        <v>0.5020662193034554</v>
+        <v>0.5031959369167502</v>
       </c>
       <c r="D360" t="s">
         <v>7</v>
@@ -10460,10 +10460,10 @@
         <v>730</v>
       </c>
       <c r="B361" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C361">
-        <v>0.352668674335384</v>
+        <v>0.3171686149683453</v>
       </c>
       <c r="D361" t="s">
         <v>7</v>
@@ -10480,7 +10480,7 @@
         <v>6</v>
       </c>
       <c r="C362">
-        <v>0.3944799399233535</v>
+        <v>0.3574227997390121</v>
       </c>
       <c r="D362" t="s">
         <v>7</v>
@@ -10497,7 +10497,7 @@
         <v>10</v>
       </c>
       <c r="C363">
-        <v>0.330260588482478</v>
+        <v>0.3122244172071442</v>
       </c>
       <c r="D363" t="s">
         <v>7</v>
@@ -10514,7 +10514,7 @@
         <v>10</v>
       </c>
       <c r="C364">
-        <v>0.3836068712760068</v>
+        <v>0.3426366343986949</v>
       </c>
       <c r="D364" t="s">
         <v>7</v>
@@ -10531,7 +10531,7 @@
         <v>6</v>
       </c>
       <c r="C365">
-        <v>0.3066676084409448</v>
+        <v>0.3045302910637068</v>
       </c>
       <c r="D365" t="s">
         <v>7</v>
@@ -10545,10 +10545,10 @@
         <v>740</v>
       </c>
       <c r="B366" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C366">
-        <v>0.2675745882909432</v>
+        <v>0.2539094688301721</v>
       </c>
       <c r="D366" t="s">
         <v>7</v>
@@ -10565,7 +10565,7 @@
         <v>6</v>
       </c>
       <c r="C367">
-        <v>0.3446768065429725</v>
+        <v>0.3148658618177833</v>
       </c>
       <c r="D367" t="s">
         <v>7</v>
@@ -10579,10 +10579,10 @@
         <v>744</v>
       </c>
       <c r="B368" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C368">
-        <v>0.3118367685621168</v>
+        <v>0.2869148972443095</v>
       </c>
       <c r="D368" t="s">
         <v>7</v>
@@ -10599,7 +10599,7 @@
         <v>6</v>
       </c>
       <c r="C369">
-        <v>0.5653072726311656</v>
+        <v>0.5196564329826667</v>
       </c>
       <c r="D369" t="s">
         <v>7</v>
@@ -10616,7 +10616,7 @@
         <v>10</v>
       </c>
       <c r="C370">
-        <v>0.3507833967610343</v>
+        <v>0.317096941277771</v>
       </c>
       <c r="D370" t="s">
         <v>7</v>
@@ -10633,7 +10633,7 @@
         <v>6</v>
       </c>
       <c r="C371">
-        <v>0.5266404256995374</v>
+        <v>0.469916988567446</v>
       </c>
       <c r="D371" t="s">
         <v>7</v>
@@ -10650,7 +10650,7 @@
         <v>6</v>
       </c>
       <c r="C372">
-        <v>0.4393559502959843</v>
+        <v>0.38091676957675</v>
       </c>
       <c r="D372" t="s">
         <v>7</v>
@@ -10667,7 +10667,7 @@
         <v>6</v>
       </c>
       <c r="C373">
-        <v>0.5027858223896546</v>
+        <v>0.45059637499795</v>
       </c>
       <c r="D373" t="s">
         <v>7</v>
@@ -10684,7 +10684,7 @@
         <v>6</v>
       </c>
       <c r="C374">
-        <v>0.556090232358282</v>
+        <v>0.5137189008111154</v>
       </c>
       <c r="D374" t="s">
         <v>7</v>
@@ -10701,7 +10701,7 @@
         <v>6</v>
       </c>
       <c r="C375">
-        <v>0.5474924861898719</v>
+        <v>0.4921766773398457</v>
       </c>
       <c r="D375" t="s">
         <v>7</v>
@@ -10715,10 +10715,10 @@
         <v>760</v>
       </c>
       <c r="B376" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C376">
-        <v>0.3783123005122446</v>
+        <v>0.3447263099141518</v>
       </c>
       <c r="D376" t="s">
         <v>7</v>
@@ -10735,7 +10735,7 @@
         <v>6</v>
       </c>
       <c r="C377">
-        <v>0.5320377168320795</v>
+        <v>0.4775837571822592</v>
       </c>
       <c r="D377" t="s">
         <v>7</v>
@@ -10752,7 +10752,7 @@
         <v>6</v>
       </c>
       <c r="C378">
-        <v>0.3636683845002708</v>
+        <v>0.3374341237878503</v>
       </c>
       <c r="D378" t="s">
         <v>7</v>
@@ -10769,7 +10769,7 @@
         <v>6</v>
       </c>
       <c r="C379">
-        <v>0.3872365221100981</v>
+        <v>0.3555302831707307</v>
       </c>
       <c r="D379" t="s">
         <v>7</v>
@@ -10786,7 +10786,7 @@
         <v>6</v>
       </c>
       <c r="C380">
-        <v>0.3920990557933828</v>
+        <v>0.3645655052776242</v>
       </c>
       <c r="D380" t="s">
         <v>7</v>
@@ -10803,7 +10803,7 @@
         <v>10</v>
       </c>
       <c r="C381">
-        <v>0.5496773919145983</v>
+        <v>0.464582901380245</v>
       </c>
       <c r="D381" t="s">
         <v>7</v>
@@ -10820,7 +10820,7 @@
         <v>6</v>
       </c>
       <c r="C382">
-        <v>0.3897021417822316</v>
+        <v>0.3491846211119511</v>
       </c>
       <c r="D382" t="s">
         <v>7</v>
@@ -10837,7 +10837,7 @@
         <v>10</v>
       </c>
       <c r="C383">
-        <v>0.4548033795569768</v>
+        <v>0.3946871752649096</v>
       </c>
       <c r="D383" t="s">
         <v>7</v>
@@ -10854,7 +10854,7 @@
         <v>44</v>
       </c>
       <c r="C384">
-        <v>0.5008440643203851</v>
+        <v>0.4306063119353531</v>
       </c>
       <c r="D384" t="s">
         <v>7</v>
@@ -10871,7 +10871,7 @@
         <v>6</v>
       </c>
       <c r="C385">
-        <v>0.4543443434414075</v>
+        <v>0.3995249981657712</v>
       </c>
       <c r="D385" t="s">
         <v>7</v>
@@ -10885,10 +10885,10 @@
         <v>780</v>
       </c>
       <c r="B386" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C386">
-        <v>0.3525562300256839</v>
+        <v>0.3177297849300156</v>
       </c>
       <c r="D386" t="s">
         <v>7</v>
@@ -10905,7 +10905,7 @@
         <v>10</v>
       </c>
       <c r="C387">
-        <v>0.4718948461293332</v>
+        <v>0.4251613238547953</v>
       </c>
       <c r="D387" t="s">
         <v>7</v>
@@ -10922,7 +10922,7 @@
         <v>44</v>
       </c>
       <c r="C388">
-        <v>0.3956299068587354</v>
+        <v>0.3394019705095096</v>
       </c>
       <c r="D388" t="s">
         <v>7</v>
@@ -10939,7 +10939,7 @@
         <v>6</v>
       </c>
       <c r="C389">
-        <v>0.3686062855597332</v>
+        <v>0.3420859442745604</v>
       </c>
       <c r="D389" t="s">
         <v>7</v>
@@ -10953,10 +10953,10 @@
         <v>788</v>
       </c>
       <c r="B390" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C390">
-        <v>0.3528130909779427</v>
+        <v>0.3215109596656983</v>
       </c>
       <c r="D390" t="s">
         <v>7</v>
@@ -10970,10 +10970,10 @@
         <v>790</v>
       </c>
       <c r="B391" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C391">
-        <v>0.3741367844867318</v>
+        <v>0.3339617475186259</v>
       </c>
       <c r="D391" t="s">
         <v>7</v>
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="C392">
-        <v>0.3327162613760653</v>
+        <v>0.3094107807679606</v>
       </c>
       <c r="D392" t="s">
         <v>7</v>
@@ -11007,7 +11007,7 @@
         <v>10</v>
       </c>
       <c r="C393">
-        <v>0.4967507115150378</v>
+        <v>0.422585750221426</v>
       </c>
       <c r="D393" t="s">
         <v>7</v>
@@ -11021,10 +11021,10 @@
         <v>796</v>
       </c>
       <c r="B394" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C394">
-        <v>0.4146437537795883</v>
+        <v>0.3514664206160411</v>
       </c>
       <c r="D394" t="s">
         <v>7</v>
@@ -11041,7 +11041,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>0.4778467014826863</v>
+        <v>0.4154461830903713</v>
       </c>
       <c r="D395" t="s">
         <v>7</v>
@@ -11058,7 +11058,7 @@
         <v>6</v>
       </c>
       <c r="C396">
-        <v>0.4462539023599051</v>
+        <v>0.3977264986486919</v>
       </c>
       <c r="D396" t="s">
         <v>7</v>
@@ -11075,7 +11075,7 @@
         <v>10</v>
       </c>
       <c r="C397">
-        <v>0.4283171153430735</v>
+        <v>0.3727010308203904</v>
       </c>
       <c r="D397" t="s">
         <v>7</v>
@@ -11092,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="C398">
-        <v>0.509280183141702</v>
+        <v>0.5025176893613559</v>
       </c>
       <c r="D398" t="s">
         <v>7</v>
@@ -11106,10 +11106,10 @@
         <v>806</v>
       </c>
       <c r="B399" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C399">
-        <v>0.4727110952455416</v>
+        <v>0.3758213984563576</v>
       </c>
       <c r="D399" t="s">
         <v>7</v>
@@ -11126,7 +11126,7 @@
         <v>6</v>
       </c>
       <c r="C400">
-        <v>0.3852298283222335</v>
+        <v>0.3642696147910479</v>
       </c>
       <c r="D400" t="s">
         <v>7</v>
@@ -11140,10 +11140,10 @@
         <v>810</v>
       </c>
       <c r="B401" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C401">
-        <v>0.5382528709664383</v>
+        <v>0.4293448600810392</v>
       </c>
       <c r="D401" t="s">
         <v>7</v>
@@ -11160,7 +11160,7 @@
         <v>6</v>
       </c>
       <c r="C402">
-        <v>0.4589390681050751</v>
+        <v>0.4091387420548581</v>
       </c>
       <c r="D402" t="s">
         <v>7</v>
@@ -11177,7 +11177,7 @@
         <v>6</v>
       </c>
       <c r="C403">
-        <v>0.2944231781964758</v>
+        <v>0.2803983124057788</v>
       </c>
       <c r="D403" t="s">
         <v>7</v>
@@ -11194,7 +11194,7 @@
         <v>10</v>
       </c>
       <c r="C404">
-        <v>0.363180026181342</v>
+        <v>0.3260053098674439</v>
       </c>
       <c r="D404" t="s">
         <v>7</v>
@@ -11211,7 +11211,7 @@
         <v>6</v>
       </c>
       <c r="C405">
-        <v>0.4562746511666228</v>
+        <v>0.4066611543799579</v>
       </c>
       <c r="D405" t="s">
         <v>7</v>
@@ -11225,10 +11225,10 @@
         <v>820</v>
       </c>
       <c r="B406" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="C406">
-        <v>0.5515217763636963</v>
+        <v>0.4943145119040144</v>
       </c>
       <c r="D406" t="s">
         <v>7</v>
@@ -11245,7 +11245,7 @@
         <v>6</v>
       </c>
       <c r="C407">
-        <v>0.4310088547781363</v>
+        <v>0.3953769858222027</v>
       </c>
       <c r="D407" t="s">
         <v>7</v>
@@ -11262,7 +11262,7 @@
         <v>6</v>
       </c>
       <c r="C408">
-        <v>0.5479843496674669</v>
+        <v>0.4868483312748518</v>
       </c>
       <c r="D408" t="s">
         <v>7</v>
@@ -11279,7 +11279,7 @@
         <v>6</v>
       </c>
       <c r="C409">
-        <v>0.56825765916293</v>
+        <v>0.4911910653642571</v>
       </c>
       <c r="D409" t="s">
         <v>7</v>
@@ -11293,10 +11293,10 @@
         <v>828</v>
       </c>
       <c r="B410" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C410">
-        <v>0.333963899886761</v>
+        <v>0.3011020914581182</v>
       </c>
       <c r="D410" t="s">
         <v>7</v>
@@ -11313,7 +11313,7 @@
         <v>10</v>
       </c>
       <c r="C411">
-        <v>0.3718694704247643</v>
+        <v>0.3473142975327259</v>
       </c>
       <c r="D411" t="s">
         <v>7</v>
@@ -11330,7 +11330,7 @@
         <v>6</v>
       </c>
       <c r="C412">
-        <v>0.5269174828656948</v>
+        <v>0.4627665926856686</v>
       </c>
       <c r="D412" t="s">
         <v>7</v>
@@ -11347,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="C413">
-        <v>0.268753374498474</v>
+        <v>0.2599578673875745</v>
       </c>
       <c r="D413" t="s">
         <v>7</v>
@@ -11361,10 +11361,10 @@
         <v>836</v>
       </c>
       <c r="B414" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C414">
-        <v>0.3835034714858351</v>
+        <v>0.328985186570726</v>
       </c>
       <c r="D414" t="s">
         <v>7</v>
@@ -11378,10 +11378,10 @@
         <v>838</v>
       </c>
       <c r="B415" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C415">
-        <v>0.3992113587275313</v>
+        <v>0.3488370915625618</v>
       </c>
       <c r="D415" t="s">
         <v>7</v>
@@ -11395,10 +11395,10 @@
         <v>840</v>
       </c>
       <c r="B416" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C416">
-        <v>0.5091818949311835</v>
+        <v>0.419403893848169</v>
       </c>
       <c r="D416" t="s">
         <v>7</v>
@@ -11415,7 +11415,7 @@
         <v>6</v>
       </c>
       <c r="C417">
-        <v>0.2815473203168448</v>
+        <v>0.2644320879809123</v>
       </c>
       <c r="D417" t="s">
         <v>7</v>
@@ -11432,7 +11432,7 @@
         <v>10</v>
       </c>
       <c r="C418">
-        <v>0.3295765061099344</v>
+        <v>0.301578174552251</v>
       </c>
       <c r="D418" t="s">
         <v>7</v>
@@ -11446,10 +11446,10 @@
         <v>846</v>
       </c>
       <c r="B419" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C419">
-        <v>0.3355905251906521</v>
+        <v>0.3113521356673561</v>
       </c>
       <c r="D419" t="s">
         <v>7</v>
@@ -11466,7 +11466,7 @@
         <v>44</v>
       </c>
       <c r="C420">
-        <v>0.4330882946170404</v>
+        <v>0.3988582410987757</v>
       </c>
       <c r="D420" t="s">
         <v>7</v>
@@ -11483,7 +11483,7 @@
         <v>44</v>
       </c>
       <c r="C421">
-        <v>0.435229571691427</v>
+        <v>0.3904075571563452</v>
       </c>
       <c r="D421" t="s">
         <v>7</v>
@@ -11500,7 +11500,7 @@
         <v>6</v>
       </c>
       <c r="C422">
-        <v>0.4086297737791083</v>
+        <v>0.3713017050557155</v>
       </c>
       <c r="D422" t="s">
         <v>7</v>
@@ -11517,7 +11517,7 @@
         <v>44</v>
       </c>
       <c r="C423">
-        <v>0.5436608511433112</v>
+        <v>0.4483461573889718</v>
       </c>
       <c r="D423" t="s">
         <v>7</v>
@@ -11534,7 +11534,7 @@
         <v>10</v>
       </c>
       <c r="C424">
-        <v>0.3561843979286954</v>
+        <v>0.3279830668591311</v>
       </c>
       <c r="D424" t="s">
         <v>7</v>
@@ -11551,7 +11551,7 @@
         <v>6</v>
       </c>
       <c r="C425">
-        <v>0.3780417541771915</v>
+        <v>0.3471956322031688</v>
       </c>
       <c r="D425" t="s">
         <v>7</v>
@@ -11565,10 +11565,10 @@
         <v>860</v>
       </c>
       <c r="B426" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C426">
-        <v>0.3968591841209711</v>
+        <v>0.3447367456443427</v>
       </c>
       <c r="D426" t="s">
         <v>7</v>
@@ -11582,10 +11582,10 @@
         <v>862</v>
       </c>
       <c r="B427" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C427">
-        <v>0.2927015597300543</v>
+        <v>0.274634999719913</v>
       </c>
       <c r="D427" t="s">
         <v>7</v>
@@ -11602,7 +11602,7 @@
         <v>6</v>
       </c>
       <c r="C428">
-        <v>0.2935762366250528</v>
+        <v>0.2828208708662532</v>
       </c>
       <c r="D428" t="s">
         <v>7</v>
@@ -11619,7 +11619,7 @@
         <v>10</v>
       </c>
       <c r="C429">
-        <v>0.4017110859337001</v>
+        <v>0.3539230641901905</v>
       </c>
       <c r="D429" t="s">
         <v>7</v>
@@ -11636,7 +11636,7 @@
         <v>6</v>
       </c>
       <c r="C430">
-        <v>0.3522715490322337</v>
+        <v>0.3354061306601833</v>
       </c>
       <c r="D430" t="s">
         <v>7</v>
@@ -11653,7 +11653,7 @@
         <v>6</v>
       </c>
       <c r="C431">
-        <v>0.319881605341448</v>
+        <v>0.2948962990152054</v>
       </c>
       <c r="D431" t="s">
         <v>7</v>
@@ -11667,10 +11667,10 @@
         <v>872</v>
       </c>
       <c r="B432" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C432">
-        <v>0.3874688223223968</v>
+        <v>0.3269346220300967</v>
       </c>
       <c r="D432" t="s">
         <v>7</v>
@@ -11687,7 +11687,7 @@
         <v>6</v>
       </c>
       <c r="C433">
-        <v>0.3528056575176793</v>
+        <v>0.3299936139856907</v>
       </c>
       <c r="D433" t="s">
         <v>7</v>
@@ -11701,10 +11701,10 @@
         <v>876</v>
       </c>
       <c r="B434" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C434">
-        <v>0.3868562949051052</v>
+        <v>0.3405461626765115</v>
       </c>
       <c r="D434" t="s">
         <v>7</v>
@@ -11721,7 +11721,7 @@
         <v>10</v>
       </c>
       <c r="C435">
-        <v>0.4450706155765732</v>
+        <v>0.3784836283365794</v>
       </c>
       <c r="D435" t="s">
         <v>7</v>
@@ -11735,10 +11735,10 @@
         <v>880</v>
       </c>
       <c r="B436" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C436">
-        <v>0.3457844821966243</v>
+        <v>0.302707054888373</v>
       </c>
       <c r="D436" t="s">
         <v>7</v>
@@ -11755,7 +11755,7 @@
         <v>10</v>
       </c>
       <c r="C437">
-        <v>0.3590717304185123</v>
+        <v>0.3226362460181619</v>
       </c>
       <c r="D437" t="s">
         <v>7</v>
@@ -11769,10 +11769,10 @@
         <v>884</v>
       </c>
       <c r="B438" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C438">
-        <v>0.3786987201899532</v>
+        <v>0.3364640959206577</v>
       </c>
       <c r="D438" t="s">
         <v>7</v>
@@ -11789,7 +11789,7 @@
         <v>6</v>
       </c>
       <c r="C439">
-        <v>0.4106590898760635</v>
+        <v>0.3758053885036527</v>
       </c>
       <c r="D439" t="s">
         <v>7</v>
@@ -11806,7 +11806,7 @@
         <v>10</v>
       </c>
       <c r="C440">
-        <v>0.4365675765952921</v>
+        <v>0.3771922406850085</v>
       </c>
       <c r="D440" t="s">
         <v>7</v>
@@ -11820,10 +11820,10 @@
         <v>890</v>
       </c>
       <c r="B441" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C441">
-        <v>0.3024182185664596</v>
+        <v>0.2936095504224355</v>
       </c>
       <c r="D441" t="s">
         <v>7</v>
@@ -11840,7 +11840,7 @@
         <v>6</v>
       </c>
       <c r="C442">
-        <v>0.3243218518696234</v>
+        <v>0.3090139534654536</v>
       </c>
       <c r="D442" t="s">
         <v>7</v>
@@ -11854,10 +11854,10 @@
         <v>894</v>
       </c>
       <c r="B443" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C443">
-        <v>0.3356376753610104</v>
+        <v>0.2996731494329868</v>
       </c>
       <c r="D443" t="s">
         <v>7</v>
@@ -11874,7 +11874,7 @@
         <v>10</v>
       </c>
       <c r="C444">
-        <v>0.3743552451976403</v>
+        <v>0.3370110013760498</v>
       </c>
       <c r="D444" t="s">
         <v>7</v>
@@ -11891,7 +11891,7 @@
         <v>6</v>
       </c>
       <c r="C445">
-        <v>0.3673638301188544</v>
+        <v>0.352624602729779</v>
       </c>
       <c r="D445" t="s">
         <v>7</v>
@@ -11908,7 +11908,7 @@
         <v>44</v>
       </c>
       <c r="C446">
-        <v>0.3833124419691462</v>
+        <v>0.3428671193937604</v>
       </c>
       <c r="D446" t="s">
         <v>7</v>
@@ -11925,7 +11925,7 @@
         <v>10</v>
       </c>
       <c r="C447">
-        <v>0.3136054766276056</v>
+        <v>0.2958025661465098</v>
       </c>
       <c r="D447" t="s">
         <v>7</v>
@@ -11942,7 +11942,7 @@
         <v>6</v>
       </c>
       <c r="C448">
-        <v>0.40510798142858</v>
+        <v>0.3632844792793226</v>
       </c>
       <c r="D448" t="s">
         <v>7</v>
@@ -11959,7 +11959,7 @@
         <v>6</v>
       </c>
       <c r="C449">
-        <v>0.4587664465532609</v>
+        <v>0.4018103950098314</v>
       </c>
       <c r="D449" t="s">
         <v>7</v>
@@ -11976,7 +11976,7 @@
         <v>44</v>
       </c>
       <c r="C450">
-        <v>0.4179405662644137</v>
+        <v>0.363439596936798</v>
       </c>
       <c r="D450" t="s">
         <v>7</v>
@@ -11993,7 +11993,7 @@
         <v>44</v>
       </c>
       <c r="C451">
-        <v>0.4827849303102942</v>
+        <v>0.4066862413986927</v>
       </c>
       <c r="D451" t="s">
         <v>7</v>
@@ -12010,7 +12010,7 @@
         <v>6</v>
       </c>
       <c r="C452">
-        <v>0.3099747894866376</v>
+        <v>0.3012304256309404</v>
       </c>
       <c r="D452" t="s">
         <v>7</v>
@@ -12027,7 +12027,7 @@
         <v>10</v>
       </c>
       <c r="C453">
-        <v>0.3873199678874892</v>
+        <v>0.3511223046004948</v>
       </c>
       <c r="D453" t="s">
         <v>7</v>
@@ -12041,10 +12041,10 @@
         <v>916</v>
       </c>
       <c r="B454" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C454">
-        <v>0.2964212206072519</v>
+        <v>0.2714273786230441</v>
       </c>
       <c r="D454" t="s">
         <v>7</v>
@@ -12061,7 +12061,7 @@
         <v>10</v>
       </c>
       <c r="C455">
-        <v>0.3689910127567897</v>
+        <v>0.3395344633723986</v>
       </c>
       <c r="D455" t="s">
         <v>7</v>
@@ -12078,7 +12078,7 @@
         <v>6</v>
       </c>
       <c r="C456">
-        <v>0.3938386295730035</v>
+        <v>0.3726166211846891</v>
       </c>
       <c r="D456" t="s">
         <v>7</v>
@@ -12092,10 +12092,10 @@
         <v>922</v>
       </c>
       <c r="B457" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C457">
-        <v>0.3738768490827961</v>
+        <v>0.3266951928260627</v>
       </c>
       <c r="D457" t="s">
         <v>7</v>
@@ -12112,7 +12112,7 @@
         <v>6</v>
       </c>
       <c r="C458">
-        <v>0.4007795957441858</v>
+        <v>0.3827141342268658</v>
       </c>
       <c r="D458" t="s">
         <v>7</v>
@@ -12129,7 +12129,7 @@
         <v>6</v>
       </c>
       <c r="C459">
-        <v>0.3948485405804614</v>
+        <v>0.3669474432690649</v>
       </c>
       <c r="D459" t="s">
         <v>7</v>
@@ -12146,7 +12146,7 @@
         <v>6</v>
       </c>
       <c r="C460">
-        <v>0.358080728552195</v>
+        <v>0.3323624801836266</v>
       </c>
       <c r="D460" t="s">
         <v>7</v>
@@ -12163,7 +12163,7 @@
         <v>6</v>
       </c>
       <c r="C461">
-        <v>0.3187248964572302</v>
+        <v>0.3190790289432909</v>
       </c>
       <c r="D461" t="s">
         <v>7</v>
@@ -12180,7 +12180,7 @@
         <v>6</v>
       </c>
       <c r="C462">
-        <v>0.3708057923447027</v>
+        <v>0.3464129205866737</v>
       </c>
       <c r="D462" t="s">
         <v>7</v>
@@ -12194,10 +12194,10 @@
         <v>934</v>
       </c>
       <c r="B463" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C463">
-        <v>0.3274994146027568</v>
+        <v>0.3092263151082527</v>
       </c>
       <c r="D463" t="s">
         <v>7</v>
@@ -12214,7 +12214,7 @@
         <v>6</v>
       </c>
       <c r="C464">
-        <v>0.4364824348854913</v>
+        <v>0.4158728010077347</v>
       </c>
       <c r="D464" t="s">
         <v>7</v>
@@ -12231,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="C465">
-        <v>0.4627526096080364</v>
+        <v>0.3994262729561958</v>
       </c>
       <c r="D465" t="s">
         <v>7</v>
@@ -12248,7 +12248,7 @@
         <v>6</v>
       </c>
       <c r="C466">
-        <v>0.5818093277334901</v>
+        <v>0.5323018283434655</v>
       </c>
       <c r="D466" t="s">
         <v>7</v>
@@ -12265,7 +12265,7 @@
         <v>6</v>
       </c>
       <c r="C467">
-        <v>0.5318681052633515</v>
+        <v>0.4766303893213598</v>
       </c>
       <c r="D467" t="s">
         <v>7</v>
@@ -12282,7 +12282,7 @@
         <v>6</v>
       </c>
       <c r="C468">
-        <v>0.4624796784844015</v>
+        <v>0.4087408973815903</v>
       </c>
       <c r="D468" t="s">
         <v>7</v>
@@ -12296,10 +12296,10 @@
         <v>946</v>
       </c>
       <c r="B469" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C469">
-        <v>0.2909468644174008</v>
+        <v>0.2727732523082841</v>
       </c>
       <c r="D469" t="s">
         <v>7</v>
@@ -12313,10 +12313,10 @@
         <v>948</v>
       </c>
       <c r="B470" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C470">
-        <v>0.3501024718936351</v>
+        <v>0.308478801471884</v>
       </c>
       <c r="D470" t="s">
         <v>7</v>
@@ -12333,7 +12333,7 @@
         <v>10</v>
       </c>
       <c r="C471">
-        <v>0.3642365524218964</v>
+        <v>0.3260341031700557</v>
       </c>
       <c r="D471" t="s">
         <v>7</v>
@@ -12347,10 +12347,10 @@
         <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C472">
-        <v>0.3641574848567489</v>
+        <v>0.3171212881658887</v>
       </c>
       <c r="D472" t="s">
         <v>7</v>
@@ -12367,7 +12367,7 @@
         <v>10</v>
       </c>
       <c r="C473">
-        <v>0.3601209059185533</v>
+        <v>0.3250987615363817</v>
       </c>
       <c r="D473" t="s">
         <v>7</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="C474">
-        <v>0.4446015758913578</v>
+        <v>0.4015630178587053</v>
       </c>
       <c r="D474" t="s">
         <v>7</v>
@@ -12401,7 +12401,7 @@
         <v>6</v>
       </c>
       <c r="C475">
-        <v>0.3737093745333434</v>
+        <v>0.3532504379379274</v>
       </c>
       <c r="D475" t="s">
         <v>7</v>
@@ -12418,7 +12418,7 @@
         <v>6</v>
       </c>
       <c r="C476">
-        <v>0.3650344834721148</v>
+        <v>0.3391441560945338</v>
       </c>
       <c r="D476" t="s">
         <v>7</v>
@@ -12435,7 +12435,7 @@
         <v>10</v>
       </c>
       <c r="C477">
-        <v>0.3618452739323825</v>
+        <v>0.3485194671375151</v>
       </c>
       <c r="D477" t="s">
         <v>7</v>
@@ -12452,7 +12452,7 @@
         <v>6</v>
       </c>
       <c r="C478">
-        <v>0.4423948961564615</v>
+        <v>0.3959082910121648</v>
       </c>
       <c r="D478" t="s">
         <v>7</v>
@@ -12469,7 +12469,7 @@
         <v>44</v>
       </c>
       <c r="C479">
-        <v>0.4901674907761368</v>
+        <v>0.4100156651729204</v>
       </c>
       <c r="D479" t="s">
         <v>7</v>
@@ -12486,7 +12486,7 @@
         <v>6</v>
       </c>
       <c r="C480">
-        <v>0.5381517481905375</v>
+        <v>0.4805159827268645</v>
       </c>
       <c r="D480" t="s">
         <v>7</v>
@@ -12503,7 +12503,7 @@
         <v>44</v>
       </c>
       <c r="C481">
-        <v>0.4275151226594582</v>
+        <v>0.3889892346766746</v>
       </c>
       <c r="D481" t="s">
         <v>7</v>
@@ -12520,7 +12520,7 @@
         <v>10</v>
       </c>
       <c r="C482">
-        <v>0.3617769502489039</v>
+        <v>0.3293314857938329</v>
       </c>
       <c r="D482" t="s">
         <v>7</v>
@@ -12537,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="C483">
-        <v>0.3480728379321548</v>
+        <v>0.3133430501439398</v>
       </c>
       <c r="D483" t="s">
         <v>7</v>
@@ -12554,7 +12554,7 @@
         <v>44</v>
       </c>
       <c r="C484">
-        <v>0.4320811055610588</v>
+        <v>0.383355294417273</v>
       </c>
       <c r="D484" t="s">
         <v>7</v>
@@ -12568,10 +12568,10 @@
         <v>978</v>
       </c>
       <c r="B485" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C485">
-        <v>0.4577739372173761</v>
+        <v>0.3810447314944797</v>
       </c>
       <c r="D485" t="s">
         <v>7</v>
@@ -12585,10 +12585,10 @@
         <v>980</v>
       </c>
       <c r="B486" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C486">
-        <v>0.5061829755067078</v>
+        <v>0.4128996560528631</v>
       </c>
       <c r="D486" t="s">
         <v>7</v>
@@ -12605,7 +12605,7 @@
         <v>44</v>
       </c>
       <c r="C487">
-        <v>0.5324847696946391</v>
+        <v>0.4616888051197234</v>
       </c>
       <c r="D487" t="s">
         <v>7</v>
@@ -12622,7 +12622,7 @@
         <v>10</v>
       </c>
       <c r="C488">
-        <v>0.3814103924333979</v>
+        <v>0.3352518732853417</v>
       </c>
       <c r="D488" t="s">
         <v>7</v>
@@ -12639,7 +12639,7 @@
         <v>6</v>
       </c>
       <c r="C489">
-        <v>0.5472925921739843</v>
+        <v>0.5096245369305251</v>
       </c>
       <c r="D489" t="s">
         <v>7</v>
@@ -12653,10 +12653,10 @@
         <v>988</v>
       </c>
       <c r="B490" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C490">
-        <v>0.3598376240194596</v>
+        <v>0.3045734093448091</v>
       </c>
       <c r="D490" t="s">
         <v>7</v>
@@ -12673,7 +12673,7 @@
         <v>6</v>
       </c>
       <c r="C491">
-        <v>0.2847988295680832</v>
+        <v>0.2769325025041985</v>
       </c>
       <c r="D491" t="s">
         <v>7</v>
@@ -12690,7 +12690,7 @@
         <v>6</v>
       </c>
       <c r="C492">
-        <v>0.4968737095919299</v>
+        <v>0.5136010269677338</v>
       </c>
       <c r="D492" t="s">
         <v>7</v>
@@ -12707,7 +12707,7 @@
         <v>6</v>
       </c>
       <c r="C493">
-        <v>0.2942361107541009</v>
+        <v>0.2820257461018201</v>
       </c>
       <c r="D493" t="s">
         <v>7</v>
@@ -12724,7 +12724,7 @@
         <v>10</v>
       </c>
       <c r="C494">
-        <v>0.3981123775930181</v>
+        <v>0.3648561918827269</v>
       </c>
       <c r="D494" t="s">
         <v>7</v>
@@ -12741,7 +12741,7 @@
         <v>44</v>
       </c>
       <c r="C495">
-        <v>0.6198801162548521</v>
+        <v>0.5187022575999229</v>
       </c>
       <c r="D495" t="s">
         <v>7</v>
@@ -12758,7 +12758,7 @@
         <v>6</v>
       </c>
       <c r="C496">
-        <v>0.5552930372159036</v>
+        <v>0.4863195649714506</v>
       </c>
       <c r="D496" t="s">
         <v>7</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="C497">
-        <v>0.3752465060328306</v>
+        <v>0.3519717079118063</v>
       </c>
       <c r="D497" t="s">
         <v>7</v>
@@ -12792,7 +12792,7 @@
         <v>6</v>
       </c>
       <c r="C498">
-        <v>0.7263049823731841</v>
+        <v>0.7132145273668897</v>
       </c>
       <c r="D498" t="s">
         <v>7</v>
@@ -12806,10 +12806,10 @@
         <v>1006</v>
       </c>
       <c r="B499" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C499">
-        <v>0.3738072432418988</v>
+        <v>0.3285835499721305</v>
       </c>
       <c r="D499" t="s">
         <v>7</v>
@@ -12826,7 +12826,7 @@
         <v>6</v>
       </c>
       <c r="C500">
-        <v>0.4665773114967099</v>
+        <v>0.4286196917800489</v>
       </c>
       <c r="D500" t="s">
         <v>7</v>
@@ -12840,10 +12840,10 @@
         <v>1010</v>
       </c>
       <c r="B501" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C501">
-        <v>0.4726646129905198</v>
+        <v>0.3828301075010806</v>
       </c>
       <c r="D501" t="s">
         <v>7</v>
@@ -12860,7 +12860,7 @@
         <v>6</v>
       </c>
       <c r="C502">
-        <v>0.654172813830409</v>
+        <v>0.6206327632966172</v>
       </c>
       <c r="D502" t="s">
         <v>7</v>
@@ -12874,10 +12874,10 @@
         <v>1014</v>
       </c>
       <c r="B503" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C503">
-        <v>0.4239101369256076</v>
+        <v>0.3639880552338601</v>
       </c>
       <c r="D503" t="s">
         <v>7</v>
@@ -12891,10 +12891,10 @@
         <v>1016</v>
       </c>
       <c r="B504" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C504">
-        <v>0.3236898762607828</v>
+        <v>0.3021363704194772</v>
       </c>
       <c r="D504" t="s">
         <v>7</v>
@@ -12911,7 +12911,7 @@
         <v>6</v>
       </c>
       <c r="C505">
-        <v>0.5053582193288489</v>
+        <v>0.4540699347775328</v>
       </c>
       <c r="D505" t="s">
         <v>7</v>
@@ -12925,10 +12925,10 @@
         <v>1020</v>
       </c>
       <c r="B506" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C506">
-        <v>0.606669037420546</v>
+        <v>0.4747589542173347</v>
       </c>
       <c r="D506" t="s">
         <v>7</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="C507">
-        <v>0.3534724180085382</v>
+        <v>0.3246802763925364</v>
       </c>
       <c r="D507" t="s">
         <v>7</v>
@@ -12959,10 +12959,10 @@
         <v>1024</v>
       </c>
       <c r="B508" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C508">
-        <v>0.3520312231605945</v>
+        <v>0.3071442718138007</v>
       </c>
       <c r="D508" t="s">
         <v>7</v>
@@ -12979,7 +12979,7 @@
         <v>10</v>
       </c>
       <c r="C509">
-        <v>0.6126131705807644</v>
+        <v>0.5251216052210858</v>
       </c>
       <c r="D509" t="s">
         <v>7</v>
@@ -12996,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="C510">
-        <v>0.3923450317469117</v>
+        <v>0.3692809043615778</v>
       </c>
       <c r="D510" t="s">
         <v>7</v>
@@ -13013,7 +13013,7 @@
         <v>44</v>
       </c>
       <c r="C511">
-        <v>0.4011121385046515</v>
+        <v>0.3436723568063269</v>
       </c>
       <c r="D511" t="s">
         <v>7</v>
@@ -13030,7 +13030,7 @@
         <v>6</v>
       </c>
       <c r="C512">
-        <v>0.3580543076495224</v>
+        <v>0.3300218555340872</v>
       </c>
       <c r="D512" t="s">
         <v>7</v>
@@ -13047,7 +13047,7 @@
         <v>6</v>
       </c>
       <c r="C513">
-        <v>0.4195153756560575</v>
+        <v>0.3938057671963004</v>
       </c>
       <c r="D513" t="s">
         <v>7</v>
@@ -13064,7 +13064,7 @@
         <v>44</v>
       </c>
       <c r="C514">
-        <v>0.5017602909299432</v>
+        <v>0.4153477452245482</v>
       </c>
       <c r="D514" t="s">
         <v>7</v>
@@ -13081,7 +13081,7 @@
         <v>6</v>
       </c>
       <c r="C515">
-        <v>0.5183877377188373</v>
+        <v>0.4891722369151522</v>
       </c>
       <c r="D515" t="s">
         <v>7</v>
@@ -13095,10 +13095,10 @@
         <v>1040</v>
       </c>
       <c r="B516" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C516">
-        <v>0.3442893827727207</v>
+        <v>0.3073456980067991</v>
       </c>
       <c r="D516" t="s">
         <v>7</v>
@@ -13112,10 +13112,10 @@
         <v>1042</v>
       </c>
       <c r="B517" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C517">
-        <v>0.3411001474694316</v>
+        <v>0.3142226328940008</v>
       </c>
       <c r="D517" t="s">
         <v>7</v>
@@ -13132,7 +13132,7 @@
         <v>10</v>
       </c>
       <c r="C518">
-        <v>0.3948749226154879</v>
+        <v>0.3425610253603771</v>
       </c>
       <c r="D518" t="s">
         <v>7</v>
@@ -13149,7 +13149,7 @@
         <v>44</v>
       </c>
       <c r="C519">
-        <v>0.5735250624980321</v>
+        <v>0.4933831591803035</v>
       </c>
       <c r="D519" t="s">
         <v>7</v>
@@ -13163,10 +13163,10 @@
         <v>1048</v>
       </c>
       <c r="B520" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C520">
-        <v>0.3908925393322007</v>
+        <v>0.3332531042789138</v>
       </c>
       <c r="D520" t="s">
         <v>7</v>
@@ -13183,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="C521">
-        <v>0.3482588951200677</v>
+        <v>0.3134946929435737</v>
       </c>
       <c r="D521" t="s">
         <v>7</v>
@@ -13197,10 +13197,10 @@
         <v>1052</v>
       </c>
       <c r="B522" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C522">
-        <v>0.4184200415875385</v>
+        <v>0.3640623252258387</v>
       </c>
       <c r="D522" t="s">
         <v>7</v>
@@ -13217,7 +13217,7 @@
         <v>6</v>
       </c>
       <c r="C523">
-        <v>0.5372616215693192</v>
+        <v>0.4688722480246025</v>
       </c>
       <c r="D523" t="s">
         <v>7</v>
@@ -13234,7 +13234,7 @@
         <v>6</v>
       </c>
       <c r="C524">
-        <v>0.3090968259362861</v>
+        <v>0.2892187179237666</v>
       </c>
       <c r="D524" t="s">
         <v>7</v>
@@ -13251,7 +13251,7 @@
         <v>44</v>
       </c>
       <c r="C525">
-        <v>0.4613459989873869</v>
+        <v>0.395507984188891</v>
       </c>
       <c r="D525" t="s">
         <v>7</v>
@@ -13268,7 +13268,7 @@
         <v>44</v>
       </c>
       <c r="C526">
-        <v>0.4989851834853846</v>
+        <v>0.4292617981757403</v>
       </c>
       <c r="D526" t="s">
         <v>7</v>
@@ -13285,7 +13285,7 @@
         <v>10</v>
       </c>
       <c r="C527">
-        <v>0.396586754778305</v>
+        <v>0.3635692969180708</v>
       </c>
       <c r="D527" t="s">
         <v>7</v>
@@ -13302,7 +13302,7 @@
         <v>6</v>
       </c>
       <c r="C528">
-        <v>0.4987051665365487</v>
+        <v>0.4467472912262813</v>
       </c>
       <c r="D528" t="s">
         <v>7</v>
@@ -13319,7 +13319,7 @@
         <v>10</v>
       </c>
       <c r="C529">
-        <v>0.3682801040755864</v>
+        <v>0.3408646256794823</v>
       </c>
       <c r="D529" t="s">
         <v>7</v>
@@ -13336,7 +13336,7 @@
         <v>44</v>
       </c>
       <c r="C530">
-        <v>0.587190397923504</v>
+        <v>0.487242250582587</v>
       </c>
       <c r="D530" t="s">
         <v>7</v>
@@ -13353,7 +13353,7 @@
         <v>44</v>
       </c>
       <c r="C531">
-        <v>0.6516558743946289</v>
+        <v>0.550425127734447</v>
       </c>
       <c r="D531" t="s">
         <v>7</v>
@@ -13367,10 +13367,10 @@
         <v>1072</v>
       </c>
       <c r="B532" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C532">
-        <v>0.2962295389728327</v>
+        <v>0.2763242916564526</v>
       </c>
       <c r="D532" t="s">
         <v>7</v>
@@ -13384,10 +13384,10 @@
         <v>1074</v>
       </c>
       <c r="B533" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C533">
-        <v>0.5619238065575358</v>
+        <v>0.4363967712307083</v>
       </c>
       <c r="D533" t="s">
         <v>7</v>
@@ -13401,10 +13401,10 @@
         <v>1076</v>
       </c>
       <c r="B534" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C534">
-        <v>0.3800675063353964</v>
+        <v>0.3343181766659485</v>
       </c>
       <c r="D534" t="s">
         <v>7</v>
@@ -13421,7 +13421,7 @@
         <v>6</v>
       </c>
       <c r="C535">
-        <v>0.3373762037480327</v>
+        <v>0.3218809495850795</v>
       </c>
       <c r="D535" t="s">
         <v>7</v>
@@ -13435,10 +13435,10 @@
         <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C536">
-        <v>0.3080273742131366</v>
+        <v>0.2926133150085877</v>
       </c>
       <c r="D536" t="s">
         <v>7</v>
@@ -13455,7 +13455,7 @@
         <v>6</v>
       </c>
       <c r="C537">
-        <v>0.4131717664376138</v>
+        <v>0.3758655265849049</v>
       </c>
       <c r="D537" t="s">
         <v>7</v>
@@ -13469,10 +13469,10 @@
         <v>1084</v>
       </c>
       <c r="B538" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C538">
-        <v>0.3144315329354996</v>
+        <v>0.2938314755717724</v>
       </c>
       <c r="D538" t="s">
         <v>7</v>
@@ -13489,7 +13489,7 @@
         <v>6</v>
       </c>
       <c r="C539">
-        <v>0.3138461162455821</v>
+        <v>0.3054116199972441</v>
       </c>
       <c r="D539" t="s">
         <v>7</v>
@@ -13503,10 +13503,10 @@
         <v>1088</v>
       </c>
       <c r="B540" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C540">
-        <v>0.2865130827840019</v>
+        <v>0.2653876443881878</v>
       </c>
       <c r="D540" t="s">
         <v>7</v>
@@ -13523,7 +13523,7 @@
         <v>6</v>
       </c>
       <c r="C541">
-        <v>0.5004709603666889</v>
+        <v>0.4458121309680424</v>
       </c>
       <c r="D541" t="s">
         <v>7</v>
@@ -13540,7 +13540,7 @@
         <v>44</v>
       </c>
       <c r="C542">
-        <v>0.3798193010024841</v>
+        <v>0.3584180038928211</v>
       </c>
       <c r="D542" t="s">
         <v>7</v>
@@ -13557,7 +13557,7 @@
         <v>6</v>
       </c>
       <c r="C543">
-        <v>0.4348356654158654</v>
+        <v>0.413068152489801</v>
       </c>
       <c r="D543" t="s">
         <v>7</v>
@@ -13574,7 +13574,7 @@
         <v>6</v>
       </c>
       <c r="C544">
-        <v>0.3914150402294408</v>
+        <v>0.3540965808879288</v>
       </c>
       <c r="D544" t="s">
         <v>7</v>
@@ -13843,7 +13843,7 @@
         <v>1143</v>
       </c>
       <c r="C563">
-        <v>0.2855484150813754</v>
+        <v>0.2908263130615064</v>
       </c>
       <c r="D563" t="s">
         <v>1144</v>
@@ -13860,7 +13860,7 @@
         <v>1143</v>
       </c>
       <c r="C564">
-        <v>0.3262320650819759</v>
+        <v>0.3192601603092695</v>
       </c>
       <c r="D564" t="s">
         <v>1144</v>
@@ -13877,7 +13877,7 @@
         <v>1143</v>
       </c>
       <c r="C565">
-        <v>0.2782669255799973</v>
+        <v>0.2798264700648698</v>
       </c>
       <c r="D565" t="s">
         <v>1144</v>
@@ -13894,7 +13894,7 @@
         <v>1143</v>
       </c>
       <c r="C566">
-        <v>0.3940464698227714</v>
+        <v>0.3680047592344373</v>
       </c>
       <c r="D566" t="s">
         <v>1144</v>
@@ -13911,7 +13911,7 @@
         <v>1143</v>
       </c>
       <c r="C567">
-        <v>0.3988758093137</v>
+        <v>0.3878544651734255</v>
       </c>
       <c r="D567" t="s">
         <v>1144</v>
@@ -13928,7 +13928,7 @@
         <v>1143</v>
       </c>
       <c r="C568">
-        <v>0.4123188325914808</v>
+        <v>0.3785190299297993</v>
       </c>
       <c r="D568" t="s">
         <v>1144</v>
@@ -13945,7 +13945,7 @@
         <v>1143</v>
       </c>
       <c r="C569">
-        <v>0.2575416750384958</v>
+        <v>0.2610385093293637</v>
       </c>
       <c r="D569" t="s">
         <v>1144</v>
@@ -13962,7 +13962,7 @@
         <v>1143</v>
       </c>
       <c r="C570">
-        <v>0.2927625854117862</v>
+        <v>0.2903403652672141</v>
       </c>
       <c r="D570" t="s">
         <v>1144</v>
@@ -13979,7 +13979,7 @@
         <v>1143</v>
       </c>
       <c r="C571">
-        <v>0.2864544627275417</v>
+        <v>0.2820870794123971</v>
       </c>
       <c r="D571" t="s">
         <v>1144</v>
@@ -13993,10 +13993,10 @@
         <v>1162</v>
       </c>
       <c r="B572" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C572">
-        <v>0.2765638921388476</v>
+        <v>0.2641493490006226</v>
       </c>
       <c r="D572" t="s">
         <v>1144</v>
@@ -14013,7 +14013,7 @@
         <v>1143</v>
       </c>
       <c r="C573">
-        <v>0.3414723130279372</v>
+        <v>0.3256046222511845</v>
       </c>
       <c r="D573" t="s">
         <v>1144</v>
@@ -14030,7 +14030,7 @@
         <v>44</v>
       </c>
       <c r="C574">
-        <v>0.3961806163165391</v>
+        <v>0.3348343797963629</v>
       </c>
       <c r="D574" t="s">
         <v>1144</v>
@@ -14047,7 +14047,7 @@
         <v>1143</v>
       </c>
       <c r="C575">
-        <v>0.3732100493008802</v>
+        <v>0.3536324355320439</v>
       </c>
       <c r="D575" t="s">
         <v>1144</v>
@@ -14064,7 +14064,7 @@
         <v>1143</v>
       </c>
       <c r="C576">
-        <v>0.368156664991985</v>
+        <v>0.3733158502191608</v>
       </c>
       <c r="D576" t="s">
         <v>1144</v>
@@ -14081,7 +14081,7 @@
         <v>6</v>
       </c>
       <c r="C577">
-        <v>0.3453925318550689</v>
+        <v>0.2811101845296978</v>
       </c>
       <c r="D577" t="s">
         <v>1144</v>
@@ -14098,7 +14098,7 @@
         <v>1143</v>
       </c>
       <c r="C578">
-        <v>0.3793094642344827</v>
+        <v>0.3719745255145175</v>
       </c>
       <c r="D578" t="s">
         <v>1144</v>
@@ -14115,7 +14115,7 @@
         <v>1143</v>
       </c>
       <c r="C579">
-        <v>0.3250164540827461</v>
+        <v>0.3160187304199947</v>
       </c>
       <c r="D579" t="s">
         <v>1144</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="C580">
-        <v>0.3218620878894965</v>
+        <v>0.3360119635170851</v>
       </c>
       <c r="D580" t="s">
         <v>1144</v>
@@ -14149,7 +14149,7 @@
         <v>1143</v>
       </c>
       <c r="C581">
-        <v>0.4655952976822675</v>
+        <v>0.445412944777631</v>
       </c>
       <c r="D581" t="s">
         <v>1144</v>
@@ -14166,7 +14166,7 @@
         <v>1143</v>
       </c>
       <c r="C582">
-        <v>0.309400385416069</v>
+        <v>0.3063098086398513</v>
       </c>
       <c r="D582" t="s">
         <v>1144</v>
@@ -14183,7 +14183,7 @@
         <v>1143</v>
       </c>
       <c r="C583">
-        <v>0.3658091273568222</v>
+        <v>0.3635717848474762</v>
       </c>
       <c r="D583" t="s">
         <v>1144</v>
@@ -14197,10 +14197,10 @@
         <v>1186</v>
       </c>
       <c r="B584" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C584">
-        <v>0.3042246957161413</v>
+        <v>0.3002970711348133</v>
       </c>
       <c r="D584" t="s">
         <v>1144</v>
@@ -14217,7 +14217,7 @@
         <v>1143</v>
       </c>
       <c r="C585">
-        <v>0.3964013693525566</v>
+        <v>0.4130856176307354</v>
       </c>
       <c r="D585" t="s">
         <v>1144</v>
@@ -14234,7 +14234,7 @@
         <v>1143</v>
       </c>
       <c r="C586">
-        <v>0.2553361711698874</v>
+        <v>0.2955601333560393</v>
       </c>
       <c r="D586" t="s">
         <v>1144</v>
@@ -14251,7 +14251,7 @@
         <v>6</v>
       </c>
       <c r="C587">
-        <v>0.3365768854851884</v>
+        <v>0.2657884407978354</v>
       </c>
       <c r="D587" t="s">
         <v>1144</v>
@@ -14268,7 +14268,7 @@
         <v>1143</v>
       </c>
       <c r="C588">
-        <v>0.3095319197554634</v>
+        <v>0.3209020474018595</v>
       </c>
       <c r="D588" t="s">
         <v>1144</v>
@@ -14285,7 +14285,7 @@
         <v>44</v>
       </c>
       <c r="C589">
-        <v>0.3999095556206499</v>
+        <v>0.3432010424624803</v>
       </c>
       <c r="D589" t="s">
         <v>1144</v>
@@ -14302,7 +14302,7 @@
         <v>6</v>
       </c>
       <c r="C590">
-        <v>0.4607922384138766</v>
+        <v>0.3782102960832002</v>
       </c>
       <c r="D590" t="s">
         <v>1144</v>
@@ -14319,7 +14319,7 @@
         <v>1143</v>
       </c>
       <c r="C591">
-        <v>0.5345850890993862</v>
+        <v>0.5149167389122534</v>
       </c>
       <c r="D591" t="s">
         <v>1144</v>
@@ -14336,7 +14336,7 @@
         <v>1143</v>
       </c>
       <c r="C592">
-        <v>0.376006978002694</v>
+        <v>0.3999254570615111</v>
       </c>
       <c r="D592" t="s">
         <v>1144</v>
@@ -14353,7 +14353,7 @@
         <v>1143</v>
       </c>
       <c r="C593">
-        <v>0.688958893423898</v>
+        <v>0.6546054907356673</v>
       </c>
       <c r="D593" t="s">
         <v>1144</v>
@@ -14370,7 +14370,7 @@
         <v>1143</v>
       </c>
       <c r="C594">
-        <v>0.4497991037722774</v>
+        <v>0.421881100474744</v>
       </c>
       <c r="D594" t="s">
         <v>1144</v>
@@ -14387,7 +14387,7 @@
         <v>6</v>
       </c>
       <c r="C595">
-        <v>0.3464765412091352</v>
+        <v>0.2893270777829852</v>
       </c>
       <c r="D595" t="s">
         <v>1144</v>
@@ -14404,7 +14404,7 @@
         <v>1143</v>
       </c>
       <c r="C596">
-        <v>0.4341918946411915</v>
+        <v>0.4309202091385831</v>
       </c>
       <c r="D596" t="s">
         <v>1144</v>
@@ -14421,7 +14421,7 @@
         <v>6</v>
       </c>
       <c r="C597">
-        <v>0.3776594281121816</v>
+        <v>0.3072839479653566</v>
       </c>
       <c r="D597" t="s">
         <v>1144</v>
@@ -14435,10 +14435,10 @@
         <v>1214</v>
       </c>
       <c r="B598" t="s">
-        <v>1143</v>
+        <v>10</v>
       </c>
       <c r="C598">
-        <v>0.2400237033279259</v>
+        <v>0.2643503276497762</v>
       </c>
       <c r="D598" t="s">
         <v>1144</v>
@@ -14455,7 +14455,7 @@
         <v>1143</v>
       </c>
       <c r="C599">
-        <v>0.2601313329844225</v>
+        <v>0.2653671239648353</v>
       </c>
       <c r="D599" t="s">
         <v>1144</v>
@@ -14472,7 +14472,7 @@
         <v>1143</v>
       </c>
       <c r="C600">
-        <v>0.2768379730721458</v>
+        <v>0.2766118037566316</v>
       </c>
       <c r="D600" t="s">
         <v>1144</v>
@@ -14489,7 +14489,7 @@
         <v>44</v>
       </c>
       <c r="C601">
-        <v>0.2999115762177406</v>
+        <v>0.2575575107338908</v>
       </c>
       <c r="D601" t="s">
         <v>1144</v>
@@ -14506,7 +14506,7 @@
         <v>1143</v>
       </c>
       <c r="C602">
-        <v>0.3822857762486591</v>
+        <v>0.3601994397871477</v>
       </c>
       <c r="D602" t="s">
         <v>1144</v>
@@ -14523,7 +14523,7 @@
         <v>1143</v>
       </c>
       <c r="C603">
-        <v>0.2948640674527304</v>
+        <v>0.2857918691570887</v>
       </c>
       <c r="D603" t="s">
         <v>1144</v>
@@ -14540,7 +14540,7 @@
         <v>6</v>
       </c>
       <c r="C604">
-        <v>0.3686517808429063</v>
+        <v>0.2956869747178931</v>
       </c>
       <c r="D604" t="s">
         <v>1144</v>
@@ -14557,7 +14557,7 @@
         <v>44</v>
       </c>
       <c r="C605">
-        <v>0.3373296272957552</v>
+        <v>0.2910767566783894</v>
       </c>
       <c r="D605" t="s">
         <v>1144</v>
@@ -14571,10 +14571,10 @@
         <v>1230</v>
       </c>
       <c r="B606" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C606">
-        <v>0.3422080186269025</v>
+        <v>0.3433054043710733</v>
       </c>
       <c r="D606" t="s">
         <v>1144</v>
@@ -14591,7 +14591,7 @@
         <v>1143</v>
       </c>
       <c r="C607">
-        <v>0.3345403526847052</v>
+        <v>0.3203248658463223</v>
       </c>
       <c r="D607" t="s">
         <v>1144</v>
@@ -14608,7 +14608,7 @@
         <v>6</v>
       </c>
       <c r="C608">
-        <v>0.3441064726401417</v>
+        <v>0.2826844735431904</v>
       </c>
       <c r="D608" t="s">
         <v>1144</v>
@@ -14622,10 +14622,10 @@
         <v>1236</v>
       </c>
       <c r="B609" t="s">
-        <v>6</v>
+        <v>1143</v>
       </c>
       <c r="C609">
-        <v>0.2994096564544887</v>
+        <v>0.2839017476099238</v>
       </c>
       <c r="D609" t="s">
         <v>1144</v>
@@ -14639,10 +14639,10 @@
         <v>1238</v>
       </c>
       <c r="B610" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C610">
-        <v>0.2556612526815089</v>
+        <v>0.2568324677155133</v>
       </c>
       <c r="D610" t="s">
         <v>1144</v>
@@ -14659,7 +14659,7 @@
         <v>44</v>
       </c>
       <c r="C611">
-        <v>0.5878903570299606</v>
+        <v>0.4932283477385989</v>
       </c>
       <c r="D611" t="s">
         <v>1144</v>
@@ -14676,7 +14676,7 @@
         <v>44</v>
       </c>
       <c r="C612">
-        <v>0.3478722290239945</v>
+        <v>0.3185129587012323</v>
       </c>
       <c r="D612" t="s">
         <v>1144</v>
@@ -14693,7 +14693,7 @@
         <v>1143</v>
       </c>
       <c r="C613">
-        <v>0.3441152500678243</v>
+        <v>0.3358444234132744</v>
       </c>
       <c r="D613" t="s">
         <v>1144</v>
@@ -14710,7 +14710,7 @@
         <v>1143</v>
       </c>
       <c r="C614">
-        <v>0.4545700294234872</v>
+        <v>0.4226347338818509</v>
       </c>
       <c r="D614" t="s">
         <v>1144</v>
@@ -14727,7 +14727,7 @@
         <v>1143</v>
       </c>
       <c r="C615">
-        <v>0.3388664958290554</v>
+        <v>0.3239562368962526</v>
       </c>
       <c r="D615" t="s">
         <v>1144</v>
@@ -14744,7 +14744,7 @@
         <v>1143</v>
       </c>
       <c r="C616">
-        <v>0.4337485429436427</v>
+        <v>0.4198850082605873</v>
       </c>
       <c r="D616" t="s">
         <v>1144</v>
@@ -14761,7 +14761,7 @@
         <v>1143</v>
       </c>
       <c r="C617">
-        <v>0.3324328559091356</v>
+        <v>0.3287888799128681</v>
       </c>
       <c r="D617" t="s">
         <v>1144</v>
@@ -14778,7 +14778,7 @@
         <v>10</v>
       </c>
       <c r="C618">
-        <v>0.3244921720352588</v>
+        <v>0.3388935145720513</v>
       </c>
       <c r="D618" t="s">
         <v>1144</v>
@@ -14795,7 +14795,7 @@
         <v>1143</v>
       </c>
       <c r="C619">
-        <v>0.4443447212557739</v>
+        <v>0.4474680767318405</v>
       </c>
       <c r="D619" t="s">
         <v>1144</v>
@@ -14809,10 +14809,10 @@
         <v>1258</v>
       </c>
       <c r="B620" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C620">
-        <v>0.2795719529751234</v>
+        <v>0.3103262638019842</v>
       </c>
       <c r="D620" t="s">
         <v>1259</v>
@@ -14826,10 +14826,10 @@
         <v>1261</v>
       </c>
       <c r="B621" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C621">
-        <v>0.3742407893655519</v>
+        <v>0.3517174321394096</v>
       </c>
       <c r="D621" t="s">
         <v>1259</v>
@@ -14843,10 +14843,10 @@
         <v>1263</v>
       </c>
       <c r="B622" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C622">
-        <v>0.2564627320476451</v>
+        <v>0.2763164365921594</v>
       </c>
       <c r="D622" t="s">
         <v>1259</v>
@@ -14860,78 +14860,78 @@
         <v>1265</v>
       </c>
       <c r="B623" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C623">
-        <v>0.2566706329475214</v>
+        <v>0.2051685561264937</v>
       </c>
       <c r="D623" t="s">
         <v>1259</v>
       </c>
       <c r="E623" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="624" spans="1:5">
       <c r="A624" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B624" t="s">
         <v>10</v>
       </c>
       <c r="C624">
-        <v>0.3128997512260232</v>
+        <v>0.2879745060480216</v>
       </c>
       <c r="D624" t="s">
         <v>1259</v>
       </c>
       <c r="E624" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="625" spans="1:5">
       <c r="A625" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B625" t="s">
-        <v>1266</v>
+        <v>10</v>
       </c>
       <c r="C625">
-        <v>0.2748091567765434</v>
+        <v>0.2413900098314504</v>
       </c>
       <c r="D625" t="s">
         <v>1259</v>
       </c>
       <c r="E625" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="626" spans="1:5">
       <c r="A626" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B626" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C626">
-        <v>0.3112103199952198</v>
+        <v>0.3296459813913543</v>
       </c>
       <c r="D626" t="s">
         <v>1259</v>
       </c>
       <c r="E626" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="627" spans="1:5">
       <c r="A627" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B627" t="s">
         <v>1274</v>
       </c>
-      <c r="B627" t="s">
-        <v>1266</v>
-      </c>
       <c r="C627">
-        <v>0.3819487650301643</v>
+        <v>0.2872692036229879</v>
       </c>
       <c r="D627" t="s">
         <v>1259</v>
@@ -14945,10 +14945,10 @@
         <v>1276</v>
       </c>
       <c r="B628" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C628">
-        <v>0.2625010223874499</v>
+        <v>0.2314055745918312</v>
       </c>
       <c r="D628" t="s">
         <v>1259</v>
@@ -14962,10 +14962,10 @@
         <v>1278</v>
       </c>
       <c r="B629" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C629">
-        <v>0.2453476357168148</v>
+        <v>0.2748846175584413</v>
       </c>
       <c r="D629" t="s">
         <v>1259</v>
@@ -14979,10 +14979,10 @@
         <v>1280</v>
       </c>
       <c r="B630" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C630">
-        <v>0.4029975429706738</v>
+        <v>0.3245024137787719</v>
       </c>
       <c r="D630" t="s">
         <v>1259</v>
@@ -14996,10 +14996,10 @@
         <v>1282</v>
       </c>
       <c r="B631" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C631">
-        <v>0.4256233767885871</v>
+        <v>0.3217051287089363</v>
       </c>
       <c r="D631" t="s">
         <v>1259</v>
@@ -15013,10 +15013,10 @@
         <v>1284</v>
       </c>
       <c r="B632" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C632">
-        <v>0.4787045911536497</v>
+        <v>0.3884712724139645</v>
       </c>
       <c r="D632" t="s">
         <v>1259</v>
@@ -15030,10 +15030,10 @@
         <v>1286</v>
       </c>
       <c r="B633" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C633">
-        <v>0.264681346461473</v>
+        <v>0.2755014677711954</v>
       </c>
       <c r="D633" t="s">
         <v>1259</v>
@@ -15047,10 +15047,10 @@
         <v>1288</v>
       </c>
       <c r="B634" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C634">
-        <v>0.4505297611403773</v>
+        <v>0.4046882516639836</v>
       </c>
       <c r="D634" t="s">
         <v>1259</v>
@@ -15064,10 +15064,10 @@
         <v>1290</v>
       </c>
       <c r="B635" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C635">
-        <v>0.4931683103110366</v>
+        <v>0.4262261506414409</v>
       </c>
       <c r="D635" t="s">
         <v>1259</v>
@@ -15084,7 +15084,7 @@
         <v>6</v>
       </c>
       <c r="C636">
-        <v>0.3499541453003878</v>
+        <v>0.397089827114733</v>
       </c>
       <c r="D636" t="s">
         <v>1259</v>
@@ -15098,10 +15098,10 @@
         <v>1294</v>
       </c>
       <c r="B637" t="s">
-        <v>1266</v>
+        <v>21</v>
       </c>
       <c r="C637">
-        <v>0.360107153665462</v>
+        <v>0.2861422063946156</v>
       </c>
       <c r="D637" t="s">
         <v>1259</v>
@@ -15115,10 +15115,10 @@
         <v>1296</v>
       </c>
       <c r="B638" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C638">
-        <v>0.5425953501478241</v>
+        <v>0.4243569174024859</v>
       </c>
       <c r="D638" t="s">
         <v>1259</v>
@@ -15135,7 +15135,7 @@
         <v>10</v>
       </c>
       <c r="C639">
-        <v>0.3917239599328542</v>
+        <v>0.3456234524523228</v>
       </c>
       <c r="D639" t="s">
         <v>1259</v>
@@ -15152,7 +15152,7 @@
         <v>10</v>
       </c>
       <c r="C640">
-        <v>0.3156642539070019</v>
+        <v>0.2827074096447414</v>
       </c>
       <c r="D640" t="s">
         <v>1259</v>
@@ -15166,10 +15166,10 @@
         <v>1302</v>
       </c>
       <c r="B641" t="s">
-        <v>1266</v>
+        <v>21</v>
       </c>
       <c r="C641">
-        <v>0.275282865843146</v>
+        <v>0.2676778266051627</v>
       </c>
       <c r="D641" t="s">
         <v>1259</v>
@@ -15183,10 +15183,10 @@
         <v>1304</v>
       </c>
       <c r="B642" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="C642">
-        <v>0.3678489336470355</v>
+        <v>0.2823052881174334</v>
       </c>
       <c r="D642" t="s">
         <v>1259</v>
@@ -15200,10 +15200,10 @@
         <v>1306</v>
       </c>
       <c r="B643" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C643">
-        <v>0.3170130638659789</v>
+        <v>0.3009756777174654</v>
       </c>
       <c r="D643" t="s">
         <v>1259</v>
@@ -15217,10 +15217,10 @@
         <v>1308</v>
       </c>
       <c r="B644" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C644">
-        <v>0.284441630395121</v>
+        <v>0.2825709909325185</v>
       </c>
       <c r="D644" t="s">
         <v>1259</v>
@@ -15234,10 +15234,10 @@
         <v>1310</v>
       </c>
       <c r="B645" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C645">
-        <v>0.2344201201127299</v>
+        <v>0.2547040325152728</v>
       </c>
       <c r="D645" t="s">
         <v>1259</v>
@@ -15251,10 +15251,10 @@
         <v>1312</v>
       </c>
       <c r="B646" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C646">
-        <v>0.3853974450695236</v>
+        <v>0.3633072581384469</v>
       </c>
       <c r="D646" t="s">
         <v>1259</v>
@@ -15268,10 +15268,10 @@
         <v>1314</v>
       </c>
       <c r="B647" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C647">
-        <v>0.2963363725264956</v>
+        <v>0.2888882344965392</v>
       </c>
       <c r="D647" t="s">
         <v>1259</v>
@@ -15285,10 +15285,10 @@
         <v>1316</v>
       </c>
       <c r="B648" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C648">
-        <v>0.2706524357275279</v>
+        <v>0.2816247240909214</v>
       </c>
       <c r="D648" t="s">
         <v>1259</v>
@@ -15302,10 +15302,10 @@
         <v>1318</v>
       </c>
       <c r="B649" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C649">
-        <v>0.3503241214132245</v>
+        <v>0.3279846474748161</v>
       </c>
       <c r="D649" t="s">
         <v>1259</v>
@@ -15319,10 +15319,10 @@
         <v>1320</v>
       </c>
       <c r="B650" t="s">
-        <v>1266</v>
+        <v>6</v>
       </c>
       <c r="C650">
-        <v>0.31707139138557</v>
+        <v>0.2631124095058909</v>
       </c>
       <c r="D650" t="s">
         <v>1259</v>
@@ -15336,10 +15336,10 @@
         <v>1322</v>
       </c>
       <c r="B651" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C651">
-        <v>0.2982426608190498</v>
+        <v>0.3089563909095435</v>
       </c>
       <c r="D651" t="s">
         <v>1259</v>
@@ -15368,10 +15368,10 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -15379,15 +15379,15 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>123</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>240</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -15403,7 +15403,7 @@
         <v>44</v>
       </c>
       <c r="B6">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -15411,15 +15411,15 @@
         <v>226</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>1266</v>
+        <v>1274</v>
       </c>
       <c r="B8">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -15427,7 +15427,7 @@
         <v>1143</v>
       </c>
       <c r="B9">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/frontend/data/uk_election_predictions.xlsx
+++ b/frontend/data/uk_election_predictions.xlsx
@@ -284,6 +284,9 @@
     <t>blackburn</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>E14001102</t>
   </si>
   <si>
@@ -693,9 +696,6 @@
   </si>
   <si>
     <t>chorley</t>
-  </si>
-  <si>
-    <t>Other</t>
   </si>
   <si>
     <t>E14001170</t>
@@ -4360,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.3016269068473654</v>
+        <v>0.2992016916259801</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -4377,7 +4377,7 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>0.4401623243779999</v>
+        <v>0.4403099988221427</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -4394,7 +4394,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>0.4167480359904406</v>
+        <v>0.4165480473830924</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -4411,7 +4411,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>0.3085380935059038</v>
+        <v>0.3090125413913826</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.3858216852295178</v>
+        <v>0.3850073850334624</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -4445,7 +4445,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>0.2969903404013247</v>
+        <v>0.2985908716928136</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -4462,7 +4462,7 @@
         <v>21</v>
       </c>
       <c r="C8">
-        <v>0.3069443243978868</v>
+        <v>0.3060269384178722</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -4479,7 +4479,7 @@
         <v>21</v>
       </c>
       <c r="C9">
-        <v>0.2903359951279176</v>
+        <v>0.2922075808692468</v>
       </c>
       <c r="D9" t="s">
         <v>7</v>
@@ -4496,7 +4496,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.3604244458439821</v>
+        <v>0.3607636501683353</v>
       </c>
       <c r="D10" t="s">
         <v>7</v>
@@ -4513,7 +4513,7 @@
         <v>6</v>
       </c>
       <c r="C11">
-        <v>0.2449683177961995</v>
+        <v>0.2426467827255835</v>
       </c>
       <c r="D11" t="s">
         <v>7</v>
@@ -4530,7 +4530,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>0.4058376615803914</v>
+        <v>0.408626721008862</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -4547,7 +4547,7 @@
         <v>21</v>
       </c>
       <c r="C13">
-        <v>0.2970034344603001</v>
+        <v>0.298761697081352</v>
       </c>
       <c r="D13" t="s">
         <v>7</v>
@@ -4564,7 +4564,7 @@
         <v>21</v>
       </c>
       <c r="C14">
-        <v>0.351900739544562</v>
+        <v>0.3510460032961505</v>
       </c>
       <c r="D14" t="s">
         <v>7</v>
@@ -4581,7 +4581,7 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>0.352408713762176</v>
+        <v>0.350275292558505</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -4598,7 +4598,7 @@
         <v>6</v>
       </c>
       <c r="C16">
-        <v>0.3112351985615457</v>
+        <v>0.3116195820956034</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -4615,7 +4615,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <v>0.3065976760963816</v>
+        <v>0.3065806973096449</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>0.333212898456059</v>
+        <v>0.3335603771548845</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -4649,7 +4649,7 @@
         <v>44</v>
       </c>
       <c r="C19">
-        <v>0.4361284057590889</v>
+        <v>0.437400747986217</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -4666,7 +4666,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0.4204931814127174</v>
+        <v>0.4208848292845027</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -4683,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.4405539608734234</v>
+        <v>0.4424325880297209</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -4700,7 +4700,7 @@
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0.3361489841799629</v>
+        <v>0.3371710101354458</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -4717,7 +4717,7 @@
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0.3947483598439713</v>
+        <v>0.3939261021441285</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -4734,7 +4734,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>0.3466696064213628</v>
+        <v>0.3492172912295869</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -4751,7 +4751,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>0.6155356369540657</v>
+        <v>0.6180511168319922</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -4768,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C26">
-        <v>0.3295551908873148</v>
+        <v>0.3291667718293597</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="C27">
-        <v>0.3012277515027705</v>
+        <v>0.301248388322216</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -4802,7 +4802,7 @@
         <v>10</v>
       </c>
       <c r="C28">
-        <v>0.3262327534250096</v>
+        <v>0.3257481849214497</v>
       </c>
       <c r="D28" t="s">
         <v>7</v>
@@ -4819,7 +4819,7 @@
         <v>44</v>
       </c>
       <c r="C29">
-        <v>0.4618654014443809</v>
+        <v>0.4626854508938525</v>
       </c>
       <c r="D29" t="s">
         <v>7</v>
@@ -4836,7 +4836,7 @@
         <v>6</v>
       </c>
       <c r="C30">
-        <v>0.3942316842809056</v>
+        <v>0.396261249586678</v>
       </c>
       <c r="D30" t="s">
         <v>7</v>
@@ -4853,7 +4853,7 @@
         <v>6</v>
       </c>
       <c r="C31">
-        <v>0.4533077506566369</v>
+        <v>0.4565580191486939</v>
       </c>
       <c r="D31" t="s">
         <v>7</v>
@@ -4870,7 +4870,7 @@
         <v>21</v>
       </c>
       <c r="C32">
-        <v>0.3854482013542957</v>
+        <v>0.3862080244982722</v>
       </c>
       <c r="D32" t="s">
         <v>7</v>
@@ -4887,7 +4887,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>0.4063664073262408</v>
+        <v>0.4140063240855956</v>
       </c>
       <c r="D33" t="s">
         <v>7</v>
@@ -4904,7 +4904,7 @@
         <v>21</v>
       </c>
       <c r="C34">
-        <v>0.3459156384426002</v>
+        <v>0.351141850126979</v>
       </c>
       <c r="D34" t="s">
         <v>7</v>
@@ -4921,7 +4921,7 @@
         <v>6</v>
       </c>
       <c r="C35">
-        <v>0.4717754394573599</v>
+        <v>0.4782865998132924</v>
       </c>
       <c r="D35" t="s">
         <v>7</v>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>0.244986401557798</v>
+        <v>0.2461402966833036</v>
       </c>
       <c r="D36" t="s">
         <v>7</v>
@@ -4955,7 +4955,7 @@
         <v>21</v>
       </c>
       <c r="C37">
-        <v>0.2753666580754036</v>
+        <v>0.2616708268214478</v>
       </c>
       <c r="D37" t="s">
         <v>7</v>
@@ -4972,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>0.3348008672778034</v>
+        <v>0.3342035059170371</v>
       </c>
       <c r="D38" t="s">
         <v>7</v>
@@ -4989,7 +4989,7 @@
         <v>21</v>
       </c>
       <c r="C39">
-        <v>0.3219178470779564</v>
+        <v>0.3259073539013843</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -5006,7 +5006,7 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0.5063553232724664</v>
+        <v>0.5064485578391427</v>
       </c>
       <c r="D40" t="s">
         <v>7</v>
@@ -5020,1166 +5020,1166 @@
         <v>88</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C41">
-        <v>0.2430329685497141</v>
+        <v>0.2640793592119803</v>
       </c>
       <c r="D41" t="s">
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0.5314891180116685</v>
+        <v>0.5288255365113376</v>
       </c>
       <c r="D42" t="s">
         <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B43" t="s">
         <v>21</v>
       </c>
       <c r="C43">
-        <v>0.3869515198907192</v>
+        <v>0.3851995902520957</v>
       </c>
       <c r="D43" t="s">
         <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B44" t="s">
         <v>21</v>
       </c>
       <c r="C44">
-        <v>0.3892888345429857</v>
+        <v>0.388265275246559</v>
       </c>
       <c r="D44" t="s">
         <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0.4148548414642107</v>
+        <v>0.4135804206760313</v>
       </c>
       <c r="D45" t="s">
         <v>7</v>
       </c>
       <c r="E45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0.4256362711393673</v>
+        <v>0.4246034296441654</v>
       </c>
       <c r="D46" t="s">
         <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" t="s">
         <v>21</v>
       </c>
       <c r="C47">
-        <v>0.3117196430688026</v>
+        <v>0.3105572605203638</v>
       </c>
       <c r="D47" t="s">
         <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
         <v>21</v>
       </c>
       <c r="C48">
-        <v>0.3910441824895293</v>
+        <v>0.3903923911452406</v>
       </c>
       <c r="D48" t="s">
         <v>7</v>
       </c>
       <c r="E48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B49" t="s">
         <v>21</v>
       </c>
       <c r="C49">
-        <v>0.3756637158880926</v>
+        <v>0.3752860040075873</v>
       </c>
       <c r="D49" t="s">
         <v>7</v>
       </c>
       <c r="E49" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B50" t="s">
         <v>21</v>
       </c>
       <c r="C50">
-        <v>0.3289263434399722</v>
+        <v>0.3292741976755496</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B51" t="s">
         <v>6</v>
       </c>
       <c r="C51">
-        <v>0.3348965287860602</v>
+        <v>0.3341769382547507</v>
       </c>
       <c r="D51" t="s">
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
         <v>6</v>
       </c>
       <c r="C52">
-        <v>0.4985539416510877</v>
+        <v>0.4991071584438536</v>
       </c>
       <c r="D52" t="s">
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
         <v>21</v>
       </c>
       <c r="C53">
-        <v>0.4130679180370659</v>
+        <v>0.4219675524376348</v>
       </c>
       <c r="D53" t="s">
         <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B54" t="s">
         <v>6</v>
       </c>
       <c r="C54">
-        <v>0.3859700199665738</v>
+        <v>0.3863166042553711</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
       </c>
       <c r="E54" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
       </c>
       <c r="C55">
-        <v>0.2839677029858616</v>
+        <v>0.2839617145525681</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
         <v>10</v>
       </c>
       <c r="C56">
-        <v>0.3840445098692734</v>
+        <v>0.3843420121634731</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
       </c>
       <c r="E56" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
       </c>
       <c r="C57">
-        <v>0.5692292577464846</v>
+        <v>0.5702290235044584</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
       </c>
       <c r="E57" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B58" t="s">
         <v>6</v>
       </c>
       <c r="C58">
-        <v>0.3229618445670541</v>
+        <v>0.3262393282672987</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
       </c>
       <c r="E58" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B59" t="s">
         <v>6</v>
       </c>
       <c r="C59">
-        <v>0.3912685901161844</v>
+        <v>0.4022009259147491</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
       </c>
       <c r="E59" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B60" t="s">
         <v>6</v>
       </c>
       <c r="C60">
-        <v>0.3189254907421513</v>
+        <v>0.3179714017000879</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B61" t="s">
         <v>6</v>
       </c>
       <c r="C61">
-        <v>0.4050574537420344</v>
+        <v>0.4054022017963776</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
       </c>
       <c r="C62">
-        <v>0.3403123823237811</v>
+        <v>0.3372937501674798</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
       </c>
       <c r="E62" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B63" t="s">
         <v>6</v>
       </c>
       <c r="C63">
-        <v>0.4035046155263314</v>
+        <v>0.4037762681466596</v>
       </c>
       <c r="D63" t="s">
         <v>7</v>
       </c>
       <c r="E63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B64" t="s">
         <v>44</v>
       </c>
       <c r="C64">
-        <v>0.234224002238754</v>
+        <v>0.2339069353130219</v>
       </c>
       <c r="D64" t="s">
         <v>7</v>
       </c>
       <c r="E64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B65" t="s">
         <v>21</v>
       </c>
       <c r="C65">
-        <v>0.31890047306172</v>
+        <v>0.3168816331239765</v>
       </c>
       <c r="D65" t="s">
         <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
       </c>
       <c r="C66">
-        <v>0.3169432919486969</v>
+        <v>0.3175050143030398</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
       </c>
       <c r="E66" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B67" t="s">
         <v>21</v>
       </c>
       <c r="C67">
-        <v>0.3077255338452973</v>
+        <v>0.3068340844684425</v>
       </c>
       <c r="D67" t="s">
         <v>7</v>
       </c>
       <c r="E67" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B68" t="s">
         <v>6</v>
       </c>
       <c r="C68">
-        <v>0.2857336115773473</v>
+        <v>0.2855501813490541</v>
       </c>
       <c r="D68" t="s">
         <v>7</v>
       </c>
       <c r="E68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C69">
-        <v>0.5546153421658755</v>
+        <v>0.5465949865949986</v>
       </c>
       <c r="D69" t="s">
         <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C70">
-        <v>0.5230811004264685</v>
+        <v>0.5166059469832697</v>
       </c>
       <c r="D70" t="s">
         <v>7</v>
       </c>
       <c r="E70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" t="s">
         <v>6</v>
       </c>
       <c r="C71">
-        <v>0.5019592056601719</v>
+        <v>0.5045031016596895</v>
       </c>
       <c r="D71" t="s">
         <v>7</v>
       </c>
       <c r="E71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
         <v>6</v>
       </c>
       <c r="C72">
-        <v>0.3584282879379614</v>
+        <v>0.3579133658392883</v>
       </c>
       <c r="D72" t="s">
         <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B73" t="s">
         <v>6</v>
       </c>
       <c r="C73">
-        <v>0.5037426176914016</v>
+        <v>0.5019976943388257</v>
       </c>
       <c r="D73" t="s">
         <v>7</v>
       </c>
       <c r="E73" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B74" t="s">
         <v>6</v>
       </c>
       <c r="C74">
-        <v>0.5115694222808229</v>
+        <v>0.5120203643762891</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B75" t="s">
         <v>10</v>
       </c>
       <c r="C75">
-        <v>0.2849954159121715</v>
+        <v>0.2854272138703015</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B76" t="s">
         <v>10</v>
       </c>
       <c r="C76">
-        <v>0.3691329508663614</v>
+        <v>0.3693854688494686</v>
       </c>
       <c r="D76" t="s">
         <v>7</v>
       </c>
       <c r="E76" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
       </c>
       <c r="C77">
-        <v>0.3107703785791928</v>
+        <v>0.3121805915480067</v>
       </c>
       <c r="D77" t="s">
         <v>7</v>
       </c>
       <c r="E77" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B78" t="s">
         <v>10</v>
       </c>
       <c r="C78">
-        <v>0.4087340540975026</v>
+        <v>0.4077279690985286</v>
       </c>
       <c r="D78" t="s">
         <v>7</v>
       </c>
       <c r="E78" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B79" t="s">
         <v>10</v>
       </c>
       <c r="C79">
-        <v>0.2608309980184269</v>
+        <v>0.2618459797068338</v>
       </c>
       <c r="D79" t="s">
         <v>7</v>
       </c>
       <c r="E79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B80" t="s">
         <v>10</v>
       </c>
       <c r="C80">
-        <v>0.3655552628102874</v>
+        <v>0.3641544954896443</v>
       </c>
       <c r="D80" t="s">
         <v>7</v>
       </c>
       <c r="E80" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
         <v>21</v>
       </c>
       <c r="C81">
-        <v>0.2918808017793055</v>
+        <v>0.2923156797733676</v>
       </c>
       <c r="D81" t="s">
         <v>7</v>
       </c>
       <c r="E81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B82" t="s">
         <v>10</v>
       </c>
       <c r="C82">
-        <v>0.4269281090389851</v>
+        <v>0.4271441342657181</v>
       </c>
       <c r="D82" t="s">
         <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B83" t="s">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>0.3927810700698774</v>
+        <v>0.3923979499348195</v>
       </c>
       <c r="D83" t="s">
         <v>7</v>
       </c>
       <c r="E83" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B84" t="s">
         <v>10</v>
       </c>
       <c r="C84">
-        <v>0.3089532099622869</v>
+        <v>0.3064950964614544</v>
       </c>
       <c r="D84" t="s">
         <v>7</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B85" t="s">
         <v>21</v>
       </c>
       <c r="C85">
-        <v>0.3226022680599834</v>
+        <v>0.321183960992183</v>
       </c>
       <c r="D85" t="s">
         <v>7</v>
       </c>
       <c r="E85" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>0.3062774014142624</v>
+        <v>0.3056929616285791</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
       </c>
       <c r="E86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
       </c>
       <c r="C87">
-        <v>0.2830761858640501</v>
+        <v>0.2837086280524186</v>
       </c>
       <c r="D87" t="s">
         <v>7</v>
       </c>
       <c r="E87" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B88" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C88">
-        <v>0.3289382328019479</v>
+        <v>0.3270196561432928</v>
       </c>
       <c r="D88" t="s">
         <v>7</v>
       </c>
       <c r="E88" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s">
         <v>10</v>
       </c>
       <c r="C89">
-        <v>0.3397001059854333</v>
+        <v>0.3400070807153096</v>
       </c>
       <c r="D89" t="s">
         <v>7</v>
       </c>
       <c r="E89" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B90" t="s">
         <v>10</v>
       </c>
       <c r="C90">
-        <v>0.3097598455852941</v>
+        <v>0.3151631481228533</v>
       </c>
       <c r="D90" t="s">
         <v>7</v>
       </c>
       <c r="E90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B91" t="s">
         <v>10</v>
       </c>
       <c r="C91">
-        <v>0.3105198274340028</v>
+        <v>0.3113320078290504</v>
       </c>
       <c r="D91" t="s">
         <v>7</v>
       </c>
       <c r="E91" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B92" t="s">
         <v>44</v>
       </c>
       <c r="C92">
-        <v>0.2913309921960212</v>
+        <v>0.2880281577610389</v>
       </c>
       <c r="D92" t="s">
         <v>7</v>
       </c>
       <c r="E92" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
         <v>21</v>
       </c>
       <c r="C93">
-        <v>0.3668994210798103</v>
+        <v>0.3655249767940006</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
       </c>
       <c r="E93" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B94" t="s">
         <v>44</v>
       </c>
       <c r="C94">
-        <v>0.26292066563484</v>
+        <v>0.2659922590162547</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
       </c>
       <c r="E94" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s">
         <v>21</v>
       </c>
       <c r="C95">
-        <v>0.3343796937535661</v>
+        <v>0.3339795312568526</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
       </c>
       <c r="E95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B96" t="s">
         <v>21</v>
       </c>
       <c r="C96">
-        <v>0.3489391872080709</v>
+        <v>0.3476077317074128</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
       </c>
       <c r="E96" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B97" t="s">
         <v>44</v>
       </c>
       <c r="C97">
-        <v>0.3375203935277251</v>
+        <v>0.3343195447186941</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B98" t="s">
         <v>44</v>
       </c>
       <c r="C98">
-        <v>0.359616784373201</v>
+        <v>0.3576031572230955</v>
       </c>
       <c r="D98" t="s">
         <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B99" t="s">
         <v>6</v>
       </c>
       <c r="C99">
-        <v>0.4357319983163068</v>
+        <v>0.4362794314931161</v>
       </c>
       <c r="D99" t="s">
         <v>7</v>
       </c>
       <c r="E99" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B100" t="s">
         <v>44</v>
       </c>
       <c r="C100">
-        <v>0.359974636848084</v>
+        <v>0.3577398452618203</v>
       </c>
       <c r="D100" t="s">
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B101" t="s">
         <v>44</v>
       </c>
       <c r="C101">
-        <v>0.4214833441594282</v>
+        <v>0.4224383696893158</v>
       </c>
       <c r="D101" t="s">
         <v>7</v>
       </c>
       <c r="E101" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B102" t="s">
         <v>6</v>
       </c>
       <c r="C102">
-        <v>0.4652757612083137</v>
+        <v>0.463935182088512</v>
       </c>
       <c r="D102" t="s">
         <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B103" t="s">
         <v>6</v>
       </c>
       <c r="C103">
-        <v>0.3530649482448727</v>
+        <v>0.3543644860041995</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
       </c>
       <c r="E103" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B104" t="s">
         <v>21</v>
       </c>
       <c r="C104">
-        <v>0.3821389719935503</v>
+        <v>0.3818463474223155</v>
       </c>
       <c r="D104" t="s">
         <v>7</v>
       </c>
       <c r="E104" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B105" t="s">
         <v>44</v>
       </c>
       <c r="C105">
-        <v>0.3505029991496064</v>
+        <v>0.3468906883129295</v>
       </c>
       <c r="D105" t="s">
         <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B106" t="s">
         <v>10</v>
       </c>
       <c r="C106">
-        <v>0.3713441568876497</v>
+        <v>0.3684446967595133</v>
       </c>
       <c r="D106" t="s">
         <v>7</v>
       </c>
       <c r="E106" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B107" t="s">
         <v>44</v>
       </c>
       <c r="C107">
-        <v>0.3445979453685457</v>
+        <v>0.3420926654464426</v>
       </c>
       <c r="D107" t="s">
         <v>7</v>
       </c>
       <c r="E107" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B108" t="s">
         <v>6</v>
       </c>
       <c r="C108">
-        <v>0.4147911036405842</v>
+        <v>0.4153235506827143</v>
       </c>
       <c r="D108" t="s">
         <v>7</v>
       </c>
       <c r="E108" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B109" t="s">
-        <v>226</v>
+        <v>6</v>
       </c>
       <c r="C109">
-        <v>0.2762897902410033</v>
+        <v>0.23986652346373</v>
       </c>
       <c r="D109" t="s">
         <v>7</v>
@@ -6196,7 +6196,7 @@
         <v>21</v>
       </c>
       <c r="C110">
-        <v>0.2822896167131076</v>
+        <v>0.2827492007464284</v>
       </c>
       <c r="D110" t="s">
         <v>7</v>
@@ -6213,7 +6213,7 @@
         <v>6</v>
       </c>
       <c r="C111">
-        <v>0.5044050663137096</v>
+        <v>0.5051963114747311</v>
       </c>
       <c r="D111" t="s">
         <v>7</v>
@@ -6230,7 +6230,7 @@
         <v>6</v>
       </c>
       <c r="C112">
-        <v>0.3838963550319209</v>
+        <v>0.3840774139835985</v>
       </c>
       <c r="D112" t="s">
         <v>7</v>
@@ -6247,7 +6247,7 @@
         <v>21</v>
       </c>
       <c r="C113">
-        <v>0.4732395833986455</v>
+        <v>0.477392251816065</v>
       </c>
       <c r="D113" t="s">
         <v>7</v>
@@ -6264,7 +6264,7 @@
         <v>6</v>
       </c>
       <c r="C114">
-        <v>0.6474976021206573</v>
+        <v>0.6486258645033915</v>
       </c>
       <c r="D114" t="s">
         <v>7</v>
@@ -6281,7 +6281,7 @@
         <v>6</v>
       </c>
       <c r="C115">
-        <v>0.2979308396707486</v>
+        <v>0.2977897413126597</v>
       </c>
       <c r="D115" t="s">
         <v>7</v>
@@ -6298,7 +6298,7 @@
         <v>6</v>
       </c>
       <c r="C116">
-        <v>0.4457092750558775</v>
+        <v>0.4466145873930153</v>
       </c>
       <c r="D116" t="s">
         <v>7</v>
@@ -6315,7 +6315,7 @@
         <v>6</v>
       </c>
       <c r="C117">
-        <v>0.2973115484591263</v>
+        <v>0.2961709750348395</v>
       </c>
       <c r="D117" t="s">
         <v>7</v>
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="C118">
-        <v>0.3879167096456849</v>
+        <v>0.3887188030525952</v>
       </c>
       <c r="D118" t="s">
         <v>7</v>
@@ -6349,7 +6349,7 @@
         <v>6</v>
       </c>
       <c r="C119">
-        <v>0.3830684436257644</v>
+        <v>0.3836643228702267</v>
       </c>
       <c r="D119" t="s">
         <v>7</v>
@@ -6366,7 +6366,7 @@
         <v>10</v>
       </c>
       <c r="C120">
-        <v>0.3625172705926554</v>
+        <v>0.3643626311021009</v>
       </c>
       <c r="D120" t="s">
         <v>7</v>
@@ -6380,10 +6380,10 @@
         <v>250</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="C121">
-        <v>0.2704350065374589</v>
+        <v>0.2695339986182627</v>
       </c>
       <c r="D121" t="s">
         <v>7</v>
@@ -6400,7 +6400,7 @@
         <v>21</v>
       </c>
       <c r="C122">
-        <v>0.306793430295135</v>
+        <v>0.3049623720759969</v>
       </c>
       <c r="D122" t="s">
         <v>7</v>
@@ -6417,7 +6417,7 @@
         <v>21</v>
       </c>
       <c r="C123">
-        <v>0.314174590373792</v>
+        <v>0.3133210416261658</v>
       </c>
       <c r="D123" t="s">
         <v>7<